--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -8,32 +8,33 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공정매뉴얼" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사전토공사" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지장물이설" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상부강화노반" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콘크리트도상" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건축" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신호" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전기" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIDE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지반조사" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사전토공사" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지장물이설" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상부강화노반" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콘크리트도상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건축" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신호" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전기" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIDE" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'공정매뉴얼'!$A$3:$P$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'공정매뉴얼'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'공정매뉴얼'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'사전토공사'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'사전토공사'!$A$1:$Q$31</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'지장물이설'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'지장물이설'!$A$1:$Q$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'상부강화노반'!$A$1:$Q$37</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'콘크리트도상'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'콘크리트도상'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'건축'!$A$1:$P$51</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'신호'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'신호'!$A$1:$P$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'통신'!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'전기'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'사전토공사'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'사전토공사'!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'지장물이설'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'지장물이설'!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'상부강화노반'!$A$1:$Q$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'콘크리트도상'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'콘크리트도상'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'건축'!$A$1:$P$51</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'신호'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'신호'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'통신'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'전기'!$A$1:$P$33</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +45,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -250,8 +251,25 @@
       <color rgb="00FFFFFF"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -333,8 +351,32 @@
         <bgColor rgb="00D97706"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7ED"/>
+        <bgColor rgb="00FFF7ED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -602,11 +644,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -954,6 +1029,102 @@
     <xf numFmtId="0" fontId="28" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1343,17 +1514,17 @@
           <t>동탄트램 집행단계 실무 매뉴얼 &amp; 지식 DB 작성 현황 대시보드</t>
         </is>
       </c>
-      <c r="C2" s="101" t="n"/>
-      <c r="D2" s="101" t="n"/>
-      <c r="E2" s="101" t="n"/>
-      <c r="F2" s="101" t="n"/>
-      <c r="G2" s="101" t="n"/>
-      <c r="H2" s="101" t="n"/>
-      <c r="I2" s="101" t="n"/>
-      <c r="J2" s="101" t="n"/>
-      <c r="K2" s="101" t="n"/>
-      <c r="L2" s="101" t="n"/>
-      <c r="M2" s="101" t="n"/>
+      <c r="C2" s="123" t="n"/>
+      <c r="D2" s="123" t="n"/>
+      <c r="E2" s="123" t="n"/>
+      <c r="F2" s="123" t="n"/>
+      <c r="G2" s="123" t="n"/>
+      <c r="H2" s="123" t="n"/>
+      <c r="I2" s="123" t="n"/>
+      <c r="J2" s="123" t="n"/>
+      <c r="K2" s="123" t="n"/>
+      <c r="L2" s="123" t="n"/>
+      <c r="M2" s="124" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="102" t="inlineStr">
@@ -1368,69 +1539,69 @@
           <t>전체 액티비티</t>
         </is>
       </c>
-      <c r="C6" s="104" t="n"/>
+      <c r="C6" s="124" t="n"/>
       <c r="D6" s="122" t="inlineStr">
         <is>
           <t>표준서 작성</t>
         </is>
       </c>
-      <c r="E6" s="104" t="n"/>
+      <c r="E6" s="124" t="n"/>
       <c r="F6" s="122" t="inlineStr">
         <is>
           <t>수행지침 작성</t>
         </is>
       </c>
-      <c r="G6" s="104" t="n"/>
+      <c r="G6" s="124" t="n"/>
       <c r="H6" s="122" t="inlineStr">
         <is>
           <t>체크리스트 작성</t>
         </is>
       </c>
-      <c r="I6" s="104" t="n"/>
+      <c r="I6" s="124" t="n"/>
       <c r="J6" s="122" t="inlineStr">
         <is>
           <t>상세절차서(HTML) 연동</t>
         </is>
       </c>
-      <c r="K6" s="104" t="n"/>
+      <c r="K6" s="124" t="n"/>
       <c r="L6" s="122" t="inlineStr">
         <is>
           <t>현장 리스크 DB</t>
         </is>
       </c>
-      <c r="M6" s="104" t="n"/>
+      <c r="M6" s="124" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="105">
         <f>E21&amp;" 개"</f>
         <v/>
       </c>
-      <c r="C7" s="104" t="n"/>
+      <c r="C7" s="124" t="n"/>
       <c r="D7" s="105">
         <f>F21&amp;" 개 (100%)"</f>
         <v/>
       </c>
-      <c r="E7" s="104" t="n"/>
+      <c r="E7" s="124" t="n"/>
       <c r="F7" s="105">
         <f>G21&amp;" 개 (100%)"</f>
         <v/>
       </c>
-      <c r="G7" s="104" t="n"/>
+      <c r="G7" s="124" t="n"/>
       <c r="H7" s="105">
         <f>H21&amp;" 개 (100%)"</f>
         <v/>
       </c>
-      <c r="I7" s="104" t="n"/>
+      <c r="I7" s="124" t="n"/>
       <c r="J7" s="105">
         <f>I21&amp;" 개 (100%)"</f>
         <v/>
       </c>
-      <c r="K7" s="104" t="n"/>
+      <c r="K7" s="124" t="n"/>
       <c r="L7" s="105">
         <f>J21&amp;" 개 (87.8%)"</f>
         <v/>
       </c>
-      <c r="M7" s="104" t="n"/>
+      <c r="M7" s="124" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="106" t="inlineStr">
@@ -1943,19 +2114,19 @@
           <t>주요 기능</t>
         </is>
       </c>
-      <c r="C25" s="104" t="n"/>
+      <c r="C25" s="124" t="n"/>
       <c r="D25" s="107" t="inlineStr">
         <is>
           <t>핵심 내용 및 구현 현황</t>
         </is>
       </c>
-      <c r="E25" s="104" t="n"/>
-      <c r="F25" s="104" t="n"/>
-      <c r="G25" s="104" t="n"/>
-      <c r="H25" s="104" t="n"/>
-      <c r="I25" s="104" t="n"/>
-      <c r="J25" s="104" t="n"/>
-      <c r="K25" s="104" t="n"/>
+      <c r="E25" s="123" t="n"/>
+      <c r="F25" s="123" t="n"/>
+      <c r="G25" s="123" t="n"/>
+      <c r="H25" s="123" t="n"/>
+      <c r="I25" s="123" t="n"/>
+      <c r="J25" s="123" t="n"/>
+      <c r="K25" s="124" t="n"/>
       <c r="L25" s="107" t="inlineStr">
         <is>
           <t>적용 상태</t>
@@ -1968,19 +2139,19 @@
           <t>시공 사진·영상 시각화</t>
         </is>
       </c>
-      <c r="C26" s="117" t="n"/>
+      <c r="C26" s="124" t="n"/>
       <c r="D26" s="112" t="inlineStr">
         <is>
           <t>공종별 현장 시공 사진, 3D BIM 모델 및 품질 시험 동영상 1:1 매핑 완료 (263개 전 작업)</t>
         </is>
       </c>
-      <c r="E26" s="117" t="n"/>
-      <c r="F26" s="117" t="n"/>
-      <c r="G26" s="117" t="n"/>
-      <c r="H26" s="117" t="n"/>
-      <c r="I26" s="117" t="n"/>
-      <c r="J26" s="117" t="n"/>
-      <c r="K26" s="117" t="n"/>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="123" t="n"/>
+      <c r="G26" s="123" t="n"/>
+      <c r="H26" s="123" t="n"/>
+      <c r="I26" s="123" t="n"/>
+      <c r="J26" s="123" t="n"/>
+      <c r="K26" s="124" t="n"/>
       <c r="L26" s="118" t="inlineStr">
         <is>
           <t>구현 완료</t>
@@ -1993,19 +2164,19 @@
           <t>전문시방서(KCS) 원문 연동</t>
         </is>
       </c>
-      <c r="C27" s="104" t="n"/>
+      <c r="C27" s="124" t="n"/>
       <c r="D27" s="109" t="inlineStr">
         <is>
           <t>국토교통부 KCS 전문시방서 PDF(1페이지 원문) 및 관련 법령 링크 바로 열기 구현</t>
         </is>
       </c>
-      <c r="E27" s="104" t="n"/>
-      <c r="F27" s="104" t="n"/>
-      <c r="G27" s="104" t="n"/>
-      <c r="H27" s="104" t="n"/>
-      <c r="I27" s="104" t="n"/>
-      <c r="J27" s="104" t="n"/>
-      <c r="K27" s="104" t="n"/>
+      <c r="E27" s="123" t="n"/>
+      <c r="F27" s="123" t="n"/>
+      <c r="G27" s="123" t="n"/>
+      <c r="H27" s="123" t="n"/>
+      <c r="I27" s="123" t="n"/>
+      <c r="J27" s="123" t="n"/>
+      <c r="K27" s="124" t="n"/>
       <c r="L27" s="120" t="inlineStr">
         <is>
           <t>구현 완료</t>
@@ -2018,19 +2189,19 @@
           <t>문장별 상세절차서(HTML) 연동</t>
         </is>
       </c>
-      <c r="C28" s="117" t="n"/>
+      <c r="C28" s="124" t="n"/>
       <c r="D28" s="112" t="inlineStr">
         <is>
           <t>체크리스트 각 항목 클릭 시 해당 작업의 1:1 독자 상세절차서(HTML) 즉시 연동</t>
         </is>
       </c>
-      <c r="E28" s="117" t="n"/>
-      <c r="F28" s="117" t="n"/>
-      <c r="G28" s="117" t="n"/>
-      <c r="H28" s="117" t="n"/>
-      <c r="I28" s="117" t="n"/>
-      <c r="J28" s="117" t="n"/>
-      <c r="K28" s="117" t="n"/>
+      <c r="E28" s="123" t="n"/>
+      <c r="F28" s="123" t="n"/>
+      <c r="G28" s="123" t="n"/>
+      <c r="H28" s="123" t="n"/>
+      <c r="I28" s="123" t="n"/>
+      <c r="J28" s="123" t="n"/>
+      <c r="K28" s="124" t="n"/>
       <c r="L28" s="118" t="inlineStr">
         <is>
           <t>구현 완료</t>
@@ -2043,19 +2214,19 @@
           <t>단일 화면 패키지 구성</t>
         </is>
       </c>
-      <c r="C29" s="104" t="n"/>
+      <c r="C29" s="124" t="n"/>
       <c r="D29" s="109" t="inlineStr">
         <is>
           <t>1개 작업 단위에 표준서, 수행지침, 체크리스트, 상세절차서를 한 화면에 통합 제공</t>
         </is>
       </c>
-      <c r="E29" s="104" t="n"/>
-      <c r="F29" s="104" t="n"/>
-      <c r="G29" s="104" t="n"/>
-      <c r="H29" s="104" t="n"/>
-      <c r="I29" s="104" t="n"/>
-      <c r="J29" s="104" t="n"/>
-      <c r="K29" s="104" t="n"/>
+      <c r="E29" s="123" t="n"/>
+      <c r="F29" s="123" t="n"/>
+      <c r="G29" s="123" t="n"/>
+      <c r="H29" s="123" t="n"/>
+      <c r="I29" s="123" t="n"/>
+      <c r="J29" s="123" t="n"/>
+      <c r="K29" s="124" t="n"/>
       <c r="L29" s="120" t="inlineStr">
         <is>
           <t>구현 완료</t>
@@ -2068,19 +2239,19 @@
           <t>현장 시공 데이터 누적 관리</t>
         </is>
       </c>
-      <c r="C30" s="117" t="n"/>
+      <c r="C30" s="124" t="n"/>
       <c r="D30" s="112" t="inlineStr">
         <is>
           <t>동탄 현장에서 발생하는 시험 성적서, 사진 데이터(v6)를 실시간 누적·업데이트</t>
         </is>
       </c>
-      <c r="E30" s="117" t="n"/>
-      <c r="F30" s="117" t="n"/>
-      <c r="G30" s="117" t="n"/>
-      <c r="H30" s="117" t="n"/>
-      <c r="I30" s="117" t="n"/>
-      <c r="J30" s="117" t="n"/>
-      <c r="K30" s="117" t="n"/>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="123" t="n"/>
+      <c r="G30" s="123" t="n"/>
+      <c r="H30" s="123" t="n"/>
+      <c r="I30" s="123" t="n"/>
+      <c r="J30" s="123" t="n"/>
+      <c r="K30" s="124" t="n"/>
       <c r="L30" s="118" t="inlineStr">
         <is>
           <t>구현 완료</t>
@@ -2105,18 +2276,18 @@
           <t>보고 안건</t>
         </is>
       </c>
-      <c r="D34" s="104" t="n"/>
+      <c r="D34" s="124" t="n"/>
       <c r="E34" s="121" t="inlineStr">
         <is>
           <t>주요 내용</t>
         </is>
       </c>
-      <c r="F34" s="104" t="n"/>
-      <c r="G34" s="104" t="n"/>
-      <c r="H34" s="104" t="n"/>
-      <c r="I34" s="104" t="n"/>
-      <c r="J34" s="104" t="n"/>
-      <c r="K34" s="104" t="n"/>
+      <c r="F34" s="123" t="n"/>
+      <c r="G34" s="123" t="n"/>
+      <c r="H34" s="123" t="n"/>
+      <c r="I34" s="123" t="n"/>
+      <c r="J34" s="123" t="n"/>
+      <c r="K34" s="124" t="n"/>
       <c r="L34" s="121" t="inlineStr">
         <is>
           <t>진행 상황</t>
@@ -2134,18 +2305,18 @@
           <t>동탄 현장 기반 매뉴얼 연속 업데이트 승인</t>
         </is>
       </c>
-      <c r="D35" s="104" t="n"/>
+      <c r="D35" s="124" t="n"/>
       <c r="E35" s="109" t="inlineStr">
         <is>
           <t>동탄 현장 실무 데이터를 바탕으로 매뉴얼(v6 ➔ v7)을 지속 보완·운영하는 체계 승인</t>
         </is>
       </c>
-      <c r="F35" s="104" t="n"/>
-      <c r="G35" s="104" t="n"/>
-      <c r="H35" s="104" t="n"/>
-      <c r="I35" s="104" t="n"/>
-      <c r="J35" s="104" t="n"/>
-      <c r="K35" s="104" t="n"/>
+      <c r="F35" s="123" t="n"/>
+      <c r="G35" s="123" t="n"/>
+      <c r="H35" s="123" t="n"/>
+      <c r="I35" s="123" t="n"/>
+      <c r="J35" s="123" t="n"/>
+      <c r="K35" s="124" t="n"/>
       <c r="L35" s="120" t="inlineStr">
         <is>
           <t>승인 완료</t>
@@ -2163,18 +2334,18 @@
           <t>사내 매뉴얼 시스템 통합 및 자산화</t>
         </is>
       </c>
-      <c r="D36" s="104" t="n"/>
+      <c r="D36" s="124" t="n"/>
       <c r="E36" s="109" t="inlineStr">
         <is>
           <t>완성된 매뉴얼을 사내 표준 시스템에 탑재하여 향후 신규 트램 사업 수주 시 재활용</t>
         </is>
       </c>
-      <c r="F36" s="104" t="n"/>
-      <c r="G36" s="104" t="n"/>
-      <c r="H36" s="104" t="n"/>
-      <c r="I36" s="104" t="n"/>
-      <c r="J36" s="104" t="n"/>
-      <c r="K36" s="104" t="n"/>
+      <c r="F36" s="123" t="n"/>
+      <c r="G36" s="123" t="n"/>
+      <c r="H36" s="123" t="n"/>
+      <c r="I36" s="123" t="n"/>
+      <c r="J36" s="123" t="n"/>
+      <c r="K36" s="124" t="n"/>
       <c r="L36" s="120" t="inlineStr">
         <is>
           <t>추진 중</t>
@@ -2185,8 +2356,8 @@
   <mergeCells count="31">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="E36:K36"/>
     <mergeCell ref="D26:K26"/>
-    <mergeCell ref="E36:K36"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
@@ -2220,6 +2391,3257 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet8">
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="19.2"/>
+  <cols>
+    <col width="9" bestFit="1" customWidth="1" style="4" min="1" max="2"/>
+    <col width="13.19921875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11.19921875" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="30.3984375" customWidth="1" style="4" min="5" max="5"/>
+    <col width="21.69921875" customWidth="1" style="4" min="6" max="6"/>
+    <col width="32.59765625" customWidth="1" style="3" min="7" max="7"/>
+    <col width="73.09765625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="19.3984375" customWidth="1" style="4" min="9" max="9"/>
+    <col width="53" customWidth="1" style="3" min="10" max="10"/>
+    <col width="14.69921875" customWidth="1" style="3" min="11" max="11"/>
+    <col width="45" customWidth="1" style="3" min="12" max="12"/>
+    <col width="14.5" customWidth="1" style="3" min="13" max="13"/>
+    <col width="45" customWidth="1" style="3" min="14" max="14"/>
+    <col width="16.09765625" customWidth="1" style="77" min="15" max="15"/>
+    <col width="15.796875" customWidth="1" style="3" min="16" max="16"/>
+    <col width="45" customWidth="1" style="77" min="17" max="17"/>
+    <col width="22" customWidth="1" style="77" min="18" max="18"/>
+    <col width="45" customWidth="1" style="3" min="19" max="35"/>
+    <col width="8.796875" customWidth="1" style="3" min="36" max="65"/>
+    <col width="8.796875" customWidth="1" style="3" min="66" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="57.6" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>L2 코드</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>L3 코드</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>L3 대공종명</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>L4 코드</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>작업단위 (Level 4 Task/Activity)</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>주관</t>
+        </is>
+      </c>
+      <c r="G1" s="29" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="H1" s="65" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="I1" s="65" t="inlineStr">
+        <is>
+          <t>산출물(결과)</t>
+        </is>
+      </c>
+      <c r="J1" s="65" t="inlineStr">
+        <is>
+          <t>표준서 (Standard) 요약</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>표준서 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="L1" s="65" t="inlineStr">
+        <is>
+          <t>수행지침 (Guideline) 요약</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>수행지침 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="N1" s="65" t="inlineStr">
+        <is>
+          <t>체크리스트 (Checklist) 요약</t>
+        </is>
+      </c>
+      <c r="O1" s="66" t="inlineStr">
+        <is>
+          <t>체크리스트 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="P1" s="21" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="Q1" s="21" t="inlineStr">
+        <is>
+          <t>첨부서류 연계 상세 설계기준</t>
+        </is>
+      </c>
+      <c r="R1" s="21" t="inlineStr">
+        <is>
+          <t>집행단계 리스크 체크리스트</t>
+        </is>
+      </c>
+      <c r="S1" s="21" t="inlineStr">
+        <is>
+          <t>협력사 시공/공사관리 자문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="199.2" customHeight="1">
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C2" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D2" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-1</t>
+        </is>
+      </c>
+      <c r="E2" s="61" t="inlineStr">
+        <is>
+          <t>설계적정성 검토</t>
+        </is>
+      </c>
+      <c r="F2" s="61" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="G2" s="60" t="inlineStr">
+        <is>
+          <t>설계적정성 및 시공성 검토</t>
+        </is>
+      </c>
+      <c r="H2" s="62" t="inlineStr">
+        <is>
+          <t>- 입찰 요구사항에 대한 설계 반영여부 검토
+- 설계도서 및 철도표준 자재 반영여부 확인
+- 타 시스템과의 인터페이스 가능 여부, 용량, 성능요구 및 통신 트렌드를 고려한 통신 시스템 선정
+- 설계단계에서 통신 음영지역이 있는지를 샘플링 시뮬레이션을 통해 확인하는지 체크 (민원방지 및 롤백 예방을 위한 방안 수립)
+- 기지/역사/터널 배선 적정성 검토
+- 현장설치 시공성 및 공기 Risk 검토
+- 공정계획의 적정성 검토</t>
+        </is>
+      </c>
+      <c r="I2" s="61" t="inlineStr">
+        <is>
+          <t>회의록, 설계검토 보고서</t>
+        </is>
+      </c>
+      <c r="J2" s="74" t="inlineStr">
+        <is>
+          <t>1) 정보통신공사업법, KDS 47 철도설계기준 및 입찰안내서 특기시방 준수 여부 사전 검증
+2) LTE-R 무선망, 8대 이종 통신시스템, 타공종 간섭 및 리스크 헷지·기회반영 설계변경 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K2" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L2" s="74" t="inlineStr">
+        <is>
+          <t>1) 설계적정성 검토: [도면↔수량산출서↔내역서] 삼각 교차대조, 법령/KDS 매핑 체크리스트 검증 및 통신계통 계산서 검토
+2) 시공성 및 설계변경: 현장 지장물 실측 조사, 타공종 3D 간섭 조정, 공법/안전 검토 및 현장 전직원+본사 동시 검토 회의로 설계변경 수립</t>
+        </is>
+      </c>
+      <c r="M2" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N2" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 관계 법령, KDS 47 00 00 철도설계기준, 입찰안내서 시방 준수 및 도면·수량·내역 교차 검증을 완료하였는가?
+2) LTE-R 무선망, 타공종 3D 간섭조정, 8대 이종 통신시스템, 관제연동 적정성 검토 및 현장전직원+본사 동시 검토 승인을 완료하였는가?</t>
+        </is>
+      </c>
+      <c r="O2" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P2" s="68" t="n"/>
+      <c r="Q2" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R2" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S2" s="73" t="n"/>
+    </row>
+    <row r="3" ht="219.6" customHeight="1">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B3" s="63" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D3" s="63" t="inlineStr">
+        <is>
+          <t>9000-2-2</t>
+        </is>
+      </c>
+      <c r="E3" s="63" t="inlineStr">
+        <is>
+          <t>착수전략 KOM</t>
+        </is>
+      </c>
+      <c r="F3" s="61" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
+        <is>
+          <t>통신설비 공사 발주 전략수립</t>
+        </is>
+      </c>
+      <c r="H3" s="62" t="inlineStr">
+        <is>
+          <t>- 통신설계 설계 및 변동요인 검토
+- 통신공사 공사 시공실적 업체Pool 검토
+- 유사사례 영업운행 실적이 확보된 시스템적용
+1) 공정계획 및 통신자재 제작 기간
+2) 통신설비 구축 실적 보유 (철도, 도시철도, 경전철)
+3) 예비품 및 소모품 포함
+4) 시공전시 통신설비 운전 및 교육 지원 (비용 포함)
+5) 예상내역상 누락 예비품 여부
+6) 현장 자재보관 창고 임대 비용 포함
+7) 공사용 전기, 물수, 청소 비용 포함
+8) 가동 후 현장 기술지원 및 기술 전수 인력기간 및 비용 포함</t>
+        </is>
+      </c>
+      <c r="I3" s="61" t="inlineStr">
+        <is>
+          <t>KOM 검토결과서, 현장설명서</t>
+        </is>
+      </c>
+      <c r="J3" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신공사 발주 착수 전 입찰조건, 적격 시공업체 Pool 분석 및 8대 현장조건 반영 발주전략 수립
+2) 주요 통신 자재 납품 수급 계획 및 시공 적격성 평가를 반영한 발주전략 KOM 보고서 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K3" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L3" s="74" t="inlineStr">
+        <is>
+          <t>1) 발주조건 &amp; 공법 분석: 공사 범위, 자재 자급/사급 조건, 공기 타당성 및 타공종 인터페이스 선행 공종 분석
+2) 전략 수립 및 승인: 리스크 헷지형 계약 조건 도출 및 현장소장/공무팀 주관 발주전략 KOM 보고서 확정</t>
+        </is>
+      </c>
+      <c r="M3" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N3" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신공사 발주 착수 전 입찰안내서 요구조건 및 현장여건 8대 특기사항을 발주 전략에 반영하였는가?
+2) 주요 자재 납품 수급 계획 및 적격 시공업체 평가 기준을 마련하여 발주전략 KOM 승인을 완수하였는가?</t>
+        </is>
+      </c>
+      <c r="O3" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P3" s="68" t="n"/>
+      <c r="Q3" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R3" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S3" s="73" t="n"/>
+    </row>
+    <row r="4" ht="133.8" customHeight="1">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D4" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-3</t>
+        </is>
+      </c>
+      <c r="E4" s="61" t="inlineStr">
+        <is>
+          <t>토목 / 건축 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F4" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G4" s="60" t="inlineStr">
+        <is>
+          <t>통신설비 설치를 위한 요구사항 검토</t>
+        </is>
+      </c>
+      <c r="H4" s="62" t="inlineStr">
+        <is>
+          <t>- 자재 반입전/공동구/케이블 인입구 등 확인, 기능실마감 및 출입문 상태</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J4" s="74" t="inlineStr">
+        <is>
+          <t>1) 토목·건축 구조물 내 통신 관로, 케이블 트레이, 기계실 배치 및 인입 배관 인터페이스 사전 검토
+2) 타공종 구조체 타설 전 통신 매립 배관 위치 검증 및 인터페이스 협의록 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K4" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L4" s="74" t="inlineStr">
+        <is>
+          <t>1) 구조체 간섭 검토: 토목·건축 도면 대조를 통한 통신 관로 굴곡율, 트레이 설치 경로 및 기계실 벽체 관통부 실측 조사
+2) 협의 수행 및 승인: 타공종 구조체 콘크리트 타설 전 통신 배관 매립 위치 현장 확인 및 3D 간섭 조정 협의록 확정</t>
+        </is>
+      </c>
+      <c r="M4" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N4" s="74" t="inlineStr">
+        <is>
+          <t>1) 시방 대조[도면 및 여건] 자재 반입 동선/공동구/케이블 인입구 등 확인, 기능실마감 및 출입문 확인 수칙을 사전 대조 확인하였는가?
+2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O4" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P4" s="68" t="n"/>
+      <c r="Q4" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R4" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S4" s="73" t="n"/>
+    </row>
+    <row r="5" ht="133.8" customHeight="1">
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-4</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="inlineStr">
+        <is>
+          <t>전기 / 신호 / 기계 / PSD / 차량 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F5" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 통신 협력업체</t>
+        </is>
+      </c>
+      <c r="G5" s="60" t="inlineStr">
+        <is>
+          <t>연계분야간 사전조율 및 인터페이스 사항 조율로 재작업 예방</t>
+        </is>
+      </c>
+      <c r="H5" s="62" t="inlineStr">
+        <is>
+          <t>- 연계분야별 조율 및 협의사항 도출
+1) 전기: 소요전력 외
+2) 신호: 공동관로 포설계획 외
+3) 차량: 차량 통신장치-차량간 연계
+4) 전기, 신호, 기계, PSD와 통신망 계통 조율
+- 일정, 분야별 필요 통신회선 수/종류, 기계실 케이블 및 세부 작업 범위</t>
+        </is>
+      </c>
+      <c r="I5" s="61" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J5" s="74" t="inlineStr">
+        <is>
+          <t>1) 전기, 신호, PSD, 차량, 관제 등 이종 시스템 간 전원, 신호선 및 데이터 통신 인터페이스 통합 검토
+2) 타공종 간 전자기 적합성(EMC/EMI), 전력 케이블 유도장해 차폐 및 서지 보호 표준 적용</t>
+        </is>
+      </c>
+      <c r="K5" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L5" s="74" t="inlineStr">
+        <is>
+          <t>1) 설비 간 인터페이스 기술 검토: 전전류/고전압 케이블 유도장해 이격거리(≥30cm) 및 타공종 신호선 서지 보호 검토
+2) 3D/BIM 간섭조정 및 승인: 이종 시스템 간 인터페이스 핀 맵, 데이터 포맷 교차 검증 및 시스템 합동 인터페이스 협의록 작성</t>
+        </is>
+      </c>
+      <c r="M5" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N5" s="74" t="inlineStr">
+        <is>
+          <t>1) 96Core 광망[통합 포설] 통신(48C)+전기(2C)+신호(12C)를 OF-SM-96Core×2조 통합 포설로 확정하였는가?
+2) KEC 점유율[KEC 33%] 전선관 내부 단면적 점유율 33% 이하 및 ELP ø150mm×6개×2조 배관을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O5" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P5" s="68" t="n"/>
+      <c r="Q5" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R5" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S5" s="73" t="n"/>
+    </row>
+    <row r="6" ht="133.8" customHeight="1">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-5</t>
+        </is>
+      </c>
+      <c r="E6" s="61" t="inlineStr">
+        <is>
+          <t>통신설비 제작사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F6" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G6" s="60" t="inlineStr">
+        <is>
+          <t>통신설비간 연동방안 검토</t>
+        </is>
+      </c>
+      <c r="H6" s="62" t="inlineStr">
+        <is>
+          <t>- 내부 인터페이스 및 인허가사항 확인, 보안성검토 요청서</t>
+        </is>
+      </c>
+      <c r="I6" s="61" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J6" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 주요 설비(LTE-R, 방송, CCTV, 역무, 관제 등) 제작사 간 프로토콜, 연동 규격 및 인터페이스 검토
+2) 제작사 간 데이터 입출력 포맷 및 연동 케이블 사양서 확정 협의록 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K6" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L6" s="74" t="inlineStr">
+        <is>
+          <t>1) 프로토콜 &amp; 연동 검토: 제작사 간 데이터 입출력 규격, 네트워크 프로토콜(TCP/IP, RS-485 등) 및 랙 치수 대조
+2) 연동 시험 수칙 수립: 제작사 간 신호 연동 핀 배열 확정 및 상호 연동 인터페이스 사양서 감리 승인 절차 수행</t>
+        </is>
+      </c>
+      <c r="M6" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N6" s="74" t="inlineStr">
+        <is>
+          <t>1) 핀 구멍 대조[연결선 대조] A회사와 B회사 장비 연결선 핀(Pin) 구멍 위치가 똑맞는지 1:1 도면으로 대조하였는가?
+2) 전원 잭 확인[코드 잭 준비] 각 장비에 220V 코드를 꽂을지 48V 전기를 줄지 전원 잭을 사전에 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O6" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P6" s="68" t="n"/>
+      <c r="Q6" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R6" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S6" s="73" t="n"/>
+    </row>
+    <row r="7" ht="145.2" customHeight="1">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-6</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 통신 협력업체</t>
+        </is>
+      </c>
+      <c r="G7" s="60" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 요구사항 사전 반영 및 시공범위 최적화</t>
+        </is>
+      </c>
+      <c r="H7" s="62" t="inlineStr">
+        <is>
+          <t>- 시운전 조율사항 및 시운전시 정보 항목도출
+- 철도 교통관제(구로/대전)와 연동할 수 있는 무선기능추가(관제/유지보수자 등), 실시간 사진 확인의 편리성 향상을 위한 기능 추가(CCTV카메라 등)
+- 합동운영자, 운영사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="I7" s="61" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J7" s="74" t="inlineStr">
+        <is>
+          <t>1) 종합관제센터 및 철도운영사 요구조건 반영 관제 화면, 통신 프로토콜 및 비상 제어 인터페이스 검토
+2) 관제 서버, 네트워크 스위치 및 운영사 통합 수선 체계 부합성 확인 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K7" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L7" s="74" t="inlineStr">
+        <is>
+          <t>1) 관제 연동 요구조건 검토: 종합관제 MMI 화면 구성, 비상 통화 프로토콜 및 운영사 통합 수선 요구사항 반영 조사
+2) 관제 인터페이스 승인: 관제 서버-현장 장치 간 제어 데이터 송수신 시험 절차 수립 및 운영사 합동 검토서 확정</t>
+        </is>
+      </c>
+      <c r="M7" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N7" s="74" t="inlineStr">
+        <is>
+          <t>1) OCC 화면배치[화면 맞추기] 동탄 종합관제실(OCC) 모니터에 트램 운행 상황이 한눈에 들어오도록 화면을 배치하였는가?
+2) 4K CCTV 65개[명당 자리] 교차로 4K CCTV 카메라 65개소가 사각지대 없이 보이도록 명당 자리를 배치하였는가?</t>
+        </is>
+      </c>
+      <c r="O7" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P7" s="68" t="n"/>
+      <c r="Q7" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R7" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S7" s="73" t="n"/>
+    </row>
+    <row r="8" ht="115.2" customHeight="1">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C8" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-7</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>발주처 품질 요구사항 검토</t>
+        </is>
+      </c>
+      <c r="F8" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G8" s="60" t="inlineStr">
+        <is>
+          <t>발주처 품질관리 기준/검사방안 확인</t>
+        </is>
+      </c>
+      <c r="H8" s="60" t="inlineStr">
+        <is>
+          <t>- 감리/감독과 품질검사(ITP/ITC) 항목 검토</t>
+        </is>
+      </c>
+      <c r="I8" s="61" t="inlineStr">
+        <is>
+          <t>ITP/ITC</t>
+        </is>
+      </c>
+      <c r="J8" s="74" t="inlineStr">
+        <is>
+          <t>1) 발주처 입찰안내서 및 시방서 상의 통신 품질 시험 기준, 자재 승인 및 시험성적서 요구조건 검토
+2) 품질시험계획서 수립 및 발주처 승인 품질 기준 준수서 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K8" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L8" s="74" t="inlineStr">
+        <is>
+          <t>1) 품질 기준 실측 수칙: 발주처 특기시방서 상의 품질 시험 항목, 샘플링 검사 비율 및 KS 규격 부합 여부 파악
+2) 품질 관리 수립: 현장 품질시험계획서 수립, 불합격 자재 반출 절차 확립 및 발주처 승인 품질 수칙 이행</t>
+        </is>
+      </c>
+      <c r="M8" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N8" s="74" t="inlineStr">
+        <is>
+          <t>1) [품질 계획] 발주처 품질검사 계획서(ITP)와 공사시방서의 품질 기준을 사전 정밀 대조하였는가?
+2) [Hold Point] 감리원 현장 직접 입회 검측 항목(Hold Point)을 사전 분류 지정하였는가?</t>
+        </is>
+      </c>
+      <c r="O8" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P8" s="68" t="n"/>
+      <c r="Q8" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R8" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S8" s="73" t="n"/>
+    </row>
+    <row r="9" ht="115.2" customHeight="1">
+      <c r="A9" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B9" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-8</t>
+        </is>
+      </c>
+      <c r="E9" s="61" t="inlineStr">
+        <is>
+          <t>자재 / 인원 / 장비 등 투입 사전 검토</t>
+        </is>
+      </c>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 협력업체 / 관리</t>
+        </is>
+      </c>
+      <c r="G9" s="60" t="inlineStr">
+        <is>
+          <t>자재 / 인원 / 장비 투입 계획 수립</t>
+        </is>
+      </c>
+      <c r="H9" s="62" t="inlineStr">
+        <is>
+          <t>- 현장 여건 및 수량을 기준으로 투입(인원, 장비, 자재) 검토</t>
+        </is>
+      </c>
+      <c r="I9" s="61" t="inlineStr">
+        <is>
+          <t>세부 공정계획 수립 및 조율</t>
+        </is>
+      </c>
+      <c r="J9" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 공사 착수 전 전문 인력 기술자격, 자재 투입 일정 및 전용 시험장비/공구 사전 검토
+2) 예정공정표 대비 인원·장비 투입 수급 타당성 및 안전 수칙 준수 검토 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K9" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>1) 투입 자원 타당성 분석: 통신 고급/중급 기술자 자격 검증, 광접속기/OTDR 시험장비 보유 상태 및 자재 수급 계획 검토
+2) 공정 수급 승인: 예정공정표 대비 적정 투입 인원 산출, 작업 안전 구역 확보 및 현장소장 투입 승인 절차 수행</t>
+        </is>
+      </c>
+      <c r="M9" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N9" s="74" t="inlineStr">
+        <is>
+          <t>1) [자원 계획] 공정별 통신 인력, 장비 수급 및 자재 수량을 사전 정밀 대조하였는가?
+2) [인력 자격] 통신 공종별 특급/고급 기술자 자격증 및 현장 배치 계획을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O9" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P9" s="68" t="n"/>
+      <c r="Q9" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R9" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S9" s="73" t="n"/>
+    </row>
+    <row r="10" ht="210.6" customHeight="1">
+      <c r="A10" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-9</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>착수 전 Big Room 회의</t>
+        </is>
+      </c>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>통신공사 수행 시, 선행공정 간섭사항 및 각종 Risk에 대한 대책 수립</t>
+        </is>
+      </c>
+      <c r="H10" s="62" t="inlineStr">
+        <is>
+          <t>본사/현장/협력사 협의체 구축 후 세부내용 검토
+- 공종별 간섭사항 검토: 노반(궤도)/전기/신호/기계/PSD/차량 인터페이스
+- 통신자재 반입/토목(도로/궤도)/자재 야적장/제작사 공장 검토
+- 통신자재 성능보장, 유사사례 리스크관리 및 성능보증 사항 검토
+- 하자 예방, 타 프로젝트 하자사례 검토 후 재발방지방안 수립
+- 인원, 자재, 장비 투입계획, 인허가사항 요건계획 검토
+- 검사의 각 안전공사 기준 공유, 감리검사 계획 확인
+- 공종별 Risk Hedge 방안 검토
+1) 안전/품질 Risk 요소 및 대책 수립
+2) 민원 대응방안 수립</t>
+        </is>
+      </c>
+      <c r="I10" s="61" t="inlineStr">
+        <is>
+          <t>Big Room 회의록(참석자 전원 서명)</t>
+        </is>
+      </c>
+      <c r="J10" s="74" t="inlineStr">
+        <is>
+          <t>1) 공사 착수 전 발주처, 감리단, 시공사 및 타공종 합동 Big Room 회의를 통한 종합 공정 및 위험요인 검토
+2) 간섭사항 사전 도출 및 공종 간 공정 마일스톤 협의록 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K10" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>1) Big Room 공조 기법: 발주처·감리단·타공종 시공사 참사 종합 공정 3D 워크스루 및 선행 공종 마일스톤 점검
+2) 간섭 리스크 해소: 공사 착수 전 분야별 간섭 위험 요소를 발굴하여 헷지 방안 수립 및 Big Room 회의록 최종 승인</t>
+        </is>
+      </c>
+      <c r="M10" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N10" s="74" t="inlineStr">
+        <is>
+          <t>1) [Big Room 체계] 본사/현장/협력사 3자 Big Room 협의체를 구축하고 착수 세부 실행계획을 대조하였는가?
+2) [인터페이스] 노반(궤도)/전기/신호/기계/차량 5대 공종 간 관통 경로 및 간섭점을 사전 도출 검출하였는가?</t>
+        </is>
+      </c>
+      <c r="O10" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P10" s="68" t="n"/>
+      <c r="Q10" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R10" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S10" s="73" t="n"/>
+    </row>
+    <row r="11" ht="115.2" customHeight="1">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-10</t>
+        </is>
+      </c>
+      <c r="E11" s="61" t="inlineStr">
+        <is>
+          <t>통신설비 제작 사양서 작성 / 승인</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G11" s="60" t="inlineStr">
+        <is>
+          <t>실제 설치되는 통신설비의 사양서를 확정하고 제작 사양서를 작성/승인</t>
+        </is>
+      </c>
+      <c r="H11" s="62" t="inlineStr">
+        <is>
+          <t>- 현장여건 및 실시설계계획보고서/포함자재사양서의 요구사항 충족 여부를 확인
+- 제작사양서, 제작도면 작성 후 감리단 승인</t>
+        </is>
+      </c>
+      <c r="I11" s="61" t="inlineStr">
+        <is>
+          <t>제작사양서, 제작도면</t>
+        </is>
+      </c>
+      <c r="J11" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신설비 세부 기술사양서, 랙 배열도(Shop Drawing) 및 전기적/기계적 상세 도면 작성 검토
+2) 감리단 및 발주처 승인을 위한 제작사양서 승인 신청서 및 공학적 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K11" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>1) 제작도서 상세 검토: 통신 랙 배열도(Shop Drawing), 전원 분배기 용량 및 단위 기기 기술 사양서 정밀 분석
+2) 공학적 승인 신청: 발주처 입찰시방과 제작사양서 1:1 대조 검증 및 감리단 공학적 승인 제출 절차 수행</t>
+        </is>
+      </c>
+      <c r="M11" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N11" s="74" t="inlineStr">
+        <is>
+          <t>1) [도서 대조] 기본/실시설계도서(보고서, 도면, 자재사양서)와 현장 기계실·역사 치수를 1:1 대조·확인하였는가?
+2) [사양서 정의] 실제 제작·설치될 통신설비의 전기적·기계적 세부 규격 및 제작도면(Shop Drawing)을 작성하였는가?</t>
+        </is>
+      </c>
+      <c r="O11" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P11" s="68" t="n"/>
+      <c r="Q11" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R11" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S11" s="73" t="n"/>
+    </row>
+    <row r="12" ht="115.2" customHeight="1">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-11</t>
+        </is>
+      </c>
+      <c r="E12" s="61" t="inlineStr">
+        <is>
+          <t>시공 계획 수립 / 승인</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="inlineStr">
+        <is>
+          <t>안전/품질이 확보된 시공계획 수립</t>
+        </is>
+      </c>
+      <c r="H12" s="60" t="inlineStr">
+        <is>
+          <t>- 공사계획: 예정공정표, 인원/장비/자재투입 계획, 통신자재 설치 절차서 등
+- 안전관리: 위험요인/대책, 안전교육/시설/점검 계획 수립
+- 품질관리: 품질하자 Risk 및 대책 수립
+- 인허가: 자가전기통신설비 설치신고 접수</t>
+        </is>
+      </c>
+      <c r="I12" s="61" t="inlineStr">
+        <is>
+          <t>시공계획서&amp;시공상세도, 자가전기통신설비 신고서/계획서</t>
+        </is>
+      </c>
+      <c r="J12" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신공사 공정별 상세 시공절차서, 안전관리계획서, 품질관리계획서 및 세부 공정표 수립
+2) 통신설비 설치 공법 타당성 및 감리단 시공계획서 승인 제출 표준 적용</t>
+        </is>
+      </c>
+      <c r="K12" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>1) 세부 시공절차 수립: 통신 관로/트레이 포설, 광케이블 접속, 기계실 랙 설치 절차서 및 안전/품질 관리계획 작성
+2) 감리 승인 및 이행: 시공상세도(Shop Drawing) 첨부, 현장 안전 위험성 평가 실시 및 감리단 시공계획서 승인 완료</t>
+        </is>
+      </c>
+      <c r="M12" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N12" s="74" t="inlineStr">
+        <is>
+          <t>1) [도서 대조] 기본/실시설계 보고서, 시방서 수치와 현장 통신기계실 실측 치수를 1:1 대조·확인하였는가?
+2) [안전 대책] 통신기계실 DC -48V 감전 방지 및 정거장 고소작업 시 안전대/2인1조 작업 대책을 수립하였는가?</t>
+        </is>
+      </c>
+      <c r="O12" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P12" s="68" t="n"/>
+      <c r="Q12" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R12" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S12" s="73" t="n"/>
+    </row>
+    <row r="13" ht="115.2" customHeight="1">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-12</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>자재공급원 검토 및 승인</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="inlineStr">
+        <is>
+          <t>통신설비의 시공성과 품질, 기능 확보를 위한 자재 공급원 검토 및 승인</t>
+        </is>
+      </c>
+      <c r="H13" s="60" t="inlineStr">
+        <is>
+          <t>- 통신자재제작능력, 유사사례 납품실적 확인
+- 성능보증 가능한 통신자재 업체 Pool 검토
+- 통신자재 설치 실적 및 설계능력 확인
+- 보안성검토 결과 확인</t>
+        </is>
+      </c>
+      <c r="I13" s="61" t="inlineStr">
+        <is>
+          <t>자재공급원/제작도서 승인 서류, 보안성검토 결과서</t>
+        </is>
+      </c>
+      <c r="J13" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 주요 자재 및 기기 자재공급원 승인 서류(KS 인증, 시험성적서, 사업자등록증 등) 검토
+2) 성능보증이 가능한 복수 자재공급원 승인 서류 수립 및 감리 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K13" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>1) 승인 서류 정밀 검토: 제조사 공장등록증, KS/KC 인증서, 최근 3년 납품 실적 및 공인시험기관 시험성적서 확인
+2) 자재 승인 및 관리: 복수 공급원 비교 검토서 작성, 불량 자재 차단 헷지 및 감리단 자재공급원 승인 획득</t>
+        </is>
+      </c>
+      <c r="M13" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N13" s="74" t="inlineStr">
+        <is>
+          <t>1) [서류 수집] 공장등록증, 사업자등록증, 카탈로그, A/S 확약서 등 6대 필수 제출 서류를 수집·확인하였는가?
+2) [사양 대조] 설계도서 수치(KCS 31 10 00)와 자재 카탈로그 규격 간 1:1 대조표를 정확히 작성하였는가?</t>
+        </is>
+      </c>
+      <c r="O13" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P13" s="68" t="n"/>
+      <c r="Q13" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R13" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S13" s="73" t="n"/>
+    </row>
+    <row r="14" ht="192" customHeight="1">
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-13</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>통신설비 공정제작 / 제작사 공장검사</t>
+        </is>
+      </c>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
+        <is>
+          <t>제작사양서/제작도면의 일치여부검토 및 현장반입 전 공장 성능검사 확인</t>
+        </is>
+      </c>
+      <c r="H14" s="60" t="inlineStr">
+        <is>
+          <t>- 외산자재 등 Delivery 일정 확인
+- 제작도서 기준으로 최종 제작상태 확인
+- 제작도면과 일치여부 확인
+- 공장 내 성능검사 시험 실시
+[공장검사 대상 항목]
+- 영상장치장치, 행선안내장치, 구내방송장치, 전송설비, 역무자동화설비, 열차무선안내장치, 여객자동안내장치, 열차무선설비, 재난방송수신설비, 선로변 통합인터페이스 통신설비, 역무용통신설비, 백본스위치, L3스위치, 광케이블, 케이블 안테나 CCTV용 Pole</t>
+        </is>
+      </c>
+      <c r="I14" s="61" t="inlineStr">
+        <is>
+          <t>공장검사 결과보고서 (감리 및 관계기관 입회)</t>
+        </is>
+      </c>
+      <c r="J14" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 기기 제작 공정 진행률 점검 및 공장시험(FAT, Factory Acceptance Test) 절차서 작성
+2) 공장 수검 검사, 품질 성능 시험성적서 확인 및 공장검사 합격증명서 발급 표준 적용</t>
+        </is>
+      </c>
+      <c r="K14" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>1) 공장검사(FAT) 준비: 제작사 공장 제작 공정률 점검, FAT 시험절차서 검토 및 검사 입회 일정 수립
+2) 입회 검사 실시: 전원 인입, 기능 시험, 방수/내열 공인시험 실측 확인 및 FAT 공장검사 합격증명서 획득</t>
+        </is>
+      </c>
+      <c r="M14" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N14" s="74" t="inlineStr">
+        <is>
+          <t>1) [외산자재 납기] 수입 광모듈, 스위치 칩셋의 선적/통관 서류(B/L)를 검수하여 현장 기계실 반입 주공정표(CPM) 대비 납기를 확인하였는가?
+2) [ITP 승인] 감리 승인된 ITP 절차서와 절연저항계(Megger), OTDR의 교정 유효기간 증명서를 사전 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O14" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P14" s="68" t="n"/>
+      <c r="Q14" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R14" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S14" s="73" t="n"/>
+    </row>
+    <row r="15" ht="115.2" customHeight="1">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-14</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>본공사 전 선행공정 인수인계 점검</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="inlineStr">
+        <is>
+          <t>통신설비 설치를 위한 현장점검/정리 상태 확인(기능실: 건축,전기/현장: 노반)</t>
+        </is>
+      </c>
+      <c r="H15" s="60" t="inlineStr">
+        <is>
+          <t>- 통신설비 설치 시 간섭여부 점검
+- 현장 정리상태 점검 (건축마감, 공조, 조명, 전원 등)
+- 장비설치를 위한 자체반입구 및 케이블 설치를 위한 공동구/오프닝 위치 확인</t>
+        </is>
+      </c>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>기록지, 현장점검결과보고서(감리입회)</t>
+        </is>
+      </c>
+      <c r="J15" s="74" t="inlineStr">
+        <is>
+          <t>1) 토목·건축 선행 공정 완료 후 통신 기계실, 케이블 트레이, 관로 인수인계 현장 상태 검측
+2) 바닥 엑세스플로어, 방화 구획 및 기초 구조체 인수인계 확인서 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K15" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>1) 선행 공종 실측 검측: 토목·건축 완료 기계실 바닥 엑세스플로어, 케이블 트레이, 방화 구획 및 랙 기초 상태 검사
+2) 인수인계 승인: 미비 사항 현장 보완 조치 요구 및 통신 시공 적격 선행 공정 인수인계 확인서 최종 승인</t>
+        </is>
+      </c>
+      <c r="M15" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N15" s="74" t="inlineStr">
+        <is>
+          <t>1) 토목 배관 도면 및 건축 구조물 도면을 대조하여 통신기계실 오프닝 위치, 지중관로 규격(Ø100/Ø50) 및 핸드홀 설치 좌표를 사전 검토하였는가?
+2) 토목, 건축, 통신 현장 담당자 3자 공조 체계를 구성하고 현장 합동 점검표, Mandrel 도통시험기 및 레이저 레벨기를 사전 준비하였는가?</t>
+        </is>
+      </c>
+      <c r="O15" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P15" s="68" t="n"/>
+      <c r="Q15" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R15" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S15" s="73" t="n"/>
+    </row>
+    <row r="16" ht="115.2" customHeight="1">
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B16" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-15</t>
+        </is>
+      </c>
+      <c r="E16" s="61" t="inlineStr">
+        <is>
+          <t>장비반입 및 안전교육</t>
+        </is>
+      </c>
+      <c r="F16" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 안전팀</t>
+        </is>
+      </c>
+      <c r="G16" s="60" t="inlineStr">
+        <is>
+          <t>장비 반입 준비 및 안전교육 완료</t>
+        </is>
+      </c>
+      <c r="H16" s="60" t="inlineStr">
+        <is>
+          <t>- 자재반입 경로, 적치장소에 대한 사전확인 및 타분야 일정, 간섭사항 협의/확인
+- 장비 Spec확인, 장비상태 점검
+- 작업원 안전교육 실시</t>
+        </is>
+      </c>
+      <c r="I16" s="61" t="inlineStr">
+        <is>
+          <t>안전교육 결과서, 측량기록지</t>
+        </is>
+      </c>
+      <c r="J16" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 시공 장비 및 차량 반입 전 장비 안전점검 및 작업자 특별안전보건교육 실시
+2) 장비 반입 허가서 작성 및 안전 교육 이수 수료증 관리 표준 적용</t>
+        </is>
+      </c>
+      <c r="K16" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>1) 장비 안전점검: 고소작업차, 광접속 차량 반입 전 안전 검사 및 작업 장비 반입 신청서 검토
+2) 안전 교육 이수: 통신 시공 작업자 대상 특별안전보건교육, 보호구 착용 점검 및 안전 교육 이수 수료 관리</t>
+        </is>
+      </c>
+      <c r="M16" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N16" s="74" t="inlineStr">
+        <is>
+          <t>1) 화물차 반입 도로의 유효 폭(W≥3.5m) 및 지상 가설재 장애물(0cm) 상태를 확인하였는가?
+2) 토목/건축 등 타분야 양중 작업 간섭 여부를 사전 협의하고 양중 시간대를 분리 조율하였는가?</t>
+        </is>
+      </c>
+      <c r="O16" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P16" s="68" t="n"/>
+      <c r="Q16" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R16" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S16" s="73" t="n"/>
+    </row>
+    <row r="17" ht="115.2" customHeight="1">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D17" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-16</t>
+        </is>
+      </c>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>자재 반입 및 검수</t>
+        </is>
+      </c>
+      <c r="F17" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주청/공동감리단</t>
+        </is>
+      </c>
+      <c r="G17" s="60" t="inlineStr">
+        <is>
+          <t>공장검사 시행 완료된 자재반입과 현장 입고 검사</t>
+        </is>
+      </c>
+      <c r="H17" s="60" t="inlineStr">
+        <is>
+          <t>- 자재 하차 위치 및 반입동선 확인
+- 승인된 자재 일치여부 확인(Serial number 등)
+- 제품의 규격, 수량 도면과 일치하는지 검토</t>
+        </is>
+      </c>
+      <c r="I17" s="61" t="inlineStr">
+        <is>
+          <t>자재검수서</t>
+        </is>
+      </c>
+      <c r="J17" s="74" t="inlineStr">
+        <is>
+          <t>1) 현장 반입 통신 자재 및 케이블의 승인 자재 일치성, 수량 및 운반 파손 여부 검수
+2) 자재검수 요청서 작성 및 감리 입회 검수 합격 확인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K17" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>1) 반입 자재 현장 검측: 자재 반입 시 자재공급원 승인품 일치 여부, 운반 외관 파손 및 시리얼 번호 현장 검수
+2) 자재검수 보고: 감리 입회 자재 검수 실시, 자재검수 요청서 결재 및 현장 통신 자재 창고 입고 관리</t>
+        </is>
+      </c>
+      <c r="M17" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N17" s="74" t="inlineStr">
+        <is>
+          <t>1) 시방 대조[도면 및 여건] 자재 하차 위치 및 반입동선 확인 수칙을 사전 대조 확인하였는가?
+2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O17" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P17" s="68" t="n"/>
+      <c r="Q17" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R17" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S17" s="73" t="n"/>
+    </row>
+    <row r="18" ht="115.2" customHeight="1">
+      <c r="A18" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C18" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D18" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-17</t>
+        </is>
+      </c>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>통신설비 반입 및 설치</t>
+        </is>
+      </c>
+      <c r="F18" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 분야별 전담팀</t>
+        </is>
+      </c>
+      <c r="G18" s="60" t="inlineStr">
+        <is>
+          <t>설계에 부합되도록 통신설비 설치</t>
+        </is>
+      </c>
+      <c r="H18" s="62" t="inlineStr">
+        <is>
+          <t>- 시공샘플이 필요한 대상을 감리/감독과 협의하여 선정후 시공검사 실시
+- 현장 선로변 설비, 각종 케이블 포설
+- 기계실 내 서버랙 및 각종 단말장치 설치 (카메라, 인터폰 등)
+- 통신실내 케이블 배선
+- 통신설비가 도면대로 설치되었는지 확인</t>
+        </is>
+      </c>
+      <c r="I18" s="61" t="inlineStr">
+        <is>
+          <t>검측서</t>
+        </is>
+      </c>
+      <c r="J18" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 기계실 랙 설비, 본선 관로 광케이블 포설 및 역무 통신 기기 수평/수직 시공 설치
+2) 케이블 성단, OTDR 접속 및 설비 고정 상태 검측 표준 적용</t>
+        </is>
+      </c>
+      <c r="K18" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>1) 설치 실무 절차: 통신 기계실 랙 고정, 광케이블/UTP 포설, 성단 작업 및 역사 역무 통신 기기 수평/수직 시공
+2) 접속 및 검측: OTDR 접속 손실(≤0.05dB) 측정, 랙 전원 인입 배선 정리 및 설비 고정 상태 감리 검측</t>
+        </is>
+      </c>
+      <c r="M18" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N18" s="74" t="inlineStr">
+        <is>
+          <t>1) 본 시공 착수 전 통신기계실 랙 배선 정돈 및 마킹 표찰 샘플을 감리단과 사전 검측하였는가?
+2) 72-Core 광케이블 융착 접속 트레이 정돈 및 접속 손실 샘플 시공 승인을 획득하였는가?</t>
+        </is>
+      </c>
+      <c r="O18" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P18" s="68" t="n"/>
+      <c r="Q18" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R18" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S18" s="73" t="n"/>
+    </row>
+    <row r="19" ht="115.2" customHeight="1">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-18</t>
+        </is>
+      </c>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>관제설비 설치</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G19" s="60" t="inlineStr">
+        <is>
+          <t>관제설비의 정위치 배치 및 설치</t>
+        </is>
+      </c>
+      <c r="H19" s="62" t="inlineStr">
+        <is>
+          <t>- 랙 베이스/케이블 등 설치 위치를 확인하고 설치후에는 도면과 일치 여부를 체크
+- 철도 교통관제(구로/대전)와 연동할 수 있게 광전송/열차무선 설비 등을 설치하고 확인</t>
+        </is>
+      </c>
+      <c r="I19" s="61" t="inlineStr">
+        <is>
+          <t>검측서</t>
+        </is>
+      </c>
+      <c r="J19" s="74" t="inlineStr">
+        <is>
+          <t>1) 종합관제센터 관제 콘솔, 대형 표시장치(DLP/LFD), 관제 서버 및 네트워크 설비 설치
+2) 관제 시스템 전원 인입, 배선 정리 및 관제 환경 설치 검측 표준 적용</t>
+        </is>
+      </c>
+      <c r="K19" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>1) 관제 환경 설치 절차: 종합관제센터 관제 콘솔 고정, DLP/LFD 대형 화면 설치, 관제 서버 랙 반입 및 배선 정리
+2) 전원 및 계통 검측: 관제 전원 분배기 전원 인입, 이중화 네트워크 케이블 성단 및 관제실 설치 상태 확인</t>
+        </is>
+      </c>
+      <c r="M19" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N19" s="74" t="inlineStr">
+        <is>
+          <t>1) OCC 관제실 전면 비디오 월 마운트 거치 프레임 레이저 수평 오차(±1.0mm 이내)를 실측하였는가?
+2) 멀티 디스플레이 패널 간 베젤 이격 단차(≤0.5mm) 미세 조율 및 방진 가스켓 부착을 완료하였는가?</t>
+        </is>
+      </c>
+      <c r="O19" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P19" s="68" t="n"/>
+      <c r="Q19" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R19" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S19" s="73" t="n"/>
+    </row>
+    <row r="20" ht="115.2" customHeight="1">
+      <c r="A20" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B20" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C20" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-19</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>통신시스템 단위시험</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G20" s="60" t="inlineStr">
+        <is>
+          <t>통신설비(열차에 설치하는 차상통신 장치 포함)설치 후 전원투입 및 기능검증</t>
+        </is>
+      </c>
+      <c r="H20" s="62" t="inlineStr">
+        <is>
+          <t>- ITP/ITC에 따라 시험/검사를 감리 확인</t>
+        </is>
+      </c>
+      <c r="I20" s="61" t="inlineStr">
+        <is>
+          <t>감리단 입회검사 및 시험점검표(ITP/ITC)</t>
+        </is>
+      </c>
+      <c r="J20" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 개별 단위 설비(LTE-R, 방송, CCTV, 역무, 전화 등) 전원 투입 및 단독 시험 실시
+2) 설비별 단위시험 절차서 준수 및 단독 기능 시험성적서 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K20" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>1) 단독 시험 수행: LTE-R 기지국/제어기, 방송, CCTV, 역무, 전화 등 개별 시스템 단위 전원 인입 및 단독 시험
+2) 단위성적서 작성: 단위시험 절차서 항목별 성능 측정, 불합격 항목 보완 조치 및 단위시험 성과표 확정</t>
+        </is>
+      </c>
+      <c r="M20" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N20" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신기계실 LTE-R DU 제어기 및 옥외 RU 무선장치에 단독 전원(220V/48V) 투입 후 부팅 정상 상태를 확인하였는가?
+2) RF 파워메터로 무선장치(RU) 송신 출력을 계측하여 표준 규격(43dBm ±0.5dB) 이내임을 검측하였는가?</t>
+        </is>
+      </c>
+      <c r="O20" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P20" s="68" t="n"/>
+      <c r="Q20" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R20" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S20" s="73" t="n"/>
+    </row>
+    <row r="21" ht="115.2" customHeight="1">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B21" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D21" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-20</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>통신시스템 통합시험</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G21" s="60" t="inlineStr">
+        <is>
+          <t>관제설비를 포함한 통신망 통합 검증</t>
+        </is>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>- 감리단 입회하에 검사/시험절차대로 수행
+1) 관제실/현장설비간 인터페이스 시험
+2) 지상 및 차상 인터페이스 시험</t>
+        </is>
+      </c>
+      <c r="I21" s="61" t="inlineStr">
+        <is>
+          <t>감리단 입회검사 및 시험점검표(ITP/ITC)</t>
+        </is>
+      </c>
+      <c r="J21" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 설비 간 데이터 연동, LTE-R 무선망 백본 이중화 절체 및 종합 네트워크 연동 시험
+2) 통합시험 절차서 준수 및 이종 통신 설비 간 상호 연동성 검측 표준 적용</t>
+        </is>
+      </c>
+      <c r="K21" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>1) 연동 시험 수행: 통신 이종 시스템 간 데이터 연동, LTE-R 코어망 백본 이중화 절체 및 종합 네트워크 연동 시험
+2) 통합 성과 확인: 관제-현장 장치 간 제어 응답속도 검측, 통합 시험 성과표 작성 및 감리 승인 완료</t>
+        </is>
+      </c>
+      <c r="M21" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N21" s="74" t="inlineStr">
+        <is>
+          <t>1) 관제센터 메인 방송 서버와 각 정거장 PIS 제어기 간 광전송 유선 인터페이스 통신 상태를 확인하였는가?
+2) 관제 콘솔에서 PIS 문구 송출 명령 전송 시 현장 안내표시기 반응 지연 시간(≤0.5초 이내)을 검측하였는가?</t>
+        </is>
+      </c>
+      <c r="O21" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P21" s="68" t="n"/>
+      <c r="Q21" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R21" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S21" s="73" t="n"/>
+    </row>
+    <row r="22" ht="115.2" customHeight="1">
+      <c r="A22" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B22" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D22" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-21</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="inlineStr">
+        <is>
+          <t>공종별 시험</t>
+        </is>
+      </c>
+      <c r="F22" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G22" s="60" t="inlineStr">
+        <is>
+          <t>발주처가 관련 법령, 설계기준, 기술기준, 시방서 등의 요구사항에 적합하도록 설치되었는지를 확인</t>
+        </is>
+      </c>
+      <c r="H22" s="60" t="inlineStr">
+        <is>
+          <t>- 철도종합시험운행 시행지침 제6조(공종별시험)에 따라 시행</t>
+        </is>
+      </c>
+      <c r="I22" s="61" t="inlineStr">
+        <is>
+          <t>공종별 시험 결과보고서</t>
+        </is>
+      </c>
+      <c r="J22" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도 종합시험운행 지침에 의거한 통신 공종별 상세 시운전 시험 절차 수립
+2) 공종별 시험 항목 검측, 무선 전계강도 측정 및 시험성적서 확정 표준 적용</t>
+        </is>
+      </c>
+      <c r="K22" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>1) 공종 시운전 절차: 철도 종합시험운행 지침에 따른 통신 공종별 상세 시험 항목(무선 품질, 음성/영상 전송) 실측
+2) 공종 시험 승인: 무선 전계강도 측정 성과표 및 공종별 시운전 시험 결과 보고서 제출 및 감리 승인</t>
+        </is>
+      </c>
+      <c r="M22" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N22" s="74" t="inlineStr">
+        <is>
+          <t>1) 본선 및 정거장 광배선반(FDF) 포설 광케이블 전체 코어에 대하여 OTDR 전수 측정을 수행하였는가?
+2) 광케이블 융착 접속점 접속 손실 수치가 시방 기준(≤0.1dB/접속점 이하)을 통과함을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O22" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P22" s="68" t="n"/>
+      <c r="Q22" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R22" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S22" s="73" t="n"/>
+    </row>
+    <row r="23" ht="115.2" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-22</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>차량 투입 전 점검</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 시공전담팀</t>
+        </is>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>발주처가 원활한 차량시운전이 되도록 노반, 건축, 궤도, 전철전력, 통신, 신호 분야를 종합하여 최종 점검</t>
+        </is>
+      </c>
+      <c r="H23" s="62" t="inlineStr">
+        <is>
+          <t>- 노반/궤도 시공상태 점검
+- 건축한계 및 차량한계 검사
+1) 건축한계: 폭(3,600mm) / 높이(5,300mm)
+2) 차량한계: 폭(3,200mm) / 높이(4,750mm)
+- 전차선, 신호, 통신 작동상태 확인</t>
+        </is>
+      </c>
+      <c r="I23" s="61" t="inlineStr">
+        <is>
+          <t>점검 결과보고서</t>
+        </is>
+      </c>
+      <c r="J23" s="74" t="inlineStr">
+        <is>
+          <t>1) 본선 트램 차량 투입 전 LTE-R 차상 통신장치, 무선 안테나 및 관제 무선 연동태세 점검
+2) 차량 투입 대비 통신 무무선 연동 안전 상태 확인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K23" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L23" s="74" t="inlineStr">
+        <is>
+          <t>1) 차상 연동 점검: 본선 트램 차량 투입 전 차량 차상 LTE-R 통신장비, 무선 안테나 및 관제 무선 연동태세 실측
+2) 투입 안전 승인: 차량 투입 시 무선 통신 끊김 예방 점검 및 차량 투입 전 통신 안전 확인서 작성</t>
+        </is>
+      </c>
+      <c r="M23" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N23" s="74" t="inlineStr">
+        <is>
+          <t>1) 본선 전 구간 궤도변 건축한계 규격(폭 3,100mm / 높이 3,800mm) 내 침범 요소 유무를 실측 확인하였는가?
+2) 궤도 주변 통신 케이블 트레이 및 광점퍼 선로 묶음이 건축한계 이내로 처지거나 돌출되지 않음을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O23" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P23" s="68" t="n"/>
+      <c r="Q23" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R23" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S23" s="73" t="n"/>
+    </row>
+    <row r="24" ht="115.2" customHeight="1">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-23</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>차량 시운전</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G24" s="60" t="inlineStr">
+        <is>
+          <t>철도안전법에 따른 철도차량 형식시험</t>
+        </is>
+      </c>
+      <c r="H24" s="60" t="inlineStr">
+        <is>
+          <t>- 철도안전법 제26조(철도차량 형식승인)에 따라 이행(주로 본선구간 수행)
+- 차량, 신호, 통신 시스템간 인터페이스 시험</t>
+        </is>
+      </c>
+      <c r="I24" s="61" t="inlineStr">
+        <is>
+          <t>철도차량 형식승인 결과 보고서</t>
+        </is>
+      </c>
+      <c r="J24" s="74" t="inlineStr">
+        <is>
+          <t>1) 트램 차량 본선 주행 시 LTE-R 무선 수신강도(RSSI/RSRP), 핸드오버 및 음성/데이터 통신 검측
+2) 주행 중 통신 끊김 여부 및 차상-지상 간 통신 품질 성과표 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K24" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L24" s="74" t="inlineStr">
+        <is>
+          <t>1) 본선 주행 시험: 트램 차량 본선 주행 중 LTE-R 무선 수신강도(RSSI ≥ -95dBm), 핸드오버 성공률(≥99.5%) 실측
+2) 주행 통신 검측: 차상-지상 간 CCTV 영상 전송 및 관제 데이터 무선 통신 품질 성과표 최종 확정</t>
+        </is>
+      </c>
+      <c r="M24" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N24" s="74" t="inlineStr">
+        <is>
+          <t>1) 본선 실 주행 최고 속도 조건에서 LTE-R 차상 단말기 수신 감도(RSSI ≥ -85dBm)를 지속 유지하였는가?
+2) 주행 중 LTE-R 기지국 간 이동 시 핸드오버 성공률 100% 및 음성 무선 통화 끊김 0건을 검측하였는가?</t>
+        </is>
+      </c>
+      <c r="O24" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P24" s="68" t="n"/>
+      <c r="Q24" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R24" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S24" s="73" t="n"/>
+    </row>
+    <row r="25" ht="115.2" customHeight="1">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B25" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-24</t>
+        </is>
+      </c>
+      <c r="E25" s="61" t="inlineStr">
+        <is>
+          <t>운영자 교육시행</t>
+        </is>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G25" s="60" t="inlineStr">
+        <is>
+          <t>영업시운전 전에 시설을 운영자를 대상으로 운영 및 유지관리방법에 대해 교육</t>
+        </is>
+      </c>
+      <c r="H25" s="60" t="inlineStr">
+        <is>
+          <t>- 통신 시스템 제작사가 만든 매뉴얼로 운영자를 교육
+: 관제설비등통신설비 운영/관리방법</t>
+        </is>
+      </c>
+      <c r="I25" s="61" t="inlineStr">
+        <is>
+          <t>운영자 교육 결과서</t>
+        </is>
+      </c>
+      <c r="J25" s="74" t="inlineStr">
+        <is>
+          <t>1) 시설물 인수인계 전 운영사 운영자 및 유지보수 요원 대상 통신 시스템 운영 교육 실시
+2) 교육 교재 작성, 시스템 운용/장해 조치 실습 및 교육 이수 확인서 작성 표준 적용</t>
+        </is>
+      </c>
+      <c r="K25" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L25" s="74" t="inlineStr">
+        <is>
+          <t>1) 교육 프로그램 실시: 운영사 운영자 및 유지관리 요원 대상 통신 시스템 구조, HMI 운용 및 비상 조치 교육
+2) 교육 이수 확정: 현장 실습 교육 수행, 질문/답변 점검 및 운영자 교육 참석 이수 확인서 최종 작성</t>
+        </is>
+      </c>
+      <c r="M25" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N25" s="74" t="inlineStr">
+        <is>
+          <t>1) 통신 4대 계통(교환, 무선, PIS/PA, CCTV) 제작사 공식 기술 매뉴얼을 수집·구비하였는가?
+2) 주요 장비 장애 시 대응할 수 있는 계통별 긴급 비상 조치 매뉴얼 교재를 편찬하였는가?</t>
+        </is>
+      </c>
+      <c r="O25" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P25" s="68" t="n"/>
+      <c r="Q25" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R25" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S25" s="73" t="n"/>
+    </row>
+    <row r="26" ht="115.2" customHeight="1">
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B26" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D26" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-25</t>
+        </is>
+      </c>
+      <c r="E26" s="61" t="inlineStr">
+        <is>
+          <t>사전점검</t>
+        </is>
+      </c>
+      <c r="F26" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G26" s="60" t="inlineStr">
+        <is>
+          <t>시설물검증시험의 가능여부를 확인하기 위하여 발주처와 운영자가 합동으로 점검</t>
+        </is>
+      </c>
+      <c r="H26" s="60" t="inlineStr">
+        <is>
+          <t>- (기준) 철도종합시험운행 시행지침 제8조 "종합시험운행을 위한 사전점검"에 따름
+- 발주처는 공종별 시험을 완료한 후 시설물 검증시험의 가능여부를 확인하기 위하여 사전점검계획을 수립하고 운영자와 합동으로 실시
+- 발주처와 운영자의 사전점검 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)</t>
+        </is>
+      </c>
+      <c r="I26" s="61" t="inlineStr">
+        <is>
+          <t>사전점검 결과보고서/승인문서(한국교통안전공단)</t>
+        </is>
+      </c>
+      <c r="J26" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 지침 제8조에 의거한 사전점검계획 수립 및 기술기준 부합성 종합 점검
+2) 사전점검 결과 보고서 작성 및 한국교통안전공단 제출 승인 표준 적용</t>
+        </is>
+      </c>
+      <c r="K26" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L26" s="74" t="inlineStr">
+        <is>
+          <t>1) 사전점검 수검 절차: 철도종합시험운행 지침 제8조에 의거 사전점검 수행반 구성 및 통신 설비 종합 점검
+2) 점검 결과 승인: 기술기준 부합 여부 사전 검증, 지적사항 조치 완료 및 한국교통안전공단 사전점검 보고서 제출</t>
+        </is>
+      </c>
+      <c r="M26" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N26" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 제8조 규정에 맞춘 사전점검계획서를 작성하였는가?
+2) 발주처, 운영기관, 책임감리단 및 현장소장이 포함된 3자 합동 사전점검반을 조직하였는가?</t>
+        </is>
+      </c>
+      <c r="O26" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P26" s="68" t="n"/>
+      <c r="Q26" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R26" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S26" s="73" t="n"/>
+    </row>
+    <row r="27" ht="153.6" customHeight="1">
+      <c r="A27" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C27" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D27" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-26</t>
+        </is>
+      </c>
+      <c r="E27" s="61" t="inlineStr">
+        <is>
+          <t>시설물 검증시험</t>
+        </is>
+      </c>
+      <c r="F27" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G27" s="60" t="inlineStr">
+        <is>
+          <t>발주처는 시설물의 정상작동 상태 등을 확인하기 위해 시설물 검증시험을 수행</t>
+        </is>
+      </c>
+      <c r="H27" s="60" t="inlineStr">
+        <is>
+          <t>- (기준) 철도종합시험운행 시행지침 제12조(시설물검증시험계획의 수립), 13조(시설물검증시험의 시행)에 따름
+- 발주처는 시설물검증시험계획을 운영자와 협의하여 수립하고 전문기관의 승인을 받은 후 시행
+- 철도종합시험운행 시설물검증시험 점검항목: 시설물의 정상작동 상태, 철도시설의 안전상태, 철도차량의 운행적합성, 철도시설과 차량 간의 연계성
+- 발주처와 운영자의 시설물 검증시험 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)</t>
+        </is>
+      </c>
+      <c r="I27" s="61" t="inlineStr">
+        <is>
+          <t>시설물 검증시험 결과보고서/승인문서(한국교통안전공단)</t>
+        </is>
+      </c>
+      <c r="J27" s="74" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 계획 수립 및 본선 주행 시험 차량을 이용한 통신 설비 최고속도 성능 검증
+2) LTE-R 무선 품질, 관제 데이터 전송률 및 시설물검증 합격 판정 표준 적용</t>
+        </is>
+      </c>
+      <c r="K27" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L27" s="74" t="inlineStr">
+        <is>
+          <t>1) 최고속도 주행 검증: 시설물검증시험 계획에 따라 시운전 열차를 최고 설계속도로 주행하며 통신 성능 실측
+2) 검증 결과 확정: LTE-R 무선망 수신강도, 데이터 전송 지연시간 실측 및 시설물검증시험 합격 판정</t>
+        </is>
+      </c>
+      <c r="M27" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N27" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 제14조에 따라 시설물검증시험계획을 작성하였는가?
+2) 전문기관인 한국교통안전공단으로부터 시설물검증시험계획 적격 승인을 수령하였는가?</t>
+        </is>
+      </c>
+      <c r="O27" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P27" s="68" t="n"/>
+      <c r="Q27" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R27" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S27" s="73" t="n"/>
+    </row>
+    <row r="28" ht="211.2" customHeight="1">
+      <c r="A28" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C28" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D28" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-27</t>
+        </is>
+      </c>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
+          <t>영업시운전</t>
+        </is>
+      </c>
+      <c r="F28" s="61" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G28" s="60" t="inlineStr">
+        <is>
+          <t>발주처는 영업시운전계획에 따라 열차운행체계를 확인하기 위해 영업시운전을 수행</t>
+        </is>
+      </c>
+      <c r="H28" s="62" t="inlineStr">
+        <is>
+          <t>- (기준) 철도종합시험운행 시행지침 제22조(영업시운전계획의 수립), 23조(영업시운전의 시행)에 따름
+- 운영자는 영업시운전계획을 발주처와 협의하여 수립하고 전문기관의 승인을 받은 후 시행
+- 영업시운전 점검항목: 열차운행체계, 철도종사자(운전/관제 등)의 업무숙달, 영업서비스 준비사항
+- 영업조건과 동일한 조건으로 열차운행을 수행하여 운전/영업분야 점검
+- 운영자는 영업시운전 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)
+- 한국교통안전공단은 보고서를 받은 날부터 14일 이내 국토교통부장관에게 보고하여야 하며, 국토부 장관은 검토 결과를 보고를 받은 날부터 7일 이내에 발주처와 시도지사에 통보</t>
+        </is>
+      </c>
+      <c r="I28" s="61" t="inlineStr">
+        <is>
+          <t>영업시운전 결과보고서/승인문서(한국교통안전공단), 국토부 승인문서</t>
+        </is>
+      </c>
+      <c r="J28" s="74" t="inlineStr">
+        <is>
+          <t>1) 실제 영업 조건과 동일한 환경에서의 통신 시스템 연속 가동 및 관제 운용 검증
+2) 영업시운전 기간 중 통신 장애 0건 달성 및 시운전 완료 보고서 확정 표준 적용</t>
+        </is>
+      </c>
+      <c r="K28" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L28" s="74" t="inlineStr">
+        <is>
+          <t>1) 영업환경 가동 검증: 영업 시운전 스케줄에 따른 통신 시스템 24시간 연속 가동 및 관제 시스템 연동 상태 검증
+2) 시운전 준공 확정: 영업시운전 기간 중 통신 장해 0건 달성 및 영업시운전 종합 결과 보고서 확정</t>
+        </is>
+      </c>
+      <c r="M28" s="78" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N28" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 제22조에 따른 영업시운전계획을 수립하였는가?
+2) 전 정거장 행선안내게시기(PIS) 도착 시각 및 열치 위치 안내 오송출 0건을 달성하였는가?</t>
+        </is>
+      </c>
+      <c r="O28" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P28" s="68" t="n"/>
+      <c r="Q28" s="75" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R28" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S28" s="73" t="n"/>
+    </row>
+    <row r="29" ht="115.2" customHeight="1">
+      <c r="A29" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-28</t>
+        </is>
+      </c>
+      <c r="E29" s="61" t="inlineStr">
+        <is>
+          <t>자가용전기통신설비 설치신고</t>
+        </is>
+      </c>
+      <c r="F29" s="61" t="inlineStr">
+        <is>
+          <t>시공사</t>
+        </is>
+      </c>
+      <c r="G29" s="60" t="inlineStr">
+        <is>
+          <t>자가용전기통신설비의 합법적 설치</t>
+        </is>
+      </c>
+      <c r="H29" s="80" t="inlineStr">
+        <is>
+          <t>- 관할 시청/구청에 설치공사 시작 21일 전까지 신고서와 설계도서 제출 (처리기간 15일)</t>
+        </is>
+      </c>
+      <c r="I29" s="61" t="inlineStr">
+        <is>
+          <t>자가전기통신설비 설치신고 필증</t>
+        </is>
+      </c>
+      <c r="J29" s="74" t="inlineStr">
+        <is>
+          <t>1) 전기통신사업법 제64조에 의거한 자가용전기통신설비 설치신고서 및 설비 개요서 작성
+2) 관할 지자체(화성시 등) 제출 및 설치신고 수리증 발급 획득 표준 적용</t>
+        </is>
+      </c>
+      <c r="K29" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L29" s="74" t="inlineStr">
+        <is>
+          <t>1) 신고 서류 작성: 전기통신사업법 제64조에 따른 자가용전기통신설비 설치신고서 및 통신망 개요도 작성
+2) 관할 관청 수리: 관할 지자체(화성시 등) 제출, 현장 서류 검토 수검 및 설치신고 수리증 발급 획득</t>
+        </is>
+      </c>
+      <c r="M29" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N29" s="74" t="inlineStr">
+        <is>
+          <t>1) 시방 대조[도면 및 여건] • 관련법령: 전기통신사업법 제64조 수칙을 사전 대조 확인하였는가?
+2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O29" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P29" s="68" t="n"/>
+      <c r="Q29" s="75" t="inlineStr">
+        <is>
+          <t>● 전기통신사업법 제64조</t>
+        </is>
+      </c>
+      <c r="R29" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S29" s="73" t="n"/>
+    </row>
+    <row r="30" ht="115.2" customHeight="1">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C30" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D30" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-29</t>
+        </is>
+      </c>
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>LTE-R 무선국허가</t>
+        </is>
+      </c>
+      <c r="F30" s="61" t="inlineStr">
+        <is>
+          <t>발주처</t>
+        </is>
+      </c>
+      <c r="G30" s="60" t="inlineStr">
+        <is>
+          <t>무선국 설치 후 사용을 위한 법적 허가 취득</t>
+        </is>
+      </c>
+      <c r="H30" s="64" t="inlineStr">
+        <is>
+          <t>- 무선국(LTE-R) 설치 후 중앙전파관리소에 신청서, 시설개요서, 공사설계서 제출 (처리기간 14일)</t>
+        </is>
+      </c>
+      <c r="I30" s="61" t="inlineStr">
+        <is>
+          <t>무선국허가증</t>
+        </is>
+      </c>
+      <c r="J30" s="74" t="inlineStr">
+        <is>
+          <t>1) 전파법 제19조에 의거한 철도무선통신망(LTE-R) 무선국 개설허가 신청서 제출
+2) KCA(한국방송통신전파진흥원) 제출 및 무선국 개설허가서 획득 표준 적용</t>
+        </is>
+      </c>
+      <c r="K30" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L30" s="74" t="inlineStr">
+        <is>
+          <t>1) 허가 신청 절차: 전파법 제19조에 따른 LTE-R 무선국 개설허가 신청서, 안테나 제원표 및 기지국 좌표 작성
+2) 무선국 허가 획득: KCA(한국방송통신전파진흥원) 서류 심사 수검 및 무선국 개설허가서 최종 발급</t>
+        </is>
+      </c>
+      <c r="M30" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N30" s="74" t="inlineStr">
+        <is>
+          <t>1) 철도무선통신망 700MHz 대역(718~728MHz/773~783MHz) 주파수 할당 조건을 확인하였는가?
+2) 본선 지상 기지국 안테나 설치 위치, 높이, 이득(dBi) 및 지향각 제원을 조사하였는가?</t>
+        </is>
+      </c>
+      <c r="O30" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P30" s="68" t="n"/>
+      <c r="Q30" s="75" t="inlineStr">
+        <is>
+          <t>● 전파법 제19조</t>
+        </is>
+      </c>
+      <c r="R30" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S30" s="73" t="n"/>
+    </row>
+    <row r="31" ht="115.2" customHeight="1">
+      <c r="A31" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D31" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-30</t>
+        </is>
+      </c>
+      <c r="E31" s="61" t="inlineStr">
+        <is>
+          <t>LTE-R 상호운용성 및 보안적합성 검증</t>
+        </is>
+      </c>
+      <c r="F31" s="61" t="inlineStr">
+        <is>
+          <t>시공사</t>
+        </is>
+      </c>
+      <c r="G31" s="60" t="inlineStr">
+        <is>
+          <t>무선 장비의 보안성 및 타 기관 상호운용성 검증</t>
+        </is>
+      </c>
+      <c r="H31" s="64" t="inlineStr">
+        <is>
+          <t>- 한국정보통신기술협회에 시험결과서 제출하여 검증 진행 (처리기간 1개월)</t>
+        </is>
+      </c>
+      <c r="I31" s="61" t="inlineStr">
+        <is>
+          <t>상호운용성,보안적합성 시험 인증서</t>
+        </is>
+      </c>
+      <c r="J31" s="74" t="inlineStr">
+        <is>
+          <t>1) 국토교통부 지침 및 국가용 보안요구사항에 의거한 LTE-R 상호운용성/보안적합성 검증
+2) 국가정보원/KISA 보안 적합성 검증 승인서 및 상호연동 시험 합격 표준 적용</t>
+        </is>
+      </c>
+      <c r="K31" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L31" s="74" t="inlineStr">
+        <is>
+          <t>1) 검증 시험 절차: 국토교통부 LTE-R 상호운용성 시험 및 국가용 보안요구사항 기반 네트워크 보안적합성 검증
+2) 보안 승인 획득: KISA/국가정보원 보안 적합성 검증 수검 및 상호운용성 검증 합격 승인서 획득</t>
+        </is>
+      </c>
+      <c r="M31" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N31" s="74" t="inlineStr">
+        <is>
+          <t>1) 시방 대조[도면 및 여건] 관련법령: 국가철도공단 표준규격(KRSA) 수칙을 사전 대조 확인하였는가?
+2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O31" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P31" s="68" t="n"/>
+      <c r="Q31" s="75" t="inlineStr">
+        <is>
+          <t>● 국가철도공단 표준규격(KRSA) 5007-R3 / 5008-R2</t>
+        </is>
+      </c>
+      <c r="R31" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S31" s="73" t="n"/>
+    </row>
+    <row r="32" ht="115.2" customHeight="1">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C32" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D32" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-31</t>
+        </is>
+      </c>
+      <c r="E32" s="61" t="inlineStr">
+        <is>
+          <t>정보통신사용전검사</t>
+        </is>
+      </c>
+      <c r="F32" s="61" t="inlineStr">
+        <is>
+          <t>시공사</t>
+        </is>
+      </c>
+      <c r="G32" s="60" t="inlineStr">
+        <is>
+          <t>시공 완료된 정보통신설비의 준공 전 사용 적합성 검증</t>
+        </is>
+      </c>
+      <c r="H32" s="64" t="inlineStr">
+        <is>
+          <t>- 관할 시청/구청에 사용전검사 신청서와 준공설계도서 제출 (처리기간 14일)</t>
+        </is>
+      </c>
+      <c r="I32" s="61" t="inlineStr">
+        <is>
+          <t>정보통신사용전검사 필증</t>
+        </is>
+      </c>
+      <c r="J32" s="74" t="inlineStr">
+        <is>
+          <t>1) 정보통신공사업법 제36조에 의거한 구내 통신 및 정보통신설비 사용전검사 신청
+2) 관할 지자체 현장 검측 수검 및 정보통신 사용전검사 필증 획득 표준 적용</t>
+        </is>
+      </c>
+      <c r="K32" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L32" s="74" t="inlineStr">
+        <is>
+          <t>1) 사용전검사 신청: 정보통신공사업법 제36조에 따른 구내 통신 설비 사용전검측 신청서 작성 및 현장 준비
+2) 필증 발급 획득: 관할 지자체 정보통신 검측 공무원 현장 실측 수검 및 정보통신 사용전검사 필증 획득</t>
+        </is>
+      </c>
+      <c r="M32" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N32" s="74" t="inlineStr">
+        <is>
+          <t>1) 구내 UTP 랜선 전수에 대해 케이블 테스터 계측 Pass 100%를 달성하였는가?
+2) 정거장 승강장 및 관제동 배관 입상부 배관 씰링 및 네임택 표기 상태를 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O32" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P32" s="68" t="n"/>
+      <c r="Q32" s="75" t="inlineStr">
+        <is>
+          <t>● 정보통신공사법 제36조</t>
+        </is>
+      </c>
+      <c r="R32" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S32" s="73" t="n"/>
+    </row>
+    <row r="33" ht="115.2" customHeight="1">
+      <c r="A33" s="61" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="inlineStr">
+        <is>
+          <t>9000-2</t>
+        </is>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>통신분야</t>
+        </is>
+      </c>
+      <c r="D33" s="61" t="inlineStr">
+        <is>
+          <t>9000-2-32</t>
+        </is>
+      </c>
+      <c r="E33" s="61" t="inlineStr">
+        <is>
+          <t>LTE-R 무선국 준공검사</t>
+        </is>
+      </c>
+      <c r="F33" s="61" t="inlineStr">
+        <is>
+          <t>발주처</t>
+        </is>
+      </c>
+      <c r="G33" s="60" t="inlineStr">
+        <is>
+          <t>무선국 전파 특성 검증 및 준공 처리</t>
+        </is>
+      </c>
+      <c r="H33" s="64" t="inlineStr">
+        <is>
+          <t>- 한국방송통신전파진흥원에 준공신고서, 안테나전력/주파수편차/불요발사강도 측정표, 안테나 Pattern 도표 제출 (처리기간 14일)</t>
+        </is>
+      </c>
+      <c r="I33" s="61" t="inlineStr">
+        <is>
+          <t>LTE-R 무선국 준공검사 확인서</t>
+        </is>
+      </c>
+      <c r="J33" s="74" t="inlineStr">
+        <is>
+          <t>1) 전파법 제24조에 의거한 KCA 무선국 준공검사 현장 실측 수검 실시
+2) 무선 전계강도 및 준공 상태 검사 합격 후 무선국 준공검사 합격증명서 획득 표준 적용</t>
+        </is>
+      </c>
+      <c r="K33" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L33" s="74" t="inlineStr">
+        <is>
+          <t>1) KCA 준공검측 수검: 전파법 제24조에 따른 KCA 무선국 준공검사 현장 무선 전계강도 및 스펙트럼 실측
+2) 합격 증명 획득: 준공 실측 합격 판정 수검 및 KCA 무선국 준공검사 합격증명서 최종 발급 획득</t>
+        </is>
+      </c>
+      <c r="M33" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N33" s="74" t="inlineStr">
+        <is>
+          <t>1) 전파법 시행령 제38조 서식에 맞춘 무선국 준공신고서를 KCA에 제출하였는가?
+2) 개설허가서 사본, 기지국 시공 내역서 및 안테나 제원표 구비를 완료하였는가?</t>
+        </is>
+      </c>
+      <c r="O33" s="67" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P33" s="68" t="n"/>
+      <c r="Q33" s="75" t="inlineStr">
+        <is>
+          <t>● 전파법 제24조</t>
+        </is>
+      </c>
+      <c r="R33" s="76" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S33" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId96"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FFFFFF00"/>
@@ -5140,7 +8562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet10">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10959,6 +14381,1833 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="125" t="inlineStr">
+        <is>
+          <t>■ 매뉴얼_공통_사전준비_지반조사(기술형)</t>
+        </is>
+      </c>
+      <c r="B1" s="126" t="n"/>
+      <c r="C1" s="126" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="127" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B2" s="128" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C2" s="128" t="inlineStr">
+        <is>
+          <t>시점(When)</t>
+        </is>
+      </c>
+      <c r="D2" s="124" t="n"/>
+      <c r="E2" s="127" t="inlineStr">
+        <is>
+          <t>목적(Why)</t>
+        </is>
+      </c>
+      <c r="F2" s="127" t="inlineStr">
+        <is>
+          <t>Activity
+방법(How)</t>
+        </is>
+      </c>
+      <c r="G2" s="127" t="inlineStr">
+        <is>
+          <t>주관부서(Who)</t>
+        </is>
+      </c>
+      <c r="H2" s="127" t="inlineStr">
+        <is>
+          <t>협업부서</t>
+        </is>
+      </c>
+      <c r="I2" s="127" t="inlineStr">
+        <is>
+          <t>산출물(What)</t>
+        </is>
+      </c>
+      <c r="J2" s="127" t="inlineStr">
+        <is>
+          <t>수행지침</t>
+        </is>
+      </c>
+      <c r="K2" s="127" t="inlineStr">
+        <is>
+          <t>표준서</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="158" t="n"/>
+      <c r="C3" s="129" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D3" s="129" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="130" t="inlineStr">
+        <is>
+          <t>공통_사전준비_지반조사(기술형)</t>
+        </is>
+      </c>
+      <c r="B4" s="123" t="n"/>
+      <c r="C4" s="123" t="n"/>
+      <c r="D4" s="123" t="n"/>
+      <c r="E4" s="123" t="n"/>
+      <c r="F4" s="123" t="n"/>
+      <c r="G4" s="123" t="n"/>
+      <c r="H4" s="123" t="n"/>
+      <c r="I4" s="123" t="n"/>
+      <c r="J4" s="123" t="n"/>
+      <c r="K4" s="124" t="n"/>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="132" t="inlineStr"/>
+      <c r="B5" s="133" t="inlineStr">
+        <is>
+          <t>발주처 계획 입수(비공식)</t>
+        </is>
+      </c>
+      <c r="C5" s="134" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="D5" s="135" t="inlineStr"/>
+      <c r="E5" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 사전 검토</t>
+        </is>
+      </c>
+      <c r="F5" s="136" t="inlineStr">
+        <is>
+          <t>• 조사설계 용역 기본계획 도서 확보 여부 확인
+• 핵심이슈 (미시추 사유, 지층/암반등급 조정여부 등) 확보 여부 확인
+• 사업지 연접 지질/지반조사 자료 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="G5" s="137" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="H5" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체, 외부지질전문가 3인이상</t>
+        </is>
+      </c>
+      <c r="I5" s="138" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 보고서</t>
+        </is>
+      </c>
+      <c r="J5" s="132" t="inlineStr"/>
+      <c r="K5" s="132" t="inlineStr"/>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="139" t="inlineStr"/>
+      <c r="B6" s="140" t="inlineStr">
+        <is>
+          <t>관심프로젝트 선정</t>
+        </is>
+      </c>
+      <c r="C6" s="141" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="inlineStr"/>
+      <c r="E6" s="142" t="inlineStr">
+        <is>
+          <t>입수된 발주정보 평가를 통한 관심 Project 선정</t>
+        </is>
+      </c>
+      <c r="F6" s="142" t="inlineStr">
+        <is>
+          <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행
+• 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
+        </is>
+      </c>
+      <c r="G6" s="143" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="H6" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I6" s="144" t="inlineStr">
+        <is>
+          <t>관심사업 List</t>
+        </is>
+      </c>
+      <c r="J6" s="139" t="inlineStr"/>
+      <c r="K6" s="139" t="inlineStr"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="133" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 모니터링</t>
+        </is>
+      </c>
+      <c r="C7" s="134" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="D7" s="135" t="inlineStr"/>
+      <c r="E7" s="136" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 수립업체 파악</t>
+        </is>
+      </c>
+      <c r="F7" s="136" t="inlineStr">
+        <is>
+          <t>• 발주처 지반조사업체 확인 후 당사 Pool List와 비교
+• 발주처 지반조사 업체 확인팀 Contact Point 확보</t>
+        </is>
+      </c>
+      <c r="G7" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H7" s="137" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="I7" s="138" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 수행 List + Contact Point List</t>
+        </is>
+      </c>
+      <c r="J7" s="132" t="inlineStr"/>
+      <c r="K7" s="132" t="inlineStr"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="140" t="inlineStr">
+        <is>
+          <t>외부 지질전문가 Pool 관리</t>
+        </is>
+      </c>
+      <c r="C8" s="141" t="inlineStr">
+        <is>
+          <t>매년 1분기</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="inlineStr"/>
+      <c r="E8" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리</t>
+        </is>
+      </c>
+      <c r="F8" s="142" t="inlineStr">
+        <is>
+          <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성
+• 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
+        </is>
+      </c>
+      <c r="G8" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H8" s="143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="144" t="inlineStr">
+        <is>
+          <t>외부지질전문가 Pool List</t>
+        </is>
+      </c>
+      <c r="J8" s="139" t="inlineStr"/>
+      <c r="K8" s="139" t="inlineStr"/>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="133" t="inlineStr">
+        <is>
+          <t>지반조사 Pool 관리</t>
+        </is>
+      </c>
+      <c r="C9" s="134" t="inlineStr">
+        <is>
+          <t>매년 1분기</t>
+        </is>
+      </c>
+      <c r="D9" s="135" t="inlineStr"/>
+      <c r="E9" s="136" t="inlineStr">
+        <is>
+          <t>발주처 계획 대응 및 개략 지반조사 결과 사전 예측을 위한 업체 관리</t>
+        </is>
+      </c>
+      <c r="F9" s="136" t="inlineStr">
+        <is>
+          <t>• 공공기관별 입찰공고 모니터링 통한 지반조사업체 입찰참여 유치(입찰 공사 여부 확인)
+• 업체 Pool List 갱신 여부 확인
+• 지반조사업체 역량 및 기술수준 평가표 평가 여부 확인 (Pool 갱신 및 신규업체 등록)
+• 조사업체 강점, 장비보유 확인
+• 조사업체 Network 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="G9" s="137" t="inlineStr">
+        <is>
+          <t>외주구매팀</t>
+        </is>
+      </c>
+      <c r="H9" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I9" s="138" t="inlineStr">
+        <is>
+          <t>조사업체 POOL/필요시 Update</t>
+        </is>
+      </c>
+      <c r="J9" s="132" t="inlineStr"/>
+      <c r="K9" s="132" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="139" t="inlineStr"/>
+      <c r="B10" s="140" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 자료 및 R/O 정보 입수</t>
+        </is>
+      </c>
+      <c r="C10" s="141" t="inlineStr">
+        <is>
+          <t>D-210</t>
+        </is>
+      </c>
+      <c r="D10" s="141" t="inlineStr">
+        <is>
+          <t>D-180</t>
+        </is>
+      </c>
+      <c r="E10" s="142" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 및 지반조사 결과 사전 획득</t>
+        </is>
+      </c>
+      <c r="F10" s="142" t="inlineStr">
+        <is>
+          <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
+        </is>
+      </c>
+      <c r="G10" s="143" t="inlineStr">
+        <is>
+          <t>지반조사 협력업체</t>
+        </is>
+      </c>
+      <c r="H10" s="143" t="inlineStr">
+        <is>
+          <t>설계 협력업체</t>
+        </is>
+      </c>
+      <c r="I10" s="144" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
+        </is>
+      </c>
+      <c r="J10" s="139" t="inlineStr"/>
+      <c r="K10" s="139" t="inlineStr"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="132" t="inlineStr"/>
+      <c r="B11" s="133" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 R/O 검토 (설계, 공정, 기획)</t>
+        </is>
+      </c>
+      <c r="C11" s="134" t="inlineStr">
+        <is>
+          <t>D-180</t>
+        </is>
+      </c>
+      <c r="D11" s="135" t="inlineStr">
+        <is>
+          <t>D-165</t>
+        </is>
+      </c>
+      <c r="E11" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 지반조사 문제점 검토</t>
+        </is>
+      </c>
+      <c r="F11" s="136" t="inlineStr">
+        <is>
+          <t>• 시추조사 위치, 수량 적정성 검토
+• 지질이상 구간 상세 조사 여부 및 적정성 검토 확인
+• 미시추 구간 지반 특성 적정성 검토확인 (측점 검토, 위치 및 물량검토)
+• 인근 사업 지반조사자료 비교 통해 당사 지반특성 분석 결과 Cross-check 확인</t>
+        </is>
+      </c>
+      <c r="G11" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀(설계)
+토목수행팀(공정)
+토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="H11" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="I11" s="138" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 검토서(설계, 공정, 기획)</t>
+        </is>
+      </c>
+      <c r="J11" s="132" t="inlineStr"/>
+      <c r="K11" s="132" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="140" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 R/O 종합검토 (원가)</t>
+        </is>
+      </c>
+      <c r="C12" s="141" t="inlineStr">
+        <is>
+          <t>D-165</t>
+        </is>
+      </c>
+      <c r="D12" s="141" t="inlineStr">
+        <is>
+          <t>D-150</t>
+        </is>
+      </c>
+      <c r="E12" s="142" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 문제점 R/O 분석</t>
+        </is>
+      </c>
+      <c r="F12" s="142" t="inlineStr">
+        <is>
+          <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
+        </is>
+      </c>
+      <c r="G12" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="H12" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀(설계)
+토목수행팀(공정)
+토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I12" s="144" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 개략 검토서</t>
+        </is>
+      </c>
+      <c r="J12" s="139" t="inlineStr"/>
+      <c r="K12" s="139" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 업체 선정</t>
+        </is>
+      </c>
+      <c r="C13" s="135" t="inlineStr">
+        <is>
+          <t>D-150</t>
+        </is>
+      </c>
+      <c r="D13" s="135" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+      <c r="E13" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 Pool 내 최적의 업체 선정</t>
+        </is>
+      </c>
+      <c r="F13" s="136" t="inlineStr">
+        <is>
+          <t>• 지반조사업체 Pool/실적 검토 및 공종별 적합성 정합 및 견적 본부 연계 검토</t>
+        </is>
+      </c>
+      <c r="G13" s="137" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H13" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I13" s="138" t="inlineStr">
+        <is>
+          <t>지반조사 입찰 참여 Pool</t>
+        </is>
+      </c>
+      <c r="J13" s="132" t="inlineStr"/>
+      <c r="K13" s="132" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="139" t="inlineStr"/>
+      <c r="B14" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 업체 계약</t>
+        </is>
+      </c>
+      <c r="C14" s="141" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+      <c r="D14" s="141" t="inlineStr">
+        <is>
+          <t>D-120</t>
+        </is>
+      </c>
+      <c r="E14" s="142" t="inlineStr">
+        <is>
+          <t>지반조사업체 용역 계약</t>
+        </is>
+      </c>
+      <c r="F14" s="142" t="inlineStr">
+        <is>
+          <t>• 일반구매시스템을 이용한 용역계약</t>
+        </is>
+      </c>
+      <c r="G14" s="143" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H14" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I14" s="144" t="inlineStr">
+        <is>
+          <t>지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="J14" s="139" t="inlineStr"/>
+      <c r="K14" s="139" t="inlineStr"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="147" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치검토</t>
+        </is>
+      </c>
+      <c r="C15" s="148" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+      <c r="D15" s="148" t="inlineStr">
+        <is>
+          <t>D-115</t>
+        </is>
+      </c>
+      <c r="E15" s="149" t="inlineStr">
+        <is>
+          <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정</t>
+        </is>
+      </c>
+      <c r="F15" s="149" t="inlineStr">
+        <is>
+          <t>• 현장답사 수행
+• 공종별 실시설계에 준하여 수량 및 위치 검토</t>
+        </is>
+      </c>
+      <c r="G15" s="150" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H15" s="150" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="I15" s="151" t="inlineStr">
+        <is>
+          <t>지반조사 계획서</t>
+        </is>
+      </c>
+      <c r="J15" s="146" t="inlineStr"/>
+      <c r="K15" s="146" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="147" t="inlineStr">
+        <is>
+          <t>지반조사계획 적정성 심사의뢰</t>
+        </is>
+      </c>
+      <c r="C16" s="148" t="inlineStr">
+        <is>
+          <t>D-115</t>
+        </is>
+      </c>
+      <c r="D16" s="148" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+      <c r="E16" s="149" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치 적정성 검토</t>
+        </is>
+      </c>
+      <c r="F16" s="149" t="inlineStr">
+        <is>
+          <t>• 지반조사 계획서 검토 및 검토</t>
+        </is>
+      </c>
+      <c r="G16" s="150" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H16" s="150" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I16" s="151" t="inlineStr">
+        <is>
+          <t>지반조사계획 의견서</t>
+        </is>
+      </c>
+      <c r="J16" s="146" t="inlineStr"/>
+      <c r="K16" s="146" t="inlineStr"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="132" t="inlineStr"/>
+      <c r="B17" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 인허가</t>
+        </is>
+      </c>
+      <c r="C17" s="135" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+      <c r="D17" s="135" t="inlineStr">
+        <is>
+          <t>D-100</t>
+        </is>
+      </c>
+      <c r="E17" s="136" t="inlineStr">
+        <is>
+          <t>지반조사 수행을 위한 인허가 승인</t>
+        </is>
+      </c>
+      <c r="F17" s="136" t="inlineStr">
+        <is>
+          <t>• 산지일시사용 신고(사업계획서, 지형도, 산지일시사용예정실측도, 복구계획서, 복지봉투)
+• 굴착행위 신고(굴착행위신고서, 위치 또는 평면도, 원상복구계획서, 토지사용 승낙서)
+• 하천점용 허가(위치도, 이해관계인 동의서, 수리계산서, 하천점용등, 사업자등록증)</t>
+        </is>
+      </c>
+      <c r="G17" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H17" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I17" s="138" t="inlineStr">
+        <is>
+          <t>인허가 서류</t>
+        </is>
+      </c>
+      <c r="J17" s="132" t="inlineStr"/>
+      <c r="K17" s="132" t="inlineStr"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="139" t="inlineStr"/>
+      <c r="B18" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치 보완</t>
+        </is>
+      </c>
+      <c r="C18" s="141" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+      <c r="D18" s="141" t="inlineStr">
+        <is>
+          <t>D-100</t>
+        </is>
+      </c>
+      <c r="E18" s="142" t="inlineStr">
+        <is>
+          <t>외부지질전문가 의견을 반영한 지반조사 계획 확정</t>
+        </is>
+      </c>
+      <c r="F18" s="142" t="inlineStr">
+        <is>
+          <t>• 외부지질전문가 지반조사 의견 검토
+• 입찰설계 지반조사 계획 보완</t>
+        </is>
+      </c>
+      <c r="G18" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H18" s="143" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상, 지반조사업체</t>
+        </is>
+      </c>
+      <c r="I18" s="144" t="inlineStr">
+        <is>
+          <t>지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="J18" s="139" t="inlineStr"/>
+      <c r="K18" s="139" t="inlineStr"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="147" t="inlineStr">
+        <is>
+          <t>지반조사 수행</t>
+        </is>
+      </c>
+      <c r="C19" s="148" t="inlineStr">
+        <is>
+          <t>D-100</t>
+        </is>
+      </c>
+      <c r="D19" s="148" t="inlineStr">
+        <is>
+          <t>D-50</t>
+        </is>
+      </c>
+      <c r="E19" s="149" t="inlineStr">
+        <is>
+          <t>과업구간 지반여건 상세 파악</t>
+        </is>
+      </c>
+      <c r="F19" s="149" t="inlineStr">
+        <is>
+          <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등)
+• 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등)
+• 실내시험 수행(요동시험, 입도시험 등)</t>
+        </is>
+      </c>
+      <c r="G19" s="150" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H19" s="150" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I19" s="151" t="inlineStr">
+        <is>
+          <t>지반조사 보고서, 시추 Core 및 샘플</t>
+        </is>
+      </c>
+      <c r="J19" s="146" t="inlineStr"/>
+      <c r="K19" s="146" t="inlineStr"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="147" t="inlineStr">
+        <is>
+          <t>지반조사 수렴 결과 분석</t>
+        </is>
+      </c>
+      <c r="C20" s="148" t="inlineStr">
+        <is>
+          <t>D-50</t>
+        </is>
+      </c>
+      <c r="D20" s="148" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="E20" s="149" t="inlineStr">
+        <is>
+          <t>지반조사 결과 오류 및 지반정수의 적합성 검토</t>
+        </is>
+      </c>
+      <c r="F20" s="149" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 보고서 검토
+• 시추조사 위치 및 심도의 적정성 검토
+• 실내시험 결과 등급 적정성 검토
+• 실시설계시 추가지반조사 필요구간 검토</t>
+        </is>
+      </c>
+      <c r="G20" s="150" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H20" s="150" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀, 지반조사업체</t>
+        </is>
+      </c>
+      <c r="I20" s="151" t="inlineStr">
+        <is>
+          <t>지반조사 결과 분석 의견서</t>
+        </is>
+      </c>
+      <c r="J20" s="146" t="inlineStr"/>
+      <c r="K20" s="146" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="132" t="inlineStr"/>
+      <c r="B21" s="145" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="C21" s="135" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="D21" s="135" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="E21" s="136" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="F21" s="136" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="G21" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가)
+토목수행팀(공정)
+토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="H21" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I21" s="138" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="J21" s="132" t="inlineStr"/>
+      <c r="K21" s="132" t="inlineStr"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 결과 R/O 종합검토</t>
+        </is>
+      </c>
+      <c r="C22" s="141" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="D22" s="141" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="E22" s="142" t="inlineStr">
+        <is>
+          <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정</t>
+        </is>
+      </c>
+      <c r="F22" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 R/O별 Cost effect 분석
+• 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
+        </is>
+      </c>
+      <c r="G22" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H22" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가)
+토목수행팀(공정)
+토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I22" s="144" t="inlineStr">
+        <is>
+          <t>입찰설계 R/O 검토서</t>
+        </is>
+      </c>
+      <c r="J22" s="139" t="inlineStr"/>
+      <c r="K22" s="139" t="inlineStr"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="132" t="inlineStr"/>
+      <c r="B23" s="145" t="inlineStr">
+        <is>
+          <t>REM 수립</t>
+        </is>
+      </c>
+      <c r="C23" s="135" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="D23" s="135" t="inlineStr">
+        <is>
+          <t>D-20</t>
+        </is>
+      </c>
+      <c r="E23" s="136" t="inlineStr">
+        <is>
+          <t>REM 차트 작성(회사의 Core Risk, T/C 공정검토 결과, 경쟁사 동향, 발주 경향) 및 보고</t>
+        </is>
+      </c>
+      <c r="F23" s="136" t="inlineStr">
+        <is>
+          <t>• Risk Profiling/Merge 방안 검토
+• 공정 착공성 검토 및 T/C 검토
+• 설계차별화 및 Idea Frame 검토</t>
+        </is>
+      </c>
+      <c r="G23" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H23" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀, 토목사업지원팀</t>
+        </is>
+      </c>
+      <c r="I23" s="138" t="inlineStr">
+        <is>
+          <t>REM 회의록</t>
+        </is>
+      </c>
+      <c r="J23" s="132" t="inlineStr"/>
+      <c r="K23" s="132" t="inlineStr"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="139" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="140" t="inlineStr">
+        <is>
+          <t>추가지반조사 계획 수립</t>
+        </is>
+      </c>
+      <c r="C24" s="141" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="D24" s="141" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="E24" s="142" t="inlineStr">
+        <is>
+          <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출</t>
+        </is>
+      </c>
+      <c r="F24" s="142" t="inlineStr">
+        <is>
+          <t>• 지반조사 수렴 결과 분석보고서 검토
+• 지반조사 결과 R/O 종합검토 결과 검토</t>
+        </is>
+      </c>
+      <c r="G24" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H24" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가)
+토목수행팀(공정)
+토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I24" s="144" t="inlineStr">
+        <is>
+          <t>추가지반조사 List</t>
+        </is>
+      </c>
+      <c r="J24" s="139" t="inlineStr"/>
+      <c r="K24" s="139" t="inlineStr"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="132" t="inlineStr"/>
+      <c r="B25" s="145" t="inlineStr">
+        <is>
+          <t>3D GPR탐사 장비 사양(차량형) 검토</t>
+        </is>
+      </c>
+      <c r="C25" s="135" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="D25" s="135" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="E25" s="136" t="inlineStr">
+        <is>
+          <t>적정 추가지반조사 규명을 위한 장비 사양 검토</t>
+        </is>
+      </c>
+      <c r="F25" s="136" t="inlineStr">
+        <is>
+          <t>• 3D GPR탐사 장비 사양(차량형)
+- 3D Radar(노르웨이)_200~3000Hz, 2.0m~3.0m : 하상도 높음
+- MIRA(스웨덴)_400~1300Hz, 1.0m~2.0m : 정밀한 입체 형상
+- StreamC(이탈리아)_200~600Hz, 1.5m~3.0m : 다양한 심도, 공동 탐지
+- VGPR(호주)_100~4000Hz, 2.0m~3.0m : 고속주행 데이터 획득
+- Road 3D(한국)_200~3000Hz, 2.0m~3.0m : 하상도 높음, 유용특화</t>
+        </is>
+      </c>
+      <c r="G25" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="H25" s="137" t="inlineStr">
+        <is>
+          <t>현장 공사팀</t>
+        </is>
+      </c>
+      <c r="I25" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="132" t="inlineStr"/>
+      <c r="K25" s="132" t="inlineStr"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="139" t="inlineStr"/>
+      <c r="B26" s="140" t="inlineStr">
+        <is>
+          <t>ECRM 수립</t>
+        </is>
+      </c>
+      <c r="C26" s="141" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="D26" s="141" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="E26" s="142" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="F26" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="G26" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가)</t>
+        </is>
+      </c>
+      <c r="H26" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀, 토목수행팀, 토목사업지원팀</t>
+        </is>
+      </c>
+      <c r="I26" s="144" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="J26" s="139" t="inlineStr"/>
+      <c r="K26" s="139" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="132" t="inlineStr"/>
+      <c r="B27" s="145" t="inlineStr">
+        <is>
+          <t>최종 Cost 검토 / 입찰</t>
+        </is>
+      </c>
+      <c r="C27" s="135" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="D27" s="135" t="inlineStr">
+        <is>
+          <t>D-0</t>
+        </is>
+      </c>
+      <c r="E27" s="136" t="inlineStr">
+        <is>
+          <t>입찰</t>
+        </is>
+      </c>
+      <c r="F27" s="136" t="inlineStr">
+        <is>
+          <t>• 최종 R/O를 반영한 투찰내역서 작성</t>
+        </is>
+      </c>
+      <c r="G27" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="H27" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="138" t="inlineStr">
+        <is>
+          <t>투찰내역서</t>
+        </is>
+      </c>
+      <c r="J27" s="132" t="inlineStr"/>
+      <c r="K27" s="132" t="inlineStr"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="153" t="inlineStr">
+        <is>
+          <t>입찰설계 현장 인수인계</t>
+        </is>
+      </c>
+      <c r="C28" s="154" t="inlineStr">
+        <is>
+          <t>D+0</t>
+        </is>
+      </c>
+      <c r="D28" s="154" t="inlineStr">
+        <is>
+          <t>D+30</t>
+        </is>
+      </c>
+      <c r="E28" s="155" t="inlineStr">
+        <is>
+          <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유</t>
+        </is>
+      </c>
+      <c r="F28" s="155" t="inlineStr">
+        <is>
+          <t>• 최종 R/O 결과 및 입찰도서 인출</t>
+        </is>
+      </c>
+      <c r="G28" s="156" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H28" s="156" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="I28" s="157" t="inlineStr">
+        <is>
+          <t>인수인계서</t>
+        </is>
+      </c>
+      <c r="J28" s="152" t="inlineStr"/>
+      <c r="K28" s="152" t="inlineStr"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="146" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B29" s="147" t="inlineStr">
+        <is>
+          <t>추가지반조사 수행</t>
+        </is>
+      </c>
+      <c r="C29" s="148" t="inlineStr">
+        <is>
+          <t>D+30</t>
+        </is>
+      </c>
+      <c r="D29" s="148" t="inlineStr">
+        <is>
+          <t>D+100</t>
+        </is>
+      </c>
+      <c r="E29" s="149" t="inlineStr">
+        <is>
+          <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge</t>
+        </is>
+      </c>
+      <c r="F29" s="149" t="inlineStr">
+        <is>
+          <t>• 추가 지반조사 계획 및 시점 확인
+- 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인)
+- 추가시추조사 수행(물리탐사, 시추조사)
+- 토질 및 암석 실내시험 수행 및 결과분석 확인
+- 공종별 핵심시설(교량, 접속도로, 토공, #200m 통과점, 터널 발파/심벽진입) 확인</t>
+        </is>
+      </c>
+      <c r="G29" s="150" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H29" s="150" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
+        </is>
+      </c>
+      <c r="I29" s="151" t="inlineStr">
+        <is>
+          <t>추가 지반조사 보고서</t>
+        </is>
+      </c>
+      <c r="J29" s="146" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K29" s="146" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="146" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="147" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과 분석</t>
+        </is>
+      </c>
+      <c r="C30" s="148" t="inlineStr">
+        <is>
+          <t>D+100</t>
+        </is>
+      </c>
+      <c r="D30" s="148" t="inlineStr">
+        <is>
+          <t>D+110</t>
+        </is>
+      </c>
+      <c r="E30" s="149" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
+        </is>
+      </c>
+      <c r="F30" s="149" t="inlineStr">
+        <is>
+          <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인
+• 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
+        </is>
+      </c>
+      <c r="G30" s="150" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H30" s="150" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
+        </is>
+      </c>
+      <c r="I30" s="151" t="inlineStr">
+        <is>
+          <t>추가 지반조사결과 종합보고서</t>
+        </is>
+      </c>
+      <c r="J30" s="146" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K30" s="146" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="132" t="inlineStr"/>
+      <c r="B31" s="145" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="C31" s="135" t="inlineStr">
+        <is>
+          <t>D+110</t>
+        </is>
+      </c>
+      <c r="D31" s="135" t="inlineStr">
+        <is>
+          <t>D+120</t>
+        </is>
+      </c>
+      <c r="E31" s="136" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="F31" s="136" t="inlineStr">
+        <is>
+          <t>• 실시설계 추가지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 검토</t>
+        </is>
+      </c>
+      <c r="G31" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H31" s="137" t="inlineStr">
+        <is>
+          <t>현장 공사팀/품질팀/공무팀, 토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I31" s="138" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="J31" s="132" t="inlineStr"/>
+      <c r="K31" s="132" t="inlineStr"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="139" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="140" t="inlineStr">
+        <is>
+          <t>실시설계 추가지반조사 결과 검토</t>
+        </is>
+      </c>
+      <c r="C32" s="141" t="inlineStr">
+        <is>
+          <t>D+110</t>
+        </is>
+      </c>
+      <c r="D32" s="141" t="inlineStr">
+        <is>
+          <t>D+120</t>
+        </is>
+      </c>
+      <c r="E32" s="142" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
+        </is>
+      </c>
+      <c r="F32" s="142" t="inlineStr">
+        <is>
+          <t>• 추가지반조사 결과 검토</t>
+        </is>
+      </c>
+      <c r="G32" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H32" s="143" t="inlineStr">
+        <is>
+          <t>현장 공사팀/품질팀/공무팀, 토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I32" s="144" t="inlineStr">
+        <is>
+          <t>실시설계 최종 R/O</t>
+        </is>
+      </c>
+      <c r="J32" s="139" t="inlineStr"/>
+      <c r="K32" s="139" t="inlineStr"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="152" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B33" s="153" t="inlineStr">
+        <is>
+          <t>최종 R/O 이행방안 수립</t>
+        </is>
+      </c>
+      <c r="C33" s="154" t="inlineStr">
+        <is>
+          <t>D+120</t>
+        </is>
+      </c>
+      <c r="D33" s="154" t="inlineStr">
+        <is>
+          <t>D+150</t>
+        </is>
+      </c>
+      <c r="E33" s="155" t="inlineStr">
+        <is>
+          <t>최종 지반조사 결과에 따른 R/O 이행방안 수립</t>
+        </is>
+      </c>
+      <c r="F33" s="155" t="inlineStr">
+        <is>
+          <t>• Core Risk 및 Hedge 방안 수립
+• Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
+        </is>
+      </c>
+      <c r="G33" s="156" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H33" s="156" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="I33" s="157" t="inlineStr">
+        <is>
+          <t>최종 R/O 이행계획서</t>
+        </is>
+      </c>
+      <c r="J33" s="152" t="inlineStr"/>
+      <c r="K33" s="152" t="inlineStr"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="152" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B34" s="153" t="inlineStr">
+        <is>
+          <t>외부지질전문가 업무평가</t>
+        </is>
+      </c>
+      <c r="C34" s="154" t="inlineStr"/>
+      <c r="D34" s="154" t="inlineStr"/>
+      <c r="E34" s="155" t="inlineStr">
+        <is>
+          <t>참여인력 전문성 평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="F34" s="155" t="inlineStr">
+        <is>
+          <t>• 외부지질 전문가 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="G34" s="156" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H34" s="156" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I34" s="157" t="inlineStr">
+        <is>
+          <t>외부지질 전문가 업무평가서</t>
+        </is>
+      </c>
+      <c r="J34" s="152" t="inlineStr"/>
+      <c r="K34" s="152" t="inlineStr"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="152" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="153" t="inlineStr">
+        <is>
+          <t>조사업체 PM 업무평가</t>
+        </is>
+      </c>
+      <c r="C35" s="154" t="inlineStr"/>
+      <c r="D35" s="154" t="inlineStr"/>
+      <c r="E35" s="155" t="inlineStr">
+        <is>
+          <t>조사업체 PM 전문성 평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="F35" s="155" t="inlineStr">
+        <is>
+          <t>• 지반조사 PM 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="G35" s="156" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H35" s="156" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I35" s="157" t="inlineStr">
+        <is>
+          <t>PM업무평가서</t>
+        </is>
+      </c>
+      <c r="J35" s="152" t="inlineStr"/>
+      <c r="K35" s="152" t="inlineStr"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="152" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B36" s="153" t="inlineStr">
+        <is>
+          <t>지반조사업체 업무평가</t>
+        </is>
+      </c>
+      <c r="C36" s="154" t="inlineStr"/>
+      <c r="D36" s="154" t="inlineStr"/>
+      <c r="E36" s="155" t="inlineStr">
+        <is>
+          <t>조사업체 업무평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="F36" s="155" t="inlineStr">
+        <is>
+          <t>• 협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="G36" s="156" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H36" s="156" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I36" s="157" t="inlineStr">
+        <is>
+          <t>협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="J36" s="152" t="inlineStr"/>
+      <c r="K36" s="152" t="inlineStr"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="132" t="inlineStr"/>
+      <c r="B37" s="145" t="inlineStr">
+        <is>
+          <t>설계변경 LL 리포트 작성</t>
+        </is>
+      </c>
+      <c r="C37" s="135" t="inlineStr"/>
+      <c r="D37" s="135" t="inlineStr"/>
+      <c r="E37" s="136" t="inlineStr">
+        <is>
+          <t>설계변경 사항 기록</t>
+        </is>
+      </c>
+      <c r="F37" s="136" t="inlineStr">
+        <is>
+          <t>• 설계변경 사유 기록관리
+• 예상 R/O대비 설계변경 사항 비교 검토</t>
+        </is>
+      </c>
+      <c r="G37" s="137" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H37" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I37" s="138" t="inlineStr">
+        <is>
+          <t>LL리포트</t>
+        </is>
+      </c>
+      <c r="J37" s="132" t="inlineStr"/>
+      <c r="K37" s="132" t="inlineStr"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="139" t="inlineStr"/>
+      <c r="B38" s="140" t="inlineStr">
+        <is>
+          <t>설계변경 LL 리포트 관리</t>
+        </is>
+      </c>
+      <c r="C38" s="141" t="inlineStr"/>
+      <c r="D38" s="141" t="inlineStr"/>
+      <c r="E38" s="142" t="inlineStr">
+        <is>
+          <t>전체 현장 설계변경 사항 기록</t>
+        </is>
+      </c>
+      <c r="F38" s="142" t="inlineStr">
+        <is>
+          <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
+        </is>
+      </c>
+      <c r="G38" s="143" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="H38" s="143" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="I38" s="144" t="inlineStr">
+        <is>
+          <t>LL리포트 List</t>
+        </is>
+      </c>
+      <c r="J38" s="139" t="inlineStr"/>
+      <c r="K38" s="139" t="inlineStr"/>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="132" t="inlineStr"/>
+      <c r="B39" s="145" t="inlineStr">
+        <is>
+          <t>지반조사업체 정산계약</t>
+        </is>
+      </c>
+      <c r="C39" s="135" t="inlineStr"/>
+      <c r="D39" s="135" t="inlineStr"/>
+      <c r="E39" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 정산</t>
+        </is>
+      </c>
+      <c r="F39" s="136" t="inlineStr">
+        <is>
+          <t>• 조사도 수량 Check 후 구매시스템 변경계약 수행
+• 변경계약 후 정산금 집행</t>
+        </is>
+      </c>
+      <c r="G39" s="137" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H39" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I39" s="138" t="inlineStr">
+        <is>
+          <t>정산계약서</t>
+        </is>
+      </c>
+      <c r="J39" s="132" t="inlineStr"/>
+      <c r="K39" s="132" t="inlineStr"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="139" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B40" s="140" t="inlineStr">
+        <is>
+          <t>매뉴얼 Update</t>
+        </is>
+      </c>
+      <c r="C40" s="141" t="inlineStr"/>
+      <c r="D40" s="141" t="inlineStr"/>
+      <c r="E40" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 매뉴얼 Update</t>
+        </is>
+      </c>
+      <c r="F40" s="142" t="inlineStr">
+        <is>
+          <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
+        </is>
+      </c>
+      <c r="G40" s="143" t="inlineStr">
+        <is>
+          <t>혁신실장</t>
+        </is>
+      </c>
+      <c r="H40" s="143" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I40" s="144" t="inlineStr">
+        <is>
+          <t>지반조사 매뉴얼</t>
+        </is>
+      </c>
+      <c r="J40" s="139" t="inlineStr"/>
+      <c r="K40" s="139" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
@@ -14008,7 +19257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFFFFF00"/>
@@ -18048,7 +23297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
@@ -21684,7 +26933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FFFFFF00"/>
@@ -24127,7 +29376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FFFFFF00"/>
@@ -29086,7 +34335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>
@@ -31440,3255 +36689,4 @@
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="landscape" paperSize="8" scale="38" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet8">
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="19.2"/>
-  <cols>
-    <col width="9" bestFit="1" customWidth="1" style="4" min="1" max="2"/>
-    <col width="13.19921875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="11.19921875" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="30.3984375" customWidth="1" style="4" min="5" max="5"/>
-    <col width="21.69921875" customWidth="1" style="4" min="6" max="6"/>
-    <col width="32.59765625" customWidth="1" style="3" min="7" max="7"/>
-    <col width="73.09765625" customWidth="1" style="3" min="8" max="8"/>
-    <col width="19.3984375" customWidth="1" style="4" min="9" max="9"/>
-    <col width="53" customWidth="1" style="3" min="10" max="10"/>
-    <col width="14.69921875" customWidth="1" style="3" min="11" max="11"/>
-    <col width="45" customWidth="1" style="3" min="12" max="12"/>
-    <col width="14.5" customWidth="1" style="3" min="13" max="13"/>
-    <col width="45" customWidth="1" style="3" min="14" max="14"/>
-    <col width="16.09765625" customWidth="1" style="77" min="15" max="15"/>
-    <col width="15.796875" customWidth="1" style="3" min="16" max="16"/>
-    <col width="45" customWidth="1" style="77" min="17" max="17"/>
-    <col width="22" customWidth="1" style="77" min="18" max="18"/>
-    <col width="45" customWidth="1" style="3" min="19" max="35"/>
-    <col width="8.796875" customWidth="1" style="3" min="36" max="65"/>
-    <col width="8.796875" customWidth="1" style="3" min="66" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="57.6" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>L2 코드</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="inlineStr">
-        <is>
-          <t>L3 코드</t>
-        </is>
-      </c>
-      <c r="C1" s="29" t="inlineStr">
-        <is>
-          <t>L3 대공종명</t>
-        </is>
-      </c>
-      <c r="D1" s="29" t="inlineStr">
-        <is>
-          <t>L4 코드</t>
-        </is>
-      </c>
-      <c r="E1" s="29" t="inlineStr">
-        <is>
-          <t>작업단위 (Level 4 Task/Activity)</t>
-        </is>
-      </c>
-      <c r="F1" s="29" t="inlineStr">
-        <is>
-          <t>주관</t>
-        </is>
-      </c>
-      <c r="G1" s="29" t="inlineStr">
-        <is>
-          <t>목적</t>
-        </is>
-      </c>
-      <c r="H1" s="65" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="I1" s="65" t="inlineStr">
-        <is>
-          <t>산출물(결과)</t>
-        </is>
-      </c>
-      <c r="J1" s="65" t="inlineStr">
-        <is>
-          <t>표준서 (Standard) 요약</t>
-        </is>
-      </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>표준서 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="L1" s="65" t="inlineStr">
-        <is>
-          <t>수행지침 (Guideline) 요약</t>
-        </is>
-      </c>
-      <c r="M1" s="30" t="inlineStr">
-        <is>
-          <t>수행지침 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="N1" s="65" t="inlineStr">
-        <is>
-          <t>체크리스트 (Checklist) 요약</t>
-        </is>
-      </c>
-      <c r="O1" s="66" t="inlineStr">
-        <is>
-          <t>체크리스트 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="P1" s="21" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="Q1" s="21" t="inlineStr">
-        <is>
-          <t>첨부서류 연계 상세 설계기준</t>
-        </is>
-      </c>
-      <c r="R1" s="21" t="inlineStr">
-        <is>
-          <t>집행단계 리스크 체크리스트</t>
-        </is>
-      </c>
-      <c r="S1" s="21" t="inlineStr">
-        <is>
-          <t>협력사 시공/공사관리 자문</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="199.2" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B2" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C2" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D2" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-1</t>
-        </is>
-      </c>
-      <c r="E2" s="61" t="inlineStr">
-        <is>
-          <t>설계적정성 검토</t>
-        </is>
-      </c>
-      <c r="F2" s="61" t="inlineStr">
-        <is>
-          <t>현장 공무팀</t>
-        </is>
-      </c>
-      <c r="G2" s="60" t="inlineStr">
-        <is>
-          <t>설계적정성 및 시공성 검토</t>
-        </is>
-      </c>
-      <c r="H2" s="62" t="inlineStr">
-        <is>
-          <t>- 입찰 요구사항에 대한 설계 반영여부 검토
-- 설계도서 및 철도표준 자재 반영여부 확인
-- 타 시스템과의 인터페이스 가능 여부, 용량, 성능요구 및 통신 트렌드를 고려한 통신 시스템 선정
-- 설계단계에서 통신 음영지역이 있는지를 샘플링 시뮬레이션을 통해 확인하는지 체크 (민원방지 및 롤백 예방을 위한 방안 수립)
-- 기지/역사/터널 배선 적정성 검토
-- 현장설치 시공성 및 공기 Risk 검토
-- 공정계획의 적정성 검토</t>
-        </is>
-      </c>
-      <c r="I2" s="61" t="inlineStr">
-        <is>
-          <t>회의록, 설계검토 보고서</t>
-        </is>
-      </c>
-      <c r="J2" s="74" t="inlineStr">
-        <is>
-          <t>1) 정보통신공사업법, KDS 47 철도설계기준 및 입찰안내서 특기시방 준수 여부 사전 검증
-2) LTE-R 무선망, 8대 이종 통신시스템, 타공종 간섭 및 리스크 헷지·기회반영 설계변경 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K2" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L2" s="74" t="inlineStr">
-        <is>
-          <t>1) 설계적정성 검토: [도면↔수량산출서↔내역서] 삼각 교차대조, 법령/KDS 매핑 체크리스트 검증 및 통신계통 계산서 검토
-2) 시공성 및 설계변경: 현장 지장물 실측 조사, 타공종 3D 간섭 조정, 공법/안전 검토 및 현장 전직원+본사 동시 검토 회의로 설계변경 수립</t>
-        </is>
-      </c>
-      <c r="M2" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N2" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 관계 법령, KDS 47 00 00 철도설계기준, 입찰안내서 시방 준수 및 도면·수량·내역 교차 검증을 완료하였는가?
-2) LTE-R 무선망, 타공종 3D 간섭조정, 8대 이종 통신시스템, 관제연동 적정성 검토 및 현장전직원+본사 동시 검토 승인을 완료하였는가?</t>
-        </is>
-      </c>
-      <c r="O2" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P2" s="68" t="n"/>
-      <c r="Q2" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R2" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S2" s="73" t="n"/>
-    </row>
-    <row r="3" ht="219.6" customHeight="1">
-      <c r="A3" s="63" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B3" s="63" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C3" s="63" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D3" s="63" t="inlineStr">
-        <is>
-          <t>9000-2-2</t>
-        </is>
-      </c>
-      <c r="E3" s="63" t="inlineStr">
-        <is>
-          <t>착수전략 KOM</t>
-        </is>
-      </c>
-      <c r="F3" s="61" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G3" s="60" t="inlineStr">
-        <is>
-          <t>통신설비 공사 발주 전략수립</t>
-        </is>
-      </c>
-      <c r="H3" s="62" t="inlineStr">
-        <is>
-          <t>- 통신설계 설계 및 변동요인 검토
-- 통신공사 공사 시공실적 업체Pool 검토
-- 유사사례 영업운행 실적이 확보된 시스템적용
-1) 공정계획 및 통신자재 제작 기간
-2) 통신설비 구축 실적 보유 (철도, 도시철도, 경전철)
-3) 예비품 및 소모품 포함
-4) 시공전시 통신설비 운전 및 교육 지원 (비용 포함)
-5) 예상내역상 누락 예비품 여부
-6) 현장 자재보관 창고 임대 비용 포함
-7) 공사용 전기, 물수, 청소 비용 포함
-8) 가동 후 현장 기술지원 및 기술 전수 인력기간 및 비용 포함</t>
-        </is>
-      </c>
-      <c r="I3" s="61" t="inlineStr">
-        <is>
-          <t>KOM 검토결과서, 현장설명서</t>
-        </is>
-      </c>
-      <c r="J3" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신공사 발주 착수 전 입찰조건, 적격 시공업체 Pool 분석 및 8대 현장조건 반영 발주전략 수립
-2) 주요 통신 자재 납품 수급 계획 및 시공 적격성 평가를 반영한 발주전략 KOM 보고서 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K3" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L3" s="74" t="inlineStr">
-        <is>
-          <t>1) 발주조건 &amp; 공법 분석: 공사 범위, 자재 자급/사급 조건, 공기 타당성 및 타공종 인터페이스 선행 공종 분석
-2) 전략 수립 및 승인: 리스크 헷지형 계약 조건 도출 및 현장소장/공무팀 주관 발주전략 KOM 보고서 확정</t>
-        </is>
-      </c>
-      <c r="M3" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N3" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신공사 발주 착수 전 입찰안내서 요구조건 및 현장여건 8대 특기사항을 발주 전략에 반영하였는가?
-2) 주요 자재 납품 수급 계획 및 적격 시공업체 평가 기준을 마련하여 발주전략 KOM 승인을 완수하였는가?</t>
-        </is>
-      </c>
-      <c r="O3" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P3" s="68" t="n"/>
-      <c r="Q3" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R3" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S3" s="73" t="n"/>
-    </row>
-    <row r="4" ht="133.8" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B4" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C4" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D4" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="61" t="inlineStr">
-        <is>
-          <t>토목 / 건축 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F4" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G4" s="60" t="inlineStr">
-        <is>
-          <t>통신설비 설치를 위한 요구사항 검토</t>
-        </is>
-      </c>
-      <c r="H4" s="62" t="inlineStr">
-        <is>
-          <t>- 자재 반입전/공동구/케이블 인입구 등 확인, 기능실마감 및 출입문 상태</t>
-        </is>
-      </c>
-      <c r="I4" s="61" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J4" s="74" t="inlineStr">
-        <is>
-          <t>1) 토목·건축 구조물 내 통신 관로, 케이블 트레이, 기계실 배치 및 인입 배관 인터페이스 사전 검토
-2) 타공종 구조체 타설 전 통신 매립 배관 위치 검증 및 인터페이스 협의록 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K4" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L4" s="74" t="inlineStr">
-        <is>
-          <t>1) 구조체 간섭 검토: 토목·건축 도면 대조를 통한 통신 관로 굴곡율, 트레이 설치 경로 및 기계실 벽체 관통부 실측 조사
-2) 협의 수행 및 승인: 타공종 구조체 콘크리트 타설 전 통신 배관 매립 위치 현장 확인 및 3D 간섭 조정 협의록 확정</t>
-        </is>
-      </c>
-      <c r="M4" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N4" s="74" t="inlineStr">
-        <is>
-          <t>1) 시방 대조[도면 및 여건] 자재 반입 동선/공동구/케이블 인입구 등 확인, 기능실마감 및 출입문 확인 수칙을 사전 대조 확인하였는가?
-2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O4" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P4" s="68" t="n"/>
-      <c r="Q4" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R4" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S4" s="73" t="n"/>
-    </row>
-    <row r="5" ht="133.8" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B5" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C5" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D5" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-4</t>
-        </is>
-      </c>
-      <c r="E5" s="61" t="inlineStr">
-        <is>
-          <t>전기 / 신호 / 기계 / PSD / 차량 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F5" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 통신 협력업체</t>
-        </is>
-      </c>
-      <c r="G5" s="60" t="inlineStr">
-        <is>
-          <t>연계분야간 사전조율 및 인터페이스 사항 조율로 재작업 예방</t>
-        </is>
-      </c>
-      <c r="H5" s="62" t="inlineStr">
-        <is>
-          <t>- 연계분야별 조율 및 협의사항 도출
-1) 전기: 소요전력 외
-2) 신호: 공동관로 포설계획 외
-3) 차량: 차량 통신장치-차량간 연계
-4) 전기, 신호, 기계, PSD와 통신망 계통 조율
-- 일정, 분야별 필요 통신회선 수/종류, 기계실 케이블 및 세부 작업 범위</t>
-        </is>
-      </c>
-      <c r="I5" s="61" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J5" s="74" t="inlineStr">
-        <is>
-          <t>1) 전기, 신호, PSD, 차량, 관제 등 이종 시스템 간 전원, 신호선 및 데이터 통신 인터페이스 통합 검토
-2) 타공종 간 전자기 적합성(EMC/EMI), 전력 케이블 유도장해 차폐 및 서지 보호 표준 적용</t>
-        </is>
-      </c>
-      <c r="K5" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L5" s="74" t="inlineStr">
-        <is>
-          <t>1) 설비 간 인터페이스 기술 검토: 전전류/고전압 케이블 유도장해 이격거리(≥30cm) 및 타공종 신호선 서지 보호 검토
-2) 3D/BIM 간섭조정 및 승인: 이종 시스템 간 인터페이스 핀 맵, 데이터 포맷 교차 검증 및 시스템 합동 인터페이스 협의록 작성</t>
-        </is>
-      </c>
-      <c r="M5" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N5" s="74" t="inlineStr">
-        <is>
-          <t>1) 96Core 광망[통합 포설] 통신(48C)+전기(2C)+신호(12C)를 OF-SM-96Core×2조 통합 포설로 확정하였는가?
-2) KEC 점유율[KEC 33%] 전선관 내부 단면적 점유율 33% 이하 및 ELP ø150mm×6개×2조 배관을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O5" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P5" s="68" t="n"/>
-      <c r="Q5" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R5" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S5" s="73" t="n"/>
-    </row>
-    <row r="6" ht="133.8" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C6" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D6" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-5</t>
-        </is>
-      </c>
-      <c r="E6" s="61" t="inlineStr">
-        <is>
-          <t>통신설비 제작사 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F6" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G6" s="60" t="inlineStr">
-        <is>
-          <t>통신설비간 연동방안 검토</t>
-        </is>
-      </c>
-      <c r="H6" s="62" t="inlineStr">
-        <is>
-          <t>- 내부 인터페이스 및 인허가사항 확인, 보안성검토 요청서</t>
-        </is>
-      </c>
-      <c r="I6" s="61" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J6" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 주요 설비(LTE-R, 방송, CCTV, 역무, 관제 등) 제작사 간 프로토콜, 연동 규격 및 인터페이스 검토
-2) 제작사 간 데이터 입출력 포맷 및 연동 케이블 사양서 확정 협의록 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K6" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L6" s="74" t="inlineStr">
-        <is>
-          <t>1) 프로토콜 &amp; 연동 검토: 제작사 간 데이터 입출력 규격, 네트워크 프로토콜(TCP/IP, RS-485 등) 및 랙 치수 대조
-2) 연동 시험 수칙 수립: 제작사 간 신호 연동 핀 배열 확정 및 상호 연동 인터페이스 사양서 감리 승인 절차 수행</t>
-        </is>
-      </c>
-      <c r="M6" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N6" s="74" t="inlineStr">
-        <is>
-          <t>1) 핀 구멍 대조[연결선 대조] A회사와 B회사 장비 연결선 핀(Pin) 구멍 위치가 똑맞는지 1:1 도면으로 대조하였는가?
-2) 전원 잭 확인[코드 잭 준비] 각 장비에 220V 코드를 꽂을지 48V 전기를 줄지 전원 잭을 사전에 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O6" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P6" s="68" t="n"/>
-      <c r="Q6" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R6" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S6" s="73" t="n"/>
-    </row>
-    <row r="7" ht="145.2" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C7" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D7" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-6</t>
-        </is>
-      </c>
-      <c r="E7" s="61" t="inlineStr">
-        <is>
-          <t>관제 및 운영사 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F7" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 통신 협력업체</t>
-        </is>
-      </c>
-      <c r="G7" s="60" t="inlineStr">
-        <is>
-          <t>관제 및 운영사 요구사항 사전 반영 및 시공범위 최적화</t>
-        </is>
-      </c>
-      <c r="H7" s="62" t="inlineStr">
-        <is>
-          <t>- 시운전 조율사항 및 시운전시 정보 항목도출
-- 철도 교통관제(구로/대전)와 연동할 수 있는 무선기능추가(관제/유지보수자 등), 실시간 사진 확인의 편리성 향상을 위한 기능 추가(CCTV카메라 등)
-- 합동운영자, 운영사 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="I7" s="61" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J7" s="74" t="inlineStr">
-        <is>
-          <t>1) 종합관제센터 및 철도운영사 요구조건 반영 관제 화면, 통신 프로토콜 및 비상 제어 인터페이스 검토
-2) 관제 서버, 네트워크 스위치 및 운영사 통합 수선 체계 부합성 확인 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K7" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L7" s="74" t="inlineStr">
-        <is>
-          <t>1) 관제 연동 요구조건 검토: 종합관제 MMI 화면 구성, 비상 통화 프로토콜 및 운영사 통합 수선 요구사항 반영 조사
-2) 관제 인터페이스 승인: 관제 서버-현장 장치 간 제어 데이터 송수신 시험 절차 수립 및 운영사 합동 검토서 확정</t>
-        </is>
-      </c>
-      <c r="M7" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N7" s="74" t="inlineStr">
-        <is>
-          <t>1) OCC 화면배치[화면 맞추기] 동탄 종합관제실(OCC) 모니터에 트램 운행 상황이 한눈에 들어오도록 화면을 배치하였는가?
-2) 4K CCTV 65개[명당 자리] 교차로 4K CCTV 카메라 65개소가 사각지대 없이 보이도록 명당 자리를 배치하였는가?</t>
-        </is>
-      </c>
-      <c r="O7" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P7" s="68" t="n"/>
-      <c r="Q7" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R7" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S7" s="73" t="n"/>
-    </row>
-    <row r="8" ht="115.2" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C8" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D8" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-7</t>
-        </is>
-      </c>
-      <c r="E8" s="61" t="inlineStr">
-        <is>
-          <t>발주처 품질 요구사항 검토</t>
-        </is>
-      </c>
-      <c r="F8" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G8" s="60" t="inlineStr">
-        <is>
-          <t>발주처 품질관리 기준/검사방안 확인</t>
-        </is>
-      </c>
-      <c r="H8" s="60" t="inlineStr">
-        <is>
-          <t>- 감리/감독과 품질검사(ITP/ITC) 항목 검토</t>
-        </is>
-      </c>
-      <c r="I8" s="61" t="inlineStr">
-        <is>
-          <t>ITP/ITC</t>
-        </is>
-      </c>
-      <c r="J8" s="74" t="inlineStr">
-        <is>
-          <t>1) 발주처 입찰안내서 및 시방서 상의 통신 품질 시험 기준, 자재 승인 및 시험성적서 요구조건 검토
-2) 품질시험계획서 수립 및 발주처 승인 품질 기준 준수서 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K8" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L8" s="74" t="inlineStr">
-        <is>
-          <t>1) 품질 기준 실측 수칙: 발주처 특기시방서 상의 품질 시험 항목, 샘플링 검사 비율 및 KS 규격 부합 여부 파악
-2) 품질 관리 수립: 현장 품질시험계획서 수립, 불합격 자재 반출 절차 확립 및 발주처 승인 품질 수칙 이행</t>
-        </is>
-      </c>
-      <c r="M8" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N8" s="74" t="inlineStr">
-        <is>
-          <t>1) [품질 계획] 발주처 품질검사 계획서(ITP)와 공사시방서의 품질 기준을 사전 정밀 대조하였는가?
-2) [Hold Point] 감리원 현장 직접 입회 검측 항목(Hold Point)을 사전 분류 지정하였는가?</t>
-        </is>
-      </c>
-      <c r="O8" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P8" s="68" t="n"/>
-      <c r="Q8" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R8" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S8" s="73" t="n"/>
-    </row>
-    <row r="9" ht="115.2" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B9" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C9" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D9" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-8</t>
-        </is>
-      </c>
-      <c r="E9" s="61" t="inlineStr">
-        <is>
-          <t>자재 / 인원 / 장비 등 투입 사전 검토</t>
-        </is>
-      </c>
-      <c r="F9" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 협력업체 / 관리</t>
-        </is>
-      </c>
-      <c r="G9" s="60" t="inlineStr">
-        <is>
-          <t>자재 / 인원 / 장비 투입 계획 수립</t>
-        </is>
-      </c>
-      <c r="H9" s="62" t="inlineStr">
-        <is>
-          <t>- 현장 여건 및 수량을 기준으로 투입(인원, 장비, 자재) 검토</t>
-        </is>
-      </c>
-      <c r="I9" s="61" t="inlineStr">
-        <is>
-          <t>세부 공정계획 수립 및 조율</t>
-        </is>
-      </c>
-      <c r="J9" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 공사 착수 전 전문 인력 기술자격, 자재 투입 일정 및 전용 시험장비/공구 사전 검토
-2) 예정공정표 대비 인원·장비 투입 수급 타당성 및 안전 수칙 준수 검토 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K9" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L9" s="74" t="inlineStr">
-        <is>
-          <t>1) 투입 자원 타당성 분석: 통신 고급/중급 기술자 자격 검증, 광접속기/OTDR 시험장비 보유 상태 및 자재 수급 계획 검토
-2) 공정 수급 승인: 예정공정표 대비 적정 투입 인원 산출, 작업 안전 구역 확보 및 현장소장 투입 승인 절차 수행</t>
-        </is>
-      </c>
-      <c r="M9" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N9" s="74" t="inlineStr">
-        <is>
-          <t>1) [자원 계획] 공정별 통신 인력, 장비 수급 및 자재 수량을 사전 정밀 대조하였는가?
-2) [인력 자격] 통신 공종별 특급/고급 기술자 자격증 및 현장 배치 계획을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O9" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P9" s="68" t="n"/>
-      <c r="Q9" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R9" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S9" s="73" t="n"/>
-    </row>
-    <row r="10" ht="210.6" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C10" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D10" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-9</t>
-        </is>
-      </c>
-      <c r="E10" s="61" t="inlineStr">
-        <is>
-          <t>착수 전 Big Room 회의</t>
-        </is>
-      </c>
-      <c r="F10" s="61" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>통신공사 수행 시, 선행공정 간섭사항 및 각종 Risk에 대한 대책 수립</t>
-        </is>
-      </c>
-      <c r="H10" s="62" t="inlineStr">
-        <is>
-          <t>본사/현장/협력사 협의체 구축 후 세부내용 검토
-- 공종별 간섭사항 검토: 노반(궤도)/전기/신호/기계/PSD/차량 인터페이스
-- 통신자재 반입/토목(도로/궤도)/자재 야적장/제작사 공장 검토
-- 통신자재 성능보장, 유사사례 리스크관리 및 성능보증 사항 검토
-- 하자 예방, 타 프로젝트 하자사례 검토 후 재발방지방안 수립
-- 인원, 자재, 장비 투입계획, 인허가사항 요건계획 검토
-- 검사의 각 안전공사 기준 공유, 감리검사 계획 확인
-- 공종별 Risk Hedge 방안 검토
-1) 안전/품질 Risk 요소 및 대책 수립
-2) 민원 대응방안 수립</t>
-        </is>
-      </c>
-      <c r="I10" s="61" t="inlineStr">
-        <is>
-          <t>Big Room 회의록(참석자 전원 서명)</t>
-        </is>
-      </c>
-      <c r="J10" s="74" t="inlineStr">
-        <is>
-          <t>1) 공사 착수 전 발주처, 감리단, 시공사 및 타공종 합동 Big Room 회의를 통한 종합 공정 및 위험요인 검토
-2) 간섭사항 사전 도출 및 공종 간 공정 마일스톤 협의록 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K10" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L10" s="74" t="inlineStr">
-        <is>
-          <t>1) Big Room 공조 기법: 발주처·감리단·타공종 시공사 참사 종합 공정 3D 워크스루 및 선행 공종 마일스톤 점검
-2) 간섭 리스크 해소: 공사 착수 전 분야별 간섭 위험 요소를 발굴하여 헷지 방안 수립 및 Big Room 회의록 최종 승인</t>
-        </is>
-      </c>
-      <c r="M10" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N10" s="74" t="inlineStr">
-        <is>
-          <t>1) [Big Room 체계] 본사/현장/협력사 3자 Big Room 협의체를 구축하고 착수 세부 실행계획을 대조하였는가?
-2) [인터페이스] 노반(궤도)/전기/신호/기계/차량 5대 공종 간 관통 경로 및 간섭점을 사전 도출 검출하였는가?</t>
-        </is>
-      </c>
-      <c r="O10" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P10" s="68" t="n"/>
-      <c r="Q10" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R10" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S10" s="73" t="n"/>
-    </row>
-    <row r="11" ht="115.2" customHeight="1">
-      <c r="A11" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B11" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C11" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D11" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-10</t>
-        </is>
-      </c>
-      <c r="E11" s="61" t="inlineStr">
-        <is>
-          <t>통신설비 제작 사양서 작성 / 승인</t>
-        </is>
-      </c>
-      <c r="F11" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G11" s="60" t="inlineStr">
-        <is>
-          <t>실제 설치되는 통신설비의 사양서를 확정하고 제작 사양서를 작성/승인</t>
-        </is>
-      </c>
-      <c r="H11" s="62" t="inlineStr">
-        <is>
-          <t>- 현장여건 및 실시설계계획보고서/포함자재사양서의 요구사항 충족 여부를 확인
-- 제작사양서, 제작도면 작성 후 감리단 승인</t>
-        </is>
-      </c>
-      <c r="I11" s="61" t="inlineStr">
-        <is>
-          <t>제작사양서, 제작도면</t>
-        </is>
-      </c>
-      <c r="J11" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신설비 세부 기술사양서, 랙 배열도(Shop Drawing) 및 전기적/기계적 상세 도면 작성 검토
-2) 감리단 및 발주처 승인을 위한 제작사양서 승인 신청서 및 공학적 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K11" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L11" s="74" t="inlineStr">
-        <is>
-          <t>1) 제작도서 상세 검토: 통신 랙 배열도(Shop Drawing), 전원 분배기 용량 및 단위 기기 기술 사양서 정밀 분석
-2) 공학적 승인 신청: 발주처 입찰시방과 제작사양서 1:1 대조 검증 및 감리단 공학적 승인 제출 절차 수행</t>
-        </is>
-      </c>
-      <c r="M11" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N11" s="74" t="inlineStr">
-        <is>
-          <t>1) [도서 대조] 기본/실시설계도서(보고서, 도면, 자재사양서)와 현장 기계실·역사 치수를 1:1 대조·확인하였는가?
-2) [사양서 정의] 실제 제작·설치될 통신설비의 전기적·기계적 세부 규격 및 제작도면(Shop Drawing)을 작성하였는가?</t>
-        </is>
-      </c>
-      <c r="O11" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P11" s="68" t="n"/>
-      <c r="Q11" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R11" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S11" s="73" t="n"/>
-    </row>
-    <row r="12" ht="115.2" customHeight="1">
-      <c r="A12" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B12" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C12" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D12" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-11</t>
-        </is>
-      </c>
-      <c r="E12" s="61" t="inlineStr">
-        <is>
-          <t>시공 계획 수립 / 승인</t>
-        </is>
-      </c>
-      <c r="F12" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G12" s="60" t="inlineStr">
-        <is>
-          <t>안전/품질이 확보된 시공계획 수립</t>
-        </is>
-      </c>
-      <c r="H12" s="60" t="inlineStr">
-        <is>
-          <t>- 공사계획: 예정공정표, 인원/장비/자재투입 계획, 통신자재 설치 절차서 등
-- 안전관리: 위험요인/대책, 안전교육/시설/점검 계획 수립
-- 품질관리: 품질하자 Risk 및 대책 수립
-- 인허가: 자가전기통신설비 설치신고 접수</t>
-        </is>
-      </c>
-      <c r="I12" s="61" t="inlineStr">
-        <is>
-          <t>시공계획서&amp;시공상세도, 자가전기통신설비 신고서/계획서</t>
-        </is>
-      </c>
-      <c r="J12" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신공사 공정별 상세 시공절차서, 안전관리계획서, 품질관리계획서 및 세부 공정표 수립
-2) 통신설비 설치 공법 타당성 및 감리단 시공계획서 승인 제출 표준 적용</t>
-        </is>
-      </c>
-      <c r="K12" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L12" s="74" t="inlineStr">
-        <is>
-          <t>1) 세부 시공절차 수립: 통신 관로/트레이 포설, 광케이블 접속, 기계실 랙 설치 절차서 및 안전/품질 관리계획 작성
-2) 감리 승인 및 이행: 시공상세도(Shop Drawing) 첨부, 현장 안전 위험성 평가 실시 및 감리단 시공계획서 승인 완료</t>
-        </is>
-      </c>
-      <c r="M12" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N12" s="74" t="inlineStr">
-        <is>
-          <t>1) [도서 대조] 기본/실시설계 보고서, 시방서 수치와 현장 통신기계실 실측 치수를 1:1 대조·확인하였는가?
-2) [안전 대책] 통신기계실 DC -48V 감전 방지 및 정거장 고소작업 시 안전대/2인1조 작업 대책을 수립하였는가?</t>
-        </is>
-      </c>
-      <c r="O12" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P12" s="68" t="n"/>
-      <c r="Q12" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R12" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S12" s="73" t="n"/>
-    </row>
-    <row r="13" ht="115.2" customHeight="1">
-      <c r="A13" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C13" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D13" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-12</t>
-        </is>
-      </c>
-      <c r="E13" s="61" t="inlineStr">
-        <is>
-          <t>자재공급원 검토 및 승인</t>
-        </is>
-      </c>
-      <c r="F13" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G13" s="60" t="inlineStr">
-        <is>
-          <t>통신설비의 시공성과 품질, 기능 확보를 위한 자재 공급원 검토 및 승인</t>
-        </is>
-      </c>
-      <c r="H13" s="60" t="inlineStr">
-        <is>
-          <t>- 통신자재제작능력, 유사사례 납품실적 확인
-- 성능보증 가능한 통신자재 업체 Pool 검토
-- 통신자재 설치 실적 및 설계능력 확인
-- 보안성검토 결과 확인</t>
-        </is>
-      </c>
-      <c r="I13" s="61" t="inlineStr">
-        <is>
-          <t>자재공급원/제작도서 승인 서류, 보안성검토 결과서</t>
-        </is>
-      </c>
-      <c r="J13" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 주요 자재 및 기기 자재공급원 승인 서류(KS 인증, 시험성적서, 사업자등록증 등) 검토
-2) 성능보증이 가능한 복수 자재공급원 승인 서류 수립 및 감리 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K13" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L13" s="74" t="inlineStr">
-        <is>
-          <t>1) 승인 서류 정밀 검토: 제조사 공장등록증, KS/KC 인증서, 최근 3년 납품 실적 및 공인시험기관 시험성적서 확인
-2) 자재 승인 및 관리: 복수 공급원 비교 검토서 작성, 불량 자재 차단 헷지 및 감리단 자재공급원 승인 획득</t>
-        </is>
-      </c>
-      <c r="M13" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N13" s="74" t="inlineStr">
-        <is>
-          <t>1) [서류 수집] 공장등록증, 사업자등록증, 카탈로그, A/S 확약서 등 6대 필수 제출 서류를 수집·확인하였는가?
-2) [사양 대조] 설계도서 수치(KCS 31 10 00)와 자재 카탈로그 규격 간 1:1 대조표를 정확히 작성하였는가?</t>
-        </is>
-      </c>
-      <c r="O13" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P13" s="68" t="n"/>
-      <c r="Q13" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R13" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S13" s="73" t="n"/>
-    </row>
-    <row r="14" ht="192" customHeight="1">
-      <c r="A14" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C14" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D14" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-13</t>
-        </is>
-      </c>
-      <c r="E14" s="61" t="inlineStr">
-        <is>
-          <t>통신설비 공정제작 / 제작사 공장검사</t>
-        </is>
-      </c>
-      <c r="F14" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G14" s="60" t="inlineStr">
-        <is>
-          <t>제작사양서/제작도면의 일치여부검토 및 현장반입 전 공장 성능검사 확인</t>
-        </is>
-      </c>
-      <c r="H14" s="60" t="inlineStr">
-        <is>
-          <t>- 외산자재 등 Delivery 일정 확인
-- 제작도서 기준으로 최종 제작상태 확인
-- 제작도면과 일치여부 확인
-- 공장 내 성능검사 시험 실시
-[공장검사 대상 항목]
-- 영상장치장치, 행선안내장치, 구내방송장치, 전송설비, 역무자동화설비, 열차무선안내장치, 여객자동안내장치, 열차무선설비, 재난방송수신설비, 선로변 통합인터페이스 통신설비, 역무용통신설비, 백본스위치, L3스위치, 광케이블, 케이블 안테나 CCTV용 Pole</t>
-        </is>
-      </c>
-      <c r="I14" s="61" t="inlineStr">
-        <is>
-          <t>공장검사 결과보고서 (감리 및 관계기관 입회)</t>
-        </is>
-      </c>
-      <c r="J14" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 기기 제작 공정 진행률 점검 및 공장시험(FAT, Factory Acceptance Test) 절차서 작성
-2) 공장 수검 검사, 품질 성능 시험성적서 확인 및 공장검사 합격증명서 발급 표준 적용</t>
-        </is>
-      </c>
-      <c r="K14" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L14" s="74" t="inlineStr">
-        <is>
-          <t>1) 공장검사(FAT) 준비: 제작사 공장 제작 공정률 점검, FAT 시험절차서 검토 및 검사 입회 일정 수립
-2) 입회 검사 실시: 전원 인입, 기능 시험, 방수/내열 공인시험 실측 확인 및 FAT 공장검사 합격증명서 획득</t>
-        </is>
-      </c>
-      <c r="M14" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N14" s="74" t="inlineStr">
-        <is>
-          <t>1) [외산자재 납기] 수입 광모듈, 스위치 칩셋의 선적/통관 서류(B/L)를 검수하여 현장 기계실 반입 주공정표(CPM) 대비 납기를 확인하였는가?
-2) [ITP 승인] 감리 승인된 ITP 절차서와 절연저항계(Megger), OTDR의 교정 유효기간 증명서를 사전 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O14" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P14" s="68" t="n"/>
-      <c r="Q14" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R14" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S14" s="73" t="n"/>
-    </row>
-    <row r="15" ht="115.2" customHeight="1">
-      <c r="A15" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C15" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D15" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-14</t>
-        </is>
-      </c>
-      <c r="E15" s="61" t="inlineStr">
-        <is>
-          <t>본공사 전 선행공정 인수인계 점검</t>
-        </is>
-      </c>
-      <c r="F15" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>통신설비 설치를 위한 현장점검/정리 상태 확인(기능실: 건축,전기/현장: 노반)</t>
-        </is>
-      </c>
-      <c r="H15" s="60" t="inlineStr">
-        <is>
-          <t>- 통신설비 설치 시 간섭여부 점검
-- 현장 정리상태 점검 (건축마감, 공조, 조명, 전원 등)
-- 장비설치를 위한 자체반입구 및 케이블 설치를 위한 공동구/오프닝 위치 확인</t>
-        </is>
-      </c>
-      <c r="I15" s="61" t="inlineStr">
-        <is>
-          <t>기록지, 현장점검결과보고서(감리입회)</t>
-        </is>
-      </c>
-      <c r="J15" s="74" t="inlineStr">
-        <is>
-          <t>1) 토목·건축 선행 공정 완료 후 통신 기계실, 케이블 트레이, 관로 인수인계 현장 상태 검측
-2) 바닥 엑세스플로어, 방화 구획 및 기초 구조체 인수인계 확인서 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K15" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L15" s="74" t="inlineStr">
-        <is>
-          <t>1) 선행 공종 실측 검측: 토목·건축 완료 기계실 바닥 엑세스플로어, 케이블 트레이, 방화 구획 및 랙 기초 상태 검사
-2) 인수인계 승인: 미비 사항 현장 보완 조치 요구 및 통신 시공 적격 선행 공정 인수인계 확인서 최종 승인</t>
-        </is>
-      </c>
-      <c r="M15" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N15" s="74" t="inlineStr">
-        <is>
-          <t>1) 토목 배관 도면 및 건축 구조물 도면을 대조하여 통신기계실 오프닝 위치, 지중관로 규격(Ø100/Ø50) 및 핸드홀 설치 좌표를 사전 검토하였는가?
-2) 토목, 건축, 통신 현장 담당자 3자 공조 체계를 구성하고 현장 합동 점검표, Mandrel 도통시험기 및 레이저 레벨기를 사전 준비하였는가?</t>
-        </is>
-      </c>
-      <c r="O15" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P15" s="68" t="n"/>
-      <c r="Q15" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R15" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S15" s="73" t="n"/>
-    </row>
-    <row r="16" ht="115.2" customHeight="1">
-      <c r="A16" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C16" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-15</t>
-        </is>
-      </c>
-      <c r="E16" s="61" t="inlineStr">
-        <is>
-          <t>장비반입 및 안전교육</t>
-        </is>
-      </c>
-      <c r="F16" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 안전팀</t>
-        </is>
-      </c>
-      <c r="G16" s="60" t="inlineStr">
-        <is>
-          <t>장비 반입 준비 및 안전교육 완료</t>
-        </is>
-      </c>
-      <c r="H16" s="60" t="inlineStr">
-        <is>
-          <t>- 자재반입 경로, 적치장소에 대한 사전확인 및 타분야 일정, 간섭사항 협의/확인
-- 장비 Spec확인, 장비상태 점검
-- 작업원 안전교육 실시</t>
-        </is>
-      </c>
-      <c r="I16" s="61" t="inlineStr">
-        <is>
-          <t>안전교육 결과서, 측량기록지</t>
-        </is>
-      </c>
-      <c r="J16" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 시공 장비 및 차량 반입 전 장비 안전점검 및 작업자 특별안전보건교육 실시
-2) 장비 반입 허가서 작성 및 안전 교육 이수 수료증 관리 표준 적용</t>
-        </is>
-      </c>
-      <c r="K16" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L16" s="74" t="inlineStr">
-        <is>
-          <t>1) 장비 안전점검: 고소작업차, 광접속 차량 반입 전 안전 검사 및 작업 장비 반입 신청서 검토
-2) 안전 교육 이수: 통신 시공 작업자 대상 특별안전보건교육, 보호구 착용 점검 및 안전 교육 이수 수료 관리</t>
-        </is>
-      </c>
-      <c r="M16" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N16" s="74" t="inlineStr">
-        <is>
-          <t>1) 화물차 반입 도로의 유효 폭(W≥3.5m) 및 지상 가설재 장애물(0cm) 상태를 확인하였는가?
-2) 토목/건축 등 타분야 양중 작업 간섭 여부를 사전 협의하고 양중 시간대를 분리 조율하였는가?</t>
-        </is>
-      </c>
-      <c r="O16" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P16" s="68" t="n"/>
-      <c r="Q16" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R16" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S16" s="73" t="n"/>
-    </row>
-    <row r="17" ht="115.2" customHeight="1">
-      <c r="A17" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C17" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D17" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-16</t>
-        </is>
-      </c>
-      <c r="E17" s="61" t="inlineStr">
-        <is>
-          <t>자재 반입 및 검수</t>
-        </is>
-      </c>
-      <c r="F17" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주청/공동감리단</t>
-        </is>
-      </c>
-      <c r="G17" s="60" t="inlineStr">
-        <is>
-          <t>공장검사 시행 완료된 자재반입과 현장 입고 검사</t>
-        </is>
-      </c>
-      <c r="H17" s="60" t="inlineStr">
-        <is>
-          <t>- 자재 하차 위치 및 반입동선 확인
-- 승인된 자재 일치여부 확인(Serial number 등)
-- 제품의 규격, 수량 도면과 일치하는지 검토</t>
-        </is>
-      </c>
-      <c r="I17" s="61" t="inlineStr">
-        <is>
-          <t>자재검수서</t>
-        </is>
-      </c>
-      <c r="J17" s="74" t="inlineStr">
-        <is>
-          <t>1) 현장 반입 통신 자재 및 케이블의 승인 자재 일치성, 수량 및 운반 파손 여부 검수
-2) 자재검수 요청서 작성 및 감리 입회 검수 합격 확인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K17" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L17" s="74" t="inlineStr">
-        <is>
-          <t>1) 반입 자재 현장 검측: 자재 반입 시 자재공급원 승인품 일치 여부, 운반 외관 파손 및 시리얼 번호 현장 검수
-2) 자재검수 보고: 감리 입회 자재 검수 실시, 자재검수 요청서 결재 및 현장 통신 자재 창고 입고 관리</t>
-        </is>
-      </c>
-      <c r="M17" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N17" s="74" t="inlineStr">
-        <is>
-          <t>1) 시방 대조[도면 및 여건] 자재 하차 위치 및 반입동선 확인 수칙을 사전 대조 확인하였는가?
-2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O17" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P17" s="68" t="n"/>
-      <c r="Q17" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R17" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S17" s="73" t="n"/>
-    </row>
-    <row r="18" ht="115.2" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B18" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C18" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D18" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-17</t>
-        </is>
-      </c>
-      <c r="E18" s="61" t="inlineStr">
-        <is>
-          <t>통신설비 반입 및 설치</t>
-        </is>
-      </c>
-      <c r="F18" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 분야별 전담팀</t>
-        </is>
-      </c>
-      <c r="G18" s="60" t="inlineStr">
-        <is>
-          <t>설계에 부합되도록 통신설비 설치</t>
-        </is>
-      </c>
-      <c r="H18" s="62" t="inlineStr">
-        <is>
-          <t>- 시공샘플이 필요한 대상을 감리/감독과 협의하여 선정후 시공검사 실시
-- 현장 선로변 설비, 각종 케이블 포설
-- 기계실 내 서버랙 및 각종 단말장치 설치 (카메라, 인터폰 등)
-- 통신실내 케이블 배선
-- 통신설비가 도면대로 설치되었는지 확인</t>
-        </is>
-      </c>
-      <c r="I18" s="61" t="inlineStr">
-        <is>
-          <t>검측서</t>
-        </is>
-      </c>
-      <c r="J18" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 기계실 랙 설비, 본선 관로 광케이블 포설 및 역무 통신 기기 수평/수직 시공 설치
-2) 케이블 성단, OTDR 접속 및 설비 고정 상태 검측 표준 적용</t>
-        </is>
-      </c>
-      <c r="K18" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L18" s="74" t="inlineStr">
-        <is>
-          <t>1) 설치 실무 절차: 통신 기계실 랙 고정, 광케이블/UTP 포설, 성단 작업 및 역사 역무 통신 기기 수평/수직 시공
-2) 접속 및 검측: OTDR 접속 손실(≤0.05dB) 측정, 랙 전원 인입 배선 정리 및 설비 고정 상태 감리 검측</t>
-        </is>
-      </c>
-      <c r="M18" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N18" s="74" t="inlineStr">
-        <is>
-          <t>1) 본 시공 착수 전 통신기계실 랙 배선 정돈 및 마킹 표찰 샘플을 감리단과 사전 검측하였는가?
-2) 72-Core 광케이블 융착 접속 트레이 정돈 및 접속 손실 샘플 시공 승인을 획득하였는가?</t>
-        </is>
-      </c>
-      <c r="O18" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P18" s="68" t="n"/>
-      <c r="Q18" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R18" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S18" s="73" t="n"/>
-    </row>
-    <row r="19" ht="115.2" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C19" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D19" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-18</t>
-        </is>
-      </c>
-      <c r="E19" s="61" t="inlineStr">
-        <is>
-          <t>관제설비 설치</t>
-        </is>
-      </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G19" s="60" t="inlineStr">
-        <is>
-          <t>관제설비의 정위치 배치 및 설치</t>
-        </is>
-      </c>
-      <c r="H19" s="62" t="inlineStr">
-        <is>
-          <t>- 랙 베이스/케이블 등 설치 위치를 확인하고 설치후에는 도면과 일치 여부를 체크
-- 철도 교통관제(구로/대전)와 연동할 수 있게 광전송/열차무선 설비 등을 설치하고 확인</t>
-        </is>
-      </c>
-      <c r="I19" s="61" t="inlineStr">
-        <is>
-          <t>검측서</t>
-        </is>
-      </c>
-      <c r="J19" s="74" t="inlineStr">
-        <is>
-          <t>1) 종합관제센터 관제 콘솔, 대형 표시장치(DLP/LFD), 관제 서버 및 네트워크 설비 설치
-2) 관제 시스템 전원 인입, 배선 정리 및 관제 환경 설치 검측 표준 적용</t>
-        </is>
-      </c>
-      <c r="K19" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L19" s="74" t="inlineStr">
-        <is>
-          <t>1) 관제 환경 설치 절차: 종합관제센터 관제 콘솔 고정, DLP/LFD 대형 화면 설치, 관제 서버 랙 반입 및 배선 정리
-2) 전원 및 계통 검측: 관제 전원 분배기 전원 인입, 이중화 네트워크 케이블 성단 및 관제실 설치 상태 확인</t>
-        </is>
-      </c>
-      <c r="M19" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N19" s="74" t="inlineStr">
-        <is>
-          <t>1) OCC 관제실 전면 비디오 월 마운트 거치 프레임 레이저 수평 오차(±1.0mm 이내)를 실측하였는가?
-2) 멀티 디스플레이 패널 간 베젤 이격 단차(≤0.5mm) 미세 조율 및 방진 가스켓 부착을 완료하였는가?</t>
-        </is>
-      </c>
-      <c r="O19" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P19" s="68" t="n"/>
-      <c r="Q19" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R19" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S19" s="73" t="n"/>
-    </row>
-    <row r="20" ht="115.2" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B20" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C20" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D20" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-19</t>
-        </is>
-      </c>
-      <c r="E20" s="61" t="inlineStr">
-        <is>
-          <t>통신시스템 단위시험</t>
-        </is>
-      </c>
-      <c r="F20" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G20" s="60" t="inlineStr">
-        <is>
-          <t>통신설비(열차에 설치하는 차상통신 장치 포함)설치 후 전원투입 및 기능검증</t>
-        </is>
-      </c>
-      <c r="H20" s="62" t="inlineStr">
-        <is>
-          <t>- ITP/ITC에 따라 시험/검사를 감리 확인</t>
-        </is>
-      </c>
-      <c r="I20" s="61" t="inlineStr">
-        <is>
-          <t>감리단 입회검사 및 시험점검표(ITP/ITC)</t>
-        </is>
-      </c>
-      <c r="J20" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 개별 단위 설비(LTE-R, 방송, CCTV, 역무, 전화 등) 전원 투입 및 단독 시험 실시
-2) 설비별 단위시험 절차서 준수 및 단독 기능 시험성적서 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K20" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L20" s="74" t="inlineStr">
-        <is>
-          <t>1) 단독 시험 수행: LTE-R 기지국/제어기, 방송, CCTV, 역무, 전화 등 개별 시스템 단위 전원 인입 및 단독 시험
-2) 단위성적서 작성: 단위시험 절차서 항목별 성능 측정, 불합격 항목 보완 조치 및 단위시험 성과표 확정</t>
-        </is>
-      </c>
-      <c r="M20" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N20" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신기계실 LTE-R DU 제어기 및 옥외 RU 무선장치에 단독 전원(220V/48V) 투입 후 부팅 정상 상태를 확인하였는가?
-2) RF 파워메터로 무선장치(RU) 송신 출력을 계측하여 표준 규격(43dBm ±0.5dB) 이내임을 검측하였는가?</t>
-        </is>
-      </c>
-      <c r="O20" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P20" s="68" t="n"/>
-      <c r="Q20" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R20" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S20" s="73" t="n"/>
-    </row>
-    <row r="21" ht="115.2" customHeight="1">
-      <c r="A21" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C21" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D21" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-20</t>
-        </is>
-      </c>
-      <c r="E21" s="61" t="inlineStr">
-        <is>
-          <t>통신시스템 통합시험</t>
-        </is>
-      </c>
-      <c r="F21" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G21" s="60" t="inlineStr">
-        <is>
-          <t>관제설비를 포함한 통신망 통합 검증</t>
-        </is>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>- 감리단 입회하에 검사/시험절차대로 수행
-1) 관제실/현장설비간 인터페이스 시험
-2) 지상 및 차상 인터페이스 시험</t>
-        </is>
-      </c>
-      <c r="I21" s="61" t="inlineStr">
-        <is>
-          <t>감리단 입회검사 및 시험점검표(ITP/ITC)</t>
-        </is>
-      </c>
-      <c r="J21" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 설비 간 데이터 연동, LTE-R 무선망 백본 이중화 절체 및 종합 네트워크 연동 시험
-2) 통합시험 절차서 준수 및 이종 통신 설비 간 상호 연동성 검측 표준 적용</t>
-        </is>
-      </c>
-      <c r="K21" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L21" s="74" t="inlineStr">
-        <is>
-          <t>1) 연동 시험 수행: 통신 이종 시스템 간 데이터 연동, LTE-R 코어망 백본 이중화 절체 및 종합 네트워크 연동 시험
-2) 통합 성과 확인: 관제-현장 장치 간 제어 응답속도 검측, 통합 시험 성과표 작성 및 감리 승인 완료</t>
-        </is>
-      </c>
-      <c r="M21" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N21" s="74" t="inlineStr">
-        <is>
-          <t>1) 관제센터 메인 방송 서버와 각 정거장 PIS 제어기 간 광전송 유선 인터페이스 통신 상태를 확인하였는가?
-2) 관제 콘솔에서 PIS 문구 송출 명령 전송 시 현장 안내표시기 반응 지연 시간(≤0.5초 이내)을 검측하였는가?</t>
-        </is>
-      </c>
-      <c r="O21" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P21" s="68" t="n"/>
-      <c r="Q21" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R21" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S21" s="73" t="n"/>
-    </row>
-    <row r="22" ht="115.2" customHeight="1">
-      <c r="A22" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B22" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C22" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D22" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-21</t>
-        </is>
-      </c>
-      <c r="E22" s="61" t="inlineStr">
-        <is>
-          <t>공종별 시험</t>
-        </is>
-      </c>
-      <c r="F22" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G22" s="60" t="inlineStr">
-        <is>
-          <t>발주처가 관련 법령, 설계기준, 기술기준, 시방서 등의 요구사항에 적합하도록 설치되었는지를 확인</t>
-        </is>
-      </c>
-      <c r="H22" s="60" t="inlineStr">
-        <is>
-          <t>- 철도종합시험운행 시행지침 제6조(공종별시험)에 따라 시행</t>
-        </is>
-      </c>
-      <c r="I22" s="61" t="inlineStr">
-        <is>
-          <t>공종별 시험 결과보고서</t>
-        </is>
-      </c>
-      <c r="J22" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도 종합시험운행 지침에 의거한 통신 공종별 상세 시운전 시험 절차 수립
-2) 공종별 시험 항목 검측, 무선 전계강도 측정 및 시험성적서 확정 표준 적용</t>
-        </is>
-      </c>
-      <c r="K22" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L22" s="74" t="inlineStr">
-        <is>
-          <t>1) 공종 시운전 절차: 철도 종합시험운행 지침에 따른 통신 공종별 상세 시험 항목(무선 품질, 음성/영상 전송) 실측
-2) 공종 시험 승인: 무선 전계강도 측정 성과표 및 공종별 시운전 시험 결과 보고서 제출 및 감리 승인</t>
-        </is>
-      </c>
-      <c r="M22" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N22" s="74" t="inlineStr">
-        <is>
-          <t>1) 본선 및 정거장 광배선반(FDF) 포설 광케이블 전체 코어에 대하여 OTDR 전수 측정을 수행하였는가?
-2) 광케이블 융착 접속점 접속 손실 수치가 시방 기준(≤0.1dB/접속점 이하)을 통과함을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O22" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P22" s="68" t="n"/>
-      <c r="Q22" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R22" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S22" s="73" t="n"/>
-    </row>
-    <row r="23" ht="115.2" customHeight="1">
-      <c r="A23" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C23" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D23" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-22</t>
-        </is>
-      </c>
-      <c r="E23" s="61" t="inlineStr">
-        <is>
-          <t>차량 투입 전 점검</t>
-        </is>
-      </c>
-      <c r="F23" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 시공전담팀</t>
-        </is>
-      </c>
-      <c r="G23" s="60" t="inlineStr">
-        <is>
-          <t>발주처가 원활한 차량시운전이 되도록 노반, 건축, 궤도, 전철전력, 통신, 신호 분야를 종합하여 최종 점검</t>
-        </is>
-      </c>
-      <c r="H23" s="62" t="inlineStr">
-        <is>
-          <t>- 노반/궤도 시공상태 점검
-- 건축한계 및 차량한계 검사
-1) 건축한계: 폭(3,600mm) / 높이(5,300mm)
-2) 차량한계: 폭(3,200mm) / 높이(4,750mm)
-- 전차선, 신호, 통신 작동상태 확인</t>
-        </is>
-      </c>
-      <c r="I23" s="61" t="inlineStr">
-        <is>
-          <t>점검 결과보고서</t>
-        </is>
-      </c>
-      <c r="J23" s="74" t="inlineStr">
-        <is>
-          <t>1) 본선 트램 차량 투입 전 LTE-R 차상 통신장치, 무선 안테나 및 관제 무선 연동태세 점검
-2) 차량 투입 대비 통신 무무선 연동 안전 상태 확인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K23" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L23" s="74" t="inlineStr">
-        <is>
-          <t>1) 차상 연동 점검: 본선 트램 차량 투입 전 차량 차상 LTE-R 통신장비, 무선 안테나 및 관제 무선 연동태세 실측
-2) 투입 안전 승인: 차량 투입 시 무선 통신 끊김 예방 점검 및 차량 투입 전 통신 안전 확인서 작성</t>
-        </is>
-      </c>
-      <c r="M23" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N23" s="74" t="inlineStr">
-        <is>
-          <t>1) 본선 전 구간 궤도변 건축한계 규격(폭 3,100mm / 높이 3,800mm) 내 침범 요소 유무를 실측 확인하였는가?
-2) 궤도 주변 통신 케이블 트레이 및 광점퍼 선로 묶음이 건축한계 이내로 처지거나 돌출되지 않음을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O23" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P23" s="68" t="n"/>
-      <c r="Q23" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R23" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S23" s="73" t="n"/>
-    </row>
-    <row r="24" ht="115.2" customHeight="1">
-      <c r="A24" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B24" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C24" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D24" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-23</t>
-        </is>
-      </c>
-      <c r="E24" s="61" t="inlineStr">
-        <is>
-          <t>차량 시운전</t>
-        </is>
-      </c>
-      <c r="F24" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G24" s="60" t="inlineStr">
-        <is>
-          <t>철도안전법에 따른 철도차량 형식시험</t>
-        </is>
-      </c>
-      <c r="H24" s="60" t="inlineStr">
-        <is>
-          <t>- 철도안전법 제26조(철도차량 형식승인)에 따라 이행(주로 본선구간 수행)
-- 차량, 신호, 통신 시스템간 인터페이스 시험</t>
-        </is>
-      </c>
-      <c r="I24" s="61" t="inlineStr">
-        <is>
-          <t>철도차량 형식승인 결과 보고서</t>
-        </is>
-      </c>
-      <c r="J24" s="74" t="inlineStr">
-        <is>
-          <t>1) 트램 차량 본선 주행 시 LTE-R 무선 수신강도(RSSI/RSRP), 핸드오버 및 음성/데이터 통신 검측
-2) 주행 중 통신 끊김 여부 및 차상-지상 간 통신 품질 성과표 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K24" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L24" s="74" t="inlineStr">
-        <is>
-          <t>1) 본선 주행 시험: 트램 차량 본선 주행 중 LTE-R 무선 수신강도(RSSI ≥ -95dBm), 핸드오버 성공률(≥99.5%) 실측
-2) 주행 통신 검측: 차상-지상 간 CCTV 영상 전송 및 관제 데이터 무선 통신 품질 성과표 최종 확정</t>
-        </is>
-      </c>
-      <c r="M24" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N24" s="74" t="inlineStr">
-        <is>
-          <t>1) 본선 실 주행 최고 속도 조건에서 LTE-R 차상 단말기 수신 감도(RSSI ≥ -85dBm)를 지속 유지하였는가?
-2) 주행 중 LTE-R 기지국 간 이동 시 핸드오버 성공률 100% 및 음성 무선 통화 끊김 0건을 검측하였는가?</t>
-        </is>
-      </c>
-      <c r="O24" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P24" s="68" t="n"/>
-      <c r="Q24" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R24" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S24" s="73" t="n"/>
-    </row>
-    <row r="25" ht="115.2" customHeight="1">
-      <c r="A25" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B25" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D25" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-24</t>
-        </is>
-      </c>
-      <c r="E25" s="61" t="inlineStr">
-        <is>
-          <t>운영자 교육시행</t>
-        </is>
-      </c>
-      <c r="F25" s="61" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G25" s="60" t="inlineStr">
-        <is>
-          <t>영업시운전 전에 시설을 운영자를 대상으로 운영 및 유지관리방법에 대해 교육</t>
-        </is>
-      </c>
-      <c r="H25" s="60" t="inlineStr">
-        <is>
-          <t>- 통신 시스템 제작사가 만든 매뉴얼로 운영자를 교육
-: 관제설비등통신설비 운영/관리방법</t>
-        </is>
-      </c>
-      <c r="I25" s="61" t="inlineStr">
-        <is>
-          <t>운영자 교육 결과서</t>
-        </is>
-      </c>
-      <c r="J25" s="74" t="inlineStr">
-        <is>
-          <t>1) 시설물 인수인계 전 운영사 운영자 및 유지보수 요원 대상 통신 시스템 운영 교육 실시
-2) 교육 교재 작성, 시스템 운용/장해 조치 실습 및 교육 이수 확인서 작성 표준 적용</t>
-        </is>
-      </c>
-      <c r="K25" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L25" s="74" t="inlineStr">
-        <is>
-          <t>1) 교육 프로그램 실시: 운영사 운영자 및 유지관리 요원 대상 통신 시스템 구조, HMI 운용 및 비상 조치 교육
-2) 교육 이수 확정: 현장 실습 교육 수행, 질문/답변 점검 및 운영자 교육 참석 이수 확인서 최종 작성</t>
-        </is>
-      </c>
-      <c r="M25" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N25" s="74" t="inlineStr">
-        <is>
-          <t>1) 통신 4대 계통(교환, 무선, PIS/PA, CCTV) 제작사 공식 기술 매뉴얼을 수집·구비하였는가?
-2) 주요 장비 장애 시 대응할 수 있는 계통별 긴급 비상 조치 매뉴얼 교재를 편찬하였는가?</t>
-        </is>
-      </c>
-      <c r="O25" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P25" s="68" t="n"/>
-      <c r="Q25" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R25" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S25" s="73" t="n"/>
-    </row>
-    <row r="26" ht="115.2" customHeight="1">
-      <c r="A26" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B26" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C26" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D26" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-25</t>
-        </is>
-      </c>
-      <c r="E26" s="61" t="inlineStr">
-        <is>
-          <t>사전점검</t>
-        </is>
-      </c>
-      <c r="F26" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G26" s="60" t="inlineStr">
-        <is>
-          <t>시설물검증시험의 가능여부를 확인하기 위하여 발주처와 운영자가 합동으로 점검</t>
-        </is>
-      </c>
-      <c r="H26" s="60" t="inlineStr">
-        <is>
-          <t>- (기준) 철도종합시험운행 시행지침 제8조 "종합시험운행을 위한 사전점검"에 따름
-- 발주처는 공종별 시험을 완료한 후 시설물 검증시험의 가능여부를 확인하기 위하여 사전점검계획을 수립하고 운영자와 합동으로 실시
-- 발주처와 운영자의 사전점검 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)</t>
-        </is>
-      </c>
-      <c r="I26" s="61" t="inlineStr">
-        <is>
-          <t>사전점검 결과보고서/승인문서(한국교통안전공단)</t>
-        </is>
-      </c>
-      <c r="J26" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 지침 제8조에 의거한 사전점검계획 수립 및 기술기준 부합성 종합 점검
-2) 사전점검 결과 보고서 작성 및 한국교통안전공단 제출 승인 표준 적용</t>
-        </is>
-      </c>
-      <c r="K26" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L26" s="74" t="inlineStr">
-        <is>
-          <t>1) 사전점검 수검 절차: 철도종합시험운행 지침 제8조에 의거 사전점검 수행반 구성 및 통신 설비 종합 점검
-2) 점검 결과 승인: 기술기준 부합 여부 사전 검증, 지적사항 조치 완료 및 한국교통안전공단 사전점검 보고서 제출</t>
-        </is>
-      </c>
-      <c r="M26" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N26" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 시행지침 제8조 규정에 맞춘 사전점검계획서를 작성하였는가?
-2) 발주처, 운영기관, 책임감리단 및 현장소장이 포함된 3자 합동 사전점검반을 조직하였는가?</t>
-        </is>
-      </c>
-      <c r="O26" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P26" s="68" t="n"/>
-      <c r="Q26" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R26" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S26" s="73" t="n"/>
-    </row>
-    <row r="27" ht="153.6" customHeight="1">
-      <c r="A27" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B27" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C27" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D27" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-26</t>
-        </is>
-      </c>
-      <c r="E27" s="61" t="inlineStr">
-        <is>
-          <t>시설물 검증시험</t>
-        </is>
-      </c>
-      <c r="F27" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G27" s="60" t="inlineStr">
-        <is>
-          <t>발주처는 시설물의 정상작동 상태 등을 확인하기 위해 시설물 검증시험을 수행</t>
-        </is>
-      </c>
-      <c r="H27" s="60" t="inlineStr">
-        <is>
-          <t>- (기준) 철도종합시험운행 시행지침 제12조(시설물검증시험계획의 수립), 13조(시설물검증시험의 시행)에 따름
-- 발주처는 시설물검증시험계획을 운영자와 협의하여 수립하고 전문기관의 승인을 받은 후 시행
-- 철도종합시험운행 시설물검증시험 점검항목: 시설물의 정상작동 상태, 철도시설의 안전상태, 철도차량의 운행적합성, 철도시설과 차량 간의 연계성
-- 발주처와 운영자의 시설물 검증시험 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)</t>
-        </is>
-      </c>
-      <c r="I27" s="61" t="inlineStr">
-        <is>
-          <t>시설물 검증시험 결과보고서/승인문서(한국교통안전공단)</t>
-        </is>
-      </c>
-      <c r="J27" s="74" t="inlineStr">
-        <is>
-          <t>1) 시설물검증시험 계획 수립 및 본선 주행 시험 차량을 이용한 통신 설비 최고속도 성능 검증
-2) LTE-R 무선 품질, 관제 데이터 전송률 및 시설물검증 합격 판정 표준 적용</t>
-        </is>
-      </c>
-      <c r="K27" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L27" s="74" t="inlineStr">
-        <is>
-          <t>1) 최고속도 주행 검증: 시설물검증시험 계획에 따라 시운전 열차를 최고 설계속도로 주행하며 통신 성능 실측
-2) 검증 결과 확정: LTE-R 무선망 수신강도, 데이터 전송 지연시간 실측 및 시설물검증시험 합격 판정</t>
-        </is>
-      </c>
-      <c r="M27" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N27" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 시행지침 제14조에 따라 시설물검증시험계획을 작성하였는가?
-2) 전문기관인 한국교통안전공단으로부터 시설물검증시험계획 적격 승인을 수령하였는가?</t>
-        </is>
-      </c>
-      <c r="O27" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P27" s="68" t="n"/>
-      <c r="Q27" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R27" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S27" s="73" t="n"/>
-    </row>
-    <row r="28" ht="211.2" customHeight="1">
-      <c r="A28" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C28" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D28" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-27</t>
-        </is>
-      </c>
-      <c r="E28" s="61" t="inlineStr">
-        <is>
-          <t>영업시운전</t>
-        </is>
-      </c>
-      <c r="F28" s="61" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G28" s="60" t="inlineStr">
-        <is>
-          <t>발주처는 영업시운전계획에 따라 열차운행체계를 확인하기 위해 영업시운전을 수행</t>
-        </is>
-      </c>
-      <c r="H28" s="62" t="inlineStr">
-        <is>
-          <t>- (기준) 철도종합시험운행 시행지침 제22조(영업시운전계획의 수립), 23조(영업시운전의 시행)에 따름
-- 운영자는 영업시운전계획을 발주처와 협의하여 수립하고 전문기관의 승인을 받은 후 시행
-- 영업시운전 점검항목: 열차운행체계, 철도종사자(운전/관제 등)의 업무숙달, 영업서비스 준비사항
-- 영업조건과 동일한 조건으로 열차운행을 수행하여 운전/영업분야 점검
-- 운영자는 영업시운전 결과보고서를 한국교통안전공단에 제출(점검후 7일 이내)
-- 한국교통안전공단은 보고서를 받은 날부터 14일 이내 국토교통부장관에게 보고하여야 하며, 국토부 장관은 검토 결과를 보고를 받은 날부터 7일 이내에 발주처와 시도지사에 통보</t>
-        </is>
-      </c>
-      <c r="I28" s="61" t="inlineStr">
-        <is>
-          <t>영업시운전 결과보고서/승인문서(한국교통안전공단), 국토부 승인문서</t>
-        </is>
-      </c>
-      <c r="J28" s="74" t="inlineStr">
-        <is>
-          <t>1) 실제 영업 조건과 동일한 환경에서의 통신 시스템 연속 가동 및 관제 운용 검증
-2) 영업시운전 기간 중 통신 장애 0건 달성 및 시운전 완료 보고서 확정 표준 적용</t>
-        </is>
-      </c>
-      <c r="K28" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L28" s="74" t="inlineStr">
-        <is>
-          <t>1) 영업환경 가동 검증: 영업 시운전 스케줄에 따른 통신 시스템 24시간 연속 가동 및 관제 시스템 연동 상태 검증
-2) 시운전 준공 확정: 영업시운전 기간 중 통신 장해 0건 달성 및 영업시운전 종합 결과 보고서 확정</t>
-        </is>
-      </c>
-      <c r="M28" s="78" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N28" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 시행지침 제22조에 따른 영업시운전계획을 수립하였는가?
-2) 전 정거장 행선안내게시기(PIS) 도착 시각 및 열치 위치 안내 오송출 0건을 달성하였는가?</t>
-        </is>
-      </c>
-      <c r="O28" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P28" s="68" t="n"/>
-      <c r="Q28" s="75" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R28" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S28" s="73" t="n"/>
-    </row>
-    <row r="29" ht="115.2" customHeight="1">
-      <c r="A29" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C29" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D29" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-28</t>
-        </is>
-      </c>
-      <c r="E29" s="61" t="inlineStr">
-        <is>
-          <t>자가용전기통신설비 설치신고</t>
-        </is>
-      </c>
-      <c r="F29" s="61" t="inlineStr">
-        <is>
-          <t>시공사</t>
-        </is>
-      </c>
-      <c r="G29" s="60" t="inlineStr">
-        <is>
-          <t>자가용전기통신설비의 합법적 설치</t>
-        </is>
-      </c>
-      <c r="H29" s="80" t="inlineStr">
-        <is>
-          <t>- 관할 시청/구청에 설치공사 시작 21일 전까지 신고서와 설계도서 제출 (처리기간 15일)</t>
-        </is>
-      </c>
-      <c r="I29" s="61" t="inlineStr">
-        <is>
-          <t>자가전기통신설비 설치신고 필증</t>
-        </is>
-      </c>
-      <c r="J29" s="74" t="inlineStr">
-        <is>
-          <t>1) 전기통신사업법 제64조에 의거한 자가용전기통신설비 설치신고서 및 설비 개요서 작성
-2) 관할 지자체(화성시 등) 제출 및 설치신고 수리증 발급 획득 표준 적용</t>
-        </is>
-      </c>
-      <c r="K29" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L29" s="74" t="inlineStr">
-        <is>
-          <t>1) 신고 서류 작성: 전기통신사업법 제64조에 따른 자가용전기통신설비 설치신고서 및 통신망 개요도 작성
-2) 관할 관청 수리: 관할 지자체(화성시 등) 제출, 현장 서류 검토 수검 및 설치신고 수리증 발급 획득</t>
-        </is>
-      </c>
-      <c r="M29" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N29" s="74" t="inlineStr">
-        <is>
-          <t>1) 시방 대조[도면 및 여건] • 관련법령: 전기통신사업법 제64조 수칙을 사전 대조 확인하였는가?
-2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O29" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P29" s="68" t="n"/>
-      <c r="Q29" s="75" t="inlineStr">
-        <is>
-          <t>● 전기통신사업법 제64조</t>
-        </is>
-      </c>
-      <c r="R29" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S29" s="73" t="n"/>
-    </row>
-    <row r="30" ht="115.2" customHeight="1">
-      <c r="A30" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C30" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D30" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-29</t>
-        </is>
-      </c>
-      <c r="E30" s="61" t="inlineStr">
-        <is>
-          <t>LTE-R 무선국허가</t>
-        </is>
-      </c>
-      <c r="F30" s="61" t="inlineStr">
-        <is>
-          <t>발주처</t>
-        </is>
-      </c>
-      <c r="G30" s="60" t="inlineStr">
-        <is>
-          <t>무선국 설치 후 사용을 위한 법적 허가 취득</t>
-        </is>
-      </c>
-      <c r="H30" s="64" t="inlineStr">
-        <is>
-          <t>- 무선국(LTE-R) 설치 후 중앙전파관리소에 신청서, 시설개요서, 공사설계서 제출 (처리기간 14일)</t>
-        </is>
-      </c>
-      <c r="I30" s="61" t="inlineStr">
-        <is>
-          <t>무선국허가증</t>
-        </is>
-      </c>
-      <c r="J30" s="74" t="inlineStr">
-        <is>
-          <t>1) 전파법 제19조에 의거한 철도무선통신망(LTE-R) 무선국 개설허가 신청서 제출
-2) KCA(한국방송통신전파진흥원) 제출 및 무선국 개설허가서 획득 표준 적용</t>
-        </is>
-      </c>
-      <c r="K30" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L30" s="74" t="inlineStr">
-        <is>
-          <t>1) 허가 신청 절차: 전파법 제19조에 따른 LTE-R 무선국 개설허가 신청서, 안테나 제원표 및 기지국 좌표 작성
-2) 무선국 허가 획득: KCA(한국방송통신전파진흥원) 서류 심사 수검 및 무선국 개설허가서 최종 발급</t>
-        </is>
-      </c>
-      <c r="M30" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N30" s="74" t="inlineStr">
-        <is>
-          <t>1) 철도무선통신망 700MHz 대역(718~728MHz/773~783MHz) 주파수 할당 조건을 확인하였는가?
-2) 본선 지상 기지국 안테나 설치 위치, 높이, 이득(dBi) 및 지향각 제원을 조사하였는가?</t>
-        </is>
-      </c>
-      <c r="O30" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P30" s="68" t="n"/>
-      <c r="Q30" s="75" t="inlineStr">
-        <is>
-          <t>● 전파법 제19조</t>
-        </is>
-      </c>
-      <c r="R30" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S30" s="73" t="n"/>
-    </row>
-    <row r="31" ht="115.2" customHeight="1">
-      <c r="A31" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B31" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C31" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D31" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-30</t>
-        </is>
-      </c>
-      <c r="E31" s="61" t="inlineStr">
-        <is>
-          <t>LTE-R 상호운용성 및 보안적합성 검증</t>
-        </is>
-      </c>
-      <c r="F31" s="61" t="inlineStr">
-        <is>
-          <t>시공사</t>
-        </is>
-      </c>
-      <c r="G31" s="60" t="inlineStr">
-        <is>
-          <t>무선 장비의 보안성 및 타 기관 상호운용성 검증</t>
-        </is>
-      </c>
-      <c r="H31" s="64" t="inlineStr">
-        <is>
-          <t>- 한국정보통신기술협회에 시험결과서 제출하여 검증 진행 (처리기간 1개월)</t>
-        </is>
-      </c>
-      <c r="I31" s="61" t="inlineStr">
-        <is>
-          <t>상호운용성,보안적합성 시험 인증서</t>
-        </is>
-      </c>
-      <c r="J31" s="74" t="inlineStr">
-        <is>
-          <t>1) 국토교통부 지침 및 국가용 보안요구사항에 의거한 LTE-R 상호운용성/보안적합성 검증
-2) 국가정보원/KISA 보안 적합성 검증 승인서 및 상호연동 시험 합격 표준 적용</t>
-        </is>
-      </c>
-      <c r="K31" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L31" s="74" t="inlineStr">
-        <is>
-          <t>1) 검증 시험 절차: 국토교통부 LTE-R 상호운용성 시험 및 국가용 보안요구사항 기반 네트워크 보안적합성 검증
-2) 보안 승인 획득: KISA/국가정보원 보안 적합성 검증 수검 및 상호운용성 검증 합격 승인서 획득</t>
-        </is>
-      </c>
-      <c r="M31" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N31" s="74" t="inlineStr">
-        <is>
-          <t>1) 시방 대조[도면 및 여건] 관련법령: 국가철도공단 표준규격(KRSA) 수칙을 사전 대조 확인하였는가?
-2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O31" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P31" s="68" t="n"/>
-      <c r="Q31" s="75" t="inlineStr">
-        <is>
-          <t>● 국가철도공단 표준규격(KRSA) 5007-R3 / 5008-R2</t>
-        </is>
-      </c>
-      <c r="R31" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S31" s="73" t="n"/>
-    </row>
-    <row r="32" ht="115.2" customHeight="1">
-      <c r="A32" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B32" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C32" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D32" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-31</t>
-        </is>
-      </c>
-      <c r="E32" s="61" t="inlineStr">
-        <is>
-          <t>정보통신사용전검사</t>
-        </is>
-      </c>
-      <c r="F32" s="61" t="inlineStr">
-        <is>
-          <t>시공사</t>
-        </is>
-      </c>
-      <c r="G32" s="60" t="inlineStr">
-        <is>
-          <t>시공 완료된 정보통신설비의 준공 전 사용 적합성 검증</t>
-        </is>
-      </c>
-      <c r="H32" s="64" t="inlineStr">
-        <is>
-          <t>- 관할 시청/구청에 사용전검사 신청서와 준공설계도서 제출 (처리기간 14일)</t>
-        </is>
-      </c>
-      <c r="I32" s="61" t="inlineStr">
-        <is>
-          <t>정보통신사용전검사 필증</t>
-        </is>
-      </c>
-      <c r="J32" s="74" t="inlineStr">
-        <is>
-          <t>1) 정보통신공사업법 제36조에 의거한 구내 통신 및 정보통신설비 사용전검사 신청
-2) 관할 지자체 현장 검측 수검 및 정보통신 사용전검사 필증 획득 표준 적용</t>
-        </is>
-      </c>
-      <c r="K32" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L32" s="74" t="inlineStr">
-        <is>
-          <t>1) 사용전검사 신청: 정보통신공사업법 제36조에 따른 구내 통신 설비 사용전검측 신청서 작성 및 현장 준비
-2) 필증 발급 획득: 관할 지자체 정보통신 검측 공무원 현장 실측 수검 및 정보통신 사용전검사 필증 획득</t>
-        </is>
-      </c>
-      <c r="M32" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N32" s="74" t="inlineStr">
-        <is>
-          <t>1) 구내 UTP 랜선 전수에 대해 케이블 테스터 계측 Pass 100%를 달성하였는가?
-2) 정거장 승강장 및 관제동 배관 입상부 배관 씰링 및 네임택 표기 상태를 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O32" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P32" s="68" t="n"/>
-      <c r="Q32" s="75" t="inlineStr">
-        <is>
-          <t>● 정보통신공사법 제36조</t>
-        </is>
-      </c>
-      <c r="R32" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S32" s="73" t="n"/>
-    </row>
-    <row r="33" ht="115.2" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="inlineStr">
-        <is>
-          <t>9000-2</t>
-        </is>
-      </c>
-      <c r="C33" s="61" t="inlineStr">
-        <is>
-          <t>통신분야</t>
-        </is>
-      </c>
-      <c r="D33" s="61" t="inlineStr">
-        <is>
-          <t>9000-2-32</t>
-        </is>
-      </c>
-      <c r="E33" s="61" t="inlineStr">
-        <is>
-          <t>LTE-R 무선국 준공검사</t>
-        </is>
-      </c>
-      <c r="F33" s="61" t="inlineStr">
-        <is>
-          <t>발주처</t>
-        </is>
-      </c>
-      <c r="G33" s="60" t="inlineStr">
-        <is>
-          <t>무선국 전파 특성 검증 및 준공 처리</t>
-        </is>
-      </c>
-      <c r="H33" s="64" t="inlineStr">
-        <is>
-          <t>- 한국방송통신전파진흥원에 준공신고서, 안테나전력/주파수편차/불요발사강도 측정표, 안테나 Pattern 도표 제출 (처리기간 14일)</t>
-        </is>
-      </c>
-      <c r="I33" s="61" t="inlineStr">
-        <is>
-          <t>LTE-R 무선국 준공검사 확인서</t>
-        </is>
-      </c>
-      <c r="J33" s="74" t="inlineStr">
-        <is>
-          <t>1) 전파법 제24조에 의거한 KCA 무선국 준공검사 현장 실측 수검 실시
-2) 무선 전계강도 및 준공 상태 검사 합격 후 무선국 준공검사 합격증명서 획득 표준 적용</t>
-        </is>
-      </c>
-      <c r="K33" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L33" s="74" t="inlineStr">
-        <is>
-          <t>1) KCA 준공검측 수검: 전파법 제24조에 따른 KCA 무선국 준공검사 현장 무선 전계강도 및 스펙트럼 실측
-2) 합격 증명 획득: 준공 실측 합격 판정 수검 및 KCA 무선국 준공검사 합격증명서 최종 발급 획득</t>
-        </is>
-      </c>
-      <c r="M33" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N33" s="74" t="inlineStr">
-        <is>
-          <t>1) 전파법 시행령 제38조 서식에 맞춘 무선국 준공신고서를 KCA에 제출하였는가?
-2) 개설허가서 사본, 기지국 시공 내역서 및 안테나 제원표 구비를 완료하였는가?</t>
-        </is>
-      </c>
-      <c r="O33" s="67" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P33" s="68" t="n"/>
-      <c r="Q33" s="75" t="inlineStr">
-        <is>
-          <t>● 전파법 제24조</t>
-        </is>
-      </c>
-      <c r="R33" s="76" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S33" s="73" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId96"/>
-  </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -9,32 +9,33 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공정매뉴얼" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지반조사" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사전토공사" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지장물이설" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상부강화노반" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콘크리트도상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건축" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신호" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전기" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIDE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지반조사(원본서식)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사전토공사" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지장물이설" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상부강화노반" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콘크리트도상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건축" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신호" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통신" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전기" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIDE" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'공정매뉴얼'!$A$3:$P$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'공정매뉴얼'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'공정매뉴얼'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'사전토공사'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'사전토공사'!$A$1:$Q$31</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'지장물이설'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'지장물이설'!$A$1:$Q$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'상부강화노반'!$A$1:$Q$37</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'콘크리트도상'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'콘크리트도상'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'건축'!$A$1:$P$51</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'신호'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'신호'!$A$1:$P$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'통신'!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'전기'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'사전토공사'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'사전토공사'!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'지장물이설'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'지장물이설'!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'상부강화노반'!$A$1:$Q$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'콘크리트도상'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'콘크리트도상'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'건축'!$A$1:$P$51</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'신호'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'신호'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'통신'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'전기'!$A$1:$P$33</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +46,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -267,6 +268,13 @@
       <name val="맑은 고딕"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="19">
@@ -681,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1125,6 +1133,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2392,6 +2415,2362 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet7">
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <cols>
+    <col width="8.796875" customWidth="1" style="1" min="1" max="3"/>
+    <col width="16" customWidth="1" style="2" min="4" max="4"/>
+    <col width="23" customWidth="1" style="2" min="5" max="5"/>
+    <col width="20.19921875" customWidth="1" style="2" min="6" max="6"/>
+    <col width="38.3984375" customWidth="1" style="2" min="7" max="7"/>
+    <col width="55.59765625" customWidth="1" style="87" min="8" max="8"/>
+    <col width="16.59765625" customWidth="1" style="2" min="9" max="9"/>
+    <col width="48.8984375" customWidth="1" style="87" min="10" max="10"/>
+    <col width="14.19921875" customWidth="1" style="1" min="11" max="11"/>
+    <col width="62.59765625" customWidth="1" style="87" min="12" max="12"/>
+    <col width="12.19921875" customWidth="1" style="1" min="13" max="13"/>
+    <col width="53.796875" customWidth="1" style="87" min="14" max="14"/>
+    <col width="15.09765625" customWidth="1" style="84" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="16" max="16"/>
+    <col width="45" customWidth="1" style="84" min="17" max="17"/>
+    <col width="22" customWidth="1" style="84" min="18" max="18"/>
+    <col width="45" customWidth="1" style="1" min="19" max="35"/>
+    <col width="8.796875" customWidth="1" style="1" min="36" max="65"/>
+    <col width="8.796875" customWidth="1" style="1" min="66" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.2" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>L2 코드</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>L3 코드</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>L3 대공종명</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>L4 코드</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>작업단위 (Level 4 Task/Activity)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>주관</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="H1" s="86" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>산출물(결과)</t>
+        </is>
+      </c>
+      <c r="J1" s="86" t="inlineStr">
+        <is>
+          <t>표준서 (Standard) 요약</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>표준서 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="L1" s="86" t="inlineStr">
+        <is>
+          <t>수행지침 (Guideline) 요약</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>수행지침 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="N1" s="86" t="inlineStr">
+        <is>
+          <t>체크리스트 (Checklist) 요약</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>체크리스트 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>첨부서류 연계 상세 설계기준</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>집행단계 리스크 체크리스트</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>협력사 시공/공사관리 자문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="203.4" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C2" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-1</t>
+        </is>
+      </c>
+      <c r="E2" s="89" t="inlineStr">
+        <is>
+          <t>설계적정성 검토</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="G2" s="83" t="inlineStr">
+        <is>
+          <t>설계적정성 및 시공성 검토
+설계오류 확인 및 수량, 내역의 오류확인</t>
+        </is>
+      </c>
+      <c r="H2" s="90" t="inlineStr">
+        <is>
+          <t>- 입찰 요구사항에 대한 설계 반영여부 검토
+- 설계도서 및 표준 자재(트램신호, 도로신호) 반영여부 확인
+- 본선 및 차량기지 규모에 맞는 시스템 및 전자연동장치 구성의 적정성 검토
+- 본선 및 차량기지에 맞는 트램신호, 도로신호 설비 배치의 적정성 검토
+- SIL 인증제품 및 철도형식승인 제품적용, 경찰정 표준에 부합하는 제품 여부 확인
+- 독과점 / 외산 / 특허 여부 확인
+- 현장설치 시공성 및 원가 Risk 검토
+- 공정계획의 적정성 검토</t>
+        </is>
+      </c>
+      <c r="I2" s="83" t="inlineStr">
+        <is>
+          <t>회의록, 설계검토보고서</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>1) 설계적정성 검토(WBS 9000-1-1) 과업 달성을 위해 SIL 4 전자연동장치 및 응답지연(≤100ms) 성능 사양의 설계도서 대조를 완료하라.
+2) 철도 표준 자재(KRS) 및 분산형 CBI 용량, 선로전환기(4.5~6.0kN) 적정성을 검증하고 승인 보고서를 완수하라.</t>
+        </is>
+      </c>
+      <c r="K2" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>1) 입찰 요구사항 상의 기술 스펙 및 자재 규격을 시방서와 사전 대조하십시오.
+2) 분산형 CBI 및 선로전환기 용량의 현장 시공성 및 원가 Risk를 철저히 검토하여 승인을 획득하십시오.</t>
+        </is>
+      </c>
+      <c r="M2" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>1) 입찰 안내서 상의 SIL 4 등급 및 무선지연(≤100ms) 사양이 설계 도서에 반영되었는가?
+2) 철도 표준 자재(KRS) 규격 및 매립 선로전환기 전환력(4.5~6.0kN) 기준을 적격 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O2" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R2" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S2" s="83" t="n"/>
+    </row>
+    <row r="3" ht="139.8" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C3" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-2</t>
+        </is>
+      </c>
+      <c r="E3" s="89" t="inlineStr">
+        <is>
+          <t>착수준비 KOM</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G3" s="83" t="inlineStr">
+        <is>
+          <t>신호(트램신호, 도로신호)공사 발주 전 착수수립
+신호공사 발주전략 수립
+발주조건 CP 사항 검토</t>
+        </is>
+      </c>
+      <c r="H3" s="91" t="inlineStr">
+        <is>
+          <t>- 설계(트램신호, 도로신호) 및 현장여건 검토
+- 신호설비 공사 시공성 및 하자발생 리스크 검토
+- 본사 실무 협의를 거쳐 현장에 전파토록 현장공무 검토
+1) 공통계획 및 보완지침 계획 수립
+2) 외주 발주/수급 사전 준비 및 기술 지원
+3) 시공전 신호자재 확인 및 기술 지원
+4) 예상내역 및 누락 아이템 보완
+- 신호설비 공사 시공실적 업체Pool 검토
+- 현설조건 검토
+1) 공정계획 및 신호자재 제작 기간
+2) 안전성 검증을 위한 SIL 인증보유
+3) 철도안전용품 인증 및 경찰청 표준규격
+4) 예비품 및 소모품 확인
+5) 시운전 신호자재 운전 및 교육 지원
+6) 예산내역서 누락 아이템 여부</t>
+        </is>
+      </c>
+      <c r="I3" s="83" t="inlineStr">
+        <is>
+          <t>본사 외주/수행/협의 부서, 착수 KOM 결과보고서, 현장설명서</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>1) 착수준비 KOM(WBS 9000-1-2) 과업을 위해 신호(트램/도로) 공사 발주전략 수립 및 CP사항 사전 검토를 완료하라.
+2) 외주 수급, 신기술자재 확인, 내역 누락 방지 조치 및 SIL 인증보유 적격 업체 Pool을 확정하라.</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>1) 신호공사 발주 전 착수 수립 시 본사 실무 협의를 거쳐 현장 전파 및 시공성 리스크를 점검하십시오.
+2) 공정계획, 안전성 SIL 인증, 무상 A/S 및 철도안전법 준수 자재 투입 계획을 사전에 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M3" s="53" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>1) 신호공사 발주 조건 CP 사항 및 하자발생 리스크 사전 검토 수칙을 수행하였는가?
+2) 적격 업체 Pool 검토 및 내역 누락 방지 조치, SIL 인증 보유 여부를 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O3" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="83" t="n"/>
+      <c r="R3" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S3" s="83" t="n"/>
+    </row>
+    <row r="4" ht="221.4" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-3</t>
+        </is>
+      </c>
+      <c r="E4" s="89" t="inlineStr">
+        <is>
+          <t>착수전 Big Room 회의</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G4" s="83" t="inlineStr">
+        <is>
+          <t>신규공사 수행 시, 선행공정 간섭 및 공종 Risk에 대해 대책 수립</t>
+        </is>
+      </c>
+      <c r="H4" s="92" t="inlineStr">
+        <is>
+          <t>본사(신호/토목/노반/전기/건축/기계/통신) 및 분야별 세부설계 검토
+- 토목/궤도 I/F 사항 검토(시공계획 확인, 궤도 시공전 블록아웃 I/F 협의)
+- 전기/통신/차량 I/F 사항 검토(분야별 I/F 사항 정리)
+- 시운전 I/F 사항 검토(시운전 계획, 시험항목, 시험기간, 배치인원, 사전점검사항 등)
+- 관제 및 운영사 I/F 사항 검토(관제분야 및 운영사 요구사항등)
+- 인원, 자재, 장비 투입계획, 양중장비 운영계획 검토
+- 분야별 인터페이스 협의(궤도, 토목, 건축, 기계설비) 표준 지침서 배포
+- 현장 및 본사 Risk 요인 도출 및 대책 수립
+- 타 공정 및 분야별 Risk 분석 대안(도로/궤도/신호공사 수행 공동조정/안전)
+- 본사/현장/협력사 협의체 구축을 통한 세부내용 검토
+- 신호자재/기자재 반입로 및 야적장/제작사 공장 검토
+- 신호자재 성능보증: 유사사례 적용실적 및 성능보증 사항 검토
+- 하자 예방: 타 프로젝트 하자사례 검토 후, 동일제품 적용 방지방안 수립
+- SIL(Safety Integration Level) 인증제품 도입:  전자연동장치, 차상신호장치, 차축검지기, 선로전환기
+- 당사의 장비 안전검사 기준 공유, 장비검사 계획 확인
+- 관계기관 인허가 및 협의
+1) 화성시/수원시 교통센터, 경찰청 교차로 신호 운영 체계 및 연계 협의</t>
+        </is>
+      </c>
+      <c r="I4" s="83" t="inlineStr">
+        <is>
+          <t>Big Room 회의록(지침 전파 서명)</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>1) 착수전 Big Room 회의(WBS 9000-1-3)를 통해 본사 및 각 분야(토목/궤도/전기/건축/기계/통신) 간 시공 인터페이스를 대조하라.
+2) 궤도 시공 전 블록아웃, 배수로, 선로전환기, 차축검지기 설치 I/F 항목을 사전 확정하라.</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>1) 신규공사 수행 시 선행공정 간섭 및 공종 Risk 대책 회의를 주관하십시오.
+2) 궤도 시공 전 블록아웃 및 선로전환기 설치 I/F에 대해 각 분야 담당자와의 협의록을 작성하십시오.</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>1) 본사 및 분야별(토목/궤도/전기/건축/통신) 세부설계 인터페이스를 검토하였는가?
+2) 궤도 시공 전 블록아웃 및 차축검지기 설치 I/F 사전 대책을 수립하였는가?</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="83" t="n"/>
+      <c r="R4" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S4" s="83" t="n"/>
+    </row>
+    <row r="5" ht="187.2" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-4</t>
+        </is>
+      </c>
+      <c r="E5" s="89" t="inlineStr">
+        <is>
+          <t>전기 / 통신 / 건축 / 도로 / 궤도 / 차량 등 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G5" s="83" t="inlineStr">
+        <is>
+          <t>완벽한 시스템 조율 및 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H5" s="93" t="inlineStr">
+        <is>
+          <t>- 토목/궤도분야 인터페이스
+1) 단계별 시공계획 확인
+2) 궤도 시공전 블록아웃, 배수로, 선로전환기, 융설장치, 차축검지기 설치 I/F
+- 전기/통신/도로/차량 인터페이스
+1) (전기) 상용전원투입 및 접지단자함 설치
+2) (통신) 통신망 연결을 위한 회선제공
+3) (통신) 공용Pole 사용에 따른 인터페이스(굴착공사/공용 배관 배선 활용 등)
+4) (차량) 차상신호 및 열차종합제어장치(TCMS) 인터페이스 협의
+5) (차량) 지상신호설비 및 선형에 따른 지상/차상 장치 연계방안 협의
+6) (전기/통신) UPS 통합 사용 관련 Feeder 공급 또는 할당 
+7) (건축) 기계실 및 관제실 A/F 설치, 면척 및 기기 배치, 출입문 크기 등</t>
+        </is>
+      </c>
+      <c r="I5" s="83" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>1) 시스템 조율(WBS 9000-1-4)을 위해 전기/통신/건축/도로/궤도/차량 분야 간 시공 인터페이스를 조율하라.
+2) 궤도 시공 전 블록아웃, 배수로, 융설장치, 차축검지기 설치 I/F 승인서를 완수하라.</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>1) 토목/궤도 단계별 시공계획을 확인하고 기계실 배선 및 현장 장치 설치 I/F를 조율하십시오.
+2) 차축검지기 및 융설장치 체결 부위의 치수 적정성을 서면으로 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>1) 토목/궤도 시공 전 블록아웃 및 배수로 설치 I/F를 사전 확인하였는가?
+2) 차량기지 및 본선 선로전환기/차축검지기 체결 인터페이스를 조율하였는가?</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="83" t="n"/>
+      <c r="R5" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S5" s="83" t="n"/>
+    </row>
+    <row r="6" ht="104.4" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C6" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-5</t>
+        </is>
+      </c>
+      <c r="E6" s="89" t="inlineStr">
+        <is>
+          <t>도로 / 궤도 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G6" s="83" t="inlineStr">
+        <is>
+          <t>선로선형 설계를 위한 사전조정 및 트램 운행 최적화</t>
+        </is>
+      </c>
+      <c r="H6" s="90" t="inlineStr">
+        <is>
+          <t>- 유관기관 피드백 수렴/조정 및 요구사항 확인
+- 궤도 분기기 통과 요구사항 검토 및 확인
+- 궤도/토목 단계별 시공계획 확인
+- 궤도 시공전 블록아웃 등 I/F사항 협의
+- 선로전환기 어스박스 설치, 차축검지기 설치, 궤도 천공위치등 협의
+- 배수설비 설치 관련 사항 협의</t>
+        </is>
+      </c>
+      <c r="I6" s="83" t="inlineStr">
+        <is>
+          <t>궤도/신호 요구사항 및 회의록</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>1) 도로/궤도 I/F(WBS 9000-1-5) 달성을 위해 선로선형 및 궤도 분기기 통과 요구사항을 검토하라.
+2) 도심 매립 궤도용 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 설치 조건 및 유관기관 피드백을 반영하라.</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>1) 유관기관 피드백 수렴 및 궤도 분기기 통과 요구사항을 사전 조정하십시오.
+2) 도로 교차로 노면 매립 궤도 시공계획과 선로전환기 설치 위치 적정성을 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M6" s="53" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>1) 궤도 분기기 통과 요구사항 및 선로선형 사전조정 결과를 확인하였는가?
+2) 노면 매립형 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 시공조건을 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O6" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="83" t="n"/>
+      <c r="R6" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S6" s="83" t="n"/>
+    </row>
+    <row r="7" ht="133.8" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-6</t>
+        </is>
+      </c>
+      <c r="E7" s="89" t="inlineStr">
+        <is>
+          <t>시공전 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G7" s="83" t="inlineStr">
+        <is>
+          <t>시스템의 설계 보완 검토를 진행하고 완벽한 연계를 위한 설계</t>
+        </is>
+      </c>
+      <c r="H7" s="91" t="inlineStr">
+        <is>
+          <t>- 토목/궤도분야 인터페이스
+1) 단계별 시공계획 확인
+2) 궤도 시공전 블록아웃, 배수로, 선로전환기, 융설장치, 차축검지기 설치 I/F
+- 전기/통신/도로/차량 인터페이스
+1) (전기) 상용전원투입 및 접지단자함 설치
+2) (통신) 통신망 연결을 위한 회선제공
+3) (통신) 공용Pole 사용에 따른 인터페이스(굴착공사/공용 배관 배선 활용 등)
+4) (차량) 차상신호 및 열차종합제어장치(TCMS) 인터페이스 협의
+5) (차량) 지상신호설비 및 선형에 따른 지상/차상 장치 연계방안 협의
+6) (전기/통신) UPS 통합 사용 관련 Feeder 공급 또는 할당 
+7) (건축) 기계실 및 관제실 A/F 설치, 면척 및 기기 배치, 출입문 크기 등</t>
+        </is>
+      </c>
+      <c r="I7" s="83" t="inlineStr">
+        <is>
+          <t>인터페이스 보고서 및 인터페이스 회의록</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>1) 시공전 인터페이스(WBS 9000-1-6)를 통해 시스템 설계 보완 및 연계 방안을 정밀 검토하라.
+2) 배관배선 인입구, 구조물 간섭 및 궤도 시공 전 설치 항목을 개시 전 차단하라.</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>1) 시스템 설계 보완검토를 통해 연계 시공 시 발생 가능한 간섭을 사전에 제거하십시오.
+2) 궤도 시공 전 블록아웃 및 케이블 인입 배관의 간섭 여부를 정밀 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>1) 시스템 설계 보완 검토를 통해 연계 설치 방안을 확정하였는가?
+2) 케이블 인입 배관 및 궤도 블록아웃 간섭을 사전 제거하였는가?</t>
+        </is>
+      </c>
+      <c r="O7" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="83" t="n"/>
+      <c r="R7" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S7" s="83" t="n"/>
+    </row>
+    <row r="8" ht="127.8" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C8" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-7</t>
+        </is>
+      </c>
+      <c r="E8" s="89" t="inlineStr">
+        <is>
+          <t>시스템 장비검토 사전 협의사항 도출 및 검토</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G8" s="83" t="inlineStr">
+        <is>
+          <t>완벽한 시스템 연계 및 동작성 확보를 위한 가이드라인 제공</t>
+        </is>
+      </c>
+      <c r="H8" s="83" t="inlineStr">
+        <is>
+          <t>- 성능보증 기능성 신호자재 단품 Spec 검토
+- 제조사 자체 시험 및 인증 확인
+- 설치 시공대장 및 제작도서 승인 서명</t>
+        </is>
+      </c>
+      <c r="I8" s="83" t="inlineStr">
+        <is>
+          <t>자체 검증서 및 제작도서 승인 서류</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>1) 장비 사전검토(WBS 9000-1-7)를 위해 기능성 신호자재 단품 Spec 및 성능보증 사양을 검토하라.
+2) 제조사 자체 시험 성적서, KRS 표준 규격 및 제작도서 승인 서명을 완수하라.</t>
+        </is>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>1) 신호자재 단품 Spec 검토 및 제조사 자체 시험성적서를 확인하십시오.
+2) 제작도서 승인 서명 및 현장 투입 전 성능보증 기능을 검증하십시오.</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>1) 성능보증 기능성 신호자재 단품 Spec 검토를 완료하였는가?
+2) 제조사 공장검수 성적서 및 제작도서 승인 서명을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O8" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="83" t="n"/>
+      <c r="R8" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S8" s="83" t="n"/>
+    </row>
+    <row r="9" ht="104.4" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-8</t>
+        </is>
+      </c>
+      <c r="E9" s="89" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G9" s="83" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 요구사항 사전 반영 및 시공신뢰 확보</t>
+        </is>
+      </c>
+      <c r="H9" s="90" t="inlineStr">
+        <is>
+          <t>- 시운전시 조율사항 및 예비사항 도출
+- 신호제어 운영사 실무 조율 및 협의
+- 철도관제를 위한 관제사 조작반 및 화면표시 정보에 대한 사전협의 항목 도출
+- 설계내용 중 신호설비 운영 및 유지보수자 편의성 향상을 위한 기능추가 / 불필요 기능 삭제 사전협의</t>
+        </is>
+      </c>
+      <c r="I9" s="83" t="inlineStr">
+        <is>
+          <t>인터페이스 회의록 및 관리대장</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제/운영사 I/F(WBS 9000-1-8) 달성을 위해 종합관제실(OCC) 요구사항을 시공 전 반영하라.
+2) 철도관제를 위한 관제사 조작반 MMI 및 예비관제 1:1 실시간 DB 동기화를 검증하라.</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제 및 운영사 실무 조율을 거쳐 시운전 시 예비사항 및 조작반 화면표시 정보를 도출하십시오.
+2) 관제센터 MMI 화면 및 조작반 정보의 실시간 동기화 상태를 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>1) 시운전 시 조율사항 및 예비사항 도출을 완료하였는가?
+2) 철도관제를 위한 관제사 조작반 MMI 표시 정보를 사전 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="83" t="n"/>
+      <c r="R9" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S9" s="83" t="n"/>
+    </row>
+    <row r="10" ht="104.4" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C10" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-9</t>
+        </is>
+      </c>
+      <c r="E10" s="89" t="inlineStr">
+        <is>
+          <t>자재 / 인원 / 장비 및 투입 사전 검토</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 협력사 / 관리감독자</t>
+        </is>
+      </c>
+      <c r="G10" s="83" t="inlineStr">
+        <is>
+          <t>자재/인원/장비 투입 계획 수립</t>
+        </is>
+      </c>
+      <c r="H10" s="83" t="inlineStr">
+        <is>
+          <t>현장 여건 및 수량을 기준으로 투입 인원, 장비 계획 규명
+- 현장여건 및 궤도 시공계획 검토에 따른 시공계획 작성
+- 시공계획 작성에 따른 인력투입계획, 자재수급계획, 장비투입계획 작성
+- 시공계획 작성에 따른 관계기관(경찰청, 지자체 교통센터) 협의사항 도출
+- 공사에 따른 민원 또는 발주처 관계기관 요구사항 점검</t>
+        </is>
+      </c>
+      <c r="I10" s="83" t="inlineStr">
+        <is>
+          <t>세부 공정계획 수립 및 보고</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>1) 자재/인원/장비 계획(WBS 9000-1-9) 수립을 위해 현장 수량 기준 투입 계획을 승인하라.
+2) 현장 여건 및 궤도 시공계획 맞춤형 투입 schedule 작성 및 수급 조정을 완수하라.</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>1) 현장 여건 및 수량을 기준으로 투입 인원, 장비 계획서를 작성하여 감리단 승인을 받으십시오.
+2) 궤도 시공계획과 연계된 자재 반입 및 작업원 투입 스케줄을 조정하십시오.</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>1) 현장 수량 기준 투입 인원 및 장비 계획 규명서를 작성하였는가?
+2) 궤도 시공계획 연계 투입 스케줄 감리단 승인을 획득하였는가?</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="83" t="n"/>
+      <c r="R10" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S10" s="83" t="n"/>
+    </row>
+    <row r="11" ht="104.4" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C11" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-10</t>
+        </is>
+      </c>
+      <c r="E11" s="89" t="inlineStr">
+        <is>
+          <t>장비반입 및 안전교육</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀 / 안전팀</t>
+        </is>
+      </c>
+      <c r="G11" s="83" t="inlineStr">
+        <is>
+          <t>장비 반입 준비 및 안전교육 완료</t>
+        </is>
+      </c>
+      <c r="H11" s="90" t="inlineStr">
+        <is>
+          <t>- 도로 굴착장비, 고속작업 시 사용할 장비, 인양장비등 관련 장비 계획 검토
+- 장비 spec 확인, 장비 성능 점검
+- 작업원 안전교육 실시</t>
+        </is>
+      </c>
+      <c r="I11" s="83" t="inlineStr">
+        <is>
+          <t>측정기록서, 안전교육 결과서</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>1) 장비안전(WBS 9000-1-10) 확보를 위해 굴착/고속작업/인양 장비 Spec 점검 및 성능 검사를 시행하라.
+2) 작업원 특별 안전교육 및 위험성평가 이행 확인서를 승인 완수하라.</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>1) 도로 굴착 및 인양 장비 Spec 확인과 장비 성능 점검을 반입 전 수행하십시오.
+2) 신호 공사 작업원에 대한 특별 안전교육 및 보호구 착용 상태를 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M11" s="53" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>1) 도로 굴착 및 인양 장비 Spec 점검 및 성능 검사를 완료하였는가?
+2) 신호 공사 작업원 특별 안전교육 실시 기록을 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="83" t="n"/>
+      <c r="R11" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S11" s="83" t="n"/>
+    </row>
+    <row r="12" ht="104.4" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C12" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-11</t>
+        </is>
+      </c>
+      <c r="E12" s="89" t="inlineStr">
+        <is>
+          <t>자재 반입 및 검수</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주청/공동감리단</t>
+        </is>
+      </c>
+      <c r="G12" s="83" t="inlineStr">
+        <is>
+          <t>공장제품 품질 확보를 위한 자재 검수 및 검사</t>
+        </is>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>- 자재공급승인원 제출 및 승인
+- 공장검수 계획 제출 및 승인
+- 각종 자재 사양 확인(KS, 표준규격, 독/과점 규격 등)
+- 자재 현지 반입 및 반입동선, 반입기간, 반입장소 검토
+- 승인된 자재 상세사양 확인(Serial number 등록)
+- 제품의 규격, 수량 도면과 일치하는지 검토</t>
+        </is>
+      </c>
+      <c r="I12" s="83" t="inlineStr">
+        <is>
+          <t>자재검수요청서 / 자재수입검사서</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>1) 자재검수(WBS 9000-1-11) 강화를 위해 자재공급승인원(MAR) 제출 및 공장검수를 시행하라.
+2) 반입 자재의 KS/KRS 규격 시험성적서 대조 검수 및 품질 보증을 완수하라.</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>1) 자재공급승인원(MAR) 및 공장검수 계획서를 제출하여 감리단 승인을 획득하십시오.
+2) 자재 현지 반입 시 사양서, 시험성적서 및 표준규격 부합 여부를 인수 검수하십시오.</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>1) 자재공급승인원(MAR) 제출 및 공장검수 승인을 획득하였는가?
+2) 반입 자재 사양 확인(KS, KRS 표준규격) 및 수량 검수를 시행하였는가?</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="83" t="n"/>
+      <c r="R12" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S12" s="83" t="n"/>
+    </row>
+    <row r="13" ht="104.4" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-12</t>
+        </is>
+      </c>
+      <c r="E13" s="89" t="inlineStr">
+        <is>
+          <t>시스템설비 설치 (현장/기능실)</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 분야별 전담팀</t>
+        </is>
+      </c>
+      <c r="G13" s="83" t="inlineStr">
+        <is>
+          <t>현장설비 및 기기실의 자체 최적의 설치작업</t>
+        </is>
+      </c>
+      <c r="H13" s="83" t="inlineStr">
+        <is>
+          <t>- 기계 장치 위치 및 마감 동선 확인
+- 승인된 자재 상세사양 확인 (Serial number 등록)
+- 제품의 규격, 수량 도면과 일치하는지 검토
+- 배선/기능실 배선 상태 및 신호 인터페이스 확인
+- 배선/기능실 케이블 및 전선 배선을 시운전 및 계측기 결과에 준하여 시행
+- 케이블 단선부 및 배선 등 내부 배선 및 배선 결과 검수서</t>
+        </is>
+      </c>
+      <c r="I13" s="83" t="inlineStr">
+        <is>
+          <t>검사 결과서</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>1) 시스템설비 설치(WBS 9000-1-12)를 위해 기계실 랙 마감 동선 및 승인 자재 상세 사양을 확인하라.
+2) 현장 신호기, 선로전환기 기초 볼트 체결 및 도면 일치 여부를 정밀 시공하라.</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>1) 기계실 장치 위치, 마감 동선 및 승인 자재 Serial Number 등록을 확인하십시오.
+2) 현장 설치 설비의 규격, 수량 및 도면 일치 여부를 정밀 측정하여 시공하십시오.</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>1) 기계실 장치 위치, 마감 동선 및 승인 자재 사양을 확인하였는가?
+2) 현장 신호기/선로전환기 기초 볼트 체결 및 규격 일치 여부를 시공하였는가?</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R13" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S13" s="83" t="n"/>
+    </row>
+    <row r="14" ht="104.4" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-14</t>
+        </is>
+      </c>
+      <c r="E14" s="89" t="inlineStr">
+        <is>
+          <t>시스템 단위시험</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G14" s="83" t="inlineStr">
+        <is>
+          <t>철도안전법상 신호시스템 규정에 대한 설치 후 현황시험 및 기능 확보</t>
+        </is>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>- 자체단독시험 및 관계부서 공동 시험수행 여부
+- 지상신호장치 및 관계부서 단위시험 결과서
+- 감리단이 승인한 검사 및 시험 점검표 (ITP/ITC) 절차에 따라 수행
+- 지상신호설비 단위시험 항목
+1) 신호기장치 / 선로전환기 장치 / 전자연동장치 / 열차자동방호장치 / 신호전원장치 / 전선로 / 안전설비 / 기타설비 / 트램신호기 / TPD 등
+- 관제설비
+1) 서버설치 / 네트워크 장치 / 콘솔장치 / 대형표시반 / LDTS</t>
+        </is>
+      </c>
+      <c r="I14" s="83" t="inlineStr">
+        <is>
+          <t>자체단독시험 및 시험결과서 (단독단위)</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>1) 단위시험(WBS 9000-1-14) 수행을 위해 철도안전법 규정에 따른 설치 후 단독 현황시험을 시행하라.
+2) 신호기, 선로전환기, 전원장치, 차축검지기 개별 ITP/ITC 시험 결과서를 승인 완수하라.</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>1) 자체 단독시험 및 관계부서 공동 시험수행 여부를 확인하십시오.
+2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 지상신호장치 단위시험 결과서를 작성하십시오.</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>1) 지상신호장치 및 관계부서 단위시험 결과서를 확인하였는가?
+2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 개별 단독 현황시험을 수행하였는가?</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R14" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S14" s="83" t="n"/>
+    </row>
+    <row r="15" ht="104.4" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C15" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-15</t>
+        </is>
+      </c>
+      <c r="E15" s="89" t="inlineStr">
+        <is>
+          <t>신호시스템 통합시험</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G15" s="83" t="inlineStr">
+        <is>
+          <t>신호시스템 단독시험 완료 후 타 분야 연계 및 시설 유효성 확인</t>
+        </is>
+      </c>
+      <c r="H15" s="90" t="inlineStr">
+        <is>
+          <t>- 관계성과 연계 인터페이스 시험
+- 지상 및 차량 인터페이스
+- 지상 및 차량 인터페이스 시 시험 결과표
+- 감리단이 승인한 검사 및 시험 점검표 (ITP/ITC) 절차에 따라 수행
+1) 관제실 및 현장 연동장치간 인터페이스 시험
+2) 지상 및 차상 인터페이스 시험
+3) 도로신호/트램신호 인터페이스 시험(우선신호 시험)</t>
+        </is>
+      </c>
+      <c r="I15" s="83" t="inlineStr">
+        <is>
+          <t>자체단독시험 및 시험결과서 (단독단위)</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>1) 통합시험(WBS 9000-1-15)을 통해 단독시험 완료 후 관제 ➔ CBI 전자연동장치 통합 연동을 검증하라.
+2) 차상-지상 무선(LTE-R) 도로-트램 우선신호 연계 시험 결과표를 승인 완수하라.</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제실 및 현장 연동장치 간 인터페이스 통합시험을 시행하십시오.
+2) 지상-차상 인터페이스 및 도로/트램 우선신호 무선 연계시험 결과표를 작성하십시오.</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제실 및 현장 연동장치 간 인터페이스 시험을 수행하였는가?
+2) 지상-차상 인터페이스 및 도로-트램 우선신호 연계 시험을 검증하였는가?</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R15" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S15" s="83" t="n"/>
+    </row>
+    <row r="16" ht="104.4" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C16" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-16</t>
+        </is>
+      </c>
+      <c r="E16" s="89" t="inlineStr">
+        <is>
+          <t>공종별 시험</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G16" s="83" t="inlineStr">
+        <is>
+          <t>철도안전기준에 따른 법정 / 설계기준 / 신기술 / 시운전 등의 요구사항의 적합성 검증</t>
+        </is>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>- 신기술공법 등 신공법 적용
+- 자료정리 및 단위 시험
+- 신기술공법/기능성/현장성 단위 시험 결과서
+- 현장설비 시험
+1) 신호기 장치: 신호기 설치 / 투시거리 및 정상 동작시험
+2) 신호부속기(진로표시기): 진로표시기 설치 및 정상 동작시험
+3) 차축검지기 설치 및 정상 동작시험
+4) 선로전환기 설치상태 확인시험
+5) 트램신호기, TPD, 설치 및 동작시험
+6) 교차로 영상유고 시스템 설치 및 동작시험
+- 신호기계실 설비 시험
+1) 전원공급장치 이중화 확인 및 절체 시험 수행
+2) 전자연동장치 설치 및 정상 동작시험
+3) 전자열쇠 정상 작동상태 확인
+4) 차축검지기부 설치 및 정상 동작시험
+- 관제설비 시험
+1) 관제실: 운영관제실 MMI 장치 동작상태
+2) 신호컴퓨터실: 신호컴퓨터실 서버 및 네트워크 정상 동작상태 확인
+3) 전원장치 정상 동작상태 확인</t>
+        </is>
+      </c>
+      <c r="I16" s="83" t="inlineStr">
+        <is>
+          <t>공종별 시험 결과보고서</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>1) 공종별 시험(WBS 9000-1-16)을 위해 신호기, 진로표시기, 선로전환기, 차축검지기 현장 동작시험을 시행하라.
+2) 신호기계실 전원 2중화 절체 시험 및 관제 CTC 서버 정상 동작 시험을 완수하라.</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>1) 현장설비(신호기 투시거리, 선로전환기 쇄정, 차축검지기) 동작시험을 시행하십시오.
+2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 정상 동작상태를 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>1) 신호기 투시거리/진로표시기 및 선로전환기 쇄정 동작시험을 수행하였는가?
+2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 동작을 검증하였는가?</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R16" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S16" s="83" t="n"/>
+    </row>
+    <row r="17" ht="104.4" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C17" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-17</t>
+        </is>
+      </c>
+      <c r="E17" s="89" t="inlineStr">
+        <is>
+          <t>차량 투입 전 점검</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 시공전담팀</t>
+        </is>
+      </c>
+      <c r="G17" s="83" t="inlineStr">
+        <is>
+          <t>차량 시험운행 전 철저한 안전대책 수립 및 품질성 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="H17" s="90" t="inlineStr">
+        <is>
+          <t>- 현장의 시설물 설치상태 점검
+1) 연동검사(설비동작, 진로취급 및 신호현시 시험 등)
+2) 신호 기계실 내 시스템 검사(연동장치, 열차제어시스템 등)
+3) 전원장치 시험(UPS 및 배터리)
+4) 신호 기계실 내부 방재예방 설비(소화기, 접지저항값 측정결과)
+5) 신호기 시공상태(설치 위치의 적정성, 신호기와 건축물과의 건축한계 적정여부 등)
+6) 선로전환기 시공상태 확인(선로전환기 전환 및 표시회로 구성 등)
+7) 전선류 시공상태 확인(케이블 단말처리 및 접속개소, 선명찰 절연저항 측정값 등)
+8) 기구함, 접속함 등 시공상태 확인(기초 시공적정여부, 전선 인입구, 접지설비, 볼트류 체결 상태 등)
+9) 본선의 시설물 성능장애 점검
+- 건축한계 및 차량한계
+- 가공선로: 폭(3,100mm)/높이(3,800mm) 및 차량한계: 폭(2,700mm)/높이(3,600mm) 정렬선 개시
+- 수전 및 전압 점검</t>
+        </is>
+      </c>
+      <c r="I17" s="83" t="inlineStr">
+        <is>
+          <t>차량 투입 전 점검 결과 보고서</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>1) 차량 투입 전 점검(WBS 9000-1-17)을 통해 연동검사 및 기계실 방재/접지저항 측정을 시행하라.
+2) 건축한계/차량한계 이격 정밀 측정 및 전원장치(UPS) 성능을 최종 검증하라.</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>1) 연동검사(설비동작, 진로취급) 및 신호기 시공상태 적정성을 점검하십시오.
+2) 건축한계(폭 3.1m/높이 3.8m) 이격 측정 및 기계실 UPS/방재예방 설비를 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>1) 연동검사 및 기계실 시스템/UPS 시험을 완료하였는가?
+2) 신호기와 건축물 간 건축한계 정밀 측정 및 방재설비를 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R17" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S17" s="83" t="n"/>
+    </row>
+    <row r="18" ht="104.4" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C18" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-18</t>
+        </is>
+      </c>
+      <c r="E18" s="89" t="inlineStr">
+        <is>
+          <t>차량 시운전</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G18" s="83" t="inlineStr">
+        <is>
+          <t>철도안전법상 철도기술기준에 적합하게 시운전 수행 여부(철도노선 규정)</t>
+        </is>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>- 철도기술기준(궤도/철도차량 안전성) 준수 여부
+1) 속도/제동 테스트수행 여부
+2) 차량, 신호, 통신 시스템간 인터페이스 시험
+- 철도안전법 제26조(철도차량 형식승인) 기준 준수
+1) 주요 외관검사 및 치수검사
+2) 주요기기 기능검사(제어전원 투입확인, 집전장치 동작확인, 추진제어장치 동작확인 등)
+- 차상신호장치 포함시 시행(차상신호장치는 차량제작사 공급 or 신호설비 공급사 공급)
+1) 지·차상 연계동작시험
+2) 차량, 신호, 통신 시스템간 인터페이스 시험
+3) 열차제어 시스템 기능시험
+- 센터간 I/F 시험
+1) 교통관제센터/트램관제센터간 정보전송 상태
+2) 차량 위치검지 시험</t>
+        </is>
+      </c>
+      <c r="I18" s="83" t="inlineStr">
+        <is>
+          <t>철도차량 안전성 결과 보고서</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>1) 차량 시운전(WBS 9000-1-18) 수행 시 철도안전법 제26조 형식승인 기준 준수 여부를 검증하라.
+2) 속도/제동 테스트, 차상-지상 연계동작 및 열차제어 시스템 기능시험을 완수하라.</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>1) 철도기술기준에 따라 속도/제동 테스트 및 주요기기 제어전원 투입을 검사하십시오.
+2) 차상신호장치 지·차상 연계동작시험 및 열차제어 시스템 기능시험을 시행하십시오.</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>1) 철도기술기준 준수 속도/제동 테스트 및 주요기기 검사를 시행하였는가?
+2) 차상-지상 연계동작시험 및 차량-신호-통신 I/F 시험을 검증하였는가?</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R18" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S18" s="83" t="n"/>
+    </row>
+    <row r="19" ht="104.4" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C19" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-19</t>
+        </is>
+      </c>
+      <c r="E19" s="89" t="inlineStr">
+        <is>
+          <t>운영자 교육시행</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>현장 시스템팀</t>
+        </is>
+      </c>
+      <c r="G19" s="83" t="inlineStr">
+        <is>
+          <t>운영요원(기관사 및 안전관리)을 위한 주행/유지 교육시행</t>
+        </is>
+      </c>
+      <c r="H19" s="90" t="inlineStr">
+        <is>
+          <t>- 시스템안전 교육(철도차량 안전점검 요령)
+- 차량, 신호, 통신 시스템간 인터페이스 사용방법 및 조작 교육
+- 관제센터와의 연계 기계실/차량내 장치(DID 보드 등) 운영 및 테스트
+- 시스템공급  장비제작사에 의한 운영자 및 유지보수자 교육
+1) (관제설비) CTC서버, 콘솔컴퓨터 등
+2) (신호 기계실) 전자연동장치, 궤도회로장치 등
+3) (현장설비) 신호기, 선로전환기, 튜닝유니트 등</t>
+        </is>
+      </c>
+      <c r="I19" s="83" t="inlineStr">
+        <is>
+          <t>운영자훈련 및 기술단계에서 운영지침서</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1) 운영자 교육(WBS 9000-1-19)을 위해 기관사 및 유지보수 요원 대상 시스템 안전 교육을 시행하라.
+2) 장비 제작사에 의한 CTC/CBI/현장설비 조작·정비 기술 교육 완료 이수증을 승인하라.</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>1) 철도차량 안전점검 요령 및 시스템 간 조작 방법에 대한 운영자 교육을 시행하십시오.
+2) CTC 서버, 전자연동장치, 현장 신호기/선로전환기 교육 이수 현황을 확인하십시오.</t>
+        </is>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>1) 기관사 및 유지보수요원 대상 시스템 안전 교육을 시행하였는가?
+2) 장비 제작사에 의한 CTC/CBI/현장설비 조작교육을 완료하였는가?</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R19" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S19" s="83" t="n"/>
+    </row>
+    <row r="20" ht="104.4" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C20" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-20</t>
+        </is>
+      </c>
+      <c r="E20" s="89" t="inlineStr">
+        <is>
+          <t>사전점검 및 철도기술기준 검토</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G20" s="83" t="inlineStr">
+        <is>
+          <t>철도종합시험운행에 따른 기능 및 성능 사전검증과 철도종합시험운행의 목적 달성의 적합여부 판정</t>
+        </is>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>- 분야외 시설물 성능장치 점검
+- (1부)철도종합시험운행 시행지침 제6조(종합시험운행을 위한 사전점검)
+- 현장점검을 위한 계획 및 체크리스트 수립에 의하여 내 조직 가능한 항목에 대해 사전기재 및 결과 기재
+- (기준) 철도종합시험운행 시행지침 제8조(종합시험운행을 위한 사전점검)
+- 현장점검을 위한 계획 및 체크리스트를 사전에 준비하여 기한 내 조치가능한 점검항목 도출
+1) 철도시설물 시공상태 및 기능확인, 공종별시험 결과보고서 검토
+2) 철도시설의 기술기준 준수여부
+3) 관련 법령에 따른 외부기관의 검사완료 가능여부 확인
+4) 시설물검증시험 전까지 대상 철도시설물 완공가능 여부확인
+5) 철도시설의 안전성 분석결과 및 분석결과에 따른 안전대책 검토
+6) 종합시험운행(시설물검증시험·영업시운전) 시행에 필요한 사항확인 등</t>
+        </is>
+      </c>
+      <c r="I20" s="83" t="inlineStr">
+        <is>
+          <t>사전점검 결과표 / 철도안전성검토서</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>1) 사전점검(WBS 9000-1-20)을 위해 철도종합시험운행 시행지침 제6조/제8조 검토 수칙을 이행하라.
+2) 시설물 시공상태, 기술기준 준수 및 완공 가능 여부 사전점검 체크리스트를 완수하라.</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 제6조/제8조에 따라 사전점검 체크리스트를 사전에 준비하십시오.
+2) 시설물 시공상태, 기술기준 준수 여부 및 공종별시험 결과보고서를 검토하십시오.</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 제6조/제8조 사전점검 체크리스트를 수립하였는가?
+2) 철도시설물 시공상태, 기술기준 준수 및 안전성 분석 결과를 검토하였는가?</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R20" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S20" s="83" t="n"/>
+    </row>
+    <row r="21" ht="104.4" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C21" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-21</t>
+        </is>
+      </c>
+      <c r="E21" s="89" t="inlineStr">
+        <is>
+          <t>시설물 검증시험</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G21" s="83" t="inlineStr">
+        <is>
+          <t>시설물검증 노선에 환경에 철도종합시험운행 시행지침에 의거 철도노선 및 관계시설을 검증하여 안전성 확보 여부 판단</t>
+        </is>
+      </c>
+      <c r="H21" s="90" t="inlineStr">
+        <is>
+          <t>- 철도종합시험운행 시행지침상 검사사항 검증
+- 철도종합시험운행 시설물검증시험 점검항목 시행
+- 시설물 특성 및 규모에 따른 설계속도 또는 선로 최고운행속도 까지 증속하여 다음의 사항을 점검
+1) 신호시설물의 정상 동작상태
+2) 신호시설물의 안전상태
+3) 철도차량의 운행 적합성 적정여부
+4) 신호설비와 차량간 연계성 적정여부</t>
+        </is>
+      </c>
+      <c r="I21" s="83" t="inlineStr">
+        <is>
+          <t>시설물 검증시험 시험결과 및 승인원, 완료결과보고서</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>1) 시설물 검증(WBS 9000-1-21)을 위해 최고운행속도 증속 시운전을 시행하고 신호 정상동작을 검증하라.
+2) 신호설비와 차량 간 연계성 및 철도차량 운행 적합성 검증 결과표를 승인 완수하라.</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>1) 설계 최고운행속도까지 단계별 증속하여 신호시설물 정상 동작 및 안전성을 점검하십시오.
+2) 신호설비와 차량 간 연계 적정성 및 철도차량 운행 적합 여부를 서면 판정하십시오.</t>
+        </is>
+      </c>
+      <c r="M21" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>1) 설계 최고운행속도 증속 시운전 시 신호시설물 정상 동작을 확인하였는가?
+2) 신호설비와 차량 간 연계성 및 차량 운행 적합성을 검증하였는가?</t>
+        </is>
+      </c>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R21" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S21" s="83" t="n"/>
+    </row>
+    <row r="22" ht="104.4" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C22" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-22</t>
+        </is>
+      </c>
+      <c r="E22" s="89" t="inlineStr">
+        <is>
+          <t>영업 시운전</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>현장소장 및 발주처 / 공동감리단</t>
+        </is>
+      </c>
+      <c r="G22" s="83" t="inlineStr">
+        <is>
+          <t>영업 시운전에 의한 수송능력을 파악하고 최종 운영기관과 인터페이스 협의를 통해 시공의 안정성 확보 여부 및 검증</t>
+        </is>
+      </c>
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>- 모의 영업 시나리오 기반 100회 정시 운행 성공률 99.8% 이상 확보
+- 영업운전과 동일한 조건으로 행사수송 수행 및 영업준비 수행
+- 철도안전관련계 체계 및 시운전수행 승인 등 관계 기관에 제출
+- 영업조건과 동일한 조건으로 열차운행을 위한 운전분야 및 영업분야 시행
+- 열차운행스케쥴 및 영업설비 점검
+- 승무원 노선숙지 등 업무숙달 훈련
+- 철도시설과 차량과의 인터페이스 최종 점검</t>
+        </is>
+      </c>
+      <c r="I22" s="83" t="inlineStr">
+        <is>
+          <t>영업 시운전 및 가동단계에서 운영지침서 및 최종 제출서(가동시험보고서)</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>1) 영업 시운전(WBS 9000-1-22)을 위해 모의 영업 시나리오 기반 100회 정시 운행 성공률(≥99.8%)을 달성하라.
+2) 영업운전과 동일 조건 열차스케줄 및 승무원 노선숙지 등 최종 영업준비를 완수하라.</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>1) 모의 영업 시나리오에 따라 100회 정시 운행 성공률(≥99.8%) 이상을 확보하십시오.
+2) 영업운전과 동일한 조건으로 열차운행 스케줄 및 영업설비 최종 점검을 완료하십시오.</t>
+        </is>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>1) 모의 영업 시나리오 기반 100회 정시 운행 성공률(≥99.8%)을 달성하였는가?
+2) 영업운전 동일 조건 행사수송 및 승무원 노선숙지 훈련을 완수하였는가?</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R22" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S22" s="83" t="n"/>
+    </row>
+    <row r="23" ht="104.4" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>9000-1</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="inlineStr">
+        <is>
+          <t>신호분야</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>9000-1-13</t>
+        </is>
+      </c>
+      <c r="E23" s="89" t="inlineStr">
+        <is>
+          <t>유지관리 설치</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="G23" s="83" t="inlineStr">
+        <is>
+          <t>관제 관제실의 장비체계 배치 및 설치</t>
+        </is>
+      </c>
+      <c r="H23" s="83" t="inlineStr">
+        <is>
+          <t>- 유지 및 보수용 상세 공사 설계배치 확인
+- 현장조성 및 유지관리 지침서 이행 여부</t>
+        </is>
+      </c>
+      <c r="I23" s="83" t="inlineStr">
+        <is>
+          <t>유지관리 지침 및 관리 이행 보고서</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>1) 유지관리 설치(WBS 9000-1-13)를 위해 관제실 유지보수용 장비 배치 및 상세 공사 설계를 확인하라.
+2) 현장조성 및 유지관리 지침서 이행 여부를 확인하고 관제 MMI 보수를 완수하라.</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제실 유지 및 보수용 상세 공사 설계 배치를 확인하고 장비를 시공하십시오.
+2) 현장 조성 및 유지관리 지침서 이행 여부를 점검하여 서면 보고하십시오.</t>
+        </is>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>1) 관제실 유지보수용 상세 공사 설계 배치를 확인하였는가?
+2) 현장조성 및 유지관리 지침서 이행 여부를 점검 확인하였는가?</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="83" t="inlineStr">
+        <is>
+          <t>● 관련분야 설계기준서 준수</t>
+        </is>
+      </c>
+      <c r="R23" s="85" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="S23" s="83" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="38" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5641,7 +8020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FFFFFF00"/>
@@ -8562,7 +10941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet10">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14386,6 +16765,3302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="159" t="inlineStr">
+        <is>
+          <t>L2 코드</t>
+        </is>
+      </c>
+      <c r="B1" s="159" t="inlineStr">
+        <is>
+          <t>L3 코드</t>
+        </is>
+      </c>
+      <c r="C1" s="159" t="inlineStr">
+        <is>
+          <t>L3 대공종명</t>
+        </is>
+      </c>
+      <c r="D1" s="159" t="inlineStr">
+        <is>
+          <t>L4 코드</t>
+        </is>
+      </c>
+      <c r="E1" s="159" t="inlineStr">
+        <is>
+          <t>일정 (D-Day)</t>
+        </is>
+      </c>
+      <c r="F1" s="159" t="inlineStr">
+        <is>
+          <t>작업단위 (Level 4 Task/Activity)</t>
+        </is>
+      </c>
+      <c r="G1" s="159" t="inlineStr">
+        <is>
+          <t>주관</t>
+        </is>
+      </c>
+      <c r="H1" s="159" t="inlineStr">
+        <is>
+          <t>협업부서</t>
+        </is>
+      </c>
+      <c r="I1" s="159" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="J1" s="159" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="K1" s="159" t="inlineStr">
+        <is>
+          <t>산출물(결과)</t>
+        </is>
+      </c>
+      <c r="L1" s="159" t="inlineStr">
+        <is>
+          <t>표준서 (Standard) 요약</t>
+        </is>
+      </c>
+      <c r="M1" s="159" t="inlineStr">
+        <is>
+          <t>표준서 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="N1" s="159" t="inlineStr">
+        <is>
+          <t>수행지침 (Guideline) 요약</t>
+        </is>
+      </c>
+      <c r="O1" s="159" t="inlineStr">
+        <is>
+          <t>수행지침 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="P1" s="159" t="inlineStr">
+        <is>
+          <t>체크리스트 (Checklist) 요약</t>
+        </is>
+      </c>
+      <c r="Q1" s="159" t="inlineStr">
+        <is>
+          <t>체크리스트 파일 (HTML)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C2" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D2" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-1</t>
+        </is>
+      </c>
+      <c r="E2" s="135" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="F2" s="145" t="inlineStr">
+        <is>
+          <t>발주처 계획 입수(비공식)</t>
+        </is>
+      </c>
+      <c r="G2" s="137" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="H2" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체, 외부지질전문가 3인이상</t>
+        </is>
+      </c>
+      <c r="I2" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 사전 검토</t>
+        </is>
+      </c>
+      <c r="J2" s="136" t="inlineStr">
+        <is>
+          <t>• 조사설계 용역 기본계획 도서 확보 여부 확인
+• 핵심이슈 (미시추 사유, 지층/암반등급 조정여부 등) 확보 여부 확인
+• 사업지 연접 지질/지반조사 자료 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="K2" s="145" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 보고서</t>
+        </is>
+      </c>
+      <c r="L2" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 사전 검토 | 발주처 기본계획 보고서</t>
+        </is>
+      </c>
+      <c r="M2" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N2" s="136" t="inlineStr">
+        <is>
+          <t>• 조사설계 용역 기본계획 도서 확보 여부 확인 • 핵심이슈 (미시추 사유, 지층/암반등급 조정여부 등) 확보 여부 확인 • 사업지 연접 지질/지반조사 자료 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="O2" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P2" s="136" t="inlineStr">
+        <is>
+          <t>1) 발주처 계획 입수(비공식) 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q2" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B3" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C3" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D3" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-2</t>
+        </is>
+      </c>
+      <c r="E3" s="141" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="F3" s="140" t="inlineStr">
+        <is>
+          <t>관심프로젝트 선정</t>
+        </is>
+      </c>
+      <c r="G3" s="143" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="H3" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I3" s="142" t="inlineStr">
+        <is>
+          <t>입수된 발주정보 평가를 통한 관심 Project 선정</t>
+        </is>
+      </c>
+      <c r="J3" s="142" t="inlineStr">
+        <is>
+          <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행
+• 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
+        </is>
+      </c>
+      <c r="K3" s="140" t="inlineStr">
+        <is>
+          <t>관심사업 List</t>
+        </is>
+      </c>
+      <c r="L3" s="142" t="inlineStr">
+        <is>
+          <t>입수된 발주정보 평가를 통한 관심 Project 선정 | 관심사업 List</t>
+        </is>
+      </c>
+      <c r="M3" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N3" s="142" t="inlineStr">
+        <is>
+          <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행 • 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
+        </is>
+      </c>
+      <c r="O3" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P3" s="142" t="inlineStr">
+        <is>
+          <t>1) 관심프로젝트 선정 적정성을 확인하였는가? 2) 관심사업 List 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q3" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B4" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C4" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D4" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-3</t>
+        </is>
+      </c>
+      <c r="E4" s="135" t="inlineStr">
+        <is>
+          <t>사전영업</t>
+        </is>
+      </c>
+      <c r="F4" s="145" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 모니터링</t>
+        </is>
+      </c>
+      <c r="G4" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H4" s="137" t="inlineStr">
+        <is>
+          <t>토목사업팀</t>
+        </is>
+      </c>
+      <c r="I4" s="136" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 수립업체 파악</t>
+        </is>
+      </c>
+      <c r="J4" s="136" t="inlineStr">
+        <is>
+          <t>• 발주처 지반조사업체 확인 후 당사 Pool List와 비교
+• 발주처 지반조사 업체 확인팀 Contact Point 확보</t>
+        </is>
+      </c>
+      <c r="K4" s="145" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 수행 List + Contact Point List</t>
+        </is>
+      </c>
+      <c r="L4" s="136" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 수립업체 파악 | 발주처 기본계획 수행 List + Contact Point List</t>
+        </is>
+      </c>
+      <c r="M4" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N4" s="136" t="inlineStr">
+        <is>
+          <t>• 발주처 지반조사업체 확인 후 당사 Pool List와 비교 • 발주처 지반조사 업체 확인팀 Contact Point 확보</t>
+        </is>
+      </c>
+      <c r="O4" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P4" s="136" t="inlineStr">
+        <is>
+          <t>1) 발주처 지반조사 모니터링 적정성을 확인하였는가? 2) 발주처 기본계획 수행 List + Contact Point List 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q4" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B5" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C5" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D5" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-4</t>
+        </is>
+      </c>
+      <c r="E5" s="141" t="inlineStr">
+        <is>
+          <t>매년 1분기</t>
+        </is>
+      </c>
+      <c r="F5" s="140" t="inlineStr">
+        <is>
+          <t>외부 지질전문가 Pool 관리</t>
+        </is>
+      </c>
+      <c r="G5" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H5" s="143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리</t>
+        </is>
+      </c>
+      <c r="J5" s="142" t="inlineStr">
+        <is>
+          <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성
+• 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
+        </is>
+      </c>
+      <c r="K5" s="140" t="inlineStr">
+        <is>
+          <t>외부지질전문가 Pool List</t>
+        </is>
+      </c>
+      <c r="L5" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리 | 외부지질전문가 Pool List</t>
+        </is>
+      </c>
+      <c r="M5" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N5" s="142" t="inlineStr">
+        <is>
+          <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성 • 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
+        </is>
+      </c>
+      <c r="O5" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P5" s="142" t="inlineStr">
+        <is>
+          <t>1) 외부 지질전문가 Pool 관리 적정성을 확인하였는가? 2) 외부지질전문가 Pool List 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q5" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B6" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C6" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D6" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-5</t>
+        </is>
+      </c>
+      <c r="E6" s="135" t="inlineStr">
+        <is>
+          <t>매년 1분기</t>
+        </is>
+      </c>
+      <c r="F6" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 Pool 관리</t>
+        </is>
+      </c>
+      <c r="G6" s="137" t="inlineStr">
+        <is>
+          <t>외주구매팀</t>
+        </is>
+      </c>
+      <c r="H6" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I6" s="136" t="inlineStr">
+        <is>
+          <t>발주처 계획 대응 및 개략 지반조사 결과 사전 예측을 위한 업체 관리</t>
+        </is>
+      </c>
+      <c r="J6" s="136" t="inlineStr">
+        <is>
+          <t>• 공공기관별 입찰공고 모니터링 통한 지반조사업체 입찰참여 유치(입찰 공사 여부 확인)
+• 업체 Pool List 갱신 여부 확인
+• 지반조사업체 역량 및 기술수준 평가표 평가 여부 확인 (Pool 갱신 및 신규업체 등록)
+• 조사업체 강점, 장비보유 확인
+• 조사업체 Network 확보 여부 확인</t>
+        </is>
+      </c>
+      <c r="K6" s="145" t="inlineStr">
+        <is>
+          <t>조사업체 POOL/필요시 Update</t>
+        </is>
+      </c>
+      <c r="L6" s="136" t="inlineStr">
+        <is>
+          <t>발주처 계획 대응 및 개략 지반조사 결과 사전 예측을 위한 업체 관리 | 조사업체 POOL/필요시 Update</t>
+        </is>
+      </c>
+      <c r="M6" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N6" s="136" t="inlineStr">
+        <is>
+          <t>• 공공기관별 입찰공고 모니터링 통한 지반조사업체 입찰참여 유치(입찰 공사 여부 확인) • 업체 Pool List 갱신 여부 확인 • 지반조사업체 역량 및 기술수준 평가표 평가 여부 확인 (Pool 갱신 및 신규업체...</t>
+        </is>
+      </c>
+      <c r="O6" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P6" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사 Pool 관리 적정성을 확인하였는가? 2) 조사업체 POOL/필요시 Update 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q6" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B7" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C7" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D7" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-6</t>
+        </is>
+      </c>
+      <c r="E7" s="141" t="inlineStr">
+        <is>
+          <t>D-210 ~ D-180</t>
+        </is>
+      </c>
+      <c r="F7" s="140" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 자료 및 R/O 정보 입수</t>
+        </is>
+      </c>
+      <c r="G7" s="143" t="inlineStr">
+        <is>
+          <t>지반조사 협력업체</t>
+        </is>
+      </c>
+      <c r="H7" s="143" t="inlineStr">
+        <is>
+          <t>설계 협력업체</t>
+        </is>
+      </c>
+      <c r="I7" s="142" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 및 지반조사 결과 사전 획득</t>
+        </is>
+      </c>
+      <c r="J7" s="142" t="inlineStr">
+        <is>
+          <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
+        </is>
+      </c>
+      <c r="K7" s="140" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
+        </is>
+      </c>
+      <c r="L7" s="142" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 및 지반조사 결과 사전 획득 | 발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
+        </is>
+      </c>
+      <c r="M7" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N7" s="142" t="inlineStr">
+        <is>
+          <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
+        </is>
+      </c>
+      <c r="O7" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P7" s="142" t="inlineStr">
+        <is>
+          <t>1) 기본계획 지반조사 자료 및 R/O 정보 입수 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 및 지반조사 보고서(비공식) 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q7" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B8" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C8" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D8" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-7</t>
+        </is>
+      </c>
+      <c r="E8" s="135" t="inlineStr">
+        <is>
+          <t>D-180 ~ D-165</t>
+        </is>
+      </c>
+      <c r="F8" s="145" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 R/O 검토 (설계, 공정, 기획)</t>
+        </is>
+      </c>
+      <c r="G8" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀(설계), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="H8" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="I8" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 지반조사 문제점 검토</t>
+        </is>
+      </c>
+      <c r="J8" s="136" t="inlineStr">
+        <is>
+          <t>• 시추조사 위치, 수량 적정성 검토
+• 지질이상 구간 상세 조사 여부 및 적정성 검토 확인
+• 미시추 구간 지반 특성 적정성 검토확인 (측점 검토, 위치 및 물량검토)
+• 인근 사업 지반조사자료 비교 통해 당사 지반특성 분석 결과 Cross-check 확인</t>
+        </is>
+      </c>
+      <c r="K8" s="145" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 검토서(설계, 공정, 기획)</t>
+        </is>
+      </c>
+      <c r="L8" s="136" t="inlineStr">
+        <is>
+          <t>발주처 기본계획 지반조사 문제점 검토 | 기본계획 지반조사 검토서(설계, 공정, 기획)</t>
+        </is>
+      </c>
+      <c r="M8" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N8" s="136" t="inlineStr">
+        <is>
+          <t>• 시추조사 위치, 수량 적정성 검토 • 지질이상 구간 상세 조사 여부 및 적정성 검토 확인 • 미시추 구간 지반 특성 적정성 검토확인 (측점 검토, 위치 및 물량검토) • 인근 사업 지반조사자료 비교 통해 당사 지...</t>
+        </is>
+      </c>
+      <c r="O8" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P8" s="136" t="inlineStr">
+        <is>
+          <t>1) 기본계획 지반조사 R/O 검토 (설계, 공정, 기획) 적정성을 확인하였는가? 2) 기본계획 지반조사 검토서(설계, 공정, 기획) 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q8" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B9" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C9" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D9" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-8</t>
+        </is>
+      </c>
+      <c r="E9" s="141" t="inlineStr">
+        <is>
+          <t>D-165 ~ D-150</t>
+        </is>
+      </c>
+      <c r="F9" s="140" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 R/O 종합검토 (원가)</t>
+        </is>
+      </c>
+      <c r="G9" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="H9" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀(설계), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I9" s="142" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 문제점 R/O 분석</t>
+        </is>
+      </c>
+      <c r="J9" s="142" t="inlineStr">
+        <is>
+          <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
+        </is>
+      </c>
+      <c r="K9" s="140" t="inlineStr">
+        <is>
+          <t>기본계획 지반조사 개략 검토서</t>
+        </is>
+      </c>
+      <c r="L9" s="142" t="inlineStr">
+        <is>
+          <t>발주처 지반조사 문제점 R/O 분석 | 기본계획 지반조사 개략 검토서</t>
+        </is>
+      </c>
+      <c r="M9" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N9" s="142" t="inlineStr">
+        <is>
+          <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
+        </is>
+      </c>
+      <c r="O9" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P9" s="142" t="inlineStr">
+        <is>
+          <t>1) 기본계획 지반조사 R/O 종합검토 (원가) 적정성을 확인하였는가? 2) 기본계획 지반조사 개략 검토서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q9" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B10" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C10" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D10" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-9</t>
+        </is>
+      </c>
+      <c r="E10" s="135" t="inlineStr">
+        <is>
+          <t>D-150 ~ D-135</t>
+        </is>
+      </c>
+      <c r="F10" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 업체 선정</t>
+        </is>
+      </c>
+      <c r="G10" s="137" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H10" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I10" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 Pool 내 최적의 업체 선정</t>
+        </is>
+      </c>
+      <c r="J10" s="136" t="inlineStr">
+        <is>
+          <t>• 지반조사업체 Pool/실적 검토 및 공종별 적합성 정합 및 견적 본부 연계 검토</t>
+        </is>
+      </c>
+      <c r="K10" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 입찰 참여 Pool</t>
+        </is>
+      </c>
+      <c r="L10" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 Pool 내 최적의 업체 선정 | 지반조사 입찰 참여 Pool</t>
+        </is>
+      </c>
+      <c r="M10" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N10" s="136" t="inlineStr">
+        <is>
+          <t>• 지반조사업체 Pool/실적 검토 및 공종별 적합성 정합 및 견적 본부 연계 검토</t>
+        </is>
+      </c>
+      <c r="O10" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P10" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사 업체 선정 적정성을 확인하였는가? 2) 지반조사 입찰 참여 Pool 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q10" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B11" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C11" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D11" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-10</t>
+        </is>
+      </c>
+      <c r="E11" s="141" t="inlineStr">
+        <is>
+          <t>D-135 ~ D-120</t>
+        </is>
+      </c>
+      <c r="F11" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 업체 계약</t>
+        </is>
+      </c>
+      <c r="G11" s="143" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H11" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I11" s="142" t="inlineStr">
+        <is>
+          <t>지반조사업체 용역 계약</t>
+        </is>
+      </c>
+      <c r="J11" s="142" t="inlineStr">
+        <is>
+          <t>• 일반구매시스템을 이용한 용역계약</t>
+        </is>
+      </c>
+      <c r="K11" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="L11" s="142" t="inlineStr">
+        <is>
+          <t>지반조사업체 용역 계약 | 지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="M11" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N11" s="142" t="inlineStr">
+        <is>
+          <t>• 일반구매시스템을 이용한 용역계약</t>
+        </is>
+      </c>
+      <c r="O11" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P11" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사 업체 계약 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q11" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B12" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C12" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D12" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-11</t>
+        </is>
+      </c>
+      <c r="E12" s="135" t="inlineStr">
+        <is>
+          <t>D-135 ~ D-115</t>
+        </is>
+      </c>
+      <c r="F12" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치검토</t>
+        </is>
+      </c>
+      <c r="G12" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H12" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="I12" s="136" t="inlineStr">
+        <is>
+          <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정</t>
+        </is>
+      </c>
+      <c r="J12" s="136" t="inlineStr">
+        <is>
+          <t>• 현장답사 수행
+• 공종별 실시설계에 준하여 수량 및 위치 검토</t>
+        </is>
+      </c>
+      <c r="K12" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 계획서</t>
+        </is>
+      </c>
+      <c r="L12" s="136" t="inlineStr">
+        <is>
+          <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정 | 지반조사 계획서</t>
+        </is>
+      </c>
+      <c r="M12" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N12" s="136" t="inlineStr">
+        <is>
+          <t>• 현장답사 수행 • 공종별 실시설계에 준하여 수량 및 위치 검토</t>
+        </is>
+      </c>
+      <c r="O12" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P12" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사 항목, 수량 및 위치검토 적정성을 확인하였는가? 2) 지반조사 계획서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q12" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B13" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C13" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D13" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-12</t>
+        </is>
+      </c>
+      <c r="E13" s="141" t="inlineStr">
+        <is>
+          <t>D-115 ~ D-105</t>
+        </is>
+      </c>
+      <c r="F13" s="140" t="inlineStr">
+        <is>
+          <t>지반조사계획 적정성 심사의뢰</t>
+        </is>
+      </c>
+      <c r="G13" s="143" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H13" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I13" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치 적정성 검토</t>
+        </is>
+      </c>
+      <c r="J13" s="142" t="inlineStr">
+        <is>
+          <t>• 지반조사 계획서 검토 및 검토</t>
+        </is>
+      </c>
+      <c r="K13" s="140" t="inlineStr">
+        <is>
+          <t>지반조사계획 의견서</t>
+        </is>
+      </c>
+      <c r="L13" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치 적정성 검토 | 지반조사계획 의견서</t>
+        </is>
+      </c>
+      <c r="M13" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N13" s="142" t="inlineStr">
+        <is>
+          <t>• 지반조사 계획서 검토 및 검토</t>
+        </is>
+      </c>
+      <c r="O13" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P13" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사계획 적정성 심사의뢰 적정성을 확인하였는가? 2) 지반조사계획 의견서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q13" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B14" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C14" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D14" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-13</t>
+        </is>
+      </c>
+      <c r="E14" s="135" t="inlineStr">
+        <is>
+          <t>D-135 ~ D-100</t>
+        </is>
+      </c>
+      <c r="F14" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 인허가</t>
+        </is>
+      </c>
+      <c r="G14" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H14" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I14" s="136" t="inlineStr">
+        <is>
+          <t>지반조사 수행을 위한 인허가 승인</t>
+        </is>
+      </c>
+      <c r="J14" s="136" t="inlineStr">
+        <is>
+          <t>• 산지일시사용 신고(사업계획서, 지형도, 산지일시사용예정실측도, 복구계획서, 복지봉투)
+• 굴착행위 신고(굴착행위신고서, 위치 또는 평면도, 원상복구계획서, 토지사용 승낙서)
+• 하천점용 허가(위치도, 이해관계인 동의서, 수리계산서, 하천점용등, 사업자등록증)</t>
+        </is>
+      </c>
+      <c r="K14" s="145" t="inlineStr">
+        <is>
+          <t>인허가 서류</t>
+        </is>
+      </c>
+      <c r="L14" s="136" t="inlineStr">
+        <is>
+          <t>지반조사 수행을 위한 인허가 승인 | 인허가 서류</t>
+        </is>
+      </c>
+      <c r="M14" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N14" s="136" t="inlineStr">
+        <is>
+          <t>• 산지일시사용 신고(사업계획서, 지형도, 산지일시사용예정실측도, 복구계획서, 복지봉투) • 굴착행위 신고(굴착행위신고서, 위치 또는 평면도, 원상복구계획서, 토지사용 승낙서) • 하천점용 허가(위치도, 이해관계인 ...</t>
+        </is>
+      </c>
+      <c r="O14" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P14" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사 인허가 적정성을 확인하였는가? 2) 인허가 서류 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q14" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B15" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C15" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D15" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-14</t>
+        </is>
+      </c>
+      <c r="E15" s="141" t="inlineStr">
+        <is>
+          <t>D-105 ~ D-100</t>
+        </is>
+      </c>
+      <c r="F15" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 항목, 수량 및 위치 보완</t>
+        </is>
+      </c>
+      <c r="G15" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H15" s="143" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상, 지반조사업체</t>
+        </is>
+      </c>
+      <c r="I15" s="142" t="inlineStr">
+        <is>
+          <t>외부지질전문가 의견을 반영한 지반조사 계획 확정</t>
+        </is>
+      </c>
+      <c r="J15" s="142" t="inlineStr">
+        <is>
+          <t>• 외부지질전문가 지반조사 의견 검토
+• 입찰설계 지반조사 계획 보완</t>
+        </is>
+      </c>
+      <c r="K15" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="L15" s="142" t="inlineStr">
+        <is>
+          <t>외부지질전문가 의견을 반영한 지반조사 계획 확정 | 지반조사 용역 계약서</t>
+        </is>
+      </c>
+      <c r="M15" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N15" s="142" t="inlineStr">
+        <is>
+          <t>• 외부지질전문가 지반조사 의견 검토 • 입찰설계 지반조사 계획 보완</t>
+        </is>
+      </c>
+      <c r="O15" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P15" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사 항목, 수량 및 위치 보완 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q15" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B16" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C16" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D16" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-15</t>
+        </is>
+      </c>
+      <c r="E16" s="135" t="inlineStr">
+        <is>
+          <t>D-100 ~ D-50</t>
+        </is>
+      </c>
+      <c r="F16" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 수행</t>
+        </is>
+      </c>
+      <c r="G16" s="137" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H16" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I16" s="136" t="inlineStr">
+        <is>
+          <t>과업구간 지반여건 상세 파악</t>
+        </is>
+      </c>
+      <c r="J16" s="136" t="inlineStr">
+        <is>
+          <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등)
+• 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등)
+• 실내시험 수행(요동시험, 입도시험 등)</t>
+        </is>
+      </c>
+      <c r="K16" s="145" t="inlineStr">
+        <is>
+          <t>지반조사 보고서, 시추 Core 및 샘플</t>
+        </is>
+      </c>
+      <c r="L16" s="136" t="inlineStr">
+        <is>
+          <t>과업구간 지반여건 상세 파악 | 지반조사 보고서, 시추 Core 및 샘플</t>
+        </is>
+      </c>
+      <c r="M16" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N16" s="136" t="inlineStr">
+        <is>
+          <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등) • 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등) • 실내시험 수행(요동시험, 입도시험 등)</t>
+        </is>
+      </c>
+      <c r="O16" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P16" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사 수행 적정성을 확인하였는가? 2) 지반조사 보고서, 시추 Core 및 샘플 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q16" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B17" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C17" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D17" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-16</t>
+        </is>
+      </c>
+      <c r="E17" s="141" t="inlineStr">
+        <is>
+          <t>D-50 ~ D-40</t>
+        </is>
+      </c>
+      <c r="F17" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 수렴 결과 분석</t>
+        </is>
+      </c>
+      <c r="G17" s="143" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H17" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀, 지반조사업체</t>
+        </is>
+      </c>
+      <c r="I17" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 결과 오류 및 지반정수의 적합성 검토</t>
+        </is>
+      </c>
+      <c r="J17" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 보고서 검토
+• 시추조사 위치 및 심도의 적정성 검토
+• 실내시험 결과 등급 적정성 검토
+• 실시설계시 추가지반조사 필요구간 검토</t>
+        </is>
+      </c>
+      <c r="K17" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 결과 분석 의견서</t>
+        </is>
+      </c>
+      <c r="L17" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 결과 오류 및 지반정수의 적합성 검토 | 지반조사 결과 분석 의견서</t>
+        </is>
+      </c>
+      <c r="M17" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N17" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 보고서 검토 • 시추조사 위치 및 심도의 적정성 검토 • 실내시험 결과 등급 적정성 검토 • 실시설계시 추가지반조사 필요구간 검토</t>
+        </is>
+      </c>
+      <c r="O17" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P17" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사 수렴 결과 분석 적정성을 확인하였는가? 2) 지반조사 결과 분석 의견서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q17" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B18" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C18" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D18" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-17</t>
+        </is>
+      </c>
+      <c r="E18" s="135" t="inlineStr">
+        <is>
+          <t>D-40 ~ D-30</t>
+        </is>
+      </c>
+      <c r="F18" s="145" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="G18" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="H18" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="I18" s="136" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="J18" s="136" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="K18" s="145" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="L18" s="136" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="M18" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N18" s="136" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="O18" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P18" s="136" t="inlineStr">
+        <is>
+          <t>1) 입찰설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q18" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B19" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C19" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D19" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-18</t>
+        </is>
+      </c>
+      <c r="E19" s="141" t="inlineStr">
+        <is>
+          <t>D-40 ~ D-30</t>
+        </is>
+      </c>
+      <c r="F19" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 결과 R/O 종합검토</t>
+        </is>
+      </c>
+      <c r="G19" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H19" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I19" s="142" t="inlineStr">
+        <is>
+          <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정</t>
+        </is>
+      </c>
+      <c r="J19" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 R/O별 Cost effect 분석
+• 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
+        </is>
+      </c>
+      <c r="K19" s="140" t="inlineStr">
+        <is>
+          <t>입찰설계 R/O 검토서</t>
+        </is>
+      </c>
+      <c r="L19" s="142" t="inlineStr">
+        <is>
+          <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정 | 입찰설계 R/O 검토서</t>
+        </is>
+      </c>
+      <c r="M19" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N19" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 R/O별 Cost effect 분석 • 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
+        </is>
+      </c>
+      <c r="O19" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P19" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사 결과 R/O 종합검토 적정성을 확인하였는가? 2) 입찰설계 R/O 검토서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q19" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B20" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C20" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D20" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-19</t>
+        </is>
+      </c>
+      <c r="E20" s="135" t="inlineStr">
+        <is>
+          <t>D-30 ~ D-20</t>
+        </is>
+      </c>
+      <c r="F20" s="145" t="inlineStr">
+        <is>
+          <t>REM 수립</t>
+        </is>
+      </c>
+      <c r="G20" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H20" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀, 토목사업지원팀</t>
+        </is>
+      </c>
+      <c r="I20" s="136" t="inlineStr">
+        <is>
+          <t>REM 차트 작성(회사의 Core Risk, T/C 공정검토 결과, 경쟁사 동향, 발주 경향) 및 보고</t>
+        </is>
+      </c>
+      <c r="J20" s="136" t="inlineStr">
+        <is>
+          <t>• Risk Profiling/Merge 방안 검토
+• 공정 착공성 검토 및 T/C 검토
+• 설계차별화 및 Idea Frame 검토</t>
+        </is>
+      </c>
+      <c r="K20" s="145" t="inlineStr">
+        <is>
+          <t>REM 회의록</t>
+        </is>
+      </c>
+      <c r="L20" s="136" t="inlineStr">
+        <is>
+          <t>REM 차트 작성(회사의 Core Risk, T/C 공정검토 결과, 경쟁사 동향, 발주 경향) 및 보고 | REM 회의록</t>
+        </is>
+      </c>
+      <c r="M20" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N20" s="136" t="inlineStr">
+        <is>
+          <t>• Risk Profiling/Merge 방안 검토 • 공정 착공성 검토 및 T/C 검토 • 설계차별화 및 Idea Frame 검토</t>
+        </is>
+      </c>
+      <c r="O20" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P20" s="136" t="inlineStr">
+        <is>
+          <t>1) REM 수립 적정성을 확인하였는가? 2) REM 회의록 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q20" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B21" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C21" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D21" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-20</t>
+        </is>
+      </c>
+      <c r="E21" s="141" t="inlineStr">
+        <is>
+          <t>D-30 ~ D-15</t>
+        </is>
+      </c>
+      <c r="F21" s="140" t="inlineStr">
+        <is>
+          <t>추가지반조사 계획 수립</t>
+        </is>
+      </c>
+      <c r="G21" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H21" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I21" s="142" t="inlineStr">
+        <is>
+          <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출</t>
+        </is>
+      </c>
+      <c r="J21" s="142" t="inlineStr">
+        <is>
+          <t>• 지반조사 수렴 결과 분석보고서 검토
+• 지반조사 결과 R/O 종합검토 결과 검토</t>
+        </is>
+      </c>
+      <c r="K21" s="140" t="inlineStr">
+        <is>
+          <t>추가지반조사 List</t>
+        </is>
+      </c>
+      <c r="L21" s="142" t="inlineStr">
+        <is>
+          <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출 | 추가지반조사 List</t>
+        </is>
+      </c>
+      <c r="M21" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N21" s="142" t="inlineStr">
+        <is>
+          <t>• 지반조사 수렴 결과 분석보고서 검토 • 지반조사 결과 R/O 종합검토 결과 검토</t>
+        </is>
+      </c>
+      <c r="O21" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P21" s="142" t="inlineStr">
+        <is>
+          <t>1) 추가지반조사 계획 수립 적정성을 확인하였는가? 2) 추가지반조사 List 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q21" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B22" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C22" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D22" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-21</t>
+        </is>
+      </c>
+      <c r="E22" s="135" t="inlineStr">
+        <is>
+          <t>D-15 ~ D-7</t>
+        </is>
+      </c>
+      <c r="F22" s="145" t="inlineStr">
+        <is>
+          <t>3D GPR탐사 장비 사양(차량형) 검토</t>
+        </is>
+      </c>
+      <c r="G22" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="H22" s="137" t="inlineStr">
+        <is>
+          <t>현장 공사팀</t>
+        </is>
+      </c>
+      <c r="I22" s="136" t="inlineStr">
+        <is>
+          <t>적정 추가지반조사 규명을 위한 장비 사양 검토</t>
+        </is>
+      </c>
+      <c r="J22" s="136" t="inlineStr">
+        <is>
+          <t>• 3D GPR탐사 장비 사양(차량형)
+- 3D Radar(노르웨이)_200~3000Hz, 2.0m~3.0m : 하상도 높음
+- MIRA(스웨덴)_400~1300Hz, 1.0m~2.0m : 정밀한 입체 형상
+- StreamC(이탈리아)_200~600Hz, 1.5m~3.0m : 다양한 심도, 공동 탐지
+- VGPR(호주)_100~4000Hz, 2.0m~3.0m : 고속주행 데이터 획득
+- Road 3D(한국)_200~3000Hz, 2.0m~3.0m : 하상도 높음, 유용특화</t>
+        </is>
+      </c>
+      <c r="K22" s="145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="136" t="inlineStr">
+        <is>
+          <t>적정 추가지반조사 규명을 위한 장비 사양 검토 | -</t>
+        </is>
+      </c>
+      <c r="M22" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N22" s="136" t="inlineStr">
+        <is>
+          <t>• 3D GPR탐사 장비 사양(차량형) - 3D Radar(노르웨이)_200~3000Hz, 2.0m~3.0m : 하상도 높음 - MIRA(스웨덴)_400~1300Hz, 1.0m~2.0m : 정밀한 입체 형상 - St...</t>
+        </is>
+      </c>
+      <c r="O22" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P22" s="136" t="inlineStr">
+        <is>
+          <t>1) 3D GPR탐사 장비 사양(차량형) 검토 적정성을 확인하였는가? 2) - 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q22" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B23" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C23" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D23" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-22</t>
+        </is>
+      </c>
+      <c r="E23" s="141" t="inlineStr">
+        <is>
+          <t>D-15 ~ D-7</t>
+        </is>
+      </c>
+      <c r="F23" s="140" t="inlineStr">
+        <is>
+          <t>ECRM 수립</t>
+        </is>
+      </c>
+      <c r="G23" s="143" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가)</t>
+        </is>
+      </c>
+      <c r="H23" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀, 토목수행팀, 토목사업지원팀</t>
+        </is>
+      </c>
+      <c r="I23" s="142" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="J23" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="K23" s="140" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="L23" s="142" t="inlineStr">
+        <is>
+          <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="M23" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N23" s="142" t="inlineStr">
+        <is>
+          <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
+        </is>
+      </c>
+      <c r="O23" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P23" s="142" t="inlineStr">
+        <is>
+          <t>1) ECRM 수립 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q23" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B24" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C24" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D24" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-23</t>
+        </is>
+      </c>
+      <c r="E24" s="135" t="inlineStr">
+        <is>
+          <t>D-7 ~ D-0</t>
+        </is>
+      </c>
+      <c r="F24" s="145" t="inlineStr">
+        <is>
+          <t>최종 Cost 검토 / 입찰</t>
+        </is>
+      </c>
+      <c r="G24" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀</t>
+        </is>
+      </c>
+      <c r="H24" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="136" t="inlineStr">
+        <is>
+          <t>입찰</t>
+        </is>
+      </c>
+      <c r="J24" s="136" t="inlineStr">
+        <is>
+          <t>• 최종 R/O를 반영한 투찰내역서 작성</t>
+        </is>
+      </c>
+      <c r="K24" s="145" t="inlineStr">
+        <is>
+          <t>투찰내역서</t>
+        </is>
+      </c>
+      <c r="L24" s="136" t="inlineStr">
+        <is>
+          <t>입찰 | 투찰내역서</t>
+        </is>
+      </c>
+      <c r="M24" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N24" s="136" t="inlineStr">
+        <is>
+          <t>• 최종 R/O를 반영한 투찰내역서 작성</t>
+        </is>
+      </c>
+      <c r="O24" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P24" s="136" t="inlineStr">
+        <is>
+          <t>1) 최종 Cost 검토 / 입찰 적정성을 확인하였는가? 2) 투찰내역서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q24" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B25" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C25" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D25" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-24</t>
+        </is>
+      </c>
+      <c r="E25" s="141" t="inlineStr">
+        <is>
+          <t>D+0 ~ D+30</t>
+        </is>
+      </c>
+      <c r="F25" s="140" t="inlineStr">
+        <is>
+          <t>입찰설계 현장 인수인계</t>
+        </is>
+      </c>
+      <c r="G25" s="143" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H25" s="143" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="I25" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유</t>
+        </is>
+      </c>
+      <c r="J25" s="142" t="inlineStr">
+        <is>
+          <t>• 최종 R/O 결과 및 입찰도서 인출</t>
+        </is>
+      </c>
+      <c r="K25" s="140" t="inlineStr">
+        <is>
+          <t>인수인계서</t>
+        </is>
+      </c>
+      <c r="L25" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유 | 인수인계서</t>
+        </is>
+      </c>
+      <c r="M25" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N25" s="142" t="inlineStr">
+        <is>
+          <t>• 최종 R/O 결과 및 입찰도서 인출</t>
+        </is>
+      </c>
+      <c r="O25" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P25" s="142" t="inlineStr">
+        <is>
+          <t>1) 입찰설계 현장 인수인계 적정성을 확인하였는가? 2) 인수인계서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q25" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="146" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B26" s="146" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C26" s="146" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D26" s="146" t="inlineStr">
+        <is>
+          <t>9000-0-25</t>
+        </is>
+      </c>
+      <c r="E26" s="148" t="inlineStr">
+        <is>
+          <t>D+30 ~ D+100</t>
+        </is>
+      </c>
+      <c r="F26" s="147" t="inlineStr">
+        <is>
+          <t>추가지반조사 수행</t>
+        </is>
+      </c>
+      <c r="G26" s="150" t="inlineStr">
+        <is>
+          <t>지반조사업체</t>
+        </is>
+      </c>
+      <c r="H26" s="150" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
+        </is>
+      </c>
+      <c r="I26" s="149" t="inlineStr">
+        <is>
+          <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge</t>
+        </is>
+      </c>
+      <c r="J26" s="149" t="inlineStr">
+        <is>
+          <t>• 추가 지반조사 계획 및 시점 확인
+- 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인)
+- 추가시추조사 수행(물리탐사, 시추조사)
+- 토질 및 암석 실내시험 수행 및 결과분석 확인
+- 공종별 핵심시설(교량, 접속도로, 토공, #200m 통과점, 터널 발파/심벽진입) 확인</t>
+        </is>
+      </c>
+      <c r="K26" s="147" t="inlineStr">
+        <is>
+          <t>추가 지반조사 보고서</t>
+        </is>
+      </c>
+      <c r="L26" s="149" t="inlineStr">
+        <is>
+          <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge | 추가 지반조사 보고서</t>
+        </is>
+      </c>
+      <c r="M26" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N26" s="149" t="inlineStr">
+        <is>
+          <t>• 추가 지반조사 계획 및 시점 확인 - 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인) - 추가시추조사 수행(물리탐사, 시추조사) - 토질 및 암석 실내시험 수행 및 결과분석 확인 - 공종별 ...</t>
+        </is>
+      </c>
+      <c r="O26" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P26" s="149" t="inlineStr">
+        <is>
+          <t>1) 추가지반조사 수행 적정성을 확인하였는가? 2) 추가 지반조사 보고서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q26" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="146" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B27" s="146" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C27" s="146" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D27" s="146" t="inlineStr">
+        <is>
+          <t>9000-0-26</t>
+        </is>
+      </c>
+      <c r="E27" s="148" t="inlineStr">
+        <is>
+          <t>D+100 ~ D+110</t>
+        </is>
+      </c>
+      <c r="F27" s="147" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과 분석</t>
+        </is>
+      </c>
+      <c r="G27" s="150" t="inlineStr">
+        <is>
+          <t>외부지질전문가 3인 이상</t>
+        </is>
+      </c>
+      <c r="H27" s="150" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
+        </is>
+      </c>
+      <c r="I27" s="149" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
+        </is>
+      </c>
+      <c r="J27" s="149" t="inlineStr">
+        <is>
+          <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인
+• 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
+        </is>
+      </c>
+      <c r="K27" s="147" t="inlineStr">
+        <is>
+          <t>추가 지반조사결과 종합보고서</t>
+        </is>
+      </c>
+      <c r="L27" s="149" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 추가 지반조사결과 종합보고서</t>
+        </is>
+      </c>
+      <c r="M27" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N27" s="149" t="inlineStr">
+        <is>
+          <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인 • 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
+        </is>
+      </c>
+      <c r="O27" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P27" s="149" t="inlineStr">
+        <is>
+          <t>1) 추가지반조사 결과 분석 적정성을 확인하였는가? 2) 추가 지반조사결과 종합보고서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q27" s="162" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B28" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C28" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D28" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-27</t>
+        </is>
+      </c>
+      <c r="E28" s="135" t="inlineStr">
+        <is>
+          <t>D+110 ~ D+120</t>
+        </is>
+      </c>
+      <c r="F28" s="145" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="G28" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H28" s="137" t="inlineStr">
+        <is>
+          <t>현장 공사팀/품질팀/공무팀, 토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I28" s="136" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
+        </is>
+      </c>
+      <c r="J28" s="136" t="inlineStr">
+        <is>
+          <t>• 실시설계 추가지반조사 결과 분석을 통한 원가 및 공정 영향 검토
+• 미시추 구간 평가 및 공정 Risk 반영 사항 검토
+• 지반조건을 고려한 발파공법성 검토</t>
+        </is>
+      </c>
+      <c r="K28" s="145" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="L28" s="136" t="inlineStr">
+        <is>
+          <t>실시설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
+        </is>
+      </c>
+      <c r="M28" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N28" s="136" t="inlineStr">
+        <is>
+          <t>• 실시설계 추가지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 검토</t>
+        </is>
+      </c>
+      <c r="O28" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P28" s="136" t="inlineStr">
+        <is>
+          <t>1) 실시설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 실시설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q28" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B29" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C29" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D29" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-28</t>
+        </is>
+      </c>
+      <c r="E29" s="141" t="inlineStr">
+        <is>
+          <t>D+110 ~ D+120</t>
+        </is>
+      </c>
+      <c r="F29" s="140" t="inlineStr">
+        <is>
+          <t>실시설계 추가지반조사 결과 검토</t>
+        </is>
+      </c>
+      <c r="G29" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H29" s="143" t="inlineStr">
+        <is>
+          <t>현장 공사팀/품질팀/공무팀, 토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I29" s="142" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
+        </is>
+      </c>
+      <c r="J29" s="142" t="inlineStr">
+        <is>
+          <t>• 추가지반조사 결과 검토</t>
+        </is>
+      </c>
+      <c r="K29" s="140" t="inlineStr">
+        <is>
+          <t>실시설계 최종 R/O</t>
+        </is>
+      </c>
+      <c r="L29" s="142" t="inlineStr">
+        <is>
+          <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 실시설계 최종 R/O</t>
+        </is>
+      </c>
+      <c r="M29" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N29" s="142" t="inlineStr">
+        <is>
+          <t>• 추가지반조사 결과 검토</t>
+        </is>
+      </c>
+      <c r="O29" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P29" s="142" t="inlineStr">
+        <is>
+          <t>1) 실시설계 추가지반조사 결과 검토 적정성을 확인하였는가? 2) 실시설계 최종 R/O 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q29" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B30" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C30" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D30" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-29</t>
+        </is>
+      </c>
+      <c r="E30" s="135" t="inlineStr">
+        <is>
+          <t>D+120 ~ D+150</t>
+        </is>
+      </c>
+      <c r="F30" s="145" t="inlineStr">
+        <is>
+          <t>최종 R/O 이행방안 수립</t>
+        </is>
+      </c>
+      <c r="G30" s="137" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H30" s="137" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="I30" s="136" t="inlineStr">
+        <is>
+          <t>최종 지반조사 결과에 따른 R/O 이행방안 수립</t>
+        </is>
+      </c>
+      <c r="J30" s="136" t="inlineStr">
+        <is>
+          <t>• Core Risk 및 Hedge 방안 수립
+• Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
+        </is>
+      </c>
+      <c r="K30" s="145" t="inlineStr">
+        <is>
+          <t>최종 R/O 이행계획서</t>
+        </is>
+      </c>
+      <c r="L30" s="136" t="inlineStr">
+        <is>
+          <t>최종 지반조사 결과에 따른 R/O 이행방안 수립 | 최종 R/O 이행계획서</t>
+        </is>
+      </c>
+      <c r="M30" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N30" s="136" t="inlineStr">
+        <is>
+          <t>• Core Risk 및 Hedge 방안 수립 • Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
+        </is>
+      </c>
+      <c r="O30" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P30" s="136" t="inlineStr">
+        <is>
+          <t>1) 최종 R/O 이행방안 수립 적정성을 확인하였는가? 2) 최종 R/O 이행계획서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q30" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B31" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C31" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D31" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-30</t>
+        </is>
+      </c>
+      <c r="E31" s="141" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F31" s="140" t="inlineStr">
+        <is>
+          <t>외부지질전문가 업무평가</t>
+        </is>
+      </c>
+      <c r="G31" s="143" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H31" s="143" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I31" s="142" t="inlineStr">
+        <is>
+          <t>참여인력 전문성 평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="J31" s="142" t="inlineStr">
+        <is>
+          <t>• 외부지질 전문가 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="K31" s="140" t="inlineStr">
+        <is>
+          <t>외부지질 전문가 업무평가서</t>
+        </is>
+      </c>
+      <c r="L31" s="142" t="inlineStr">
+        <is>
+          <t>참여인력 전문성 평가 및 특이사항 기록 | 외부지질 전문가 업무평가서</t>
+        </is>
+      </c>
+      <c r="M31" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N31" s="142" t="inlineStr">
+        <is>
+          <t>• 외부지질 전문가 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="O31" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P31" s="142" t="inlineStr">
+        <is>
+          <t>1) 외부지질전문가 업무평가 적정성을 확인하였는가? 2) 외부지질 전문가 업무평가서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q31" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B32" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C32" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D32" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-31</t>
+        </is>
+      </c>
+      <c r="E32" s="135" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F32" s="145" t="inlineStr">
+        <is>
+          <t>조사업체 PM 업무평가</t>
+        </is>
+      </c>
+      <c r="G32" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀</t>
+        </is>
+      </c>
+      <c r="H32" s="137" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I32" s="136" t="inlineStr">
+        <is>
+          <t>조사업체 PM 전문성 평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="J32" s="136" t="inlineStr">
+        <is>
+          <t>• 지반조사 PM 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="K32" s="145" t="inlineStr">
+        <is>
+          <t>PM업무평가서</t>
+        </is>
+      </c>
+      <c r="L32" s="136" t="inlineStr">
+        <is>
+          <t>조사업체 PM 전문성 평가 및 특이사항 기록 | PM업무평가서</t>
+        </is>
+      </c>
+      <c r="M32" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N32" s="136" t="inlineStr">
+        <is>
+          <t>• 지반조사 PM 업무평가서 작성</t>
+        </is>
+      </c>
+      <c r="O32" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P32" s="136" t="inlineStr">
+        <is>
+          <t>1) 조사업체 PM 업무평가 적정성을 확인하였는가? 2) PM업무평가서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q32" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B33" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C33" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D33" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-32</t>
+        </is>
+      </c>
+      <c r="E33" s="141" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F33" s="140" t="inlineStr">
+        <is>
+          <t>지반조사업체 업무평가</t>
+        </is>
+      </c>
+      <c r="G33" s="143" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H33" s="143" t="inlineStr">
+        <is>
+          <t>현장 공사팀/공무팀</t>
+        </is>
+      </c>
+      <c r="I33" s="142" t="inlineStr">
+        <is>
+          <t>조사업체 업무평가 및 특이사항 기록</t>
+        </is>
+      </c>
+      <c r="J33" s="142" t="inlineStr">
+        <is>
+          <t>• 협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="K33" s="140" t="inlineStr">
+        <is>
+          <t>협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="L33" s="142" t="inlineStr">
+        <is>
+          <t>조사업체 업무평가 및 특이사항 기록 | 협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="M33" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N33" s="142" t="inlineStr">
+        <is>
+          <t>• 협력업체 업무평가서</t>
+        </is>
+      </c>
+      <c r="O33" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P33" s="142" t="inlineStr">
+        <is>
+          <t>1) 지반조사업체 업무평가 적정성을 확인하였는가? 2) 협력업체 업무평가서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q33" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B34" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C34" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D34" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-33</t>
+        </is>
+      </c>
+      <c r="E34" s="135" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F34" s="145" t="inlineStr">
+        <is>
+          <t>설계변경 LL 리포트 작성</t>
+        </is>
+      </c>
+      <c r="G34" s="137" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="H34" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I34" s="136" t="inlineStr">
+        <is>
+          <t>설계변경 사항 기록</t>
+        </is>
+      </c>
+      <c r="J34" s="136" t="inlineStr">
+        <is>
+          <t>• 설계변경 사유 기록관리
+• 예상 R/O대비 설계변경 사항 비교 검토</t>
+        </is>
+      </c>
+      <c r="K34" s="145" t="inlineStr">
+        <is>
+          <t>LL리포트</t>
+        </is>
+      </c>
+      <c r="L34" s="136" t="inlineStr">
+        <is>
+          <t>설계변경 사항 기록 | LL리포트</t>
+        </is>
+      </c>
+      <c r="M34" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N34" s="136" t="inlineStr">
+        <is>
+          <t>• 설계변경 사유 기록관리 • 예상 R/O대비 설계변경 사항 비교 검토</t>
+        </is>
+      </c>
+      <c r="O34" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P34" s="136" t="inlineStr">
+        <is>
+          <t>1) 설계변경 LL 리포트 작성 적정성을 확인하였는가? 2) LL리포트 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q34" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B35" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C35" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D35" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-34</t>
+        </is>
+      </c>
+      <c r="E35" s="141" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F35" s="140" t="inlineStr">
+        <is>
+          <t>설계변경 LL 리포트 관리</t>
+        </is>
+      </c>
+      <c r="G35" s="143" t="inlineStr">
+        <is>
+          <t>토목수행팀</t>
+        </is>
+      </c>
+      <c r="H35" s="143" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="I35" s="142" t="inlineStr">
+        <is>
+          <t>전체 현장 설계변경 사항 기록</t>
+        </is>
+      </c>
+      <c r="J35" s="142" t="inlineStr">
+        <is>
+          <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
+        </is>
+      </c>
+      <c r="K35" s="140" t="inlineStr">
+        <is>
+          <t>LL리포트 List</t>
+        </is>
+      </c>
+      <c r="L35" s="142" t="inlineStr">
+        <is>
+          <t>전체 현장 설계변경 사항 기록 | LL리포트 List</t>
+        </is>
+      </c>
+      <c r="M35" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N35" s="142" t="inlineStr">
+        <is>
+          <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
+        </is>
+      </c>
+      <c r="O35" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P35" s="142" t="inlineStr">
+        <is>
+          <t>1) 설계변경 LL 리포트 관리 적정성을 확인하였는가? 2) LL리포트 List 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q35" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="132" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B36" s="132" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C36" s="132" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D36" s="132" t="inlineStr">
+        <is>
+          <t>9000-0-35</t>
+        </is>
+      </c>
+      <c r="E36" s="135" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F36" s="145" t="inlineStr">
+        <is>
+          <t>지반조사업체 정산계약</t>
+        </is>
+      </c>
+      <c r="G36" s="137" t="inlineStr">
+        <is>
+          <t>일반구매팀</t>
+        </is>
+      </c>
+      <c r="H36" s="137" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I36" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 정산</t>
+        </is>
+      </c>
+      <c r="J36" s="136" t="inlineStr">
+        <is>
+          <t>• 조사도 수량 Check 후 구매시스템 변경계약 수행
+• 변경계약 후 정산금 집행</t>
+        </is>
+      </c>
+      <c r="K36" s="145" t="inlineStr">
+        <is>
+          <t>정산계약서</t>
+        </is>
+      </c>
+      <c r="L36" s="136" t="inlineStr">
+        <is>
+          <t>지반조사업체 정산 | 정산계약서</t>
+        </is>
+      </c>
+      <c r="M36" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N36" s="136" t="inlineStr">
+        <is>
+          <t>• 조사도 수량 Check 후 구매시스템 변경계약 수행 • 변경계약 후 정산금 집행</t>
+        </is>
+      </c>
+      <c r="O36" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P36" s="136" t="inlineStr">
+        <is>
+          <t>1) 지반조사업체 정산계약 적정성을 확인하였는가? 2) 정산계약서 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q36" s="160" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="139" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B37" s="139" t="inlineStr">
+        <is>
+          <t>9000-0</t>
+        </is>
+      </c>
+      <c r="C37" s="139" t="inlineStr">
+        <is>
+          <t>사전준비_지반조사</t>
+        </is>
+      </c>
+      <c r="D37" s="139" t="inlineStr">
+        <is>
+          <t>9000-0-36</t>
+        </is>
+      </c>
+      <c r="E37" s="141" t="inlineStr">
+        <is>
+          <t>- ~ -</t>
+        </is>
+      </c>
+      <c r="F37" s="140" t="inlineStr">
+        <is>
+          <t>매뉴얼 Update</t>
+        </is>
+      </c>
+      <c r="G37" s="143" t="inlineStr">
+        <is>
+          <t>혁신실장</t>
+        </is>
+      </c>
+      <c r="H37" s="143" t="inlineStr">
+        <is>
+          <t>현장 공무팀</t>
+        </is>
+      </c>
+      <c r="I37" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 매뉴얼 Update</t>
+        </is>
+      </c>
+      <c r="J37" s="142" t="inlineStr">
+        <is>
+          <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
+        </is>
+      </c>
+      <c r="K37" s="140" t="inlineStr">
+        <is>
+          <t>지반조사 매뉴얼</t>
+        </is>
+      </c>
+      <c r="L37" s="142" t="inlineStr">
+        <is>
+          <t>지반조사 매뉴얼 Update | 지반조사 매뉴얼</t>
+        </is>
+      </c>
+      <c r="M37" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 표준서 열기 📄</t>
+        </is>
+      </c>
+      <c r="N37" s="142" t="inlineStr">
+        <is>
+          <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
+        </is>
+      </c>
+      <c r="O37" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 수행지침 열기 📄</t>
+        </is>
+      </c>
+      <c r="P37" s="142" t="inlineStr">
+        <is>
+          <t>1) 매뉴얼 Update 적정성을 확인하였는가? 2) 지반조사 매뉴얼 산출물을 확보하였는가?</t>
+        </is>
+      </c>
+      <c r="Q37" s="161" t="inlineStr">
+        <is>
+          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14411,7 +20086,7 @@
       <c r="B1" s="126" t="n"/>
       <c r="C1" s="126" t="n"/>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="127" t="inlineStr">
         <is>
           <t>No.</t>
@@ -14465,8 +20140,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="158" t="n"/>
+    <row r="3">
+      <c r="B3" s="126" t="n"/>
       <c r="C3" s="129" t="inlineStr">
         <is>
           <t>Start</t>
@@ -14479,21 +20154,21 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="163" t="inlineStr">
         <is>
           <t>공통_사전준비_지반조사(기술형)</t>
         </is>
       </c>
-      <c r="B4" s="123" t="n"/>
-      <c r="C4" s="123" t="n"/>
-      <c r="D4" s="123" t="n"/>
-      <c r="E4" s="123" t="n"/>
-      <c r="F4" s="123" t="n"/>
-      <c r="G4" s="123" t="n"/>
-      <c r="H4" s="123" t="n"/>
-      <c r="I4" s="123" t="n"/>
-      <c r="J4" s="123" t="n"/>
-      <c r="K4" s="124" t="n"/>
+      <c r="B4" s="131" t="n"/>
+      <c r="C4" s="131" t="n"/>
+      <c r="D4" s="131" t="n"/>
+      <c r="E4" s="131" t="n"/>
+      <c r="F4" s="131" t="n"/>
+      <c r="G4" s="131" t="n"/>
+      <c r="H4" s="131" t="n"/>
+      <c r="I4" s="131" t="n"/>
+      <c r="J4" s="131" t="n"/>
+      <c r="K4" s="131" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="132" t="inlineStr"/>
@@ -14539,46 +20214,46 @@
       <c r="K5" s="132" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="139" t="inlineStr"/>
-      <c r="B6" s="140" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr"/>
+      <c r="B6" s="133" t="inlineStr">
         <is>
           <t>관심프로젝트 선정</t>
         </is>
       </c>
-      <c r="C6" s="141" t="inlineStr">
+      <c r="C6" s="134" t="inlineStr">
         <is>
           <t>사전영업</t>
         </is>
       </c>
-      <c r="D6" s="141" t="inlineStr"/>
-      <c r="E6" s="142" t="inlineStr">
+      <c r="D6" s="135" t="inlineStr"/>
+      <c r="E6" s="136" t="inlineStr">
         <is>
           <t>입수된 발주정보 평가를 통한 관심 Project 선정</t>
         </is>
       </c>
-      <c r="F6" s="142" t="inlineStr">
+      <c r="F6" s="136" t="inlineStr">
         <is>
           <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행
 • 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
         </is>
       </c>
-      <c r="G6" s="143" t="inlineStr">
+      <c r="G6" s="137" t="inlineStr">
         <is>
           <t>토목사업팀</t>
         </is>
       </c>
-      <c r="H6" s="143" t="inlineStr">
+      <c r="H6" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="I6" s="144" t="inlineStr">
+      <c r="I6" s="138" t="inlineStr">
         <is>
           <t>관심사업 List</t>
         </is>
       </c>
-      <c r="J6" s="139" t="inlineStr"/>
-      <c r="K6" s="139" t="inlineStr"/>
+      <c r="J6" s="132" t="inlineStr"/>
+      <c r="K6" s="132" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="132" t="inlineStr">
@@ -14627,50 +20302,50 @@
       <c r="K7" s="132" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="139" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="140" t="inlineStr">
+      <c r="B8" s="133" t="inlineStr">
         <is>
           <t>외부 지질전문가 Pool 관리</t>
         </is>
       </c>
-      <c r="C8" s="141" t="inlineStr">
+      <c r="C8" s="134" t="inlineStr">
         <is>
           <t>매년 1분기</t>
         </is>
       </c>
-      <c r="D8" s="141" t="inlineStr"/>
-      <c r="E8" s="142" t="inlineStr">
+      <c r="D8" s="135" t="inlineStr"/>
+      <c r="E8" s="136" t="inlineStr">
         <is>
           <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리</t>
         </is>
       </c>
-      <c r="F8" s="142" t="inlineStr">
+      <c r="F8" s="136" t="inlineStr">
         <is>
           <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성
 • 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
         </is>
       </c>
-      <c r="G8" s="143" t="inlineStr">
+      <c r="G8" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H8" s="143" t="inlineStr">
+      <c r="H8" s="137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="144" t="inlineStr">
+      <c r="I8" s="138" t="inlineStr">
         <is>
           <t>외부지질전문가 Pool List</t>
         </is>
       </c>
-      <c r="J8" s="139" t="inlineStr"/>
-      <c r="K8" s="139" t="inlineStr"/>
+      <c r="J8" s="132" t="inlineStr"/>
+      <c r="K8" s="132" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="132" t="inlineStr">
@@ -14722,49 +20397,49 @@
       <c r="K9" s="132" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="139" t="inlineStr"/>
-      <c r="B10" s="140" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr"/>
+      <c r="B10" s="133" t="inlineStr">
         <is>
           <t>기본계획 지반조사 자료 및 R/O 정보 입수</t>
         </is>
       </c>
-      <c r="C10" s="141" t="inlineStr">
+      <c r="C10" s="134" t="inlineStr">
         <is>
           <t>D-210</t>
         </is>
       </c>
-      <c r="D10" s="141" t="inlineStr">
+      <c r="D10" s="135" t="inlineStr">
         <is>
           <t>D-180</t>
         </is>
       </c>
-      <c r="E10" s="142" t="inlineStr">
+      <c r="E10" s="136" t="inlineStr">
         <is>
           <t>발주처 기본계획 및 지반조사 결과 사전 획득</t>
         </is>
       </c>
-      <c r="F10" s="142" t="inlineStr">
+      <c r="F10" s="136" t="inlineStr">
         <is>
           <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
         </is>
       </c>
-      <c r="G10" s="143" t="inlineStr">
+      <c r="G10" s="137" t="inlineStr">
         <is>
           <t>지반조사 협력업체</t>
         </is>
       </c>
-      <c r="H10" s="143" t="inlineStr">
+      <c r="H10" s="137" t="inlineStr">
         <is>
           <t>설계 협력업체</t>
         </is>
       </c>
-      <c r="I10" s="144" t="inlineStr">
+      <c r="I10" s="138" t="inlineStr">
         <is>
           <t>발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
         </is>
       </c>
-      <c r="J10" s="139" t="inlineStr"/>
-      <c r="K10" s="139" t="inlineStr"/>
+      <c r="J10" s="132" t="inlineStr"/>
+      <c r="K10" s="132" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="132" t="inlineStr"/>
@@ -14798,9 +20473,7 @@
       </c>
       <c r="G11" s="137" t="inlineStr">
         <is>
-          <t>포스코스마트엔지니어링팀(설계)
-토목수행팀(공정)
-토목사업지원팀(기획)</t>
+          <t>포스코스마트엔지니어링팀(설계), 토목수행팀(공정), 토목사업지원팀(기획)</t>
         </is>
       </c>
       <c r="H11" s="137" t="inlineStr">
@@ -14817,55 +20490,53 @@
       <c r="K11" s="132" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="139" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B12" s="140" t="inlineStr">
+      <c r="B12" s="145" t="inlineStr">
         <is>
           <t>기본계획 지반조사 R/O 종합검토 (원가)</t>
         </is>
       </c>
-      <c r="C12" s="141" t="inlineStr">
+      <c r="C12" s="135" t="inlineStr">
         <is>
           <t>D-165</t>
         </is>
       </c>
-      <c r="D12" s="141" t="inlineStr">
+      <c r="D12" s="135" t="inlineStr">
         <is>
           <t>D-150</t>
         </is>
       </c>
-      <c r="E12" s="142" t="inlineStr">
+      <c r="E12" s="136" t="inlineStr">
         <is>
           <t>발주처 지반조사 문제점 R/O 분석</t>
         </is>
       </c>
-      <c r="F12" s="142" t="inlineStr">
+      <c r="F12" s="136" t="inlineStr">
         <is>
           <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
         </is>
       </c>
-      <c r="G12" s="143" t="inlineStr">
+      <c r="G12" s="137" t="inlineStr">
         <is>
           <t>토목견적팀</t>
         </is>
       </c>
-      <c r="H12" s="143" t="inlineStr">
-        <is>
-          <t>포스코스마트엔지니어링팀(설계)
-토목수행팀(공정)
-토목사업지원팀(기획)</t>
-        </is>
-      </c>
-      <c r="I12" s="144" t="inlineStr">
+      <c r="H12" s="137" t="inlineStr">
+        <is>
+          <t>포스코스마트엔지니어링팀(설계), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I12" s="138" t="inlineStr">
         <is>
           <t>기본계획 지반조사 개략 검토서</t>
         </is>
       </c>
-      <c r="J12" s="139" t="inlineStr"/>
-      <c r="K12" s="139" t="inlineStr"/>
+      <c r="J12" s="132" t="inlineStr"/>
+      <c r="K12" s="132" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="132" t="inlineStr">
@@ -14917,148 +20588,148 @@
       <c r="K13" s="132" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="139" t="inlineStr"/>
-      <c r="B14" s="140" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr"/>
+      <c r="B14" s="145" t="inlineStr">
         <is>
           <t>지반조사 업체 계약</t>
         </is>
       </c>
-      <c r="C14" s="141" t="inlineStr">
+      <c r="C14" s="135" t="inlineStr">
         <is>
           <t>D-135</t>
         </is>
       </c>
-      <c r="D14" s="141" t="inlineStr">
+      <c r="D14" s="135" t="inlineStr">
         <is>
           <t>D-120</t>
         </is>
       </c>
-      <c r="E14" s="142" t="inlineStr">
+      <c r="E14" s="136" t="inlineStr">
         <is>
           <t>지반조사업체 용역 계약</t>
         </is>
       </c>
-      <c r="F14" s="142" t="inlineStr">
+      <c r="F14" s="136" t="inlineStr">
         <is>
           <t>• 일반구매시스템을 이용한 용역계약</t>
         </is>
       </c>
-      <c r="G14" s="143" t="inlineStr">
+      <c r="G14" s="137" t="inlineStr">
         <is>
           <t>일반구매팀</t>
         </is>
       </c>
-      <c r="H14" s="143" t="inlineStr">
+      <c r="H14" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="I14" s="144" t="inlineStr">
+      <c r="I14" s="138" t="inlineStr">
         <is>
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J14" s="139" t="inlineStr"/>
-      <c r="K14" s="139" t="inlineStr"/>
+      <c r="J14" s="132" t="inlineStr"/>
+      <c r="K14" s="132" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="146" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B15" s="147" t="inlineStr">
+      <c r="B15" s="145" t="inlineStr">
         <is>
           <t>지반조사 항목, 수량 및 위치검토</t>
         </is>
       </c>
-      <c r="C15" s="148" t="inlineStr">
+      <c r="C15" s="135" t="inlineStr">
         <is>
           <t>D-135</t>
         </is>
       </c>
-      <c r="D15" s="148" t="inlineStr">
+      <c r="D15" s="135" t="inlineStr">
         <is>
           <t>D-115</t>
         </is>
       </c>
-      <c r="E15" s="149" t="inlineStr">
+      <c r="E15" s="136" t="inlineStr">
         <is>
           <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정</t>
         </is>
       </c>
-      <c r="F15" s="149" t="inlineStr">
+      <c r="F15" s="136" t="inlineStr">
         <is>
           <t>• 현장답사 수행
 • 공종별 실시설계에 준하여 수량 및 위치 검토</t>
         </is>
       </c>
-      <c r="G15" s="150" t="inlineStr">
+      <c r="G15" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H15" s="150" t="inlineStr">
+      <c r="H15" s="137" t="inlineStr">
         <is>
           <t>지반조사업체</t>
         </is>
       </c>
-      <c r="I15" s="151" t="inlineStr">
+      <c r="I15" s="138" t="inlineStr">
         <is>
           <t>지반조사 계획서</t>
         </is>
       </c>
-      <c r="J15" s="146" t="inlineStr"/>
-      <c r="K15" s="146" t="inlineStr"/>
+      <c r="J15" s="132" t="inlineStr"/>
+      <c r="K15" s="132" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="146" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B16" s="147" t="inlineStr">
+      <c r="B16" s="145" t="inlineStr">
         <is>
           <t>지반조사계획 적정성 심사의뢰</t>
         </is>
       </c>
-      <c r="C16" s="148" t="inlineStr">
+      <c r="C16" s="135" t="inlineStr">
         <is>
           <t>D-115</t>
         </is>
       </c>
-      <c r="D16" s="148" t="inlineStr">
+      <c r="D16" s="135" t="inlineStr">
         <is>
           <t>D-105</t>
         </is>
       </c>
-      <c r="E16" s="149" t="inlineStr">
+      <c r="E16" s="136" t="inlineStr">
         <is>
           <t>지반조사 항목, 수량 및 위치 적정성 검토</t>
         </is>
       </c>
-      <c r="F16" s="149" t="inlineStr">
+      <c r="F16" s="136" t="inlineStr">
         <is>
           <t>• 지반조사 계획서 검토 및 검토</t>
         </is>
       </c>
-      <c r="G16" s="150" t="inlineStr">
+      <c r="G16" s="137" t="inlineStr">
         <is>
           <t>외부지질전문가 3인 이상</t>
         </is>
       </c>
-      <c r="H16" s="150" t="inlineStr">
+      <c r="H16" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="I16" s="151" t="inlineStr">
+      <c r="I16" s="138" t="inlineStr">
         <is>
           <t>지반조사계획 의견서</t>
         </is>
       </c>
-      <c r="J16" s="146" t="inlineStr"/>
-      <c r="K16" s="146" t="inlineStr"/>
+      <c r="J16" s="132" t="inlineStr"/>
+      <c r="K16" s="132" t="inlineStr"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="132" t="inlineStr"/>
@@ -15108,129 +20779,129 @@
       <c r="K17" s="132" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="139" t="inlineStr"/>
-      <c r="B18" s="140" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr"/>
+      <c r="B18" s="145" t="inlineStr">
         <is>
           <t>지반조사 항목, 수량 및 위치 보완</t>
         </is>
       </c>
-      <c r="C18" s="141" t="inlineStr">
+      <c r="C18" s="135" t="inlineStr">
         <is>
           <t>D-105</t>
         </is>
       </c>
-      <c r="D18" s="141" t="inlineStr">
+      <c r="D18" s="135" t="inlineStr">
         <is>
           <t>D-100</t>
         </is>
       </c>
-      <c r="E18" s="142" t="inlineStr">
+      <c r="E18" s="136" t="inlineStr">
         <is>
           <t>외부지질전문가 의견을 반영한 지반조사 계획 확정</t>
         </is>
       </c>
-      <c r="F18" s="142" t="inlineStr">
+      <c r="F18" s="136" t="inlineStr">
         <is>
           <t>• 외부지질전문가 지반조사 의견 검토
 • 입찰설계 지반조사 계획 보완</t>
         </is>
       </c>
-      <c r="G18" s="143" t="inlineStr">
+      <c r="G18" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H18" s="143" t="inlineStr">
+      <c r="H18" s="137" t="inlineStr">
         <is>
           <t>외부지질전문가 3인 이상, 지반조사업체</t>
         </is>
       </c>
-      <c r="I18" s="144" t="inlineStr">
+      <c r="I18" s="138" t="inlineStr">
         <is>
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J18" s="139" t="inlineStr"/>
-      <c r="K18" s="139" t="inlineStr"/>
+      <c r="J18" s="132" t="inlineStr"/>
+      <c r="K18" s="132" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="146" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B19" s="147" t="inlineStr">
+      <c r="B19" s="145" t="inlineStr">
         <is>
           <t>지반조사 수행</t>
         </is>
       </c>
-      <c r="C19" s="148" t="inlineStr">
+      <c r="C19" s="135" t="inlineStr">
         <is>
           <t>D-100</t>
         </is>
       </c>
-      <c r="D19" s="148" t="inlineStr">
+      <c r="D19" s="135" t="inlineStr">
         <is>
           <t>D-50</t>
         </is>
       </c>
-      <c r="E19" s="149" t="inlineStr">
+      <c r="E19" s="136" t="inlineStr">
         <is>
           <t>과업구간 지반여건 상세 파악</t>
         </is>
       </c>
-      <c r="F19" s="149" t="inlineStr">
+      <c r="F19" s="136" t="inlineStr">
         <is>
           <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등)
 • 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등)
 • 실내시험 수행(요동시험, 입도시험 등)</t>
         </is>
       </c>
-      <c r="G19" s="150" t="inlineStr">
+      <c r="G19" s="137" t="inlineStr">
         <is>
           <t>지반조사업체</t>
         </is>
       </c>
-      <c r="H19" s="150" t="inlineStr">
+      <c r="H19" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="I19" s="151" t="inlineStr">
+      <c r="I19" s="138" t="inlineStr">
         <is>
           <t>지반조사 보고서, 시추 Core 및 샘플</t>
         </is>
       </c>
-      <c r="J19" s="146" t="inlineStr"/>
-      <c r="K19" s="146" t="inlineStr"/>
+      <c r="J19" s="132" t="inlineStr"/>
+      <c r="K19" s="132" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="146" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="147" t="inlineStr">
+      <c r="B20" s="145" t="inlineStr">
         <is>
           <t>지반조사 수렴 결과 분석</t>
         </is>
       </c>
-      <c r="C20" s="148" t="inlineStr">
+      <c r="C20" s="135" t="inlineStr">
         <is>
           <t>D-50</t>
         </is>
       </c>
-      <c r="D20" s="148" t="inlineStr">
+      <c r="D20" s="135" t="inlineStr">
         <is>
           <t>D-40</t>
         </is>
       </c>
-      <c r="E20" s="149" t="inlineStr">
+      <c r="E20" s="136" t="inlineStr">
         <is>
           <t>지반조사 결과 오류 및 지반정수의 적합성 검토</t>
         </is>
       </c>
-      <c r="F20" s="149" t="inlineStr">
+      <c r="F20" s="136" t="inlineStr">
         <is>
           <t>• 입찰설계 지반조사 보고서 검토
 • 시추조사 위치 및 심도의 적정성 검토
@@ -15238,23 +20909,23 @@
 • 실시설계시 추가지반조사 필요구간 검토</t>
         </is>
       </c>
-      <c r="G20" s="150" t="inlineStr">
+      <c r="G20" s="137" t="inlineStr">
         <is>
           <t>외부지질전문가 3인 이상</t>
         </is>
       </c>
-      <c r="H20" s="150" t="inlineStr">
+      <c r="H20" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀, 지반조사업체</t>
         </is>
       </c>
-      <c r="I20" s="151" t="inlineStr">
+      <c r="I20" s="138" t="inlineStr">
         <is>
           <t>지반조사 결과 분석 의견서</t>
         </is>
       </c>
-      <c r="J20" s="146" t="inlineStr"/>
-      <c r="K20" s="146" t="inlineStr"/>
+      <c r="J20" s="132" t="inlineStr"/>
+      <c r="K20" s="132" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="132" t="inlineStr"/>
@@ -15287,9 +20958,7 @@
       </c>
       <c r="G21" s="137" t="inlineStr">
         <is>
-          <t>토목견적팀(원가)
-토목수행팀(공정)
-토목사업지원팀(기획)</t>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
         </is>
       </c>
       <c r="H21" s="137" t="inlineStr">
@@ -15306,56 +20975,54 @@
       <c r="K21" s="132" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="139" t="inlineStr">
+      <c r="A22" s="132" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="140" t="inlineStr">
+      <c r="B22" s="145" t="inlineStr">
         <is>
           <t>지반조사 결과 R/O 종합검토</t>
         </is>
       </c>
-      <c r="C22" s="141" t="inlineStr">
+      <c r="C22" s="135" t="inlineStr">
         <is>
           <t>D-40</t>
         </is>
       </c>
-      <c r="D22" s="141" t="inlineStr">
+      <c r="D22" s="135" t="inlineStr">
         <is>
           <t>D-30</t>
         </is>
       </c>
-      <c r="E22" s="142" t="inlineStr">
+      <c r="E22" s="136" t="inlineStr">
         <is>
           <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정</t>
         </is>
       </c>
-      <c r="F22" s="142" t="inlineStr">
+      <c r="F22" s="136" t="inlineStr">
         <is>
           <t>• 입찰설계 지반조사 R/O별 Cost effect 분석
 • 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
         </is>
       </c>
-      <c r="G22" s="143" t="inlineStr">
+      <c r="G22" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H22" s="143" t="inlineStr">
-        <is>
-          <t>토목견적팀(원가)
-토목수행팀(공정)
-토목사업지원팀(기획)</t>
-        </is>
-      </c>
-      <c r="I22" s="144" t="inlineStr">
+      <c r="H22" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I22" s="138" t="inlineStr">
         <is>
           <t>입찰설계 R/O 검토서</t>
         </is>
       </c>
-      <c r="J22" s="139" t="inlineStr"/>
-      <c r="K22" s="139" t="inlineStr"/>
+      <c r="J22" s="132" t="inlineStr"/>
+      <c r="K22" s="132" t="inlineStr"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="132" t="inlineStr"/>
@@ -15405,56 +21072,54 @@
       <c r="K23" s="132" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="139" t="inlineStr">
+      <c r="A24" s="132" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="140" t="inlineStr">
+      <c r="B24" s="145" t="inlineStr">
         <is>
           <t>추가지반조사 계획 수립</t>
         </is>
       </c>
-      <c r="C24" s="141" t="inlineStr">
+      <c r="C24" s="135" t="inlineStr">
         <is>
           <t>D-30</t>
         </is>
       </c>
-      <c r="D24" s="141" t="inlineStr">
+      <c r="D24" s="135" t="inlineStr">
         <is>
           <t>D-15</t>
         </is>
       </c>
-      <c r="E24" s="142" t="inlineStr">
+      <c r="E24" s="136" t="inlineStr">
         <is>
           <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출</t>
         </is>
       </c>
-      <c r="F24" s="142" t="inlineStr">
+      <c r="F24" s="136" t="inlineStr">
         <is>
           <t>• 지반조사 수렴 결과 분석보고서 검토
 • 지반조사 결과 R/O 종합검토 결과 검토</t>
         </is>
       </c>
-      <c r="G24" s="143" t="inlineStr">
+      <c r="G24" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H24" s="143" t="inlineStr">
-        <is>
-          <t>토목견적팀(원가)
-토목수행팀(공정)
-토목사업지원팀(기획)</t>
-        </is>
-      </c>
-      <c r="I24" s="144" t="inlineStr">
+      <c r="H24" s="137" t="inlineStr">
+        <is>
+          <t>토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
+        </is>
+      </c>
+      <c r="I24" s="138" t="inlineStr">
         <is>
           <t>추가지반조사 List</t>
         </is>
       </c>
-      <c r="J24" s="139" t="inlineStr"/>
-      <c r="K24" s="139" t="inlineStr"/>
+      <c r="J24" s="132" t="inlineStr"/>
+      <c r="K24" s="132" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="132" t="inlineStr"/>
@@ -15507,51 +21172,51 @@
       <c r="K25" s="132" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="139" t="inlineStr"/>
-      <c r="B26" s="140" t="inlineStr">
+      <c r="A26" s="132" t="inlineStr"/>
+      <c r="B26" s="145" t="inlineStr">
         <is>
           <t>ECRM 수립</t>
         </is>
       </c>
-      <c r="C26" s="141" t="inlineStr">
+      <c r="C26" s="135" t="inlineStr">
         <is>
           <t>D-15</t>
         </is>
       </c>
-      <c r="D26" s="141" t="inlineStr">
+      <c r="D26" s="135" t="inlineStr">
         <is>
           <t>D-7</t>
         </is>
       </c>
-      <c r="E26" s="142" t="inlineStr">
+      <c r="E26" s="136" t="inlineStr">
         <is>
           <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토</t>
         </is>
       </c>
-      <c r="F26" s="142" t="inlineStr">
+      <c r="F26" s="136" t="inlineStr">
         <is>
           <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토
 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토
 • 지반조건을 고려한 발파공법성 여부 검토</t>
         </is>
       </c>
-      <c r="G26" s="143" t="inlineStr">
+      <c r="G26" s="137" t="inlineStr">
         <is>
           <t>토목견적팀(원가)</t>
         </is>
       </c>
-      <c r="H26" s="143" t="inlineStr">
+      <c r="H26" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀, 토목수행팀, 토목사업지원팀</t>
         </is>
       </c>
-      <c r="I26" s="144" t="inlineStr">
+      <c r="I26" s="138" t="inlineStr">
         <is>
           <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J26" s="139" t="inlineStr"/>
-      <c r="K26" s="139" t="inlineStr"/>
+      <c r="J26" s="132" t="inlineStr"/>
+      <c r="K26" s="132" t="inlineStr"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="132" t="inlineStr"/>
@@ -15599,81 +21264,81 @@
       <c r="K27" s="132" t="inlineStr"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="152" t="inlineStr">
+      <c r="A28" s="132" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B28" s="153" t="inlineStr">
+      <c r="B28" s="145" t="inlineStr">
         <is>
           <t>입찰설계 현장 인수인계</t>
         </is>
       </c>
-      <c r="C28" s="154" t="inlineStr">
+      <c r="C28" s="135" t="inlineStr">
         <is>
           <t>D+0</t>
         </is>
       </c>
-      <c r="D28" s="154" t="inlineStr">
+      <c r="D28" s="135" t="inlineStr">
         <is>
           <t>D+30</t>
         </is>
       </c>
-      <c r="E28" s="155" t="inlineStr">
+      <c r="E28" s="136" t="inlineStr">
         <is>
           <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유</t>
         </is>
       </c>
-      <c r="F28" s="155" t="inlineStr">
+      <c r="F28" s="136" t="inlineStr">
         <is>
           <t>• 최종 R/O 결과 및 입찰도서 인출</t>
         </is>
       </c>
-      <c r="G28" s="156" t="inlineStr">
+      <c r="G28" s="137" t="inlineStr">
         <is>
           <t>현장소장</t>
         </is>
       </c>
-      <c r="H28" s="156" t="inlineStr">
+      <c r="H28" s="137" t="inlineStr">
         <is>
           <t>토목수행팀</t>
         </is>
       </c>
-      <c r="I28" s="157" t="inlineStr">
+      <c r="I28" s="138" t="inlineStr">
         <is>
           <t>인수인계서</t>
         </is>
       </c>
-      <c r="J28" s="152" t="inlineStr"/>
-      <c r="K28" s="152" t="inlineStr"/>
+      <c r="J28" s="132" t="inlineStr"/>
+      <c r="K28" s="132" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="146" t="inlineStr">
+      <c r="A29" s="132" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B29" s="147" t="inlineStr">
+      <c r="B29" s="145" t="inlineStr">
         <is>
           <t>추가지반조사 수행</t>
         </is>
       </c>
-      <c r="C29" s="148" t="inlineStr">
+      <c r="C29" s="135" t="inlineStr">
         <is>
           <t>D+30</t>
         </is>
       </c>
-      <c r="D29" s="148" t="inlineStr">
+      <c r="D29" s="135" t="inlineStr">
         <is>
           <t>D+100</t>
         </is>
       </c>
-      <c r="E29" s="149" t="inlineStr">
+      <c r="E29" s="136" t="inlineStr">
         <is>
           <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge</t>
         </is>
       </c>
-      <c r="F29" s="149" t="inlineStr">
+      <c r="F29" s="136" t="inlineStr">
         <is>
           <t>• 추가 지반조사 계획 및 시점 확인
 - 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인)
@@ -15682,85 +21347,85 @@
 - 공종별 핵심시설(교량, 접속도로, 토공, #200m 통과점, 터널 발파/심벽진입) 확인</t>
         </is>
       </c>
-      <c r="G29" s="150" t="inlineStr">
+      <c r="G29" s="137" t="inlineStr">
         <is>
           <t>지반조사업체</t>
         </is>
       </c>
-      <c r="H29" s="150" t="inlineStr">
+      <c r="H29" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
         </is>
       </c>
-      <c r="I29" s="151" t="inlineStr">
+      <c r="I29" s="138" t="inlineStr">
         <is>
           <t>추가 지반조사 보고서</t>
         </is>
       </c>
-      <c r="J29" s="146" t="inlineStr">
+      <c r="J29" s="132" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K29" s="146" t="inlineStr">
+      <c r="K29" s="132" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="146" t="inlineStr">
+      <c r="A30" s="132" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B30" s="147" t="inlineStr">
+      <c r="B30" s="145" t="inlineStr">
         <is>
           <t>추가지반조사 결과 분석</t>
         </is>
       </c>
-      <c r="C30" s="148" t="inlineStr">
+      <c r="C30" s="135" t="inlineStr">
         <is>
           <t>D+100</t>
         </is>
       </c>
-      <c r="D30" s="148" t="inlineStr">
+      <c r="D30" s="135" t="inlineStr">
         <is>
           <t>D+110</t>
         </is>
       </c>
-      <c r="E30" s="149" t="inlineStr">
+      <c r="E30" s="136" t="inlineStr">
         <is>
           <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
         </is>
       </c>
-      <c r="F30" s="149" t="inlineStr">
+      <c r="F30" s="136" t="inlineStr">
         <is>
           <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인
 • 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
         </is>
       </c>
-      <c r="G30" s="150" t="inlineStr">
+      <c r="G30" s="137" t="inlineStr">
         <is>
           <t>외부지질전문가 3인 이상</t>
         </is>
       </c>
-      <c r="H30" s="150" t="inlineStr">
+      <c r="H30" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/공무팀, 포스코스마트엔지니어링팀, 토목수행팀</t>
         </is>
       </c>
-      <c r="I30" s="151" t="inlineStr">
+      <c r="I30" s="138" t="inlineStr">
         <is>
           <t>추가 지반조사결과 종합보고서</t>
         </is>
       </c>
-      <c r="J30" s="146" t="inlineStr">
+      <c r="J30" s="132" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="146" t="inlineStr">
+      <c r="K30" s="132" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -15814,226 +21479,250 @@
       <c r="K31" s="132" t="inlineStr"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="139" t="inlineStr">
+      <c r="A32" s="132" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B32" s="140" t="inlineStr">
+      <c r="B32" s="145" t="inlineStr">
         <is>
           <t>실시설계 추가지반조사 결과 검토</t>
         </is>
       </c>
-      <c r="C32" s="141" t="inlineStr">
+      <c r="C32" s="135" t="inlineStr">
         <is>
           <t>D+110</t>
         </is>
       </c>
-      <c r="D32" s="141" t="inlineStr">
+      <c r="D32" s="135" t="inlineStr">
         <is>
           <t>D+120</t>
         </is>
       </c>
-      <c r="E32" s="142" t="inlineStr">
+      <c r="E32" s="136" t="inlineStr">
         <is>
           <t>추가지반조사 결과에 기반한 최종 R/O 확정</t>
         </is>
       </c>
-      <c r="F32" s="142" t="inlineStr">
+      <c r="F32" s="136" t="inlineStr">
         <is>
           <t>• 추가지반조사 결과 검토</t>
         </is>
       </c>
-      <c r="G32" s="143" t="inlineStr">
+      <c r="G32" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H32" s="143" t="inlineStr">
+      <c r="H32" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/품질팀/공무팀, 토목견적팀(원가), 토목수행팀(공정), 토목사업지원팀(기획)</t>
         </is>
       </c>
-      <c r="I32" s="144" t="inlineStr">
+      <c r="I32" s="138" t="inlineStr">
         <is>
           <t>실시설계 최종 R/O</t>
         </is>
       </c>
-      <c r="J32" s="139" t="inlineStr"/>
-      <c r="K32" s="139" t="inlineStr"/>
+      <c r="J32" s="132" t="inlineStr"/>
+      <c r="K32" s="132" t="inlineStr"/>
     </row>
     <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="152" t="inlineStr">
+      <c r="A33" s="132" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B33" s="153" t="inlineStr">
+      <c r="B33" s="145" t="inlineStr">
         <is>
           <t>최종 R/O 이행방안 수립</t>
         </is>
       </c>
-      <c r="C33" s="154" t="inlineStr">
+      <c r="C33" s="135" t="inlineStr">
         <is>
           <t>D+120</t>
         </is>
       </c>
-      <c r="D33" s="154" t="inlineStr">
+      <c r="D33" s="135" t="inlineStr">
         <is>
           <t>D+150</t>
         </is>
       </c>
-      <c r="E33" s="155" t="inlineStr">
+      <c r="E33" s="136" t="inlineStr">
         <is>
           <t>최종 지반조사 결과에 따른 R/O 이행방안 수립</t>
         </is>
       </c>
-      <c r="F33" s="155" t="inlineStr">
+      <c r="F33" s="136" t="inlineStr">
         <is>
           <t>• Core Risk 및 Hedge 방안 수립
 • Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
         </is>
       </c>
-      <c r="G33" s="156" t="inlineStr">
+      <c r="G33" s="137" t="inlineStr">
         <is>
           <t>현장소장</t>
         </is>
       </c>
-      <c r="H33" s="156" t="inlineStr">
+      <c r="H33" s="137" t="inlineStr">
         <is>
           <t>토목수행팀</t>
         </is>
       </c>
-      <c r="I33" s="157" t="inlineStr">
+      <c r="I33" s="138" t="inlineStr">
         <is>
           <t>최종 R/O 이행계획서</t>
         </is>
       </c>
-      <c r="J33" s="152" t="inlineStr"/>
-      <c r="K33" s="152" t="inlineStr"/>
+      <c r="J33" s="132" t="inlineStr"/>
+      <c r="K33" s="132" t="inlineStr"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="152" t="inlineStr">
+      <c r="A34" s="132" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B34" s="153" t="inlineStr">
+      <c r="B34" s="145" t="inlineStr">
         <is>
           <t>외부지질전문가 업무평가</t>
         </is>
       </c>
-      <c r="C34" s="154" t="inlineStr"/>
-      <c r="D34" s="154" t="inlineStr"/>
-      <c r="E34" s="155" t="inlineStr">
+      <c r="C34" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="136" t="inlineStr">
         <is>
           <t>참여인력 전문성 평가 및 특이사항 기록</t>
         </is>
       </c>
-      <c r="F34" s="155" t="inlineStr">
+      <c r="F34" s="136" t="inlineStr">
         <is>
           <t>• 외부지질 전문가 업무평가서 작성</t>
         </is>
       </c>
-      <c r="G34" s="156" t="inlineStr">
+      <c r="G34" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H34" s="156" t="inlineStr">
+      <c r="H34" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/공무팀</t>
         </is>
       </c>
-      <c r="I34" s="157" t="inlineStr">
+      <c r="I34" s="138" t="inlineStr">
         <is>
           <t>외부지질 전문가 업무평가서</t>
         </is>
       </c>
-      <c r="J34" s="152" t="inlineStr"/>
-      <c r="K34" s="152" t="inlineStr"/>
+      <c r="J34" s="132" t="inlineStr"/>
+      <c r="K34" s="132" t="inlineStr"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="152" t="inlineStr">
+      <c r="A35" s="132" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B35" s="153" t="inlineStr">
+      <c r="B35" s="145" t="inlineStr">
         <is>
           <t>조사업체 PM 업무평가</t>
         </is>
       </c>
-      <c r="C35" s="154" t="inlineStr"/>
-      <c r="D35" s="154" t="inlineStr"/>
-      <c r="E35" s="155" t="inlineStr">
+      <c r="C35" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="136" t="inlineStr">
         <is>
           <t>조사업체 PM 전문성 평가 및 특이사항 기록</t>
         </is>
       </c>
-      <c r="F35" s="155" t="inlineStr">
+      <c r="F35" s="136" t="inlineStr">
         <is>
           <t>• 지반조사 PM 업무평가서 작성</t>
         </is>
       </c>
-      <c r="G35" s="156" t="inlineStr">
+      <c r="G35" s="137" t="inlineStr">
         <is>
           <t>포스코스마트엔지니어링팀</t>
         </is>
       </c>
-      <c r="H35" s="156" t="inlineStr">
+      <c r="H35" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/공무팀</t>
         </is>
       </c>
-      <c r="I35" s="157" t="inlineStr">
+      <c r="I35" s="138" t="inlineStr">
         <is>
           <t>PM업무평가서</t>
         </is>
       </c>
-      <c r="J35" s="152" t="inlineStr"/>
-      <c r="K35" s="152" t="inlineStr"/>
+      <c r="J35" s="132" t="inlineStr"/>
+      <c r="K35" s="132" t="inlineStr"/>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="152" t="inlineStr">
+      <c r="A36" s="132" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B36" s="153" t="inlineStr">
+      <c r="B36" s="145" t="inlineStr">
         <is>
           <t>지반조사업체 업무평가</t>
         </is>
       </c>
-      <c r="C36" s="154" t="inlineStr"/>
-      <c r="D36" s="154" t="inlineStr"/>
-      <c r="E36" s="155" t="inlineStr">
+      <c r="C36" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="136" t="inlineStr">
         <is>
           <t>조사업체 업무평가 및 특이사항 기록</t>
         </is>
       </c>
-      <c r="F36" s="155" t="inlineStr">
+      <c r="F36" s="136" t="inlineStr">
         <is>
           <t>• 협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="G36" s="156" t="inlineStr">
+      <c r="G36" s="137" t="inlineStr">
         <is>
           <t>현장소장</t>
         </is>
       </c>
-      <c r="H36" s="156" t="inlineStr">
+      <c r="H36" s="137" t="inlineStr">
         <is>
           <t>현장 공사팀/공무팀</t>
         </is>
       </c>
-      <c r="I36" s="157" t="inlineStr">
+      <c r="I36" s="138" t="inlineStr">
         <is>
           <t>협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="J36" s="152" t="inlineStr"/>
-      <c r="K36" s="152" t="inlineStr"/>
+      <c r="J36" s="132" t="inlineStr"/>
+      <c r="K36" s="132" t="inlineStr"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="132" t="inlineStr"/>
@@ -16042,8 +21731,16 @@
           <t>설계변경 LL 리포트 작성</t>
         </is>
       </c>
-      <c r="C37" s="135" t="inlineStr"/>
-      <c r="D37" s="135" t="inlineStr"/>
+      <c r="C37" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E37" s="136" t="inlineStr">
         <is>
           <t>설계변경 사항 기록</t>
@@ -16074,41 +21771,49 @@
       <c r="K37" s="132" t="inlineStr"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="139" t="inlineStr"/>
-      <c r="B38" s="140" t="inlineStr">
+      <c r="A38" s="132" t="inlineStr"/>
+      <c r="B38" s="145" t="inlineStr">
         <is>
           <t>설계변경 LL 리포트 관리</t>
         </is>
       </c>
-      <c r="C38" s="141" t="inlineStr"/>
-      <c r="D38" s="141" t="inlineStr"/>
-      <c r="E38" s="142" t="inlineStr">
+      <c r="C38" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="136" t="inlineStr">
         <is>
           <t>전체 현장 설계변경 사항 기록</t>
         </is>
       </c>
-      <c r="F38" s="142" t="inlineStr">
+      <c r="F38" s="136" t="inlineStr">
         <is>
           <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
         </is>
       </c>
-      <c r="G38" s="143" t="inlineStr">
+      <c r="G38" s="137" t="inlineStr">
         <is>
           <t>토목수행팀</t>
         </is>
       </c>
-      <c r="H38" s="143" t="inlineStr">
+      <c r="H38" s="137" t="inlineStr">
         <is>
           <t>현장소장</t>
         </is>
       </c>
-      <c r="I38" s="144" t="inlineStr">
+      <c r="I38" s="138" t="inlineStr">
         <is>
           <t>LL리포트 List</t>
         </is>
       </c>
-      <c r="J38" s="139" t="inlineStr"/>
-      <c r="K38" s="139" t="inlineStr"/>
+      <c r="J38" s="132" t="inlineStr"/>
+      <c r="K38" s="132" t="inlineStr"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="132" t="inlineStr"/>
@@ -16117,8 +21822,16 @@
           <t>지반조사업체 정산계약</t>
         </is>
       </c>
-      <c r="C39" s="135" t="inlineStr"/>
-      <c r="D39" s="135" t="inlineStr"/>
+      <c r="C39" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E39" s="136" t="inlineStr">
         <is>
           <t>지반조사업체 정산</t>
@@ -16149,45 +21862,53 @@
       <c r="K39" s="132" t="inlineStr"/>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="139" t="inlineStr">
+      <c r="A40" s="132" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B40" s="140" t="inlineStr">
+      <c r="B40" s="145" t="inlineStr">
         <is>
           <t>매뉴얼 Update</t>
         </is>
       </c>
-      <c r="C40" s="141" t="inlineStr"/>
-      <c r="D40" s="141" t="inlineStr"/>
-      <c r="E40" s="142" t="inlineStr">
+      <c r="C40" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="136" t="inlineStr">
         <is>
           <t>지반조사 매뉴얼 Update</t>
         </is>
       </c>
-      <c r="F40" s="142" t="inlineStr">
+      <c r="F40" s="136" t="inlineStr">
         <is>
           <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
         </is>
       </c>
-      <c r="G40" s="143" t="inlineStr">
+      <c r="G40" s="137" t="inlineStr">
         <is>
           <t>혁신실장</t>
         </is>
       </c>
-      <c r="H40" s="143" t="inlineStr">
+      <c r="H40" s="137" t="inlineStr">
         <is>
           <t>현장 공무팀</t>
         </is>
       </c>
-      <c r="I40" s="144" t="inlineStr">
+      <c r="I40" s="138" t="inlineStr">
         <is>
           <t>지반조사 매뉴얼</t>
         </is>
       </c>
-      <c r="J40" s="139" t="inlineStr"/>
-      <c r="K40" s="139" t="inlineStr"/>
+      <c r="J40" s="132" t="inlineStr"/>
+      <c r="K40" s="132" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -16207,7 +21928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
@@ -19257,7 +24978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFFFFF00"/>
@@ -23297,7 +29018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
@@ -26933,7 +32654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FFFFFF00"/>
@@ -29376,7 +35097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FFFFFF00"/>
@@ -34333,2360 +40054,4 @@
     <brk id="16" min="0" max="1048575" man="1"/>
   </colBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet7">
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
-  <cols>
-    <col width="8.796875" customWidth="1" style="1" min="1" max="3"/>
-    <col width="16" customWidth="1" style="2" min="4" max="4"/>
-    <col width="23" customWidth="1" style="2" min="5" max="5"/>
-    <col width="20.19921875" customWidth="1" style="2" min="6" max="6"/>
-    <col width="38.3984375" customWidth="1" style="2" min="7" max="7"/>
-    <col width="55.59765625" customWidth="1" style="87" min="8" max="8"/>
-    <col width="16.59765625" customWidth="1" style="2" min="9" max="9"/>
-    <col width="48.8984375" customWidth="1" style="87" min="10" max="10"/>
-    <col width="14.19921875" customWidth="1" style="1" min="11" max="11"/>
-    <col width="62.59765625" customWidth="1" style="87" min="12" max="12"/>
-    <col width="12.19921875" customWidth="1" style="1" min="13" max="13"/>
-    <col width="53.796875" customWidth="1" style="87" min="14" max="14"/>
-    <col width="15.09765625" customWidth="1" style="84" min="15" max="15"/>
-    <col width="18" customWidth="1" style="1" min="16" max="16"/>
-    <col width="45" customWidth="1" style="84" min="17" max="17"/>
-    <col width="22" customWidth="1" style="84" min="18" max="18"/>
-    <col width="45" customWidth="1" style="1" min="19" max="35"/>
-    <col width="8.796875" customWidth="1" style="1" min="36" max="65"/>
-    <col width="8.796875" customWidth="1" style="1" min="66" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="31.2" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>L2 코드</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>L3 코드</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>L3 대공종명</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>L4 코드</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>작업단위 (Level 4 Task/Activity)</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>주관</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>목적</t>
-        </is>
-      </c>
-      <c r="H1" s="86" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>산출물(결과)</t>
-        </is>
-      </c>
-      <c r="J1" s="86" t="inlineStr">
-        <is>
-          <t>표준서 (Standard) 요약</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>표준서 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="L1" s="86" t="inlineStr">
-        <is>
-          <t>수행지침 (Guideline) 요약</t>
-        </is>
-      </c>
-      <c r="M1" s="6" t="inlineStr">
-        <is>
-          <t>수행지침 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="N1" s="86" t="inlineStr">
-        <is>
-          <t>체크리스트 (Checklist) 요약</t>
-        </is>
-      </c>
-      <c r="O1" s="8" t="inlineStr">
-        <is>
-          <t>체크리스트 파일 (HTML)</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>첨부서류 연계 상세 설계기준</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>집행단계 리스크 체크리스트</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>협력사 시공/공사관리 자문</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="203.4" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C2" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-1</t>
-        </is>
-      </c>
-      <c r="E2" s="89" t="inlineStr">
-        <is>
-          <t>설계적정성 검토</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>현장 공무팀</t>
-        </is>
-      </c>
-      <c r="G2" s="83" t="inlineStr">
-        <is>
-          <t>설계적정성 및 시공성 검토
-설계오류 확인 및 수량, 내역의 오류확인</t>
-        </is>
-      </c>
-      <c r="H2" s="90" t="inlineStr">
-        <is>
-          <t>- 입찰 요구사항에 대한 설계 반영여부 검토
-- 설계도서 및 표준 자재(트램신호, 도로신호) 반영여부 확인
-- 본선 및 차량기지 규모에 맞는 시스템 및 전자연동장치 구성의 적정성 검토
-- 본선 및 차량기지에 맞는 트램신호, 도로신호 설비 배치의 적정성 검토
-- SIL 인증제품 및 철도형식승인 제품적용, 경찰정 표준에 부합하는 제품 여부 확인
-- 독과점 / 외산 / 특허 여부 확인
-- 현장설치 시공성 및 원가 Risk 검토
-- 공정계획의 적정성 검토</t>
-        </is>
-      </c>
-      <c r="I2" s="83" t="inlineStr">
-        <is>
-          <t>회의록, 설계검토보고서</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>1) 설계적정성 검토(WBS 9000-1-1) 과업 달성을 위해 SIL 4 전자연동장치 및 응답지연(≤100ms) 성능 사양의 설계도서 대조를 완료하라.
-2) 철도 표준 자재(KRS) 및 분산형 CBI 용량, 선로전환기(4.5~6.0kN) 적정성을 검증하고 승인 보고서를 완수하라.</t>
-        </is>
-      </c>
-      <c r="K2" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>1) 입찰 요구사항 상의 기술 스펙 및 자재 규격을 시방서와 사전 대조하십시오.
-2) 분산형 CBI 및 선로전환기 용량의 현장 시공성 및 원가 Risk를 철저히 검토하여 승인을 획득하십시오.</t>
-        </is>
-      </c>
-      <c r="M2" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N2" s="11" t="inlineStr">
-        <is>
-          <t>1) 입찰 안내서 상의 SIL 4 등급 및 무선지연(≤100ms) 사양이 설계 도서에 반영되었는가?
-2) 철도 표준 자재(KRS) 규격 및 매립 선로전환기 전환력(4.5~6.0kN) 기준을 적격 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O2" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R2" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S2" s="83" t="n"/>
-    </row>
-    <row r="3" ht="139.8" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C3" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-2</t>
-        </is>
-      </c>
-      <c r="E3" s="89" t="inlineStr">
-        <is>
-          <t>착수준비 KOM</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G3" s="83" t="inlineStr">
-        <is>
-          <t>신호(트램신호, 도로신호)공사 발주 전 착수수립
-신호공사 발주전략 수립
-발주조건 CP 사항 검토</t>
-        </is>
-      </c>
-      <c r="H3" s="91" t="inlineStr">
-        <is>
-          <t>- 설계(트램신호, 도로신호) 및 현장여건 검토
-- 신호설비 공사 시공성 및 하자발생 리스크 검토
-- 본사 실무 협의를 거쳐 현장에 전파토록 현장공무 검토
-1) 공통계획 및 보완지침 계획 수립
-2) 외주 발주/수급 사전 준비 및 기술 지원
-3) 시공전 신호자재 확인 및 기술 지원
-4) 예상내역 및 누락 아이템 보완
-- 신호설비 공사 시공실적 업체Pool 검토
-- 현설조건 검토
-1) 공정계획 및 신호자재 제작 기간
-2) 안전성 검증을 위한 SIL 인증보유
-3) 철도안전용품 인증 및 경찰청 표준규격
-4) 예비품 및 소모품 확인
-5) 시운전 신호자재 운전 및 교육 지원
-6) 예산내역서 누락 아이템 여부</t>
-        </is>
-      </c>
-      <c r="I3" s="83" t="inlineStr">
-        <is>
-          <t>본사 외주/수행/협의 부서, 착수 KOM 결과보고서, 현장설명서</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>1) 착수준비 KOM(WBS 9000-1-2) 과업을 위해 신호(트램/도로) 공사 발주전략 수립 및 CP사항 사전 검토를 완료하라.
-2) 외주 수급, 신기술자재 확인, 내역 누락 방지 조치 및 SIL 인증보유 적격 업체 Pool을 확정하라.</t>
-        </is>
-      </c>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>1) 신호공사 발주 전 착수 수립 시 본사 실무 협의를 거쳐 현장 전파 및 시공성 리스크를 점검하십시오.
-2) 공정계획, 안전성 SIL 인증, 무상 A/S 및 철도안전법 준수 자재 투입 계획을 사전에 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M3" s="53" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>1) 신호공사 발주 조건 CP 사항 및 하자발생 리스크 사전 검토 수칙을 수행하였는가?
-2) 적격 업체 Pool 검토 및 내역 누락 방지 조치, SIL 인증 보유 여부를 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O3" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="83" t="n"/>
-      <c r="R3" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S3" s="83" t="n"/>
-    </row>
-    <row r="4" ht="221.4" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C4" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-3</t>
-        </is>
-      </c>
-      <c r="E4" s="89" t="inlineStr">
-        <is>
-          <t>착수전 Big Room 회의</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G4" s="83" t="inlineStr">
-        <is>
-          <t>신규공사 수행 시, 선행공정 간섭 및 공종 Risk에 대해 대책 수립</t>
-        </is>
-      </c>
-      <c r="H4" s="92" t="inlineStr">
-        <is>
-          <t>본사(신호/토목/노반/전기/건축/기계/통신) 및 분야별 세부설계 검토
-- 토목/궤도 I/F 사항 검토(시공계획 확인, 궤도 시공전 블록아웃 I/F 협의)
-- 전기/통신/차량 I/F 사항 검토(분야별 I/F 사항 정리)
-- 시운전 I/F 사항 검토(시운전 계획, 시험항목, 시험기간, 배치인원, 사전점검사항 등)
-- 관제 및 운영사 I/F 사항 검토(관제분야 및 운영사 요구사항등)
-- 인원, 자재, 장비 투입계획, 양중장비 운영계획 검토
-- 분야별 인터페이스 협의(궤도, 토목, 건축, 기계설비) 표준 지침서 배포
-- 현장 및 본사 Risk 요인 도출 및 대책 수립
-- 타 공정 및 분야별 Risk 분석 대안(도로/궤도/신호공사 수행 공동조정/안전)
-- 본사/현장/협력사 협의체 구축을 통한 세부내용 검토
-- 신호자재/기자재 반입로 및 야적장/제작사 공장 검토
-- 신호자재 성능보증: 유사사례 적용실적 및 성능보증 사항 검토
-- 하자 예방: 타 프로젝트 하자사례 검토 후, 동일제품 적용 방지방안 수립
-- SIL(Safety Integration Level) 인증제품 도입:  전자연동장치, 차상신호장치, 차축검지기, 선로전환기
-- 당사의 장비 안전검사 기준 공유, 장비검사 계획 확인
-- 관계기관 인허가 및 협의
-1) 화성시/수원시 교통센터, 경찰청 교차로 신호 운영 체계 및 연계 협의</t>
-        </is>
-      </c>
-      <c r="I4" s="83" t="inlineStr">
-        <is>
-          <t>Big Room 회의록(지침 전파 서명)</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>1) 착수전 Big Room 회의(WBS 9000-1-3)를 통해 본사 및 각 분야(토목/궤도/전기/건축/기계/통신) 간 시공 인터페이스를 대조하라.
-2) 궤도 시공 전 블록아웃, 배수로, 선로전환기, 차축검지기 설치 I/F 항목을 사전 확정하라.</t>
-        </is>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>1) 신규공사 수행 시 선행공정 간섭 및 공종 Risk 대책 회의를 주관하십시오.
-2) 궤도 시공 전 블록아웃 및 선로전환기 설치 I/F에 대해 각 분야 담당자와의 협의록을 작성하십시오.</t>
-        </is>
-      </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>1) 본사 및 분야별(토목/궤도/전기/건축/통신) 세부설계 인터페이스를 검토하였는가?
-2) 궤도 시공 전 블록아웃 및 차축검지기 설치 I/F 사전 대책을 수립하였는가?</t>
-        </is>
-      </c>
-      <c r="O4" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="83" t="n"/>
-      <c r="R4" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S4" s="83" t="n"/>
-    </row>
-    <row r="5" ht="187.2" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C5" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-4</t>
-        </is>
-      </c>
-      <c r="E5" s="89" t="inlineStr">
-        <is>
-          <t>전기 / 통신 / 건축 / 도로 / 궤도 / 차량 등 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G5" s="83" t="inlineStr">
-        <is>
-          <t>완벽한 시스템 조율 및 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="H5" s="93" t="inlineStr">
-        <is>
-          <t>- 토목/궤도분야 인터페이스
-1) 단계별 시공계획 확인
-2) 궤도 시공전 블록아웃, 배수로, 선로전환기, 융설장치, 차축검지기 설치 I/F
-- 전기/통신/도로/차량 인터페이스
-1) (전기) 상용전원투입 및 접지단자함 설치
-2) (통신) 통신망 연결을 위한 회선제공
-3) (통신) 공용Pole 사용에 따른 인터페이스(굴착공사/공용 배관 배선 활용 등)
-4) (차량) 차상신호 및 열차종합제어장치(TCMS) 인터페이스 협의
-5) (차량) 지상신호설비 및 선형에 따른 지상/차상 장치 연계방안 협의
-6) (전기/통신) UPS 통합 사용 관련 Feeder 공급 또는 할당 
-7) (건축) 기계실 및 관제실 A/F 설치, 면척 및 기기 배치, 출입문 크기 등</t>
-        </is>
-      </c>
-      <c r="I5" s="83" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>1) 시스템 조율(WBS 9000-1-4)을 위해 전기/통신/건축/도로/궤도/차량 분야 간 시공 인터페이스를 조율하라.
-2) 궤도 시공 전 블록아웃, 배수로, 융설장치, 차축검지기 설치 I/F 승인서를 완수하라.</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>1) 토목/궤도 단계별 시공계획을 확인하고 기계실 배선 및 현장 장치 설치 I/F를 조율하십시오.
-2) 차축검지기 및 융설장치 체결 부위의 치수 적정성을 서면으로 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>1) 토목/궤도 시공 전 블록아웃 및 배수로 설치 I/F를 사전 확인하였는가?
-2) 차량기지 및 본선 선로전환기/차축검지기 체결 인터페이스를 조율하였는가?</t>
-        </is>
-      </c>
-      <c r="O5" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="83" t="n"/>
-      <c r="R5" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S5" s="83" t="n"/>
-    </row>
-    <row r="6" ht="104.4" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C6" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-5</t>
-        </is>
-      </c>
-      <c r="E6" s="89" t="inlineStr">
-        <is>
-          <t>도로 / 궤도 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G6" s="83" t="inlineStr">
-        <is>
-          <t>선로선형 설계를 위한 사전조정 및 트램 운행 최적화</t>
-        </is>
-      </c>
-      <c r="H6" s="90" t="inlineStr">
-        <is>
-          <t>- 유관기관 피드백 수렴/조정 및 요구사항 확인
-- 궤도 분기기 통과 요구사항 검토 및 확인
-- 궤도/토목 단계별 시공계획 확인
-- 궤도 시공전 블록아웃 등 I/F사항 협의
-- 선로전환기 어스박스 설치, 차축검지기 설치, 궤도 천공위치등 협의
-- 배수설비 설치 관련 사항 협의</t>
-        </is>
-      </c>
-      <c r="I6" s="83" t="inlineStr">
-        <is>
-          <t>궤도/신호 요구사항 및 회의록</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>1) 도로/궤도 I/F(WBS 9000-1-5) 달성을 위해 선로선형 및 궤도 분기기 통과 요구사항을 검토하라.
-2) 도심 매립 궤도용 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 설치 조건 및 유관기관 피드백을 반영하라.</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>1) 유관기관 피드백 수렴 및 궤도 분기기 통과 요구사항을 사전 조정하십시오.
-2) 도로 교차로 노면 매립 궤도 시공계획과 선로전환기 설치 위치 적정성을 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M6" s="53" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>1) 궤도 분기기 통과 요구사항 및 선로선형 사전조정 결과를 확인하였는가?
-2) 노면 매립형 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 시공조건을 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="83" t="n"/>
-      <c r="R6" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S6" s="83" t="n"/>
-    </row>
-    <row r="7" ht="133.8" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C7" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-6</t>
-        </is>
-      </c>
-      <c r="E7" s="89" t="inlineStr">
-        <is>
-          <t>시공전 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G7" s="83" t="inlineStr">
-        <is>
-          <t>시스템의 설계 보완 검토를 진행하고 완벽한 연계를 위한 설계</t>
-        </is>
-      </c>
-      <c r="H7" s="91" t="inlineStr">
-        <is>
-          <t>- 토목/궤도분야 인터페이스
-1) 단계별 시공계획 확인
-2) 궤도 시공전 블록아웃, 배수로, 선로전환기, 융설장치, 차축검지기 설치 I/F
-- 전기/통신/도로/차량 인터페이스
-1) (전기) 상용전원투입 및 접지단자함 설치
-2) (통신) 통신망 연결을 위한 회선제공
-3) (통신) 공용Pole 사용에 따른 인터페이스(굴착공사/공용 배관 배선 활용 등)
-4) (차량) 차상신호 및 열차종합제어장치(TCMS) 인터페이스 협의
-5) (차량) 지상신호설비 및 선형에 따른 지상/차상 장치 연계방안 협의
-6) (전기/통신) UPS 통합 사용 관련 Feeder 공급 또는 할당 
-7) (건축) 기계실 및 관제실 A/F 설치, 면척 및 기기 배치, 출입문 크기 등</t>
-        </is>
-      </c>
-      <c r="I7" s="83" t="inlineStr">
-        <is>
-          <t>인터페이스 보고서 및 인터페이스 회의록</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>1) 시공전 인터페이스(WBS 9000-1-6)를 통해 시스템 설계 보완 및 연계 방안을 정밀 검토하라.
-2) 배관배선 인입구, 구조물 간섭 및 궤도 시공 전 설치 항목을 개시 전 차단하라.</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>1) 시스템 설계 보완검토를 통해 연계 시공 시 발생 가능한 간섭을 사전에 제거하십시오.
-2) 궤도 시공 전 블록아웃 및 케이블 인입 배관의 간섭 여부를 정밀 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>1) 시스템 설계 보완 검토를 통해 연계 설치 방안을 확정하였는가?
-2) 케이블 인입 배관 및 궤도 블록아웃 간섭을 사전 제거하였는가?</t>
-        </is>
-      </c>
-      <c r="O7" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="83" t="n"/>
-      <c r="R7" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="127.8" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C8" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-7</t>
-        </is>
-      </c>
-      <c r="E8" s="89" t="inlineStr">
-        <is>
-          <t>시스템 장비검토 사전 협의사항 도출 및 검토</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G8" s="83" t="inlineStr">
-        <is>
-          <t>완벽한 시스템 연계 및 동작성 확보를 위한 가이드라인 제공</t>
-        </is>
-      </c>
-      <c r="H8" s="83" t="inlineStr">
-        <is>
-          <t>- 성능보증 기능성 신호자재 단품 Spec 검토
-- 제조사 자체 시험 및 인증 확인
-- 설치 시공대장 및 제작도서 승인 서명</t>
-        </is>
-      </c>
-      <c r="I8" s="83" t="inlineStr">
-        <is>
-          <t>자체 검증서 및 제작도서 승인 서류</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>1) 장비 사전검토(WBS 9000-1-7)를 위해 기능성 신호자재 단품 Spec 및 성능보증 사양을 검토하라.
-2) 제조사 자체 시험 성적서, KRS 표준 규격 및 제작도서 승인 서명을 완수하라.</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>1) 신호자재 단품 Spec 검토 및 제조사 자체 시험성적서를 확인하십시오.
-2) 제작도서 승인 서명 및 현장 투입 전 성능보증 기능을 검증하십시오.</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>1) 성능보증 기능성 신호자재 단품 Spec 검토를 완료하였는가?
-2) 제조사 공장검수 성적서 및 제작도서 승인 서명을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="83" t="n"/>
-      <c r="R8" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S8" s="83" t="n"/>
-    </row>
-    <row r="9" ht="104.4" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C9" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-8</t>
-        </is>
-      </c>
-      <c r="E9" s="89" t="inlineStr">
-        <is>
-          <t>관제 및 운영사 인터페이스 협의</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G9" s="83" t="inlineStr">
-        <is>
-          <t>관제 및 운영사 요구사항 사전 반영 및 시공신뢰 확보</t>
-        </is>
-      </c>
-      <c r="H9" s="90" t="inlineStr">
-        <is>
-          <t>- 시운전시 조율사항 및 예비사항 도출
-- 신호제어 운영사 실무 조율 및 협의
-- 철도관제를 위한 관제사 조작반 및 화면표시 정보에 대한 사전협의 항목 도출
-- 설계내용 중 신호설비 운영 및 유지보수자 편의성 향상을 위한 기능추가 / 불필요 기능 삭제 사전협의</t>
-        </is>
-      </c>
-      <c r="I9" s="83" t="inlineStr">
-        <is>
-          <t>인터페이스 회의록 및 관리대장</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제/운영사 I/F(WBS 9000-1-8) 달성을 위해 종합관제실(OCC) 요구사항을 시공 전 반영하라.
-2) 철도관제를 위한 관제사 조작반 MMI 및 예비관제 1:1 실시간 DB 동기화를 검증하라.</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제 및 운영사 실무 조율을 거쳐 시운전 시 예비사항 및 조작반 화면표시 정보를 도출하십시오.
-2) 관제센터 MMI 화면 및 조작반 정보의 실시간 동기화 상태를 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>1) 시운전 시 조율사항 및 예비사항 도출을 완료하였는가?
-2) 철도관제를 위한 관제사 조작반 MMI 표시 정보를 사전 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="83" t="n"/>
-      <c r="R9" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S9" s="83" t="n"/>
-    </row>
-    <row r="10" ht="104.4" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C10" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-9</t>
-        </is>
-      </c>
-      <c r="E10" s="89" t="inlineStr">
-        <is>
-          <t>자재 / 인원 / 장비 및 투입 사전 검토</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 협력사 / 관리감독자</t>
-        </is>
-      </c>
-      <c r="G10" s="83" t="inlineStr">
-        <is>
-          <t>자재/인원/장비 투입 계획 수립</t>
-        </is>
-      </c>
-      <c r="H10" s="83" t="inlineStr">
-        <is>
-          <t>현장 여건 및 수량을 기준으로 투입 인원, 장비 계획 규명
-- 현장여건 및 궤도 시공계획 검토에 따른 시공계획 작성
-- 시공계획 작성에 따른 인력투입계획, 자재수급계획, 장비투입계획 작성
-- 시공계획 작성에 따른 관계기관(경찰청, 지자체 교통센터) 협의사항 도출
-- 공사에 따른 민원 또는 발주처 관계기관 요구사항 점검</t>
-        </is>
-      </c>
-      <c r="I10" s="83" t="inlineStr">
-        <is>
-          <t>세부 공정계획 수립 및 보고</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>1) 자재/인원/장비 계획(WBS 9000-1-9) 수립을 위해 현장 수량 기준 투입 계획을 승인하라.
-2) 현장 여건 및 궤도 시공계획 맞춤형 투입 schedule 작성 및 수급 조정을 완수하라.</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>1) 현장 여건 및 수량을 기준으로 투입 인원, 장비 계획서를 작성하여 감리단 승인을 받으십시오.
-2) 궤도 시공계획과 연계된 자재 반입 및 작업원 투입 스케줄을 조정하십시오.</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>1) 현장 수량 기준 투입 인원 및 장비 계획 규명서를 작성하였는가?
-2) 궤도 시공계획 연계 투입 스케줄 감리단 승인을 획득하였는가?</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="83" t="n"/>
-      <c r="R10" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S10" s="83" t="n"/>
-    </row>
-    <row r="11" ht="104.4" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C11" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-10</t>
-        </is>
-      </c>
-      <c r="E11" s="89" t="inlineStr">
-        <is>
-          <t>장비반입 및 안전교육</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀 / 안전팀</t>
-        </is>
-      </c>
-      <c r="G11" s="83" t="inlineStr">
-        <is>
-          <t>장비 반입 준비 및 안전교육 완료</t>
-        </is>
-      </c>
-      <c r="H11" s="90" t="inlineStr">
-        <is>
-          <t>- 도로 굴착장비, 고속작업 시 사용할 장비, 인양장비등 관련 장비 계획 검토
-- 장비 spec 확인, 장비 성능 점검
-- 작업원 안전교육 실시</t>
-        </is>
-      </c>
-      <c r="I11" s="83" t="inlineStr">
-        <is>
-          <t>측정기록서, 안전교육 결과서</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>1) 장비안전(WBS 9000-1-10) 확보를 위해 굴착/고속작업/인양 장비 Spec 점검 및 성능 검사를 시행하라.
-2) 작업원 특별 안전교육 및 위험성평가 이행 확인서를 승인 완수하라.</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>1) 도로 굴착 및 인양 장비 Spec 확인과 장비 성능 점검을 반입 전 수행하십시오.
-2) 신호 공사 작업원에 대한 특별 안전교육 및 보호구 착용 상태를 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M11" s="53" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>1) 도로 굴착 및 인양 장비 Spec 점검 및 성능 검사를 완료하였는가?
-2) 신호 공사 작업원 특별 안전교육 실시 기록을 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="83" t="n"/>
-      <c r="R11" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S11" s="83" t="n"/>
-    </row>
-    <row r="12" ht="104.4" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C12" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-11</t>
-        </is>
-      </c>
-      <c r="E12" s="89" t="inlineStr">
-        <is>
-          <t>자재 반입 및 검수</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주청/공동감리단</t>
-        </is>
-      </c>
-      <c r="G12" s="83" t="inlineStr">
-        <is>
-          <t>공장제품 품질 확보를 위한 자재 검수 및 검사</t>
-        </is>
-      </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>- 자재공급승인원 제출 및 승인
-- 공장검수 계획 제출 및 승인
-- 각종 자재 사양 확인(KS, 표준규격, 독/과점 규격 등)
-- 자재 현지 반입 및 반입동선, 반입기간, 반입장소 검토
-- 승인된 자재 상세사양 확인(Serial number 등록)
-- 제품의 규격, 수량 도면과 일치하는지 검토</t>
-        </is>
-      </c>
-      <c r="I12" s="83" t="inlineStr">
-        <is>
-          <t>자재검수요청서 / 자재수입검사서</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>1) 자재검수(WBS 9000-1-11) 강화를 위해 자재공급승인원(MAR) 제출 및 공장검수를 시행하라.
-2) 반입 자재의 KS/KRS 규격 시험성적서 대조 검수 및 품질 보증을 완수하라.</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>1) 자재공급승인원(MAR) 및 공장검수 계획서를 제출하여 감리단 승인을 획득하십시오.
-2) 자재 현지 반입 시 사양서, 시험성적서 및 표준규격 부합 여부를 인수 검수하십시오.</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>1) 자재공급승인원(MAR) 제출 및 공장검수 승인을 획득하였는가?
-2) 반입 자재 사양 확인(KS, KRS 표준규격) 및 수량 검수를 시행하였는가?</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="83" t="n"/>
-      <c r="R12" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S12" s="83" t="n"/>
-    </row>
-    <row r="13" ht="104.4" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C13" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-12</t>
-        </is>
-      </c>
-      <c r="E13" s="89" t="inlineStr">
-        <is>
-          <t>시스템설비 설치 (현장/기능실)</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 분야별 전담팀</t>
-        </is>
-      </c>
-      <c r="G13" s="83" t="inlineStr">
-        <is>
-          <t>현장설비 및 기기실의 자체 최적의 설치작업</t>
-        </is>
-      </c>
-      <c r="H13" s="83" t="inlineStr">
-        <is>
-          <t>- 기계 장치 위치 및 마감 동선 확인
-- 승인된 자재 상세사양 확인 (Serial number 등록)
-- 제품의 규격, 수량 도면과 일치하는지 검토
-- 배선/기능실 배선 상태 및 신호 인터페이스 확인
-- 배선/기능실 케이블 및 전선 배선을 시운전 및 계측기 결과에 준하여 시행
-- 케이블 단선부 및 배선 등 내부 배선 및 배선 결과 검수서</t>
-        </is>
-      </c>
-      <c r="I13" s="83" t="inlineStr">
-        <is>
-          <t>검사 결과서</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>1) 시스템설비 설치(WBS 9000-1-12)를 위해 기계실 랙 마감 동선 및 승인 자재 상세 사양을 확인하라.
-2) 현장 신호기, 선로전환기 기초 볼트 체결 및 도면 일치 여부를 정밀 시공하라.</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>1) 기계실 장치 위치, 마감 동선 및 승인 자재 Serial Number 등록을 확인하십시오.
-2) 현장 설치 설비의 규격, 수량 및 도면 일치 여부를 정밀 측정하여 시공하십시오.</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>1) 기계실 장치 위치, 마감 동선 및 승인 자재 사양을 확인하였는가?
-2) 현장 신호기/선로전환기 기초 볼트 체결 및 규격 일치 여부를 시공하였는가?</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R13" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S13" s="83" t="n"/>
-    </row>
-    <row r="14" ht="104.4" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C14" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-14</t>
-        </is>
-      </c>
-      <c r="E14" s="89" t="inlineStr">
-        <is>
-          <t>시스템 단위시험</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G14" s="83" t="inlineStr">
-        <is>
-          <t>철도안전법상 신호시스템 규정에 대한 설치 후 현황시험 및 기능 확보</t>
-        </is>
-      </c>
-      <c r="H14" s="90" t="inlineStr">
-        <is>
-          <t>- 자체단독시험 및 관계부서 공동 시험수행 여부
-- 지상신호장치 및 관계부서 단위시험 결과서
-- 감리단이 승인한 검사 및 시험 점검표 (ITP/ITC) 절차에 따라 수행
-- 지상신호설비 단위시험 항목
-1) 신호기장치 / 선로전환기 장치 / 전자연동장치 / 열차자동방호장치 / 신호전원장치 / 전선로 / 안전설비 / 기타설비 / 트램신호기 / TPD 등
-- 관제설비
-1) 서버설치 / 네트워크 장치 / 콘솔장치 / 대형표시반 / LDTS</t>
-        </is>
-      </c>
-      <c r="I14" s="83" t="inlineStr">
-        <is>
-          <t>자체단독시험 및 시험결과서 (단독단위)</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>1) 단위시험(WBS 9000-1-14) 수행을 위해 철도안전법 규정에 따른 설치 후 단독 현황시험을 시행하라.
-2) 신호기, 선로전환기, 전원장치, 차축검지기 개별 ITP/ITC 시험 결과서를 승인 완수하라.</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>1) 자체 단독시험 및 관계부서 공동 시험수행 여부를 확인하십시오.
-2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 지상신호장치 단위시험 결과서를 작성하십시오.</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>1) 지상신호장치 및 관계부서 단위시험 결과서를 확인하였는가?
-2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 개별 단독 현황시험을 수행하였는가?</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P14" s="10" t="n"/>
-      <c r="Q14" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R14" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S14" s="83" t="n"/>
-    </row>
-    <row r="15" ht="104.4" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C15" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-15</t>
-        </is>
-      </c>
-      <c r="E15" s="89" t="inlineStr">
-        <is>
-          <t>신호시스템 통합시험</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G15" s="83" t="inlineStr">
-        <is>
-          <t>신호시스템 단독시험 완료 후 타 분야 연계 및 시설 유효성 확인</t>
-        </is>
-      </c>
-      <c r="H15" s="90" t="inlineStr">
-        <is>
-          <t>- 관계성과 연계 인터페이스 시험
-- 지상 및 차량 인터페이스
-- 지상 및 차량 인터페이스 시 시험 결과표
-- 감리단이 승인한 검사 및 시험 점검표 (ITP/ITC) 절차에 따라 수행
-1) 관제실 및 현장 연동장치간 인터페이스 시험
-2) 지상 및 차상 인터페이스 시험
-3) 도로신호/트램신호 인터페이스 시험(우선신호 시험)</t>
-        </is>
-      </c>
-      <c r="I15" s="83" t="inlineStr">
-        <is>
-          <t>자체단독시험 및 시험결과서 (단독단위)</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>1) 통합시험(WBS 9000-1-15)을 통해 단독시험 완료 후 관제 ➔ CBI 전자연동장치 통합 연동을 검증하라.
-2) 차상-지상 무선(LTE-R) 도로-트램 우선신호 연계 시험 결과표를 승인 완수하라.</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제실 및 현장 연동장치 간 인터페이스 통합시험을 시행하십시오.
-2) 지상-차상 인터페이스 및 도로/트램 우선신호 무선 연계시험 결과표를 작성하십시오.</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제실 및 현장 연동장치 간 인터페이스 시험을 수행하였는가?
-2) 지상-차상 인터페이스 및 도로-트램 우선신호 연계 시험을 검증하였는가?</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R15" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S15" s="83" t="n"/>
-    </row>
-    <row r="16" ht="104.4" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C16" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-16</t>
-        </is>
-      </c>
-      <c r="E16" s="89" t="inlineStr">
-        <is>
-          <t>공종별 시험</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G16" s="83" t="inlineStr">
-        <is>
-          <t>철도안전기준에 따른 법정 / 설계기준 / 신기술 / 시운전 등의 요구사항의 적합성 검증</t>
-        </is>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>- 신기술공법 등 신공법 적용
-- 자료정리 및 단위 시험
-- 신기술공법/기능성/현장성 단위 시험 결과서
-- 현장설비 시험
-1) 신호기 장치: 신호기 설치 / 투시거리 및 정상 동작시험
-2) 신호부속기(진로표시기): 진로표시기 설치 및 정상 동작시험
-3) 차축검지기 설치 및 정상 동작시험
-4) 선로전환기 설치상태 확인시험
-5) 트램신호기, TPD, 설치 및 동작시험
-6) 교차로 영상유고 시스템 설치 및 동작시험
-- 신호기계실 설비 시험
-1) 전원공급장치 이중화 확인 및 절체 시험 수행
-2) 전자연동장치 설치 및 정상 동작시험
-3) 전자열쇠 정상 작동상태 확인
-4) 차축검지기부 설치 및 정상 동작시험
-- 관제설비 시험
-1) 관제실: 운영관제실 MMI 장치 동작상태
-2) 신호컴퓨터실: 신호컴퓨터실 서버 및 네트워크 정상 동작상태 확인
-3) 전원장치 정상 동작상태 확인</t>
-        </is>
-      </c>
-      <c r="I16" s="83" t="inlineStr">
-        <is>
-          <t>공종별 시험 결과보고서</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>1) 공종별 시험(WBS 9000-1-16)을 위해 신호기, 진로표시기, 선로전환기, 차축검지기 현장 동작시험을 시행하라.
-2) 신호기계실 전원 2중화 절체 시험 및 관제 CTC 서버 정상 동작 시험을 완수하라.</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>1) 현장설비(신호기 투시거리, 선로전환기 쇄정, 차축검지기) 동작시험을 시행하십시오.
-2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 정상 동작상태를 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>1) 신호기 투시거리/진로표시기 및 선로전환기 쇄정 동작시험을 수행하였는가?
-2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 동작을 검증하였는가?</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R16" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S16" s="83" t="n"/>
-    </row>
-    <row r="17" ht="104.4" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C17" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-17</t>
-        </is>
-      </c>
-      <c r="E17" s="89" t="inlineStr">
-        <is>
-          <t>차량 투입 전 점검</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 시공전담팀</t>
-        </is>
-      </c>
-      <c r="G17" s="83" t="inlineStr">
-        <is>
-          <t>차량 시험운행 전 철저한 안전대책 수립 및 품질성 확보 여부 확인</t>
-        </is>
-      </c>
-      <c r="H17" s="90" t="inlineStr">
-        <is>
-          <t>- 현장의 시설물 설치상태 점검
-1) 연동검사(설비동작, 진로취급 및 신호현시 시험 등)
-2) 신호 기계실 내 시스템 검사(연동장치, 열차제어시스템 등)
-3) 전원장치 시험(UPS 및 배터리)
-4) 신호 기계실 내부 방재예방 설비(소화기, 접지저항값 측정결과)
-5) 신호기 시공상태(설치 위치의 적정성, 신호기와 건축물과의 건축한계 적정여부 등)
-6) 선로전환기 시공상태 확인(선로전환기 전환 및 표시회로 구성 등)
-7) 전선류 시공상태 확인(케이블 단말처리 및 접속개소, 선명찰 절연저항 측정값 등)
-8) 기구함, 접속함 등 시공상태 확인(기초 시공적정여부, 전선 인입구, 접지설비, 볼트류 체결 상태 등)
-9) 본선의 시설물 성능장애 점검
-- 건축한계 및 차량한계
-- 가공선로: 폭(3,100mm)/높이(3,800mm) 및 차량한계: 폭(2,700mm)/높이(3,600mm) 정렬선 개시
-- 수전 및 전압 점검</t>
-        </is>
-      </c>
-      <c r="I17" s="83" t="inlineStr">
-        <is>
-          <t>차량 투입 전 점검 결과 보고서</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>1) 차량 투입 전 점검(WBS 9000-1-17)을 통해 연동검사 및 기계실 방재/접지저항 측정을 시행하라.
-2) 건축한계/차량한계 이격 정밀 측정 및 전원장치(UPS) 성능을 최종 검증하라.</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>1) 연동검사(설비동작, 진로취급) 및 신호기 시공상태 적정성을 점검하십시오.
-2) 건축한계(폭 3.1m/높이 3.8m) 이격 측정 및 기계실 UPS/방재예방 설비를 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>1) 연동검사 및 기계실 시스템/UPS 시험을 완료하였는가?
-2) 신호기와 건축물 간 건축한계 정밀 측정 및 방재설비를 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R17" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S17" s="83" t="n"/>
-    </row>
-    <row r="18" ht="104.4" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C18" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-18</t>
-        </is>
-      </c>
-      <c r="E18" s="89" t="inlineStr">
-        <is>
-          <t>차량 시운전</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G18" s="83" t="inlineStr">
-        <is>
-          <t>철도안전법상 철도기술기준에 적합하게 시운전 수행 여부(철도노선 규정)</t>
-        </is>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>- 철도기술기준(궤도/철도차량 안전성) 준수 여부
-1) 속도/제동 테스트수행 여부
-2) 차량, 신호, 통신 시스템간 인터페이스 시험
-- 철도안전법 제26조(철도차량 형식승인) 기준 준수
-1) 주요 외관검사 및 치수검사
-2) 주요기기 기능검사(제어전원 투입확인, 집전장치 동작확인, 추진제어장치 동작확인 등)
-- 차상신호장치 포함시 시행(차상신호장치는 차량제작사 공급 or 신호설비 공급사 공급)
-1) 지·차상 연계동작시험
-2) 차량, 신호, 통신 시스템간 인터페이스 시험
-3) 열차제어 시스템 기능시험
-- 센터간 I/F 시험
-1) 교통관제센터/트램관제센터간 정보전송 상태
-2) 차량 위치검지 시험</t>
-        </is>
-      </c>
-      <c r="I18" s="83" t="inlineStr">
-        <is>
-          <t>철도차량 안전성 결과 보고서</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>1) 차량 시운전(WBS 9000-1-18) 수행 시 철도안전법 제26조 형식승인 기준 준수 여부를 검증하라.
-2) 속도/제동 테스트, 차상-지상 연계동작 및 열차제어 시스템 기능시험을 완수하라.</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>1) 철도기술기준에 따라 속도/제동 테스트 및 주요기기 제어전원 투입을 검사하십시오.
-2) 차상신호장치 지·차상 연계동작시험 및 열차제어 시스템 기능시험을 시행하십시오.</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>1) 철도기술기준 준수 속도/제동 테스트 및 주요기기 검사를 시행하였는가?
-2) 차상-지상 연계동작시험 및 차량-신호-통신 I/F 시험을 검증하였는가?</t>
-        </is>
-      </c>
-      <c r="O18" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R18" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S18" s="83" t="n"/>
-    </row>
-    <row r="19" ht="104.4" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C19" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-19</t>
-        </is>
-      </c>
-      <c r="E19" s="89" t="inlineStr">
-        <is>
-          <t>운영자 교육시행</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>현장 시스템팀</t>
-        </is>
-      </c>
-      <c r="G19" s="83" t="inlineStr">
-        <is>
-          <t>운영요원(기관사 및 안전관리)을 위한 주행/유지 교육시행</t>
-        </is>
-      </c>
-      <c r="H19" s="90" t="inlineStr">
-        <is>
-          <t>- 시스템안전 교육(철도차량 안전점검 요령)
-- 차량, 신호, 통신 시스템간 인터페이스 사용방법 및 조작 교육
-- 관제센터와의 연계 기계실/차량내 장치(DID 보드 등) 운영 및 테스트
-- 시스템공급  장비제작사에 의한 운영자 및 유지보수자 교육
-1) (관제설비) CTC서버, 콘솔컴퓨터 등
-2) (신호 기계실) 전자연동장치, 궤도회로장치 등
-3) (현장설비) 신호기, 선로전환기, 튜닝유니트 등</t>
-        </is>
-      </c>
-      <c r="I19" s="83" t="inlineStr">
-        <is>
-          <t>운영자훈련 및 기술단계에서 운영지침서</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>1) 운영자 교육(WBS 9000-1-19)을 위해 기관사 및 유지보수 요원 대상 시스템 안전 교육을 시행하라.
-2) 장비 제작사에 의한 CTC/CBI/현장설비 조작·정비 기술 교육 완료 이수증을 승인하라.</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>1) 철도차량 안전점검 요령 및 시스템 간 조작 방법에 대한 운영자 교육을 시행하십시오.
-2) CTC 서버, 전자연동장치, 현장 신호기/선로전환기 교육 이수 현황을 확인하십시오.</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>1) 기관사 및 유지보수요원 대상 시스템 안전 교육을 시행하였는가?
-2) 장비 제작사에 의한 CTC/CBI/현장설비 조작교육을 완료하였는가?</t>
-        </is>
-      </c>
-      <c r="O19" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R19" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S19" s="83" t="n"/>
-    </row>
-    <row r="20" ht="104.4" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C20" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-20</t>
-        </is>
-      </c>
-      <c r="E20" s="89" t="inlineStr">
-        <is>
-          <t>사전점검 및 철도기술기준 검토</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G20" s="83" t="inlineStr">
-        <is>
-          <t>철도종합시험운행에 따른 기능 및 성능 사전검증과 철도종합시험운행의 목적 달성의 적합여부 판정</t>
-        </is>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>- 분야외 시설물 성능장치 점검
-- (1부)철도종합시험운행 시행지침 제6조(종합시험운행을 위한 사전점검)
-- 현장점검을 위한 계획 및 체크리스트 수립에 의하여 내 조직 가능한 항목에 대해 사전기재 및 결과 기재
-- (기준) 철도종합시험운행 시행지침 제8조(종합시험운행을 위한 사전점검)
-- 현장점검을 위한 계획 및 체크리스트를 사전에 준비하여 기한 내 조치가능한 점검항목 도출
-1) 철도시설물 시공상태 및 기능확인, 공종별시험 결과보고서 검토
-2) 철도시설의 기술기준 준수여부
-3) 관련 법령에 따른 외부기관의 검사완료 가능여부 확인
-4) 시설물검증시험 전까지 대상 철도시설물 완공가능 여부확인
-5) 철도시설의 안전성 분석결과 및 분석결과에 따른 안전대책 검토
-6) 종합시험운행(시설물검증시험·영업시운전) 시행에 필요한 사항확인 등</t>
-        </is>
-      </c>
-      <c r="I20" s="83" t="inlineStr">
-        <is>
-          <t>사전점검 결과표 / 철도안전성검토서</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>1) 사전점검(WBS 9000-1-20)을 위해 철도종합시험운행 시행지침 제6조/제8조 검토 수칙을 이행하라.
-2) 시설물 시공상태, 기술기준 준수 및 완공 가능 여부 사전점검 체크리스트를 완수하라.</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 시행지침 제6조/제8조에 따라 사전점검 체크리스트를 사전에 준비하십시오.
-2) 시설물 시공상태, 기술기준 준수 여부 및 공종별시험 결과보고서를 검토하십시오.</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>1) 철도종합시험운행 시행지침 제6조/제8조 사전점검 체크리스트를 수립하였는가?
-2) 철도시설물 시공상태, 기술기준 준수 및 안전성 분석 결과를 검토하였는가?</t>
-        </is>
-      </c>
-      <c r="O20" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R20" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S20" s="83" t="n"/>
-    </row>
-    <row r="21" ht="104.4" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C21" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-21</t>
-        </is>
-      </c>
-      <c r="E21" s="89" t="inlineStr">
-        <is>
-          <t>시설물 검증시험</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G21" s="83" t="inlineStr">
-        <is>
-          <t>시설물검증 노선에 환경에 철도종합시험운행 시행지침에 의거 철도노선 및 관계시설을 검증하여 안전성 확보 여부 판단</t>
-        </is>
-      </c>
-      <c r="H21" s="90" t="inlineStr">
-        <is>
-          <t>- 철도종합시험운행 시행지침상 검사사항 검증
-- 철도종합시험운행 시설물검증시험 점검항목 시행
-- 시설물 특성 및 규모에 따른 설계속도 또는 선로 최고운행속도 까지 증속하여 다음의 사항을 점검
-1) 신호시설물의 정상 동작상태
-2) 신호시설물의 안전상태
-3) 철도차량의 운행 적합성 적정여부
-4) 신호설비와 차량간 연계성 적정여부</t>
-        </is>
-      </c>
-      <c r="I21" s="83" t="inlineStr">
-        <is>
-          <t>시설물 검증시험 시험결과 및 승인원, 완료결과보고서</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>1) 시설물 검증(WBS 9000-1-21)을 위해 최고운행속도 증속 시운전을 시행하고 신호 정상동작을 검증하라.
-2) 신호설비와 차량 간 연계성 및 철도차량 운행 적합성 검증 결과표를 승인 완수하라.</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>1) 설계 최고운행속도까지 단계별 증속하여 신호시설물 정상 동작 및 안전성을 점검하십시오.
-2) 신호설비와 차량 간 연계 적정성 및 철도차량 운행 적합 여부를 서면 판정하십시오.</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>1) 설계 최고운행속도 증속 시운전 시 신호시설물 정상 동작을 확인하였는가?
-2) 신호설비와 차량 간 연계성 및 차량 운행 적합성을 검증하였는가?</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R21" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S21" s="83" t="n"/>
-    </row>
-    <row r="22" ht="104.4" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C22" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-22</t>
-        </is>
-      </c>
-      <c r="E22" s="89" t="inlineStr">
-        <is>
-          <t>영업 시운전</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>현장소장 및 발주처 / 공동감리단</t>
-        </is>
-      </c>
-      <c r="G22" s="83" t="inlineStr">
-        <is>
-          <t>영업 시운전에 의한 수송능력을 파악하고 최종 운영기관과 인터페이스 협의를 통해 시공의 안정성 확보 여부 및 검증</t>
-        </is>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>- 모의 영업 시나리오 기반 100회 정시 운행 성공률 99.8% 이상 확보
-- 영업운전과 동일한 조건으로 행사수송 수행 및 영업준비 수행
-- 철도안전관련계 체계 및 시운전수행 승인 등 관계 기관에 제출
-- 영업조건과 동일한 조건으로 열차운행을 위한 운전분야 및 영업분야 시행
-- 열차운행스케쥴 및 영업설비 점검
-- 승무원 노선숙지 등 업무숙달 훈련
-- 철도시설과 차량과의 인터페이스 최종 점검</t>
-        </is>
-      </c>
-      <c r="I22" s="83" t="inlineStr">
-        <is>
-          <t>영업 시운전 및 가동단계에서 운영지침서 및 최종 제출서(가동시험보고서)</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>1) 영업 시운전(WBS 9000-1-22)을 위해 모의 영업 시나리오 기반 100회 정시 운행 성공률(≥99.8%)을 달성하라.
-2) 영업운전과 동일 조건 열차스케줄 및 승무원 노선숙지 등 최종 영업준비를 완수하라.</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>1) 모의 영업 시나리오에 따라 100회 정시 운행 성공률(≥99.8%) 이상을 확보하십시오.
-2) 영업운전과 동일한 조건으로 열차운행 스케줄 및 영업설비 최종 점검을 완료하십시오.</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>1) 모의 영업 시나리오 기반 100회 정시 운행 성공률(≥99.8%)을 달성하였는가?
-2) 영업운전 동일 조건 행사수송 및 승무원 노선숙지 훈련을 완수하였는가?</t>
-        </is>
-      </c>
-      <c r="O22" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="n"/>
-      <c r="Q22" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R22" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S22" s="83" t="n"/>
-    </row>
-    <row r="23" ht="104.4" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>9000-1</t>
-        </is>
-      </c>
-      <c r="C23" s="83" t="inlineStr">
-        <is>
-          <t>신호분야</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>9000-1-13</t>
-        </is>
-      </c>
-      <c r="E23" s="89" t="inlineStr">
-        <is>
-          <t>유지관리 설치</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="G23" s="83" t="inlineStr">
-        <is>
-          <t>관제 관제실의 장비체계 배치 및 설치</t>
-        </is>
-      </c>
-      <c r="H23" s="83" t="inlineStr">
-        <is>
-          <t>- 유지 및 보수용 상세 공사 설계배치 확인
-- 현장조성 및 유지관리 지침서 이행 여부</t>
-        </is>
-      </c>
-      <c r="I23" s="83" t="inlineStr">
-        <is>
-          <t>유지관리 지침 및 관리 이행 보고서</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>1) 유지관리 설치(WBS 9000-1-13)를 위해 관제실 유지보수용 장비 배치 및 상세 공사 설계를 확인하라.
-2) 현장조성 및 유지관리 지침서 이행 여부를 확인하고 관제 MMI 보수를 완수하라.</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 표준서 열기 📄</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제실 유지 및 보수용 상세 공사 설계 배치를 확인하고 장비를 시공하십시오.
-2) 현장 조성 및 유지관리 지침서 이행 여부를 점검하여 서면 보고하십시오.</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 수행지침 열기 📄</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>1) 관제실 유지보수용 상세 공사 설계 배치를 확인하였는가?
-2) 현장조성 및 유지관리 지침서 이행 여부를 점검 확인하였는가?</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="inlineStr">
-        <is>
-          <t>👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="n"/>
-      <c r="Q23" s="83" t="inlineStr">
-        <is>
-          <t>● 관련분야 설계기준서 준수</t>
-        </is>
-      </c>
-      <c r="R23" s="85" t="inlineStr">
-        <is>
-          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
-        </is>
-      </c>
-      <c r="S23" s="83" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
-  </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="38" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -46,7 +46,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -273,6 +273,13 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000284C7"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="9"/>
       <u val="single"/>
     </font>
@@ -689,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1148,6 +1155,30 @@
     <xf numFmtId="0" fontId="25" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2601,7 +2632,7 @@
 2) 철도 표준 자재(KRS) 및 분산형 CBI 용량, 선로전환기(4.5~6.0kN) 적정성을 검증하고 승인 보고서를 완수하라.</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -2612,7 +2643,7 @@
 2) 분산형 CBI 및 선로전환기 용량의 현장 시공성 및 원가 Risk를 철저히 검토하여 승인을 획득하십시오.</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -2623,7 +2654,7 @@
 2) 철도 표준 자재(KRS) 규격 및 매립 선로전환기 전환력(4.5~6.0kN) 기준을 적격 확인하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="17" t="inlineStr">
+      <c r="O2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -2709,7 +2740,7 @@
 2) 외주 수급, 신기술자재 확인, 내역 누락 방지 조치 및 SIL 인증보유 적격 업체 Pool을 확정하라.</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -2720,7 +2751,7 @@
 2) 공정계획, 안전성 SIL 인증, 무상 A/S 및 철도안전법 준수 자재 투입 계획을 사전에 확인하십시오.</t>
         </is>
       </c>
-      <c r="M3" s="53" t="inlineStr">
+      <c r="M3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -2731,7 +2762,7 @@
 2) 적격 업체 Pool 검토 및 내역 누락 방지 조치, SIL 인증 보유 여부를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -2813,7 +2844,7 @@
 2) 궤도 시공 전 블록아웃, 배수로, 선로전환기, 차축검지기 설치 I/F 항목을 사전 확정하라.</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -2824,7 +2855,7 @@
 2) 궤도 시공 전 블록아웃 및 선로전환기 설치 I/F에 대해 각 분야 담당자와의 협의록을 작성하십시오.</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
+      <c r="M4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -2835,7 +2866,7 @@
 2) 궤도 시공 전 블록아웃 및 차축검지기 설치 I/F 사전 대책을 수립하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="17" t="inlineStr">
+      <c r="O4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -2911,7 +2942,7 @@
 2) 궤도 시공 전 블록아웃, 배수로, 융설장치, 차축검지기 설치 I/F 승인서를 완수하라.</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -2922,7 +2953,7 @@
 2) 차축검지기 및 융설장치 체결 부위의 치수 적정성을 서면으로 확인하십시오.</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr">
+      <c r="M5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -2933,7 +2964,7 @@
 2) 차량기지 및 본선 선로전환기/차축검지기 체결 인터페이스를 조율하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
+      <c r="O5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3004,7 +3035,7 @@
 2) 도심 매립 궤도용 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 설치 조건 및 유관기관 피드백을 반영하라.</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="K6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3015,7 +3046,7 @@
 2) 도로 교차로 노면 매립 궤도 시공계획과 선로전환기 설치 위치 적정성을 확인하십시오.</t>
         </is>
       </c>
-      <c r="M6" s="53" t="inlineStr">
+      <c r="M6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3026,7 +3057,7 @@
 2) 노면 매립형 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 시공조건을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3102,7 +3133,7 @@
 2) 배관배선 인입구, 구조물 간섭 및 궤도 시공 전 설치 항목을 개시 전 차단하라.</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3113,7 +3144,7 @@
 2) 궤도 시공 전 블록아웃 및 케이블 인입 배관의 간섭 여부를 정밀 확인하십시오.</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="M7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3124,7 +3155,7 @@
 2) 케이블 인입 배관 및 궤도 블록아웃 간섭을 사전 제거하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3192,7 +3223,7 @@
 2) 제조사 자체 시험 성적서, KRS 표준 규격 및 제작도서 승인 서명을 완수하라.</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3203,7 +3234,7 @@
 2) 제작도서 승인 서명 및 현장 투입 전 성능보증 기능을 검증하십시오.</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="M8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3214,7 +3245,7 @@
 2) 제조사 공장검수 성적서 및 제작도서 승인 서명을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3283,7 +3314,7 @@
 2) 철도관제를 위한 관제사 조작반 MMI 및 예비관제 1:1 실시간 DB 동기화를 검증하라.</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3294,7 +3325,7 @@
 2) 관제센터 MMI 화면 및 조작반 정보의 실시간 동기화 상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="M9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3305,7 +3336,7 @@
 2) 철도관제를 위한 관제사 조작반 MMI 표시 정보를 사전 검토하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3375,7 +3406,7 @@
 2) 현장 여건 및 궤도 시공계획 맞춤형 투입 schedule 작성 및 수급 조정을 완수하라.</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3386,7 +3417,7 @@
 2) 궤도 시공계획과 연계된 자재 반입 및 작업원 투입 스케줄을 조정하십시오.</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr">
+      <c r="M10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3397,7 +3428,7 @@
 2) 궤도 시공계획 연계 투입 스케줄 감리단 승인을 획득하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3465,7 +3496,7 @@
 2) 작업원 특별 안전교육 및 위험성평가 이행 확인서를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3476,7 +3507,7 @@
 2) 신호 공사 작업원에 대한 특별 안전교육 및 보호구 착용 상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M11" s="53" t="inlineStr">
+      <c r="M11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3487,7 +3518,7 @@
 2) 신호 공사 작업원 특별 안전교육 실시 기록을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3558,7 +3589,7 @@
 2) 반입 자재의 KS/KRS 규격 시험성적서 대조 검수 및 품질 보증을 완수하라.</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3569,7 +3600,7 @@
 2) 자재 현지 반입 시 사양서, 시험성적서 및 표준규격 부합 여부를 인수 검수하십시오.</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr">
+      <c r="M12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3580,7 +3611,7 @@
 2) 반입 자재 사양 확인(KS, KRS 표준규격) 및 수량 검수를 시행하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="O12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3651,7 +3682,7 @@
 2) 현장 신호기, 선로전환기 기초 볼트 체결 및 도면 일치 여부를 정밀 시공하라.</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3662,7 +3693,7 @@
 2) 현장 설치 설비의 규격, 수량 및 도면 일치 여부를 정밀 측정하여 시공하십시오.</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3673,7 +3704,7 @@
 2) 현장 신호기/선로전환기 기초 볼트 체결 및 규격 일치 여부를 시공하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="O13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3749,7 +3780,7 @@
 2) 신호기, 선로전환기, 전원장치, 차축검지기 개별 ITP/ITC 시험 결과서를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="K14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3760,7 +3791,7 @@
 2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 지상신호장치 단위시험 결과서를 작성하십시오.</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr">
+      <c r="M14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3771,7 +3802,7 @@
 2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 개별 단독 현황시험을 수행하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="O14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3847,7 +3878,7 @@
 2) 차상-지상 무선(LTE-R) 도로-트램 우선신호 연계 시험 결과표를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3858,7 +3889,7 @@
 2) 지상-차상 인터페이스 및 도로/트램 우선신호 무선 연계시험 결과표를 작성하십시오.</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3869,7 +3900,7 @@
 2) 지상-차상 인터페이스 및 도로-트램 우선신호 연계 시험을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -3957,7 +3988,7 @@
 2) 신호기계실 전원 2중화 절체 시험 및 관제 CTC 서버 정상 동작 시험을 완수하라.</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -3968,7 +3999,7 @@
 2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 정상 동작상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -3979,7 +4010,7 @@
 2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 동작을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4061,7 +4092,7 @@
 2) 건축한계/차량한계 이격 정밀 측정 및 전원장치(UPS) 성능을 최종 검증하라.</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4072,7 +4103,7 @@
 2) 건축한계(폭 3.1m/높이 3.8m) 이격 측정 및 기계실 UPS/방재예방 설비를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4083,7 +4114,7 @@
 2) 신호기와 건축물 간 건축한계 정밀 측정 및 방재설비를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="O17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4165,7 +4196,7 @@
 2) 속도/제동 테스트, 차상-지상 연계동작 및 열차제어 시스템 기능시험을 완수하라.</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4176,7 +4207,7 @@
 2) 차상신호장치 지·차상 연계동작시험 및 열차제어 시스템 기능시험을 시행하십시오.</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4187,7 +4218,7 @@
 2) 차상-지상 연계동작시험 및 차량-신호-통신 I/F 시험을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="O18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4263,7 +4294,7 @@
 2) 장비 제작사에 의한 CTC/CBI/현장설비 조작·정비 기술 교육 완료 이수증을 승인하라.</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4274,7 +4305,7 @@
 2) CTC 서버, 전자연동장치, 현장 신호기/선로전환기 교육 이수 현황을 확인하십시오.</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4285,7 +4316,7 @@
 2) 장비 제작사에 의한 CTC/CBI/현장설비 조작교육을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="O19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4365,7 +4396,7 @@
 2) 시설물 시공상태, 기술기준 준수 및 완공 가능 여부 사전점검 체크리스트를 완수하라.</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4376,7 +4407,7 @@
 2) 시설물 시공상태, 기술기준 준수 여부 및 공종별시험 결과보고서를 검토하십시오.</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr">
+      <c r="M20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4387,7 +4418,7 @@
 2) 철도시설물 시공상태, 기술기준 준수 및 안전성 분석 결과를 검토하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="O20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4463,7 +4494,7 @@
 2) 신호설비와 차량 간 연계성 및 철도차량 운행 적합성 검증 결과표를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4474,7 +4505,7 @@
 2) 신호설비와 차량 간 연계 적정성 및 철도차량 운행 적합 여부를 서면 판정하십시오.</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="M21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4485,7 +4516,7 @@
 2) 신호설비와 차량 간 연계성 및 차량 운행 적합성을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="O21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4561,7 +4592,7 @@
 2) 영업운전과 동일 조건 열차스케줄 및 승무원 노선숙지 등 최종 영업준비를 완수하라.</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="K22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4572,7 +4603,7 @@
 2) 영업운전과 동일한 조건으로 열차운행 스케줄 및 영업설비 최종 점검을 완료하십시오.</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr">
+      <c r="M22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4583,7 +4614,7 @@
 2) 영업운전 동일 조건 행사수송 및 승무원 노선숙지 훈련을 완수하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="O22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4654,7 +4685,7 @@
 2) 현장조성 및 유지관리 지침서 이행 여부를 확인하고 관제 MMI 보수를 완수하라.</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4665,7 +4696,7 @@
 2) 현장 조성 및 유지관리 지침서 이행 여부를 점검하여 서면 보고하십시오.</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr">
+      <c r="M23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4676,7 +4707,7 @@
 2) 현장조성 및 유지관리 지침서 이행 여부를 점검 확인하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="O23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -4956,7 +4987,7 @@
 2) LTE-R 무선망, 8대 이종 통신시스템, 타공종 간섭 및 리스크 헷지·기회반영 설계변경 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K2" s="78" t="inlineStr">
+      <c r="K2" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -4967,7 +4998,7 @@
 2) 시공성 및 설계변경: 현장 지장물 실측 조사, 타공종 3D 간섭 조정, 공법/안전 검토 및 현장 전직원+본사 동시 검토 회의로 설계변경 수립</t>
         </is>
       </c>
-      <c r="M2" s="78" t="inlineStr">
+      <c r="M2" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -4978,7 +5009,7 @@
 2) LTE-R 무선망, 타공종 3D 간섭조정, 8대 이종 통신시스템, 관제연동 적정성 검토 및 현장전직원+본사 동시 검토 승인을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="67" t="inlineStr">
+      <c r="O2" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5058,7 +5089,7 @@
 2) 주요 통신 자재 납품 수급 계획 및 시공 적격성 평가를 반영한 발주전략 KOM 보고서 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K3" s="78" t="inlineStr">
+      <c r="K3" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5069,7 +5100,7 @@
 2) 전략 수립 및 승인: 리스크 헷지형 계약 조건 도출 및 현장소장/공무팀 주관 발주전략 KOM 보고서 확정</t>
         </is>
       </c>
-      <c r="M3" s="78" t="inlineStr">
+      <c r="M3" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5080,7 +5111,7 @@
 2) 주요 자재 납품 수급 계획 및 적격 시공업체 평가 기준을 마련하여 발주전략 KOM 승인을 완수하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="67" t="inlineStr">
+      <c r="O3" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5150,7 +5181,7 @@
 2) 타공종 구조체 타설 전 통신 매립 배관 위치 검증 및 인터페이스 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K4" s="67" t="inlineStr">
+      <c r="K4" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5161,7 +5192,7 @@
 2) 협의 수행 및 승인: 타공종 구조체 콘크리트 타설 전 통신 배관 매립 위치 현장 확인 및 3D 간섭 조정 협의록 확정</t>
         </is>
       </c>
-      <c r="M4" s="67" t="inlineStr">
+      <c r="M4" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5172,7 +5203,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="78" t="inlineStr">
+      <c r="O4" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5247,7 +5278,7 @@
 2) 타공종 간 전자기 적합성(EMC/EMI), 전력 케이블 유도장해 차폐 및 서지 보호 표준 적용</t>
         </is>
       </c>
-      <c r="K5" s="67" t="inlineStr">
+      <c r="K5" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5258,7 +5289,7 @@
 2) 3D/BIM 간섭조정 및 승인: 이종 시스템 간 인터페이스 핀 맵, 데이터 포맷 교차 검증 및 시스템 합동 인터페이스 협의록 작성</t>
         </is>
       </c>
-      <c r="M5" s="67" t="inlineStr">
+      <c r="M5" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5269,7 +5300,7 @@
 2) KEC 점유율[KEC 33%] 전선관 내부 단면적 점유율 33% 이하 및 ELP ø150mm×6개×2조 배관을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="78" t="inlineStr">
+      <c r="O5" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5339,7 +5370,7 @@
 2) 제작사 간 데이터 입출력 포맷 및 연동 케이블 사양서 확정 협의록 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K6" s="78" t="inlineStr">
+      <c r="K6" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5350,7 +5381,7 @@
 2) 연동 시험 수칙 수립: 제작사 간 신호 연동 핀 배열 확정 및 상호 연동 인터페이스 사양서 감리 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M6" s="78" t="inlineStr">
+      <c r="M6" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5361,7 +5392,7 @@
 2) 전원 잭 확인[코드 잭 준비] 각 장비에 220V 코드를 꽂을지 48V 전기를 줄지 전원 잭을 사전에 확인하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="78" t="inlineStr">
+      <c r="O6" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5433,7 +5464,7 @@
 2) 관제 서버, 네트워크 스위치 및 운영사 통합 수선 체계 부합성 확인 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K7" s="67" t="inlineStr">
+      <c r="K7" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5444,7 +5475,7 @@
 2) 관제 인터페이스 승인: 관제 서버-현장 장치 간 제어 데이터 송수신 시험 절차 수립 및 운영사 합동 검토서 확정</t>
         </is>
       </c>
-      <c r="M7" s="78" t="inlineStr">
+      <c r="M7" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5455,7 +5486,7 @@
 2) 4K CCTV 65개[명당 자리] 교차로 4K CCTV 카메라 65개소가 사각지대 없이 보이도록 명당 자리를 배치하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="78" t="inlineStr">
+      <c r="O7" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5525,7 +5556,7 @@
 2) 품질시험계획서 수립 및 발주처 승인 품질 기준 준수서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K8" s="67" t="inlineStr">
+      <c r="K8" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5536,7 +5567,7 @@
 2) 품질 관리 수립: 현장 품질시험계획서 수립, 불합격 자재 반출 절차 확립 및 발주처 승인 품질 수칙 이행</t>
         </is>
       </c>
-      <c r="M8" s="67" t="inlineStr">
+      <c r="M8" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5547,7 +5578,7 @@
 2) [Hold Point] 감리원 현장 직접 입회 검측 항목(Hold Point)을 사전 분류 지정하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="67" t="inlineStr">
+      <c r="O8" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5617,7 +5648,7 @@
 2) 예정공정표 대비 인원·장비 투입 수급 타당성 및 안전 수칙 준수 검토 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K9" s="78" t="inlineStr">
+      <c r="K9" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5628,7 +5659,7 @@
 2) 공정 수급 승인: 예정공정표 대비 적정 투입 인원 산출, 작업 안전 구역 확보 및 현장소장 투입 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M9" s="67" t="inlineStr">
+      <c r="M9" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5639,7 +5670,7 @@
 2) [인력 자격] 통신 공종별 특급/고급 기술자 자격증 및 현장 배치 계획을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="78" t="inlineStr">
+      <c r="O9" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5718,7 +5749,7 @@
 2) 간섭사항 사전 도출 및 공종 간 공정 마일스톤 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K10" s="67" t="inlineStr">
+      <c r="K10" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5729,7 +5760,7 @@
 2) 간섭 리스크 해소: 공사 착수 전 분야별 간섭 위험 요소를 발굴하여 헷지 방안 수립 및 Big Room 회의록 최종 승인</t>
         </is>
       </c>
-      <c r="M10" s="67" t="inlineStr">
+      <c r="M10" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5740,7 +5771,7 @@
 2) [인터페이스] 노반(궤도)/전기/신호/기계/차량 5대 공종 간 관통 경로 및 간섭점을 사전 도출 검출하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="67" t="inlineStr">
+      <c r="O10" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5811,7 +5842,7 @@
 2) 감리단 및 발주처 승인을 위한 제작사양서 승인 신청서 및 공학적 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K11" s="67" t="inlineStr">
+      <c r="K11" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5822,7 +5853,7 @@
 2) 공학적 승인 신청: 발주처 입찰시방과 제작사양서 1:1 대조 검증 및 감리단 공학적 승인 제출 절차 수행</t>
         </is>
       </c>
-      <c r="M11" s="67" t="inlineStr">
+      <c r="M11" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5833,7 +5864,7 @@
 2) [사양서 정의] 실제 제작·설치될 통신설비의 전기적·기계적 세부 규격 및 제작도면(Shop Drawing)을 작성하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="67" t="inlineStr">
+      <c r="O11" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -5906,7 +5937,7 @@
 2) 통신설비 설치 공법 타당성 및 감리단 시공계획서 승인 제출 표준 적용</t>
         </is>
       </c>
-      <c r="K12" s="67" t="inlineStr">
+      <c r="K12" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -5917,7 +5948,7 @@
 2) 감리 승인 및 이행: 시공상세도(Shop Drawing) 첨부, 현장 안전 위험성 평가 실시 및 감리단 시공계획서 승인 완료</t>
         </is>
       </c>
-      <c r="M12" s="67" t="inlineStr">
+      <c r="M12" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -5928,7 +5959,7 @@
 2) [안전 대책] 통신기계실 DC -48V 감전 방지 및 정거장 고소작업 시 안전대/2인1조 작업 대책을 수립하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="67" t="inlineStr">
+      <c r="O12" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6001,7 +6032,7 @@
 2) 성능보증이 가능한 복수 자재공급원 승인 서류 수립 및 감리 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K13" s="67" t="inlineStr">
+      <c r="K13" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6012,7 +6043,7 @@
 2) 자재 승인 및 관리: 복수 공급원 비교 검토서 작성, 불량 자재 차단 헷지 및 감리단 자재공급원 승인 획득</t>
         </is>
       </c>
-      <c r="M13" s="67" t="inlineStr">
+      <c r="M13" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6023,7 +6054,7 @@
 2) [사양 대조] 설계도서 수치(KCS 31 10 00)와 자재 카탈로그 규격 간 1:1 대조표를 정확히 작성하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="67" t="inlineStr">
+      <c r="O13" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6098,7 +6129,7 @@
 2) 공장 수검 검사, 품질 성능 시험성적서 확인 및 공장검사 합격증명서 발급 표준 적용</t>
         </is>
       </c>
-      <c r="K14" s="67" t="inlineStr">
+      <c r="K14" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6109,7 +6140,7 @@
 2) 입회 검사 실시: 전원 인입, 기능 시험, 방수/내열 공인시험 실측 확인 및 FAT 공장검사 합격증명서 획득</t>
         </is>
       </c>
-      <c r="M14" s="67" t="inlineStr">
+      <c r="M14" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6120,7 +6151,7 @@
 2) [ITP 승인] 감리 승인된 ITP 절차서와 절연저항계(Megger), OTDR의 교정 유효기간 증명서를 사전 확인하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="67" t="inlineStr">
+      <c r="O14" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6192,7 +6223,7 @@
 2) 바닥 엑세스플로어, 방화 구획 및 기초 구조체 인수인계 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K15" s="67" t="inlineStr">
+      <c r="K15" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6203,7 +6234,7 @@
 2) 인수인계 승인: 미비 사항 현장 보완 조치 요구 및 통신 시공 적격 선행 공정 인수인계 확인서 최종 승인</t>
         </is>
       </c>
-      <c r="M15" s="78" t="inlineStr">
+      <c r="M15" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6214,7 +6245,7 @@
 2) 토목, 건축, 통신 현장 담당자 3자 공조 체계를 구성하고 현장 합동 점검표, Mandrel 도통시험기 및 레이저 레벨기를 사전 준비하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="67" t="inlineStr">
+      <c r="O15" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6286,7 +6317,7 @@
 2) 장비 반입 허가서 작성 및 안전 교육 이수 수료증 관리 표준 적용</t>
         </is>
       </c>
-      <c r="K16" s="78" t="inlineStr">
+      <c r="K16" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6297,7 +6328,7 @@
 2) 안전 교육 이수: 통신 시공 작업자 대상 특별안전보건교육, 보호구 착용 점검 및 안전 교육 이수 수료 관리</t>
         </is>
       </c>
-      <c r="M16" s="67" t="inlineStr">
+      <c r="M16" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6308,7 +6339,7 @@
 2) 토목/건축 등 타분야 양중 작업 간섭 여부를 사전 협의하고 양중 시간대를 분리 조율하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="67" t="inlineStr">
+      <c r="O16" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6380,7 +6411,7 @@
 2) 자재검수 요청서 작성 및 감리 입회 검수 합격 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K17" s="67" t="inlineStr">
+      <c r="K17" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6391,7 +6422,7 @@
 2) 자재검수 보고: 감리 입회 자재 검수 실시, 자재검수 요청서 결재 및 현장 통신 자재 창고 입고 관리</t>
         </is>
       </c>
-      <c r="M17" s="67" t="inlineStr">
+      <c r="M17" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6402,7 +6433,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="78" t="inlineStr">
+      <c r="O17" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6476,7 +6507,7 @@
 2) 케이블 성단, OTDR 접속 및 설비 고정 상태 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K18" s="67" t="inlineStr">
+      <c r="K18" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6487,7 +6518,7 @@
 2) 접속 및 검측: OTDR 접속 손실(≤0.05dB) 측정, 랙 전원 인입 배선 정리 및 설비 고정 상태 감리 검측</t>
         </is>
       </c>
-      <c r="M18" s="67" t="inlineStr">
+      <c r="M18" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6498,7 +6529,7 @@
 2) 72-Core 광케이블 융착 접속 트레이 정돈 및 접속 손실 샘플 시공 승인을 획득하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="78" t="inlineStr">
+      <c r="O18" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6569,7 +6600,7 @@
 2) 관제 시스템 전원 인입, 배선 정리 및 관제 환경 설치 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K19" s="67" t="inlineStr">
+      <c r="K19" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6580,7 +6611,7 @@
 2) 전원 및 계통 검측: 관제 전원 분배기 전원 인입, 이중화 네트워크 케이블 성단 및 관제실 설치 상태 확인</t>
         </is>
       </c>
-      <c r="M19" s="67" t="inlineStr">
+      <c r="M19" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6591,7 +6622,7 @@
 2) 멀티 디스플레이 패널 간 베젤 이격 단차(≤0.5mm) 미세 조율 및 방진 가스켓 부착을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="67" t="inlineStr">
+      <c r="O19" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6661,7 +6692,7 @@
 2) 설비별 단위시험 절차서 준수 및 단독 기능 시험성적서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K20" s="67" t="inlineStr">
+      <c r="K20" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6672,7 +6703,7 @@
 2) 단위성적서 작성: 단위시험 절차서 항목별 성능 측정, 불합격 항목 보완 조치 및 단위시험 성과표 확정</t>
         </is>
       </c>
-      <c r="M20" s="67" t="inlineStr">
+      <c r="M20" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6683,7 +6714,7 @@
 2) RF 파워메터로 무선장치(RU) 송신 출력을 계측하여 표준 규격(43dBm ±0.5dB) 이내임을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="78" t="inlineStr">
+      <c r="O20" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6755,7 +6786,7 @@
 2) 통합시험 절차서 준수 및 이종 통신 설비 간 상호 연동성 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K21" s="67" t="inlineStr">
+      <c r="K21" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6766,7 +6797,7 @@
 2) 통합 성과 확인: 관제-현장 장치 간 제어 응답속도 검측, 통합 시험 성과표 작성 및 감리 승인 완료</t>
         </is>
       </c>
-      <c r="M21" s="78" t="inlineStr">
+      <c r="M21" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6777,7 +6808,7 @@
 2) 관제 콘솔에서 PIS 문구 송출 명령 전송 시 현장 안내표시기 반응 지연 시간(≤0.5초 이내)을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="67" t="inlineStr">
+      <c r="O21" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6847,7 +6878,7 @@
 2) 공종별 시험 항목 검측, 무선 전계강도 측정 및 시험성적서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K22" s="67" t="inlineStr">
+      <c r="K22" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6858,7 +6889,7 @@
 2) 공종 시험 승인: 무선 전계강도 측정 성과표 및 공종별 시운전 시험 결과 보고서 제출 및 감리 승인</t>
         </is>
       </c>
-      <c r="M22" s="67" t="inlineStr">
+      <c r="M22" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6869,7 +6900,7 @@
 2) 광케이블 융착 접속점 접속 손실 수치가 시방 기준(≤0.1dB/접속점 이하)을 통과함을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="78" t="inlineStr">
+      <c r="O22" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -6943,7 +6974,7 @@
 2) 차량 투입 대비 통신 무무선 연동 안전 상태 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K23" s="67" t="inlineStr">
+      <c r="K23" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -6954,7 +6985,7 @@
 2) 투입 안전 승인: 차량 투입 시 무선 통신 끊김 예방 점검 및 차량 투입 전 통신 안전 확인서 작성</t>
         </is>
       </c>
-      <c r="M23" s="67" t="inlineStr">
+      <c r="M23" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -6965,7 +6996,7 @@
 2) 궤도 주변 통신 케이블 트레이 및 광점퍼 선로 묶음이 건축한계 이내로 처지거나 돌출되지 않음을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="67" t="inlineStr">
+      <c r="O23" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7036,7 +7067,7 @@
 2) 주행 중 통신 끊김 여부 및 차상-지상 간 통신 품질 성과표 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K24" s="67" t="inlineStr">
+      <c r="K24" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7047,7 +7078,7 @@
 2) 주행 통신 검측: 차상-지상 간 CCTV 영상 전송 및 관제 데이터 무선 통신 품질 성과표 최종 확정</t>
         </is>
       </c>
-      <c r="M24" s="67" t="inlineStr">
+      <c r="M24" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7058,7 +7089,7 @@
 2) 주행 중 LTE-R 기지국 간 이동 시 핸드오버 성공률 100% 및 음성 무선 통화 끊김 0건을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O24" s="67" t="inlineStr">
+      <c r="O24" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7129,7 +7160,7 @@
 2) 교육 교재 작성, 시스템 운용/장해 조치 실습 및 교육 이수 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K25" s="67" t="inlineStr">
+      <c r="K25" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7140,7 +7171,7 @@
 2) 교육 이수 확정: 현장 실습 교육 수행, 질문/답변 점검 및 운영자 교육 참석 이수 확인서 최종 작성</t>
         </is>
       </c>
-      <c r="M25" s="67" t="inlineStr">
+      <c r="M25" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7151,7 +7182,7 @@
 2) 주요 장비 장애 시 대응할 수 있는 계통별 긴급 비상 조치 매뉴얼 교재를 편찬하였는가?</t>
         </is>
       </c>
-      <c r="O25" s="67" t="inlineStr">
+      <c r="O25" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7223,7 +7254,7 @@
 2) 사전점검 결과 보고서 작성 및 한국교통안전공단 제출 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K26" s="67" t="inlineStr">
+      <c r="K26" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7234,7 +7265,7 @@
 2) 점검 결과 승인: 기술기준 부합 여부 사전 검증, 지적사항 조치 완료 및 한국교통안전공단 사전점검 보고서 제출</t>
         </is>
       </c>
-      <c r="M26" s="67" t="inlineStr">
+      <c r="M26" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7245,7 +7276,7 @@
 2) 발주처, 운영기관, 책임감리단 및 현장소장이 포함된 3자 합동 사전점검반을 조직하였는가?</t>
         </is>
       </c>
-      <c r="O26" s="67" t="inlineStr">
+      <c r="O26" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7318,7 +7349,7 @@
 2) LTE-R 무선 품질, 관제 데이터 전송률 및 시설물검증 합격 판정 표준 적용</t>
         </is>
       </c>
-      <c r="K27" s="67" t="inlineStr">
+      <c r="K27" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7329,7 +7360,7 @@
 2) 검증 결과 확정: LTE-R 무선망 수신강도, 데이터 전송 지연시간 실측 및 시설물검증시험 합격 판정</t>
         </is>
       </c>
-      <c r="M27" s="67" t="inlineStr">
+      <c r="M27" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7340,7 +7371,7 @@
 2) 전문기관인 한국교통안전공단으로부터 시설물검증시험계획 적격 승인을 수령하였는가?</t>
         </is>
       </c>
-      <c r="O27" s="67" t="inlineStr">
+      <c r="O27" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7415,7 +7446,7 @@
 2) 영업시운전 기간 중 통신 장애 0건 달성 및 시운전 완료 보고서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K28" s="67" t="inlineStr">
+      <c r="K28" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7426,7 +7457,7 @@
 2) 시운전 준공 확정: 영업시운전 기간 중 통신 장해 0건 달성 및 영업시운전 종합 결과 보고서 확정</t>
         </is>
       </c>
-      <c r="M28" s="78" t="inlineStr">
+      <c r="M28" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7437,7 +7468,7 @@
 2) 전 정거장 행선안내게시기(PIS) 도착 시각 및 열치 위치 안내 오송출 0건을 달성하였는가?</t>
         </is>
       </c>
-      <c r="O28" s="67" t="inlineStr">
+      <c r="O28" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7507,7 +7538,7 @@
 2) 관할 지자체(화성시 등) 제출 및 설치신고 수리증 발급 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K29" s="67" t="inlineStr">
+      <c r="K29" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7518,7 +7549,7 @@
 2) 관할 관청 수리: 관할 지자체(화성시 등) 제출, 현장 서류 검토 수검 및 설치신고 수리증 발급 획득</t>
         </is>
       </c>
-      <c r="M29" s="67" t="inlineStr">
+      <c r="M29" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7529,7 +7560,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O29" s="67" t="inlineStr">
+      <c r="O29" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7599,7 +7630,7 @@
 2) KCA(한국방송통신전파진흥원) 제출 및 무선국 개설허가서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K30" s="67" t="inlineStr">
+      <c r="K30" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7610,7 +7641,7 @@
 2) 무선국 허가 획득: KCA(한국방송통신전파진흥원) 서류 심사 수검 및 무선국 개설허가서 최종 발급</t>
         </is>
       </c>
-      <c r="M30" s="67" t="inlineStr">
+      <c r="M30" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7621,7 +7652,7 @@
 2) 본선 지상 기지국 안테나 설치 위치, 높이, 이득(dBi) 및 지향각 제원을 조사하였는가?</t>
         </is>
       </c>
-      <c r="O30" s="67" t="inlineStr">
+      <c r="O30" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7691,7 +7722,7 @@
 2) 국가정보원/KISA 보안 적합성 검증 승인서 및 상호연동 시험 합격 표준 적용</t>
         </is>
       </c>
-      <c r="K31" s="67" t="inlineStr">
+      <c r="K31" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7702,7 +7733,7 @@
 2) 보안 승인 획득: KISA/국가정보원 보안 적합성 검증 수검 및 상호운용성 검증 합격 승인서 획득</t>
         </is>
       </c>
-      <c r="M31" s="67" t="inlineStr">
+      <c r="M31" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7713,7 +7744,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O31" s="67" t="inlineStr">
+      <c r="O31" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7783,7 +7814,7 @@
 2) 관할 지자체 현장 검측 수검 및 정보통신 사용전검사 필증 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K32" s="67" t="inlineStr">
+      <c r="K32" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7794,7 +7825,7 @@
 2) 필증 발급 획득: 관할 지자체 정보통신 검측 공무원 현장 실측 수검 및 정보통신 사용전검사 필증 획득</t>
         </is>
       </c>
-      <c r="M32" s="67" t="inlineStr">
+      <c r="M32" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7805,7 +7836,7 @@
 2) 정거장 승강장 및 관제동 배관 입상부 배관 씰링 및 네임택 표기 상태를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O32" s="67" t="inlineStr">
+      <c r="O32" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7875,7 +7906,7 @@
 2) 무선 전계강도 및 준공 상태 검사 합격 후 무선국 준공검사 합격증명서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K33" s="67" t="inlineStr">
+      <c r="K33" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7886,7 +7917,7 @@
 2) 합격 증명 획득: 준공 실측 합격 판정 수검 및 KCA 무선국 준공검사 합격증명서 최종 발급 획득</t>
         </is>
       </c>
-      <c r="M33" s="67" t="inlineStr">
+      <c r="M33" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7897,7 +7928,7 @@
 2) 개설허가서 사본, 기지국 시공 내역서 및 안테나 제원표 구비를 완료하였는가?</t>
         </is>
       </c>
-      <c r="O33" s="67" t="inlineStr">
+      <c r="O33" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8204,7 +8235,7 @@
           <t>"전기공사업법, 전기사업법, 한국전기설비규정(KEC), 도로법(점용허가) 및 산업안전보건법 준수 여부를 1:1 검토한다."</t>
         </is>
       </c>
-      <c r="K2" s="72" t="inlineStr">
+      <c r="K2" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8214,7 +8245,7 @@
           <t>본 지침서는 동탄트램 전기분야 사업 착공 전설계도서의 기술적·법적 적정성 검토 방법과현장 여건, 타공종 간섭, 공법·장비 시공성(Constructability) 검토 절차를 명확히 제시하여, 시공 위험 요소는 사전에 헷지(H...</t>
         </is>
       </c>
-      <c r="M2" s="72" t="inlineStr">
+      <c r="M2" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8224,7 +8255,7 @@
           <t>본 체크리스트는 철도설계기준(KDS 47 00 00) 및 전기사업법에 의거하여,전기 분야 전반(송변전, 전력, 전차선, 배전, 접지, 인허가 등)에 대한 핵심 설계 적정성을 점검하고, 리스크(Risk) 헷지 및 기회(Oppo...</t>
         </is>
       </c>
-      <c r="O2" s="70" t="inlineStr">
+      <c r="O2" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8296,7 +8327,7 @@
           <t>공정표 대비 노면전차 특수자재(전차선 강성가선, 변압기 등)의 공장 제작/조달 Lead Time을 사전 반영함.</t>
         </is>
       </c>
-      <c r="K3" s="72" t="inlineStr">
+      <c r="K3" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8306,7 +8337,7 @@
           <t>본 지침서는 동탄트램 노면전차설비 공사 발주 전설계 및 현장 여건을 정밀 파악하고 8대 현실조건(자재 제작 Lead Time, 철도/경전철 시공 실적 Pool, 예비품, 시공중/후 운전 및 교육지원, 현장 자재창고 임대료, ...</t>
         </is>
       </c>
-      <c r="M3" s="72" t="inlineStr">
+      <c r="M3" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8316,7 +8347,7 @@
           <t>본 체크리스트는 동탄트램 노면전차설비 공사 발주 착수 전8대 현실조건(자재 Lead Time, 시공 실적 Pool, 예비품, 시공중/후 교육 및 기술지원, 현장 자재창고 임대료, 가설 전원/용수/청소, 개통 후 상주 기술지원...</t>
         </is>
       </c>
-      <c r="O3" s="70" t="inlineStr">
+      <c r="O3" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8378,7 +8409,7 @@
           <t>"정류기, 변압기, ESS 대형 기자재 반입 동선, 출입문 유효 폭/높이(H x W) 및 양중 훅 위치 실측 검증"</t>
         </is>
       </c>
-      <c r="K4" s="72" t="inlineStr">
+      <c r="K4" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8388,7 +8419,7 @@
           <t>본 지침서는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 공동구/횡단관로/인입구 좌표, 전기 기능실 마감, 토목 공사용 매립 배관 검측 및 3D BIM 간섭 해소 절차를 명확히 제시하여, 콘크리트 구조체 타설 완료 후 ...</t>
         </is>
       </c>
-      <c r="M4" s="72" t="inlineStr">
+      <c r="M4" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8398,7 +8429,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 변전실 개구부, 공동구/인입구 3D BIM 좌표, 전기 기능실 마감 및 토목 공사용 매립 배관의 적정성을 사전에 검측하여 구조체 타설 후 굴착/파쇄 재시공 충...</t>
         </is>
       </c>
-      <c r="O4" s="70" t="inlineStr">
+      <c r="O4" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8464,7 +8495,7 @@
           <t>"신호, 통신, 기계, PSD 및 트램 차량 전력 공급 관로, 배선 용량 및 트레이 타공 누락 사항 정밀 추출"</t>
         </is>
       </c>
-      <c r="K5" s="72" t="inlineStr">
+      <c r="K5" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8474,7 +8505,7 @@
           <t>전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 예방함</t>
         </is>
       </c>
-      <c r="M5" s="72" t="inlineStr">
+      <c r="M5" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8484,7 +8515,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 ...</t>
         </is>
       </c>
-      <c r="O5" s="70" t="inlineStr">
+      <c r="O5" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8545,7 +8576,7 @@
           <t>"SCADA RTU, 변전소 GIS, 정류기, ESS 릴레이 간 IEC 61850 및 Modbus 통신 핀 맵/신호 주소 1:1 검증"</t>
         </is>
       </c>
-      <c r="K6" s="72" t="inlineStr">
+      <c r="K6" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8555,7 +8586,7 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조율 및 제작사양서 확정</t>
         </is>
       </c>
-      <c r="M6" s="72" t="inlineStr">
+      <c r="M6" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8565,7 +8596,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조...</t>
         </is>
       </c>
-      <c r="O6" s="70" t="inlineStr">
+      <c r="O6" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8631,7 +8662,7 @@
           <t>"지자체(수원시, 화성시) 도로교통관제 센터와 트램 우선신호 제어기 간 통신 인터페이스 및 연동 협의"</t>
         </is>
       </c>
-      <c r="K7" s="72" t="inlineStr">
+      <c r="K7" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8641,7 +8672,7 @@
           <t>수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 협의</t>
         </is>
       </c>
-      <c r="M7" s="72" t="inlineStr">
+      <c r="M7" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8651,7 +8682,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 ...</t>
         </is>
       </c>
-      <c r="O7" s="70" t="inlineStr">
+      <c r="O7" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8712,7 +8743,7 @@
           <t>"감리/감독원 입회 품질검측계획서(ITP: Inspection &amp; Test Plan) 작성 및 Hold Point(필수정지점) / Witness Point(입회점) 구분 명시"</t>
         </is>
       </c>
-      <c r="K8" s="72" t="inlineStr">
+      <c r="K8" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8722,7 +8753,7 @@
           <t>감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반출 통제 수칙</t>
         </is>
       </c>
-      <c r="M8" s="72" t="inlineStr">
+      <c r="M8" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8732,7 +8763,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반...</t>
         </is>
       </c>
-      <c r="O8" s="70" t="inlineStr">
+      <c r="O8" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8793,7 +8824,7 @@
           <t>"변압기, GIS, 정류기, ESS, 전차선 등 주요 전기자재 공장 제작 및 수급 소요 기간(Lead Time 30~60일)을 공정표와 사전 연동 통제"</t>
         </is>
       </c>
-      <c r="K9" s="72" t="inlineStr">
+      <c r="K9" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8803,7 +8834,7 @@
           <t>현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획서 승인</t>
         </is>
       </c>
-      <c r="M9" s="81" t="inlineStr">
+      <c r="M9" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8813,7 +8844,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획...</t>
         </is>
       </c>
-      <c r="O9" s="70" t="inlineStr">
+      <c r="O9" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8874,7 +8905,7 @@
           <t>"관할 한전에 수전 용량 계산서, 건축허가서, 22.9kV 수전 단선도 첨부 전기사용신청서 제출(처리기간 1개월) 및 인수점 지중 맨홀 협의"</t>
         </is>
       </c>
-      <c r="K10" s="72" t="inlineStr">
+      <c r="K10" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8884,7 +8915,7 @@
           <t>한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do List 추적 관리</t>
         </is>
       </c>
-      <c r="M10" s="72" t="inlineStr">
+      <c r="M10" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8894,7 +8925,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do Lis...</t>
         </is>
       </c>
-      <c r="O10" s="70" t="inlineStr">
+      <c r="O10" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8965,7 +8996,7 @@
           <t>"노반(궤도), 신호, 통신, 기계, PSD, 차량 인터페이스 및 3D BIM 공간 간섭을 전면 사전 검토한다."</t>
         </is>
       </c>
-      <c r="K11" s="72" t="inlineStr">
+      <c r="K11" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8975,7 +9006,7 @@
           <t>본 지침서는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체 구축 방법,3D BIM 공종 간섭 조율, 자재 반입 동선/야적장 확보, 타 프로젝트 하자사례 분석 및 안전/민원 Risk He...</t>
         </is>
       </c>
-      <c r="M11" s="72" t="inlineStr">
+      <c r="M11" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8985,7 +9016,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체를 구축하여 3D BIM 공종 간섭, 자재 반입 동선, 타 현장 하자사례 재발방지책 및 Risk Hedge 방안을 확정하기 ...</t>
         </is>
       </c>
-      <c r="O11" s="70" t="inlineStr">
+      <c r="O11" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9047,7 +9078,7 @@
           <t>"변압기 용량, 정류기 정격, ESS 배터리 세부 기술사양서 검토 및 시방 규격 1:1 대조 파악"</t>
         </is>
       </c>
-      <c r="K12" s="72" t="inlineStr">
+      <c r="K12" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9057,7 +9088,7 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따른 상세 기술사양서 및 공장 제작 승인도면(Shop Drawing) 검토</t>
         </is>
       </c>
-      <c r="M12" s="72" t="inlineStr">
+      <c r="M12" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9067,7 +9098,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 제작 사양서 작성 / 승인 업무 이행에 대해전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따...</t>
         </is>
       </c>
-      <c r="O12" s="70" t="inlineStr">
+      <c r="O12" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9131,7 +9162,7 @@
           <t>"변전기기 반입, Cable Tray 설치, 전차선 지주 입립 시공 순서 및 3D BIM 공정 수립"</t>
         </is>
       </c>
-      <c r="K13" s="72" t="inlineStr">
+      <c r="K13" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9141,7 +9172,7 @@
           <t>전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책 수립 후 감리단 공학적 승인 완수</t>
         </is>
       </c>
-      <c r="M13" s="72" t="inlineStr">
+      <c r="M13" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9151,7 +9182,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 계획 수립 / 승인 업무 이행에 대해전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책...</t>
         </is>
       </c>
-      <c r="O13" s="70" t="inlineStr">
+      <c r="O13" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9214,7 +9245,7 @@
           <t>"제조사 공장등록증, 사업자등록증, ISO 품질인증서 및 유사 철도/트램 납품 실적 검증"</t>
         </is>
       </c>
-      <c r="K14" s="72" t="inlineStr">
+      <c r="K14" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9224,7 +9255,7 @@
           <t>전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) 감리단 적격 승인 수검</t>
         </is>
       </c>
-      <c r="M14" s="72" t="inlineStr">
+      <c r="M14" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9234,7 +9265,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재공급원/기자재 제작도서 승인 업무 이행에 대해전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) ...</t>
         </is>
       </c>
-      <c r="O14" s="70" t="inlineStr">
+      <c r="O14" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9300,7 +9331,7 @@
           <t>"제작사 부품 조달 현황, 외함 판금/도장 및 내부 배선 조립 공정 공정표 100% 관리"</t>
         </is>
       </c>
-      <c r="K15" s="72" t="inlineStr">
+      <c r="K15" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9310,7 +9341,7 @@
           <t>정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acceptance Test) 수행과 시험성적서 승인 완수</t>
         </is>
       </c>
-      <c r="M15" s="72" t="inlineStr">
+      <c r="M15" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9320,7 +9351,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 공정제작 / 제작사 공장검사 업무 이행에 대해정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acc...</t>
         </is>
       </c>
-      <c r="O15" s="70" t="inlineStr">
+      <c r="O15" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9383,7 +9414,7 @@
           <t>"건축 변전실 구조물 완성도, 노반 궤도 시공 상태 및 전기 설치 간섭 여부 정밀 실측"</t>
         </is>
       </c>
-      <c r="K16" s="72" t="inlineStr">
+      <c r="K16" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9393,7 +9424,7 @@
           <t>토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행</t>
         </is>
       </c>
-      <c r="M16" s="72" t="inlineStr">
+      <c r="M16" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9403,7 +9434,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 본공사 전 선행공정 인수인계 점검 업무 이행에 대해토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행 관...</t>
         </is>
       </c>
-      <c r="O16" s="70" t="inlineStr">
+      <c r="O16" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9466,7 +9497,7 @@
           <t>"장비 진입 경로 및 적치장 사전확인, 타분야 작업 일정 및 지상/지하 구조물 간섭 협의"</t>
         </is>
       </c>
-      <c r="K17" s="72" t="inlineStr">
+      <c r="K17" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9476,7 +9507,7 @@
           <t>고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시</t>
         </is>
       </c>
-      <c r="M17" s="72" t="inlineStr">
+      <c r="M17" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9486,7 +9517,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 장비반입 및 안전교육 업무 이행에 대해고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시 관련 실무 요소...</t>
         </is>
       </c>
-      <c r="O17" s="70" t="inlineStr">
+      <c r="O17" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9549,7 +9580,7 @@
           <t>"자재 하차 통제 구획 설정, 크레인 양중 신호수 배치 및 자재 반입 동선 안전 확보"</t>
         </is>
       </c>
-      <c r="K18" s="72" t="inlineStr">
+      <c r="K18" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9559,7 +9590,7 @@
           <t>전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 확인</t>
         </is>
       </c>
-      <c r="M18" s="72" t="inlineStr">
+      <c r="M18" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9569,7 +9600,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재 반입 및 검수 업무 이행에 대해전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 ...</t>
         </is>
       </c>
-      <c r="O18" s="70" t="inlineStr">
+      <c r="O18" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9632,7 +9663,7 @@
           <t>"감리/감독 협의를 통한 시공 샘플 대상 선정, 시험시공 수행 및 시공 기준서 확정"</t>
         </is>
       </c>
-      <c r="K19" s="72" t="inlineStr">
+      <c r="K19" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9642,7 +9673,7 @@
           <t>변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측</t>
         </is>
       </c>
-      <c r="M19" s="72" t="inlineStr">
+      <c r="M19" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9652,7 +9683,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전철전력설비 반입 및 설치 업무 이행에 대해변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측 관련 ...</t>
         </is>
       </c>
-      <c r="O19" s="70" t="inlineStr">
+      <c r="O19" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9715,7 +9746,7 @@
           <t>"한전 인수점 지중 맨홀부터 수전 전기실까지 Cable Tray 수평도 및 고정 행거 설치"</t>
         </is>
       </c>
-      <c r="K20" s="72" t="inlineStr">
+      <c r="K20" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9725,7 +9756,7 @@
           <t>한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완수</t>
         </is>
       </c>
-      <c r="M20" s="72" t="inlineStr">
+      <c r="M20" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9735,7 +9766,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전용 케이블 트레이 및 케이블 포설 업무 이행에 대해한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완...</t>
         </is>
       </c>
-      <c r="O20" s="70" t="inlineStr">
+      <c r="O20" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9799,7 +9830,7 @@
           <t>"한국전기안전공사 KESC 사용전검사 합격 필증 수령 및 수전 사전 조건 완수"</t>
         </is>
       </c>
-      <c r="K21" s="72" t="inlineStr">
+      <c r="K21" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9809,7 +9840,7 @@
           <t>KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급전) 시행</t>
         </is>
       </c>
-      <c r="M21" s="72" t="inlineStr">
+      <c r="M21" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9819,7 +9850,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전 및 전기공급(급전) 업무 이행에 대해KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급...</t>
         </is>
       </c>
-      <c r="O21" s="70" t="inlineStr">
+      <c r="O21" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9884,7 +9915,7 @@
           <t>"감리단 제출용 SCADA 종합연동시험 계획서, 포인트 맵 및 점검 절차서 작성"</t>
         </is>
       </c>
-      <c r="K22" s="72" t="inlineStr">
+      <c r="K22" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9894,7 +9925,7 @@
           <t>책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험 수행 및 검측 승인</t>
         </is>
       </c>
-      <c r="M22" s="72" t="inlineStr">
+      <c r="M22" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9904,7 +9935,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 종합연동시험(SCADA) 실시 업무 이행에 대해책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험...</t>
         </is>
       </c>
-      <c r="O22" s="70" t="inlineStr">
+      <c r="O22" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9965,7 +9996,7 @@
           <t>"철도종합시험운행 시행지침 제6조에 따른 전기 공종별 시험 항목 및 절차서 확정"</t>
         </is>
       </c>
-      <c r="K23" s="72" t="inlineStr">
+      <c r="K23" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9975,7 +10006,7 @@
           <t>철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인</t>
         </is>
       </c>
-      <c r="M23" s="72" t="inlineStr">
+      <c r="M23" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9985,7 +10016,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 공종별 시험 업무 이행에 대해철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인 관련 실무 요...</t>
         </is>
       </c>
-      <c r="O23" s="70" t="inlineStr">
+      <c r="O23" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10049,7 +10080,7 @@
           <t>"궤도 시공 정밀도 확인 및 트램 차량 건축한계(폭 3,600mm) 간섭 여부 레이저 실측"</t>
         </is>
       </c>
-      <c r="K24" s="72" t="inlineStr">
+      <c r="K24" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10059,7 +10090,7 @@
           <t>노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수</t>
         </is>
       </c>
-      <c r="M24" s="72" t="inlineStr">
+      <c r="M24" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10069,7 +10100,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 투입 전 점검 업무 이행에 대해노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수 관...</t>
         </is>
       </c>
-      <c r="O24" s="70" t="inlineStr">
+      <c r="O24" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10131,7 +10162,7 @@
           <t>"철도안전법 철도차량 형식승인 절차에 따른 본선 구간 전기-차량 시운전 계획 수립"</t>
         </is>
       </c>
-      <c r="K25" s="72" t="inlineStr">
+      <c r="K25" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10141,7 +10172,7 @@
           <t>철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행</t>
         </is>
       </c>
-      <c r="M25" s="72" t="inlineStr">
+      <c r="M25" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10151,7 +10182,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 시운전 업무 이행에 대해철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행 관련 실...</t>
         </is>
       </c>
-      <c r="O25" s="70" t="inlineStr">
+      <c r="O25" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10213,7 +10244,7 @@
           <t>"전기자재 제작사 작성 운영/유지보수 매뉴얼, 비상 조치 절차서 및 교육 교재 검토"</t>
         </is>
       </c>
-      <c r="K26" s="72" t="inlineStr">
+      <c r="K26" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10223,7 +10254,7 @@
           <t>전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부</t>
         </is>
       </c>
-      <c r="M26" s="72" t="inlineStr">
+      <c r="M26" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10233,7 +10264,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 운영자 교육시행 업무 이행에 대해전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부 관련 ...</t>
         </is>
       </c>
-      <c r="O26" s="70" t="inlineStr">
+      <c r="O26" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10296,7 +10327,7 @@
           <t>"철도종합시험운행 시행지침 제8조에 의거, 발주처-운영자 합동 사전점검 계획서 수립"</t>
         </is>
       </c>
-      <c r="K27" s="72" t="inlineStr">
+      <c r="K27" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10306,7 +10337,7 @@
           <t>철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수</t>
         </is>
       </c>
-      <c r="M27" s="72" t="inlineStr">
+      <c r="M27" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10316,7 +10347,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 사전점검 업무 이행에 대해철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수 관련 실무...</t>
         </is>
       </c>
-      <c r="O27" s="70" t="inlineStr">
+      <c r="O27" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10380,7 +10411,7 @@
           <t>"시설물검증시험계획을 운영자와 협의 수립하고 한국교통안전공단 전문기관 승인 수검"</t>
         </is>
       </c>
-      <c r="K28" s="72" t="inlineStr">
+      <c r="K28" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10390,7 +10421,7 @@
           <t>철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출</t>
         </is>
       </c>
-      <c r="M28" s="72" t="inlineStr">
+      <c r="M28" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10400,7 +10431,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시설물 검증시험 업무 이행에 대해철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출...</t>
         </is>
       </c>
-      <c r="O28" s="70" t="inlineStr">
+      <c r="O28" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10466,7 +10497,7 @@
           <t>"운영자-발주처 협의 영업시운전계획 수립, 국토부 전문기관(교통안전공단) 승인 완수"</t>
         </is>
       </c>
-      <c r="K29" s="72" t="inlineStr">
+      <c r="K29" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10476,7 +10507,7 @@
           <t>철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고</t>
         </is>
       </c>
-      <c r="M29" s="72" t="inlineStr">
+      <c r="M29" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10486,7 +10517,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 영업시운전 업무 이행에 대해철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고 ...</t>
         </is>
       </c>
-      <c r="O29" s="70" t="inlineStr">
+      <c r="O29" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10547,7 +10578,7 @@
           <t>"관할 한국전력공사 제출용 전기사용신청서, 변전소 용량 계산서 및 위임장 작성"</t>
         </is>
       </c>
-      <c r="K30" s="72" t="inlineStr">
+      <c r="K30" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10557,7 +10588,7 @@
           <t>관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수</t>
         </is>
       </c>
-      <c r="M30" s="72" t="inlineStr">
+      <c r="M30" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10567,7 +10598,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용신청 업무 이행에 대해관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수 관련 실무 요소를 100% 사전...</t>
         </is>
       </c>
-      <c r="O30" s="70" t="inlineStr">
+      <c r="O30" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10628,7 +10659,7 @@
           <t>"전기사업법 시행규칙에 맞춘 공사계획서 및 전기설비 공사계획신고서 정밀 작성"</t>
         </is>
       </c>
-      <c r="K31" s="72" t="inlineStr">
+      <c r="K31" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10638,7 +10669,7 @@
           <t>관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료</t>
         </is>
       </c>
-      <c r="M31" s="72" t="inlineStr">
+      <c r="M31" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10648,7 +10679,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 공사계획신고 업무 이행에 대해관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료 관련 실무 요소를 100% 사전 검측하여 시공 하자...</t>
         </is>
       </c>
-      <c r="O31" s="70" t="inlineStr">
+      <c r="O31" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10709,7 +10740,7 @@
           <t>"노면전차선로 지주, 강성 가선, 브래킷 수량조서 및 시공 승인도면(Shop Drawing) 작성"</t>
         </is>
       </c>
-      <c r="K32" s="72" t="inlineStr">
+      <c r="K32" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10719,7 +10750,7 @@
           <t>한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수</t>
         </is>
       </c>
-      <c r="M32" s="72" t="inlineStr">
+      <c r="M32" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10729,7 +10760,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 노면전차선로 적합성 검증 업무 이행에 대해한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수 관련 실무 요소를 100...</t>
         </is>
       </c>
-      <c r="O32" s="70" t="inlineStr">
+      <c r="O32" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10803,7 +10834,7 @@
           <t>"전기설비 설치 완료 후 7일 전 사용전검사신청서, 감리배치서, 단선도, 자재성적서 제출"</t>
         </is>
       </c>
-      <c r="K33" s="72" t="inlineStr">
+      <c r="K33" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10813,7 +10844,7 @@
           <t>전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전), 경찰서 도로공사신고(3일전) 통합 수검 완료</t>
         </is>
       </c>
-      <c r="M33" s="72" t="inlineStr">
+      <c r="M33" s="170" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10823,7 +10854,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용전검사 (전력/전차선/송변전) 업무 이행에 대해전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전...</t>
         </is>
       </c>
-      <c r="O33" s="70" t="inlineStr">
+      <c r="O33" s="171" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16937,7 +16968,7 @@
           <t>발주처 기본계획 사전 검토 | 발주처 기본계획 보고서</t>
         </is>
       </c>
-      <c r="M2" s="160" t="inlineStr">
+      <c r="M2" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16947,7 +16978,7 @@
           <t>• 조사설계 용역 기본계획 도서 확보 여부 확인 • 핵심이슈 (미시추 사유, 지층/암반등급 조정여부 등) 확보 여부 확인 • 사업지 연접 지질/지반조사 자료 확보 여부 확인</t>
         </is>
       </c>
-      <c r="O2" s="160" t="inlineStr">
+      <c r="O2" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16957,7 +16988,7 @@
           <t>1) 발주처 계획 입수(비공식) 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q2" s="160" t="inlineStr">
+      <c r="Q2" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17025,7 +17056,7 @@
           <t>입수된 발주정보 평가를 통한 관심 Project 선정 | 관심사업 List</t>
         </is>
       </c>
-      <c r="M3" s="161" t="inlineStr">
+      <c r="M3" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17035,7 +17066,7 @@
           <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행 • 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
         </is>
       </c>
-      <c r="O3" s="161" t="inlineStr">
+      <c r="O3" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17045,7 +17076,7 @@
           <t>1) 관심프로젝트 선정 적정성을 확인하였는가? 2) 관심사업 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q3" s="161" t="inlineStr">
+      <c r="Q3" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17113,7 +17144,7 @@
           <t>발주처 지반조사 수립업체 파악 | 발주처 기본계획 수행 List + Contact Point List</t>
         </is>
       </c>
-      <c r="M4" s="160" t="inlineStr">
+      <c r="M4" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17123,7 +17154,7 @@
           <t>• 발주처 지반조사업체 확인 후 당사 Pool List와 비교 • 발주처 지반조사 업체 확인팀 Contact Point 확보</t>
         </is>
       </c>
-      <c r="O4" s="160" t="inlineStr">
+      <c r="O4" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17133,7 +17164,7 @@
           <t>1) 발주처 지반조사 모니터링 적정성을 확인하였는가? 2) 발주처 기본계획 수행 List + Contact Point List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q4" s="160" t="inlineStr">
+      <c r="Q4" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17201,7 +17232,7 @@
           <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리 | 외부지질전문가 Pool List</t>
         </is>
       </c>
-      <c r="M5" s="161" t="inlineStr">
+      <c r="M5" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17211,7 +17242,7 @@
           <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성 • 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
         </is>
       </c>
-      <c r="O5" s="161" t="inlineStr">
+      <c r="O5" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17221,7 +17252,7 @@
           <t>1) 외부 지질전문가 Pool 관리 적정성을 확인하였는가? 2) 외부지질전문가 Pool List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q5" s="161" t="inlineStr">
+      <c r="Q5" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17292,7 +17323,7 @@
           <t>발주처 계획 대응 및 개략 지반조사 결과 사전 예측을 위한 업체 관리 | 조사업체 POOL/필요시 Update</t>
         </is>
       </c>
-      <c r="M6" s="160" t="inlineStr">
+      <c r="M6" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17302,7 +17333,7 @@
           <t>• 공공기관별 입찰공고 모니터링 통한 지반조사업체 입찰참여 유치(입찰 공사 여부 확인) • 업체 Pool List 갱신 여부 확인 • 지반조사업체 역량 및 기술수준 평가표 평가 여부 확인 (Pool 갱신 및 신규업체...</t>
         </is>
       </c>
-      <c r="O6" s="160" t="inlineStr">
+      <c r="O6" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17312,7 +17343,7 @@
           <t>1) 지반조사 Pool 관리 적정성을 확인하였는가? 2) 조사업체 POOL/필요시 Update 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q6" s="160" t="inlineStr">
+      <c r="Q6" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17379,7 +17410,7 @@
           <t>발주처 기본계획 및 지반조사 결과 사전 획득 | 발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
         </is>
       </c>
-      <c r="M7" s="161" t="inlineStr">
+      <c r="M7" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17389,7 +17420,7 @@
           <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
         </is>
       </c>
-      <c r="O7" s="161" t="inlineStr">
+      <c r="O7" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17399,7 +17430,7 @@
           <t>1) 기본계획 지반조사 자료 및 R/O 정보 입수 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 및 지반조사 보고서(비공식) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q7" s="161" t="inlineStr">
+      <c r="Q7" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17469,7 +17500,7 @@
           <t>발주처 기본계획 지반조사 문제점 검토 | 기본계획 지반조사 검토서(설계, 공정, 기획)</t>
         </is>
       </c>
-      <c r="M8" s="160" t="inlineStr">
+      <c r="M8" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17479,7 +17510,7 @@
           <t>• 시추조사 위치, 수량 적정성 검토 • 지질이상 구간 상세 조사 여부 및 적정성 검토 확인 • 미시추 구간 지반 특성 적정성 검토확인 (측점 검토, 위치 및 물량검토) • 인근 사업 지반조사자료 비교 통해 당사 지...</t>
         </is>
       </c>
-      <c r="O8" s="160" t="inlineStr">
+      <c r="O8" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17489,7 +17520,7 @@
           <t>1) 기본계획 지반조사 R/O 검토 (설계, 공정, 기획) 적정성을 확인하였는가? 2) 기본계획 지반조사 검토서(설계, 공정, 기획) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q8" s="160" t="inlineStr">
+      <c r="Q8" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17556,7 +17587,7 @@
           <t>발주처 지반조사 문제점 R/O 분석 | 기본계획 지반조사 개략 검토서</t>
         </is>
       </c>
-      <c r="M9" s="161" t="inlineStr">
+      <c r="M9" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17566,7 +17597,7 @@
           <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
         </is>
       </c>
-      <c r="O9" s="161" t="inlineStr">
+      <c r="O9" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17576,7 +17607,7 @@
           <t>1) 기본계획 지반조사 R/O 종합검토 (원가) 적정성을 확인하였는가? 2) 기본계획 지반조사 개략 검토서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q9" s="161" t="inlineStr">
+      <c r="Q9" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17643,7 +17674,7 @@
           <t>지반조사업체 Pool 내 최적의 업체 선정 | 지반조사 입찰 참여 Pool</t>
         </is>
       </c>
-      <c r="M10" s="160" t="inlineStr">
+      <c r="M10" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17653,7 +17684,7 @@
           <t>• 지반조사업체 Pool/실적 검토 및 공종별 적합성 정합 및 견적 본부 연계 검토</t>
         </is>
       </c>
-      <c r="O10" s="160" t="inlineStr">
+      <c r="O10" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17663,7 +17694,7 @@
           <t>1) 지반조사 업체 선정 적정성을 확인하였는가? 2) 지반조사 입찰 참여 Pool 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q10" s="160" t="inlineStr">
+      <c r="Q10" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17730,7 +17761,7 @@
           <t>지반조사업체 용역 계약 | 지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="M11" s="161" t="inlineStr">
+      <c r="M11" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17740,7 +17771,7 @@
           <t>• 일반구매시스템을 이용한 용역계약</t>
         </is>
       </c>
-      <c r="O11" s="161" t="inlineStr">
+      <c r="O11" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17750,7 +17781,7 @@
           <t>1) 지반조사 업체 계약 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q11" s="161" t="inlineStr">
+      <c r="Q11" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17818,7 +17849,7 @@
           <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정 | 지반조사 계획서</t>
         </is>
       </c>
-      <c r="M12" s="160" t="inlineStr">
+      <c r="M12" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17828,7 +17859,7 @@
           <t>• 현장답사 수행 • 공종별 실시설계에 준하여 수량 및 위치 검토</t>
         </is>
       </c>
-      <c r="O12" s="160" t="inlineStr">
+      <c r="O12" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17838,7 +17869,7 @@
           <t>1) 지반조사 항목, 수량 및 위치검토 적정성을 확인하였는가? 2) 지반조사 계획서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q12" s="160" t="inlineStr">
+      <c r="Q12" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17905,7 +17936,7 @@
           <t>지반조사 항목, 수량 및 위치 적정성 검토 | 지반조사계획 의견서</t>
         </is>
       </c>
-      <c r="M13" s="161" t="inlineStr">
+      <c r="M13" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17915,7 +17946,7 @@
           <t>• 지반조사 계획서 검토 및 검토</t>
         </is>
       </c>
-      <c r="O13" s="161" t="inlineStr">
+      <c r="O13" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17925,7 +17956,7 @@
           <t>1) 지반조사계획 적정성 심사의뢰 적정성을 확인하였는가? 2) 지반조사계획 의견서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q13" s="161" t="inlineStr">
+      <c r="Q13" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17994,7 +18025,7 @@
           <t>지반조사 수행을 위한 인허가 승인 | 인허가 서류</t>
         </is>
       </c>
-      <c r="M14" s="160" t="inlineStr">
+      <c r="M14" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18004,7 +18035,7 @@
           <t>• 산지일시사용 신고(사업계획서, 지형도, 산지일시사용예정실측도, 복구계획서, 복지봉투) • 굴착행위 신고(굴착행위신고서, 위치 또는 평면도, 원상복구계획서, 토지사용 승낙서) • 하천점용 허가(위치도, 이해관계인 ...</t>
         </is>
       </c>
-      <c r="O14" s="160" t="inlineStr">
+      <c r="O14" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18014,7 +18045,7 @@
           <t>1) 지반조사 인허가 적정성을 확인하였는가? 2) 인허가 서류 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q14" s="160" t="inlineStr">
+      <c r="Q14" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18082,7 +18113,7 @@
           <t>외부지질전문가 의견을 반영한 지반조사 계획 확정 | 지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="M15" s="161" t="inlineStr">
+      <c r="M15" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18092,7 +18123,7 @@
           <t>• 외부지질전문가 지반조사 의견 검토 • 입찰설계 지반조사 계획 보완</t>
         </is>
       </c>
-      <c r="O15" s="161" t="inlineStr">
+      <c r="O15" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18102,7 +18133,7 @@
           <t>1) 지반조사 항목, 수량 및 위치 보완 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q15" s="161" t="inlineStr">
+      <c r="Q15" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18171,7 +18202,7 @@
           <t>과업구간 지반여건 상세 파악 | 지반조사 보고서, 시추 Core 및 샘플</t>
         </is>
       </c>
-      <c r="M16" s="160" t="inlineStr">
+      <c r="M16" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18181,7 +18212,7 @@
           <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등) • 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등) • 실내시험 수행(요동시험, 입도시험 등)</t>
         </is>
       </c>
-      <c r="O16" s="160" t="inlineStr">
+      <c r="O16" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18191,7 +18222,7 @@
           <t>1) 지반조사 수행 적정성을 확인하였는가? 2) 지반조사 보고서, 시추 Core 및 샘플 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q16" s="160" t="inlineStr">
+      <c r="Q16" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18261,7 +18292,7 @@
           <t>지반조사 결과 오류 및 지반정수의 적합성 검토 | 지반조사 결과 분석 의견서</t>
         </is>
       </c>
-      <c r="M17" s="161" t="inlineStr">
+      <c r="M17" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18271,7 +18302,7 @@
           <t>• 입찰설계 지반조사 보고서 검토 • 시추조사 위치 및 심도의 적정성 검토 • 실내시험 결과 등급 적정성 검토 • 실시설계시 추가지반조사 필요구간 검토</t>
         </is>
       </c>
-      <c r="O17" s="161" t="inlineStr">
+      <c r="O17" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18281,7 +18312,7 @@
           <t>1) 지반조사 수렴 결과 분석 적정성을 확인하였는가? 2) 지반조사 결과 분석 의견서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q17" s="161" t="inlineStr">
+      <c r="Q17" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18350,7 +18381,7 @@
           <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M18" s="160" t="inlineStr">
+      <c r="M18" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18360,7 +18391,7 @@
           <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
         </is>
       </c>
-      <c r="O18" s="160" t="inlineStr">
+      <c r="O18" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18370,7 +18401,7 @@
           <t>1) 입찰설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q18" s="160" t="inlineStr">
+      <c r="Q18" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18438,7 +18469,7 @@
           <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정 | 입찰설계 R/O 검토서</t>
         </is>
       </c>
-      <c r="M19" s="161" t="inlineStr">
+      <c r="M19" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18448,7 +18479,7 @@
           <t>• 입찰설계 지반조사 R/O별 Cost effect 분석 • 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
         </is>
       </c>
-      <c r="O19" s="161" t="inlineStr">
+      <c r="O19" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18458,7 +18489,7 @@
           <t>1) 지반조사 결과 R/O 종합검토 적정성을 확인하였는가? 2) 입찰설계 R/O 검토서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q19" s="161" t="inlineStr">
+      <c r="Q19" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18527,7 +18558,7 @@
           <t>REM 차트 작성(회사의 Core Risk, T/C 공정검토 결과, 경쟁사 동향, 발주 경향) 및 보고 | REM 회의록</t>
         </is>
       </c>
-      <c r="M20" s="160" t="inlineStr">
+      <c r="M20" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18537,7 +18568,7 @@
           <t>• Risk Profiling/Merge 방안 검토 • 공정 착공성 검토 및 T/C 검토 • 설계차별화 및 Idea Frame 검토</t>
         </is>
       </c>
-      <c r="O20" s="160" t="inlineStr">
+      <c r="O20" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18547,7 +18578,7 @@
           <t>1) REM 수립 적정성을 확인하였는가? 2) REM 회의록 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q20" s="160" t="inlineStr">
+      <c r="Q20" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18615,7 +18646,7 @@
           <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출 | 추가지반조사 List</t>
         </is>
       </c>
-      <c r="M21" s="161" t="inlineStr">
+      <c r="M21" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18625,7 +18656,7 @@
           <t>• 지반조사 수렴 결과 분석보고서 검토 • 지반조사 결과 R/O 종합검토 결과 검토</t>
         </is>
       </c>
-      <c r="O21" s="161" t="inlineStr">
+      <c r="O21" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18635,7 +18666,7 @@
           <t>1) 추가지반조사 계획 수립 적정성을 확인하였는가? 2) 추가지반조사 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q21" s="161" t="inlineStr">
+      <c r="Q21" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18707,7 +18738,7 @@
           <t>적정 추가지반조사 규명을 위한 장비 사양 검토 | -</t>
         </is>
       </c>
-      <c r="M22" s="160" t="inlineStr">
+      <c r="M22" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18717,7 +18748,7 @@
           <t>• 3D GPR탐사 장비 사양(차량형) - 3D Radar(노르웨이)_200~3000Hz, 2.0m~3.0m : 하상도 높음 - MIRA(스웨덴)_400~1300Hz, 1.0m~2.0m : 정밀한 입체 형상 - St...</t>
         </is>
       </c>
-      <c r="O22" s="160" t="inlineStr">
+      <c r="O22" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18727,7 +18758,7 @@
           <t>1) 3D GPR탐사 장비 사양(차량형) 검토 적정성을 확인하였는가? 2) - 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q22" s="160" t="inlineStr">
+      <c r="Q22" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18796,7 +18827,7 @@
           <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M23" s="161" t="inlineStr">
+      <c r="M23" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18806,7 +18837,7 @@
           <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
         </is>
       </c>
-      <c r="O23" s="161" t="inlineStr">
+      <c r="O23" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18816,7 +18847,7 @@
           <t>1) ECRM 수립 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q23" s="161" t="inlineStr">
+      <c r="Q23" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18883,7 +18914,7 @@
           <t>입찰 | 투찰내역서</t>
         </is>
       </c>
-      <c r="M24" s="160" t="inlineStr">
+      <c r="M24" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18893,7 +18924,7 @@
           <t>• 최종 R/O를 반영한 투찰내역서 작성</t>
         </is>
       </c>
-      <c r="O24" s="160" t="inlineStr">
+      <c r="O24" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18903,7 +18934,7 @@
           <t>1) 최종 Cost 검토 / 입찰 적정성을 확인하였는가? 2) 투찰내역서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q24" s="160" t="inlineStr">
+      <c r="Q24" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18970,7 +19001,7 @@
           <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유 | 인수인계서</t>
         </is>
       </c>
-      <c r="M25" s="161" t="inlineStr">
+      <c r="M25" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18980,7 +19011,7 @@
           <t>• 최종 R/O 결과 및 입찰도서 인출</t>
         </is>
       </c>
-      <c r="O25" s="161" t="inlineStr">
+      <c r="O25" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18990,7 +19021,7 @@
           <t>1) 입찰설계 현장 인수인계 적정성을 확인하였는가? 2) 인수인계서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q25" s="161" t="inlineStr">
+      <c r="Q25" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19061,7 +19092,7 @@
           <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge | 추가 지반조사 보고서</t>
         </is>
       </c>
-      <c r="M26" s="162" t="inlineStr">
+      <c r="M26" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19071,7 +19102,7 @@
           <t>• 추가 지반조사 계획 및 시점 확인 - 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인) - 추가시추조사 수행(물리탐사, 시추조사) - 토질 및 암석 실내시험 수행 및 결과분석 확인 - 공종별 ...</t>
         </is>
       </c>
-      <c r="O26" s="162" t="inlineStr">
+      <c r="O26" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19081,7 +19112,7 @@
           <t>1) 추가지반조사 수행 적정성을 확인하였는가? 2) 추가 지반조사 보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q26" s="162" t="inlineStr">
+      <c r="Q26" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19149,7 +19180,7 @@
           <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 추가 지반조사결과 종합보고서</t>
         </is>
       </c>
-      <c r="M27" s="162" t="inlineStr">
+      <c r="M27" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19159,7 +19190,7 @@
           <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인 • 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
         </is>
       </c>
-      <c r="O27" s="162" t="inlineStr">
+      <c r="O27" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19169,7 +19200,7 @@
           <t>1) 추가지반조사 결과 분석 적정성을 확인하였는가? 2) 추가 지반조사결과 종합보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q27" s="162" t="inlineStr">
+      <c r="Q27" s="166" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19238,7 +19269,7 @@
           <t>실시설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M28" s="160" t="inlineStr">
+      <c r="M28" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19248,7 +19279,7 @@
           <t>• 실시설계 추가지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 검토</t>
         </is>
       </c>
-      <c r="O28" s="160" t="inlineStr">
+      <c r="O28" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19258,7 +19289,7 @@
           <t>1) 실시설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 실시설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q28" s="160" t="inlineStr">
+      <c r="Q28" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19325,7 +19356,7 @@
           <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 실시설계 최종 R/O</t>
         </is>
       </c>
-      <c r="M29" s="161" t="inlineStr">
+      <c r="M29" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19335,7 +19366,7 @@
           <t>• 추가지반조사 결과 검토</t>
         </is>
       </c>
-      <c r="O29" s="161" t="inlineStr">
+      <c r="O29" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19345,7 +19376,7 @@
           <t>1) 실시설계 추가지반조사 결과 검토 적정성을 확인하였는가? 2) 실시설계 최종 R/O 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q29" s="161" t="inlineStr">
+      <c r="Q29" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19413,7 +19444,7 @@
           <t>최종 지반조사 결과에 따른 R/O 이행방안 수립 | 최종 R/O 이행계획서</t>
         </is>
       </c>
-      <c r="M30" s="160" t="inlineStr">
+      <c r="M30" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19423,7 +19454,7 @@
           <t>• Core Risk 및 Hedge 방안 수립 • Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
         </is>
       </c>
-      <c r="O30" s="160" t="inlineStr">
+      <c r="O30" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19433,7 +19464,7 @@
           <t>1) 최종 R/O 이행방안 수립 적정성을 확인하였는가? 2) 최종 R/O 이행계획서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q30" s="160" t="inlineStr">
+      <c r="Q30" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19500,7 +19531,7 @@
           <t>참여인력 전문성 평가 및 특이사항 기록 | 외부지질 전문가 업무평가서</t>
         </is>
       </c>
-      <c r="M31" s="161" t="inlineStr">
+      <c r="M31" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19510,7 +19541,7 @@
           <t>• 외부지질 전문가 업무평가서 작성</t>
         </is>
       </c>
-      <c r="O31" s="161" t="inlineStr">
+      <c r="O31" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19520,7 +19551,7 @@
           <t>1) 외부지질전문가 업무평가 적정성을 확인하였는가? 2) 외부지질 전문가 업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q31" s="161" t="inlineStr">
+      <c r="Q31" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19587,7 +19618,7 @@
           <t>조사업체 PM 전문성 평가 및 특이사항 기록 | PM업무평가서</t>
         </is>
       </c>
-      <c r="M32" s="160" t="inlineStr">
+      <c r="M32" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19597,7 +19628,7 @@
           <t>• 지반조사 PM 업무평가서 작성</t>
         </is>
       </c>
-      <c r="O32" s="160" t="inlineStr">
+      <c r="O32" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19607,7 +19638,7 @@
           <t>1) 조사업체 PM 업무평가 적정성을 확인하였는가? 2) PM업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q32" s="160" t="inlineStr">
+      <c r="Q32" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19674,7 +19705,7 @@
           <t>조사업체 업무평가 및 특이사항 기록 | 협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="M33" s="161" t="inlineStr">
+      <c r="M33" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19684,7 +19715,7 @@
           <t>• 협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="O33" s="161" t="inlineStr">
+      <c r="O33" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19694,7 +19725,7 @@
           <t>1) 지반조사업체 업무평가 적정성을 확인하였는가? 2) 협력업체 업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q33" s="161" t="inlineStr">
+      <c r="Q33" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19762,7 +19793,7 @@
           <t>설계변경 사항 기록 | LL리포트</t>
         </is>
       </c>
-      <c r="M34" s="160" t="inlineStr">
+      <c r="M34" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19772,7 +19803,7 @@
           <t>• 설계변경 사유 기록관리 • 예상 R/O대비 설계변경 사항 비교 검토</t>
         </is>
       </c>
-      <c r="O34" s="160" t="inlineStr">
+      <c r="O34" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19782,7 +19813,7 @@
           <t>1) 설계변경 LL 리포트 작성 적정성을 확인하였는가? 2) LL리포트 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q34" s="160" t="inlineStr">
+      <c r="Q34" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19849,7 +19880,7 @@
           <t>전체 현장 설계변경 사항 기록 | LL리포트 List</t>
         </is>
       </c>
-      <c r="M35" s="161" t="inlineStr">
+      <c r="M35" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19859,7 +19890,7 @@
           <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
         </is>
       </c>
-      <c r="O35" s="161" t="inlineStr">
+      <c r="O35" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19869,7 +19900,7 @@
           <t>1) 설계변경 LL 리포트 관리 적정성을 확인하였는가? 2) LL리포트 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q35" s="161" t="inlineStr">
+      <c r="Q35" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19937,7 +19968,7 @@
           <t>지반조사업체 정산 | 정산계약서</t>
         </is>
       </c>
-      <c r="M36" s="160" t="inlineStr">
+      <c r="M36" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19947,7 +19978,7 @@
           <t>• 조사도 수량 Check 후 구매시스템 변경계약 수행 • 변경계약 후 정산금 집행</t>
         </is>
       </c>
-      <c r="O36" s="160" t="inlineStr">
+      <c r="O36" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19957,7 +19988,7 @@
           <t>1) 지반조사업체 정산계약 적정성을 확인하였는가? 2) 정산계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q36" s="160" t="inlineStr">
+      <c r="Q36" s="164" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -20024,7 +20055,7 @@
           <t>지반조사 매뉴얼 Update | 지반조사 매뉴얼</t>
         </is>
       </c>
-      <c r="M37" s="161" t="inlineStr">
+      <c r="M37" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -20034,7 +20065,7 @@
           <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
         </is>
       </c>
-      <c r="O37" s="161" t="inlineStr">
+      <c r="O37" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -20044,13 +20075,123 @@
           <t>1) 매뉴얼 Update 적정성을 확인하였는가? 2) 지반조사 매뉴얼 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q37" s="161" t="inlineStr">
+      <c r="Q37" s="165" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId108"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20141,7 +20282,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="126" t="n"/>
+      <c r="B3" s="158" t="n"/>
       <c r="C3" s="129" t="inlineStr">
         <is>
           <t>Start</t>
@@ -20159,16 +20300,16 @@
           <t>공통_사전준비_지반조사(기술형)</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n"/>
-      <c r="C4" s="131" t="n"/>
-      <c r="D4" s="131" t="n"/>
-      <c r="E4" s="131" t="n"/>
-      <c r="F4" s="131" t="n"/>
-      <c r="G4" s="131" t="n"/>
-      <c r="H4" s="131" t="n"/>
-      <c r="I4" s="131" t="n"/>
-      <c r="J4" s="131" t="n"/>
-      <c r="K4" s="131" t="n"/>
+      <c r="B4" s="123" t="n"/>
+      <c r="C4" s="123" t="n"/>
+      <c r="D4" s="123" t="n"/>
+      <c r="E4" s="123" t="n"/>
+      <c r="F4" s="123" t="n"/>
+      <c r="G4" s="123" t="n"/>
+      <c r="H4" s="123" t="n"/>
+      <c r="I4" s="123" t="n"/>
+      <c r="J4" s="123" t="n"/>
+      <c r="K4" s="124" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="132" t="inlineStr"/>
@@ -20210,8 +20351,16 @@
           <t>발주처 기본계획 보고서</t>
         </is>
       </c>
-      <c r="J5" s="132" t="inlineStr"/>
-      <c r="K5" s="132" t="inlineStr"/>
+      <c r="J5" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K5" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="132" t="inlineStr"/>
@@ -20252,8 +20401,16 @@
           <t>관심사업 List</t>
         </is>
       </c>
-      <c r="J6" s="132" t="inlineStr"/>
-      <c r="K6" s="132" t="inlineStr"/>
+      <c r="J6" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K6" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="132" t="inlineStr">
@@ -20298,8 +20455,16 @@
           <t>발주처 기본계획 수행 List + Contact Point List</t>
         </is>
       </c>
-      <c r="J7" s="132" t="inlineStr"/>
-      <c r="K7" s="132" t="inlineStr"/>
+      <c r="J7" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K7" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="132" t="inlineStr">
@@ -20344,8 +20509,16 @@
           <t>외부지질전문가 Pool List</t>
         </is>
       </c>
-      <c r="J8" s="132" t="inlineStr"/>
-      <c r="K8" s="132" t="inlineStr"/>
+      <c r="J8" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K8" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="132" t="inlineStr">
@@ -20393,8 +20566,16 @@
           <t>조사업체 POOL/필요시 Update</t>
         </is>
       </c>
-      <c r="J9" s="132" t="inlineStr"/>
-      <c r="K9" s="132" t="inlineStr"/>
+      <c r="J9" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K9" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="132" t="inlineStr"/>
@@ -20438,8 +20619,16 @@
           <t>발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
         </is>
       </c>
-      <c r="J10" s="132" t="inlineStr"/>
-      <c r="K10" s="132" t="inlineStr"/>
+      <c r="J10" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K10" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="132" t="inlineStr"/>
@@ -20486,8 +20675,16 @@
           <t>기본계획 지반조사 검토서(설계, 공정, 기획)</t>
         </is>
       </c>
-      <c r="J11" s="132" t="inlineStr"/>
-      <c r="K11" s="132" t="inlineStr"/>
+      <c r="J11" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K11" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="132" t="inlineStr">
@@ -20535,8 +20732,16 @@
           <t>기본계획 지반조사 개략 검토서</t>
         </is>
       </c>
-      <c r="J12" s="132" t="inlineStr"/>
-      <c r="K12" s="132" t="inlineStr"/>
+      <c r="J12" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K12" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="132" t="inlineStr">
@@ -20584,8 +20789,16 @@
           <t>지반조사 입찰 참여 Pool</t>
         </is>
       </c>
-      <c r="J13" s="132" t="inlineStr"/>
-      <c r="K13" s="132" t="inlineStr"/>
+      <c r="J13" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K13" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="132" t="inlineStr"/>
@@ -20629,8 +20842,16 @@
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J14" s="132" t="inlineStr"/>
-      <c r="K14" s="132" t="inlineStr"/>
+      <c r="J14" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K14" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="132" t="inlineStr">
@@ -20679,8 +20900,16 @@
           <t>지반조사 계획서</t>
         </is>
       </c>
-      <c r="J15" s="132" t="inlineStr"/>
-      <c r="K15" s="132" t="inlineStr"/>
+      <c r="J15" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K15" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="132" t="inlineStr">
@@ -20728,8 +20957,16 @@
           <t>지반조사계획 의견서</t>
         </is>
       </c>
-      <c r="J16" s="132" t="inlineStr"/>
-      <c r="K16" s="132" t="inlineStr"/>
+      <c r="J16" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K16" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="132" t="inlineStr"/>
@@ -20775,8 +21012,16 @@
           <t>인허가 서류</t>
         </is>
       </c>
-      <c r="J17" s="132" t="inlineStr"/>
-      <c r="K17" s="132" t="inlineStr"/>
+      <c r="J17" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K17" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="132" t="inlineStr"/>
@@ -20821,8 +21066,16 @@
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J18" s="132" t="inlineStr"/>
-      <c r="K18" s="132" t="inlineStr"/>
+      <c r="J18" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K18" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="132" t="inlineStr">
@@ -20872,8 +21125,16 @@
           <t>지반조사 보고서, 시추 Core 및 샘플</t>
         </is>
       </c>
-      <c r="J19" s="132" t="inlineStr"/>
-      <c r="K19" s="132" t="inlineStr"/>
+      <c r="J19" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K19" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="132" t="inlineStr">
@@ -20924,8 +21185,16 @@
           <t>지반조사 결과 분석 의견서</t>
         </is>
       </c>
-      <c r="J20" s="132" t="inlineStr"/>
-      <c r="K20" s="132" t="inlineStr"/>
+      <c r="J20" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K20" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="132" t="inlineStr"/>
@@ -20971,8 +21240,16 @@
           <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J21" s="132" t="inlineStr"/>
-      <c r="K21" s="132" t="inlineStr"/>
+      <c r="J21" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K21" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="132" t="inlineStr">
@@ -21021,8 +21298,16 @@
           <t>입찰설계 R/O 검토서</t>
         </is>
       </c>
-      <c r="J22" s="132" t="inlineStr"/>
-      <c r="K22" s="132" t="inlineStr"/>
+      <c r="J22" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K22" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="132" t="inlineStr"/>
@@ -21068,8 +21353,16 @@
           <t>REM 회의록</t>
         </is>
       </c>
-      <c r="J23" s="132" t="inlineStr"/>
-      <c r="K23" s="132" t="inlineStr"/>
+      <c r="J23" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K23" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="132" t="inlineStr">
@@ -21118,8 +21411,16 @@
           <t>추가지반조사 List</t>
         </is>
       </c>
-      <c r="J24" s="132" t="inlineStr"/>
-      <c r="K24" s="132" t="inlineStr"/>
+      <c r="J24" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K24" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="132" t="inlineStr"/>
@@ -21168,8 +21469,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="132" t="inlineStr"/>
-      <c r="K25" s="132" t="inlineStr"/>
+      <c r="J25" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K25" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="132" t="inlineStr"/>
@@ -21215,8 +21524,16 @@
           <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J26" s="132" t="inlineStr"/>
-      <c r="K26" s="132" t="inlineStr"/>
+      <c r="J26" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K26" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="132" t="inlineStr"/>
@@ -21260,8 +21577,16 @@
           <t>투찰내역서</t>
         </is>
       </c>
-      <c r="J27" s="132" t="inlineStr"/>
-      <c r="K27" s="132" t="inlineStr"/>
+      <c r="J27" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K27" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="132" t="inlineStr">
@@ -21309,8 +21634,16 @@
           <t>인수인계서</t>
         </is>
       </c>
-      <c r="J28" s="132" t="inlineStr"/>
-      <c r="K28" s="132" t="inlineStr"/>
+      <c r="J28" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K28" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="132" t="inlineStr">
@@ -21362,12 +21695,12 @@
           <t>추가 지반조사 보고서</t>
         </is>
       </c>
-      <c r="J29" s="132" t="inlineStr">
+      <c r="J29" s="164" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K29" s="132" t="inlineStr">
+      <c r="K29" s="164" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -21420,12 +21753,12 @@
           <t>추가 지반조사결과 종합보고서</t>
         </is>
       </c>
-      <c r="J30" s="132" t="inlineStr">
+      <c r="J30" s="164" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="132" t="inlineStr">
+      <c r="K30" s="164" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -21475,8 +21808,16 @@
           <t>실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J31" s="132" t="inlineStr"/>
-      <c r="K31" s="132" t="inlineStr"/>
+      <c r="J31" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K31" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="132" t="inlineStr">
@@ -21524,8 +21865,16 @@
           <t>실시설계 최종 R/O</t>
         </is>
       </c>
-      <c r="J32" s="132" t="inlineStr"/>
-      <c r="K32" s="132" t="inlineStr"/>
+      <c r="J32" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K32" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="132" t="inlineStr">
@@ -21574,8 +21923,16 @@
           <t>최종 R/O 이행계획서</t>
         </is>
       </c>
-      <c r="J33" s="132" t="inlineStr"/>
-      <c r="K33" s="132" t="inlineStr"/>
+      <c r="J33" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K33" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="132" t="inlineStr">
@@ -21623,8 +21980,16 @@
           <t>외부지질 전문가 업무평가서</t>
         </is>
       </c>
-      <c r="J34" s="132" t="inlineStr"/>
-      <c r="K34" s="132" t="inlineStr"/>
+      <c r="J34" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K34" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="132" t="inlineStr">
@@ -21672,8 +22037,16 @@
           <t>PM업무평가서</t>
         </is>
       </c>
-      <c r="J35" s="132" t="inlineStr"/>
-      <c r="K35" s="132" t="inlineStr"/>
+      <c r="J35" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K35" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="132" t="inlineStr">
@@ -21721,8 +22094,16 @@
           <t>협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="J36" s="132" t="inlineStr"/>
-      <c r="K36" s="132" t="inlineStr"/>
+      <c r="J36" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K36" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="132" t="inlineStr"/>
@@ -21767,8 +22148,16 @@
           <t>LL리포트</t>
         </is>
       </c>
-      <c r="J37" s="132" t="inlineStr"/>
-      <c r="K37" s="132" t="inlineStr"/>
+      <c r="J37" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K37" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="132" t="inlineStr"/>
@@ -21812,8 +22201,16 @@
           <t>LL리포트 List</t>
         </is>
       </c>
-      <c r="J38" s="132" t="inlineStr"/>
-      <c r="K38" s="132" t="inlineStr"/>
+      <c r="J38" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K38" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="132" t="inlineStr"/>
@@ -21858,8 +22255,16 @@
           <t>정산계약서</t>
         </is>
       </c>
-      <c r="J39" s="132" t="inlineStr"/>
-      <c r="K39" s="132" t="inlineStr"/>
+      <c r="J39" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K39" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="132" t="inlineStr">
@@ -21907,8 +22312,16 @@
           <t>지반조사 매뉴얼</t>
         </is>
       </c>
-      <c r="J40" s="132" t="inlineStr"/>
-      <c r="K40" s="132" t="inlineStr"/>
+      <c r="J40" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K40" s="164" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -21924,6 +22337,80 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="G2:G3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22119,7 +22606,7 @@
           <t>KDS 47 10 00 철도지반 설계기준 | 현장 가설 둔차선, 용지 경계 및 원지반 고저차 3D 레벨 현측 | 토공사 사전 현장 조사 보고서</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22129,7 +22616,7 @@
           <t>1) 현장 가설 도로 및 용지 경계 현측 ➔ 2) 광학 레벨 원지반 고저차 측정 ➔ 3) 진입 도로 장애 요소 매핑 ➔ 4) 현장 조사 보고서 감리 제출</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22139,7 +22626,7 @@
           <t>가설 도로 폭/구배 현측, 원지반 고저차 레벨 측량 및 3D BIM 도면 오차 점검 (현장 조사 보고서)</t>
         </is>
       </c>
-      <c r="P2" s="17" t="inlineStr">
+      <c r="P2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22213,7 +22700,7 @@
           <t>KCS 47 10 25 시방 검토 | 사전 토공 토사/암석 깎기 및 성토 시방 규정 | 발주처·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22223,7 +22710,7 @@
           <t>1) 사전 토공 시방 요구조건 분석 ➔ 2) 3D BIM 도면 깎기/성토 수량 검증 ➔ 3) 토공 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22233,7 +22720,7 @@
           <t>KCS 47 10 25 사전 토공 시방 검토, 토사/암석 깎기 수량 산출 및 3D BIM 간섭 zero (3자 킥오프 결재)</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22307,7 +22794,7 @@
           <t>지하안전법 제23조 | 현장 지장물, 연약 지반 층후 및 사면 붕괴 위험 요소 추출 | 사전 토공 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22317,7 +22804,7 @@
           <t>1) 지하 매설 지장물 &amp; 연약지반 현출 ➔ 2) 사면 붕괴 위험 구간 추출 ➔ 3) 흙막이 가설재 보강 수립 ➔ 4) 토공 리스크 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22327,7 +22814,7 @@
           <t>지중 매설물 탐사, 연약 지반 층후 분석 및 사면 붕괴 위험 구간 흙막이 가설재 보강 수립</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22401,7 +22888,7 @@
           <t>건산법 상생협력 수칙 | 토공 전문 기술자 1:1 전담 배치 &amp; 3자 주간 소통 회의 | 일일 Safety TBM 100% 이행</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22411,7 +22898,7 @@
           <t>1) 토공 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 복지 지원 &amp; Safety TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22421,7 +22908,7 @@
           <t>토공 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 Safety TBM/음주 측정</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22495,7 +22982,7 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 우회 차선 설계 | 전담 신호수(2인 2조) &amp; LED 경광등 배치</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22505,7 +22992,7 @@
           <t>1) 교통 우회 차선 &amp; 둔차선 도면 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22515,7 +23002,7 @@
           <t>동탄경찰서 도로점용 허가, 가설 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22589,7 +23076,7 @@
           <t>KCS 47 10 25 자재 시방 | 굴착 장비, 가설 펜스 및 배수관 자재 발주 승인 | 공인시험기관 성적표 수속</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22599,7 +23086,7 @@
           <t>1) 굴착 장비 및 가설 펜스 자재 선정 ➔ 2) 공인시험기관 시험성적서 검수 ➔ 3) 자재 발주 신청서 제출 ➔ 4) 자재 반입 검수 통보서 결재</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22609,7 +23096,7 @@
           <t>KCS 47 10 25 굴착 장비/가설재 자재 승인, 공인시험기관 시험성적서 검수 및 자재 반입 통보</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22679,7 +23166,7 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 차단 | 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22689,7 +23176,7 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22699,7 +23186,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22773,7 +23260,7 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 4자 빅룸 회의 | 사전 토공 마일스톤 서명 결재</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22783,7 +23270,7 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 사전 토공 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22793,7 +23280,7 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 사전 토공 마일스톤 연동 및 간섭 리스크 서명</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22867,7 +23354,7 @@
           <t>도로법 및 환경영향평가법 | 지자체 도로점용 허가 및 비산먼지 발생신고 수속 | 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22877,7 +23364,7 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22887,7 +23374,7 @@
           <t>지자체 도로/하천점용 허가서 접수, 비산먼지 발생사업 신고 필증 수속 및 보증보험 제출</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22961,7 +23448,7 @@
           <t>도로교통법 안전 수칙 | 경찰서 차선 점용 허가 및 가설 둔차선 도로 복구 이행 보증보험 | 교통대책 감리 승인</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22971,7 +23458,7 @@
           <t>1) 경찰서 차선 점용 허가증 수령 ➔ 2) 도로 복구 보증보험 증권 제출 ➔ 3) 전담 신호수 &amp; LED 경광등 배치 ➔ 4) 교통대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22981,7 +23468,7 @@
           <t>동탄경찰서 차선 점용 허가, 도로 복구 이행 보증보험 제출 및 전담 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23055,7 +23542,7 @@
           <t>지하안전관리에 관한 특별법 | GPR 3D 관로 탐사 &amp; 인력 시탐 줄파기(깊이 1.5m) | 점용기관 현장 입회 이설 방호</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23065,7 +23552,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 서면 승인</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23075,7 +23562,7 @@
           <t>GPR 3D 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 점용기관 1:1 현장 입회 매달기 방호</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23149,7 +23636,7 @@
           <t>국유재산법 및 공유재산법 | 토지 기공승낙서 인허가 확인 및 진입로 점용 범위 실측 | 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23159,7 +23646,7 @@
           <t>1) 국유지/공유지 기공승낙서 수속 ➔ 2) 진입 도로 점용 범위 실측 ➔ 3) 토지 소유주 사용 협의 ➔ 4) 기공승낙서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23169,7 +23656,7 @@
           <t>국유지/공유지 기공승낙서 인허가 검증, 진입 도로 점용 범위 실측 및 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23243,7 +23730,7 @@
           <t>소음진동관리법 준수 | 야간 공사 소음 방음벽(H=3m) 및 세륜기(깊이 1.2m) 가동 | 단수/단전 주민 사전 안내</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23253,7 +23740,7 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23263,7 +23750,7 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 세륜기(깊이 1.2m) 가동 및 단수/단전 주민 사전 고지</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23337,7 +23824,7 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23347,7 +23834,7 @@
           <t>1) 미보상 필지 현출 &amp; 지적 대조 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 우회 토공 동선 수립 ➔ 4) 용지 보상 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23357,7 +23844,7 @@
           <t>미보상 필지 지적 대조, 경계 가설 펜스(H=1.8m) 차단 및 우회 토공 동선 서면 승인</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23431,7 +23918,7 @@
           <t>건진법 시행령 제89조 | 사전 토공 시공계획서 표준 8대 목차 검토 | 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23441,7 +23928,7 @@
           <t>1) 사전 토공 시공계획서 작성 ➔ 2) 8대 목차 &amp; KCS 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 시공계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23451,7 +23938,7 @@
           <t>사전 토공 시공계획서 표준 8대 목차, KCS 수치 수록 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23525,7 +24012,7 @@
           <t>KCS 47 10 25 토공 시방 | 깎기/성토 토공 유동표 작성 및 3D BIM 도면 대조 | 책임감리원 최종 승인</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23535,7 +24022,7 @@
           <t>1) 토공 깎기/성토 유동표 작성 ➔ 2) 3D BIM 모델 표고 대조 ➔ 3) 사면 안성성 계산서 부착 ➔ 4) 토공 시공계획서 감리 최종 결재</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23545,7 +24032,7 @@
           <t>토공 깎기/성토 유동표 작성, 3D BIM 모델 표고 대조 및 사면 안전성 계산서 감리 결재</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23619,7 +24106,7 @@
           <t>건진법 설계변경 수칙 | 궤도/구조물 후행 공종 요구 표고 오차(±10mm) 반영 | 설계변경 실정보고서 작성</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23629,7 +24116,7 @@
           <t>1) 궤도/구조물 후행 요구 조건 수집 ➔ 2) 마무리면 표고 오차(±10mm) 반영 ➔ 3) 설계변경 실정보고서 작성 ➔ 4) 책임감리원 기술 승인</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23639,7 +24126,7 @@
           <t>궤도/구조물 후행 요구 조건 반영, 마무리면 표고 오차(±10mm) 반영 및 설계변경 실정보고</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23713,7 +24200,7 @@
           <t>지방계약법 정산 수칙 | 착수 전 토종 변경 및 수량 증감 실정보고 작성 | 총사업비 변경 승인 수속</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23723,7 +24210,7 @@
           <t>1) 토질 변경 &amp; 수량 증감 실정보고 작성 ➔ 2) 단가 비교표 작성 ➔ 3) 설계변경 도서 제출 ➔ 4) 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23733,7 +24220,7 @@
           <t>토질 변경 &amp; 수량 증감 실정보고서 작성, 단가 비교표 작성 및 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="P19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23807,7 +24294,7 @@
           <t>건진법 설계변경 규정 | 수량 산출서 및 단가 비교표 작성 | 책임감리원 기술 검토 의견서 첨부</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23817,7 +24304,7 @@
           <t>1) 변경 수량 산출서 정밀 집계 ➔ 2) 신규 단가 산정 서류 부착 ➔ 3) 감리단 기술 검토 수속 ➔ 4) 설계변경 제출 서면 결재</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23827,7 +24314,7 @@
           <t>변경 수량 산출서 정밀 집계, 신규 단가 산정 서류 첨부 및 책임감리원 기술 검토 수속</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23901,7 +24388,7 @@
           <t>도로교통법 안전 수칙 | 게이트 바리케이트, 야간 LED 경광등 부설 | 전담 안전 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23911,7 +24398,7 @@
           <t>1) 게이트 바리케이트 &amp; 경광등 부설 ➔ 2) 우회 차선 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23921,7 +24408,7 @@
           <t>게이트 바리케이트/LED 경광등 설치, 우회 차선 표지판 검측 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23995,7 +24482,7 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 굴착기, 덤프 정기검사증 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24005,7 +24492,7 @@
           <t>1) 10t+ 굴착기/덤프 사양 검수 ➔ 2) 건설기계 정기검사증 점검 ➔ 3) 후방 카메라/경보음 시동 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24015,7 +24502,7 @@
           <t>자중 10t+ 굴착기/덤프 정기검사증, 후방 카메라/경보음 시동 점검 및 반입 허가 결재</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24089,7 +24576,7 @@
           <t>KCS 47 10 25 산림 벌목 시방 | 수목 벌목 및 뿌리 제거(벌근) 깊이 30cm 이상 | 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24099,7 +24586,7 @@
           <t>1) 현장 지반 수목 벌목 시행 ➔ 2) 뿌리 제거(벌근) 깊이 30cm 굴착 ➔ 3) 임목 폐기물 수속 처리 ➔ 4) 벌목 벌근 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24109,7 +24596,7 @@
           <t>현장 수목 벌목 시행, 뿌리 제거(벌근) 깊이 30cm 이상 굴착 및 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24183,7 +24670,7 @@
           <t>폐기물관리법 준수 | 기존 아스콘/콘크리트 구조물 안전 삭평 철거 | 건설 폐기물 성적표 수속</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24193,7 +24680,7 @@
           <t>1) 기존 아스콘/콘크리트 삭평 철거 ➔ 2) 폐기물 분리 수거 &amp; 적재 ➔ 3) 건설 폐기물 위탁 처리 ➔ 4) 지장물 처리 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24203,7 +24690,7 @@
           <t>기존 아스콘/콘크리트 삭평 철거, 건설 폐기물 분리 수거 적재 및 폐기물 성적서 수속</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24277,7 +24764,7 @@
           <t>KCS 47 10 25 가설 도로 | 덤프트럭 진입 가설 도로 폭 6m 포설 | 쇄석 골재(두께 20cm) 부설 &amp; 살수</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24287,7 +24774,7 @@
           <t>1) 가설 도로 폭 6m 성토 굴착 ➔ 2) 쇄석 골재(두께 20cm) 부설 ➔ 3) 10t 롤러 다짐 &amp; 살수 ➔ 4) 진입로 조성 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24297,7 +24784,7 @@
           <t>가설 도로 폭 6m 성토 굴착, 쇄석 골재(두께 20cm) 부설, 10t 롤러 다짐 및 살수 점검</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24371,7 +24858,7 @@
           <t>KCS 47 10 25 배수 시방 | 가배수로(0.6×0.6m) &amp; 가침사지 설치 | 세륜기(깊이 1.2m) 가동 및 배수 검측</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24381,7 +24868,7 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 터파기 ➔ 2) 세륜기(깊이 1.2m) 부설 ➔ 3) 양수 펌프 비치 ➔ 4) 배수 환경 시설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24391,7 +24878,7 @@
           <t>가배수로(0.6×0.6m) &amp; 가침사지 설치, 세륜기(깊이 1.2m) 가동 및 수중 양수 펌프 비치</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24465,7 +24952,7 @@
           <t>KCS 47 10 25 굴착 규정 | 3D GPS 굴착기 표고 오차 ±20mm 통제 | 사면 비탈면 경사(1:1.5) 준수</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24475,7 +24962,7 @@
           <t>1) 3D GPS 굴착기 정밀 세팅 ➔ 2) 토사 깎기 &amp; 사면 비탈면(1:1.5) 굴착 ➔ 3) 표고 오차(±20mm) 검측 ➔ 4) 토공 굴착 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="N27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24485,7 +24972,7 @@
           <t>3D GPS 굴착기 표고 오차 ±20mm 통제, 사면 비탈면 경사(1:1.5 이하) 준수 및 굴착 검측</t>
         </is>
       </c>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="P27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24559,7 +25046,7 @@
           <t>KS F 2310 규정 준수 | 굴착 바닥 원지반 평판재하시험 K30 ≥ 70 MN/m³ | 덤프트럭 펌핑 연약 지반 점검</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24569,7 +25056,7 @@
           <t>1) 굴착 바닥 원지반 수평 정리 ➔ 2) K30 평판재하시험(≥70 MN/m³) ➔ 3) 덤프트럭 펌핑 연약 지반 점검 ➔ 4) 노상토 지지력 성과표 승인</t>
         </is>
       </c>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="N28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24579,7 +25066,7 @@
           <t>굴착 바닥 평판재하시험 K30 ≥ 70 MN/m³, 덤프트럭 펌핑 연약 지반 점검 및 노상토 승인</t>
         </is>
       </c>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="P28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24653,7 +25140,7 @@
           <t>KCS 47 10 25 성토 시방 | 층두께 ≤ 30cm 토사 포설 | 10t 강동 롤러 다짐(들밀도 다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24663,7 +25150,7 @@
           <t>1) 성토 토사 30cm 층포설 ➔ 2) 살수차 최적함수비 살수 ➔ 3) 10t 강동 롤러 다짐(다짐도≥90%) ➔ 4) 성토 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="N29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24673,7 +25160,7 @@
           <t>성토 토사 30cm 층포설, 살수차 최적함수비 OMC 살수 및 10t 롤러 다짐(다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="P29" s="17" t="inlineStr">
+      <c r="P29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24747,7 +25234,7 @@
           <t>현장 통합 소통 수칙 | 일일 TBM 및 품질/안전 지원 대장 수록 | 감리 입회 검측 서면 승인</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
+      <c r="L30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24757,7 +25244,7 @@
           <t>1) 일일 현장 품질/안전 지원 ➔ 2) TBM 및 근로자 교육 ➔ 3) 공정 장애 요소 해소 ➔ 4) 현장 지원 대장 서면 승인</t>
         </is>
       </c>
-      <c r="N30" s="17" t="inlineStr">
+      <c r="N30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24767,7 +25254,7 @@
           <t>일일 현장 품질/안전 지원 대장, TBM 및 근로자 교육 시행 서면 승인</t>
         </is>
       </c>
-      <c r="P30" s="17" t="inlineStr">
+      <c r="P30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24841,7 +25328,7 @@
           <t>KCS 47 10 25 인계인수 수칙 | 토공-강화노반 시공팀 3자 합동 레벨 측량 | 마무리면 인계인수서 서명</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24851,7 +25338,7 @@
           <t>1) 토공-강화노반 시공팀 3자 합동 현측 ➔ 2) 마무리면 레벨 오차(±10mm) 확인 ➔ 3) 인계인수 합의서 서명 ➔ 4) 토공 마무리면 인계 완료</t>
         </is>
       </c>
-      <c r="N31" s="17" t="inlineStr">
+      <c r="N31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24861,7 +25348,7 @@
           <t>토공-강화노반 시공팀 3자 합동 레벨 측량, 마무리면 레벨 오차(±10mm) 인계인수서 서명</t>
         </is>
       </c>
-      <c r="P31" s="17" t="inlineStr">
+      <c r="P31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25169,7 +25656,7 @@
           <t>지하안전관리에 관한 특별법 제23조 | 현장 지반 조사, GPR 탐사 데이터 및 신설 궤도 간섭 리스크 사전 분석 | 지장물 이설 리스크 관리계획 수립</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25179,7 +25666,7 @@
           <t>1) 지반 조사 주상도 &amp; GPR 데이터 대조 ➔ 2) 신설 궤도 구조물 간섭 관로 추출 ➔ 3) 기관별 이설 우선순위 수립 ➔ 4) 지장물 리스크 보고서 결재</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25189,7 +25676,7 @@
           <t>지반 시추 주상도, GPR 3D 지중 관로 탐사 데이터 대조 및 신설 궤도 구조물 간섭 관로 사전 현출 점검</t>
         </is>
       </c>
-      <c r="P2" s="17" t="inlineStr">
+      <c r="P2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25267,7 +25754,7 @@
           <t>KCS 47 10 25 시방 준수 | 도급분 지장물 이설 발주 시방서 검토 &amp; 3D BIM 도면 대조 | 발주처·감리·시공 3자 킥오프 미팅 결재</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25277,7 +25764,7 @@
           <t>1) 도급분 이설 시방서 요구조건 검토 ➔ 2) 3D BIM 도면 관로 좌표 대조 ➔ 3) 공기 지연 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25287,7 +25774,7 @@
           <t>KCS 47 10 25 시방 요구조건, 도급분 지장물 이설 수량 및 3D BIM 도면 간섭 zero 검증</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25365,7 +25852,7 @@
           <t>지방계약법 및 관할 점용기관 규정 | 위수탁 지장물 이설 협약서 작성 &amp; 공문 발송 | 기관별 이설 소요 기간 및 예산 확보</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25375,7 +25862,7 @@
           <t>1) 관할 점용기관 이설 요청 공문 작성 ➔ 2) 이설 협약서 정산 조건 수속 ➔ 3) 기관별 이설 소요 기간 협의 ➔ 4) 위수탁 이설 확약 공문 수령</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25385,7 +25872,7 @@
           <t>위수탁 이설 요청 공문 부착, 점용기관 협약 조건 수속 및 이설 예비비 계상 서약</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25463,7 +25950,7 @@
           <t>건설산업기본법 제29조 | 상하수도 설비 전문건설업 면허 및 적정성(≥ 82%) 평가 | 노무비 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25473,7 +25960,7 @@
           <t>1) 상하수도 전문건설업 면허 심사 ➔ 2) 하도급 적정성(≥ 82%) 평가 ➔ 3) 노무비 전용계좌 개설 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25483,7 +25970,7 @@
           <t>상하수도 전문건설업 면허/실적 심사, 하도급 적정성 평가(≥ 82%) 및 노무비 전용계좌 지정</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25561,7 +26048,7 @@
           <t>지하안전법 수칙 | 한국전력, 도시가스, 수자원공사 1:1 현장 합동 조사 | 매설 위치, 관경(mm), 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25571,7 +26058,7 @@
           <t>1) 한전/가스/수자원공사 1:1 현장 입회 ➔ 2) 관로 위치, 관경(mm), 깊이 현측 ➔ 3) 3D BIM 매설 관로 매핑 ➔ 4) 지장물 조사서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25581,7 +26068,7 @@
           <t>한국전력, 도시가스, 수자원공사 1:1 현장 입회 및 지하 매설물 관경(mm), 심도 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25659,7 +26146,7 @@
           <t>KCS 47 10 25 배수 및 관체 수칙 | 지장물 이설 공정표, 가설 방호 및 교통 우회 계획 수립 | 공사 착수 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25669,7 +26156,7 @@
           <t>1) 지장물 이설 공정표 수립 ➔ 2) 가설 매달기 방호 &amp; 우회 차선 설계 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 이설 계획서 책임감리원 승인</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25679,7 +26166,7 @@
           <t>지장물 이설 공정표 수립, 가설 매달기 방호/우회 차선 설계 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25757,7 +26244,7 @@
           <t>건산법 상생협력 규정 | 지장물 전담 기술자 1:1 현장 배치 | 주간 3자 소통 회의 및 일일 TBM/안전교육 시행</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25767,7 +26254,7 @@
           <t>1) 지장물 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25777,7 +26264,7 @@
           <t>지장물 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM/음주 측정(0.00%)</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25855,7 +26342,7 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 합동 빅룸 회의 | 지장물 간섭 Zero 및 마일스톤 연동 확정</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25865,7 +26352,7 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 지장물 이설 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25875,7 +26362,7 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 지장물 간섭 Zero 및 마일스톤 연동 회의록 서명</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25953,7 +26440,7 @@
           <t>도로법 및 하천법 준수 | 지자체 도로점용 허가 및 하천점용 허가서 접수 | 관련 부서 협의 및 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25963,7 +26450,7 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25973,7 +26460,7 @@
           <t>지자체 도로점용 허가 &amp; 하천점용 허가서 수속, 보증보험 증권 제출 및 법정 인허가 필증 검수</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26051,7 +26538,7 @@
           <t>도로교통법 제69조 | 관할 경찰서 교통안전 심의 및 점용 허가 수령 | 우회 차선 도면 작성 및 안전 신호수 배치</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26061,7 +26548,7 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26071,7 +26558,7 @@
           <t>동탄경찰서 도로점용 허가, 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26149,7 +26636,7 @@
           <t>대기환경보전법 및 소음진동관리법 | 야간 공사 소음 억제 방음벽(H=3m) 및 세륜기 가동 | 단수/단전 사전 안내 및 민원 대응반 가동</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26159,7 +26646,7 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26169,7 +26656,7 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 이동식 세륜기(깊이 1.2m) 가동 및 단수 사전 주민 알림</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26247,7 +26734,7 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단 및 우회 동선</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26257,7 +26744,7 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26267,7 +26754,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26345,7 +26832,7 @@
           <t>수도법 및 하수도법 규정 | 맑은물사업소 합동 이설 위치 검토 &amp; 수돗물 단수 일정 수협 | 신구관 접속 설계도서 서면 결재</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26355,7 +26842,7 @@
           <t>1) 맑은물사업소 이설 위치 현측 ➔ 2) 단수 일정(최대 6시간) 협의 ➔ 3) 신구관 접속 도면 검토 ➔ 4) 이설 승인 공문 수령</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26365,7 +26852,7 @@
           <t>맑은물사업소 합동 이설 위치 검토, 수돗물 단수 일정(최대 6h) 수협 및 신구관 접속 도면 결재</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26443,7 +26930,7 @@
           <t>지하관로 설계기준 준수 | 위수탁 기관 설계도서 기술 검토 &amp; 3D BIM 간섭 점검 | 총사업비 변경 승인 및 설계 도서 수록</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26453,7 +26940,7 @@
           <t>1) 위수탁 기관 설계도서 수속 ➔ 2) 3D BIM 간섭 리스크 점검 ➔ 3) 총사업비 변경 수량 검증 ➔ 4) 위수탁 설계도서 감리 승인</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26463,7 +26950,7 @@
           <t>위수탁 기관 설계도서 기술 검토, 3D BIM 간섭 리스크 점검 및 총사업비 변경 수량 승인</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26541,7 +27028,7 @@
           <t>건진법 시행령 규정 | 현장 지장물 현출에 따른 실정보고서 작성 | 공법 변경 및 수량 증감에 대한 책임감리 승인</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26551,7 +27038,7 @@
           <t>1) 현장 지장물 현출 실정보고 작성 ➔ 2) 공법 변경 &amp; 수량 증감 산출 ➔ 3) 기술 검토 의견서 첨부 ➔ 4) 실정보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26561,7 +27048,7 @@
           <t>현장 지장물 현출 실정보고서 작성, 공법 변경 및 수량 증감 산출 책임감리원 승인</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26639,7 +27126,7 @@
           <t>지방자치단체 계약법 | 관할 점용기관과 위수탁 이설 협약서 정산 조건 체결 | 공사비 분담금 및 예비비 계상 합의</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26649,7 +27136,7 @@
           <t>1) 관할 점용기관 협약 조건 수속 ➔ 2) 정산 분담금 &amp; 예비비 협의 ➔ 3) 위수탁 계약서 작성 ➔ 4) 위수탁 이설 계약 체결 승인</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26659,7 +27146,7 @@
           <t>관할 점용기관 위수탁 이설 협약서 체결, 공사비 분담금 및 예비비 계상 합의 서약</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26737,7 +27224,7 @@
           <t>도로법 제61조 준수 | 지자체 도로 굴착 허가 신청서 접수 및 심의 필 | 도로 복구 이행 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26747,7 +27234,7 @@
           <t>1) 도로 굴착 허가 신청서 작성 ➔ 2) 지자체 도로굴착 심의 필 ➔ 3) 복구 보증보험 증권 제출 ➔ 4) 도로 굴착 허가증 감리 결재</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26757,7 +27244,7 @@
           <t>지자체 도로 굴착 허가 신청서 접수, 심의 필증 수령 및 도로 복구 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26835,7 +27322,7 @@
           <t>도로교통법 안전 수칙 | 게이트 및 굴착 구간 안전 바리케이트, LED 경광등 부설 | 전담 신호수(2인 2조) 100% 현장 배치</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26845,7 +27332,7 @@
           <t>1) 굴착 구간 안전 바리케이트 부설 ➔ 2) 야간 LED 경광등 &amp; 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26855,7 +27342,7 @@
           <t>굴착 구간 안전 바리케이트 부설, 야간 LED 경광등 설치 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="P19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -26933,7 +27420,7 @@
           <t>지하안전법 제23조 | GPR 3D 탐사 후 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) | 실체 관로 노출 및 위치 표지판 비치</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -26943,7 +27430,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 실체 관로 노출 &amp; 위치 매핑 ➔ 4) 지장물 현측표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -26953,7 +27440,7 @@
           <t>GPR 3D 지중 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 실체 관로 노출 매핑</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27031,7 +27518,7 @@
           <t>KCS 47 10 25 굴착 시방 | 굴착 사면 비탈면 경사(1:1.5) 준수 및 흙막이 가설재 부설 | 굴착 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27041,7 +27528,7 @@
           <t>1) 굴착 비탈면 경사(1:1.5) 측량 ➔ 2) 굴착 &amp; 흙막이 가설재 부설 ➔ 3) 바닥 원지반 K30(≥70) 검측 ➔ 4) 굴착 완료 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27051,7 +27538,7 @@
           <t>굴착 비탈면 경사(1:1.5 이하) 측량, 흙막이 가설재 부설 및 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27129,7 +27616,7 @@
           <t>KS 관로 자재 규정 준수 | 신규 상하수도관/가스관 부설 및 모래 기초(두께 10cm) 부설 | 관로 경사(≥ 0.5%) 및 수평 위치 검측</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27139,7 +27626,7 @@
           <t>1) 관로 모래 기초(10cm) 부설 ➔ 2) 신규 상하수도관/가스관 부설 ➔ 3) 관로 종단 구배(≥0.5%) 검측 ➔ 4) 신규 관로 부설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27149,7 +27636,7 @@
           <t>관로 모래 기초(두께 10cm) 부설, 신규 상하수도관/가스관 부설 및 종단 구배(≥ 0.5%) 검측</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27227,7 +27714,7 @@
           <t>수도시설 공학 규정 | 무단수 천공기 및 밸브 차단 장치 정밀 세팅 | 수압 시험 및 밸브 가동 상태 시운전 검측</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27237,7 +27724,7 @@
           <t>1) 무단수 천공기 정밀 세팅 ➔ 2) 차단 밸브 &amp; 챔버 설치 ➔ 3) 수압 시험 및 가동 시운전 ➔ 4) 무단수 시설 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27247,7 +27734,7 @@
           <t>무단수 천공기 정밀 세팅, 차단 밸브 &amp; 챔버 설치 및 수압 시험/가동 시운전 검측</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27325,7 +27812,7 @@
           <t>관로 연결 시방 수칙 | 신구 관로 접속 부위 수압 시험(10kgf/cm², 1시간 유지) | 누수 여부 점검 및 부식 방지 랩핑 부설</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27335,7 +27822,7 @@
           <t>1) 신구 관로 접속 부위 부설 ➔ 2) 수압 시험(10kgf/cm², 1h 유지) ➔ 3) 부식 방지 피복 랩핑 시행 ➔ 4) 관로 접속 검측 성과표 승인</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27345,7 +27832,7 @@
           <t>신구 관로 접속 부위 부설, 수압 시험(10kgf/cm², 1h 유지) 및 부식 방지 피복 랩핑 검측</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27423,7 +27910,7 @@
           <t>폐기물관리법 준수 | 폐관로 수거 및 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 | 아스콘 가포설 및 평탄성 통제</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27433,7 +27920,7 @@
           <t>1) 기존 폐관로 안전 철거/수거 ➔ 2) 토사 30cm 층다짐(다짐도≥95%) ➔ 3) 아스콘 가포설 &amp; 평탄성 검측 ➔ 4) 원상복구 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27443,7 +27930,7 @@
           <t>기존 폐관로 안전 철거/수거, 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 및 아스콘 가포설</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27521,7 +28008,7 @@
           <t>수도법 규정 준수 | 광역상수관(Ø500mm+) 이설 수압 시험 및 수질 검사 합격 | 한국수자원공사 입회 인수 완료</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27531,7 +28018,7 @@
           <t>1) 광역상수관(Ø500mm+) 부설 ➔ 2) 수압 시험 &amp; 수질 검사 시행 ➔ 3) 한국수자원공사 현장 입회 ➔ 4) 광역상수관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27541,7 +28028,7 @@
           <t>광역상수관(Ø500mm+) 부설, 수압 시험 및 수질 검사 합격 (한국수자원공사 1:1 입회 검측)</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27619,7 +28106,7 @@
           <t>지자체 상수도 시방 | 배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 | 맑은물사업소 합동 현측 승인</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27629,7 +28116,7 @@
           <t>1) 배수관(Ø200~300mm) 이설 부설 ➔ 2) 탁수 퇴수 &amp; 잔류염소 시험 ➔ 3) 맑은물사업소 합동 현측 ➔ 4) 상수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="N27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27639,7 +28126,7 @@
           <t>배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 합격 (맑은물사업소 현측)</t>
         </is>
       </c>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="P27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27717,7 +28204,7 @@
           <t>하수도정비 기본계획 | 하수관(Ø400mm+) 연결, CCTV 관로 내부 검사 및 통수 담수 시험 | 하수도사업소 현장 인수</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27727,7 +28214,7 @@
           <t>1) 하수관(Ø400mm+) 연결 부설 ➔ 2) CCTV 관로 내부 검사 시행 ➔ 3) 통수 담수 시험 완료 ➔ 4) 하수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="N28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27737,7 +28224,7 @@
           <t>하수관(Ø400mm+) 연결 부설, CCTV 관로 내부 검사 &amp; 통수 담수 시험 합격 (하수도사업소 인수)</t>
         </is>
       </c>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="P28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27815,7 +28302,7 @@
           <t>도시가스사업법 규정 | 가스관(중압/아중압) 비파괴검사(RT 100%) 및 기밀 시험 합격 | 도시가스사 1:1 입회 검측</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27825,7 +28312,7 @@
           <t>1) 도시가스관 매설 &amp; 용접 ➔ 2) 비파괴검사(RT 100%) &amp; 기밀 시험 ➔ 3) 도시가스사 1:1 입회 검측 ➔ 4) 가스관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="N29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27835,7 +28322,7 @@
           <t>도시가스관 매설 &amp; 용접, 비파괴검사(RT 100%) 및 기밀 시험 합격 (도시가스사 1:1 입회)</t>
         </is>
       </c>
-      <c r="P29" s="17" t="inlineStr">
+      <c r="P29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -27913,7 +28400,7 @@
           <t>집단에너지사업법 규정 | 난방 수송관 100% 비파괴검사 및 보온재 피복 랩핑 검수 | 지역난방공사 시운전 인수</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
+      <c r="L30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -27923,7 +28410,7 @@
           <t>1) 난방 수송관 매설 &amp; 용접 ➔ 2) 100% 비파괴검사 &amp; 피복 랩핑 ➔ 3) 지역난방공사 시운전 인수 ➔ 4) 지역난방관 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="17" t="inlineStr">
+      <c r="N30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -27933,7 +28420,7 @@
           <t>난방 수송관 매설 &amp; 용접, 100% 비파괴검사 및 피복 랩핑 검수 (지역난방공사 인수)</t>
         </is>
       </c>
-      <c r="P30" s="17" t="inlineStr">
+      <c r="P30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28011,7 +28498,7 @@
           <t>전기통신사업법 준수 | 통신 광케이블 관로 부설 및 절연 저항/광손실 실측 | KT/SKT 통신사 광신호 시험 승인</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28021,7 +28508,7 @@
           <t>1) 통신 광케이블 관로 부설 ➔ 2) 광케이블 포설 &amp; 접속 ➔ 3) 절연저항 &amp; 광손실 시험 ➔ 4) KT/SKT 통신사 광신호 승인</t>
         </is>
       </c>
-      <c r="N31" s="17" t="inlineStr">
+      <c r="N31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28031,7 +28518,7 @@
           <t>통신 광케이블 관로 부설, 절연 저항 &amp; 광손실 실측 합격 (KT/SKT 광신호 승인)</t>
         </is>
       </c>
-      <c r="P31" s="17" t="inlineStr">
+      <c r="P31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28109,7 +28596,7 @@
           <t>전기공사업법 규정 | 22.9kV 특고압 전력 관로/맨홀 부설 및 절연내력 시험 | 한전(KEPCO) 현장 입회 휴전 Cut-over</t>
         </is>
       </c>
-      <c r="L32" s="17" t="inlineStr">
+      <c r="L32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28119,7 +28606,7 @@
           <t>1) 22.9kV 특고압 관로/맨홀 부설 ➔ 2) 전력 케이블 인입 &amp; 내력 시험 ➔ 3) 한전 입회 휴전 Cut-over ➔ 4) 전력관로 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N32" s="17" t="inlineStr">
+      <c r="N32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28129,7 +28616,7 @@
           <t>22.9kV 특고압 관로/맨홀 부설, 절연내력 시험 합격 (한전 KEPCO 입회 휴전 Cut-over)</t>
         </is>
       </c>
-      <c r="P32" s="17" t="inlineStr">
+      <c r="P32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28206,7 +28693,7 @@
           <t>송유관안전관리법 규정 | 송유관 비파괴 NDT 검사 및 초음파 탐상 시험 100% | 대한송유관공사 안전 인계</t>
         </is>
       </c>
-      <c r="L33" s="17" t="inlineStr">
+      <c r="L33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28216,7 +28703,7 @@
           <t>1) 송유관 용접 부설 ➔ 2) NDT 비파괴검사 &amp; 초음파 탐상 ➔ 3) 송유관공사 안전 점검 ➔ 4) 송유관 이설 완료 서면 승인</t>
         </is>
       </c>
-      <c r="N33" s="17" t="inlineStr">
+      <c r="N33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28226,7 +28713,7 @@
           <t>송유관 용접 부설, NDT 비파괴검사 및 초음파 탐상 시험 100% 합격 (대한송유관공사 인수)</t>
         </is>
       </c>
-      <c r="P33" s="17" t="inlineStr">
+      <c r="P33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28303,7 +28790,7 @@
           <t>상하수도 총괄 지침 | 신설 관로 수압·수질·CCTV 검사 종합 대장 작성 | 지자체 3자 합동 최종 현현 점검</t>
         </is>
       </c>
-      <c r="L34" s="17" t="inlineStr">
+      <c r="L34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28313,7 +28800,7 @@
           <t>1) 신설 관로 종합 현측 ➔ 2) 수압/수질/CCTV 검사 종합 ➔ 3) 지자체 3자 합동 점검 ➔ 4) 상하수도 최종 점검 대장 승인</t>
         </is>
       </c>
-      <c r="N34" s="17" t="inlineStr">
+      <c r="N34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28323,7 +28810,7 @@
           <t>신설 관로 종합 현측, 수압/수질/CCTV 검사 종합 대장 작성 및 지자체 3자 합동 점검</t>
         </is>
       </c>
-      <c r="P34" s="17" t="inlineStr">
+      <c r="P34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28400,7 +28887,7 @@
           <t>위수탁 총괄 지침 | 위탁기관 1:1 현장 최종 인수 검측 및 3D BIM 준공 도면 대조 | 지장물 이설 준공 보고서</t>
         </is>
       </c>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="L35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28410,7 +28897,7 @@
           <t>1) 위탁기관 1:1 인수 검측 ➔ 2) 3D BIM 준공 도면 대조 ➔ 3) 이설 완료 현장 서명 ➔ 4) 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N35" s="17" t="inlineStr">
+      <c r="N35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28420,7 +28907,7 @@
           <t>위탁기관 1:1 인수 검측, 3D BIM 준공 도면 대조 및 이설 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P35" s="17" t="inlineStr">
+      <c r="P35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28497,7 +28984,7 @@
           <t>지방계약법 정산 수칙 | 실제 실정보고 투입 물량 및 단가 산정 정산서 작성 | 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="L36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28507,7 +28994,7 @@
           <t>1) 실정보고 투입 물량 집계 ➔ 2) 정산 단가 산정 서류 작성 ➔ 3) 정산서 감리 기술 검토 ➔ 4) 정산 금액 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N36" s="17" t="inlineStr">
+      <c r="N36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28517,7 +29004,7 @@
           <t>실정보고 투입 물량 집계, 정산 단가 산정 서류 작성 및 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="P36" s="17" t="inlineStr">
+      <c r="P36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28594,7 +29081,7 @@
           <t>위수탁 정산 규정 | 관할 위탁기관에 최종 정산금 청구서 및 집행 영수증 작성 | 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="L37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28604,7 +29091,7 @@
           <t>1) 위탁기관 정산 청구서 작성 ➔ 2) 증빙 영수증 &amp; 성과표 첨부 ➔ 3) 정산금 지급 수속 ➔ 4) 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="N37" s="17" t="inlineStr">
+      <c r="N37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28614,7 +29101,7 @@
           <t>위탁기관 정산 청구서 작성, 증빙 영수증 &amp; 성과표 부착 및 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="P37" s="17" t="inlineStr">
+      <c r="P37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28691,7 +29178,7 @@
           <t>건진법 설계변경 수칙 | 도급분 및 위수탁분 총사업비 변경 계약 체결 | 발주처 변경 공문 수령 완료</t>
         </is>
       </c>
-      <c r="L38" s="17" t="inlineStr">
+      <c r="L38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28701,7 +29188,7 @@
           <t>1) 설계변경 총사업비 산정 ➔ 2) 도급/위수탁 변경 변경 수속 ➔ 3) 발주처 변경 공문 수령 ➔ 4) 설계변경 정산 최종 승인</t>
         </is>
       </c>
-      <c r="N38" s="17" t="inlineStr">
+      <c r="N38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28711,7 +29198,7 @@
           <t>설계변경 총사업비 산정, 도급/위수탁 변경 변경 수속 및 발주처 변경 공문 수령</t>
         </is>
       </c>
-      <c r="P38" s="17" t="inlineStr">
+      <c r="P38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28788,7 +29275,7 @@
           <t>공정 간섭 관리 지침 | 선행 토공 및 측량 기준점 성과 인수 대장 작성 | 3자 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="L39" s="17" t="inlineStr">
+      <c r="L39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -28798,7 +29285,7 @@
           <t>1) 선행 토공 &amp; 측량 성과 인수 ➔ 2) 현장 지장물 인계인수 ➔ 3) 3자 합동 현측 실시 ➔ 4) 인계인수서 3자 서명 완료</t>
         </is>
       </c>
-      <c r="N39" s="17" t="inlineStr">
+      <c r="N39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -28808,7 +29295,7 @@
           <t>선행 토공 및 측량 성과 인수 대장 작성, 3자 합동 현측 및 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="P39" s="17" t="inlineStr">
+      <c r="P39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -28829,6 +29316,9 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="G43" s="45" t="n"/>
     </row>
@@ -29209,7 +29699,7 @@
           <t>KDS 47 10 00 철도지반 설계기준 준수 | 시추 주상도, GPR 3D 매핑 및 N치 &lt; 4 연약지반 층후 경출 | PVD/DCM 개량 공법 확정</t>
         </is>
       </c>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="168" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29219,7 +29709,7 @@
           <t>1) 시추 주상도 &amp; GPR 3D 매핑 분석 ➔ 2) N치 &lt; 4 연약지반 심도 경계 추출 ➔ 3) PVD/DCM 개량 공법 검토 ➔ 4) 기술사 서명 지반조사 보고서 감리 승인</t>
         </is>
       </c>
-      <c r="N2" s="79" t="inlineStr">
+      <c r="N2" s="168" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29229,7 +29719,7 @@
           <t>시추 주상도 대조, GPR 지중 탐사 3D 매핑 및 N치 &lt; 4 연약지반 층후 경출 (PVD/DCM 개량 승인)</t>
         </is>
       </c>
-      <c r="P2" s="24" t="inlineStr">
+      <c r="P2" s="168" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29303,7 +29793,7 @@
           <t>KCS 47 10 25 시방 검토 | 쇄석 입도 50mm 및 다짐도 ≥ 95% 명시 | 3D BIM 도면 대조 &amp; 리스크 예비비 수립 킥오프 승인</t>
         </is>
       </c>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29313,7 +29803,7 @@
           <t>1) 발주처 시방서 요구조건 분석 ➔ 2) 3D BIM 도면 표고/구배 검증 ➔ 3) 지장물/용지 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="79" t="inlineStr">
+      <c r="N3" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29323,7 +29813,7 @@
           <t>KCS 47 10 25 시방 검토, 쇄석 입도 50mm/다짐도 95% 명시 및 3D BIM 도면 대조 (발주전략 킥오프 결재)</t>
         </is>
       </c>
-      <c r="P3" s="24" t="inlineStr">
+      <c r="P3" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29397,7 +29887,7 @@
           <t>철도안전법 제45조 준수 | 궤도 중심 30m 법정 경계 측량(오차 ≤ 5mm) | 행위신고서 작성 및 운행선안전관리자 1:1 배치</t>
         </is>
       </c>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29407,7 +29897,7 @@
           <t>1) 궤도 중심 30m 법정 경계 측량 ➔ 2) 행위신고서/안전계획서 접수 ➔ 3) 관할 철도운영기관 기술 심의 ➔ 4) 운행선안전관리자 현장 1:1 배치</t>
         </is>
       </c>
-      <c r="N4" s="79" t="inlineStr">
+      <c r="N4" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29417,7 +29907,7 @@
           <t>궤도 중심 30m 법정 경계 측량(오차 ≤ 5mm), 행위신고서 접수 및 운행선안전관리자 1:1 현장 배치</t>
         </is>
       </c>
-      <c r="P4" s="24" t="inlineStr">
+      <c r="P4" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29491,7 +29981,7 @@
           <t>공공측량 작업규정 준수 | 국가 CP/TBM 기준점 인수 및 GRS80 수준측량(폐합오차 ≤ 5mm√K) | 현장 인조점 3개소 매설 성과 확보</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29501,7 +29991,7 @@
           <t>1) 국가 CP/TBM 기준점 인수 ➔ 2) GRS80 수준측량(폐합오차 ≤ 5mm√K) ➔ 3) 현장 인조점 3개소 매설 ➔ 4) 측량 성과표 작성 &amp; 3D BIM 승인</t>
         </is>
       </c>
-      <c r="N5" s="79" t="inlineStr">
+      <c r="N5" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29511,7 +30001,7 @@
           <t>국가 CP/TBM 기준점 인수, GRS80 수준측량(폐합오차 ≤ 5mm√K) 및 현장 인조점 3개소 매설 성과</t>
         </is>
       </c>
-      <c r="P5" s="24" t="inlineStr">
+      <c r="P5" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29585,7 +30075,7 @@
           <t>지하안전관리에 관한 특별법 제23조 | GPR 지중 탐사 &amp; 인력 줄파기(깊이 1.5m) | 점용기관 입회 매달기 방호 및 이설 완료 승인</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29595,7 +30085,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N6" s="79" t="inlineStr">
+      <c r="N6" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29605,7 +30095,7 @@
           <t>GPR 3D 관로 탐사, 인력 시탐 줄파기(깊이 1.5m) 및 점용기관 1:1 현장 입회 매달기 방호</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr">
+      <c r="P6" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29679,7 +30169,7 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 설치 | 3D 우회 토공 동선 수립 및 마일스톤 연동</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29689,7 +30179,7 @@
           <t>1) 미보상 사유지 필지 추출 ➔ 2) 경계 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="N7" s="79" t="inlineStr">
+      <c r="N7" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29699,7 +30189,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="P7" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29773,7 +30263,7 @@
           <t>건산법 상생협력 규정 | 토공 전문 기술자 1:1 전담 배치 | 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM 시행</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29783,7 +30273,7 @@
           <t>1) 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 전담 조직표 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="79" t="inlineStr">
+      <c r="N8" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29793,7 +30283,7 @@
           <t>토공 전담 기술자 1:1 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM/복지 지원</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr">
+      <c r="P8" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29867,7 +30357,7 @@
           <t>건진법 시행령 제89조 | KCS 47 10 25 다짐 수칙(다짐도 ≥ 95%, K30 ≥ 110) 명시 | 착공 14일 전 책임감리단 기술 승인</t>
         </is>
       </c>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29877,7 +30367,7 @@
           <t>1) 시공계획서 표준 8대 목차 작성 ➔ 2) KCS 47 10 25 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 책임감리원 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N9" s="79" t="inlineStr">
+      <c r="N9" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29887,7 +30377,7 @@
           <t>시공계획서 표준 8대 목차, KCS 47 10 25 다짐 수칙 수록 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr">
+      <c r="P9" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29961,7 +30451,7 @@
           <t>건설근로자법 준수 | 공종별 기술 수첩 및 장비 조종원 면허 1:1 현측 | 일일 음주 측정(0.00%) 및 작업조 조직표 승인</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29971,7 +30461,7 @@
           <t>1) 토공 롤러/그레이더 조종원 자격 검증 ➔ 2) 건설기계 면허증 1:1 대조 ➔ 3) 일일 음주 측정 &amp; Safety TBM ➔ 4) 작업조 편성표 감리 승인</t>
         </is>
       </c>
-      <c r="N10" s="79" t="inlineStr">
+      <c r="N10" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29981,7 +30471,7 @@
           <t>조종원/기술자 자격 수첩 1:1 대조, 건설기계 면허증 검증 및 일일 음주 측정(0.00%)/TBM</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr">
+      <c r="P10" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30055,7 +30545,7 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 강동/타이어 롤러 및 3D GPS 모터그레이더 정기검사 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30065,7 +30555,7 @@
           <t>1) 10t+ 강동/타이어 롤러 사양 확정 ➔ 2) 정기검사증 &amp; 등록증 검수 ➔ 3) 3D GPS 수신기/후방 카메라 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="N11" s="79" t="inlineStr">
+      <c r="N11" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30075,7 +30565,7 @@
           <t>자중 10t+ 강동/타이어 롤러 정기검사증, 3D GPS 수신기/후방 카메라 센서 테스트 및 반입 승인</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr">
+      <c r="P11" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30149,7 +30639,7 @@
           <t>KCS 47 10 25 쇄석 입도 규정 | 최대입경 50mm 이하, #200체 통과량 ≤ 5% | 수정다짐 CBR ≥ 30% 성적 산출 및 입도 DB 구축</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30159,7 +30649,7 @@
           <t>1) 석산 공급원 사전 승인 수속 ➔ 2) 쇄석 입도(Dmax 50mm) 체가름 시험 ➔ 3) 수정다짐 CBR(≥30%) 성적 산출 ➔ 4) 노반 재료 입도 DB 감리 승인</t>
         </is>
       </c>
-      <c r="N12" s="79" t="inlineStr">
+      <c r="N12" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30169,7 +30659,7 @@
           <t>쇄석 최대입경(Dmax ≤ 50mm), #200체 통과량(≤ 5%) 및 수정다짐 CBR(≥ 30%) 성적서 DB</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="P12" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30243,7 +30733,7 @@
           <t>토양환경보전법 준수 | 화성시 정식 사토장 인허가 확인 | 최대건조밀도 γd max ≥ 1.90g/cm³ &amp; 토양오염 8개 항목 검사 완수</t>
         </is>
       </c>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30253,7 +30743,7 @@
           <t>1) 화성시 정식 사토장 허가 검증 ➔ 2) γd max ≥ 1.90g/cm³ &amp; 오염 시험 ➔ 3) 덤프 운행 송장 일일 집계 ➔ 4) 사토 계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N13" s="79" t="inlineStr">
+      <c r="N13" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30263,7 +30753,7 @@
           <t>화성시 정식 사토장 인허가, 최대건조밀도 γd max ≥ 1.90g/cm³ 및 토양오염 8개 항목 검사 합격</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr">
+      <c r="P13" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30337,7 +30827,7 @@
           <t>KCS 47 10 25 임시 배수 시방 | 성토 사면 가배수로(0.6×0.6m) &amp; 가침사지 2개소 | HDPE 유공관(Ø200mm, 구배 ≥ 0.5%) 부설</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30347,7 +30837,7 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 설계 ➔ 2) HDPE 유공관(Ø200mm) 자재 검수 ➔ 3) 비상 양수 펌프(200L/min) 비치 ➔ 4) 배수 처리 계획서 감리 승인</t>
         </is>
       </c>
-      <c r="N14" s="79" t="inlineStr">
+      <c r="N14" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30357,7 +30847,7 @@
           <t>성토 사면 가배수로(0.6×0.6m), 가침사지 2개소 및 HDPE 유공관(Ø200mm, 구배 ≥ 0.5%) 설치</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="P14" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30431,7 +30921,7 @@
           <t>건진법 제62조 준수 | 국토안전관리원 전산 적정 심사 필 | CSI 건설공사 안전관리 종합망 전산 등록 및 감리 승인</t>
         </is>
       </c>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30441,7 +30931,7 @@
           <t>1) 건진법 제62조 안전관리계획 작성 ➔ 2) 국토안전관리원 전산 적정 심사 ➔ 3) CSI 안전관리 종합망 등록 ➔ 4) 책임감리원 서면 승인</t>
         </is>
       </c>
-      <c r="N15" s="79" t="inlineStr">
+      <c r="N15" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30451,7 +30941,7 @@
           <t>건진법 제62조 안전관리계획서 작성, 국토안전관리원 적정 심사 및 CSI 전산망 등록 결재</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr">
+      <c r="P15" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30525,7 +31015,7 @@
           <t>건진법 제55조 준수 | 노반 다짐도(500m³당 1회), K30(2,000m²당 1회), Ev2(1,000m²당 1회) | 현장 시험실 장비 교정 검수</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30535,7 +31025,7 @@
           <t>1) 다짐도/K30/Ev2 시험 빈도 수립 ➔ 2) 현장 시험실 장비 교정 검수 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 품질관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="79" t="inlineStr">
+      <c r="N16" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30545,7 +31035,7 @@
           <t>노반 다짐도(500m³당 1회), K30(2,000m²당 1회), Ev2(1,000m²당 1회) 시험 빈도 &amp; 장비 교정</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr">
+      <c r="P16" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30619,7 +31109,7 @@
           <t>대기환경보전법 제44조 | 지자체 비산먼지 발생사업 신고 필 | 이동식 세륜기(깊이 1.2m) &amp; 가설 방음벽(H=3m) 가동</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30629,7 +31119,7 @@
           <t>1) 세륜기(깊이 1.2m) &amp; 방음벽(3m) 설계 ➔ 2) 지자체 비산먼지 발생신고 ➔ 3) 살수차 1일 3회 살수 ➔ 4) 환경관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N17" s="79" t="inlineStr">
+      <c r="N17" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30639,7 +31129,7 @@
           <t>지자체 비산먼지 발생신고 필증, 이동식 세륜기(깊이 1.2m) &amp; 가설 방음벽(H=3m) 가동 점검</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr">
+      <c r="P17" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30713,7 +31203,7 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 도로점용 허가 수령 | 전담 안전 신호수(2인 2조) 및 LED 경광등 배치</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30723,7 +31213,7 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N18" s="79" t="inlineStr">
+      <c r="N18" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30733,7 +31223,7 @@
           <t>동탄경찰서 도로점용 허가, 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr">
+      <c r="P18" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30807,7 +31297,7 @@
           <t>건산법 제29조 준수 | 토공 전문건설업 면허 및 하도급율(≥ 82%) 적정성 심사 | 노무비 지급 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30817,7 +31307,7 @@
           <t>1) 토공 전문 면허 &amp; 실적 심사 ➔ 2) 하도급 적정성 평가(≥82%) ➔ 3) 노무비 지급 전용계좌 지정 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N19" s="79" t="inlineStr">
+      <c r="N19" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30827,7 +31317,7 @@
           <t>토공 전문건설업 면허/실적 심사, 하도급 비율(≥ 82%) 평가 및 노무비 지급 전용계좌 지정</t>
         </is>
       </c>
-      <c r="P19" s="24" t="inlineStr">
+      <c r="P19" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30901,7 +31391,7 @@
           <t>KCS 47 10 25 자재 검수 | KS F 2527 쇄석골재, HDPE 유공관, 부직포(200g/m²) 공인성적서 | 현장 반입 검수 및 승인 통보</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -30911,7 +31401,7 @@
           <t>1) KS F 2527 쇄석/유공관 서류 검토 ➔ 2) 공인시험기관 시험성적서 부착 ➔ 3) 자재 승인 신청서 제출 ➔ 4) 자재 반입 검수 및 승인 결재</t>
         </is>
       </c>
-      <c r="N20" s="79" t="inlineStr">
+      <c r="N20" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -30921,7 +31411,7 @@
           <t>KS F 2527 쇄석골재, HDPE 유공관, 투수성 부직포(200g/m²) 공인성적서 및 현장 반입 검수</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr">
+      <c r="P20" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -30995,7 +31485,7 @@
           <t>KCS 47 10 25 현장 시험 수칙 | 50m 시험 구간 쇄석 30cm 부설 | 패스별 침하량 실측(침하 정지 Δh ≤ 1mm) 강동 4회 다짐 확정</t>
         </is>
       </c>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31005,7 +31495,7 @@
           <t>1) 50m 시험 다짐 구간 지정 ➔ 2) 쇄석 30cm 두께 포설 ➔ 3) 패스별 침하량(Δh≤1mm) 측정 ➔ 4) 다짐 횟수(강동 4회) 보고서 승인</t>
         </is>
       </c>
-      <c r="N21" s="79" t="inlineStr">
+      <c r="N21" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31015,7 +31505,7 @@
           <t>50m 시험 구간 쇄석 30cm 포설, 패스별 침하량(Δh ≤ 1mm) 실측 및 강동 4회 다짐 횟수 확정</t>
         </is>
       </c>
-      <c r="P21" s="24" t="inlineStr">
+      <c r="P21" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31089,7 +31579,7 @@
           <t>KCS 47 10 25 원지반 규정 | 유기질 표토(15~30cm) 제거 및 전압 다짐 | 원지반 K30 ≥ 70 MN/m³ 시험 &amp; 덤프트럭 펌핑 점검</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31099,7 +31589,7 @@
           <t>1) 표토(15~30cm) 제거 &amp; 정전압 다짐 ➔ 2) 원지반 표고 레벨 측량 ➔ 3) K30(≥70 MN/m³) &amp; 펌핑 검측 ➔ 4) 원지반 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N22" s="79" t="inlineStr">
+      <c r="N22" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31109,7 +31599,7 @@
           <t>유기질 표토(15~30cm) 제거전압 다짐, 원지반 K30 ≥ 70 MN/m³ 평판재하 및 덤프 펌핑 점검</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr">
+      <c r="P22" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31183,7 +31673,7 @@
           <t>KCS 47 10 25 하부노반 시방 | 토사 층두께 ≤ 30cm 포설 다짐 | 들밀도 다짐도 ≥ 90% (KS F 2311) &amp; K30 ≥ 90 MN/m³ 검측</t>
         </is>
       </c>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31193,7 +31683,7 @@
           <t>1) 하부노반 30cm 층포설 &amp; 다짐 ➔ 2) 들밀도(≥90%) &amp; K30(≥90) 시험 ➔ 3) 마무리면 레벨 오차(±20mm) 검측 ➔ 4) 하부노반 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="79" t="inlineStr">
+      <c r="N23" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31203,7 +31693,7 @@
           <t>토사 층두께 ≤ 30cm 포설 다짐, 들밀도 다짐도 ≥ 90% (KS F 2311) 및 K30 ≥ 90 MN/m³ 검측</t>
         </is>
       </c>
-      <c r="P23" s="24" t="inlineStr">
+      <c r="P23" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31277,7 +31767,7 @@
           <t>KCS 47 10 25 상부노반 시방 | 토사 30cm 포설 다짐 | 맹암거 투수성 부직포(200g/m²) &amp; HDPE 유공관(Ø200mm) 매몰 검측</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31287,7 +31777,7 @@
           <t>1) 상부노반 토사 30cm 포설 ➔ 2) 맹암거 부직포(200g/m²) 부설 ➔ 3) HDPE 유공관(Ø200mm) 종단 연결 ➔ 4) 상부노반 시공 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N24" s="79" t="inlineStr">
+      <c r="N24" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31297,7 +31787,7 @@
           <t>상부노반 토사 30cm 포설, 맹암거 투수성 부직포(200g/m²) 및 HDPE 유공관(Ø200mm) 매몰 검측</t>
         </is>
       </c>
-      <c r="P24" s="24" t="inlineStr">
+      <c r="P24" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31371,7 +31861,7 @@
           <t>KCS 47 10 25 강화노반 쇄석 시방 | 3D GPS 쇄석(50mm) 30cm 포설 | 최적함수비 OMC 살수 &amp; 강동 4회/타이어 2회 다짐 (표고 오차 ±10mm)</t>
         </is>
       </c>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31381,7 +31871,7 @@
           <t>1) 3D GPS 모터그레이더 쇄석(50mm) 30cm 포설 ➔ 2) 살수차 최적함수비 OMC 살수 ➔ 3) 강동 4회 + 타이어 2회 다짐 ➔ 4) 표고 오차(±10mm) 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="79" t="inlineStr">
+      <c r="N25" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31391,7 +31881,7 @@
           <t>3D GPS 쇄석(50mm) 30cm 포설, OMC 분무 살수 및 강동 4회/타이어 2회 다짐 (표고 오차 ±10mm)</t>
         </is>
       </c>
-      <c r="P25" s="24" t="inlineStr">
+      <c r="P25" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31465,7 +31955,7 @@
           <t>KCS 47 10 25 다짐 검측 수칙 | 노반 들밀도 다짐도 ≥ 95% | K30 ≥ 110 MN/m³ &amp; 동적변형계수 Ev2 ≥ 60 MPa (Ev2/Ev1 ≤ 2.2) 검측</t>
         </is>
       </c>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31475,7 +31965,7 @@
           <t>1) 들밀도 시험(다짐도 ≥ 95%) ➔ 2) K30 평판재하시험(≥ 110 MN/m³) ➔ 3) 동적변형계수 Ev2(≥ 60 MPa) 시험 ➔ 4) 다짐 검측 종합 보고서 승인</t>
         </is>
       </c>
-      <c r="N26" s="79" t="inlineStr">
+      <c r="N26" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31485,7 +31975,7 @@
           <t>노반 들밀도 다짐도 ≥ 95%, 평판재하 K30 ≥ 110 MN/m³ 및 동적변형계수 Ev2 ≥ 60 MPa (Ev2/Ev1 ≤ 2.2)</t>
         </is>
       </c>
-      <c r="P26" s="24" t="inlineStr">
+      <c r="P26" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31559,7 +32049,7 @@
           <t>KS F 2310 규정 준수 | Ø300mm 재하판 산모래 밀착 및 15t 유압 잭 하중 재하 | 1.25mm 침하 P-S 곡선 산출 K30 ≥ 110 MN/m³ 성적서</t>
         </is>
       </c>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31569,7 +32059,7 @@
           <t>1) Ø300mm 재하판 산모래 밀착 ➔ 2) 15t 유압 잭 &amp; 다이얼 게이지 교정 ➔ 3) 1.25mm 침하 P-S 곡선 산출 ➔ 4) K30 ≥ 110 MN/m³ 성적서 승인</t>
         </is>
       </c>
-      <c r="N27" s="79" t="inlineStr">
+      <c r="N27" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31579,7 +32069,7 @@
           <t>Ø300mm 재하판 산모래 밀착, 15t 유압 잭 재하 및 1.25mm 침하 P-S 곡선 K30 ≥ 110 MN/m³ 성적서</t>
         </is>
       </c>
-      <c r="P27" s="24" t="inlineStr">
+      <c r="P27" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31653,7 +32143,7 @@
           <t>DIN 18134 규정 준수 | LWD 동적 평판재하시험 1,000m²당 1회 | 2차 변형계수 Ev2 ≥ 60 MPa &amp; 변형계수 비율 Ev2/Ev1 ≤ 2.2 검측</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31663,7 +32153,7 @@
           <t>1) LWD 동적 평판재하시험기 교정 ➔ 2) 1,000m²당 1회 무작위 시험 ➔ 3) 1차/2차 하중 재하 Ev2/Ev1 산출 ➔ 4) Ev2 ≥ 60 MPa 성적서 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="79" t="inlineStr">
+      <c r="N28" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31673,7 +32163,7 @@
           <t>LWD 동적 평판재하시험 1,000m²당 1회, 2차 변형계수 Ev2 ≥ 60 MPa 및 비율 Ev2/Ev1 ≤ 2.2 검측</t>
         </is>
       </c>
-      <c r="P28" s="24" t="inlineStr">
+      <c r="P28" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31747,7 +32237,7 @@
           <t>KCS 47 10 25 평탄성 수칙 | 3m 알루미늄 직선자 20m 간격 연속 측정 | 최대 갭 오차 ±10mm 이내 통제 &amp; 요철 부위 삭평 재다짐</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31757,7 +32247,7 @@
           <t>1) 3m 알루미늄 직선자 교정 ➔ 2) 20m 간격 종횡단 연속 검측 ➔ 3) 갭 오차(±10mm) 요철 삭평/재다짐 ➔ 4) 평탄성 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N29" s="79" t="inlineStr">
+      <c r="N29" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31767,7 +32257,7 @@
           <t>3m 알루미늄 직선자 20m 간격 연속 측정, 최대 갭 오차 ±10mm 이내 통제 및 요철 삭평/재다짐</t>
         </is>
       </c>
-      <c r="P29" s="24" t="inlineStr">
+      <c r="P29" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31841,7 +32331,7 @@
           <t>KCS 47 10 25 측량 지침 | GRS80 광학 토탈스테이션 10m 간격 연속 측량 | 중심선(X,Y) 및 표고(Z) 오차 ±10mm 3D BIM 검측</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31851,7 +32341,7 @@
           <t>1) GRS80 토탈스테이션 정밀 세팅 ➔ 2) 10m 간격 중심선 &amp; 표고 실측 ➔ 3) 3D BIM CAD 좌표(오차 ±10mm) 대조 ➔ 4) 종횡단 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="79" t="inlineStr">
+      <c r="N30" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31861,7 +32351,7 @@
           <t>GRS80 광학 토탈스테이션 10m 간격 측정, 궤도 중심선(X,Y) 및 표고(Z) 오차 ±10mm 3D BIM 검측</t>
         </is>
       </c>
-      <c r="P30" s="24" t="inlineStr">
+      <c r="P30" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -31935,7 +32425,7 @@
           <t>건진법 NCR 조치 절차 | 감리단 부적합 통지서 수령 후 표면 15cm 파쇄 | OMC 살수 재다짐 및 1:1 재검측 NCR 서면 종결 승인</t>
         </is>
       </c>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -31945,7 +32435,7 @@
           <t>1) 감리단 NCR 통지서 수령 ➔ 2) 해당 구역 표면 15cm 파쇄 &amp; OMC 재다짐 ➔ 3) 1:1 재검측(다짐도/K30/Ev2) ➔ 4) NCR 조치 결과 보고서 감리 종결 승인</t>
         </is>
       </c>
-      <c r="N31" s="79" t="inlineStr">
+      <c r="N31" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -31955,7 +32445,7 @@
           <t>감리단 부적합(NCR) 수령 후 해당 구역 표면 15cm 파쇄, OMC 살수 재다짐 및 1:1 재검측 서면 종결</t>
         </is>
       </c>
-      <c r="P31" s="24" t="inlineStr">
+      <c r="P31" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32029,7 +32519,7 @@
           <t>KCS 47 10 25 성토 사면 수칙 | 사면 비탈면 경사(1:1.5 이하) 측량 | 사면 다짐도 ≥ 90% 검측 &amp; 식생 거적 덮개(Jute Mat) 부설</t>
         </is>
       </c>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32039,7 +32529,7 @@
           <t>1) 성토 사면 경사(1:1.5 이하) 측량 ➔ 2) 사면 다짐도(≥ 90%) 검측 ➔ 3) 식생 거적(Jute Mat) 30cm 겹침 부설 ➔ 4) 사면 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N32" s="79" t="inlineStr">
+      <c r="N32" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32049,7 +32539,7 @@
           <t>성토 사면 비탈면 경사(1:1.5 이하) 측량, 사면 다짐도 ≥ 90% 검측 및 식생 거적(Jute Mat) 부설</t>
         </is>
       </c>
-      <c r="P32" s="24" t="inlineStr">
+      <c r="P32" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32123,7 +32613,7 @@
           <t>KCS 47 10 25 노반 배수 시방 | U형 측구(0.4×0.4m, 버림 10cm) 부설 | 집수정 인버트 모타르 사춤, 주철 그레이팅 체결 &amp; 담수 시험</t>
         </is>
       </c>
-      <c r="L33" s="24" t="inlineStr">
+      <c r="L33" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32133,7 +32623,7 @@
           <t>1) U형 측구 기초 버림(10cm) 타설 ➔ 2) U형 측구(0.4×0.4m) 부설 &amp; 인버트 사춤 ➔ 3) 주철 그레이팅 체결 &amp; 담수 시험 ➔ 4) 배수시설 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N33" s="79" t="inlineStr">
+      <c r="N33" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32143,7 +32633,7 @@
           <t>U형 측구(0.4×0.4m, 버림 10cm) 부설, 집수정 인버트 모타르 사춤 및 주철 그레이팅 체결/담수 시험</t>
         </is>
       </c>
-      <c r="P33" s="24" t="inlineStr">
+      <c r="P33" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32217,7 +32707,7 @@
           <t>KCS 47 10 25 완성면 관리 규정 | 통제 바리케이트(중장비 진입 100% 차단) | 미세 분무 살수(골재이탈 예방) &amp; 완성면 보호 대장 작성</t>
         </is>
       </c>
-      <c r="L34" s="24" t="inlineStr">
+      <c r="L34" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32227,7 +32717,7 @@
           <t>1) 완성면 통제 바리케이트 설치 ➔ 2) 미세 분무 살수 &amp; 비닐 덮개 야적 ➔ 3) 일일 완성면 훼손 점검 ➔ 4) 완성면 보호 점검 대장 감리 승인</t>
         </is>
       </c>
-      <c r="N34" s="79" t="inlineStr">
+      <c r="N34" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32237,7 +32727,7 @@
           <t>통제 바리케이트(중장비 진입 100% 차단), 미세 분무 살수(골재이탈 예방) 및 완성면 보호 대장 작성</t>
         </is>
       </c>
-      <c r="P34" s="24" t="inlineStr">
+      <c r="P34" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32311,7 +32801,7 @@
           <t>건진법 시행규칙 공사기록 | 일일 투입 인원, 장비, 성토 물량(m³) 정밀 집계 | CSI 건설공사 관리 시스템 전산 등록 &amp; 감리 일일 직인</t>
         </is>
       </c>
-      <c r="L35" s="24" t="inlineStr">
+      <c r="L35" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32321,7 +32811,7 @@
           <t>1) 일일 인원/장비/물량 집계 ➔ 2) 품질 시험 성적 &amp; TBM 수록 ➔ 3) CSI 전산 시스템 등록 ➔ 4) 책임감리원 일일 서면 직인 결재</t>
         </is>
       </c>
-      <c r="N35" s="79" t="inlineStr">
+      <c r="N35" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32331,7 +32821,7 @@
           <t>일일 투입 인원/장비/성토 물량(m³) 집계, CSI 전산 관리 시스템 등록 및 감리 일일 서면 직인</t>
         </is>
       </c>
-      <c r="P35" s="24" t="inlineStr">
+      <c r="P35" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32405,7 +32895,7 @@
           <t>건진법 &amp; KCS 47 10 25 총괄 수칙 | 공사 착수 24시간 전 검측 요청서 제출 | 책임감리원 1:1 현장 입회 &amp; 16개 체크리스트 서명 대장</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32415,7 +32905,7 @@
           <t>1) 공종별 검측요청서 24시간 전 제출 ➔ 2) 책임감리원 1:1 현장 입회 ➔ 3) 16개 체크리스트 서명 ➔ 4) 검측 총괄 승인 대장 감리 결재</t>
         </is>
       </c>
-      <c r="N36" s="79" t="inlineStr">
+      <c r="N36" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32425,7 +32915,7 @@
           <t>공사 착수 24시간 전 검측 요청서 제출, 책임감리원 1:1 현장 입회 및 16개 체크리스트 서명 대장</t>
         </is>
       </c>
-      <c r="P36" s="24" t="inlineStr">
+      <c r="P36" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32499,7 +32989,7 @@
           <t>KCS 47 10 25 최종 인계인수 | 토공-궤도-감리 3자 합동 현측(표고 ±10mm, K30 ≥ 110) | 인계인수 합의서 서명 및 노반 완공 통보</t>
         </is>
       </c>
-      <c r="L37" s="24" t="inlineStr">
+      <c r="L37" s="168" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -32509,7 +32999,7 @@
           <t>1) 3자(토공-궤도-감리) 합동 현측 ➔ 2) 표고(±10mm) &amp; K30(≥110) 재검측 ➔ 3) 인계인수 합의서 3자 서명 ➔ 4) 상부강화노반 최종 완공 통보</t>
         </is>
       </c>
-      <c r="N37" s="79" t="inlineStr">
+      <c r="N37" s="168" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -32519,7 +33009,7 @@
           <t>토공-궤도-감리 3자 합동 현측(표고 ±10mm, K30 ≥ 110), 인계인수 합의서 서명 및 완공 통보</t>
         </is>
       </c>
-      <c r="P37" s="24" t="inlineStr">
+      <c r="P37" s="168" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -32845,7 +33335,7 @@
           <t>KDS 47 30 00 궤도 설계기준 및 국토교통부 트램 건설 규칙을 엄격히 준수한다. 노반부-궤도부 선형 및 종단 계획고 일치 오차 0mm 검토.</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32856,7 +33346,7 @@
 2) 궤도 정밀 검측: 궤간(1435mm), 캔트(±2mm), 수평(±2mm), 고저(±2mm/10m), 비틀림(1.5mm/3m) 실시간 검측</t>
         </is>
       </c>
-      <c r="N2" s="53" t="inlineStr">
+      <c r="N2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32866,7 +33356,7 @@
           <t>설계 도면 간섭 검속, 궤도 중심선 계획 표고 대조, 종단 구배 한계치 준수 확인</t>
         </is>
       </c>
-      <c r="P2" s="53" t="inlineStr">
+      <c r="P2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32941,7 +33431,7 @@
           <t>침목, 체결구, 홈레일 등 궤도 주요 자재의 현장 보관 기준 수립. 배수 경사 2% 및 지반 다짐도 95% 이상 야적장 확보.</t>
         </is>
       </c>
-      <c r="L3" s="53" t="inlineStr">
+      <c r="L3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32952,7 +33442,7 @@
 2) 장대레일 운반 트레일러(길이 30m 이상) 회전반경 및 크레인 인양 진입로 확보</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32962,7 +33452,7 @@
           <t>야적장 지반 다짐도 95% 이상, 배수 경사 2% 이상 확보, 자재 천막 덮개 구비</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33037,7 +33527,7 @@
           <t>EN 14730 테르밋 및 EN 14587 가스압접 용접을 위한 작업 공간 확보. 정척레일(25m)을 200m 장대로 용접하는 평탄 작업대 수평 오차 ±1mm 이내 확보.</t>
         </is>
       </c>
-      <c r="L4" s="53" t="inlineStr">
+      <c r="L4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33048,7 +33538,7 @@
 2) 가스압접/플래시버트 용접용 대용량 전력 및 아세틸렌/산소 가스 안전 저장소 확보</t>
         </is>
       </c>
-      <c r="N4" s="53" t="inlineStr">
+      <c r="N4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33058,7 +33548,7 @@
           <t>용접장 평탄성 오차 ±1mm 이내, 전력 공급 및 방풍 시설 완비, NDT(비파괴) 대기 공간 확보</t>
         </is>
       </c>
-      <c r="P4" s="53" t="inlineStr">
+      <c r="P4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33138,7 +33628,7 @@
           <t>KCS 47 30 00 시방 기준 준수. 궤도 자재 품질 확인서 및 외산 홈레일 조달 리스크 대응 전략 수립.</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
+      <c r="L5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33149,7 +33639,7 @@
 2) KDS 47 30 00 및 KS 규격 만족 자재 목록 및 세부 발주 물량 확정</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33159,7 +33649,7 @@
           <t>품질 요구조건 특기시방서 의결, 외산 홈레일 선적일정 검토, 자재 인도 시점 확약</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33234,7 +33724,7 @@
           <t>EN ISO 9606-1 용접 자격자 및 궤도 정밀 검측원(Track Master 운용원) 확보 심사 기준.</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33245,7 +33735,7 @@
 2) 스핀들 게이지 조정, 캔트 달성구배, 테르밋 산화반응 제어 사전 모의 훈련</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33255,7 +33745,7 @@
           <t>용접공 자격증 원본 대조, 정밀 검측 장비 검교정 확인, 궤도 전문 기술사 면허 검토</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33331,7 +33821,7 @@
           <t>KCS 47 30 00 콘크리트 궤도 시방 준수. 펌프카 타설압력에 의한 궤광 변위 방지 지지 계획 수립.</t>
         </is>
       </c>
-      <c r="L7" s="53" t="inlineStr">
+      <c r="L7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33342,7 +33832,7 @@
 2) 레미콘 운반시간(60분 이내) 및 펌프카 배치 공간 사전 확보</t>
         </is>
       </c>
-      <c r="N7" s="53" t="inlineStr">
+      <c r="N7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33352,7 +33842,7 @@
           <t>구간별 펌프카 배치도 작성, 타설 시 궤광 고정 잭 지지 계획 승인, 콘크리트 슬럼프 품질 확인</t>
         </is>
       </c>
-      <c r="P7" s="53" t="inlineStr">
+      <c r="P7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33435,7 +33925,7 @@
           <t>노반-궤도 간 인터페이스, 신호 루프 센서 및 누설 전류(Stray Current) 부식 방지 디오드 접지선 매설 계획 의결.</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33446,7 +33936,7 @@
 2) 도로 매설 궤도 표면과 도로 포장 표면 마감 높이 일치성 확정</t>
         </is>
       </c>
-      <c r="N8" s="53" t="inlineStr">
+      <c r="N8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33456,7 +33946,7 @@
           <t>신호 센서 매설 위치 철근 간섭 해결, 접지선 용접부 연속성 확인, 부서 합동 서명 날인</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33531,7 +34021,7 @@
           <t>장대레일 운반 트레일러(길이 25m 이상) 도로 회전 반경 R=15m 확보 및 타공종 가설재 간섭 배제.</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33542,7 +34032,7 @@
 2) 전담 신호수 배치 및 대형 레일 운반 차량 유도</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33552,7 +34042,7 @@
           <t>트레일러 회전 시뮬레이션 승인, 가설 비계 간섭 범위 해제, 도로 점용 허가 필증 확인</t>
         </is>
       </c>
-      <c r="P9" s="53" t="inlineStr">
+      <c r="P9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33627,7 +34117,7 @@
           <t>홈레일, 체결구, 탄성 충전재 등 주요 자재의 해상 운송 및 국내 보관 일정 검토. OMC 품질 시방 확보.</t>
         </is>
       </c>
-      <c r="L10" s="53" t="inlineStr">
+      <c r="L10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33638,7 +34128,7 @@
 2) PST 슬래브 공장 생산 강도 및 홈레일 단면 검수</t>
         </is>
       </c>
-      <c r="N10" s="53" t="inlineStr">
+      <c r="N10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33648,7 +34138,7 @@
           <t>선적 서류 및 통관 승인서 구비, 국내 야적장 2차 보관 상태 점검, 자재 공급 승인서 확인</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33724,7 +34214,7 @@
           <t>KDS 47 30 00 및 EN 규격 기준 자재 발주서 승인. 공급원 검토 승인 요청서 작성 요령 준수.</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33735,7 +34225,7 @@
 2) 공장 검사(FAT) 조건 및 성적서 첨부 명시</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33745,7 +34235,7 @@
           <t>자재 발주 수량 설계 대조, 공급원 승인 필증 원본 확인, 발주 공문 승인 요청</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33821,7 +34311,7 @@
           <t>콘크리트도상 시공 절차 및 공정 스케줄 작성. 궤간(+3,-1mm), 캔트(±2mm) 관리계획 수립.</t>
         </is>
       </c>
-      <c r="L12" s="53" t="inlineStr">
+      <c r="L12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33832,7 +34322,7 @@
 2) 스핀들 게이지 조정, 테르밋 용접(EN 14730) 및 TCL 콘크리트 타설 수칙 수립</t>
         </is>
       </c>
-      <c r="N12" s="53" t="inlineStr">
+      <c r="N12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33842,7 +34332,7 @@
           <t>시공계획서 감리단 최종 승인, 선형 관리 한계선 설정 확인, 품질보증계획서 제출</t>
         </is>
       </c>
-      <c r="P12" s="53" t="inlineStr">
+      <c r="P12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33917,7 +34407,7 @@
           <t>반입 자재의 공장 성적서 대조 및 감리 입회 자재 인수 검사 수행. 변형/균열 자재 전량 반출.</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33928,7 +34418,7 @@
 2) 레일 표면 흠집 및 PST 패널 치수 오차(±2mm) 측정</t>
         </is>
       </c>
-      <c r="N13" s="53" t="inlineStr">
+      <c r="N13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33938,7 +34428,7 @@
           <t>인수 검서 보고서 감리 서명, 자재 고유 마킹 대조, 손상 자재 반출 대장 기록</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34014,7 +34504,7 @@
           <t>기초 노반 표면의 지지력 검증. 평판재하시험 K30 ≥ 110 MN/m³ 또는 Ev2 ≥ 120 MPa 확인.</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34025,7 +34515,7 @@
 2) 노반 높이 오차(±10mm 이내) 광학 레벨 측량 검증</t>
         </is>
       </c>
-      <c r="N14" s="53" t="inlineStr">
+      <c r="N14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34035,7 +34525,7 @@
           <t>K30 성적서 원본 대조, 노반 마무리면 요철 제거 상태, 횡단 구배 2.0% 만족 확인</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34110,7 +34600,7 @@
           <t>강화노반 상부 기초콘크리트(HBR) 28일 압축강도 ≥ 21 MPa 확보. 고주파 다짐 및 습윤 양생 7일.</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34121,7 +34611,7 @@
 2) 콜드조인트 방지 연속 타설 및 바이브레이터 밀실 다짐</t>
         </is>
       </c>
-      <c r="N15" s="53" t="inlineStr">
+      <c r="N15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34131,7 +34621,7 @@
           <t>HBR 강도 시험 성적서, 습윤 부직포 포설 상태, 타설 두께 오차 ±10mm 이내 검속</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34207,7 +34697,7 @@
           <t>PC 슬래브 패널 평탄성 오차 ±3mm 이내 거치. 광학 토탈스테이션 연동 정밀 3D 얼라인먼트.</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34218,7 +34708,7 @@
 2) 점 인양 빔으로 패널 거치 후 스핀들 게이지 정밀 수평 조정</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34228,7 +34718,7 @@
           <t>Screw Jack 레벨 정위치 고정, 3D 광학 실측 좌표 일치, 코너 크랙 육안 검사</t>
         </is>
       </c>
-      <c r="P16" s="53" t="inlineStr">
+      <c r="P16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34304,7 +34794,7 @@
           <t>전단앵커 구멍 천공 깊이 및 수직도 확보. 무수축 모르타르 그라우트 압축강도 ≥ 30 MPa 충전.</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34315,7 +34805,7 @@
 2) 음향 탐사로 공기 공동 파악 및 45 MPa 몰드 시험 확인</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34325,7 +34815,7 @@
           <t>천공 깊이 측정 게이지 점검, 앵커 인장 강도 확인, 원웨이 주입 배출구 몰탈 오버플로우 확인</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34400,7 +34890,7 @@
           <t>1,435mm 표준궤 정밀 유지 타이바 설치. 철근 피복 두께 40mm 확보 및 신호 감선 이격 150mm.</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34411,7 +34901,7 @@
 2) 궤간 1,435mm(+3,-1mm) 고정 및 캔트/수평 오차 ±2mm 이내 정밀 정열</t>
         </is>
       </c>
-      <c r="N18" s="53" t="inlineStr">
+      <c r="N18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34421,7 +34911,7 @@
           <t>철근 결속선 긴장 상태, 타이바 조임 토크 확인, 신호 루프 케이블 배근 이격 확인</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34496,7 +34986,7 @@
           <t>타설 측압 대비 서포트 앵커 W=1.0m 간격 고정. 거푸집 수평/수직 처짐 변위 ±2mm 이내 통제.</t>
         </is>
       </c>
-      <c r="L19" s="53" t="inlineStr">
+      <c r="L19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34507,7 +34997,7 @@
 2) 거푸집 면 이물질 청소 및 환경 친화 박리제 균일 도포</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34517,7 +35007,7 @@
           <t>거푸집 지지대 앵커 조임, 박리제 도포 상태, 이음매 틈새 누수 패킹 확인</t>
         </is>
       </c>
-      <c r="P19" s="53" t="inlineStr">
+      <c r="P19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34593,7 +35083,7 @@
           <t>TCL 도상 콘크리트 강도 ≥ 35 MPa. 타설 중 실시간 궤간척(Gauge Bar) 캔트 오차 ±2mm 보정.</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34604,7 +35094,7 @@
 2) 고주파 다짐 실시 및 타설 중 실시간 궤간/캔트 오차 미세 조율</t>
         </is>
       </c>
-      <c r="N20" s="53" t="inlineStr">
+      <c r="N20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34614,7 +35104,7 @@
           <t>타설 중 궤간척 실시간 모니터링, 슬럼프 및 공기량 시험, 습윤 양생 부직포 포설 확인</t>
         </is>
       </c>
-      <c r="P20" s="53" t="inlineStr">
+      <c r="P20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34690,7 +35180,7 @@
           <t>EN 14587 규격 준수. 레일 단부 가열(1200℃) 후 압송. 용접부 직선도 1m당 ±0.2mm 이내 정밀 연마.</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34701,7 +35191,7 @@
 2) EN 14587 프로그램에 따라 자동 가열 및 버(Burr) 핫 쉐어링 전단</t>
         </is>
       </c>
-      <c r="N21" s="53" t="inlineStr">
+      <c r="N21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34711,7 +35201,7 @@
           <t>가스 압접 압력 게이지 확인, 용접부 급랭 방지 덮개 설치, 비파괴 시험(UT) 성적서 결재</t>
         </is>
       </c>
-      <c r="P21" s="53" t="inlineStr">
+      <c r="P21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34788,7 +35278,7 @@
           <t>EN 14730 규격 준수. 도가니 반응 후 슬래그 분리. 직선도 오차 ±0.2mm 이내 및 NDT 100% 합격.</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34799,7 +35289,7 @@
 2) 몰드 밀봉 후 테르밋 소모품點火 반응 주입 및 약 5분 후 유압 전단</t>
         </is>
       </c>
-      <c r="N22" s="53" t="inlineStr">
+      <c r="N22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34809,7 +35299,7 @@
           <t>테르밋 용제 예열 온도 확인, 도가니 수평 고정, 비파괴 검사(UT/MT) 전수 실시</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34885,7 +35375,7 @@
           <t>레일 마무리면 평탄성 1m 기준 오차 ±0.2mm 이내 밀링. 레일 과열에 의한 열응력 크랙 방지.</t>
         </is>
       </c>
-      <c r="L23" s="53" t="inlineStr">
+      <c r="L23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34896,7 +35386,7 @@
 2) 장대레일 구간 연마/밀링 장비 점검 및 표면 단차 사전 조사</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34906,7 +35396,7 @@
           <t>레일 조도/평탄성 측정 성적서, 절삭유 적정 분사 상태, 마이크로미터 선로 실측</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34980,7 +35470,7 @@
           <t>전기/신호/노반 담당자 입회 하에 궤도 회로 절연 저항 ≥ 100MΩ 검속. 준공 도면 일치 서명.</t>
         </is>
       </c>
-      <c r="L24" s="58" t="inlineStr">
+      <c r="L24" s="169" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34991,7 +35481,7 @@
 2) 구간별 NDT 용접 성과표, 강도 성적서 및 궤도 정열표 대조</t>
         </is>
       </c>
-      <c r="N24" s="55" t="inlineStr">
+      <c r="N24" s="169" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35001,7 +35491,7 @@
           <t>3자 공동 인수 서명 날인, 절연 저항 테스트 결과표 첨부, CAD 준공 대장 제출</t>
         </is>
       </c>
-      <c r="P24" s="58" t="inlineStr">
+      <c r="P24" s="169" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35283,7 +35773,7 @@
 2) 설계 적정성 검토 달성을 위한 필수 시공 방법(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반영 유무 및 확...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K2" s="34" t="inlineStr">
+      <c r="K2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35294,7 +35784,7 @@
 2) 실무 작업방법 수칙(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M2" s="88" t="inlineStr">
+      <c r="M2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35305,7 +35795,7 @@
 2) 미검측 및 정량 시방 미달에 따른 설계 적정성 검토 (WBS 9000-4-1) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 설계변경 예상 List, 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O2" s="34" t="inlineStr">
+      <c r="O2" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35379,7 +35869,7 @@
 2) 발주전략 KOM 달성을 위한 필수 시공 방법(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 지반상태(기초,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K3" s="34" t="inlineStr">
+      <c r="K3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35390,7 +35880,7 @@
 2) 실무 작업방법 수칙(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M3" s="88" t="inlineStr">
+      <c r="M3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35401,7 +35891,7 @@
 2) 미검측 및 정량 시방 미달에 따른 발주전략 KOM (WBS 9000-4-2) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 KOM 검토결과서, 현설서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O3" s="34" t="inlineStr">
+      <c r="O3" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35474,7 +35964,7 @@
 2) 착공전 건축 인허가 달성을 위한 필수 시공 방법(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출 (-&gt;관할 소...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35485,7 +35975,7 @@
 2) 실무 작업방법 수칙(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35496,7 +35986,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착공전 건축 인허가 (WBS 9000-4-3) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고/승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O4" s="34" t="inlineStr">
+      <c r="O4" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35569,7 +36059,7 @@
 2) 건축허가 요청 달성을 위한 필수 시공 방법(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 관할지자체(시,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K5" s="34" t="inlineStr">
+      <c r="K5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35580,7 +36070,7 @@
 2) 실무 작업방법 수칙(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M5" s="34" t="inlineStr">
+      <c r="M5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35591,7 +36081,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축허가 요청 (WBS 9000-4-4) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축허가 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O5" s="34" t="inlineStr">
+      <c r="O5" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35664,7 +36154,7 @@
 2) 착공신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처리기간 3일 이...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K6" s="34" t="inlineStr">
+      <c r="K6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35675,7 +36165,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M6" s="88" t="inlineStr">
+      <c r="M6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35686,7 +36176,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착공신고서 제출 (WBS 9000-4-5) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 착공신고서 승인 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O6" s="34" t="inlineStr">
+      <c r="O6" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35758,7 +36248,7 @@
 2) 소방시설공사 착공 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 처리기간 2일 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K7" s="34" t="inlineStr">
+      <c r="K7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35769,7 +36259,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M7" s="34" t="inlineStr">
+      <c r="M7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35780,7 +36270,7 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 착공 신고서 제출 (WBS 9000-4-6) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설공사 착공신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O7" s="34" t="inlineStr">
+      <c r="O7" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35852,7 +36342,7 @@
 2) 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 처리기간 14일...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K8" s="34" t="inlineStr">
+      <c r="K8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35863,7 +36353,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M8" s="34" t="inlineStr">
+      <c r="M8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35874,7 +36364,7 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) (WBS 9000-4-7) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신공사 착공전 설계도 확인결과 통보서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O8" s="34" t="inlineStr">
+      <c r="O8" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35946,7 +36436,7 @@
 2) 선행공종 인수사항 확인 달성을 위한 필수 시공 방법(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K9" s="34" t="inlineStr">
+      <c r="K9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35957,7 +36447,7 @@
 2) 실무 작업방법 수칙(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M9" s="34" t="inlineStr">
+      <c r="M9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35968,7 +36458,7 @@
 2) 미검측 및 정량 시방 미달에 따른 선행공종 인수사항 확인 (WBS 9000-4-8) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 인수사항 List 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O9" s="34" t="inlineStr">
+      <c r="O9" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36040,7 +36530,7 @@
 2) 인터페이스 사항 검토 및 지원 달성을 위한 필수 시공 방법(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장 지원 파견검토...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K10" s="34" t="inlineStr">
+      <c r="K10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36051,7 +36541,7 @@
 2) 실무 작업방법 수칙(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M10" s="34" t="inlineStr">
+      <c r="M10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36062,7 +36552,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 사항 검토 및 지원 (WBS 9000-4-9) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O10" s="34" t="inlineStr">
+      <c r="O10" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36132,7 +36622,7 @@
 2) 품질/안전 LL 공유 달성을 위한 필수 시공 방법(시공시 발생가능 품질, 안전 하자 최소화...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="K11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36143,7 +36633,7 @@
 2) 실무 작업방법 수칙(시공시 발생가능 품질, 안전 하자 최소화)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M11" s="34" t="inlineStr">
+      <c r="M11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36154,7 +36644,7 @@
 2) 미검측 및 정량 시방 미달에 따른 품질/안전 LL 공유 (WBS 9000-4-10) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공계획수립시 반영 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O11" s="34" t="inlineStr">
+      <c r="O11" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36226,7 +36716,7 @@
 2) 자재공급원승인 및 자재발주 달성을 위한 필수 시공 방법(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 승인 제출 및 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K12" s="34" t="inlineStr">
+      <c r="K12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36237,7 +36727,7 @@
 2) 실무 작업방법 수칙(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M12" s="34" t="inlineStr">
+      <c r="M12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36248,7 +36738,7 @@
 2) 미검측 및 정량 시방 미달에 따른 자재공급원승인 및 자재발주 (WBS 9000-4-11) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 구매 의뢰 승인, 자재공급원 승인서류 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O12" s="34" t="inlineStr">
+      <c r="O12" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36327,7 +36817,7 @@
 2) 착수전 Big Room 회의 달성을 위한 필수 시공 방법(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방착공신고, 정보...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36338,7 +36828,7 @@
 2) 실무 작업방법 수칙(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M13" s="88" t="inlineStr">
+      <c r="M13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36349,7 +36839,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착수전 Big Room 회의 (WBS 9000-4-12) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 Big Room 회의록(참석자 전원 서명) 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O13" s="34" t="inlineStr">
+      <c r="O13" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36422,7 +36912,7 @@
 2) 시공계획 수립/승인 달성을 위한 필수 시공 방법(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: 위험요인/대책,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K14" s="34" t="inlineStr">
+      <c r="K14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36433,7 +36923,7 @@
 2) 실무 작업방법 수칙(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M14" s="34" t="inlineStr">
+      <c r="M14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36444,7 +36934,7 @@
 2) 미검측 및 정량 시방 미달에 따른 시공계획 수립/승인 (WBS 9000-4-13) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 (승인)관리시공계획서&amp;시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O14" s="34" t="inlineStr">
+      <c r="O14" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36517,7 +37007,7 @@
 2) 측량, 자재/장비 반입, 안전교육 달성을 위한 필수 시공 방법(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안전검사 작업원 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36528,7 +37018,7 @@
 2) 실무 작업방법 수칙(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M15" s="34" t="inlineStr">
+      <c r="M15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36539,7 +37029,7 @@
 2) 미검측 및 정량 시방 미달에 따른 측량, 자재/장비 반입, 안전교육 (WBS 9000-4-14) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량기록지, 안전교육 결과서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O15" s="34" t="inlineStr">
+      <c r="O15" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36611,7 +37101,7 @@
 2) 자재 검수 달성을 위한 필수 시공 방법(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K16" s="34" t="inlineStr">
+      <c r="K16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36622,7 +37112,7 @@
 2) 실무 작업방법 수칙(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M16" s="34" t="inlineStr">
+      <c r="M16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36633,7 +37123,7 @@
 2) 미검측 및 정량 시방 미달에 따른 자재 검수 (WBS 9000-4-15) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 자재검수서, 품질시험 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O16" s="34" t="inlineStr">
+      <c r="O16" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36703,7 +37193,7 @@
 2) 터파기/지반 정리 달성을 위한 필수 시공 방법(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36714,7 +37204,7 @@
 2) 실무 작업방법 수칙(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M17" s="34" t="inlineStr">
+      <c r="M17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36725,7 +37215,7 @@
 2) 미검측 및 정량 시방 미달에 따른 터파기/지반 정리 (WBS 9000-4-16) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량 성과, 지지력시험성과 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O17" s="34" t="inlineStr">
+      <c r="O17" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36795,7 +37285,7 @@
 2) 바닥(버림) 콘크리트 타설 달성을 위한 필수 시공 방법(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K18" s="34" t="inlineStr">
+      <c r="K18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36806,7 +37296,7 @@
 2) 실무 작업방법 수칙(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M18" s="34" t="inlineStr">
+      <c r="M18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36817,7 +37307,7 @@
 2) 미검측 및 정량 시방 미달에 따른 바닥(버림) 콘크리트 타설 (WBS 9000-4-17) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O18" s="34" t="inlineStr">
+      <c r="O18" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36887,7 +37377,7 @@
 2) 인터페이스 회의(매주) 달성을 위한 필수 시공 방법(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한 선후행공정 시...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="K19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36898,7 +37388,7 @@
 2) 실무 작업방법 수칙(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M19" s="34" t="inlineStr">
+      <c r="M19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36909,7 +37399,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 회의(매주) (WBS 9000-4-18) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O19" s="34" t="inlineStr">
+      <c r="O19" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36979,7 +37469,7 @@
 2) 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) 달성을 위한 필수 시공 방법(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결정, 각종 필증...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K20" s="34" t="inlineStr">
+      <c r="K20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36990,7 +37480,7 @@
 2) 실무 작업방법 수칙(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M20" s="34" t="inlineStr">
+      <c r="M20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37001,7 +37491,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) (WBS 9000-4-19) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O20" s="34" t="inlineStr">
+      <c r="O20" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37071,7 +37561,7 @@
 2) 인터페이스 각 공종별 Issue (토목분야) 달성을 위한 필수 시공 방법(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K21" s="34" t="inlineStr">
+      <c r="K21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37082,7 +37572,7 @@
 2) 실무 작업방법 수칙(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M21" s="34" t="inlineStr">
+      <c r="M21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37093,7 +37583,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (토목분야) (WBS 9000-4-20) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O21" s="34" t="inlineStr">
+      <c r="O21" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37163,7 +37653,7 @@
 2) 기초~상부슬라브 구조물 시공 달성을 위한 필수 시공 방법(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K22" s="34" t="inlineStr">
+      <c r="K22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37174,7 +37664,7 @@
 2) 실무 작업방법 수칙(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M22" s="34" t="inlineStr">
+      <c r="M22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37185,7 +37675,7 @@
 2) 미검측 및 정량 시방 미달에 따른 기초~상부슬라브 구조물 시공 (WBS 9000-4-21) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 각종 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O22" s="34" t="inlineStr">
+      <c r="O22" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37255,7 +37745,7 @@
 2) 철근 가공 달성을 위한 필수 시공 방법(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K23" s="34" t="inlineStr">
+      <c r="K23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37266,7 +37756,7 @@
 2) 실무 작업방법 수칙(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M23" s="34" t="inlineStr">
+      <c r="M23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37277,7 +37767,7 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 가공 (WBS 9000-4-22) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O23" s="34" t="inlineStr">
+      <c r="O23" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37347,7 +37837,7 @@
 2) 작업발판, 비계 및 동바리 설치 달성을 위한 필수 시공 방법(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K24" s="34" t="inlineStr">
+      <c r="K24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37358,7 +37848,7 @@
 2) 실무 작업방법 수칙(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M24" s="34" t="inlineStr">
+      <c r="M24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37369,7 +37859,7 @@
 2) 미검측 및 정량 시방 미달에 따른 작업발판, 비계 및 동바리 설치 (WBS 9000-4-23) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 비계 및 동바리 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O24" s="34" t="inlineStr">
+      <c r="O24" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37439,7 +37929,7 @@
 2) 철근 조립 달성을 위한 필수 시공 방법(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="K25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37450,7 +37940,7 @@
 2) 실무 작업방법 수칙(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M25" s="34" t="inlineStr">
+      <c r="M25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37461,7 +37951,7 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 조립 (WBS 9000-4-24) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O25" s="34" t="inlineStr">
+      <c r="O25" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37531,7 +38021,7 @@
 2) 거푸집 조립 달성을 위한 필수 시공 방법(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K26" s="34" t="inlineStr">
+      <c r="K26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37542,7 +38032,7 @@
 2) 실무 작업방법 수칙(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M26" s="34" t="inlineStr">
+      <c r="M26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37553,7 +38043,7 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 조립 (WBS 9000-4-25) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 거푸집 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O26" s="34" t="inlineStr">
+      <c r="O26" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37625,7 +38115,7 @@
 2) 콘크리트 타설 및 다짐 달성을 위한 필수 시공 방법(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라브 타설시 동바...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37636,7 +38126,7 @@
 2) 실무 작업방법 수칙(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M27" s="34" t="inlineStr">
+      <c r="M27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37647,7 +38137,7 @@
 2) 미검측 및 정량 시방 미달에 따른 콘크리트 타설 및 다짐 (WBS 9000-4-26) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 콘크리트 구조물 확보, 타설보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O27" s="34" t="inlineStr">
+      <c r="O27" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37717,7 +38207,7 @@
 2) 거푸집 해체 달성을 위한 필수 시공 방법(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태 Double ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K28" s="34" t="inlineStr">
+      <c r="K28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37728,7 +38218,7 @@
 2) 실무 작업방법 수칙(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M28" s="34" t="inlineStr">
+      <c r="M28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37739,7 +38229,7 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 해체 (WBS 9000-4-27) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해체 완료 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O28" s="34" t="inlineStr">
+      <c r="O28" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37809,7 +38299,7 @@
 2) 건축 내부 및 마감공사 달성을 위한 필수 시공 방법(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K29" s="34" t="inlineStr">
+      <c r="K29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37820,7 +38310,7 @@
 2) 실무 작업방법 수칙(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M29" s="34" t="inlineStr">
+      <c r="M29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37831,7 +38321,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축 내부 및 마감공사 (WBS 9000-4-28) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O29" s="34" t="inlineStr">
+      <c r="O29" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37901,7 +38391,7 @@
 2) 창호,유리 및 금속지붕공사 달성을 위한 필수 시공 방법(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K30" s="34" t="inlineStr">
+      <c r="K30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37912,7 +38402,7 @@
 2) 실무 작업방법 수칙(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M30" s="34" t="inlineStr">
+      <c r="M30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37923,7 +38413,7 @@
 2) 미검측 및 정량 시방 미달에 따른 창호,유리 및 금속지붕공사 (WBS 9000-4-29) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공상세도 및 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O30" s="34" t="inlineStr">
+      <c r="O30" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37993,7 +38483,7 @@
 2) 조적공사 달성을 위한 필수 시공 방법(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="K31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38004,7 +38494,7 @@
 2) 실무 작업방법 수칙(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M31" s="34" t="inlineStr">
+      <c r="M31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38015,7 +38505,7 @@
 2) 미검측 및 정량 시방 미달에 따른 조적공사 (WBS 9000-4-30) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시멘트 벽돌 및 블록 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O31" s="34" t="inlineStr">
+      <c r="O31" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38085,7 +38575,7 @@
 2) 내부 방수공사 달성을 위한 필수 시공 방법(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K32" s="34" t="inlineStr">
+      <c r="K32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38096,7 +38586,7 @@
 2) 실무 작업방법 수칙(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M32" s="34" t="inlineStr">
+      <c r="M32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38107,7 +38597,7 @@
 2) 미검측 및 정량 시방 미달에 따른 내부 방수공사 (WBS 9000-4-31) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 방수공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O32" s="34" t="inlineStr">
+      <c r="O32" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38177,7 +38667,7 @@
 2) 미장 및 타일공사 달성을 위한 필수 시공 방법(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K33" s="34" t="inlineStr">
+      <c r="K33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38188,7 +38678,7 @@
 2) 실무 작업방법 수칙(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M33" s="34" t="inlineStr">
+      <c r="M33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38199,7 +38689,7 @@
 2) 미검측 및 정량 시방 미달에 따른 미장 및 타일공사 (WBS 9000-4-32) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 미장,타일 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O33" s="34" t="inlineStr">
+      <c r="O33" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38269,7 +38759,7 @@
 2) 수장 및 잡철물공사 달성을 위한 필수 시공 방법(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 도어, 난간,창...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K34" s="34" t="inlineStr">
+      <c r="K34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38280,7 +38770,7 @@
 2) 실무 작업방법 수칙(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M34" s="34" t="inlineStr">
+      <c r="M34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38291,7 +38781,7 @@
 2) 미검측 및 정량 시방 미달에 따른 수장 및 잡철물공사 (WBS 9000-4-33) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 수장 및 잡철물검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O34" s="34" t="inlineStr">
+      <c r="O34" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38361,7 +38851,7 @@
 2) 도장공사 달성을 위한 필수 시공 방법(도장재 (붓, 롤러등)로 벽면에 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K35" s="34" t="inlineStr">
+      <c r="K35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38372,7 +38862,7 @@
 2) 실무 작업방법 수칙(도장재 (붓, 롤러등)로 벽면에 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M35" s="34" t="inlineStr">
+      <c r="M35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38383,7 +38873,7 @@
 2) 미검측 및 정량 시방 미달에 따른 도장공사 (WBS 9000-4-34) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 도장공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O35" s="34" t="inlineStr">
+      <c r="O35" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38453,7 +38943,7 @@
 2) 인테리어 및 무대공사 달성을 위한 필수 시공 방법(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K36" s="34" t="inlineStr">
+      <c r="K36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38464,7 +38954,7 @@
 2) 실무 작업방법 수칙(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M36" s="34" t="inlineStr">
+      <c r="M36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38475,7 +38965,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인테리어 및 무대공사 (WBS 9000-4-35) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 각 공종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O36" s="34" t="inlineStr">
+      <c r="O36" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38545,7 +39035,7 @@
 2) 준공전 건축 인허가 달성을 위한 필수 시공 방법(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강기 설치검사 신...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K37" s="34" t="inlineStr">
+      <c r="K37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38556,7 +39046,7 @@
 2) 실무 작업방법 수칙(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M37" s="34" t="inlineStr">
+      <c r="M37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38567,7 +39057,7 @@
 2) 미검측 및 정량 시방 미달에 따른 준공전 건축 인허가 (WBS 9000-4-36) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고 / 승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O37" s="34" t="inlineStr">
+      <c r="O37" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38639,7 +39129,7 @@
 2) 소방시설공사 완공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리기간 3일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K38" s="34" t="inlineStr">
+      <c r="K38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38650,7 +39140,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M38" s="34" t="inlineStr">
+      <c r="M38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38661,7 +39151,7 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 완공검사 (WBS 9000-4-37) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설 완공검사 증명서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O38" s="34" t="inlineStr">
+      <c r="O38" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38733,7 +39223,7 @@
 2) 승강기 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K39" s="34" t="inlineStr">
+      <c r="K39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38744,7 +39234,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M39" s="34" t="inlineStr">
+      <c r="M39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38755,7 +39245,7 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치 신고서 제출 (WBS 9000-4-38) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O39" s="34" t="inlineStr">
+      <c r="O39" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38826,7 +39316,7 @@
 2) 저수조 설치현황 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K40" s="34" t="inlineStr">
+      <c r="K40" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38837,7 +39327,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M40" s="34" t="inlineStr">
+      <c r="M40" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38848,7 +39338,7 @@
 2) 미검측 및 정량 시방 미달에 따른 저수조 설치현황 신고서 제출 (WBS 9000-4-39) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 저수조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O40" s="34" t="inlineStr">
+      <c r="O40" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38920,7 +39410,7 @@
 2) 오수처리시설 / 정화조 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K41" s="34" t="inlineStr">
+      <c r="K41" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38931,7 +39421,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M41" s="34" t="inlineStr">
+      <c r="M41" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38942,7 +39432,7 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 설치 신고서 제출 (WBS 9000-4-40) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설/정화조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
+      <c r="O41" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39013,7 +39503,7 @@
 2) 전기사용전 검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K42" s="34" t="inlineStr">
+      <c r="K42" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39024,7 +39514,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M42" s="34" t="inlineStr">
+      <c r="M42" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39035,7 +39525,7 @@
 2) 미검측 및 정량 시방 미달에 따른 전기사용전 검사 (WBS 9000-4-41) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 전기사용전 검사 필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O42" s="34" t="inlineStr">
+      <c r="O42" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39107,7 +39597,7 @@
 2) 승강기 설치검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 서식 제출후 처...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K43" s="34" t="inlineStr">
+      <c r="K43" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39118,7 +39608,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M43" s="34" t="inlineStr">
+      <c r="M43" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39129,7 +39619,7 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치검사 (WBS 9000-4-42) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 사용필증, 합격증보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O43" s="34" t="inlineStr">
+      <c r="O43" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39199,7 +39689,7 @@
 2) 배수설비 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K44" s="34" t="inlineStr">
+      <c r="K44" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39210,7 +39700,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M44" s="34" t="inlineStr">
+      <c r="M44" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39221,7 +39711,7 @@
 2) 미검측 및 정량 시방 미달에 따른 배수설비 설치 신고서 제출 (WBS 9000-4-43) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 배수설비 사용필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O44" s="34" t="inlineStr">
+      <c r="O44" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39293,7 +39783,7 @@
 2) 정보통신공사 사용전검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후 처리기간 14...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K45" s="34" t="inlineStr">
+      <c r="K45" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39304,7 +39794,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M45" s="34" t="inlineStr">
+      <c r="M45" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39315,7 +39805,7 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 사용전검사 (WBS 9000-4-44) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신사용전 검사필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O45" s="34" t="inlineStr">
+      <c r="O45" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39387,7 +39877,7 @@
 2) 오수처리시설 / 정화조 준공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K46" s="34" t="inlineStr">
+      <c r="K46" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39398,7 +39888,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M46" s="34" t="inlineStr">
+      <c r="M46" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39409,7 +39899,7 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 준공검사 (WBS 9000-4-45) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설 / 정화조 준공필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O46" s="34" t="inlineStr">
+      <c r="O46" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39480,7 +39970,7 @@
 2) 급수공사 신청서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K47" s="34" t="inlineStr">
+      <c r="K47" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39491,7 +39981,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M47" s="34" t="inlineStr">
+      <c r="M47" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39502,7 +39992,7 @@
 2) 미검측 및 정량 시방 미달에 따른 급수공사 신청서 제출 (WBS 9000-4-46) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 급수 사용허가 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O47" s="34" t="inlineStr">
+      <c r="O47" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39573,7 +40063,7 @@
 2) 업무대행 건축사 사용승인 검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 별지 제17호 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K48" s="34" t="inlineStr">
+      <c r="K48" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39584,7 +40074,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M48" s="34" t="inlineStr">
+      <c r="M48" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39595,7 +40085,7 @@
 2) 미검측 및 정량 시방 미달에 따른 업무대행 건축사 사용승인 검사 (WBS 9000-4-47) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O48" s="34" t="inlineStr">
+      <c r="O48" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39667,7 +40157,7 @@
 2) 건축물 사용승인 신청 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식 제출후 처리기...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="K49" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39678,7 +40168,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M49" s="34" t="inlineStr">
+      <c r="M49" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39689,7 +40179,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물 사용승인 신청 (WBS 9000-4-48) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O49" s="34" t="inlineStr">
+      <c r="O49" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39759,7 +40249,7 @@
 2) 건축물대장 등재 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K50" s="34" t="inlineStr">
+      <c r="K50" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39770,7 +40260,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M50" s="34" t="inlineStr">
+      <c r="M50" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39781,7 +40271,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물대장 등재 (WBS 9000-4-49) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 대장 등재 확인 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O50" s="34" t="inlineStr">
+      <c r="O50" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -39854,7 +40344,7 @@
 2) 후속 구조물 인계 달성을 위한 필수 시공 방법(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명서, 전기사용전...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K51" s="34" t="inlineStr">
+      <c r="K51" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -39865,7 +40355,7 @@
 2) 실무 작업방법 수칙(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M51" s="34" t="inlineStr">
+      <c r="M51" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -39876,7 +40366,7 @@
 2) 미검측 및 정량 시방 미달에 따른 후속 구조물 인계 (WBS 9000-4-50) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 유지관리기관 인수인계서, 건축 인허가 서류, 준공도서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O51" s="34" t="inlineStr">
+      <c r="O51" s="167" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>

--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sskjh\antigravity\01_전문업무_및_엔지니어링\11_현장_프로젝트\01_동탄트램\08.메뉴얼 및 평면도\최종\02_메뉴얼 공종프로섹스(집행단계)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5DBD876-39C2-4679-97B6-DA3F7FA4A645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEE9C214-AED6-466A-ADA5-E477AD29DB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12498,15 +12498,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12515,17 +12524,8 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -12857,7 +12857,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="156" t="s">
         <v>575</v>
       </c>
       <c r="C2" s="149"/>
@@ -12878,58 +12878,58 @@
       </c>
     </row>
     <row r="6" spans="2:13" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="146" t="s">
         <v>577</v>
       </c>
       <c r="C6" s="147"/>
-      <c r="D6" s="154" t="s">
+      <c r="D6" s="146" t="s">
         <v>578</v>
       </c>
       <c r="E6" s="147"/>
-      <c r="F6" s="154" t="s">
+      <c r="F6" s="146" t="s">
         <v>579</v>
       </c>
       <c r="G6" s="147"/>
-      <c r="H6" s="154" t="s">
+      <c r="H6" s="146" t="s">
         <v>580</v>
       </c>
       <c r="I6" s="147"/>
-      <c r="J6" s="154" t="s">
+      <c r="J6" s="146" t="s">
         <v>581</v>
       </c>
       <c r="K6" s="147"/>
-      <c r="L6" s="154" t="s">
+      <c r="L6" s="146" t="s">
         <v>582</v>
       </c>
       <c r="M6" s="147"/>
     </row>
     <row r="7" spans="2:13" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="152" t="str">
+      <c r="B7" s="155" t="str">
         <f>E21&amp;" 개"</f>
         <v>233 개</v>
       </c>
       <c r="C7" s="147"/>
-      <c r="D7" s="152" t="str">
+      <c r="D7" s="155" t="str">
         <f>F21&amp;" 개 (100%)"</f>
         <v>263 개 (100%)</v>
       </c>
       <c r="E7" s="147"/>
-      <c r="F7" s="152" t="str">
+      <c r="F7" s="155" t="str">
         <f>G21&amp;" 개 (100%)"</f>
         <v>263 개 (100%)</v>
       </c>
       <c r="G7" s="147"/>
-      <c r="H7" s="152" t="str">
+      <c r="H7" s="155" t="str">
         <f>H21&amp;" 개 (100%)"</f>
         <v>263 개 (100%)</v>
       </c>
       <c r="I7" s="147"/>
-      <c r="J7" s="152" t="str">
+      <c r="J7" s="155" t="str">
         <f>I21&amp;" 개 (100%)"</f>
         <v>233 개 (100%)</v>
       </c>
       <c r="K7" s="147"/>
-      <c r="L7" s="152" t="str">
+      <c r="L7" s="155" t="str">
         <f>J21&amp;" 개 (87.8%)"</f>
         <v>231 개 (87.8%)</v>
       </c>
@@ -13359,11 +13359,11 @@
       </c>
     </row>
     <row r="25" spans="2:12" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="153" t="s">
+      <c r="B25" s="148" t="s">
         <v>610</v>
       </c>
       <c r="C25" s="147"/>
-      <c r="D25" s="153" t="s">
+      <c r="D25" s="148" t="s">
         <v>611</v>
       </c>
       <c r="E25" s="149"/>
@@ -13378,11 +13378,11 @@
       </c>
     </row>
     <row r="26" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="156" t="s">
+      <c r="B26" s="152" t="s">
         <v>613</v>
       </c>
       <c r="C26" s="147"/>
-      <c r="D26" s="151" t="s">
+      <c r="D26" s="154" t="s">
         <v>614</v>
       </c>
       <c r="E26" s="149"/>
@@ -13397,11 +13397,11 @@
       </c>
     </row>
     <row r="27" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="155" t="s">
+      <c r="B27" s="153" t="s">
         <v>616</v>
       </c>
       <c r="C27" s="147"/>
-      <c r="D27" s="150" t="s">
+      <c r="D27" s="151" t="s">
         <v>617</v>
       </c>
       <c r="E27" s="149"/>
@@ -13416,11 +13416,11 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="152" t="s">
         <v>618</v>
       </c>
       <c r="C28" s="147"/>
-      <c r="D28" s="151" t="s">
+      <c r="D28" s="154" t="s">
         <v>619</v>
       </c>
       <c r="E28" s="149"/>
@@ -13435,11 +13435,11 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="155" t="s">
+      <c r="B29" s="153" t="s">
         <v>620</v>
       </c>
       <c r="C29" s="147"/>
-      <c r="D29" s="150" t="s">
+      <c r="D29" s="151" t="s">
         <v>621</v>
       </c>
       <c r="E29" s="149"/>
@@ -13454,11 +13454,11 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="156" t="s">
+      <c r="B30" s="152" t="s">
         <v>622</v>
       </c>
       <c r="C30" s="147"/>
-      <c r="D30" s="151" t="s">
+      <c r="D30" s="154" t="s">
         <v>623</v>
       </c>
       <c r="E30" s="149"/>
@@ -13481,11 +13481,11 @@
       <c r="B34" s="94" t="s">
         <v>585</v>
       </c>
-      <c r="C34" s="146" t="s">
+      <c r="C34" s="150" t="s">
         <v>625</v>
       </c>
       <c r="D34" s="147"/>
-      <c r="E34" s="146" t="s">
+      <c r="E34" s="150" t="s">
         <v>626</v>
       </c>
       <c r="F34" s="149"/>
@@ -13502,11 +13502,11 @@
       <c r="B35" s="93" t="s">
         <v>628</v>
       </c>
-      <c r="C35" s="155" t="s">
+      <c r="C35" s="153" t="s">
         <v>629</v>
       </c>
       <c r="D35" s="147"/>
-      <c r="E35" s="150" t="s">
+      <c r="E35" s="151" t="s">
         <v>630</v>
       </c>
       <c r="F35" s="149"/>
@@ -13523,11 +13523,11 @@
       <c r="B36" s="93" t="s">
         <v>632</v>
       </c>
-      <c r="C36" s="155" t="s">
+      <c r="C36" s="153" t="s">
         <v>633</v>
       </c>
       <c r="D36" s="147"/>
-      <c r="E36" s="150" t="s">
+      <c r="E36" s="151" t="s">
         <v>634</v>
       </c>
       <c r="F36" s="149"/>
@@ -13542,22 +13542,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="E34:K34"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:K30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E35:K35"/>
-    <mergeCell ref="C34:D34"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E36:K36"/>
     <mergeCell ref="D26:K26"/>
@@ -13573,6 +13557,22 @@
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="D27:K27"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="D28:K28"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:K30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E35:K35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="D25:K25"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -757,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1194,6 +1194,9 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2645,8 +2648,8 @@
 2) 철도 표준 자재(KRS) 및 분산형 CBI 용량, 선로전환기(4.5~6.0kN) 적정성을 검증하고 승인 보고서를 완수하라.</t>
         </is>
       </c>
-      <c r="K2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -2655,8 +2658,8 @@
 2) 분산형 CBI 및 선로전환기 용량의 현장 시공성 및 원가 Risk를 철저히 검토하여 승인을 획득하십시오.</t>
         </is>
       </c>
-      <c r="M2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N2" s="11" t="inlineStr">
@@ -2665,8 +2668,8 @@
 2) 철도 표준 자재(KRS) 규격 및 매립 선로전환기 전환력(4.5~6.0kN) 기준을 적격 확인하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P2" s="10" t="n"/>
@@ -2750,8 +2753,8 @@
 2) 외주 수급, 신기술자재 확인, 내역 누락 방지 조치 및 SIL 인증보유 적격 업체 Pool을 확정하라.</t>
         </is>
       </c>
-      <c r="K3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\표준서\착수준비 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\표준서\착수준비 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -2760,8 +2763,8 @@
 2) 공정계획, 안전성 SIL 인증, 무상 A/S 및 철도안전법 준수 자재 투입 계획을 사전에 확인하십시오.</t>
         </is>
       </c>
-      <c r="M3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N3" s="11" t="inlineStr">
@@ -2770,8 +2773,8 @@
 2) 적격 업체 Pool 검토 및 내역 누락 방지 조치, SIL 인증 보유 여부를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\체크리스트\착수준비 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\2_착수준비 KOM\체크리스트\착수준비 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P3" s="10" t="n"/>
@@ -2851,8 +2854,8 @@
 2) 궤도 시공 전 블록아웃, 배수로, 선로전환기, 차축검지기 설치 I/F 항목을 사전 확정하라.</t>
         </is>
       </c>
-      <c r="K4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -2861,8 +2864,8 @@
 2) 궤도 시공 전 블록아웃 및 선로전환기 설치 I/F에 대해 각 분야 담당자와의 협의록을 작성하십시오.</t>
         </is>
       </c>
-      <c r="M4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N4" s="11" t="inlineStr">
@@ -2871,8 +2874,8 @@
 2) 궤도 시공 전 블록아웃 및 차축검지기 설치 I/F 사전 대책을 수립하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\3_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P4" s="10" t="n"/>
@@ -2946,8 +2949,8 @@
 2) 궤도 시공 전 블록아웃, 배수로, 융설장치, 차축검지기 설치 I/F 승인서를 완수하라.</t>
         </is>
       </c>
-      <c r="K5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\표준서\전기 _ 통신 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\표준서\전기 _ 통신 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L5" s="11" t="inlineStr">
@@ -2956,8 +2959,8 @@
 2) 차축검지기 및 융설장치 체결 부위의 치수 적정성을 서면으로 확인하십시오.</t>
         </is>
       </c>
-      <c r="M5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -2966,8 +2969,8 @@
 2) 차량기지 및 본선 선로전환기/차축검지기 체결 인터페이스를 조율하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\체크리스트\전기 _ 통신 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\4_전기 _ 통신 _ PSD _ 차량 인터페이스 협의\체크리스트\전기 _ 통신 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P5" s="10" t="n"/>
@@ -3036,8 +3039,8 @@
 2) 도심 매립 궤도용 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 설치 조건 및 유관기관 피드백을 반영하라.</t>
         </is>
       </c>
-      <c r="K6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\표준서\도로 _ 궤도 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\표준서\도로 _ 궤도 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L6" s="11" t="inlineStr">
@@ -3046,8 +3049,8 @@
 2) 도로 교차로 노면 매립 궤도 시공계획과 선로전환기 설치 위치 적정성을 확인하십시오.</t>
         </is>
       </c>
-      <c r="M6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -3056,8 +3059,8 @@
 2) 노면 매립형 선로전환기(전환력 4.5~6.0kN, 유격 ≤1.5mm) 시공조건을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\체크리스트\도로 _ 궤도 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\5_도로 _ 궤도 인터페이스 협의\체크리스트\도로 _ 궤도 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P6" s="10" t="n"/>
@@ -3131,8 +3134,8 @@
 2) 배관배선 인입구, 구조물 간섭 및 궤도 시공 전 설치 항목을 개시 전 차단하라.</t>
         </is>
       </c>
-      <c r="K7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\표준서\시공전 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\표준서\시공전 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -3141,8 +3144,8 @@
 2) 궤도 시공 전 블록아웃 및 케이블 인입 배관의 간섭 여부를 정밀 확인하십시오.</t>
         </is>
       </c>
-      <c r="M7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -3151,8 +3154,8 @@
 2) 케이블 인입 배관 및 궤도 블록아웃 간섭을 사전 제거하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\체크리스트\시공전 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\6_시공전 인터페이스 협의\체크리스트\시공전 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P7" s="10" t="n"/>
@@ -3218,8 +3221,8 @@
 2) 제조사 자체 시험 성적서, KRS 표준 규격 및 제작도서 승인 서명을 완수하라.</t>
         </is>
       </c>
-      <c r="K8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\표준서\시스템 장비검토 사전 협의사항 도출 및 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\표준서\시스템 장비검토 사전 협의사항 도출 및 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -3228,8 +3231,8 @@
 2) 제작도서 승인 서명 및 현장 투입 전 성능보증 기능을 검증하십시오.</t>
         </is>
       </c>
-      <c r="M8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\수행지침\CBI_CPU_2중화_절체_반응_속도(≤0.5초)_검토_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\수행지침\CBI_CPU_2중화_절체_반응_속도(≤0.5초)_검토_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -3238,8 +3241,8 @@
 2) 제조사 공장검수 성적서 및 제작도서 승인 서명을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\체크리스트\시스템 장비검토 사전 협의사항 도출 및 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\7_시스템 장비검토 사전 협의사항 도출 및 검토\체크리스트\시스템 장비검토 사전 협의사항 도출 및 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P8" s="10" t="n"/>
@@ -3306,8 +3309,8 @@
 2) 철도관제를 위한 관제사 조작반 MMI 및 예비관제 1:1 실시간 DB 동기화를 검증하라.</t>
         </is>
       </c>
-      <c r="K9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -3316,8 +3319,8 @@
 2) 관제센터 MMI 화면 및 조작반 정보의 실시간 동기화 상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -3326,8 +3329,8 @@
 2) 철도관제를 위한 관제사 조작반 MMI 표시 정보를 사전 검토하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\체크리스트\관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\8_관제 및 운영사 인터페이스 협의\체크리스트\관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P9" s="10" t="n"/>
@@ -3395,8 +3398,8 @@
 2) 현장 여건 및 궤도 시공계획 맞춤형 투입 schedule 작성 및 수급 조정을 완수하라.</t>
         </is>
       </c>
-      <c r="K10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\표준서\자재 _ 인원 _ 장비 및 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\표준서\자재 _ 인원 _ 장비 및 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -3405,8 +3408,8 @@
 2) 궤도 시공계획과 연계된 자재 반입 및 작업원 투입 스케줄을 조정하십시오.</t>
         </is>
       </c>
-      <c r="M10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N10" s="11" t="inlineStr">
@@ -3415,8 +3418,8 @@
 2) 궤도 시공계획 연계 투입 스케줄 감리단 승인을 획득하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\체크리스트\자재 _ 인원 _ 장비 및 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\9_자재 _ 인원 _ 장비 및 투입 사전 검토\체크리스트\자재 _ 인원 _ 장비 및 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P10" s="10" t="n"/>
@@ -3482,8 +3485,8 @@
 2) 작업원 특별 안전교육 및 위험성평가 이행 확인서를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -3492,8 +3495,8 @@
 2) 신호 공사 작업원에 대한 특별 안전교육 및 보호구 착용 상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N11" s="11" t="inlineStr">
@@ -3502,8 +3505,8 @@
 2) 신호 공사 작업원 특별 안전교육 실시 기록을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\체크리스트\장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\10_장비반입 및 안전교육\체크리스트\장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P11" s="10" t="n"/>
@@ -3572,8 +3575,8 @@
 2) 반입 자재의 KS/KRS 규격 시험성적서 대조 검수 및 품질 보증을 완수하라.</t>
         </is>
       </c>
-      <c r="K12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -3582,8 +3585,8 @@
 2) 자재 현지 반입 시 사양서, 시험성적서 및 표준규격 부합 여부를 인수 검수하십시오.</t>
         </is>
       </c>
-      <c r="M12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -3592,8 +3595,8 @@
 2) 반입 자재 사양 확인(KS, KRS 표준규격) 및 수량 검수를 시행하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\체크리스트\자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\11_자재 반입 및 검수\체크리스트\자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P12" s="10" t="n"/>
@@ -3662,8 +3665,8 @@
 2) 현장 신호기, 선로전환기 기초 볼트 체결 및 도면 일치 여부를 정밀 시공하라.</t>
         </is>
       </c>
-      <c r="K13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\표준서\시스템설비 설치 (현장_기능실)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\표준서\시스템설비 설치 (현장_기능실)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -3672,8 +3675,8 @@
 2) 현장 설치 설비의 규격, 수량 및 도면 일치 여부를 정밀 측정하여 시공하십시오.</t>
         </is>
       </c>
-      <c r="M13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N13" s="11" t="inlineStr">
@@ -3682,8 +3685,8 @@
 2) 현장 신호기/선로전환기 기초 볼트 체결 및 규격 일치 여부를 시공하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\체크리스트\시스템설비 설치 (현장_기능실)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\12_시스템설비 설치 (현장_기능실)\체크리스트\시스템설비 설치 (현장_기능실)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P13" s="10" t="n"/>
@@ -3757,8 +3760,8 @@
 2) 신호기, 선로전환기, 전원장치, 차축검지기 개별 ITP/ITC 시험 결과서를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\표준서\시스템 단위시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\표준서\시스템 단위시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -3767,8 +3770,8 @@
 2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 지상신호장치 단위시험 결과서를 작성하십시오.</t>
         </is>
       </c>
-      <c r="M14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\수행지침\CBI_IO_릴레이_모듈_동작_상태_검측_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\수행지침\CBI_IO_릴레이_모듈_동작_상태_검측_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N14" s="11" t="inlineStr">
@@ -3777,8 +3780,8 @@
 2) 감리단 승인 점검표(ITP/ITC) 절차에 따라 개별 단독 현황시험을 수행하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\체크리스트\시스템 단위시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\13_시스템 단위시험\체크리스트\시스템 단위시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P14" s="10" t="n"/>
@@ -3852,8 +3855,8 @@
 2) 차상-지상 무선(LTE-R) 도로-트램 우선신호 연계 시험 결과표를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\표준서\신호시스템 통합시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\표준서\신호시스템 통합시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -3862,8 +3865,8 @@
 2) 지상-차상 인터페이스 및 도로/트램 우선신호 무선 연계시험 결과표를 작성하십시오.</t>
         </is>
       </c>
-      <c r="M15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N15" s="11" t="inlineStr">
@@ -3872,8 +3875,8 @@
 2) 지상-차상 인터페이스 및 도로-트램 우선신호 연계 시험을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\체크리스트\신호시스템 통합시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\14_신호시스템 통합시험\체크리스트\신호시스템 통합시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P15" s="10" t="n"/>
@@ -3959,8 +3962,8 @@
 2) 신호기계실 전원 2중화 절체 시험 및 관제 CTC 서버 정상 동작 시험을 완수하라.</t>
         </is>
       </c>
-      <c r="K16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\표준서\공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\표준서\공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L16" s="11" t="inlineStr">
@@ -3969,8 +3972,8 @@
 2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 정상 동작상태를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -3979,8 +3982,8 @@
 2) 기계실 전원공급장치 이중화 절체 시험 및 관제 서버 동작을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\체크리스트\공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\15_공종별 시험\체크리스트\공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P16" s="10" t="n"/>
@@ -4060,8 +4063,8 @@
 2) 건축한계/차량한계 이격 정밀 측정 및 전원장치(UPS) 성능을 최종 검증하라.</t>
         </is>
       </c>
-      <c r="K17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -4070,8 +4073,8 @@
 2) 건축한계(폭 3.1m/높이 3.8m) 이격 측정 및 기계실 UPS/방재예방 설비를 확인하십시오.</t>
         </is>
       </c>
-      <c r="M17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -4080,8 +4083,8 @@
 2) 신호기와 건축물 간 건축한계 정밀 측정 및 방재설비를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\체크리스트\차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\16_차량 투입 전 점검\체크리스트\차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P17" s="10" t="n"/>
@@ -4161,8 +4164,8 @@
 2) 속도/제동 테스트, 차상-지상 연계동작 및 열차제어 시스템 기능시험을 완수하라.</t>
         </is>
       </c>
-      <c r="K18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\표준서\차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\표준서\차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -4171,8 +4174,8 @@
 2) 차상신호장치 지·차상 연계동작시험 및 열차제어 시스템 기능시험을 시행하십시오.</t>
         </is>
       </c>
-      <c r="M18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -4181,8 +4184,8 @@
 2) 차상-지상 연계동작시험 및 차량-신호-통신 I/F 시험을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\체크리스트\차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\17_차량 시운전\체크리스트\차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P18" s="10" t="n"/>
@@ -4256,8 +4259,8 @@
 2) 장비 제작사에 의한 CTC/CBI/현장설비 조작·정비 기술 교육 완료 이수증을 승인하라.</t>
         </is>
       </c>
-      <c r="K19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L19" s="11" t="inlineStr">
@@ -4266,8 +4269,8 @@
 2) CTC 서버, 전자연동장치, 현장 신호기/선로전환기 교육 이수 현황을 확인하십시오.</t>
         </is>
       </c>
-      <c r="M19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N19" s="11" t="inlineStr">
@@ -4276,8 +4279,8 @@
 2) 장비 제작사에 의한 CTC/CBI/현장설비 조작교육을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\체크리스트\운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\18_운영자 교육시행\체크리스트\운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P19" s="10" t="n"/>
@@ -4355,8 +4358,8 @@
 2) 시설물 시공상태, 기술기준 준수 및 완공 가능 여부 사전점검 체크리스트를 완수하라.</t>
         </is>
       </c>
-      <c r="K20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\표준서\사전점검 및 철도기술기준 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\표준서\사전점검 및 철도기술기준 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -4365,8 +4368,8 @@
 2) 시설물 시공상태, 기술기준 준수 여부 및 공종별시험 결과보고서를 검토하십시오.</t>
         </is>
       </c>
-      <c r="M20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -4375,8 +4378,8 @@
 2) 철도시설물 시공상태, 기술기준 준수 및 안전성 분석 결과를 검토하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\체크리스트\사전점검 및 철도기술기준 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\19_사전점검 및 철도기술기준 검토\체크리스트\사전점검 및 철도기술기준 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P20" s="10" t="n"/>
@@ -4450,8 +4453,8 @@
 2) 신호설비와 차량 간 연계성 및 철도차량 운행 적합성 검증 결과표를 승인 완수하라.</t>
         </is>
       </c>
-      <c r="K21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -4460,8 +4463,8 @@
 2) 신호설비와 차량 간 연계 적정성 및 철도차량 운행 적합 여부를 서면 판정하십시오.</t>
         </is>
       </c>
-      <c r="M21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -4470,8 +4473,8 @@
 2) 신호설비와 차량 간 연계성 및 차량 운행 적합성을 검증하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\체크리스트\시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\20_시설물 검증시험\체크리스트\시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P21" s="10" t="n"/>
@@ -4545,8 +4548,8 @@
 2) 영업운전과 동일 조건 열차스케줄 및 승무원 노선숙지 등 최종 영업준비를 완수하라.</t>
         </is>
       </c>
-      <c r="K22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\표준서\영업 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\표준서\영업 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L22" s="11" t="inlineStr">
@@ -4555,8 +4558,8 @@
 2) 영업운전과 동일한 조건으로 열차운행 스케줄 및 영업설비 최종 점검을 완료하십시오.</t>
         </is>
       </c>
-      <c r="M22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -4565,8 +4568,8 @@
 2) 영업운전 동일 조건 행사수송 및 승무원 노선숙지 훈련을 완수하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\체크리스트\영업 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\21_영업 시운전\체크리스트\영업 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P22" s="10" t="n"/>
@@ -4635,8 +4638,8 @@
 2) 현장조성 및 유지관리 지침서 이행 여부를 확인하고 관제 MMI 보수를 완수하라.</t>
         </is>
       </c>
-      <c r="K23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\표준서\유지관리 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\표준서\유지관리 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L23" s="11" t="inlineStr">
@@ -4645,8 +4648,8 @@
 2) 현장 조성 및 유지관리 지침서 이행 여부를 점검하여 서면 보고하십시오.</t>
         </is>
       </c>
-      <c r="M23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\수행지침\LTE-R_무선_AP를_통한_신호_제어_데이터_송수신_레벨_상세절차서.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -4655,8 +4658,8 @@
 2) 현장조성 및 유지관리 지침서 이행 여부를 점검 확인하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\체크리스트\유지관리 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\7.신호분야\22_유지관리 설치\체크리스트\유지관리 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P23" s="10" t="n"/>
@@ -4866,8 +4869,8 @@
 2) LTE-R 무선망, 8대 이종 통신시스템, 타공종 간섭 및 리스크 헷지·기회반영 설계변경 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L2" s="65" t="inlineStr">
@@ -4876,8 +4879,8 @@
 2) 시공성 및 설계변경: 현장 지장물 실측 조사, 타공종 3D 간섭 조정, 공법/안전 검토 및 현장 전직원+본사 동시 검토 회의로 설계변경 수립</t>
         </is>
       </c>
-      <c r="M2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N2" s="65" t="inlineStr">
@@ -4886,8 +4889,8 @@
 2) LTE-R 무선망, 타공종 3D 간섭조정, 8대 이종 통신시스템, 관제연동 적정성 검토 및 현장전직원+본사 동시 검토 승인을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\체크리스트\9000-2-1_설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\1_설계적정성 검토\체크리스트\9000-2-1_설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P2" s="61" t="n"/>
@@ -4965,8 +4968,8 @@
 2) 주요 통신 자재 납품 수급 계획 및 시공 적격성 평가를 반영한 발주전략 KOM 보고서 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L3" s="65" t="inlineStr">
@@ -4975,8 +4978,8 @@
 2) 전략 수립 및 승인: 리스크 헷지형 계약 조건 도출 및 현장소장/공무팀 주관 발주전략 KOM 보고서 확정</t>
         </is>
       </c>
-      <c r="M3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N3" s="65" t="inlineStr">
@@ -4985,8 +4988,8 @@
 2) 주요 자재 납품 수급 계획 및 적격 시공업체 평가 기준을 마련하여 발주전략 KOM 승인을 완수하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\2_착수전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P3" s="61" t="n"/>
@@ -5054,8 +5057,8 @@
 2) 타공종 구조체 타설 전 통신 매립 배관 위치 검증 및 인터페이스 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\표준서\토목 _ 건축 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\표준서\토목 _ 건축 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L4" s="65" t="inlineStr">
@@ -5064,8 +5067,8 @@
 2) 협의 수행 및 승인: 타공종 구조체 콘크리트 타설 전 통신 배관 매립 위치 현장 확인 및 3D 간섭 조정 협의록 확정</t>
         </is>
       </c>
-      <c r="M4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\수행지침\토목 _ 건축 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\수행지침\토목 _ 건축 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N4" s="65" t="inlineStr">
@@ -5074,8 +5077,8 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\체크리스트\9000-2-3_토목 _ 건축 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\3_토목 _ 건축 인터페이스 협의\체크리스트\9000-2-3_토목 _ 건축 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P4" s="61" t="n"/>
@@ -5148,8 +5151,8 @@
 2) 타공종 간 전자기 적합성(EMC/EMI), 전력 케이블 유도장해 차폐 및 서지 보호 표준 적용</t>
         </is>
       </c>
-      <c r="K5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\표준서\전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\표준서\전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L5" s="65" t="inlineStr">
@@ -5158,8 +5161,8 @@
 2) 3D/BIM 간섭조정 및 승인: 이종 시스템 간 인터페이스 핀 맵, 데이터 포맷 교차 검증 및 시스템 합동 인터페이스 협의록 작성</t>
         </is>
       </c>
-      <c r="M5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\수행지침\전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\수행지침\전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N5" s="65" t="inlineStr">
@@ -5168,8 +5171,8 @@
 2) KEC 점유율[KEC 33%] 전선관 내부 단면적 점유율 33% 이하 및 ELP ø150mm×6개×2조 배관을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\체크리스트\9000-2-4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의\체크리스트\9000-2-4_전기 _ 신호 _ 기계 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P5" s="61" t="n"/>
@@ -5237,8 +5240,8 @@
 2) 제작사 간 데이터 입출력 포맷 및 연동 케이블 사양서 확정 협의록 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\표준서\통신설비 제작사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\표준서\통신설비 제작사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L6" s="65" t="inlineStr">
@@ -5247,8 +5250,8 @@
 2) 연동 시험 수칙 수립: 제작사 간 신호 연동 핀 배열 확정 및 상호 연동 인터페이스 사양서 감리 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\수행지침\통신설비 제작사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\수행지침\통신설비 제작사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N6" s="65" t="inlineStr">
@@ -5257,8 +5260,8 @@
 2) 전원 잭 확인[코드 잭 준비] 각 장비에 220V 코드를 꽂을지 48V 전기를 줄지 전원 잭을 사전에 확인하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\체크리스트\9000-2-5_통신설비 제작사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\5_통신설비 제작사 인터페이스 협의\체크리스트\9000-2-5_통신설비 제작사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P6" s="61" t="n"/>
@@ -5328,8 +5331,8 @@
 2) 관제 서버, 네트워크 스위치 및 운영사 통합 수선 체계 부합성 확인 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L7" s="65" t="inlineStr">
@@ -5338,8 +5341,8 @@
 2) 관제 인터페이스 승인: 관제 서버-현장 장치 간 제어 데이터 송수신 시험 절차 수립 및 운영사 합동 검토서 확정</t>
         </is>
       </c>
-      <c r="M7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\수행지침\관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\수행지침\관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N7" s="65" t="inlineStr">
@@ -5348,8 +5351,8 @@
 2) 4K CCTV 65개[명당 자리] 교차로 4K CCTV 카메라 65개소가 사각지대 없이 보이도록 명당 자리를 배치하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\체크리스트\9000-2-6_관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\6_관제 및 운영사 인터페이스 협의\체크리스트\9000-2-6_관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P7" s="61" t="n"/>
@@ -5417,8 +5420,8 @@
 2) 품질시험계획서 수립 및 발주처 승인 품질 기준 준수서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\표준서\발주처 품질 요구사항 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\표준서\발주처 품질 요구사항 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L8" s="65" t="inlineStr">
@@ -5427,8 +5430,8 @@
 2) 품질 관리 수립: 현장 품질시험계획서 수립, 불합격 자재 반출 절차 확립 및 발주처 승인 품질 수칙 이행</t>
         </is>
       </c>
-      <c r="M8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\수행지침\발주처 품질 요구사항 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\수행지침\발주처 품질 요구사항 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N8" s="65" t="inlineStr">
@@ -5437,8 +5440,8 @@
 2) [Hold Point] 감리원 현장 직접 입회 검측 항목(Hold Point)을 사전 분류 지정하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\체크리스트\9000-2-7_발주처 품질 요구사항 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\7_발주처 품질 요구사항 검토\체크리스트\9000-2-7_발주처 품질 요구사항 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P8" s="61" t="n"/>
@@ -5506,8 +5509,8 @@
 2) 예정공정표 대비 인원·장비 투입 수급 타당성 및 안전 수칙 준수 검토 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\표준서\자재 인력 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\표준서\자재 인력 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L9" s="65" t="inlineStr">
@@ -5516,8 +5519,8 @@
 2) 공정 수급 승인: 예정공정표 대비 적정 투입 인원 산출, 작업 안전 구역 확보 및 현장소장 투입 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\수행지침\자재 인력 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\수행지침\자재 인력 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N9" s="65" t="inlineStr">
@@ -5526,8 +5529,8 @@
 2) [인력 자격] 통신 공종별 특급/고급 기술자 자격증 및 현장 배치 계획을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\체크리스트\자재 인력 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\체크리스트\자재 인력 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P9" s="61" t="n"/>
@@ -5604,8 +5607,8 @@
 2) 간섭사항 사전 도출 및 공종 간 공정 마일스톤 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\표준서\자재 인력 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\표준서\자재 인력 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L10" s="65" t="inlineStr">
@@ -5614,8 +5617,8 @@
 2) 간섭 리스크 해소: 공사 착수 전 분야별 간섭 위험 요소를 발굴하여 헷지 방안 수립 및 Big Room 회의록 최종 승인</t>
         </is>
       </c>
-      <c r="M10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\수행지침\자재 인력 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\수행지침\자재 인력 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N10" s="65" t="inlineStr">
@@ -5624,8 +5627,8 @@
 2) [인터페이스] 노반(궤도)/전기/신호/기계/차량 5대 공종 간 관통 경로 및 간섭점을 사전 도출 검출하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\체크리스트\자재 인력 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\8_자재 인력 장비 등 투입 사전 검토\체크리스트\자재 인력 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P10" s="61" t="n"/>
@@ -5694,8 +5697,8 @@
 2) 감리단 및 발주처 승인을 위한 제작사양서 승인 신청서 및 공학적 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\표준서\착수 전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\표준서\착수 전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L11" s="65" t="inlineStr">
@@ -5704,8 +5707,8 @@
 2) 공학적 승인 신청: 발주처 입찰시방과 제작사양서 1:1 대조 검증 및 감리단 공학적 승인 제출 절차 수행</t>
         </is>
       </c>
-      <c r="M11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\수행지침\착수 전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\수행지침\착수 전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N11" s="65" t="inlineStr">
@@ -5714,8 +5717,8 @@
 2) [사양서 정의] 실제 제작·설치될 통신설비의 전기적·기계적 세부 규격 및 제작도면(Shop Drawing)을 작성하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\체크리스트\9000-2-9_착수 전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\9_착수 전 Big Room 회의\체크리스트\9000-2-9_착수 전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P11" s="61" t="n"/>
@@ -5786,8 +5789,8 @@
 2) 통신설비 설치 공법 타당성 및 감리단 시공계획서 승인 제출 표준 적용</t>
         </is>
       </c>
-      <c r="K12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\표준서\통신설비 제작 사양서 작성 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\표준서\통신설비 제작 사양서 작성 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L12" s="65" t="inlineStr">
@@ -5796,8 +5799,8 @@
 2) 감리 승인 및 이행: 시공상세도(Shop Drawing) 첨부, 현장 안전 위험성 평가 실시 및 감리단 시공계획서 승인 완료</t>
         </is>
       </c>
-      <c r="M12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\수행지침\통신설비 제작 사양서 작성 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\수행지침\통신설비 제작 사양서 작성 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N12" s="65" t="inlineStr">
@@ -5806,8 +5809,8 @@
 2) [안전 대책] 통신기계실 DC -48V 감전 방지 및 정거장 고소작업 시 안전대/2인1조 작업 대책을 수립하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\체크리스트\9000-2-10_통신설비 제작 사양서 작성 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\10_통신설비 제작 사양서 작성 _ 승인\체크리스트\9000-2-10_통신설비 제작 사양서 작성 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P12" s="61" t="n"/>
@@ -5878,8 +5881,8 @@
 2) 성능보증이 가능한 복수 자재공급원 승인 서류 수립 및 감리 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\표준서\시공 계획 수립 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\표준서\시공 계획 수립 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L13" s="65" t="inlineStr">
@@ -5888,8 +5891,8 @@
 2) 자재 승인 및 관리: 복수 공급원 비교 검토서 작성, 불량 자재 차단 헷지 및 감리단 자재공급원 승인 획득</t>
         </is>
       </c>
-      <c r="M13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\수행지침\시공 계획 수립 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\수행지침\시공 계획 수립 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N13" s="65" t="inlineStr">
@@ -5898,8 +5901,8 @@
 2) [사양 대조] 설계도서 수치(KCS 31 10 00)와 자재 카탈로그 규격 간 1:1 대조표를 정확히 작성하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\체크리스트\9000-2-11_시공 계획 수립 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\11_시공 계획 수립 _ 승인\체크리스트\9000-2-11_시공 계획 수립 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P13" s="61" t="n"/>
@@ -5972,8 +5975,8 @@
 2) 공장 수검 검사, 품질 성능 시험성적서 확인 및 공장검사 합격증명서 발급 표준 적용</t>
         </is>
       </c>
-      <c r="K14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\표준서\자재공급원 검토 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\표준서\자재공급원 검토 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L14" s="65" t="inlineStr">
@@ -5982,8 +5985,8 @@
 2) 입회 검사 실시: 전원 인입, 기능 시험, 방수/내열 공인시험 실측 확인 및 FAT 공장검사 합격증명서 획득</t>
         </is>
       </c>
-      <c r="M14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\수행지침\자재공급원 검토 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\수행지침\자재공급원 검토 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N14" s="65" t="inlineStr">
@@ -5992,8 +5995,8 @@
 2) [ITP 승인] 감리 승인된 ITP 절차서와 절연저항계(Megger), OTDR의 교정 유효기간 증명서를 사전 확인하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\체크리스트\9000-2-12_자재공급원 검토 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\12_자재공급원 검토 및 승인\체크리스트\9000-2-12_자재공급원 검토 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P14" s="61" t="n"/>
@@ -6063,8 +6066,8 @@
 2) 바닥 엑세스플로어, 방화 구획 및 기초 구조체 인수인계 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\표준서\통신설비 공정제작 _ 제작사 공장검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\표준서\통신설비 공정제작 _ 제작사 공장검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L15" s="65" t="inlineStr">
@@ -6073,8 +6076,8 @@
 2) 인수인계 승인: 미비 사항 현장 보완 조치 요구 및 통신 시공 적격 선행 공정 인수인계 확인서 최종 승인</t>
         </is>
       </c>
-      <c r="M15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\수행지침\통신설비 공정제작 _ 제작사 공장검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\수행지침\통신설비 공정제작 _ 제작사 공장검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N15" s="65" t="inlineStr">
@@ -6083,8 +6086,8 @@
 2) 토목, 건축, 통신 현장 담당자 3자 공조 체계를 구성하고 현장 합동 점검표, Mandrel 도통시험기 및 레이저 레벨기를 사전 준비하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\체크리스트\9000-2-13_통신설비 공정제작 _ 제작사 공장검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\13_통신설비 공정제작 _ 제작사 공장검사\체크리스트\9000-2-13_통신설비 공정제작 _ 제작사 공장검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P15" s="61" t="n"/>
@@ -6154,8 +6157,8 @@
 2) 장비 반입 허가서 작성 및 안전 교육 이수 수료증 관리 표준 적용</t>
         </is>
       </c>
-      <c r="K16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\표준서\본공사 전 선행공정 인수인계 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\표준서\본공사 전 선행공정 인수인계 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L16" s="65" t="inlineStr">
@@ -6164,8 +6167,8 @@
 2) 안전 교육 이수: 통신 시공 작업자 대상 특별안전보건교육, 보호구 착용 점검 및 안전 교육 이수 수료 관리</t>
         </is>
       </c>
-      <c r="M16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\수행지침\본공사 전 선행공정 인수인계 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\수행지침\본공사 전 선행공정 인수인계 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N16" s="65" t="inlineStr">
@@ -6174,8 +6177,8 @@
 2) 토목/건축 등 타분야 양중 작업 간섭 여부를 사전 협의하고 양중 시간대를 분리 조율하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\체크리스트\9000-2-14_본공사 전 선행공정 인수인계 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\14_본공사 전 선행공정 인수인계 점검\체크리스트\9000-2-14_본공사 전 선행공정 인수인계 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P16" s="61" t="n"/>
@@ -6245,8 +6248,8 @@
 2) 자재검수 요청서 작성 및 감리 입회 검수 합격 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L17" s="65" t="inlineStr">
@@ -6255,8 +6258,8 @@
 2) 자재검수 보고: 감리 입회 자재 검수 실시, 자재검수 요청서 결재 및 현장 통신 자재 창고 입고 관리</t>
         </is>
       </c>
-      <c r="M17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\수행지침\장비반입 및 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\수행지침\장비반입 및 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N17" s="65" t="inlineStr">
@@ -6265,8 +6268,8 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\체크리스트\9000-2-15_장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\15_장비반입 및 안전교육\체크리스트\9000-2-15_장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P17" s="61" t="n"/>
@@ -6338,8 +6341,8 @@
 2) 케이블 성단, OTDR 접속 및 설비 고정 상태 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L18" s="65" t="inlineStr">
@@ -6348,8 +6351,8 @@
 2) 접속 및 검측: OTDR 접속 손실(≤0.05dB) 측정, 랙 전원 인입 배선 정리 및 설비 고정 상태 감리 검측</t>
         </is>
       </c>
-      <c r="M18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\수행지침\자재 반입 및 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\수행지침\자재 반입 및 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N18" s="65" t="inlineStr">
@@ -6358,8 +6361,8 @@
 2) 72-Core 광케이블 융착 접속 트레이 정돈 및 접속 손실 샘플 시공 승인을 획득하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\체크리스트\9000-2-16_자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\16_자재 반입 및 검수\체크리스트\9000-2-16_자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P18" s="61" t="n"/>
@@ -6428,8 +6431,8 @@
 2) 관제 시스템 전원 인입, 배선 정리 및 관제 환경 설치 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\표준서\통신설비 반입 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\표준서\통신설비 반입 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L19" s="65" t="inlineStr">
@@ -6438,8 +6441,8 @@
 2) 전원 및 계통 검측: 관제 전원 분배기 전원 인입, 이중화 네트워크 케이블 성단 및 관제실 설치 상태 확인</t>
         </is>
       </c>
-      <c r="M19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\수행지침\통신설비 반입 및 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\수행지침\통신설비 반입 및 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N19" s="65" t="inlineStr">
@@ -6448,8 +6451,8 @@
 2) 멀티 디스플레이 패널 간 베젤 이격 단차(≤0.5mm) 미세 조율 및 방진 가스켓 부착을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\체크리스트\9000-2-17_통신설비 반입 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\17_통신설비 반입 및 설치\체크리스트\9000-2-17_통신설비 반입 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P19" s="61" t="n"/>
@@ -6517,8 +6520,8 @@
 2) 설비별 단위시험 절차서 준수 및 단독 기능 시험성적서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\표준서\관제설비 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\표준서\관제설비 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L20" s="65" t="inlineStr">
@@ -6527,8 +6530,8 @@
 2) 단위성적서 작성: 단위시험 절차서 항목별 성능 측정, 불합격 항목 보완 조치 및 단위시험 성과표 확정</t>
         </is>
       </c>
-      <c r="M20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\수행지침\관제설비 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\수행지침\관제설비 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N20" s="65" t="inlineStr">
@@ -6537,8 +6540,8 @@
 2) RF 파워메터로 무선장치(RU) 송신 출력을 계측하여 표준 규격(43dBm ±0.5dB) 이내임을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\체크리스트\9000-2-18_관제설비 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\18_관제설비 설치\체크리스트\9000-2-18_관제설비 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P20" s="61" t="n"/>
@@ -6608,8 +6611,8 @@
 2) 통합시험 절차서 준수 및 이종 통신 설비 간 상호 연동성 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\표준서\통신시스템 단위시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\표준서\통신시스템 단위시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L21" s="65" t="inlineStr">
@@ -6618,8 +6621,8 @@
 2) 통합 성과 확인: 관제-현장 장치 간 제어 응답속도 검측, 통합 시험 성과표 작성 및 감리 승인 완료</t>
         </is>
       </c>
-      <c r="M21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\수행지침\통신시스템 단위시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\수행지침\통신시스템 단위시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N21" s="65" t="inlineStr">
@@ -6628,8 +6631,8 @@
 2) 관제 콘솔에서 PIS 문구 송출 명령 전송 시 현장 안내표시기 반응 지연 시간(≤0.5초 이내)을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\체크리스트\9000-2-19_통신시스템 단위시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\19_통신시스템 단위시험\체크리스트\9000-2-19_통신시스템 단위시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P21" s="61" t="n"/>
@@ -6697,8 +6700,8 @@
 2) 공종별 시험 항목 검측, 무선 전계강도 측정 및 시험성적서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\표준서\통신시스템 통합시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\표준서\통신시스템 통합시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L22" s="65" t="inlineStr">
@@ -6707,8 +6710,8 @@
 2) 공종 시험 승인: 무선 전계강도 측정 성과표 및 공종별 시운전 시험 결과 보고서 제출 및 감리 승인</t>
         </is>
       </c>
-      <c r="M22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\수행지침\통신시스템 통합시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\수행지침\통신시스템 통합시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N22" s="65" t="inlineStr">
@@ -6717,8 +6720,8 @@
 2) 광케이블 융착 접속점 접속 손실 수치가 시방 기준(≤0.1dB/접속점 이하)을 통과함을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\체크리스트\9000-2-20_통신시스템 통합시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\20_통신시스템 통합시험\체크리스트\9000-2-20_통신시스템 통합시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P22" s="61" t="n"/>
@@ -6790,8 +6793,8 @@
 2) 차량 투입 대비 통신 무무선 연동 안전 상태 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\표준서\9000-2-21_공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\표준서\9000-2-21_공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L23" s="65" t="inlineStr">
@@ -6800,8 +6803,8 @@
 2) 투입 안전 승인: 차량 투입 시 무선 통신 끊김 예방 점검 및 차량 투입 전 통신 안전 확인서 작성</t>
         </is>
       </c>
-      <c r="M23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\수행지침\공종별 시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\수행지침\공종별 시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N23" s="65" t="inlineStr">
@@ -6810,8 +6813,8 @@
 2) 궤도 주변 통신 케이블 트레이 및 광점퍼 선로 묶음이 건축한계 이내로 처지거나 돌출되지 않음을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\체크리스트\9000-2-21_공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\21_공종별 시험\체크리스트\9000-2-21_공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P23" s="61" t="n"/>
@@ -6880,8 +6883,8 @@
 2) 주행 중 통신 끊김 여부 및 차상-지상 간 통신 품질 성과표 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L24" s="65" t="inlineStr">
@@ -6890,8 +6893,8 @@
 2) 주행 통신 검측: 차상-지상 간 CCTV 영상 전송 및 관제 데이터 무선 통신 품질 성과표 최종 확정</t>
         </is>
       </c>
-      <c r="M24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\수행지침\차량 투입 전 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\수행지침\차량 투입 전 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N24" s="65" t="inlineStr">
@@ -6900,8 +6903,8 @@
 2) 주행 중 LTE-R 기지국 간 이동 시 핸드오버 성공률 100% 및 음성 무선 통화 끊김 0건을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\체크리스트\9000-2-22_차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\22_차량 투입 전 점검\체크리스트\9000-2-22_차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P24" s="61" t="n"/>
@@ -6970,8 +6973,8 @@
 2) 교육 교재 작성, 시스템 운용/장해 조치 실습 및 교육 이수 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\표준서\9000-2-23_차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\표준서\9000-2-23_차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L25" s="65" t="inlineStr">
@@ -6980,8 +6983,8 @@
 2) 교육 이수 확정: 현장 실습 교육 수행, 질문/답변 점검 및 운영자 교육 참석 이수 확인서 최종 작성</t>
         </is>
       </c>
-      <c r="M25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\수행지침\차량 시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\수행지침\차량 시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N25" s="65" t="inlineStr">
@@ -6990,8 +6993,8 @@
 2) 주요 장비 장애 시 대응할 수 있는 계통별 긴급 비상 조치 매뉴얼 교재를 편찬하였는가?</t>
         </is>
       </c>
-      <c r="O25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\체크리스트\9000-2-23_차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\23_차량 시운전\체크리스트\9000-2-23_차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P25" s="61" t="n"/>
@@ -7061,8 +7064,8 @@
 2) 사전점검 결과 보고서 작성 및 한국교통안전공단 제출 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L26" s="65" t="inlineStr">
@@ -7071,8 +7074,8 @@
 2) 점검 결과 승인: 기술기준 부합 여부 사전 검증, 지적사항 조치 완료 및 한국교통안전공단 사전점검 보고서 제출</t>
         </is>
       </c>
-      <c r="M26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\수행지침\운영자 교육시행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\수행지침\운영자 교육시행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N26" s="65" t="inlineStr">
@@ -7081,8 +7084,8 @@
 2) 발주처, 운영기관, 책임감리단 및 현장소장이 포함된 3자 합동 사전점검반을 조직하였는가?</t>
         </is>
       </c>
-      <c r="O26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\체크리스트\9000-2-24_운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\24_운영자 교육시행\체크리스트\9000-2-24_운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P26" s="61" t="n"/>
@@ -7153,8 +7156,8 @@
 2) LTE-R 무선 품질, 관제 데이터 전송률 및 시설물검증 합격 판정 표준 적용</t>
         </is>
       </c>
-      <c r="K27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\표준서\9000-2-25_사전점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\표준서\9000-2-25_사전점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L27" s="65" t="inlineStr">
@@ -7163,8 +7166,8 @@
 2) 검증 결과 확정: LTE-R 무선망 수신강도, 데이터 전송 지연시간 실측 및 시설물검증시험 합격 판정</t>
         </is>
       </c>
-      <c r="M27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\수행지침\9000-2-25_사전점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\수행지침\9000-2-25_사전점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N27" s="65" t="inlineStr">
@@ -7173,8 +7176,8 @@
 2) 전문기관인 한국교통안전공단으로부터 시설물검증시험계획 적격 승인을 수령하였는가?</t>
         </is>
       </c>
-      <c r="O27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\체크리스트\9000-2-25_사전점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\25_사전점검\체크리스트\9000-2-25_사전점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P27" s="61" t="n"/>
@@ -7247,8 +7250,8 @@
 2) 영업시운전 기간 중 통신 장애 0건 달성 및 시운전 완료 보고서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L28" s="65" t="inlineStr">
@@ -7257,8 +7260,8 @@
 2) 시운전 준공 확정: 영업시운전 기간 중 통신 장해 0건 달성 및 영업시운전 종합 결과 보고서 확정</t>
         </is>
       </c>
-      <c r="M28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\수행지침\시설물 검증시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\수행지침\시설물 검증시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N28" s="65" t="inlineStr">
@@ -7267,8 +7270,8 @@
 2) 전 정거장 행선안내게시기(PIS) 도착 시각 및 열치 위치 안내 오송출 0건을 달성하였는가?</t>
         </is>
       </c>
-      <c r="O28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\체크리스트\9000-2-26_시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\26_시설물 검증시험\체크리스트\9000-2-26_시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P28" s="61" t="n"/>
@@ -7336,8 +7339,8 @@
 2) 관할 지자체(화성시 등) 제출 및 설치신고 수리증 발급 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\표준서\9000-2-27_영업시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\표준서\9000-2-27_영업시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L29" s="65" t="inlineStr">
@@ -7346,8 +7349,8 @@
 2) 관할 관청 수리: 관할 지자체(화성시 등) 제출, 현장 서류 검토 수검 및 설치신고 수리증 발급 획득</t>
         </is>
       </c>
-      <c r="M29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\수행지침\9000-2-27_영업시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\수행지침\9000-2-27_영업시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N29" s="65" t="inlineStr">
@@ -7356,8 +7359,8 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\체크리스트\9000-2-27_영업시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\27_영업시운전\체크리스트\9000-2-27_영업시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P29" s="61" t="n"/>
@@ -7425,8 +7428,8 @@
 2) KCA(한국방송통신전파진흥원) 제출 및 무선국 개설허가서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\표준서\자가용전기통신설비 설치신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\표준서\자가용전기통신설비 설치신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L30" s="65" t="inlineStr">
@@ -7435,8 +7438,8 @@
 2) 무선국 허가 획득: KCA(한국방송통신전파진흥원) 서류 심사 수검 및 무선국 개설허가서 최종 발급</t>
         </is>
       </c>
-      <c r="M30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\수행지침\자가용전기통신설비 설치신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\수행지침\자가용전기통신설비 설치신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N30" s="65" t="inlineStr">
@@ -7445,8 +7448,8 @@
 2) 본선 지상 기지국 안테나 설치 위치, 높이, 이득(dBi) 및 지향각 제원을 조사하였는가?</t>
         </is>
       </c>
-      <c r="O30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\체크리스트\9000-2-28_자가용전기통신설비 설치신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\28_자가용전기통신설비 설치신고\체크리스트\9000-2-28_자가용전기통신설비 설치신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P30" s="61" t="n"/>
@@ -7514,8 +7517,8 @@
 2) 국가정보원/KISA 보안 적합성 검증 승인서 및 상호연동 시험 합격 표준 적용</t>
         </is>
       </c>
-      <c r="K31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\표준서\LTE-R 무선국 허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\표준서\LTE-R 무선국 허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L31" s="65" t="inlineStr">
@@ -7524,8 +7527,8 @@
 2) 보안 승인 획득: KISA/국가정보원 보안 적합성 검증 수검 및 상호운용성 검증 합격 승인서 획득</t>
         </is>
       </c>
-      <c r="M31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\수행지침\LTE-R 무선국 허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\수행지침\LTE-R 무선국 허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N31" s="65" t="inlineStr">
@@ -7534,8 +7537,8 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\체크리스트\LTE-R 무선국 허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국 허가\체크리스트\LTE-R 무선국 허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P31" s="61" t="n"/>
@@ -7603,8 +7606,8 @@
 2) 관할 지자체 현장 검측 수검 및 정보통신 사용전검사 필증 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\표준서\LTE-R 무선국허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\표준서\LTE-R 무선국허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L32" s="65" t="inlineStr">
@@ -7613,8 +7616,8 @@
 2) 필증 발급 획득: 관할 지자체 정보통신 검측 공무원 현장 실측 수검 및 정보통신 사용전검사 필증 획득</t>
         </is>
       </c>
-      <c r="M32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\수행지침\LTE-R 무선국허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\수행지침\LTE-R 무선국허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N32" s="65" t="inlineStr">
@@ -7623,8 +7626,8 @@
 2) 정거장 승강장 및 관제동 배관 입상부 배관 씰링 및 네임택 표기 상태를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\체크리스트\9000-2-29_LTE-R 무선국허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\29_LTE-R 무선국허가\체크리스트\9000-2-29_LTE-R 무선국허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P32" s="61" t="n"/>
@@ -7692,8 +7695,8 @@
 2) 무선 전계강도 및 준공 상태 검사 합격 후 무선국 준공검사 합격증명서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\표준서\LTE-R 상호운용성 및 보안적합성 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\표준서\LTE-R 상호운용성 및 보안적합성 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L33" s="65" t="inlineStr">
@@ -7702,8 +7705,8 @@
 2) 합격 증명 획득: 준공 실측 합격 판정 수검 및 KCA 무선국 준공검사 합격증명서 최종 발급 획득</t>
         </is>
       </c>
-      <c r="M33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\수행지침\LTE-R 상호운용성 및 보안적합성 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\수행지침\LTE-R 상호운용성 및 보안적합성 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N33" s="65" t="inlineStr">
@@ -7712,8 +7715,8 @@
 2) 개설허가서 사본, 기지국 시공 내역서 및 안테나 제원표 구비를 완료하였는가?</t>
         </is>
       </c>
-      <c r="O33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\체크리스트\9000-2-30_LTE-R 상호운용성 및 보안적합성 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\9.통신분야\30_LTE-R 상호운용성 및 보안적합성 검증\체크리스트\9000-2-30_LTE-R 상호운용성 및 보안적합성 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P33" s="61" t="n"/>
@@ -7920,8 +7923,8 @@
           <t>"전기공사업법, 전기사업법, 한국전기설비규정(KEC), 도로법(점용허가) 및 산업안전보건법 준수 여부를 1:1 검토한다."</t>
         </is>
       </c>
-      <c r="K2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L2" s="70" t="inlineStr">
@@ -7929,8 +7932,8 @@
           <t>본 지침서는 동탄트램 전기분야 사업 착공 전설계도서의 기술적·법적 적정성 검토 방법과현장 여건, 타공종 간섭, 공법·장비 시공성(Constructability) 검토 절차를 명확히 제시하여, 시공 위험 요소는 사전에 헷지(H...</t>
         </is>
       </c>
-      <c r="M2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N2" s="70" t="inlineStr">
@@ -7938,8 +7941,8 @@
           <t>본 체크리스트는 철도설계기준(KDS 47 00 00) 및 전기사업법에 의거하여,전기 분야 전반(송변전, 전력, 전차선, 배전, 접지, 인허가 등)에 대한 핵심 설계 적정성을 점검하고, 리스크(Risk) 헷지 및 기회(Oppo...</t>
         </is>
       </c>
-      <c r="O2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P2" s="10" t="n"/>
@@ -8009,8 +8012,8 @@
           <t>공정표 대비 노면전차 특수자재(전차선 강성가선, 변압기 등)의 공장 제작/조달 Lead Time을 사전 반영함.</t>
         </is>
       </c>
-      <c r="K3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L3" s="70" t="inlineStr">
@@ -8018,8 +8021,8 @@
           <t>본 지침서는 동탄트램 노면전차설비 공사 발주 전설계 및 현장 여건을 정밀 파악하고 8대 현실조건(자재 제작 Lead Time, 철도/경전철 시공 실적 Pool, 예비품, 시공중/후 운전 및 교육지원, 현장 자재창고 임대료, ...</t>
         </is>
       </c>
-      <c r="M3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N3" s="70" t="inlineStr">
@@ -8027,8 +8030,8 @@
           <t>본 체크리스트는 동탄트램 노면전차설비 공사 발주 착수 전8대 현실조건(자재 Lead Time, 시공 실적 Pool, 예비품, 시공중/후 교육 및 기술지원, 현장 자재창고 임대료, 가설 전원/용수/청소, 개통 후 상주 기술지원...</t>
         </is>
       </c>
-      <c r="O3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P3" s="10" t="n"/>
@@ -8088,8 +8091,8 @@
           <t>"정류기, 변압기, ESS 대형 기자재 반입 동선, 출입문 유효 폭/높이(H x W) 및 양중 훅 위치 실측 검증"</t>
         </is>
       </c>
-      <c r="K4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\표준서\토목 _ 건축 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\표준서\토목 _ 건축 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L4" s="70" t="inlineStr">
@@ -8097,8 +8100,8 @@
           <t>본 지침서는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 공동구/횡단관로/인입구 좌표, 전기 기능실 마감, 토목 공사용 매립 배관 검측 및 3D BIM 간섭 해소 절차를 명확히 제시하여, 콘크리트 구조체 타설 완료 후 ...</t>
         </is>
       </c>
-      <c r="M4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\수행지침\토목 _ 건축 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\수행지침\토목 _ 건축 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N4" s="70" t="inlineStr">
@@ -8106,8 +8109,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 변전실 개구부, 공동구/인입구 3D BIM 좌표, 전기 기능실 마감 및 토목 공사용 매립 배관의 적정성을 사전에 검측하여 구조체 타설 후 굴착/파쇄 재시공 충...</t>
         </is>
       </c>
-      <c r="O4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\체크리스트\토목 _ 건축 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\3_토목 _ 건축 인터페이스 협의\체크리스트\토목 _ 건축 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P4" s="10" t="n"/>
@@ -8171,8 +8174,8 @@
           <t>"신호, 통신, 기계, PSD 및 트램 차량 전력 공급 관로, 배선 용량 및 트레이 타공 누락 사항 정밀 추출"</t>
         </is>
       </c>
-      <c r="K5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\표준서\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\표준서\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L5" s="70" t="inlineStr">
@@ -8180,8 +8183,8 @@
           <t>전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 예방함</t>
         </is>
       </c>
-      <c r="M5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\수행지침\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\수행지침\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N5" s="70" t="inlineStr">
@@ -8189,8 +8192,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 ...</t>
         </is>
       </c>
-      <c r="O5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\체크리스트\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\4_신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의\체크리스트\신호 _ 통신 _ 기계 _ PSD _ 차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P5" s="10" t="n"/>
@@ -8249,8 +8252,8 @@
           <t>"SCADA RTU, 변전소 GIS, 정류기, ESS 릴레이 간 IEC 61850 및 Modbus 통신 핀 맵/신호 주소 1:1 검증"</t>
         </is>
       </c>
-      <c r="K6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\표준서\전기설비 제작사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\표준서\전기설비 제작사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L6" s="70" t="inlineStr">
@@ -8258,8 +8261,8 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조율 및 제작사양서 확정</t>
         </is>
       </c>
-      <c r="M6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\수행지침\전기설비 제작사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\수행지침\전기설비 제작사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N6" s="70" t="inlineStr">
@@ -8267,8 +8270,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조...</t>
         </is>
       </c>
-      <c r="O6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\체크리스트\전기설비 제작사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\5_전기설비 제작사 인터페이스 협의\체크리스트\전기설비 제작사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P6" s="10" t="n"/>
@@ -8332,8 +8335,8 @@
           <t>"지자체(수원시, 화성시) 도로교통관제 센터와 트램 우선신호 제어기 간 통신 인터페이스 및 연동 협의"</t>
         </is>
       </c>
-      <c r="K7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\표준서\관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L7" s="70" t="inlineStr">
@@ -8341,8 +8344,8 @@
           <t>수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 협의</t>
         </is>
       </c>
-      <c r="M7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\수행지침\관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\수행지침\관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N7" s="70" t="inlineStr">
@@ -8350,8 +8353,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 ...</t>
         </is>
       </c>
-      <c r="O7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\체크리스트\관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\6_관제 및 운영사 인터페이스 협의\체크리스트\관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P7" s="10" t="n"/>
@@ -8410,8 +8413,8 @@
           <t>"감리/감독원 입회 품질검측계획서(ITP: Inspection &amp; Test Plan) 작성 및 Hold Point(필수정지점) / Witness Point(입회점) 구분 명시"</t>
         </is>
       </c>
-      <c r="K8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\표준서\발주처 품질 요구사항 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\표준서\발주처 품질 요구사항 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L8" s="70" t="inlineStr">
@@ -8419,8 +8422,8 @@
           <t>감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반출 통제 수칙</t>
         </is>
       </c>
-      <c r="M8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\수행지침\발주처 품질 요구사항 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\수행지침\발주처 품질 요구사항 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N8" s="70" t="inlineStr">
@@ -8428,8 +8431,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반...</t>
         </is>
       </c>
-      <c r="O8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\체크리스트\발주처 품질 요구사항 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\7_발주처 품질 요구사항 검토\체크리스트\발주처 품질 요구사항 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P8" s="10" t="n"/>
@@ -8488,8 +8491,8 @@
           <t>"변압기, GIS, 정류기, ESS, 전차선 등 주요 전기자재 공장 제작 및 수급 소요 기간(Lead Time 30~60일)을 공정표와 사전 연동 통제"</t>
         </is>
       </c>
-      <c r="K9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\표준서\자재 _ 인원 _ 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\표준서\자재 _ 인원 _ 장비 등 투입 사전 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L9" s="70" t="inlineStr">
@@ -8497,8 +8500,8 @@
           <t>현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획서 승인</t>
         </is>
       </c>
-      <c r="M9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\수행지침\자재 _ 인원 _ 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\수행지침\자재 _ 인원 _ 장비 등 투입 사전 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N9" s="70" t="inlineStr">
@@ -8506,8 +8509,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획...</t>
         </is>
       </c>
-      <c r="O9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\체크리스트\자재 _ 인원 _ 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\8_자재 _ 인원 _ 장비 등 투입 사전 검토\체크리스트\자재 _ 인원 _ 장비 등 투입 사전 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P9" s="10" t="n"/>
@@ -8566,8 +8569,8 @@
           <t>"관할 한전에 수전 용량 계산서, 건축허가서, 22.9kV 수전 단선도 첨부 전기사용신청서 제출(처리기간 1개월) 및 인수점 지중 맨홀 협의"</t>
         </is>
       </c>
-      <c r="K10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\표준서\인허가 준비_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\표준서\인허가 준비_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L10" s="70" t="inlineStr">
@@ -8575,8 +8578,8 @@
           <t>한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do List 추적 관리</t>
         </is>
       </c>
-      <c r="M10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\수행지침\인허가 준비_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\수행지침\인허가 준비_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N10" s="70" t="inlineStr">
@@ -8584,8 +8587,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do Lis...</t>
         </is>
       </c>
-      <c r="O10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\체크리스트\인허가 준비_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\9_인허가 준비\체크리스트\인허가 준비_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P10" s="10" t="n"/>
@@ -8654,8 +8657,8 @@
           <t>"노반(궤도), 신호, 통신, 기계, PSD, 차량 인터페이스 및 3D BIM 공간 간섭을 전면 사전 검토한다."</t>
         </is>
       </c>
-      <c r="K11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\표준서\착수 전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\표준서\착수 전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L11" s="70" t="inlineStr">
@@ -8663,8 +8666,8 @@
           <t>본 지침서는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체 구축 방법,3D BIM 공종 간섭 조율, 자재 반입 동선/야적장 확보, 타 프로젝트 하자사례 분석 및 안전/민원 Risk He...</t>
         </is>
       </c>
-      <c r="M11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\수행지침\착수 전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\수행지침\착수 전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N11" s="70" t="inlineStr">
@@ -8672,8 +8675,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체를 구축하여 3D BIM 공종 간섭, 자재 반입 동선, 타 현장 하자사례 재발방지책 및 Risk Hedge 방안을 확정하기 ...</t>
         </is>
       </c>
-      <c r="O11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\체크리스트\착수 전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\10_착수 전 Big Room 회의\체크리스트\착수 전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P11" s="10" t="n"/>
@@ -8733,8 +8736,8 @@
           <t>"변압기 용량, 정류기 정격, ESS 배터리 세부 기술사양서 검토 및 시방 규격 1:1 대조 파악"</t>
         </is>
       </c>
-      <c r="K12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\표준서\전기설비 제작 사양서 작성 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\표준서\전기설비 제작 사양서 작성 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L12" s="70" t="inlineStr">
@@ -8742,8 +8745,8 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따른 상세 기술사양서 및 공장 제작 승인도면(Shop Drawing) 검토</t>
         </is>
       </c>
-      <c r="M12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\수행지침\전기설비 제작 사양서 작성 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\수행지침\전기설비 제작 사양서 작성 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N12" s="70" t="inlineStr">
@@ -8751,8 +8754,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 제작 사양서 작성 / 승인 업무 이행에 대해전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따...</t>
         </is>
       </c>
-      <c r="O12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\체크리스트\전기설비 제작 사양서 작성 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\11_전기설비 제작 사양서 작성 _ 승인\체크리스트\전기설비 제작 사양서 작성 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P12" s="10" t="n"/>
@@ -8814,8 +8817,8 @@
           <t>"변전기기 반입, Cable Tray 설치, 전차선 지주 입립 시공 순서 및 3D BIM 공정 수립"</t>
         </is>
       </c>
-      <c r="K13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\표준서\시공 계획 수립 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\표준서\시공 계획 수립 _ 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L13" s="70" t="inlineStr">
@@ -8823,8 +8826,8 @@
           <t>전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책 수립 후 감리단 공학적 승인 완수</t>
         </is>
       </c>
-      <c r="M13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\수행지침\시공 계획 수립 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\수행지침\시공 계획 수립 _ 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N13" s="70" t="inlineStr">
@@ -8832,8 +8835,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 계획 수립 / 승인 업무 이행에 대해전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책...</t>
         </is>
       </c>
-      <c r="O13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\체크리스트\시공 계획 수립 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\12_시공 계획 수립 _ 승인\체크리스트\시공 계획 수립 _ 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P13" s="10" t="n"/>
@@ -8894,8 +8897,8 @@
           <t>"제조사 공장등록증, 사업자등록증, ISO 품질인증서 및 유사 철도/트램 납품 실적 검증"</t>
         </is>
       </c>
-      <c r="K14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\표준서\자재공급원_기자재 제작도서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\표준서\자재공급원_기자재 제작도서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L14" s="70" t="inlineStr">
@@ -8903,8 +8906,8 @@
           <t>전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) 감리단 적격 승인 수검</t>
         </is>
       </c>
-      <c r="M14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\수행지침\자재공급원_기자재 제작도서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\수행지침\자재공급원_기자재 제작도서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N14" s="70" t="inlineStr">
@@ -8912,8 +8915,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재공급원/기자재 제작도서 승인 업무 이행에 대해전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) ...</t>
         </is>
       </c>
-      <c r="O14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\체크리스트\자재공급원_기자재 제작도서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\13_자재공급원_기자재 제작도서 승인\체크리스트\자재공급원_기자재 제작도서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P14" s="10" t="n"/>
@@ -8977,8 +8980,8 @@
           <t>"제작사 부품 조달 현황, 외함 판금/도장 및 내부 배선 조립 공정 공정표 100% 관리"</t>
         </is>
       </c>
-      <c r="K15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\표준서\전기설비 공정제작 _ 제작사 공장검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\표준서\전기설비 공정제작 _ 제작사 공장검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L15" s="70" t="inlineStr">
@@ -8986,8 +8989,8 @@
           <t>정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acceptance Test) 수행과 시험성적서 승인 완수</t>
         </is>
       </c>
-      <c r="M15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\수행지침\전기설비 공정제작 _ 제작사 공장검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\수행지침\전기설비 공정제작 _ 제작사 공장검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N15" s="70" t="inlineStr">
@@ -8995,8 +8998,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 공정제작 / 제작사 공장검사 업무 이행에 대해정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acc...</t>
         </is>
       </c>
-      <c r="O15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\체크리스트\전기설비 공정제작 _ 제작사 공장검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\14_전기설비 공정제작 _ 제작사 공장검사\체크리스트\전기설비 공정제작 _ 제작사 공장검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P15" s="10" t="n"/>
@@ -9057,8 +9060,8 @@
           <t>"건축 변전실 구조물 완성도, 노반 궤도 시공 상태 및 전기 설치 간섭 여부 정밀 실측"</t>
         </is>
       </c>
-      <c r="K16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\표준서\본공사 전 선행공정 인수인계 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\표준서\본공사 전 선행공정 인수인계 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L16" s="70" t="inlineStr">
@@ -9066,8 +9069,8 @@
           <t>토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행</t>
         </is>
       </c>
-      <c r="M16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\수행지침\본공사 전 선행공정 인수인계 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\수행지침\본공사 전 선행공정 인수인계 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N16" s="70" t="inlineStr">
@@ -9075,8 +9078,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 본공사 전 선행공정 인수인계 점검 업무 이행에 대해토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행 관...</t>
         </is>
       </c>
-      <c r="O16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\체크리스트\본공사 전 선행공정 인수인계 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\15_본공사 전 선행공정 인수인계 점검\체크리스트\본공사 전 선행공정 인수인계 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P16" s="10" t="n"/>
@@ -9137,8 +9140,8 @@
           <t>"장비 진입 경로 및 적치장 사전확인, 타분야 작업 일정 및 지상/지하 구조물 간섭 협의"</t>
         </is>
       </c>
-      <c r="K17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\표준서\장비반입 및 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L17" s="70" t="inlineStr">
@@ -9146,8 +9149,8 @@
           <t>고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시</t>
         </is>
       </c>
-      <c r="M17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\수행지침\장비반입 및 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\수행지침\장비반입 및 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N17" s="70" t="inlineStr">
@@ -9155,8 +9158,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 장비반입 및 안전교육 업무 이행에 대해고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시 관련 실무 요소...</t>
         </is>
       </c>
-      <c r="O17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\체크리스트\장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\16_장비반입 및 안전교육\체크리스트\장비반입 및 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P17" s="10" t="n"/>
@@ -9217,8 +9220,8 @@
           <t>"자재 하차 통제 구획 설정, 크레인 양중 신호수 배치 및 자재 반입 동선 안전 확보"</t>
         </is>
       </c>
-      <c r="K18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\표준서\자재 반입 및 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L18" s="70" t="inlineStr">
@@ -9226,8 +9229,8 @@
           <t>전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 확인</t>
         </is>
       </c>
-      <c r="M18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\수행지침\자재 반입 및 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\수행지침\자재 반입 및 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N18" s="70" t="inlineStr">
@@ -9235,8 +9238,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재 반입 및 검수 업무 이행에 대해전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 ...</t>
         </is>
       </c>
-      <c r="O18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\체크리스트\자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\17_자재 반입 및 검수\체크리스트\자재 반입 및 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P18" s="10" t="n"/>
@@ -9297,8 +9300,8 @@
           <t>"감리/감독 협의를 통한 시공 샘플 대상 선정, 시험시공 수행 및 시공 기준서 확정"</t>
         </is>
       </c>
-      <c r="K19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\표준서\전철전력설비 반입 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\표준서\전철전력설비 반입 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L19" s="70" t="inlineStr">
@@ -9306,8 +9309,8 @@
           <t>변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측</t>
         </is>
       </c>
-      <c r="M19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\수행지침\전철전력설비 반입 및 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\수행지침\전철전력설비 반입 및 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N19" s="70" t="inlineStr">
@@ -9315,8 +9318,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 전철전력설비 반입 및 설치 업무 이행에 대해변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측 관련 ...</t>
         </is>
       </c>
-      <c r="O19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\체크리스트\전철전력설비 반입 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\18_전철전력설비 반입 및 설치\체크리스트\전철전력설비 반입 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P19" s="10" t="n"/>
@@ -9377,8 +9380,8 @@
           <t>"한전 인수점 지중 맨홀부터 수전 전기실까지 Cable Tray 수평도 및 고정 행거 설치"</t>
         </is>
       </c>
-      <c r="K20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\표준서\수전용 케이블 트레이 및 케이블 포설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\표준서\수전용 케이블 트레이 및 케이블 포설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L20" s="70" t="inlineStr">
@@ -9386,8 +9389,8 @@
           <t>한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완수</t>
         </is>
       </c>
-      <c r="M20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\수행지침\수전용 케이블 트레이 및 케이블 포설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\수행지침\수전용 케이블 트레이 및 케이블 포설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N20" s="70" t="inlineStr">
@@ -9395,8 +9398,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전용 케이블 트레이 및 케이블 포설 업무 이행에 대해한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완...</t>
         </is>
       </c>
-      <c r="O20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\체크리스트\수전용 케이블 트레이 및 케이블 포설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\19_수전용 케이블 트레이 및 케이블 포설\체크리스트\수전용 케이블 트레이 및 케이블 포설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P20" s="10" t="n"/>
@@ -9458,8 +9461,8 @@
           <t>"한국전기안전공사 KESC 사용전검사 합격 필증 수령 및 수전 사전 조건 완수"</t>
         </is>
       </c>
-      <c r="K21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\표준서\수전 및 전기공급(급전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\표준서\수전 및 전기공급(급전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L21" s="70" t="inlineStr">
@@ -9467,8 +9470,8 @@
           <t>KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급전) 시행</t>
         </is>
       </c>
-      <c r="M21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\수행지침\수전 및 전기공급(급전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\수행지침\수전 및 전기공급(급전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N21" s="70" t="inlineStr">
@@ -9476,8 +9479,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전 및 전기공급(급전) 업무 이행에 대해KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급...</t>
         </is>
       </c>
-      <c r="O21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\체크리스트\수전 및 전기공급(급전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\20_수전 및 전기공급(급전)\체크리스트\수전 및 전기공급(급전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P21" s="10" t="n"/>
@@ -9540,8 +9543,8 @@
           <t>"감리단 제출용 SCADA 종합연동시험 계획서, 포인트 맵 및 점검 절차서 작성"</t>
         </is>
       </c>
-      <c r="K22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\표준서\종합연동시험(SCADA) 실시_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\표준서\종합연동시험(SCADA) 실시_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L22" s="70" t="inlineStr">
@@ -9549,8 +9552,8 @@
           <t>책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험 수행 및 검측 승인</t>
         </is>
       </c>
-      <c r="M22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\수행지침\종합연동시험(SCADA) 실시_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\수행지침\종합연동시험(SCADA) 실시_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N22" s="70" t="inlineStr">
@@ -9558,8 +9561,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 종합연동시험(SCADA) 실시 업무 이행에 대해책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험...</t>
         </is>
       </c>
-      <c r="O22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\체크리스트\종합연동시험(SCADA) 실시_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\21_종합연동시험(SCADA) 실시\체크리스트\종합연동시험(SCADA) 실시_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P22" s="10" t="n"/>
@@ -9618,8 +9621,8 @@
           <t>"철도종합시험운행 시행지침 제6조에 따른 전기 공종별 시험 항목 및 절차서 확정"</t>
         </is>
       </c>
-      <c r="K23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\표준서\공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\표준서\공종별 시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L23" s="70" t="inlineStr">
@@ -9627,8 +9630,8 @@
           <t>철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인</t>
         </is>
       </c>
-      <c r="M23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\수행지침\공종별 시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\수행지침\공종별 시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N23" s="70" t="inlineStr">
@@ -9636,8 +9639,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 공종별 시험 업무 이행에 대해철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인 관련 실무 요...</t>
         </is>
       </c>
-      <c r="O23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\체크리스트\공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\22_공종별 시험\체크리스트\공종별 시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P23" s="10" t="n"/>
@@ -9699,8 +9702,8 @@
           <t>"궤도 시공 정밀도 확인 및 트램 차량 건축한계(폭 3,600mm) 간섭 여부 레이저 실측"</t>
         </is>
       </c>
-      <c r="K24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\표준서\차량 투입 전 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L24" s="70" t="inlineStr">
@@ -9708,8 +9711,8 @@
           <t>노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수</t>
         </is>
       </c>
-      <c r="M24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\수행지침\차량 투입 전 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\수행지침\차량 투입 전 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N24" s="70" t="inlineStr">
@@ -9717,8 +9720,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 투입 전 점검 업무 이행에 대해노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수 관...</t>
         </is>
       </c>
-      <c r="O24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\체크리스트\차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\23_차량 투입 전 점검\체크리스트\차량 투입 전 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P24" s="10" t="n"/>
@@ -9778,8 +9781,8 @@
           <t>"철도안전법 철도차량 형식승인 절차에 따른 본선 구간 전기-차량 시운전 계획 수립"</t>
         </is>
       </c>
-      <c r="K25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\표준서\차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\표준서\차량 시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L25" s="70" t="inlineStr">
@@ -9787,8 +9790,8 @@
           <t>철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행</t>
         </is>
       </c>
-      <c r="M25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\수행지침\차량 시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\수행지침\차량 시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N25" s="70" t="inlineStr">
@@ -9796,8 +9799,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 시운전 업무 이행에 대해철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행 관련 실...</t>
         </is>
       </c>
-      <c r="O25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\체크리스트\차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\24_차량 시운전\체크리스트\차량 시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P25" s="10" t="n"/>
@@ -9857,8 +9860,8 @@
           <t>"전기자재 제작사 작성 운영/유지보수 매뉴얼, 비상 조치 절차서 및 교육 교재 검토"</t>
         </is>
       </c>
-      <c r="K26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\표준서\운영자 교육시행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L26" s="70" t="inlineStr">
@@ -9866,8 +9869,8 @@
           <t>전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부</t>
         </is>
       </c>
-      <c r="M26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\수행지침\운영자 교육시행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\수행지침\운영자 교육시행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N26" s="70" t="inlineStr">
@@ -9875,8 +9878,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 운영자 교육시행 업무 이행에 대해전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부 관련 ...</t>
         </is>
       </c>
-      <c r="O26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\체크리스트\운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\25_운영자 교육시행\체크리스트\운영자 교육시행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P26" s="10" t="n"/>
@@ -9937,8 +9940,8 @@
           <t>"철도종합시험운행 시행지침 제8조에 의거, 발주처-운영자 합동 사전점검 계획서 수립"</t>
         </is>
       </c>
-      <c r="K27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\표준서\사전점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\표준서\사전점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L27" s="70" t="inlineStr">
@@ -9946,8 +9949,8 @@
           <t>철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수</t>
         </is>
       </c>
-      <c r="M27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\수행지침\사전점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\수행지침\사전점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N27" s="70" t="inlineStr">
@@ -9955,8 +9958,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 사전점검 업무 이행에 대해철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수 관련 실무...</t>
         </is>
       </c>
-      <c r="O27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\체크리스트\사전점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\26_사전점검\체크리스트\사전점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P27" s="10" t="n"/>
@@ -10018,8 +10021,8 @@
           <t>"시설물검증시험계획을 운영자와 협의 수립하고 한국교통안전공단 전문기관 승인 수검"</t>
         </is>
       </c>
-      <c r="K28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\표준서\시설물 검증시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L28" s="70" t="inlineStr">
@@ -10027,8 +10030,8 @@
           <t>철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출</t>
         </is>
       </c>
-      <c r="M28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\수행지침\시설물 검증시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\수행지침\시설물 검증시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N28" s="70" t="inlineStr">
@@ -10036,8 +10039,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 시설물 검증시험 업무 이행에 대해철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출...</t>
         </is>
       </c>
-      <c r="O28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\체크리스트\시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\27_시설물 검증시험\체크리스트\시설물 검증시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P28" s="10" t="n"/>
@@ -10101,8 +10104,8 @@
           <t>"운영자-발주처 협의 영업시운전계획 수립, 국토부 전문기관(교통안전공단) 승인 완수"</t>
         </is>
       </c>
-      <c r="K29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\표준서\영업시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\표준서\영업시운전_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L29" s="70" t="inlineStr">
@@ -10110,8 +10113,8 @@
           <t>철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고</t>
         </is>
       </c>
-      <c r="M29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\수행지침\영업시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\수행지침\영업시운전_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N29" s="70" t="inlineStr">
@@ -10119,8 +10122,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 영업시운전 업무 이행에 대해철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고 ...</t>
         </is>
       </c>
-      <c r="O29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\체크리스트\영업시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\28_영업시운전\체크리스트\영업시운전_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P29" s="10" t="n"/>
@@ -10179,8 +10182,8 @@
           <t>"관할 한국전력공사 제출용 전기사용신청서, 변전소 용량 계산서 및 위임장 작성"</t>
         </is>
       </c>
-      <c r="K30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\표준서\전기 사용신청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\표준서\전기 사용신청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L30" s="70" t="inlineStr">
@@ -10188,8 +10191,8 @@
           <t>관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수</t>
         </is>
       </c>
-      <c r="M30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\수행지침\전기 사용신청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\수행지침\전기 사용신청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N30" s="70" t="inlineStr">
@@ -10197,8 +10200,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용신청 업무 이행에 대해관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수 관련 실무 요소를 100% 사전...</t>
         </is>
       </c>
-      <c r="O30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\체크리스트\전기 사용신청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\29_전기 사용신청\체크리스트\전기 사용신청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P30" s="10" t="n"/>
@@ -10257,8 +10260,8 @@
           <t>"전기사업법 시행규칙에 맞춘 공사계획서 및 전기설비 공사계획신고서 정밀 작성"</t>
         </is>
       </c>
-      <c r="K31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\표준서\공사계획신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\표준서\공사계획신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L31" s="70" t="inlineStr">
@@ -10266,8 +10269,8 @@
           <t>관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료</t>
         </is>
       </c>
-      <c r="M31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\수행지침\공사계획신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\수행지침\공사계획신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N31" s="70" t="inlineStr">
@@ -10275,8 +10278,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 공사계획신고 업무 이행에 대해관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료 관련 실무 요소를 100% 사전 검측하여 시공 하자...</t>
         </is>
       </c>
-      <c r="O31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\체크리스트\공사계획신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\30_공사계획신고\체크리스트\공사계획신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P31" s="10" t="n"/>
@@ -10335,8 +10338,8 @@
           <t>"노면전차선로 지주, 강성 가선, 브래킷 수량조서 및 시공 승인도면(Shop Drawing) 작성"</t>
         </is>
       </c>
-      <c r="K32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\표준서\전차선로 적합성 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\표준서\전차선로 적합성 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L32" s="70" t="inlineStr">
@@ -10344,8 +10347,8 @@
           <t>한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수</t>
         </is>
       </c>
-      <c r="M32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\수행지침\전차선로 적합성 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\수행지침\전차선로 적합성 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N32" s="70" t="inlineStr">
@@ -10353,8 +10356,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 노면전차선로 적합성 검증 업무 이행에 대해한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수 관련 실무 요소를 100...</t>
         </is>
       </c>
-      <c r="O32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\체크리스트\전차선로 적합성 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\31_전차선로 적합성 검증\체크리스트\전차선로 적합성 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P32" s="10" t="n"/>
@@ -10426,8 +10429,8 @@
           <t>"전기설비 설치 완료 후 7일 전 사용전검사신청서, 감리배치서, 단선도, 자재성적서 제출"</t>
         </is>
       </c>
-      <c r="K33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\표준서\전기 사용전검사 (전력_전차선_송변전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\표준서\전기 사용전검사 (전력_전차선_송변전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L33" s="70" t="inlineStr">
@@ -10435,8 +10438,8 @@
           <t>전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전), 경찰서 도로공사신고(3일전) 통합 수검 완료</t>
         </is>
       </c>
-      <c r="M33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\수행지침\전기 사용전검사 (전력_전차선_송변전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\수행지침\전기 사용전검사 (전력_전차선_송변전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N33" s="70" t="inlineStr">
@@ -10444,8 +10447,8 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용전검사 (전력/전차선/송변전) 업무 이행에 대해전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전...</t>
         </is>
       </c>
-      <c r="O33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\체크리스트\전기 사용전검사 (전력_전차선_송변전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\8.전기분야\32_전기 사용전검사 (전력_전차선_송변전)\체크리스트\전기 사용전검사 (전력_전차선_송변전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P33" s="10" t="n"/>
@@ -22077,8 +22080,8 @@
           <t>KDS 47 10 00 철도지반 설계기준 | 현장 가설 둔차선, 용지 경계 및 원지반 고저차 3D 레벨 현측 | 토공사 사전 현장 조사 보고서</t>
         </is>
       </c>
-      <c r="O2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\표준서\Site Survey_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\표준서\Site Survey_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P2" s="130" t="inlineStr">
@@ -22086,8 +22089,8 @@
           <t>1) 현장 가설 도로 및 용지 경계 현측 ➔ 2) 광학 레벨 원지반 고저차 측정 ➔ 3) 진입 도로 장애 요소 매핑 ➔ 4) 현장 조사 보고서 감리 제출</t>
         </is>
       </c>
-      <c r="Q2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\수행지침\Site Survey_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\수행지침\Site Survey_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R2" s="124" t="inlineStr">
@@ -22095,8 +22098,8 @@
           <t>가설 도로 폭/구배 현측, 원지반 고저차 레벨 측량 및 3D BIM 도면 오차 점검 (현장 조사 보고서)</t>
         </is>
       </c>
-      <c r="S2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\체크리스트\Site Survey_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\1_Site Survey\체크리스트\Site Survey_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T2" s="124" t="n"/>
@@ -22171,8 +22174,8 @@
           <t>KCS 47 10 25 시방 검토 | 사전 토공 토사/암석 깎기 및 성토 시방 규정 | 발주처·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="O3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\표준서\2_발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\표준서\2_발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P3" s="130" t="inlineStr">
@@ -22180,8 +22183,8 @@
           <t>1) 사전 토공 시방 요구조건 분석 ➔ 2) 3D BIM 도면 깎기/성토 수량 검증 ➔ 3) 토공 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="Q3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\수행지침\2_발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\수행지침\2_발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R3" s="124" t="inlineStr">
@@ -22189,8 +22192,8 @@
           <t>KCS 47 10 25 사전 토공 시방 검토, 토사/암석 깎기 수량 산출 및 3D BIM 간섭 zero (3자 킥오프 결재)</t>
         </is>
       </c>
-      <c r="S3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\체크리스트\2_발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\2_발주전략 KOM\체크리스트\2_발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T3" s="124" t="n"/>
@@ -22265,8 +22268,8 @@
           <t>지하안전법 제23조 | 현장 지장물, 연약 지반 층후 및 사면 붕괴 위험 요소 추출 | 사전 토공 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="O4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\표준서\Site Survey Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\표준서\Site Survey Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P4" s="130" t="inlineStr">
@@ -22274,8 +22277,8 @@
           <t>1) 지하 매설 지장물 &amp; 연약지반 현출 ➔ 2) 사면 붕괴 위험 구간 추출 ➔ 3) 흙막이 가설재 보강 수립 ➔ 4) 토공 리스크 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="Q4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\수행지침\Site Survey Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\수행지침\Site Survey Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R4" s="124" t="inlineStr">
@@ -22283,8 +22286,8 @@
           <t>지중 매설물 탐사, 연약 지반 층후 분석 및 사면 붕괴 위험 구간 흙막이 가설재 보강 수립</t>
         </is>
       </c>
-      <c r="S4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\체크리스트\Site Survey Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\3_Site Survey Risk 검토\체크리스트\Site Survey Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T4" s="124" t="n"/>
@@ -22359,8 +22362,8 @@
           <t>건산법 상생협력 수칙 | 토공 전문 기술자 1:1 전담 배치 &amp; 3자 주간 소통 회의 | 일일 Safety TBM 100% 이행</t>
         </is>
       </c>
-      <c r="O5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P5" s="130" t="inlineStr">
@@ -22368,8 +22371,8 @@
           <t>1) 토공 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 복지 지원 &amp; Safety TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R5" s="124" t="inlineStr">
@@ -22377,8 +22380,8 @@
           <t>토공 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 Safety TBM/음주 측정</t>
         </is>
       </c>
-      <c r="S5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\4_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T5" s="124" t="n"/>
@@ -22453,8 +22456,8 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 우회 차선 설계 | 전담 신호수(2인 2조) &amp; LED 경광등 배치</t>
         </is>
       </c>
-      <c r="O6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\표준서\공사중 교통처리계획_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\표준서\공사중 교통처리계획_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P6" s="130" t="inlineStr">
@@ -22462,8 +22465,8 @@
           <t>1) 교통 우회 차선 &amp; 둔차선 도면 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\수행지침\공사중 교통처리계획_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\수행지침\공사중 교통처리계획_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R6" s="124" t="inlineStr">
@@ -22471,8 +22474,8 @@
           <t>동탄경찰서 도로점용 허가, 가설 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="S6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\체크리스트\공사중 교통처리계획_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\5_공사중 교통처리계획\체크리스트\공사중 교통처리계획_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T6" s="124" t="n"/>
@@ -22547,8 +22550,8 @@
           <t>KCS 47 10 25 자재 시방 | 굴착 장비, 가설 펜스 및 배수관 자재 발주 승인 | 공인시험기관 성적표 수속</t>
         </is>
       </c>
-      <c r="O7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\표준서\자재발주 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\표준서\자재발주 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P7" s="130" t="inlineStr">
@@ -22556,8 +22559,8 @@
           <t>1) 굴착 장비 및 가설 펜스 자재 선정 ➔ 2) 공인시험기관 시험성적서 검수 ➔ 3) 자재 발주 신청서 제출 ➔ 4) 자재 반입 검수 통보서 결재</t>
         </is>
       </c>
-      <c r="Q7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R7" s="124" t="inlineStr">
@@ -22565,8 +22568,8 @@
           <t>KCS 47 10 25 굴착 장비/가설재 자재 승인, 공인시험기관 시험성적서 검수 및 자재 반입 통보</t>
         </is>
       </c>
-      <c r="S7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\6_자재발주 요청\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T7" s="124" t="n"/>
@@ -22637,8 +22640,8 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 차단 | 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="O8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\표준서\용지 사용 Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\표준서\용지 사용 Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P8" s="130" t="inlineStr">
@@ -22646,8 +22649,8 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="Q8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\수행지침\용지 사용 Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\수행지침\용지 사용 Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R8" s="124" t="inlineStr">
@@ -22655,8 +22658,8 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="S8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\체크리스트\용지 사용 Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\7_용지 사용 Risk 검토\체크리스트\용지 사용 Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T8" s="124" t="n"/>
@@ -22731,8 +22734,8 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 4자 빅룸 회의 | 사전 토공 마일스톤 서명 결재</t>
         </is>
       </c>
-      <c r="O9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P9" s="130" t="inlineStr">
@@ -22740,8 +22743,8 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 사전 토공 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="Q9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R9" s="124" t="inlineStr">
@@ -22749,8 +22752,8 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 사전 토공 마일스톤 연동 및 간섭 리스크 서명</t>
         </is>
       </c>
-      <c r="S9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\8_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T9" s="124" t="n"/>
@@ -22825,8 +22828,8 @@
           <t>도로법 및 환경영향평가법 | 지자체 도로점용 허가 및 비산먼지 발생신고 수속 | 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="O10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\표준서\인허가 절차 진행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\표준서\인허가 절차 진행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P10" s="130" t="inlineStr">
@@ -22834,8 +22837,8 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="Q10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\수행지침\인허가 절차 진행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\수행지침\인허가 절차 진행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R10" s="124" t="inlineStr">
@@ -22843,8 +22846,8 @@
           <t>지자체 도로/하천점용 허가서 접수, 비산먼지 발생사업 신고 필증 수속 및 보증보험 제출</t>
         </is>
       </c>
-      <c r="S10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\체크리스트\인허가 절차 진행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\9_인허가 절차 진행\체크리스트\인허가 절차 진행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T10" s="124" t="n"/>
@@ -22919,8 +22922,8 @@
           <t>도로교통법 안전 수칙 | 경찰서 차선 점용 허가 및 가설 둔차선 도로 복구 이행 보증보험 | 교통대책 감리 승인</t>
         </is>
       </c>
-      <c r="O11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\표준서\교통처리대책 협의 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\표준서\교통처리대책 협의 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P11" s="130" t="inlineStr">
@@ -22928,8 +22931,8 @@
           <t>1) 경찰서 차선 점용 허가증 수령 ➔ 2) 도로 복구 보증보험 증권 제출 ➔ 3) 전담 신호수 &amp; LED 경광등 배치 ➔ 4) 교통대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\수행지침\교통처리대책 협의 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\수행지침\교통처리대책 협의 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R11" s="124" t="inlineStr">
@@ -22937,8 +22940,8 @@
           <t>동탄경찰서 차선 점용 허가, 도로 복구 이행 보증보험 제출 및 전담 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="S11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\체크리스트\교통처리대책 협의 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\10_교통처리대책 협의 및 승인\체크리스트\교통처리대책 협의 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T11" s="124" t="n"/>
@@ -23013,8 +23016,8 @@
           <t>지하안전관리에 관한 특별법 | GPR 3D 관로 탐사 &amp; 인력 시탐 줄파기(깊이 1.5m) | 점용기관 현장 입회 이설 방호</t>
         </is>
       </c>
-      <c r="O12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\표준서\지장물 검토 및 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\표준서\지장물 검토 및 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P12" s="130" t="inlineStr">
@@ -23022,8 +23025,8 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 서면 승인</t>
         </is>
       </c>
-      <c r="Q12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\수행지침\지장물 검토 및 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\수행지침\지장물 검토 및 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R12" s="124" t="inlineStr">
@@ -23031,8 +23034,8 @@
           <t>GPR 3D 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 점용기관 1:1 현장 입회 매달기 방호</t>
         </is>
       </c>
-      <c r="S12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\체크리스트\지장물 검토 및 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\11_지장물 검토 및 협의\체크리스트\지장물 검토 및 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T12" s="124" t="n"/>
@@ -23107,8 +23110,8 @@
           <t>국유재산법 및 공유재산법 | 토지 기공승낙서 인허가 확인 및 진입로 점용 범위 실측 | 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="O13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\표준서\기공승낙 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\표준서\기공승낙 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P13" s="130" t="inlineStr">
@@ -23116,8 +23119,8 @@
           <t>1) 국유지/공유지 기공승낙서 수속 ➔ 2) 진입 도로 점용 범위 실측 ➔ 3) 토지 소유주 사용 협의 ➔ 4) 기공승낙서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\수행지침\기공승낙 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\수행지침\기공승낙 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R13" s="124" t="inlineStr">
@@ -23125,8 +23128,8 @@
           <t>국유지/공유지 기공승낙서 인허가 검증, 진입 도로 점용 범위 실측 및 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="S13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\체크리스트\기공승낙 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\12_기공승낙 적정성 검토\체크리스트\기공승낙 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T13" s="124" t="n"/>
@@ -23201,8 +23204,8 @@
           <t>소음진동관리법 준수 | 야간 공사 소음 방음벽(H=3m) 및 세륜기(깊이 1.2m) 가동 | 단수/단전 주민 사전 안내</t>
         </is>
       </c>
-      <c r="O14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\표준서\민원 저감 대책 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\표준서\민원 저감 대책 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P14" s="130" t="inlineStr">
@@ -23210,8 +23213,8 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="Q14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\수행지침\민원 저감 대책 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\수행지침\민원 저감 대책 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R14" s="124" t="inlineStr">
@@ -23219,8 +23222,8 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 세륜기(깊이 1.2m) 가동 및 단수/단전 주민 사전 고지</t>
         </is>
       </c>
-      <c r="S14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\체크리스트\민원 저감 대책 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\13_민원 저감 대책 수립\체크리스트\민원 저감 대책 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T14" s="124" t="n"/>
@@ -23295,8 +23298,8 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단</t>
         </is>
       </c>
-      <c r="O15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\표준서\용지보상 Risk 파악_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\표준서\용지보상 Risk 파악_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P15" s="130" t="inlineStr">
@@ -23304,8 +23307,8 @@
           <t>1) 미보상 필지 현출 &amp; 지적 대조 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 우회 토공 동선 수립 ➔ 4) 용지 보상 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="Q15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\수행지침\용지보상 Risk 파악_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\수행지침\용지보상 Risk 파악_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R15" s="124" t="inlineStr">
@@ -23313,8 +23316,8 @@
           <t>미보상 필지 지적 대조, 경계 가설 펜스(H=1.8m) 차단 및 우회 토공 동선 서면 승인</t>
         </is>
       </c>
-      <c r="S15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\체크리스트\용지보상 Risk 파악_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\14_용지보상 Risk 파악\체크리스트\용지보상 Risk 파악_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T15" s="124" t="n"/>
@@ -23389,8 +23392,8 @@
           <t>건진법 시행령 제89조 | 사전 토공 시공계획서 표준 8대 목차 검토 | 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="O16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\표준서\시공계획서 검토 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\표준서\시공계획서 검토 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P16" s="130" t="inlineStr">
@@ -23398,8 +23401,8 @@
           <t>1) 사전 토공 시공계획서 작성 ➔ 2) 8대 목차 &amp; KCS 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 시공계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\수행지침\시공계획서 검토 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\수행지침\시공계획서 검토 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R16" s="124" t="inlineStr">
@@ -23407,8 +23410,8 @@
           <t>사전 토공 시공계획서 표준 8대 목차, KCS 수치 수록 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="S16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\체크리스트\시공계획서 검토 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\15_시공계획서 검토 지원\체크리스트\시공계획서 검토 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T16" s="124" t="n"/>
@@ -23483,8 +23486,8 @@
           <t>KCS 47 10 25 토공 시방 | 깎기/성토 토공 유동표 작성 및 3D BIM 도면 대조 | 책임감리원 최종 승인</t>
         </is>
       </c>
-      <c r="O17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\표준서\설계변경 (착수전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\표준서\설계변경 (착수전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P17" s="130" t="inlineStr">
@@ -23492,8 +23495,8 @@
           <t>1) 토공 깎기/성토 유동표 작성 ➔ 2) 3D BIM 모델 표고 대조 ➔ 3) 사면 안성성 계산서 부착 ➔ 4) 토공 시공계획서 감리 최종 결재</t>
         </is>
       </c>
-      <c r="Q17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\수행지침\설계변경 (착수전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\수행지침\설계변경 (착수전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R17" s="124" t="inlineStr">
@@ -23501,8 +23504,8 @@
           <t>토공 깎기/성토 유동표 작성, 3D BIM 모델 표고 대조 및 사면 안전성 계산서 감리 결재</t>
         </is>
       </c>
-      <c r="S17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\체크리스트\설계변경 (착수전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\16_시공계획 수립\체크리스트\설계변경 (착수전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T17" s="124" t="n"/>
@@ -23577,8 +23580,8 @@
           <t>건진법 설계변경 수칙 | 궤도/구조물 후행 공종 요구 표고 오차(±10mm) 반영 | 설계변경 실정보고서 작성</t>
         </is>
       </c>
-      <c r="O18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\표준서\후행공종 요구조건 반영 설계변경 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\표준서\후행공종 요구조건 반영 설계변경 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P18" s="130" t="inlineStr">
@@ -23586,8 +23589,8 @@
           <t>1) 궤도/구조물 후행 요구 조건 수집 ➔ 2) 마무리면 표고 오차(±10mm) 반영 ➔ 3) 설계변경 실정보고서 작성 ➔ 4) 책임감리원 기술 승인</t>
         </is>
       </c>
-      <c r="Q18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\수행지침\후행공종 요구조건 반영 설계변경 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\수행지침\후행공종 요구조건 반영 설계변경 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R18" s="124" t="inlineStr">
@@ -23595,8 +23598,8 @@
           <t>궤도/구조물 후행 요구 조건 반영, 마무리면 표고 오차(±10mm) 반영 및 설계변경 실정보고</t>
         </is>
       </c>
-      <c r="S18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\체크리스트\후행공종 요구조건 반영 설계변경 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\17_후행공종 요구조건 반영 설계변경 검토\체크리스트\후행공종 요구조건 반영 설계변경 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T18" s="124" t="n"/>
@@ -23671,8 +23674,8 @@
           <t>지방계약법 정산 수칙 | 착수 전 토종 변경 및 수량 증감 실정보고 작성 | 총사업비 변경 승인 수속</t>
         </is>
       </c>
-      <c r="O19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\표준서\설계변경 (착수전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\표준서\설계변경 (착수전)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P19" s="130" t="inlineStr">
@@ -23680,8 +23683,8 @@
           <t>1) 토질 변경 &amp; 수량 증감 실정보고 작성 ➔ 2) 단가 비교표 작성 ➔ 3) 설계변경 도서 제출 ➔ 4) 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="Q19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\수행지침\설계변경 (착수전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\수행지침\설계변경 (착수전)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R19" s="124" t="inlineStr">
@@ -23689,8 +23692,8 @@
           <t>토질 변경 &amp; 수량 증감 실정보고서 작성, 단가 비교표 작성 및 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="S19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\체크리스트\설계변경 (착수전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경 (착수전)\체크리스트\설계변경 (착수전)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T19" s="124" t="n"/>
@@ -23765,8 +23768,8 @@
           <t>건진법 설계변경 규정 | 수량 산출서 및 단가 비교표 작성 | 책임감리원 기술 검토 의견서 첨부</t>
         </is>
       </c>
-      <c r="O20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\표준서\후행공종 요구조건 반영 설계변경 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\표준서\후행공종 요구조건 반영 설계변경 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P20" s="130" t="inlineStr">
@@ -23774,8 +23777,8 @@
           <t>1) 변경 수량 산출서 정밀 집계 ➔ 2) 신규 단가 산정 서류 부착 ➔ 3) 감리단 기술 검토 수속 ➔ 4) 설계변경 제출 서면 결재</t>
         </is>
       </c>
-      <c r="Q20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\수행지침\후행공종 요구조건 반영 설계변경 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\수행지침\후행공종 요구조건 반영 설계변경 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R20" s="124" t="inlineStr">
@@ -23783,8 +23786,8 @@
           <t>변경 수량 산출서 정밀 집계, 신규 단가 산정 서류 첨부 및 책임감리원 기술 검토 수속</t>
         </is>
       </c>
-      <c r="S20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\체크리스트\후행공종 요구조건 반영 설계변경 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\18_설계변경_착수전\체크리스트\후행공종 요구조건 반영 설계변경 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T20" s="124" t="n"/>
@@ -23859,8 +23862,8 @@
           <t>도로교통법 안전 수칙 | 게이트 바리케이트, 야간 LED 경광등 부설 | 전담 안전 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="O21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\표준서\설계변경 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\표준서\설계변경 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P21" s="130" t="inlineStr">
@@ -23868,8 +23871,8 @@
           <t>1) 게이트 바리케이트 &amp; 경광등 부설 ➔ 2) 우회 차선 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="Q21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\수행지침\설계변경 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\수행지침\설계변경 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R21" s="124" t="inlineStr">
@@ -23877,8 +23880,8 @@
           <t>게이트 바리케이트/LED 경광등 설치, 우회 차선 표지판 검측 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="S21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\체크리스트\설계변경 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\19_설계변경 지원\체크리스트\설계변경 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T21" s="124" t="n"/>
@@ -23953,8 +23956,8 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 굴착기, 덤프 정기검사증 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="O22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\표준서\교통관리 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\표준서\교통관리 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P22" s="130" t="inlineStr">
@@ -23962,8 +23965,8 @@
           <t>1) 10t+ 굴착기/덤프 사양 검수 ➔ 2) 건설기계 정기검사증 점검 ➔ 3) 후방 카메라/경보음 시동 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="Q22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\수행지침\교통관리 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\수행지침\교통관리 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R22" s="124" t="inlineStr">
@@ -23971,8 +23974,8 @@
           <t>자중 10t+ 굴착기/덤프 정기검사증, 후방 카메라/경보음 시동 점검 및 반입 허가 결재</t>
         </is>
       </c>
-      <c r="S22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\체크리스트\교통관리 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\20_교통관리 및 교통안전시설 설치\체크리스트\교통관리 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T22" s="124" t="n"/>
@@ -24047,8 +24050,8 @@
           <t>KCS 47 10 25 산림 벌목 시방 | 수목 벌목 및 뿌리 제거(벌근) 깊이 30cm 이상 | 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="O23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\표준서\장비 검수 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\표준서\장비 검수 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P23" s="130" t="inlineStr">
@@ -24056,8 +24059,8 @@
           <t>1) 현장 지반 수목 벌목 시행 ➔ 2) 뿌리 제거(벌근) 깊이 30cm 굴착 ➔ 3) 임목 폐기물 수속 처리 ➔ 4) 벌목 벌근 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="Q23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\수행지침\장비 검수 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\수행지침\장비 검수 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R23" s="124" t="inlineStr">
@@ -24065,8 +24068,8 @@
           <t>현장 수목 벌목 시행, 뿌리 제거(벌근) 깊이 30cm 이상 굴착 및 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="S23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\체크리스트\장비 검수 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\21_장비 검수 지원\체크리스트\장비 검수 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T23" s="124" t="n"/>
@@ -24141,8 +24144,8 @@
           <t>폐기물관리법 준수 | 기존 아스콘/콘크리트 구조물 안전 삭평 철거 | 건설 폐기물 성적표 수속</t>
         </is>
       </c>
-      <c r="O24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\표준서\벌목_벌근제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\표준서\벌목_벌근제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P24" s="130" t="inlineStr">
@@ -24150,8 +24153,8 @@
           <t>1) 기존 아스콘/콘크리트 삭평 철거 ➔ 2) 폐기물 분리 수거 &amp; 적재 ➔ 3) 건설 폐기물 위탁 처리 ➔ 4) 지장물 처리 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="Q24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\수행지침\벌목_벌근제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\수행지침\벌목_벌근제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R24" s="124" t="inlineStr">
@@ -24159,8 +24162,8 @@
           <t>기존 아스콘/콘크리트 삭평 철거, 건설 폐기물 분리 수거 적재 및 폐기물 성적서 수속</t>
         </is>
       </c>
-      <c r="S24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\체크리스트\벌목_벌근제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\22_벌목_벌근제거\체크리스트\벌목_벌근제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T24" s="124" t="n"/>
@@ -24235,8 +24238,8 @@
           <t>KCS 47 10 25 가설 도로 | 덤프트럭 진입 가설 도로 폭 6m 포설 | 쇄석 골재(두께 20cm) 부설 &amp; 살수</t>
         </is>
       </c>
-      <c r="O25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\표준서\기존구조물 _ 지장물 처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\표준서\기존구조물 _ 지장물 처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P25" s="130" t="inlineStr">
@@ -24244,8 +24247,8 @@
           <t>1) 가설 도로 폭 6m 성토 굴착 ➔ 2) 쇄석 골재(두께 20cm) 부설 ➔ 3) 10t 롤러 다짐 &amp; 살수 ➔ 4) 진입로 조성 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="Q25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\수행지침\기존구조물 _ 지장물 처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\수행지침\기존구조물 _ 지장물 처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R25" s="124" t="inlineStr">
@@ -24253,8 +24256,8 @@
           <t>가설 도로 폭 6m 성토 굴착, 쇄석 골재(두께 20cm) 부설, 10t 롤러 다짐 및 살수 점검</t>
         </is>
       </c>
-      <c r="S25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\체크리스트\기존구조물 _ 지장물 처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물 _ 지장물 처리\체크리스트\기존구조물 _ 지장물 처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T25" s="124" t="n"/>
@@ -24329,8 +24332,8 @@
           <t>KCS 47 10 25 배수 시방 | 가배수로(0.6×0.6m) &amp; 가침사지 설치 | 세륜기(깊이 1.2m) 가동 및 배수 검측</t>
         </is>
       </c>
-      <c r="O26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\표준서\기존구조물 _ 지장물 처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\표준서\기존구조물 _ 지장물 처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P26" s="130" t="inlineStr">
@@ -24338,8 +24341,8 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 터파기 ➔ 2) 세륜기(깊이 1.2m) 부설 ➔ 3) 양수 펌프 비치 ➔ 4) 배수 환경 시설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="Q26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\수행지침\기존구조물 _ 지장물 처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\수행지침\기존구조물 _ 지장물 처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R26" s="124" t="inlineStr">
@@ -24347,8 +24350,8 @@
           <t>가배수로(0.6×0.6m) &amp; 가침사지 설치, 세륜기(깊이 1.2m) 가동 및 수중 양수 펌프 비치</t>
         </is>
       </c>
-      <c r="S26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\체크리스트\기존구조물 _ 지장물 처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\23_기존구조물_지장물 처리\체크리스트\기존구조물 _ 지장물 처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T26" s="124" t="n"/>
@@ -24423,8 +24426,8 @@
           <t>KCS 47 10 25 굴착 규정 | 3D GPS 굴착기 표고 오차 ±20mm 통제 | 사면 비탈면 경사(1:1.5) 준수</t>
         </is>
       </c>
-      <c r="O27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\표준서\진입로 조성_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\표준서\진입로 조성_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P27" s="130" t="inlineStr">
@@ -24432,8 +24435,8 @@
           <t>1) 3D GPS 굴착기 정밀 세팅 ➔ 2) 토사 깎기 &amp; 사면 비탈면(1:1.5) 굴착 ➔ 3) 표고 오차(±20mm) 검측 ➔ 4) 토공 굴착 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="Q27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\수행지침\진입로 조성_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\수행지침\진입로 조성_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R27" s="124" t="inlineStr">
@@ -24441,8 +24444,8 @@
           <t>3D GPS 굴착기 표고 오차 ±20mm 통제, 사면 비탈면 경사(1:1.5 이하) 준수 및 굴착 검측</t>
         </is>
       </c>
-      <c r="S27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\체크리스트\진입로 조성_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\24_진입로 조성\체크리스트\진입로 조성_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T27" s="124" t="n"/>
@@ -24517,8 +24520,8 @@
           <t>KS F 2310 규정 준수 | 굴착 바닥 원지반 평판재하시험 K30 ≥ 70 MN/m³ | 덤프트럭 펌핑 연약 지반 점검</t>
         </is>
       </c>
-      <c r="O28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\표준서\배수_환경시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\표준서\배수_환경시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P28" s="130" t="inlineStr">
@@ -24526,8 +24529,8 @@
           <t>1) 굴착 바닥 원지반 수평 정리 ➔ 2) K30 평판재하시험(≥70 MN/m³) ➔ 3) 덤프트럭 펌핑 연약 지반 점검 ➔ 4) 노상토 지지력 성과표 승인</t>
         </is>
       </c>
-      <c r="Q28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\수행지침\배수_환경시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\수행지침\배수_환경시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R28" s="124" t="inlineStr">
@@ -24535,8 +24538,8 @@
           <t>굴착 바닥 평판재하시험 K30 ≥ 70 MN/m³, 덤프트럭 펌핑 연약 지반 점검 및 노상토 승인</t>
         </is>
       </c>
-      <c r="S28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\체크리스트\배수_환경시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\25_배수_환경시설 설치\체크리스트\배수_환경시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T28" s="124" t="n"/>
@@ -24611,8 +24614,8 @@
           <t>KCS 47 10 25 성토 시방 | 층두께 ≤ 30cm 토사 포설 | 10t 강동 롤러 다짐(들밀도 다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="O29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\표준서\토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\표준서\토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P29" s="130" t="inlineStr">
@@ -24620,8 +24623,8 @@
           <t>1) 성토 토사 30cm 층포설 ➔ 2) 살수차 최적함수비 살수 ➔ 3) 10t 강동 롤러 다짐(다짐도≥90%) ➔ 4) 성토 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="Q29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\수행지침\토공 굴착_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\수행지침\토공 굴착_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R29" s="124" t="inlineStr">
@@ -24629,8 +24632,8 @@
           <t>성토 토사 30cm 층포설, 살수차 최적함수비 OMC 살수 및 10t 롤러 다짐(다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="S29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\체크리스트\토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\26_토공 굴착\체크리스트\토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T29" s="124" t="n"/>
@@ -24705,8 +24708,8 @@
           <t>현장 통합 소통 수칙 | 일일 TBM 및 품질/안전 지원 대장 수록 | 감리 입회 검측 서면 승인</t>
         </is>
       </c>
-      <c r="O30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\표준서\노상토 지지력 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\표준서\노상토 지지력 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P30" s="130" t="inlineStr">
@@ -24714,8 +24717,8 @@
           <t>1) 일일 현장 품질/안전 지원 ➔ 2) TBM 및 근로자 교육 ➔ 3) 공정 장애 요소 해소 ➔ 4) 현장 지원 대장 서면 승인</t>
         </is>
       </c>
-      <c r="Q30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\수행지침\노상토 지지력 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\수행지침\노상토 지지력 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R30" s="124" t="inlineStr">
@@ -24723,8 +24726,8 @@
           <t>일일 현장 품질/안전 지원 대장, TBM 및 근로자 교육 시행 서면 승인</t>
         </is>
       </c>
-      <c r="S30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\체크리스트\노상토 지지력 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\27_노상토 지지력 확인\체크리스트\노상토 지지력 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T30" s="124" t="n"/>
@@ -24799,8 +24802,8 @@
           <t>KCS 47 10 25 인계인수 수칙 | 토공-강화노반 시공팀 3자 합동 레벨 측량 | 마무리면 인계인수서 서명</t>
         </is>
       </c>
-      <c r="O31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\표준서\쌓기 및 다짐(필요시)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\표준서\쌓기 및 다짐(필요시)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P31" s="130" t="inlineStr">
@@ -24808,8 +24811,8 @@
           <t>1) 토공-강화노반 시공팀 3자 합동 현측 ➔ 2) 마무리면 레벨 오차(±10mm) 확인 ➔ 3) 인계인수 합의서 서명 ➔ 4) 토공 마무리면 인계 완료</t>
         </is>
       </c>
-      <c r="Q31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\수행지침\쌓기 및 다짐(필요시)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\수행지침\쌓기 및 다짐(필요시)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R31" s="124" t="inlineStr">
@@ -24817,8 +24820,8 @@
           <t>토공-강화노반 시공팀 3자 합동 레벨 측량, 마무리면 레벨 오차(±10mm) 인계인수서 서명</t>
         </is>
       </c>
-      <c r="S31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\체크리스트\쌓기 및 다짐(필요시)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\28_쌓기 및 다짐_필요시\체크리스트\쌓기 및 다짐(필요시)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T31" s="124" t="n"/>
@@ -24849,18 +24852,18 @@
       <c r="L32" s="130" t="n"/>
       <c r="M32" s="130" t="n"/>
       <c r="N32" s="130" t="n"/>
-      <c r="O32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\표준서\현장지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\표준서\현장지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P32" s="130" t="n"/>
-      <c r="Q32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\수행지침\현장지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\수행지침\현장지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R32" s="124" t="n"/>
-      <c r="S32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\체크리스트\현장지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\29_현장지원\체크리스트\현장지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T32" s="124" t="n"/>
@@ -24883,18 +24886,18 @@
       <c r="L33" s="130" t="n"/>
       <c r="M33" s="130" t="n"/>
       <c r="N33" s="130" t="n"/>
-      <c r="O33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\표준서\강화노반 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\표준서\강화노반 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P33" s="130" t="n"/>
-      <c r="Q33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\수행지침\강화노반 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\수행지침\강화노반 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R33" s="124" t="n"/>
-      <c r="S33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\체크리스트\강화노반 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\30_강화노반 인계\체크리스트\강화노반 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T33" s="124" t="n"/>
@@ -24917,18 +24920,18 @@
       <c r="L34" s="130" t="n"/>
       <c r="M34" s="130" t="n"/>
       <c r="N34" s="130" t="n"/>
-      <c r="O34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\표준서\Task_32_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="O34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\표준서\Task_32_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="P34" s="130" t="n"/>
-      <c r="Q34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\수행지침\Task_32_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="Q34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\수행지침\Task_32_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="R34" s="124" t="n"/>
-      <c r="S34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\체크리스트\Task_32_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="S34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\2.사전토공사\32_Task_32\체크리스트\Task_32_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="T34" s="124" t="n"/>
@@ -25818,8 +25821,8 @@
           <t>지하안전관리에 관한 특별법 제23조 | 현장 지반 조사, GPR 탐사 데이터 및 신설 궤도 간섭 리스크 사전 분석 | 지장물 이설 리스크 관리계획 수립</t>
         </is>
       </c>
-      <c r="L2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\표준서\1_Site Survey Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\표준서\1_Site Survey Risk 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M2" s="16" t="inlineStr">
@@ -25827,8 +25830,8 @@
           <t>1) 지반 조사 주상도 &amp; GPR 데이터 대조 ➔ 2) 신설 궤도 구조물 간섭 관로 추출 ➔ 3) 기관별 이설 우선순위 수립 ➔ 4) 지장물 리스크 보고서 결재</t>
         </is>
       </c>
-      <c r="N2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\수행지침\1_Site Survey Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\수행지침\1_Site Survey Risk 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O2" s="40" t="inlineStr">
@@ -25836,8 +25839,8 @@
           <t>지반 시추 주상도, GPR 3D 지중 관로 탐사 데이터 대조 및 신설 궤도 구조물 간섭 관로 사전 현출 점검</t>
         </is>
       </c>
-      <c r="P2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\체크리스트\1_Site Survey Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\1_Site Survey Risk 검토\체크리스트\1_Site Survey Risk 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q2" s="13" t="n"/>
@@ -25913,8 +25916,8 @@
           <t>KCS 47 10 25 시방 준수 | 도급분 지장물 이설 발주 시방서 검토 &amp; 3D BIM 도면 대조 | 발주처·감리·시공 3자 킥오프 미팅 결재</t>
         </is>
       </c>
-      <c r="L3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\표준서\2_발주전략 KOM (도급지분)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\표준서\2_발주전략 KOM (도급지분)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M3" s="14" t="inlineStr">
@@ -25922,8 +25925,8 @@
           <t>1) 도급분 이설 시방서 요구조건 검토 ➔ 2) 3D BIM 도면 관로 좌표 대조 ➔ 3) 공기 지연 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\수행지침\2_발주전략 KOM (도급지분)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\수행지침\2_발주전략 KOM (도급지분)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O3" s="41" t="inlineStr">
@@ -25931,8 +25934,8 @@
           <t>KCS 47 10 25 시방 요구조건, 도급분 지장물 이설 수량 및 3D BIM 도면 간섭 zero 검증</t>
         </is>
       </c>
-      <c r="P3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\체크리스트\2_발주전략 KOM (도급지분)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전략 KOM (도급지분)\체크리스트\2_발주전략 KOM (도급지분)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q3" s="13" t="n"/>
@@ -26008,8 +26011,8 @@
           <t>지방계약법 및 관할 점용기관 규정 | 위수탁 지장물 이설 협약서 작성 &amp; 공문 발송 | 기관별 이설 소요 기간 및 예산 확보</t>
         </is>
       </c>
-      <c r="L4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\표준서\발주전적 KOM (도급지분)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\표준서\발주전적 KOM (도급지분)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M4" s="14" t="inlineStr">
@@ -26017,8 +26020,8 @@
           <t>1) 관할 점용기관 이설 요청 공문 작성 ➔ 2) 이설 협약서 정산 조건 수속 ➔ 3) 기관별 이설 소요 기간 협의 ➔ 4) 위수탁 이설 확약 공문 수령</t>
         </is>
       </c>
-      <c r="N4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\수행지침\발주전적 KOM (도급지분)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\수행지침\발주전적 KOM (도급지분)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O4" s="41" t="inlineStr">
@@ -26026,8 +26029,8 @@
           <t>위수탁 이설 요청 공문 부착, 점용기관 협약 조건 수속 및 이설 예비비 계상 서약</t>
         </is>
       </c>
-      <c r="P4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\체크리스트\발주전적 KOM (도급지분)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\2_발주전적 KOM (도급지분)\체크리스트\발주전적 KOM (도급지분)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q4" s="13" t="n"/>
@@ -26103,8 +26106,8 @@
           <t>건설산업기본법 제29조 | 상하수도 설비 전문건설업 면허 및 적정성(≥ 82%) 평가 | 노무비 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\표준서\3_지장물 이설 요청 (위수탁고)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\표준서\3_지장물 이설 요청 (위수탁고)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -26112,8 +26115,8 @@
           <t>1) 상하수도 전문건설업 면허 심사 ➔ 2) 하도급 적정성(≥ 82%) 평가 ➔ 3) 노무비 전용계좌 개설 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\수행지침\3_지장물 이설 요청 (위수탁고)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\수행지침\3_지장물 이설 요청 (위수탁고)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O5" s="41" t="inlineStr">
@@ -26121,8 +26124,8 @@
           <t>상하수도 전문건설업 면허/실적 심사, 하도급 적정성 평가(≥ 82%) 및 노무비 전용계좌 지정</t>
         </is>
       </c>
-      <c r="P5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\체크리스트\3_지장물 이설 요청 (위수탁고)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\3_지장물 이설 요청 (위수탁고)\체크리스트\3_지장물 이설 요청 (위수탁고)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q5" s="13" t="n"/>
@@ -26198,8 +26201,8 @@
           <t>지하안전법 수칙 | 한국전력, 도시가스, 수자원공사 1:1 현장 합동 조사 | 매설 위치, 관경(mm), 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="L6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\표준서\4_도급자분 이설업체 선정(상_하수)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\표준서\4_도급자분 이설업체 선정(상_하수)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -26207,8 +26210,8 @@
           <t>1) 한전/가스/수자원공사 1:1 현장 입회 ➔ 2) 관로 위치, 관경(mm), 깊이 현측 ➔ 3) 3D BIM 매설 관로 매핑 ➔ 4) 지장물 조사서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\수행지침\4_도급자분 이설업체 선정(상_하수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\수행지침\4_도급자분 이설업체 선정(상_하수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O6" s="41" t="inlineStr">
@@ -26216,8 +26219,8 @@
           <t>한국전력, 도시가스, 수자원공사 1:1 현장 입회 및 지하 매설물 관경(mm), 심도 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="P6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\체크리스트\4_도급자분 이설업체 선정(상_하수)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_도급자분 이설업체 선정(상_하수)\체크리스트\4_도급자분 이설업체 선정(상_하수)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q6" s="13" t="n"/>
@@ -26293,8 +26296,8 @@
           <t>KCS 47 10 25 배수 및 관체 수칙 | 지장물 이설 공정표, 가설 방호 및 교통 우회 계획 수립 | 공사 착수 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="L7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -26302,8 +26305,8 @@
           <t>1) 지장물 이설 공정표 수립 ➔ 2) 가설 매달기 방호 &amp; 우회 차선 설계 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 이설 계획서 책임감리원 승인</t>
         </is>
       </c>
-      <c r="N7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O7" s="41" t="inlineStr">
@@ -26311,8 +26314,8 @@
           <t>지장물 이설 공정표 수립, 가설 매달기 방호/우회 차선 설계 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\4_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="n"/>
@@ -26388,8 +26391,8 @@
           <t>건산법 상생협력 규정 | 지장물 전담 기술자 1:1 현장 배치 | 주간 3자 소통 회의 및 일일 TBM/안전교육 시행</t>
         </is>
       </c>
-      <c r="L8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\표준서\5_지장물 조사 (위탁기관 합동)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\표준서\5_지장물 조사 (위탁기관 합동)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M8" s="14" t="inlineStr">
@@ -26397,8 +26400,8 @@
           <t>1) 지장물 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\수행지침\5_지장물 조사 (위탁기관 합동)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\수행지침\5_지장물 조사 (위탁기관 합동)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O8" s="41" t="inlineStr">
@@ -26406,8 +26409,8 @@
           <t>지장물 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM/음주 측정(0.00%)</t>
         </is>
       </c>
-      <c r="P8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\체크리스트\5_지장물 조사 (위탁기관 합동)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_지장물 조사 (위탁기관 합동)\체크리스트\5_지장물 조사 (위탁기관 합동)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q8" s="13" t="n"/>
@@ -26483,8 +26486,8 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 합동 빅룸 회의 | 지장물 간섭 Zero 및 마일스톤 연동 확정</t>
         </is>
       </c>
-      <c r="L9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M9" s="14" t="inlineStr">
@@ -26492,8 +26495,8 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 지장물 이설 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="N9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O9" s="41" t="inlineStr">
@@ -26501,8 +26504,8 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 지장물 간섭 Zero 및 마일스톤 연동 회의록 서명</t>
         </is>
       </c>
-      <c r="P9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\5_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q9" s="13" t="n"/>
@@ -26578,8 +26581,8 @@
           <t>도로법 및 하천법 준수 | 지자체 도로점용 허가 및 하천점용 허가서 접수 | 관련 부서 협의 및 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="L10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\표준서\관리기관(맑은물사업소) 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\표준서\관리기관(맑은물사업소) 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M10" s="14" t="inlineStr">
@@ -26587,8 +26590,8 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="N10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\수행지침\관리기관(맑은물사업소) 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\수행지침\관리기관(맑은물사업소) 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O10" s="41" t="inlineStr">
@@ -26596,8 +26599,8 @@
           <t>지자체 도로점용 허가 &amp; 하천점용 허가서 수속, 보증보험 증권 제출 및 법정 인허가 필증 검수</t>
         </is>
       </c>
-      <c r="P10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\체크리스트\관리기관(맑은물사업소) 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_관리기관(맑은물사업소) 협의\체크리스트\관리기관(맑은물사업소) 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q10" s="13" t="n"/>
@@ -26673,8 +26676,8 @@
           <t>도로교통법 제69조 | 관할 경찰서 교통안전 심의 및 점용 허가 수령 | 우회 차선 도면 작성 및 안전 신호수 배치</t>
         </is>
       </c>
-      <c r="L11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\표준서\지장물 이설 계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\표준서\지장물 이설 계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M11" s="14" t="inlineStr">
@@ -26682,8 +26685,8 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O11" s="41" t="inlineStr">
@@ -26691,8 +26694,8 @@
           <t>동탄경찰서 도로점용 허가, 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\체크리스트\지장물 이설 계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\6_지장물 이설 계획 수립\체크리스트\지장물 이설 계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q11" s="13" t="n"/>
@@ -26768,8 +26771,8 @@
           <t>대기환경보전법 및 소음진동관리법 | 야간 공사 소음 억제 방음벽(H=3m) 및 세륜기 가동 | 단수/단전 사전 안내 및 민원 대응반 가동</t>
         </is>
       </c>
-      <c r="L12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\표준서\위수탁 지장물 이설 설계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\표준서\위수탁 지장물 이설 설계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M12" s="14" t="inlineStr">
@@ -26777,8 +26780,8 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="N12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O12" s="41" t="inlineStr">
@@ -26786,8 +26789,8 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 이동식 세륜기(깊이 1.2m) 가동 및 단수 사전 주민 알림</t>
         </is>
       </c>
-      <c r="P12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\체크리스트\위수탁 지장물 이설 설계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_위수탁 지장물 이설 설계\체크리스트\위수탁 지장물 이설 설계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q12" s="13" t="n"/>
@@ -26863,8 +26866,8 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단 및 우회 동선</t>
         </is>
       </c>
-      <c r="L13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\표준서\7_최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\표준서\7_최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M13" s="14" t="inlineStr">
@@ -26872,8 +26875,8 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="N13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\수행지침\7_최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\수행지침\7_최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O13" s="41" t="inlineStr">
@@ -26881,8 +26884,8 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\체크리스트\7_최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\7_최고의 팀 만들기 지원\체크리스트\7_최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q13" s="13" t="n"/>
@@ -26958,8 +26961,8 @@
           <t>수도법 및 하수도법 규정 | 맑은물사업소 합동 이설 위치 검토 &amp; 수돗물 단수 일정 수협 | 신구관 접속 설계도서 서면 결재</t>
         </is>
       </c>
-      <c r="L14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\표준서\상하수도 이설계획 실정보고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\표준서\상하수도 이설계획 실정보고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M14" s="14" t="inlineStr">
@@ -26967,8 +26970,8 @@
           <t>1) 맑은물사업소 이설 위치 현측 ➔ 2) 단수 일정(최대 6시간) 협의 ➔ 3) 신구관 접속 도면 검토 ➔ 4) 이설 승인 공문 수령</t>
         </is>
       </c>
-      <c r="N14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\수행지침\상하수도 이설계획 실정보고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\수행지침\상하수도 이설계획 실정보고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O14" s="41" t="inlineStr">
@@ -26976,8 +26979,8 @@
           <t>맑은물사업소 합동 이설 위치 검토, 수돗물 단수 일정(최대 6h) 수협 및 신구관 접속 도면 결재</t>
         </is>
       </c>
-      <c r="P14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\체크리스트\상하수도 이설계획 실정보고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_상하수도 이설계획 실정보고\체크리스트\상하수도 이설계획 실정보고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q14" s="13" t="n"/>
@@ -27053,8 +27056,8 @@
           <t>지하관로 설계기준 준수 | 위수탁 기관 설계도서 기술 검토 &amp; 3D BIM 간섭 점검 | 총사업비 변경 승인 및 설계 도서 수록</t>
         </is>
       </c>
-      <c r="L15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\표준서\8_착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\표준서\8_착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M15" s="14" t="inlineStr">
@@ -27062,8 +27065,8 @@
           <t>1) 위수탁 기관 설계도서 수속 ➔ 2) 3D BIM 간섭 리스크 점검 ➔ 3) 총사업비 변경 수량 검증 ➔ 4) 위수탁 설계도서 감리 승인</t>
         </is>
       </c>
-      <c r="N15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\수행지침\8_착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\수행지침\8_착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O15" s="41" t="inlineStr">
@@ -27071,8 +27074,8 @@
           <t>위수탁 기관 설계도서 기술 검토, 3D BIM 간섭 리스크 점검 및 총사업비 변경 수량 승인</t>
         </is>
       </c>
-      <c r="P15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\체크리스트\8_착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\8_착수전 Big Room 회의\체크리스트\8_착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q15" s="13" t="n"/>
@@ -27148,8 +27151,8 @@
           <t>건진법 시행령 규정 | 현장 지장물 현출에 따른 실정보고서 작성 | 공법 변경 및 수량 증감에 대한 책임감리 승인</t>
         </is>
       </c>
-      <c r="L16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\표준서\위수탁 계약 체결_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\표준서\위수탁 계약 체결_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M16" s="14" t="inlineStr">
@@ -27157,8 +27160,8 @@
           <t>1) 현장 지장물 현출 실정보고 작성 ➔ 2) 공법 변경 &amp; 수량 증감 산출 ➔ 3) 기술 검토 의견서 첨부 ➔ 4) 실정보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O16" s="41" t="inlineStr">
@@ -27166,8 +27169,8 @@
           <t>현장 지장물 현출 실정보고서 작성, 공법 변경 및 수량 증감 산출 책임감리원 승인</t>
         </is>
       </c>
-      <c r="P16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\체크리스트\위수탁 계약 체결_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_위수탁 계약 체결\체크리스트\위수탁 계약 체결_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q16" s="13" t="n"/>
@@ -27243,8 +27246,8 @@
           <t>지방자치단체 계약법 | 관할 점용기관과 위수탁 이설 협약서 정산 조건 체결 | 공사비 분담금 및 예비비 계상 합의</t>
         </is>
       </c>
-      <c r="L17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\표준서\9_인허가 절차 진행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\표준서\9_인허가 절차 진행_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M17" s="14" t="inlineStr">
@@ -27252,8 +27255,8 @@
           <t>1) 관할 점용기관 협약 조건 수속 ➔ 2) 정산 분담금 &amp; 예비비 협의 ➔ 3) 위수탁 계약서 작성 ➔ 4) 위수탁 이설 계약 체결 승인</t>
         </is>
       </c>
-      <c r="N17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\수행지침\9_인허가 절차 진행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\수행지침\9_인허가 절차 진행_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O17" s="41" t="inlineStr">
@@ -27261,8 +27264,8 @@
           <t>관할 점용기관 위수탁 이설 협약서 체결, 공사비 분담금 및 예비비 계상 합의 서약</t>
         </is>
       </c>
-      <c r="P17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\체크리스트\9_인허가 절차 진행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\9_인허가 절차 진행\체크리스트\9_인허가 절차 진행_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q17" s="13" t="n"/>
@@ -27338,8 +27341,8 @@
           <t>도로법 제61조 준수 | 지자체 도로 굴착 허가 신청서 접수 및 심의 필 | 도로 복구 이행 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="L18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\표준서\10_교통처리대책 협의 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\표준서\10_교통처리대책 협의 및 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M18" s="14" t="inlineStr">
@@ -27347,8 +27350,8 @@
           <t>1) 도로 굴착 허가 신청서 작성 ➔ 2) 지자체 도로굴착 심의 필 ➔ 3) 복구 보증보험 증권 제출 ➔ 4) 도로 굴착 허가증 감리 결재</t>
         </is>
       </c>
-      <c r="N18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\수행지침\10_교통처리대책 협의 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\수행지침\10_교통처리대책 협의 및 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O18" s="41" t="inlineStr">
@@ -27356,8 +27359,8 @@
           <t>지자체 도로 굴착 허가 신청서 접수, 심의 필증 수령 및 도로 복구 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="P18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\체크리스트\10_교통처리대책 협의 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_교통처리대책 협의 및 승인\체크리스트\10_교통처리대책 협의 및 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q18" s="13" t="n"/>
@@ -27433,8 +27436,8 @@
           <t>도로교통법 안전 수칙 | 게이트 및 굴착 구간 안전 바리케이트, LED 경광등 부설 | 전담 신호수(2인 2조) 100% 현장 배치</t>
         </is>
       </c>
-      <c r="L19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\표준서\도로점용_굴착행위 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\표준서\도로점용_굴착행위 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M19" s="14" t="inlineStr">
@@ -27442,8 +27445,8 @@
           <t>1) 굴착 구간 안전 바리케이트 부설 ➔ 2) 야간 LED 경광등 &amp; 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="N19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\수행지침\도로점용_굴착행위 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\수행지침\도로점용_굴착행위 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O19" s="41" t="inlineStr">
@@ -27451,8 +27454,8 @@
           <t>굴착 구간 안전 바리케이트 부설, 야간 LED 경광등 설치 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="P19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\체크리스트\도로점용_굴착행위 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\10_도로점용_굴착행위 인허가\체크리스트\도로점용_굴착행위 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q19" s="13" t="n"/>
@@ -27528,8 +27531,8 @@
           <t>지하안전법 제23조 | GPR 3D 탐사 후 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) | 실체 관로 노출 및 위치 표지판 비치</t>
         </is>
       </c>
-      <c r="L20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\표준서\교통통제 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\표준서\교통통제 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M20" s="14" t="inlineStr">
@@ -27537,8 +27540,8 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 실체 관로 노출 &amp; 위치 매핑 ➔ 4) 지장물 현측표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\수행지침\교통통제 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\수행지침\교통통제 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O20" s="41" t="inlineStr">
@@ -27546,8 +27549,8 @@
           <t>GPR 3D 지중 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 실체 관로 노출 매핑</t>
         </is>
       </c>
-      <c r="P20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\체크리스트\교통통제 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_교통통제 및 교통안전시설 설치\체크리스트\교통통제 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q20" s="13" t="n"/>
@@ -27623,8 +27626,8 @@
           <t>KCS 47 10 25 굴착 시방 | 굴착 사면 비탈면 경사(1:1.5) 준수 및 흙막이 가설재 부설 | 굴착 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="L21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\표준서\11_민원 저감 대책 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\표준서\11_민원 저감 대책 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M21" s="14" t="inlineStr">
@@ -27632,8 +27635,8 @@
           <t>1) 굴착 비탈면 경사(1:1.5) 측량 ➔ 2) 굴착 &amp; 흙막이 가설재 부설 ➔ 3) 바닥 원지반 K30(≥70) 검측 ➔ 4) 굴착 완료 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\수행지침\11_민원 저감 대책 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\수행지침\11_민원 저감 대책 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O21" s="41" t="inlineStr">
@@ -27641,8 +27644,8 @@
           <t>굴착 비탈면 경사(1:1.5 이하) 측량, 흙막이 가설재 부설 및 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="P21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\체크리스트\11_민원 저감 대책 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\11_민원 저감 대책 수립\체크리스트\11_민원 저감 대책 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q21" s="13" t="n"/>
@@ -27718,8 +27721,8 @@
           <t>KS 관로 자재 규정 준수 | 신규 상하수도관/가스관 부설 및 모래 기초(두께 10cm) 부설 | 관로 경사(≥ 0.5%) 및 수평 위치 검측</t>
         </is>
       </c>
-      <c r="L22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\표준서\12_용지보상 Risk 파악_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\표준서\12_용지보상 Risk 파악_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M22" s="14" t="inlineStr">
@@ -27727,8 +27730,8 @@
           <t>1) 관로 모래 기초(10cm) 부설 ➔ 2) 신규 상하수도관/가스관 부설 ➔ 3) 관로 종단 구배(≥0.5%) 검측 ➔ 4) 신규 관로 부설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\수행지침\12_용지보상 Risk 파악_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\수행지침\12_용지보상 Risk 파악_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O22" s="41" t="inlineStr">
@@ -27736,8 +27739,8 @@
           <t>관로 모래 기초(두께 10cm) 부설, 신규 상하수도관/가스관 부설 및 종단 구배(≥ 0.5%) 검측</t>
         </is>
       </c>
-      <c r="P22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\체크리스트\12_용지보상 Risk 파악_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_용지보상 Risk 파악\체크리스트\12_용지보상 Risk 파악_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q22" s="13" t="n"/>
@@ -27813,8 +27816,8 @@
           <t>수도시설 공학 규정 | 무단수 천공기 및 밸브 차단 장치 정밀 세팅 | 수압 시험 및 밸브 가동 상태 시운전 검측</t>
         </is>
       </c>
-      <c r="L23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\표준서\줄따기(GPR)를 통한 기존 지장물 매설 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\표준서\줄따기(GPR)를 통한 기존 지장물 매설 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M23" s="14" t="inlineStr">
@@ -27822,8 +27825,8 @@
           <t>1) 무단수 천공기 정밀 세팅 ➔ 2) 차단 밸브 &amp; 챔버 설치 ➔ 3) 수압 시험 및 가동 시운전 ➔ 4) 무단수 시설 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O23" s="41" t="inlineStr">
@@ -27831,8 +27834,8 @@
           <t>무단수 천공기 정밀 세팅, 차단 밸브 &amp; 챔버 설치 및 수압 시험/가동 시운전 검측</t>
         </is>
       </c>
-      <c r="P23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\체크리스트\줄따기(GPR)를 통한 기존 지장물 매설 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\12_줄따기(GPR)를 통한 기존 지장물 매설 확인\체크리스트\줄따기(GPR)를 통한 기존 지장물 매설 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q23" s="13" t="n"/>
@@ -27908,8 +27911,8 @@
           <t>관로 연결 시방 수칙 | 신구 관로 접속 부위 수압 시험(10kgf/cm², 1시간 유지) | 누수 여부 점검 및 부식 방지 랩핑 부설</t>
         </is>
       </c>
-      <c r="L24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\표준서\13_관리기관(맑은물사업소) 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\표준서\13_관리기관(맑은물사업소) 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -27917,8 +27920,8 @@
           <t>1) 신구 관로 접속 부위 부설 ➔ 2) 수압 시험(10kgf/cm², 1h 유지) ➔ 3) 부식 방지 피복 랩핑 시행 ➔ 4) 관로 접속 검측 성과표 승인</t>
         </is>
       </c>
-      <c r="N24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\수행지침\관리기관(맑은물사업소) 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\수행지침\관리기관(맑은물사업소) 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O24" s="41" t="inlineStr">
@@ -27926,8 +27929,8 @@
           <t>신구 관로 접속 부위 부설, 수압 시험(10kgf/cm², 1h 유지) 및 부식 방지 피복 랩핑 검측</t>
         </is>
       </c>
-      <c r="P24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\체크리스트\관리기관(맑은물사업소) 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_관리기관(맑은물사업소) 협의\체크리스트\관리기관(맑은물사업소) 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q24" s="13" t="n"/>
@@ -28003,8 +28006,8 @@
           <t>폐기물관리법 준수 | 폐관로 수거 및 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 | 아스콘 가포설 및 평탄성 통제</t>
         </is>
       </c>
-      <c r="L25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\표준서\이설 위치 토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\표준서\이설 위치 토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -28012,8 +28015,8 @@
           <t>1) 기존 폐관로 안전 철거/수거 ➔ 2) 토사 30cm 층다짐(다짐도≥95%) ➔ 3) 아스콘 가포설 &amp; 평탄성 검측 ➔ 4) 원상복구 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O25" s="41" t="inlineStr">
@@ -28021,8 +28024,8 @@
           <t>기존 폐관로 안전 철거/수거, 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 및 아스콘 가포설</t>
         </is>
       </c>
-      <c r="P25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\체크리스트\이설 위치 토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\13_이설 위치 토공 굴착\체크리스트\이설 위치 토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q25" s="13" t="n"/>
@@ -28098,8 +28101,8 @@
           <t>수도법 규정 준수 | 광역상수관(Ø500mm+) 이설 수압 시험 및 수질 검사 합격 | 한국수자원공사 입회 인수 완료</t>
         </is>
       </c>
-      <c r="L26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\표준서\신규관로 매설 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\표준서\신규관로 매설 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -28107,8 +28110,8 @@
           <t>1) 광역상수관(Ø500mm+) 부설 ➔ 2) 수압 시험 &amp; 수질 검사 시행 ➔ 3) 한국수자원공사 현장 입회 ➔ 4) 광역상수관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O26" s="41" t="inlineStr">
@@ -28116,8 +28119,8 @@
           <t>광역상수관(Ø500mm+) 부설, 수압 시험 및 수질 검사 합격 (한국수자원공사 1:1 입회 검측)</t>
         </is>
       </c>
-      <c r="P26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\체크리스트\신규관로 매설 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_신규관로 매설 및 설치\체크리스트\신규관로 매설 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q26" s="13" t="n"/>
@@ -28193,8 +28196,8 @@
           <t>지자체 상수도 시방 | 배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 | 맑은물사업소 합동 현측 승인</t>
         </is>
       </c>
-      <c r="L27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\표준서\14_위수탁 지장물 이설 설계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\표준서\14_위수탁 지장물 이설 설계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -28202,8 +28205,8 @@
           <t>1) 배수관(Ø200~300mm) 이설 부설 ➔ 2) 탁수 퇴수 &amp; 잔류염소 시험 ➔ 3) 맑은물사업소 합동 현측 ➔ 4) 상수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O27" s="41" t="inlineStr">
@@ -28211,8 +28214,8 @@
           <t>배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 합격 (맑은물사업소 현측)</t>
         </is>
       </c>
-      <c r="P27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\체크리스트\위수탁 지장물 이설 설계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\14_위수탁 지장물 이설 설계\체크리스트\위수탁 지장물 이설 설계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q27" s="13" t="n"/>
@@ -28288,8 +28291,8 @@
           <t>하수도정비 기본계획 | 하수관(Ø400mm+) 연결, CCTV 관로 내부 검사 및 통수 담수 시험 | 하수도사업소 현장 인수</t>
         </is>
       </c>
-      <c r="L28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\표준서\무단수 연결을 위한 시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\표준서\무단수 연결을 위한 시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -28297,8 +28300,8 @@
           <t>1) 하수관(Ø400mm+) 연결 부설 ➔ 2) CCTV 관로 내부 검사 시행 ➔ 3) 통수 담수 시험 완료 ➔ 4) 하수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\수행지침\무단수 연결을 위한 시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\수행지침\무단수 연결을 위한 시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O28" s="41" t="inlineStr">
@@ -28306,8 +28309,8 @@
           <t>하수관(Ø400mm+) 연결 부설, CCTV 관로 내부 검사 &amp; 통수 담수 시험 합격 (하수도사업소 인수)</t>
         </is>
       </c>
-      <c r="P28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\체크리스트\무단수 연결을 위한 시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_무단수 연결을 위한 시설 설치\체크리스트\무단수 연결을 위한 시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q28" s="13" t="n"/>
@@ -28383,8 +28386,8 @@
           <t>도시가스사업법 규정 | 가스관(중압/아중압) 비파괴검사(RT 100%) 및 기밀 시험 합격 | 도시가스사 1:1 입회 검측</t>
         </is>
       </c>
-      <c r="L29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\표준서\15_상하수도 이설계획 실정보고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\표준서\15_상하수도 이설계획 실정보고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -28392,8 +28395,8 @@
           <t>1) 도시가스관 매설 &amp; 용접 ➔ 2) 비파괴검사(RT 100%) &amp; 기밀 시험 ➔ 3) 도시가스사 1:1 입회 검측 ➔ 4) 가스관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\수행지침\상하수도 이설계획 실정보고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\수행지침\상하수도 이설계획 실정보고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O29" s="41" t="inlineStr">
@@ -28401,8 +28404,8 @@
           <t>도시가스관 매설 &amp; 용접, 비파괴검사(RT 100%) 및 기밀 시험 합격 (도시가스사 1:1 입회)</t>
         </is>
       </c>
-      <c r="P29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\체크리스트\상하수도 이설계획 실정보고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\15_상하수도 이설계획 실정보고\체크리스트\상하수도 이설계획 실정보고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q29" s="13" t="n"/>
@@ -28478,8 +28481,8 @@
           <t>집단에너지사업법 규정 | 난방 수송관 100% 비파괴검사 및 보온재 피복 랩핑 검수 | 지역난방공사 시운전 인수</t>
         </is>
       </c>
-      <c r="L30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\표준서\신규관로 및 연결관로 접속_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\표준서\신규관로 및 연결관로 접속_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -28487,8 +28490,8 @@
           <t>1) 난방 수송관 매설 &amp; 용접 ➔ 2) 100% 비파괴검사 &amp; 피복 랩핑 ➔ 3) 지역난방공사 시운전 인수 ➔ 4) 지역난방관 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O30" s="41" t="inlineStr">
@@ -28496,8 +28499,8 @@
           <t>난방 수송관 매설 &amp; 용접, 100% 비파괴검사 및 피복 랩핑 검수 (지역난방공사 인수)</t>
         </is>
       </c>
-      <c r="P30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\체크리스트\신규관로 및 연결관로 접속_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_신규관로 및 연결관로 접속\체크리스트\신규관로 및 연결관로 접속_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q30" s="13" t="n"/>
@@ -28573,8 +28576,8 @@
           <t>전기통신사업법 준수 | 통신 광케이블 관로 부설 및 절연 저항/광손실 실측 | KT/SKT 통신사 광신호 시험 승인</t>
         </is>
       </c>
-      <c r="L31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\표준서\16_위수탁 계약 체결_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\표준서\16_위수탁 계약 체결_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -28582,8 +28585,8 @@
           <t>1) 통신 광케이블 관로 부설 ➔ 2) 광케이블 포설 &amp; 접속 ➔ 3) 절연저항 &amp; 광손실 시험 ➔ 4) KT/SKT 통신사 광신호 승인</t>
         </is>
       </c>
-      <c r="N31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O31" s="41" t="inlineStr">
@@ -28591,8 +28594,8 @@
           <t>통신 광케이블 관로 부설, 절연 저항 &amp; 광손실 실측 합격 (KT/SKT 광신호 승인)</t>
         </is>
       </c>
-      <c r="P31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\체크리스트\위수탁 계약 체결_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\16_위수탁 계약 체결\체크리스트\위수탁 계약 체결_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q31" s="13" t="n"/>
@@ -28668,8 +28671,8 @@
           <t>전기공사업법 규정 | 22.9kV 특고압 전력 관로/맨홀 부설 및 절연내력 시험 | 한전(KEPCO) 현장 입회 휴전 Cut-over</t>
         </is>
       </c>
-      <c r="L32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\표준서\기존관로 철거 및 원상복구_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\표준서\기존관로 철거 및 원상복구_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M32" s="47" t="inlineStr">
@@ -28677,8 +28680,8 @@
           <t>1) 22.9kV 특고압 관로/맨홀 부설 ➔ 2) 전력 케이블 인입 &amp; 내력 시험 ➔ 3) 한전 입회 휴전 Cut-over ➔ 4) 전력관로 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\수행지침\기존관로 철거 및 원상복구_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\수행지침\기존관로 철거 및 원상복구_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O32" s="48" t="inlineStr">
@@ -28686,8 +28689,8 @@
           <t>22.9kV 특고압 관로/맨홀 부설, 절연내력 시험 합격 (한전 KEPCO 입회 휴전 Cut-over)</t>
         </is>
       </c>
-      <c r="P32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\체크리스트\기존관로 철거 및 원상복구_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_기존관로 철거 및 원상복구\체크리스트\기존관로 철거 및 원상복구_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R32" t="inlineStr">
@@ -28762,8 +28765,8 @@
           <t>송유관안전관리법 규정 | 송유관 비파괴 NDT 검사 및 초음파 탐상 시험 100% | 대한송유관공사 안전 인계</t>
         </is>
       </c>
-      <c r="L33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\표준서\17_도로점용_굴착행위 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\표준서\17_도로점용_굴착행위 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M33" s="47" t="inlineStr">
@@ -28771,8 +28774,8 @@
           <t>1) 송유관 용접 부설 ➔ 2) NDT 비파괴검사 &amp; 초음파 탐상 ➔ 3) 송유관공사 안전 점검 ➔ 4) 송유관 이설 완료 서면 승인</t>
         </is>
       </c>
-      <c r="N33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\수행지침\도로점용_굴착행위 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\수행지침\도로점용_굴착행위 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O33" s="48" t="inlineStr">
@@ -28780,8 +28783,8 @@
           <t>송유관 용접 부설, NDT 비파괴검사 및 초음파 탐상 시험 100% 합격 (대한송유관공사 인수)</t>
         </is>
       </c>
-      <c r="P33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\체크리스트\도로점용_굴착행위 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\17_도로점용_굴착행위 인허가\체크리스트\도로점용_굴착행위 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R33" t="inlineStr">
@@ -28856,8 +28859,8 @@
           <t>상하수도 총괄 지침 | 신설 관로 수압·수질·CCTV 검사 종합 대장 작성 | 지자체 3자 합동 최종 현현 점검</t>
         </is>
       </c>
-      <c r="L34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\표준서\광역상수관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\표준서\광역상수관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M34" s="47" t="inlineStr">
@@ -28865,8 +28868,8 @@
           <t>1) 신설 관로 종합 현측 ➔ 2) 수압/수질/CCTV 검사 종합 ➔ 3) 지자체 3자 합동 점검 ➔ 4) 상하수도 최종 점검 대장 승인</t>
         </is>
       </c>
-      <c r="N34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\수행지침\광역상수관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\수행지침\광역상수관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O34" s="48" t="inlineStr">
@@ -28874,8 +28877,8 @@
           <t>신설 관로 종합 현측, 수압/수질/CCTV 검사 종합 대장 작성 및 지자체 3자 합동 점검</t>
         </is>
       </c>
-      <c r="P34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\체크리스트\광역상수관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_광역상수관 이설 공사\체크리스트\광역상수관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R34" t="inlineStr">
@@ -28950,8 +28953,8 @@
           <t>위수탁 총괄 지침 | 위탁기관 1:1 현장 최종 인수 검측 및 3D BIM 준공 도면 대조 | 지장물 이설 준공 보고서</t>
         </is>
       </c>
-      <c r="L35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\표준서\18_교통통제 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\표준서\18_교통통제 및 교통안전시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M35" s="47" t="inlineStr">
@@ -28959,8 +28962,8 @@
           <t>1) 위탁기관 1:1 인수 검측 ➔ 2) 3D BIM 준공 도면 대조 ➔ 3) 이설 완료 현장 서명 ➔ 4) 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\수행지침\교통통제 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\수행지침\교통통제 및 교통안전시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O35" s="48" t="inlineStr">
@@ -28968,8 +28971,8 @@
           <t>위탁기관 1:1 인수 검측, 3D BIM 준공 도면 대조 및 이설 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\체크리스트\교통통제 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\18_교통통제 및 교통안전시설 설치\체크리스트\교통통제 및 교통안전시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R35" t="inlineStr">
@@ -29044,8 +29047,8 @@
           <t>지방계약법 정산 수칙 | 실제 실정보고 투입 물량 및 단가 산정 정산서 작성 | 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="L36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\표준서\상수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\표준서\상수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M36" s="47" t="inlineStr">
@@ -29053,8 +29056,8 @@
           <t>1) 실정보고 투입 물량 집계 ➔ 2) 정산 단가 산정 서류 작성 ➔ 3) 정산서 감리 기술 검토 ➔ 4) 정산 금액 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\수행지침\상수도 관로 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\수행지침\상수도 관로 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O36" s="48" t="inlineStr">
@@ -29062,8 +29065,8 @@
           <t>실정보고 투입 물량 집계, 정산 단가 산정 서류 작성 및 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="P36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\체크리스트\상수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_상수도 관로 이설 공사\체크리스트\상수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R36" t="inlineStr">
@@ -29138,8 +29141,8 @@
           <t>위수탁 정산 규정 | 관할 위탁기관에 최종 정산금 청구서 및 집행 영수증 작성 | 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="L37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\표준서\19_줄따기(GPR)를 통한 기존 지장물 매설 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\표준서\19_줄따기(GPR)를 통한 기존 지장물 매설 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M37" s="47" t="inlineStr">
@@ -29147,8 +29150,8 @@
           <t>1) 위탁기관 정산 청구서 작성 ➔ 2) 증빙 영수증 &amp; 성과표 첨부 ➔ 3) 정산금 지급 수속 ➔ 4) 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="N37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O37" s="48" t="inlineStr">
@@ -29156,8 +29159,8 @@
           <t>위탁기관 정산 청구서 작성, 증빙 영수증 &amp; 성과표 부착 및 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="P37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\체크리스트\줄따기(GPR)를 통한 기존 지장물 매설 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\19_줄따기(GPR)를 통한 기존 지장물 매설 확인\체크리스트\줄따기(GPR)를 통한 기존 지장물 매설 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R37" t="inlineStr">
@@ -29232,8 +29235,8 @@
           <t>건진법 설계변경 수칙 | 도급분 및 위수탁분 총사업비 변경 계약 체결 | 발주처 변경 공문 수령 완료</t>
         </is>
       </c>
-      <c r="L38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\표준서\20_이설 위치 토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\표준서\20_이설 위치 토공 굴착_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M38" s="47" t="inlineStr">
@@ -29241,8 +29244,8 @@
           <t>1) 설계변경 총사업비 산정 ➔ 2) 도급/위수탁 변경 변경 수속 ➔ 3) 발주처 변경 공문 수령 ➔ 4) 설계변경 정산 최종 승인</t>
         </is>
       </c>
-      <c r="N38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O38" s="48" t="inlineStr">
@@ -29250,8 +29253,8 @@
           <t>설계변경 총사업비 산정, 도급/위수탁 변경 변경 수속 및 발주처 변경 공문 수령</t>
         </is>
       </c>
-      <c r="P38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\체크리스트\이설 위치 토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_이설 위치 토공 굴착\체크리스트\이설 위치 토공 굴착_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R38" t="inlineStr">
@@ -29326,8 +29329,8 @@
           <t>공정 간섭 관리 지침 | 선행 토공 및 측량 기준점 성과 인수 대장 작성 | 3자 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="L39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\표준서\하수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\표준서\하수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M39" s="47" t="inlineStr">
@@ -29335,8 +29338,8 @@
           <t>1) 선행 토공 &amp; 측량 성과 인수 ➔ 2) 현장 지장물 인계인수 ➔ 3) 3자 합동 현측 실시 ➔ 4) 인계인수서 3자 서명 완료</t>
         </is>
       </c>
-      <c r="N39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O39" s="48" t="inlineStr">
@@ -29344,8 +29347,8 @@
           <t>선행 토공 및 측량 성과 인수 대장 작성, 3자 합동 현측 및 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="P39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\체크리스트\하수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\20_하수도 관로 이설 공사\체크리스트\하수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="R39" t="inlineStr">
@@ -29365,344 +29368,344 @@
       </c>
     </row>
     <row r="40">
-      <c r="L40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\표준서\도시가스관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\수행지침\도시가스관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\체크리스트\도시가스관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\표준서\도시가스관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\수행지침\도시가스관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_도시가스관 이설 공사\체크리스트\도시가스관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="L41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\표준서\21_신규관로 매설 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\체크리스트\신규관로 매설 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\표준서\21_신규관로 매설 및 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\21_신규관로 매설 및 설치\체크리스트\신규관로 매설 및 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="L42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\표준서\22_무단수 연결을 위한 시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\수행지침\무단수 연결을 위한 시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\체크리스트\무단수 연결을 위한 시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\표준서\22_무단수 연결을 위한 시설 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\수행지침\무단수 연결을 위한 시설 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_무단수 연결을 위한 시설 설치\체크리스트\무단수 연결을 위한 시설 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="G43" s="42" t="n"/>
-      <c r="L43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\표준서\지역난방관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\체크리스트\지역난방관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\표준서\지역난방관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\22_지역난방관 이설 공사\체크리스트\지역난방관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="G44" s="42" t="n"/>
-      <c r="L44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\표준서\23_신규관로 및 연결관로 접속_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\체크리스트\신규관로 및 연결관로 접속_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\표준서\23_신규관로 및 연결관로 접속_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_신규관로 및 연결관로 접속\체크리스트\신규관로 및 연결관로 접속_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="22.8" customHeight="1" s="148">
       <c r="G45" s="43" t="n"/>
-      <c r="L45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\표준서\통신관로 및 케이블 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\체크리스트\통신관로 및 케이블 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\표준서\통신관로 및 케이블 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\23_통신관로 및 케이블 이설 공사\체크리스트\통신관로 및 케이블 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="G46" s="42" t="n"/>
-      <c r="L46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\표준서\24_기존관로 철거 및 원상복구_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\수행지침\기존관로 철거 및 원상복구_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\체크리스트\기존관로 철거 및 원상복구_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\표준서\24_기존관로 철거 및 원상복구_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\수행지침\기존관로 철거 및 원상복구_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_기존관로 철거 및 원상복구\체크리스트\기존관로 철거 및 원상복구_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="G47" s="44" t="n"/>
-      <c r="L47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\표준서\특고압 전력관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\체크리스트\특고압 전력관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\표준서\특고압 전력관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\24_특고압 전력관로 이설 공사\체크리스트\특고압 전력관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="G48" s="44" t="n"/>
-      <c r="L48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\표준서\25_광역상수관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\수행지침\광역상수관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\체크리스트\광역상수관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\표준서\25_광역상수관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\수행지침\광역상수관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_광역상수관 이설 공사\체크리스트\광역상수관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="22.8" customHeight="1" s="148">
       <c r="G49" s="43" t="n"/>
-      <c r="L49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\표준서\송유관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\수행지침\송유관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\체크리스트\송유관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\표준서\송유관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\수행지침\송유관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\25_송유관 이설 공사\체크리스트\송유관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="G50" s="42" t="n"/>
-      <c r="L50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\표준서\26_상수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\수행지침\상수도 관로 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\체크리스트\상수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\표준서\26_상수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\수행지침\상수도 관로 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상수도 관로 이설 공사\체크리스트\상수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="G51" s="44" t="n"/>
-      <c r="L51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\표준서\상하수도 이설 시공 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\체크리스트\상하수도 이설 시공 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\표준서\상하수도 이설 시공 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\26_상하수도 이설 시공 최종 점검\체크리스트\상하수도 이설 시공 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="G52" s="44" t="n"/>
-      <c r="L52" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\표준서\위수탁 지하지장물 이설 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N52" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P52" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\체크리스트\위수탁 지하지장물 이설 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L52" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\표준서\위수탁 지하지장물 이설 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N52" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P52" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_위수탁 지하지장물 이설 최종 점검\체크리스트\위수탁 지하지장물 이설 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="22.8" customHeight="1" s="148">
       <c r="G53" s="43" t="n"/>
-      <c r="L53" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\표준서\27_하수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N53" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P53" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\체크리스트\하수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L53" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\표준서\27_하수도 관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N53" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P53" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\27_하수도 관로 이설 공사\체크리스트\하수도 관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="G54" s="42" t="n"/>
-      <c r="L54" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\표준서\28_도시가스관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N54" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\수행지침\도시가스관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P54" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\체크리스트\도시가스관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L54" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\표준서\28_도시가스관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N54" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\수행지침\도시가스관 이설 공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P54" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_도시가스관 이설 공사\체크리스트\도시가스관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="G55" s="44" t="n"/>
-      <c r="L55" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\표준서\상하수도 이설 정산 금액 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N55" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\수행지침\상하수도 이설 정산 금액 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P55" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\체크리스트\상하수도 이설 정산 금액 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L55" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\표준서\상하수도 이설 정산 금액 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N55" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\수행지침\상하수도 이설 정산 금액 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P55" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\28_상하수도 이설 정산 금액 검토\체크리스트\상하수도 이설 정산 금액 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="G56" s="44" t="n"/>
-      <c r="L56" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\표준서\위수탁 처리 정산금액 지급_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N56" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P56" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\체크리스트\위수탁 처리 정산금액 지급_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L56" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\표준서\위수탁 처리 정산금액 지급_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N56" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P56" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_위수탁 처리 정산금액 지급\체크리스트\위수탁 처리 정산금액 지급_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="22.8" customHeight="1" s="148">
       <c r="G57" s="43" t="n"/>
-      <c r="L57" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\표준서\29_지역난방관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N57" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P57" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\체크리스트\지역난방관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L57" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\표준서\29_지역난방관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N57" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P57" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\29_지역난방관 이설 공사\체크리스트\지역난방관 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="G58" s="42" t="n"/>
-      <c r="L58" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\표준서\도급자분_위수탁분 설계변경 정산_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N58" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\수행지침\도급자분 이설업체 선정(상_하수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P58" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\체크리스트\도급자분_위수탁분 설계변경 정산_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L58" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\표준서\도급자분_위수탁분 설계변경 정산_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N58" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\수행지침\도급자분 이설업체 선정(상_하수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P58" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_도급자분_위수탁분 설계변경 정산\체크리스트\도급자분_위수탁분 설계변경 정산_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="G59" s="44" t="n"/>
-      <c r="L59" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\표준서\30_통신관로 및 케이블 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N59" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P59" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\체크리스트\통신관로 및 케이블 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L59" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\표준서\30_통신관로 및 케이블 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N59" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P59" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\30_통신관로 및 케이블 이설 공사\체크리스트\통신관로 및 케이블 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="G60" s="44" t="n"/>
-      <c r="L60" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\표준서\31_특고압 전력관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N60" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P60" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\체크리스트\특고압 전력관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L60" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\표준서\31_특고압 전력관로 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N60" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\수행지침\수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P60" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\31_특고압 전력관로 이설 공사\체크리스트\특고압 전력관로 이설 공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="G61" s="44" t="n"/>
-      <c r="L61" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\표준서\32_송유관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N61" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P61" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\체크리스트\상하수도 이설 시공 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L61" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\표준서\32_송유관 이설 공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N61" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P61" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\32_송유관 이설 공사\체크리스트\상하수도 이설 시공 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="G62" s="45" t="n"/>
-      <c r="L62" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\표준서\33_상하수도 이설 시공 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="N62" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
-        <v/>
-      </c>
-      <c r="P62" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\체크리스트\위수탁 지하지장물 이설 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="L62" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\표준서\33_상하수도 이설 시공 최종 점검_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="N62" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\수행지침\상하수도 이설 시공 최종 점검_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="P62" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\3.지장물이설\33_상하수도 이설 시공 최종 점검\체크리스트\위수탁 지하지장물 이설 최종 점검_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
     </row>
@@ -29910,8 +29913,8 @@
           <t>KDS 47 10 00 철도지반 설계기준 준수 | 시추 주상도, GPR 3D 매핑 및 N치 &lt; 4 연약지반 층후 경출 | PVD/DCM 개량 공법 확정</t>
         </is>
       </c>
-      <c r="L2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\지반조사 상세검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\지반조사 상세검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M2" s="22" t="inlineStr">
@@ -29919,8 +29922,8 @@
           <t>1) 시추 주상도 &amp; GPR 3D 매핑 분석 ➔ 2) N치 &lt; 4 연약지반 심도 경계 추출 ➔ 3) PVD/DCM 개량 공법 검토 ➔ 4) 기술사 서명 지반조사 보고서 감리 승인</t>
         </is>
       </c>
-      <c r="N2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O2" t="inlineStr">
@@ -29928,8 +29931,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\체크리스트\지반조사 상세검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\체크리스트\지반조사 상세검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q2" t="inlineStr">
@@ -30005,8 +30008,8 @@
           <t>KCS 47 10 25 시방 검토 | 쇄석 입도 50mm 및 다짐도 ≥ 95% 명시 | 3D BIM 도면 대조 &amp; 리스크 예비비 수립 킥오프 승인</t>
         </is>
       </c>
-      <c r="L3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M3" s="22" t="inlineStr">
@@ -30014,8 +30017,8 @@
           <t>1) 발주처 시방서 요구조건 분석 ➔ 2) 3D BIM 도면 표고/구배 검증 ➔ 3) 지장물/용지 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O3" t="inlineStr">
@@ -30023,8 +30026,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q3" t="inlineStr">
@@ -30100,8 +30103,8 @@
           <t>철도안전법 제45조 준수 | 궤도 중심 30m 법정 경계 측량(오차 ≤ 5mm) | 행위신고서 작성 및 운행선안전관리자 1:1 배치</t>
         </is>
       </c>
-      <c r="L4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\표준서\철도보호지구 행위신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\표준서\철도보호지구 행위신고_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M4" s="22" t="inlineStr">
@@ -30109,8 +30112,8 @@
           <t>1) 궤도 중심 30m 법정 경계 측량 ➔ 2) 행위신고서/안전계획서 접수 ➔ 3) 관할 철도운영기관 기술 심의 ➔ 4) 운행선안전관리자 현장 1:1 배치</t>
         </is>
       </c>
-      <c r="N4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\수행지침\철도보호지구 행위신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\수행지침\철도보호지구 행위신고_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O4" t="inlineStr">
@@ -30118,8 +30121,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\체크리스트\철도보호지구 행위신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\3_철도보호지구에서의 행위신고(필요시)\체크리스트\철도보호지구 행위신고_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q4" t="inlineStr">
@@ -30195,8 +30198,8 @@
           <t>공공측량 작업규정 준수 | 국가 CP/TBM 기준점 인수 및 GRS80 수준측량(폐합오차 ≤ 5mm√K) | 현장 인조점 3개소 매설 성과 확보</t>
         </is>
       </c>
-      <c r="L5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\표준서\착수전 측량 Data 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\표준서\착수전 측량 Data 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M5" s="22" t="inlineStr">
@@ -30204,8 +30207,8 @@
           <t>1) 국가 CP/TBM 기준점 인수 ➔ 2) GRS80 수준측량(폐합오차 ≤ 5mm√K) ➔ 3) 현장 인조점 3개소 매설 ➔ 4) 측량 성과표 작성 &amp; 3D BIM 승인</t>
         </is>
       </c>
-      <c r="N5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\수행지침\착수전 측량 Data 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\수행지침\착수전 측량 Data 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O5" t="inlineStr">
@@ -30213,8 +30216,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\체크리스트\착수전 측량 Data 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\4_착수전 측량 Data 확인\체크리스트\착수전 측량 Data 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q5" t="inlineStr">
@@ -30290,8 +30293,8 @@
           <t>지하안전관리에 관한 특별법 제23조 | GPR 지중 탐사 &amp; 인력 줄파기(깊이 1.5m) | 점용기관 입회 매달기 방호 및 이설 완료 승인</t>
         </is>
       </c>
-      <c r="L6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\표준서\지장물이설 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\표준서\지장물이설 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M6" s="22" t="inlineStr">
@@ -30299,8 +30302,8 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\수행지침\지장물이설 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\수행지침\지장물이설 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O6" t="inlineStr">
@@ -30308,8 +30311,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\체크리스트\지장물이설 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\5_지장물이설 협의\체크리스트\지장물이설 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q6" t="inlineStr">
@@ -30385,8 +30388,8 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 설치 | 3D 우회 토공 동선 수립 및 마일스톤 연동</t>
         </is>
       </c>
-      <c r="L7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\표준서\용지보상RISK 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\표준서\용지보상RISK 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -30394,8 +30397,8 @@
           <t>1) 미보상 사유지 필지 추출 ➔ 2) 경계 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="N7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\수행지침\용지보상RISK 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\수행지침\용지보상RISK 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O7" t="inlineStr">
@@ -30403,8 +30406,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\체크리스트\용지보상RISK 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\6_용지보상RISK 검토\체크리스트\용지보상RISK 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q7" t="inlineStr">
@@ -30480,8 +30483,8 @@
           <t>건산법 상생협력 규정 | 토공 전문 기술자 1:1 전담 배치 | 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM 시행</t>
         </is>
       </c>
-      <c r="L8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M8" s="22" t="inlineStr">
@@ -30489,8 +30492,8 @@
           <t>1) 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 전담 조직표 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O8" t="inlineStr">
@@ -30498,8 +30501,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\7_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q8" t="inlineStr">
@@ -30575,8 +30578,8 @@
           <t>건진법 시행령 제89조 | KCS 47 10 25 다짐 수칙(다짐도 ≥ 95%, K30 ≥ 110) 명시 | 착공 14일 전 책임감리단 기술 승인</t>
         </is>
       </c>
-      <c r="L9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\표준서\연약지반 처리공법 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\표준서\연약지반 처리공법 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -30584,8 +30587,8 @@
           <t>1) 시공계획서 표준 8대 목차 작성 ➔ 2) KCS 47 10 25 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 책임감리원 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\수행지침\연약지반 처리공법 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\수행지침\연약지반 처리공법 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O9" t="inlineStr">
@@ -30593,8 +30596,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\체크리스트\연약지반 처리공법 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\8_연약지반 처리공법 검토(필요시)\체크리스트\연약지반 처리공법 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q9" t="inlineStr">
@@ -30670,8 +30673,8 @@
           <t>건설근로자법 준수 | 공종별 기술 수첩 및 장비 조종원 면허 1:1 현측 | 일일 음주 측정(0.00%) 및 작업조 조직표 승인</t>
         </is>
       </c>
-      <c r="L10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\표준서\토공 유동표 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\표준서\토공 유동표 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M10" s="22" t="inlineStr">
@@ -30679,8 +30682,8 @@
           <t>1) 토공 롤러/그레이더 조종원 자격 검증 ➔ 2) 건설기계 면허증 1:1 대조 ➔ 3) 일일 음주 측정 &amp; Safety TBM ➔ 4) 작업조 편성표 감리 승인</t>
         </is>
       </c>
-      <c r="N10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\수행지침\토공 유동표 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\수행지침\토공 유동표 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O10" t="inlineStr">
@@ -30688,8 +30691,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\체크리스트\토공 유동표 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\9_토공 유동표 확인\체크리스트\토공 유동표 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q10" t="inlineStr">
@@ -30765,8 +30768,8 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 강동/타이어 롤러 및 3D GPS 모터그레이더 정기검사 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="L11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\표준서\기공승낙 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\표준서\기공승낙 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -30774,8 +30777,8 @@
           <t>1) 10t+ 강동/타이어 롤러 사양 확정 ➔ 2) 정기검사증 &amp; 등록증 검수 ➔ 3) 3D GPS 수신기/후방 카메라 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="N11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\수행지침\기공승낙 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\수행지침\기공승낙 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O11" t="inlineStr">
@@ -30783,8 +30786,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\체크리스트\기공승낙 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\10_기공승낙 적정성 검토\체크리스트\기공승낙 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q11" t="inlineStr">
@@ -30860,8 +30863,8 @@
           <t>KCS 47 10 25 쇄석 입도 규정 | 최대입경 50mm 이하, #200체 통과량 ≤ 5% | 수정다짐 CBR ≥ 30% 성적 산출 및 입도 DB 구축</t>
         </is>
       </c>
-      <c r="L12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\표준서\폐기물처리계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\표준서\폐기물처리계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -30869,8 +30872,8 @@
           <t>1) 석산 공급원 사전 승인 수속 ➔ 2) 쇄석 입도(Dmax 50mm) 체가름 시험 ➔ 3) 수정다짐 CBR(≥30%) 성적 산출 ➔ 4) 노반 재료 입도 DB 감리 승인</t>
         </is>
       </c>
-      <c r="N12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\수행지침\폐기물처리계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\수행지침\폐기물처리계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O12" t="inlineStr">
@@ -30878,8 +30881,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\체크리스트\폐기물처리계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\11_폐기물처리계획 수립\체크리스트\폐기물처리계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q12" t="inlineStr">
@@ -30955,8 +30958,8 @@
           <t>토양환경보전법 준수 | 화성시 정식 사토장 인허가 확인 | 최대건조밀도 γd max ≥ 1.90g/cm³ &amp; 토양오염 8개 항목 검사 완수</t>
         </is>
       </c>
-      <c r="L13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\표준서\철도운행협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\표준서\철도운행협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -30964,8 +30967,8 @@
           <t>1) 화성시 정식 사토장 허가 검증 ➔ 2) γd max ≥ 1.90g/cm³ &amp; 오염 시험 ➔ 3) 덤프 운행 송장 일일 집계 ➔ 4) 사토 계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\수행지침\철도운행협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\수행지침\철도운행협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O13" t="inlineStr">
@@ -30973,8 +30976,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\체크리스트\철도운행협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\12_철도운행협의(필요시)\체크리스트\철도운행협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q13" t="inlineStr">
@@ -31050,8 +31053,8 @@
           <t>KCS 47 10 25 임시 배수 시방 | 성토 사면 가배수로(0.6×0.6m) &amp; 가침사지 2개소 | HDPE 유공관(Ø200mm, 구배 ≥ 0.5%) 부설</t>
         </is>
       </c>
-      <c r="L14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\표준서\작수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\표준서\작수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -31059,8 +31062,8 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 설계 ➔ 2) HDPE 유공관(Ø200mm) 자재 검수 ➔ 3) 비상 양수 펌프(200L/min) 비치 ➔ 4) 배수 처리 계획서 감리 승인</t>
         </is>
       </c>
-      <c r="N14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\수행지침\작수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\수행지침\작수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O14" t="inlineStr">
@@ -31068,8 +31071,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\체크리스트\작수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\13_작수전 Big Room 회의\체크리스트\작수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q14" t="inlineStr">
@@ -31145,8 +31148,8 @@
           <t>건진법 제62조 준수 | 국토안전관리원 전산 적정 심사 필 | CSI 건설공사 안전관리 종합망 전산 등록 및 감리 승인</t>
         </is>
       </c>
-      <c r="L15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\표준서\시공 계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\표준서\시공 계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -31154,8 +31157,8 @@
           <t>1) 건진법 제62조 안전관리계획 작성 ➔ 2) 국토안전관리원 전산 적정 심사 ➔ 3) CSI 안전관리 종합망 등록 ➔ 4) 책임감리원 서면 승인</t>
         </is>
       </c>
-      <c r="N15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\수행지침\시공 계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\수행지침\시공 계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O15" t="inlineStr">
@@ -31163,8 +31166,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\체크리스트\시공 계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\14_시공 계획 수립\체크리스트\시공 계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q15" t="inlineStr">
@@ -31240,8 +31243,8 @@
           <t>건진법 제55조 준수 | 노반 다짐도(500m³당 1회), K30(2,000m²당 1회), Ev2(1,000m²당 1회) | 현장 시험실 장비 교정 검수</t>
         </is>
       </c>
-      <c r="L16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\표준서\사토장_토취장 선정 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\표준서\사토장_토취장 선정 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -31249,8 +31252,8 @@
           <t>1) 다짐도/K30/Ev2 시험 빈도 수립 ➔ 2) 현장 시험실 장비 교정 검수 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 품질관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\수행지침\사토장_토취장 선정 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\수행지침\사토장_토취장 선정 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O16" t="inlineStr">
@@ -31258,8 +31261,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\체크리스트\사토장_토취장 선정 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\15_사토장_토취장 선정 검토(필요시)\체크리스트\사토장_토취장 선정 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q16" t="inlineStr">
@@ -31335,8 +31338,8 @@
           <t>대기환경보전법 제44조 | 지자체 비산먼지 발생사업 신고 필 | 이동식 세륜기(깊이 1.2m) &amp; 가설 방음벽(H=3m) 가동</t>
         </is>
       </c>
-      <c r="L17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\표준서\공사사전준비_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\표준서\공사사전준비_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -31344,8 +31347,8 @@
           <t>1) 세륜기(깊이 1.2m) &amp; 방음벽(3m) 설계 ➔ 2) 지자체 비산먼지 발생신고 ➔ 3) 살수차 1일 3회 살수 ➔ 4) 환경관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\수행지침\공사사전준비_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\수행지침\공사사전준비_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O17" t="inlineStr">
@@ -31353,8 +31356,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\체크리스트\공사사전준비_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\16_공사사전준비\체크리스트\공사사전준비_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q17" t="inlineStr">
@@ -31430,8 +31433,8 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 도로점용 허가 수령 | 전담 안전 신호수(2인 2조) 및 LED 경광등 배치</t>
         </is>
       </c>
-      <c r="L18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\표준서\임시배수시설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\표준서\임시배수시설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -31439,8 +31442,8 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\수행지침\임시배수시설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\수행지침\임시배수시설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O18" t="inlineStr">
@@ -31448,8 +31451,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\체크리스트\임시배수시설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\17_임시배수시설\체크리스트\임시배수시설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q18" t="inlineStr">
@@ -31525,8 +31528,8 @@
           <t>건산법 제29조 준수 | 토공 전문건설업 면허 및 하도급율(≥ 82%) 적정성 심사 | 노무비 지급 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\표준서\쌓기재료 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\표준서\쌓기재료 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -31534,8 +31537,8 @@
           <t>1) 토공 전문 면허 &amp; 실적 심사 ➔ 2) 하도급 적정성 평가(≥82%) ➔ 3) 노무비 지급 전용계좌 지정 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\수행지침\쌓기재료 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\수행지침\쌓기재료 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O19" t="inlineStr">
@@ -31543,8 +31546,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\체크리스트\쌓기재료 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\18_쌓기재료 검사\체크리스트\쌓기재료 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q19" t="inlineStr">
@@ -31620,8 +31623,8 @@
           <t>KCS 47 10 25 자재 검수 | KS F 2527 쇄석골재, HDPE 유공관, 부직포(200g/m²) 공인성적서 | 현장 반입 검수 및 승인 통보</t>
         </is>
       </c>
-      <c r="L20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\표준서\장비 검수 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\표준서\장비 검수 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -31629,8 +31632,8 @@
           <t>1) KS F 2527 쇄석/유공관 서류 검토 ➔ 2) 공인시험기관 시험성적서 부착 ➔ 3) 자재 승인 신청서 제출 ➔ 4) 자재 반입 검수 및 승인 결재</t>
         </is>
       </c>
-      <c r="N20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\수행지침\장비 검수 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\수행지침\장비 검수 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O20" t="inlineStr">
@@ -31638,8 +31641,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\체크리스트\장비 검수 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\19_장비 검수 지원\체크리스트\장비 검수 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q20" t="inlineStr">
@@ -31715,8 +31718,8 @@
           <t>KCS 47 10 25 현장 시험 수칙 | 50m 시험 구간 쇄석 30cm 부설 | 패스별 침하량 실측(침하 정지 Δh ≤ 1mm) 강동 4회 다짐 확정</t>
         </is>
       </c>
-      <c r="L21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\표준서\선로 종_횡단 및 용지경계측량_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\표준서\선로 종_횡단 및 용지경계측량_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -31724,8 +31727,8 @@
           <t>1) 50m 시험 다짐 구간 지정 ➔ 2) 쇄석 30cm 두께 포설 ➔ 3) 패스별 침하량(Δh≤1mm) 측정 ➔ 4) 다짐 횟수(강동 4회) 보고서 승인</t>
         </is>
       </c>
-      <c r="N21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\수행지침\선로 종_횡단 및 용지경계측량_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\수행지침\선로 종_횡단 및 용지경계측량_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O21" t="inlineStr">
@@ -31733,8 +31736,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\체크리스트\선로 종_횡단 및 용지경계측량_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\20_선로 종_횡단 및 용지경계측량\체크리스트\선로 종_횡단 및 용지경계측량_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q21" t="inlineStr">
@@ -31810,8 +31813,8 @@
           <t>KCS 47 10 25 원지반 규정 | 유기질 표토(15~30cm) 제거 및 전압 다짐 | 원지반 K30 ≥ 70 MN/m³ 시험 &amp; 덤프트럭 펌핑 점검</t>
         </is>
       </c>
-      <c r="L22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\표준서\규준틀 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\표준서\규준틀 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -31819,8 +31822,8 @@
           <t>1) 표토(15~30cm) 제거 &amp; 정전압 다짐 ➔ 2) 원지반 표고 레벨 측량 ➔ 3) K30(≥70 MN/m³) &amp; 펌핑 검측 ➔ 4) 원지반 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\수행지침\규준틀 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\수행지침\규준틀 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O22" t="inlineStr">
@@ -31828,8 +31831,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\체크리스트\규준틀 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\21_규준틀 설치\체크리스트\규준틀 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q22" t="inlineStr">
@@ -31905,8 +31908,8 @@
           <t>KCS 47 10 25 하부노반 시방 | 토사 층두께 ≤ 30cm 포설 다짐 | 들밀도 다짐도 ≥ 90% (KS F 2311) &amp; K30 ≥ 90 MN/m³ 검측</t>
         </is>
       </c>
-      <c r="L23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\표준서\준비배수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\표준서\준비배수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -31914,8 +31917,8 @@
           <t>1) 하부노반 30cm 층포설 &amp; 다짐 ➔ 2) 들밀도(≥90%) &amp; K30(≥90) 시험 ➔ 3) 마무리면 레벨 오차(±20mm) 검측 ➔ 4) 하부노반 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\수행지침\준비배수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\수행지침\준비배수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O23" t="inlineStr">
@@ -31923,8 +31926,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\체크리스트\준비배수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\22_준비배수\체크리스트\준비배수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q23" t="inlineStr">
@@ -32000,8 +32003,8 @@
           <t>KCS 47 10 25 상부노반 시방 | 토사 30cm 포설 다짐 | 맹암거 투수성 부직포(200g/m²) &amp; HDPE 유공관(Ø200mm) 매몰 검측</t>
         </is>
       </c>
-      <c r="L24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\표준서\벌개제근_표토제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\표준서\벌개제근_표토제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -32009,8 +32012,8 @@
           <t>1) 상부노반 토사 30cm 포설 ➔ 2) 맹암거 부직포(200g/m²) 부설 ➔ 3) HDPE 유공관(Ø200mm) 종단 연결 ➔ 4) 상부노반 시공 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\수행지침\벌개제근_표토제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\수행지침\벌개제근_표토제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O24" t="inlineStr">
@@ -32018,8 +32021,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\체크리스트\벌개제근_표토제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\23_벌개제근_표토제거\체크리스트\벌개제근_표토제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q24" t="inlineStr">
@@ -32095,8 +32098,8 @@
           <t>KCS 47 10 25 강화노반 쇄석 시방 | 3D GPS 쇄석(50mm) 30cm 포설 | 최적함수비 OMC 살수 &amp; 강동 4회/타이어 2회 다짐 (표고 오차 ±10mm)</t>
         </is>
       </c>
-      <c r="L25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\표준서\구조물 및 지장물 제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\표준서\구조물 및 지장물 제거_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -32104,8 +32107,8 @@
           <t>1) 3D GPS 모터그레이더 쇄석(50mm) 30cm 포설 ➔ 2) 살수차 최적함수비 OMC 살수 ➔ 3) 강동 4회 + 타이어 2회 다짐 ➔ 4) 표고 오차(±10mm) 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\수행지침\구조물 및 지장물 제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\수행지침\구조물 및 지장물 제거_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O25" t="inlineStr">
@@ -32113,8 +32116,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\체크리스트\구조물 및 지장물 제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\24_구조물 및 지장물 제거\체크리스트\구조물 및 지장물 제거_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q25" t="inlineStr">
@@ -32190,8 +32193,8 @@
           <t>KCS 47 10 25 다짐 검측 수칙 | 노반 들밀도 다짐도 ≥ 95% | K30 ≥ 110 MN/m³ &amp; 동적변형계수 Ev2 ≥ 60 MPa (Ev2/Ev1 ≤ 2.2) 검측</t>
         </is>
       </c>
-      <c r="L26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\표준서\진입로 조성_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\표준서\진입로 조성_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -32199,8 +32202,8 @@
           <t>1) 들밀도 시험(다짐도 ≥ 95%) ➔ 2) K30 평판재하시험(≥ 110 MN/m³) ➔ 3) 동적변형계수 Ev2(≥ 60 MPa) 시험 ➔ 4) 다짐 검측 종합 보고서 승인</t>
         </is>
       </c>
-      <c r="N26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\수행지침\진입로 조성_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\수행지침\진입로 조성_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O26" t="inlineStr">
@@ -32208,8 +32211,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\체크리스트\진입로 조성_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\25_진입로 조성\체크리스트\진입로 조성_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q26" t="inlineStr">
@@ -32285,8 +32288,8 @@
           <t>KS F 2310 규정 준수 | Ø300mm 재하판 산모래 밀착 및 15t 유압 잭 하중 재하 | 1.25mm 침하 P-S 곡선 산출 K30 ≥ 110 MN/m³ 성적서</t>
         </is>
       </c>
-      <c r="L27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\표준서\노반쌓기_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\표준서\노반쌓기_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -32294,8 +32297,8 @@
           <t>1) Ø300mm 재하판 산모래 밀착 ➔ 2) 15t 유압 잭 &amp; 다이얼 게이지 교정 ➔ 3) 1.25mm 침하 P-S 곡선 산출 ➔ 4) K30 ≥ 110 MN/m³ 성적서 승인</t>
         </is>
       </c>
-      <c r="N27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\수행지침\노반쌓기_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\수행지침\노반쌓기_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O27" t="inlineStr">
@@ -32303,8 +32306,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\체크리스트\노반쌓기_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\26_노반쌓기\체크리스트\노반쌓기_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q27" t="inlineStr">
@@ -32380,8 +32383,8 @@
           <t>DIN 18134 규정 준수 | LWD 동적 평판재하시험 1,000m²당 1회 | 2차 변형계수 Ev2 ≥ 60 MPa &amp; 변형계수 비율 Ev2/Ev1 ≤ 2.2 검측</t>
         </is>
       </c>
-      <c r="L28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\표준서\하부노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\표준서\하부노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -32389,8 +32392,8 @@
           <t>1) LWD 동적 평판재하시험기 교정 ➔ 2) 1,000m²당 1회 무작위 시험 ➔ 3) 1차/2차 하중 재하 Ev2/Ev1 산출 ➔ 4) Ev2 ≥ 60 MPa 성적서 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\수행지침\하부노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\수행지침\하부노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O28" t="inlineStr">
@@ -32398,8 +32401,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\체크리스트\하부노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\27_하부노반 시공\체크리스트\하부노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q28" t="inlineStr">
@@ -32475,8 +32478,8 @@
           <t>KCS 47 10 25 평탄성 수칙 | 3m 알루미늄 직선자 20m 간격 연속 측정 | 최대 갭 오차 ±10mm 이내 통제 &amp; 요철 부위 삭평 재다짐</t>
         </is>
       </c>
-      <c r="L29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\표준서\상부노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\표준서\상부노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -32484,8 +32487,8 @@
           <t>1) 3m 알루미늄 직선자 교정 ➔ 2) 20m 간격 종횡단 연속 검측 ➔ 3) 갭 오차(±10mm) 요철 삭평/재다짐 ➔ 4) 평탄성 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\수행지침\상부노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\수행지침\상부노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O29" t="inlineStr">
@@ -32493,8 +32496,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\체크리스트\상부노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\28_상부노반 시공\체크리스트\상부노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q29" t="inlineStr">
@@ -32570,8 +32573,8 @@
           <t>KCS 47 10 25 측량 지침 | GRS80 광학 토탈스테이션 10m 간격 연속 측량 | 중심선(X,Y) 및 표고(Z) 오차 ±10mm 3D BIM 검측</t>
         </is>
       </c>
-      <c r="L30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\표준서\강화노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\표준서\강화노반 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -32579,8 +32582,8 @@
           <t>1) GRS80 토탈스테이션 정밀 세팅 ➔ 2) 10m 간격 중심선 &amp; 표고 실측 ➔ 3) 3D BIM CAD 좌표(오차 ±10mm) 대조 ➔ 4) 종횡단 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\수행지침\강화노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\수행지침\강화노반 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O30" t="inlineStr">
@@ -32588,8 +32591,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\체크리스트\강화노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\29_강화노반 시공\체크리스트\강화노반 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q30" t="inlineStr">
@@ -32665,8 +32668,8 @@
           <t>건진법 NCR 조치 절차 | 감리단 부적합 통지서 수령 후 표면 15cm 파쇄 | OMC 살수 재다짐 및 1:1 재검측 NCR 서면 종결 승인</t>
         </is>
       </c>
-      <c r="L31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\표준서\토공 유동운반_사토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\표준서\토공 유동운반_사토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -32674,8 +32677,8 @@
           <t>1) 감리단 NCR 통지서 수령 ➔ 2) 해당 구역 표면 15cm 파쇄 &amp; OMC 재다짐 ➔ 3) 1:1 재검측(다짐도/K30/Ev2) ➔ 4) NCR 조치 결과 보고서 감리 종결 승인</t>
         </is>
       </c>
-      <c r="N31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\수행지침\토공 유동운반_사토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\수행지침\토공 유동운반_사토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O31" t="inlineStr">
@@ -32683,8 +32686,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\체크리스트\토공 유동운반_사토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\30_토공 유동운반_사토\체크리스트\토공 유동운반_사토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q31" t="inlineStr">
@@ -32760,8 +32763,8 @@
           <t>KCS 47 10 25 성토 사면 수칙 | 사면 비탈면 경사(1:1.5 이하) 측량 | 사면 다짐도 ≥ 90% 검측 &amp; 식생 거적 덮개(Jute Mat) 부설</t>
         </is>
       </c>
-      <c r="L32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\표준서\연약지반처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\표준서\연약지반처리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -32769,8 +32772,8 @@
           <t>1) 성토 사면 경사(1:1.5 이하) 측량 ➔ 2) 사면 다짐도(≥ 90%) 검측 ➔ 3) 식생 거적(Jute Mat) 30cm 겹침 부설 ➔ 4) 사면 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\수행지침\연약지반처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\수행지침\연약지반처리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O32" t="inlineStr">
@@ -32778,8 +32781,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\체크리스트\연약지반처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\31_연약지반처리(필요시)\체크리스트\연약지반처리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q32" t="inlineStr">
@@ -32855,8 +32858,8 @@
           <t>KCS 47 10 25 노반 배수 시방 | U형 측구(0.4×0.4m, 버림 10cm) 부설 | 집수정 인버트 모타르 사춤, 주철 그레이팅 체결 &amp; 담수 시험</t>
         </is>
       </c>
-      <c r="L33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\표준서\절성토경계부 배수구조물 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\표준서\절성토경계부 배수구조물 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -32864,8 +32867,8 @@
           <t>1) U형 측구 기초 버림(10cm) 타설 ➔ 2) U형 측구(0.4×0.4m) 부설 &amp; 인버트 사춤 ➔ 3) 주철 그레이팅 체결 &amp; 담수 시험 ➔ 4) 배수시설 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\수행지침\절성토경계부 배수구조물 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\수행지침\절성토경계부 배수구조물 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O33" t="inlineStr">
@@ -32873,8 +32876,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\체크리스트\절성토경계부 배수구조물 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\32_절성토경계부 배수구조물(맹암거) 시공\체크리스트\절성토경계부 배수구조물 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q33" t="inlineStr">
@@ -32950,8 +32953,8 @@
           <t>KCS 47 10 25 완성면 관리 규정 | 통제 바리케이트(중장비 진입 100% 차단) | 미세 분무 살수(골재이탈 예방) &amp; 완성면 보호 대장 작성</t>
         </is>
       </c>
-      <c r="L34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\표준서\암석쌓기_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\표준서\암석쌓기_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -32959,8 +32962,8 @@
           <t>1) 완성면 통제 바리케이트 설치 ➔ 2) 미세 분무 살수 &amp; 비닐 덮개 야적 ➔ 3) 일일 완성면 훼손 점검 ➔ 4) 완성면 보호 점검 대장 감리 승인</t>
         </is>
       </c>
-      <c r="N34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\수행지침\암석쌓기_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\수행지침\암석쌓기_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O34" t="inlineStr">
@@ -32968,8 +32971,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\체크리스트\암석쌓기_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\33_암석쌓기\체크리스트\암석쌓기_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q34" t="inlineStr">
@@ -33045,8 +33048,8 @@
           <t>건진법 시행규칙 공사기록 | 일일 투입 인원, 장비, 성토 물량(m³) 정밀 집계 | CSI 건설공사 관리 시스템 전산 등록 &amp; 감리 일일 직인</t>
         </is>
       </c>
-      <c r="L35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\표준서\방치기간 확보_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\표준서\방치기간 확보_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -33054,8 +33057,8 @@
           <t>1) 일일 인원/장비/물량 집계 ➔ 2) 품질 시험 성적 &amp; TBM 수록 ➔ 3) CSI 전산 시스템 등록 ➔ 4) 책임감리원 일일 서면 직인 결재</t>
         </is>
       </c>
-      <c r="N35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\수행지침\방치기간 확보_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\수행지침\방치기간 확보_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O35" t="inlineStr">
@@ -33063,8 +33066,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\체크리스트\방치기간 확보_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\34_방치기간 확보\체크리스트\방치기간 확보_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q35" t="inlineStr">
@@ -33140,8 +33143,8 @@
           <t>건진법 &amp; KCS 47 10 25 총괄 수칙 | 공사 착수 24시간 전 검측 요청서 제출 | 책임감리원 1:1 현장 입회 &amp; 16개 체크리스트 서명 대장</t>
         </is>
       </c>
-      <c r="L36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\표준서\토공마무리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\표준서\토공마무리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -33149,8 +33152,8 @@
           <t>1) 공종별 검측요청서 24시간 전 제출 ➔ 2) 책임감리원 1:1 현장 입회 ➔ 3) 16개 체크리스트 서명 ➔ 4) 검측 총괄 승인 대장 감리 결재</t>
         </is>
       </c>
-      <c r="N36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\수행지침\토공마무리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\수행지침\토공마무리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O36" t="inlineStr">
@@ -33158,8 +33161,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\체크리스트\토공마무리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\35_토공마무리\체크리스트\토공마무리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q36" t="inlineStr">
@@ -33235,8 +33238,8 @@
           <t>KCS 47 10 25 최종 인계인수 | 토공-궤도-감리 3자 합동 현측(표고 ±10mm, K30 ≥ 110) | 인계인수 합의서 서명 및 노반 완공 통보</t>
         </is>
       </c>
-      <c r="L37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\표준서\토공 마무리면 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\표준서\토공 마무리면 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -33244,8 +33247,8 @@
           <t>1) 3자(토공-궤도-감리) 합동 현측 ➔ 2) 표고(±10mm) &amp; K30(≥110) 재검측 ➔ 3) 인계인수 합의서 3자 서명 ➔ 4) 상부강화노반 최종 완공 통보</t>
         </is>
       </c>
-      <c r="N37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\수행지침\토공 마무리면 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\수행지침\토공 마무리면 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O37" t="inlineStr">
@@ -33253,8 +33256,8 @@
           <t>👉 [클릭] 표준서 열기 📄</t>
         </is>
       </c>
-      <c r="P37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\체크리스트\토공 마무리면 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\36_토공 마무리면 인계\체크리스트\토공 마무리면 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q37" t="inlineStr">
@@ -33472,8 +33475,8 @@
           <t>KDS 47 30 00 궤도 설계기준 및 국토교통부 트램 건설 규칙을 엄격히 준수한다. 노반부-궤도부 선형 및 종단 계획고 일치 오차 0mm 검토.</t>
         </is>
       </c>
-      <c r="L2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\표준서\설계적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M2" s="14" t="inlineStr">
@@ -33482,8 +33485,8 @@
 2) 궤도 정밀 검측: 궤간(1435mm), 캔트(±2mm), 수평(±2mm), 고저(±2mm/10m), 비틀림(1.5mm/3m) 실시간 검측</t>
         </is>
       </c>
-      <c r="N2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\수행지침\설계적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O2" s="14" t="inlineStr">
@@ -33491,8 +33494,8 @@
           <t>설계 도면 간섭 검속, 궤도 중심선 계획 표고 대조, 종단 구배 한계치 준수 확인</t>
         </is>
       </c>
-      <c r="P2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\1_설계적정성 검토\체크리스트\설계적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q2" s="13" t="n"/>
@@ -33565,8 +33568,8 @@
           <t>침목, 체결구, 홈레일 등 궤도 주요 자재의 현장 보관 기준 수립. 배수 경사 2% 및 지반 다짐도 95% 이상 야적장 확보.</t>
         </is>
       </c>
-      <c r="L3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\표준서\자재 야적장 선정_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\표준서\자재 야적장 선정_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M3" s="14" t="inlineStr">
@@ -33575,8 +33578,8 @@
 2) 장대레일 운반 트레일러(길이 30m 이상) 회전반경 및 크레인 인양 진입로 확보</t>
         </is>
       </c>
-      <c r="N3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\수행지침\자재 야적장 선정_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\수행지침\자재 야적장 선정_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O3" s="14" t="inlineStr">
@@ -33584,8 +33587,8 @@
           <t>야적장 지반 다짐도 95% 이상, 배수 경사 2% 이상 확보, 자재 천막 덮개 구비</t>
         </is>
       </c>
-      <c r="P3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\체크리스트\자재 야적장 선정_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\2_자재 야적장 선정\체크리스트\자재 야적장 선정_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q3" s="13" t="n"/>
@@ -33658,8 +33661,8 @@
           <t>EN 14730 테르밋 및 EN 14587 가스압접 용접을 위한 작업 공간 확보. 정척레일(25m)을 200m 장대로 용접하는 평탄 작업대 수평 오차 ±1mm 이내 확보.</t>
         </is>
       </c>
-      <c r="L4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\표준서\레일 용접장 선정_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\표준서\레일 용접장 선정_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M4" s="14" t="inlineStr">
@@ -33668,8 +33671,8 @@
 2) 가스압접/플래시버트 용접용 대용량 전력 및 아세틸렌/산소 가스 안전 저장소 확보</t>
         </is>
       </c>
-      <c r="N4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\수행지침\레일 용접장 선정_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\수행지침\레일 용접장 선정_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O4" s="14" t="inlineStr">
@@ -33677,8 +33680,8 @@
           <t>용접장 평탄성 오차 ±1mm 이내, 전력 공급 및 방풍 시설 완비, NDT(비파괴) 대기 공간 확보</t>
         </is>
       </c>
-      <c r="P4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\체크리스트\레일 용접장 선정_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\3_레일 용접장 선정\체크리스트\레일 용접장 선정_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q4" s="13" t="n"/>
@@ -33756,8 +33759,8 @@
           <t>KCS 47 30 00 시방 기준 준수. 궤도 자재 품질 확인서 및 외산 홈레일 조달 리스크 대응 전략 수립.</t>
         </is>
       </c>
-      <c r="L5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -33766,8 +33769,8 @@
 2) KDS 47 30 00 및 KS 규격 만족 자재 목록 및 세부 발주 물량 확정</t>
         </is>
       </c>
-      <c r="N5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O5" s="14" t="inlineStr">
@@ -33775,8 +33778,8 @@
           <t>품질 요구조건 특기시방서 의결, 외산 홈레일 선적일정 검토, 자재 인도 시점 확약</t>
         </is>
       </c>
-      <c r="P5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\4_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q5" s="13" t="n"/>
@@ -33849,8 +33852,8 @@
           <t>EN ISO 9606-1 용접 자격자 및 궤도 정밀 검측원(Track Master 운용원) 확보 심사 기준.</t>
         </is>
       </c>
-      <c r="L6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\표준서\최고의 팀 만들기 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -33859,8 +33862,8 @@
 2) 스핀들 게이지 조정, 캔트 달성구배, 테르밋 산화반응 제어 사전 모의 훈련</t>
         </is>
       </c>
-      <c r="N6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\수행지침\최고의 팀 만들기 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O6" s="14" t="inlineStr">
@@ -33868,8 +33871,8 @@
           <t>용접공 자격증 원본 대조, 정밀 검측 장비 검교정 확인, 궤도 전문 기술사 면허 검토</t>
         </is>
       </c>
-      <c r="P6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\5_최고의 팀 만들기 지원\체크리스트\최고의 팀 만들기 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q6" s="13" t="n"/>
@@ -33943,8 +33946,8 @@
           <t>KCS 47 30 00 콘크리트 궤도 시방 준수. 펌프카 타설압력에 의한 궤광 변위 방지 지지 계획 수립.</t>
         </is>
       </c>
-      <c r="L7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\표준서\콘크리트 타설방법_계획 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\표준서\콘크리트 타설방법_계획 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -33953,8 +33956,8 @@
 2) 레미콘 운반시간(60분 이내) 및 펌프카 배치 공간 사전 확보</t>
         </is>
       </c>
-      <c r="N7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\수행지침\콘크리트 타설방법_계획 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\수행지침\콘크리트 타설방법_계획 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -33962,8 +33965,8 @@
           <t>구간별 펌프카 배치도 작성, 타설 시 궤광 고정 잭 지지 계획 승인, 콘크리트 슬럼프 품질 확인</t>
         </is>
       </c>
-      <c r="P7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\체크리스트\콘크리트 타설방법_계획 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\6_콘크리트 타설방법_계획 검토\체크리스트\콘크리트 타설방법_계획 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="n"/>
@@ -34044,8 +34047,8 @@
           <t>노반-궤도 간 인터페이스, 신호 루프 센서 및 누설 전류(Stray Current) 부식 방지 디오드 접지선 매설 계획 의결.</t>
         </is>
       </c>
-      <c r="L8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\표준서\작수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\표준서\작수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M8" s="14" t="inlineStr">
@@ -34054,8 +34057,8 @@
 2) 도로 매설 궤도 표면과 도로 포장 표면 마감 높이 일치성 확정</t>
         </is>
       </c>
-      <c r="N8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\수행지침\작수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\수행지침\작수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O8" s="14" t="inlineStr">
@@ -34063,8 +34066,8 @@
           <t>신호 센서 매설 위치 철근 간섭 해결, 접지선 용접부 연속성 확인, 부서 합동 서명 날인</t>
         </is>
       </c>
-      <c r="P8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\체크리스트\작수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\7_작수전 Big Room 회의\체크리스트\작수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q8" s="13" t="n"/>
@@ -34137,8 +34140,8 @@
           <t>장대레일 운반 트레일러(길이 25m 이상) 도로 회전 반경 R=15m 확보 및 타공종 가설재 간섭 배제.</t>
         </is>
       </c>
-      <c r="L9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\표준서\장비,자재 반입로_반입구 간섭 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\표준서\장비,자재 반입로_반입구 간섭 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M9" s="14" t="inlineStr">
@@ -34147,8 +34150,8 @@
 2) 전담 신호수 배치 및 대형 레일 운반 차량 유도</t>
         </is>
       </c>
-      <c r="N9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\수행지침\장비,자재 반입로_반입구 간섭 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\수행지침\장비,자재 반입로_반입구 간섭 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -34156,8 +34159,8 @@
           <t>트레일러 회전 시뮬레이션 승인, 가설 비계 간섭 범위 해제, 도로 점용 허가 필증 확인</t>
         </is>
       </c>
-      <c r="P9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\체크리스트\장비,자재 반입로_반입구 간섭 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\8_장비,자재 반입로_반입구 간섭 검토\체크리스트\장비,자재 반입로_반입구 간섭 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q9" s="13" t="n"/>
@@ -34230,8 +34233,8 @@
           <t>홈레일, 체결구, 탄성 충전재 등 주요 자재의 해상 운송 및 국내 보관 일정 검토. OMC 품질 시방 확보.</t>
         </is>
       </c>
-      <c r="L10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\표준서\자재조달계획 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\표준서\자재조달계획 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M10" s="14" t="inlineStr">
@@ -34240,8 +34243,8 @@
 2) PST 슬래브 공장 생산 강도 및 홈레일 단면 검수</t>
         </is>
       </c>
-      <c r="N10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\수행지침\자재조달계획 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\수행지침\자재조달계획 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O10" s="14" t="inlineStr">
@@ -34249,8 +34252,8 @@
           <t>선적 서류 및 통관 승인서 구비, 국내 야적장 2차 보관 상태 점검, 자재 공급 승인서 확인</t>
         </is>
       </c>
-      <c r="P10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\체크리스트\자재조달계획 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\9_자재조달계획 검토\체크리스트\자재조달계획 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q10" s="13" t="n"/>
@@ -34324,8 +34327,8 @@
           <t>KDS 47 30 00 및 EN 규격 기준 자재 발주서 승인. 공급원 검토 승인 요청서 작성 요령 준수.</t>
         </is>
       </c>
-      <c r="L11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\표준서\자재 발주 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\표준서\자재 발주 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M11" s="14" t="inlineStr">
@@ -34334,8 +34337,8 @@
 2) 공장 검사(FAT) 조건 및 성적서 첨부 명시</t>
         </is>
       </c>
-      <c r="N11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\수행지침\자재 발주 요청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\수행지침\자재 발주 요청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -34343,8 +34346,8 @@
           <t>자재 발주 수량 설계 대조, 공급원 승인 필증 원본 확인, 발주 공문 승인 요청</t>
         </is>
       </c>
-      <c r="P11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\체크리스트\자재 발주 요청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\10_자재 발주 요청\체크리스트\자재 발주 요청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q11" s="13" t="n"/>
@@ -34418,8 +34421,8 @@
           <t>콘크리트도상 시공 절차 및 공정 스케줄 작성. 궤간(+3,-1mm), 캔트(±2mm) 관리계획 수립.</t>
         </is>
       </c>
-      <c r="L12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\표준서\시공계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\표준서\시공계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M12" s="14" t="inlineStr">
@@ -34428,8 +34431,8 @@
 2) 스핀들 게이지 조정, 테르밋 용접(EN 14730) 및 TCL 콘크리트 타설 수칙 수립</t>
         </is>
       </c>
-      <c r="N12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\수행지침\11_시공계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\수행지침\11_시공계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O12" s="14" t="inlineStr">
@@ -34437,8 +34440,8 @@
           <t>시공계획서 감리단 최종 승인, 선형 관리 한계선 설정 확인, 품질보증계획서 제출</t>
         </is>
       </c>
-      <c r="P12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\체크리스트\시공계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\11_시공계획 수립\체크리스트\시공계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q12" s="13" t="n"/>
@@ -34511,8 +34514,8 @@
           <t>반입 자재의 공장 성적서 대조 및 감리 입회 자재 인수 검사 수행. 변형/균열 자재 전량 반출.</t>
         </is>
       </c>
-      <c r="L13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\표준서\자재 반입_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="L13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\표준서\자재 반입_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="M13" s="14" t="inlineStr">
@@ -34521,8 +34524,8 @@
 2) 레일 표면 흠집 및 PST 패널 치수 오차(±2mm) 측정</t>
         </is>
       </c>
-      <c r="N13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\수행지침\자재 반입_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="N13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\수행지침\자재 반입_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -34530,8 +34533,8 @@
           <t>인수 검서 보고서 감리 서명, 자재 고유 마킹 대조, 손상 자재 반출 대장 기록</t>
         </is>
       </c>
-      <c r="P13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\체크리스트\자재 반입_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="P13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\5.콘크리트도상\12_자재 반입\체크리스트\자재 반입_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="Q13" s="13" t="n"/>
@@ -35803,8 +35806,8 @@
 2) 설계 적정성 검토 달성을 위한 필수 시공 방법(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반영 유무 및 확...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\표준서\설계 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\표준서\설계 적정성 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L2" s="31" t="inlineStr">
@@ -35813,8 +35816,8 @@
 2) 실무 작업방법 수칙(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\수행지침\설계 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\수행지침\설계 적정성 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N2" s="31" t="inlineStr">
@@ -35823,8 +35826,8 @@
 2) 미검측 및 정량 시방 미달에 따른 설계 적정성 검토 (WBS 9000-4-1) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 설계변경 예상 List, 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O2" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\체크리스트\설계 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O2" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\1_설계 적정성 검토\체크리스트\설계 적정성 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P2" s="30" t="n"/>
@@ -35896,8 +35899,8 @@
 2) 발주전략 KOM 달성을 위한 필수 시공 방법(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 지반상태(기초,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\표준서\발주전략 KOM_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L3" s="31" t="inlineStr">
@@ -35906,8 +35909,8 @@
 2) 실무 작업방법 수칙(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\수행지침\발주전략 KOM_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N3" s="31" t="inlineStr">
@@ -35916,8 +35919,8 @@
 2) 미검측 및 정량 시방 미달에 따른 발주전략 KOM (WBS 9000-4-2) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 KOM 검토결과서, 현설서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O3" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O3" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\2_발주전략 KOM\체크리스트\발주전략 KOM_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P3" s="30" t="n"/>
@@ -35988,8 +35991,8 @@
 2) 착공전 건축 인허가 달성을 위한 필수 시공 방법(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출 (-&gt;관할 소...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\표준서\착공전 건축 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\표준서\착공전 건축 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L4" s="31" t="inlineStr">
@@ -35998,8 +36001,8 @@
 2) 실무 작업방법 수칙(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\수행지침\착공전 건축 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\수행지침\착공전 건축 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N4" s="31" t="inlineStr">
@@ -36008,8 +36011,8 @@
 2) 미검측 및 정량 시방 미달에 따른 착공전 건축 인허가 (WBS 9000-4-3) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고/승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O4" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\체크리스트\착공전 건축 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O4" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\3_착공전 건축 인허가\체크리스트\착공전 건축 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P4" s="30" t="n"/>
@@ -36080,8 +36083,8 @@
 2) 건축허가 요청 달성을 위한 필수 시공 방법(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 관할지자체(시,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\표준서\건축허가 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\표준서\건축허가 요청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L5" s="31" t="inlineStr">
@@ -36090,8 +36093,8 @@
 2) 실무 작업방법 수칙(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\수행지침\건축허가 요청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\수행지침\건축허가 요청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N5" s="31" t="inlineStr">
@@ -36100,8 +36103,8 @@
 2) 미검측 및 정량 시방 미달에 따른 건축허가 요청 (WBS 9000-4-4) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축허가 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O5" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\체크리스트\건축허가 요청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O5" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\4_건축허가 요청\체크리스트\건축허가 요청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P5" s="30" t="n"/>
@@ -36172,8 +36175,8 @@
 2) 착공신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처리기간 3일 이...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\표준서\착공신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\표준서\착공신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L6" s="31" t="inlineStr">
@@ -36182,8 +36185,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\수행지침\착공신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\수행지침\착공신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N6" s="31" t="inlineStr">
@@ -36192,8 +36195,8 @@
 2) 미검측 및 정량 시방 미달에 따른 착공신고서 제출 (WBS 9000-4-5) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 착공신고서 승인 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O6" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\체크리스트\착공신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O6" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\5_착공신고서 제출\체크리스트\착공신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P6" s="30" t="n"/>
@@ -36263,8 +36266,8 @@
 2) 소방시설공사 착공 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 처리기간 2일 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\표준서\소방시설공사 착공 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\표준서\소방시설공사 착공 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L7" s="31" t="inlineStr">
@@ -36273,8 +36276,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\수행지침\소방시설공사 착공 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\수행지침\소방시설공사 착공 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N7" s="31" t="inlineStr">
@@ -36283,8 +36286,8 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 착공 신고서 제출 (WBS 9000-4-6) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설공사 착공신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O7" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\체크리스트\소방시설공사 착공 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O7" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\6_소방시설공사 착공 신고서 제출\체크리스트\소방시설공사 착공 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P7" s="30" t="n"/>
@@ -36354,8 +36357,8 @@
 2) 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 처리기간 14일...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\표준서\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\표준서\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L8" s="31" t="inlineStr">
@@ -36364,8 +36367,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\수행지침\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\수행지침\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N8" s="31" t="inlineStr">
@@ -36374,8 +36377,8 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) (WBS 9000-4-7) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신공사 착공전 설계도 확인결과 통보서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O8" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\체크리스트\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O8" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\7_정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)\체크리스트\정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P8" s="30" t="n"/>
@@ -36445,8 +36448,8 @@
 2) 선행공종 인수사항 확인 달성을 위한 필수 시공 방법(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\표준서\선행공종 인수사항 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\표준서\선행공종 인수사항 확인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L9" s="31" t="inlineStr">
@@ -36455,8 +36458,8 @@
 2) 실무 작업방법 수칙(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\수행지침\선행공종 인수사항 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\수행지침\선행공종 인수사항 확인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N9" s="31" t="inlineStr">
@@ -36465,8 +36468,8 @@
 2) 미검측 및 정량 시방 미달에 따른 선행공종 인수사항 확인 (WBS 9000-4-8) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 인수사항 List 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O9" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\체크리스트\선행공종 인수사항 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O9" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\8_선행공종 인수사항 확인\체크리스트\선행공종 인수사항 확인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P9" s="30" t="n"/>
@@ -36536,8 +36539,8 @@
 2) 인터페이스 사항 검토 및 지원 달성을 위한 필수 시공 방법(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장 지원 파견검토...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\표준서\인터페이스 사항 검토 및 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\표준서\인터페이스 사항 검토 및 지원_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L10" s="31" t="inlineStr">
@@ -36546,8 +36549,8 @@
 2) 실무 작업방법 수칙(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\수행지침\인터페이스 사항 검토 및 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\수행지침\인터페이스 사항 검토 및 지원_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N10" s="31" t="inlineStr">
@@ -36556,8 +36559,8 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 사항 검토 및 지원 (WBS 9000-4-9) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O10" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\체크리스트\인터페이스 사항 검토 및 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O10" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\9_인터페이스 사항 검토 및 지원\체크리스트\인터페이스 사항 검토 및 지원_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P10" s="30" t="n"/>
@@ -36625,8 +36628,8 @@
 2) 품질/안전 LL 공유 달성을 위한 필수 시공 방법(시공시 발생가능 품질, 안전 하자 최소화...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\표준서\품질_안전 LL 공유_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\표준서\품질_안전 LL 공유_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L11" s="31" t="inlineStr">
@@ -36635,8 +36638,8 @@
 2) 실무 작업방법 수칙(시공시 발생가능 품질, 안전 하자 최소화)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\수행지침\품질_안전 LL 공유_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\수행지침\품질_안전 LL 공유_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N11" s="31" t="inlineStr">
@@ -36645,8 +36648,8 @@
 2) 미검측 및 정량 시방 미달에 따른 품질/안전 LL 공유 (WBS 9000-4-10) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공계획수립시 반영 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O11" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\체크리스트\품질_안전 LL 공유_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O11" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\10_품질_안전 LL 공유\체크리스트\품질_안전 LL 공유_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P11" s="30" t="n"/>
@@ -36716,8 +36719,8 @@
 2) 자재공급원승인 및 자재발주 달성을 위한 필수 시공 방법(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 승인 제출 및 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\표준서\자재공급원승인 및 자재발주_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\표준서\자재공급원승인 및 자재발주_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L12" s="31" t="inlineStr">
@@ -36726,8 +36729,8 @@
 2) 실무 작업방법 수칙(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\수행지침\자재공급원승인 및 자재발주_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\수행지침\자재공급원승인 및 자재발주_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N12" s="31" t="inlineStr">
@@ -36736,8 +36739,8 @@
 2) 미검측 및 정량 시방 미달에 따른 자재공급원승인 및 자재발주 (WBS 9000-4-11) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 구매 의뢰 승인, 자재공급원 승인서류 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O12" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\체크리스트\자재공급원승인 및 자재발주_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O12" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\11_자재공급원승인 및 자재발주\체크리스트\자재공급원승인 및 자재발주_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P12" s="30" t="n"/>
@@ -36814,8 +36817,8 @@
 2) 착수전 Big Room 회의 달성을 위한 필수 시공 방법(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방착공신고, 정보...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\표준서\착수전 Big Room 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L13" s="31" t="inlineStr">
@@ -36824,8 +36827,8 @@
 2) 실무 작업방법 수칙(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\수행지침\착수전 Big Room 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N13" s="31" t="inlineStr">
@@ -36834,8 +36837,8 @@
 2) 미검측 및 정량 시방 미달에 따른 착수전 Big Room 회의 (WBS 9000-4-12) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 Big Room 회의록(참석자 전원 서명) 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O13" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O13" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\12_착수전 Big Room 회의\체크리스트\착수전 Big Room 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P13" s="30" t="n"/>
@@ -36906,8 +36909,8 @@
 2) 시공계획 수립/승인 달성을 위한 필수 시공 방법(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: 위험요인/대책,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\표준서\시공계획 수립_승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\표준서\시공계획 수립_승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L14" s="31" t="inlineStr">
@@ -36916,8 +36919,8 @@
 2) 실무 작업방법 수칙(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\수행지침\시공계획 수립_승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\수행지침\시공계획 수립_승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N14" s="31" t="inlineStr">
@@ -36926,8 +36929,8 @@
 2) 미검측 및 정량 시방 미달에 따른 시공계획 수립/승인 (WBS 9000-4-13) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 (승인)관리시공계획서&amp;시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O14" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\체크리스트\시공계획 수립_승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O14" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\13_시공계획 수립_승인\체크리스트\시공계획 수립_승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P14" s="30" t="n"/>
@@ -36998,8 +37001,8 @@
 2) 측량, 자재/장비 반입, 안전교육 달성을 위한 필수 시공 방법(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안전검사 작업원 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\표준서\측량, 자재_장비 반입, 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\표준서\측량, 자재_장비 반입, 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L15" s="31" t="inlineStr">
@@ -37008,8 +37011,8 @@
 2) 실무 작업방법 수칙(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\수행지침\측량, 자재_장비 반입, 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\수행지침\측량, 자재_장비 반입, 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N15" s="31" t="inlineStr">
@@ -37018,8 +37021,8 @@
 2) 미검측 및 정량 시방 미달에 따른 측량, 자재/장비 반입, 안전교육 (WBS 9000-4-14) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량기록지, 안전교육 결과서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O15" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\체크리스트\측량, 자재_장비 반입, 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O15" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\14_측량, 자재_장비 반입, 안전교육\체크리스트\측량, 자재_장비 반입, 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P15" s="30" t="n"/>
@@ -37089,8 +37092,8 @@
 2) 자재 검수 달성을 위한 필수 시공 방법(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\표준서\자재 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\표준서\자재 검수_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L16" s="31" t="inlineStr">
@@ -37099,8 +37102,8 @@
 2) 실무 작업방법 수칙(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\수행지침\자재 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\수행지침\자재 검수_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N16" s="31" t="inlineStr">
@@ -37109,8 +37112,8 @@
 2) 미검측 및 정량 시방 미달에 따른 자재 검수 (WBS 9000-4-15) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 자재검수서, 품질시험 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O16" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\체크리스트\자재 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O16" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\15_자재 검수\체크리스트\자재 검수_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P16" s="30" t="n"/>
@@ -37178,8 +37181,8 @@
 2) 터파기/지반 정리 달성을 위한 필수 시공 방법(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\표준서\터파기_지반 정리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\표준서\터파기_지반 정리_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L17" s="31" t="inlineStr">
@@ -37188,8 +37191,8 @@
 2) 실무 작업방법 수칙(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\수행지침\터파기_지반 정리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\수행지침\터파기_지반 정리_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N17" s="31" t="inlineStr">
@@ -37198,8 +37201,8 @@
 2) 미검측 및 정량 시방 미달에 따른 터파기/지반 정리 (WBS 9000-4-16) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량 성과, 지지력시험성과 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O17" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\체크리스트\터파기_지반 정리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O17" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\16_터파기_지반 정리\체크리스트\터파기_지반 정리_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P17" s="30" t="n"/>
@@ -37267,8 +37270,8 @@
 2) 바닥(버림) 콘크리트 타설 달성을 위한 필수 시공 방법(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\표준서\바닥(버림) 콘크리트 타설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\표준서\바닥(버림) 콘크리트 타설_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L18" s="31" t="inlineStr">
@@ -37277,8 +37280,8 @@
 2) 실무 작업방법 수칙(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\수행지침\바닥(버림) 콘크리트 타설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\수행지침\바닥(버림) 콘크리트 타설_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N18" s="31" t="inlineStr">
@@ -37287,8 +37290,8 @@
 2) 미검측 및 정량 시방 미달에 따른 바닥(버림) 콘크리트 타설 (WBS 9000-4-17) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O18" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\체크리스트\바닥(버림) 콘크리트 타설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O18" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\17_바닥(버림) 콘크리트 타설\체크리스트\바닥(버림) 콘크리트 타설_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P18" s="30" t="n"/>
@@ -37356,8 +37359,8 @@
 2) 인터페이스 회의(매주) 달성을 위한 필수 시공 방법(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한 선후행공정 시...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\표준서\인터페이스 회의(매주)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\표준서\인터페이스 회의(매주)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L19" s="31" t="inlineStr">
@@ -37366,8 +37369,8 @@
 2) 실무 작업방법 수칙(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\수행지침\인터페이스 회의(매주)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\수행지침\인터페이스 회의(매주)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N19" s="31" t="inlineStr">
@@ -37376,8 +37379,8 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 회의(매주) (WBS 9000-4-18) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O19" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\체크리스트\인터페이스 회의(매주)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O19" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\18_인터페이스 회의(매주)\체크리스트\인터페이스 회의(매주)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P19" s="30" t="n"/>
@@ -37445,8 +37448,8 @@
 2) 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) 달성을 위한 필수 시공 방법(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결정, 각종 필증...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\표준서\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\표준서\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L20" s="31" t="inlineStr">
@@ -37455,8 +37458,8 @@
 2) 실무 작업방법 수칙(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\수행지침\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\수행지침\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N20" s="31" t="inlineStr">
@@ -37465,8 +37468,8 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) (WBS 9000-4-19) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O20" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\체크리스트\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O20" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\19_인터페이스 각 공종별 Issue (기계, 전기, 통신분야)\체크리스트\인터페이스 각 공종별 Issue (기계, 전기, 통신분야)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P20" s="30" t="n"/>
@@ -37534,8 +37537,8 @@
 2) 인터페이스 각 공종별 Issue (토목분야) 달성을 위한 필수 시공 방법(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\표준서\인터페이스 각 공종별 Issue (토목분야)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\표준서\인터페이스 각 공종별 Issue (토목분야)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L21" s="31" t="inlineStr">
@@ -37544,8 +37547,8 @@
 2) 실무 작업방법 수칙(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\수행지침\인터페이스 각 공종별 Issue (토목분야)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\수행지침\인터페이스 각 공종별 Issue (토목분야)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N21" s="31" t="inlineStr">
@@ -37554,8 +37557,8 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (토목분야) (WBS 9000-4-20) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O21" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\체크리스트\인터페이스 각 공종별 Issue (토목분야)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O21" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\20_인터페이스 각 공종별 Issue (토목분야)\체크리스트\인터페이스 각 공종별 Issue (토목분야)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P21" s="30" t="n"/>
@@ -37623,8 +37626,8 @@
 2) 기초~상부슬라브 구조물 시공 달성을 위한 필수 시공 방법(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\표준서\기초~상부슬라브 구조물 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\표준서\기초~상부슬라브 구조물 시공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L22" s="31" t="inlineStr">
@@ -37633,8 +37636,8 @@
 2) 실무 작업방법 수칙(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\수행지침\기초~상부슬라브 구조물 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\수행지침\기초~상부슬라브 구조물 시공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N22" s="31" t="inlineStr">
@@ -37643,8 +37646,8 @@
 2) 미검측 및 정량 시방 미달에 따른 기초~상부슬라브 구조물 시공 (WBS 9000-4-21) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 각종 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O22" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\체크리스트\기초~상부슬라브 구조물 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O22" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\21_기초~상부슬라브 구조물 시공\체크리스트\기초~상부슬라브 구조물 시공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P22" s="30" t="n"/>
@@ -37712,8 +37715,8 @@
 2) 철근 가공 달성을 위한 필수 시공 방법(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\표준서\철근 가공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\표준서\철근 가공_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L23" s="31" t="inlineStr">
@@ -37722,8 +37725,8 @@
 2) 실무 작업방법 수칙(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\수행지침\철근 가공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\수행지침\철근 가공_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N23" s="31" t="inlineStr">
@@ -37732,8 +37735,8 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 가공 (WBS 9000-4-22) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O23" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\체크리스트\철근 가공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O23" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\22_철근 가공\체크리스트\철근 가공_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P23" s="30" t="n"/>
@@ -37801,8 +37804,8 @@
 2) 작업발판, 비계 및 동바리 설치 달성을 위한 필수 시공 방법(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\표준서\작업발판, 비계 및 동바리 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\표준서\작업발판, 비계 및 동바리 설치_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L24" s="31" t="inlineStr">
@@ -37811,8 +37814,8 @@
 2) 실무 작업방법 수칙(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\수행지침\작업발판, 비계 및 동바리 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\수행지침\작업발판, 비계 및 동바리 설치_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N24" s="31" t="inlineStr">
@@ -37821,8 +37824,8 @@
 2) 미검측 및 정량 시방 미달에 따른 작업발판, 비계 및 동바리 설치 (WBS 9000-4-23) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 비계 및 동바리 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O24" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\체크리스트\작업발판, 비계 및 동바리 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O24" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\23_작업발판, 비계 및 동바리 설치\체크리스트\작업발판, 비계 및 동바리 설치_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P24" s="30" t="n"/>
@@ -37890,8 +37893,8 @@
 2) 철근 조립 달성을 위한 필수 시공 방법(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\표준서\철근 조립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\표준서\철근 조립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L25" s="31" t="inlineStr">
@@ -37900,8 +37903,8 @@
 2) 실무 작업방법 수칙(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\수행지침\철근 조립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\수행지침\철근 조립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N25" s="31" t="inlineStr">
@@ -37910,8 +37913,8 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 조립 (WBS 9000-4-24) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O25" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\체크리스트\철근 조립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O25" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\24_철근 조립\체크리스트\철근 조립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P25" s="30" t="n"/>
@@ -37979,8 +37982,8 @@
 2) 거푸집 조립 달성을 위한 필수 시공 방법(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\표준서\거푸집 조립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\표준서\거푸집 조립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L26" s="31" t="inlineStr">
@@ -37989,8 +37992,8 @@
 2) 실무 작업방법 수칙(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\수행지침\거푸집 조립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\수행지침\거푸집 조립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N26" s="31" t="inlineStr">
@@ -37999,8 +38002,8 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 조립 (WBS 9000-4-25) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 거푸집 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O26" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\체크리스트\거푸집 조립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O26" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\25_거푸집 조립\체크리스트\거푸집 조립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P26" s="30" t="n"/>
@@ -38070,8 +38073,8 @@
 2) 콘크리트 타설 및 다짐 달성을 위한 필수 시공 방법(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라브 타설시 동바...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\표준서\콘크리트 타설 및 다짐_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\표준서\콘크리트 타설 및 다짐_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L27" s="31" t="inlineStr">
@@ -38080,8 +38083,8 @@
 2) 실무 작업방법 수칙(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\수행지침\콘크리트 타설 및 다짐_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\수행지침\콘크리트 타설 및 다짐_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N27" s="31" t="inlineStr">
@@ -38090,8 +38093,8 @@
 2) 미검측 및 정량 시방 미달에 따른 콘크리트 타설 및 다짐 (WBS 9000-4-26) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 콘크리트 구조물 확보, 타설보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O27" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\체크리스트\콘크리트 타설 및 다짐_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O27" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\26_콘크리트 타설 및 다짐\체크리스트\콘크리트 타설 및 다짐_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P27" s="30" t="n"/>
@@ -38159,8 +38162,8 @@
 2) 거푸집 해체 달성을 위한 필수 시공 방법(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태 Double ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\표준서\거푸집 해체_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\표준서\거푸집 해체_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L28" s="31" t="inlineStr">
@@ -38169,8 +38172,8 @@
 2) 실무 작업방법 수칙(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\수행지침\거푸집 해체_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\수행지침\거푸집 해체_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N28" s="31" t="inlineStr">
@@ -38179,8 +38182,8 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 해체 (WBS 9000-4-27) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해체 완료 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O28" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\체크리스트\거푸집 해체_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O28" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\27_거푸집 해체\체크리스트\거푸집 해체_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P28" s="30" t="n"/>
@@ -38248,8 +38251,8 @@
 2) 건축 내부 및 마감공사 달성을 위한 필수 시공 방법(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\표준서\건축 내부 및 마감공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\표준서\건축 내부 및 마감공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L29" s="31" t="inlineStr">
@@ -38258,8 +38261,8 @@
 2) 실무 작업방법 수칙(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\수행지침\건축 내부 및 마감공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\수행지침\건축 내부 및 마감공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N29" s="31" t="inlineStr">
@@ -38268,8 +38271,8 @@
 2) 미검측 및 정량 시방 미달에 따른 건축 내부 및 마감공사 (WBS 9000-4-28) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O29" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\체크리스트\건축 내부 및 마감공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O29" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\28_건축 내부 및 마감공사\체크리스트\건축 내부 및 마감공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P29" s="30" t="n"/>
@@ -38337,8 +38340,8 @@
 2) 창호,유리 및 금속지붕공사 달성을 위한 필수 시공 방법(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\표준서\창호,유리 및 금속지붕공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\표준서\창호,유리 및 금속지붕공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L30" s="31" t="inlineStr">
@@ -38347,8 +38350,8 @@
 2) 실무 작업방법 수칙(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\수행지침\창호,유리 및 금속지붕공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\수행지침\창호,유리 및 금속지붕공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N30" s="31" t="inlineStr">
@@ -38357,8 +38360,8 @@
 2) 미검측 및 정량 시방 미달에 따른 창호,유리 및 금속지붕공사 (WBS 9000-4-29) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공상세도 및 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O30" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\체크리스트\창호,유리 및 금속지붕공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O30" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\29_창호,유리 및 금속지붕공사\체크리스트\창호,유리 및 금속지붕공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P30" s="30" t="n"/>
@@ -38426,8 +38429,8 @@
 2) 조적공사 달성을 위한 필수 시공 방법(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\표준서\조적공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\표준서\조적공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L31" s="31" t="inlineStr">
@@ -38436,8 +38439,8 @@
 2) 실무 작업방법 수칙(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\수행지침\조적공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\수행지침\조적공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N31" s="31" t="inlineStr">
@@ -38446,8 +38449,8 @@
 2) 미검측 및 정량 시방 미달에 따른 조적공사 (WBS 9000-4-30) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시멘트 벽돌 및 블록 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O31" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\체크리스트\조적공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O31" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\30_조적공사\체크리스트\조적공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P31" s="30" t="n"/>
@@ -38515,8 +38518,8 @@
 2) 내부 방수공사 달성을 위한 필수 시공 방법(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\표준서\내부 방수공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\표준서\내부 방수공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L32" s="31" t="inlineStr">
@@ -38525,8 +38528,8 @@
 2) 실무 작업방법 수칙(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\수행지침\내부 방수공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\수행지침\내부 방수공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N32" s="31" t="inlineStr">
@@ -38535,8 +38538,8 @@
 2) 미검측 및 정량 시방 미달에 따른 내부 방수공사 (WBS 9000-4-31) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 방수공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O32" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\체크리스트\내부 방수공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O32" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\31_내부 방수공사\체크리스트\내부 방수공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P32" s="30" t="n"/>
@@ -38604,8 +38607,8 @@
 2) 미장 및 타일공사 달성을 위한 필수 시공 방법(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\표준서\미장 및 타일공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\표준서\미장 및 타일공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L33" s="31" t="inlineStr">
@@ -38614,8 +38617,8 @@
 2) 실무 작업방법 수칙(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\수행지침\미장 및 타일공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\수행지침\미장 및 타일공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N33" s="31" t="inlineStr">
@@ -38624,8 +38627,8 @@
 2) 미검측 및 정량 시방 미달에 따른 미장 및 타일공사 (WBS 9000-4-32) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 미장,타일 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O33" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\체크리스트\미장 및 타일공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O33" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\32_미장 및 타일공사\체크리스트\미장 및 타일공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P33" s="30" t="n"/>
@@ -38693,8 +38696,8 @@
 2) 수장 및 잡철물공사 달성을 위한 필수 시공 방법(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 도어, 난간,창...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\표준서\수장 및 잡철물공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\표준서\수장 및 잡철물공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L34" s="31" t="inlineStr">
@@ -38703,8 +38706,8 @@
 2) 실무 작업방법 수칙(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\수행지침\수장 및 잡철물공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\수행지침\수장 및 잡철물공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N34" s="31" t="inlineStr">
@@ -38713,8 +38716,8 @@
 2) 미검측 및 정량 시방 미달에 따른 수장 및 잡철물공사 (WBS 9000-4-33) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 수장 및 잡철물검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O34" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\체크리스트\수장 및 잡철물공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O34" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\33_수장 및 잡철물공사\체크리스트\수장 및 잡철물공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P34" s="30" t="n"/>
@@ -38782,8 +38785,8 @@
 2) 도장공사 달성을 위한 필수 시공 방법(도장재 (붓, 롤러등)로 벽면에 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\표준서\도장공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\표준서\도장공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L35" s="31" t="inlineStr">
@@ -38792,8 +38795,8 @@
 2) 실무 작업방법 수칙(도장재 (붓, 롤러등)로 벽면에 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\수행지침\도장공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\수행지침\도장공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N35" s="31" t="inlineStr">
@@ -38802,8 +38805,8 @@
 2) 미검측 및 정량 시방 미달에 따른 도장공사 (WBS 9000-4-34) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 도장공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O35" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\체크리스트\도장공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O35" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\34_도장공사\체크리스트\도장공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P35" s="30" t="n"/>
@@ -38871,8 +38874,8 @@
 2) 인테리어 및 무대공사 달성을 위한 필수 시공 방법(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\표준서\인테리어 및 무대공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\표준서\인테리어 및 무대공사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L36" s="31" t="inlineStr">
@@ -38881,8 +38884,8 @@
 2) 실무 작업방법 수칙(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\수행지침\인테리어 및 무대공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\수행지침\인테리어 및 무대공사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N36" s="31" t="inlineStr">
@@ -38891,8 +38894,8 @@
 2) 미검측 및 정량 시방 미달에 따른 인테리어 및 무대공사 (WBS 9000-4-35) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 각 공종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O36" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\체크리스트\인테리어 및 무대공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O36" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\35_인테리어 및 무대공사\체크리스트\인테리어 및 무대공사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P36" s="30" t="n"/>
@@ -38960,8 +38963,8 @@
 2) 준공전 건축 인허가 달성을 위한 필수 시공 방법(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강기 설치검사 신...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\표준서\준공전 건축 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\표준서\준공전 건축 인허가_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L37" s="31" t="inlineStr">
@@ -38970,8 +38973,8 @@
 2) 실무 작업방법 수칙(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\수행지침\준공전 건축 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\수행지침\준공전 건축 인허가_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N37" s="31" t="inlineStr">
@@ -38980,8 +38983,8 @@
 2) 미검측 및 정량 시방 미달에 따른 준공전 건축 인허가 (WBS 9000-4-36) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고 / 승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O37" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\체크리스트\준공전 건축 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O37" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\36_준공전 건축 인허가\체크리스트\준공전 건축 인허가_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P37" s="30" t="n"/>
@@ -39051,8 +39054,8 @@
 2) 소방시설공사 완공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리기간 3일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\표준서\소방시설공사 완공검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\표준서\소방시설공사 완공검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L38" s="31" t="inlineStr">
@@ -39061,8 +39064,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\수행지침\소방시설공사 완공검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\수행지침\소방시설공사 완공검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N38" s="31" t="inlineStr">
@@ -39071,8 +39074,8 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 완공검사 (WBS 9000-4-37) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설 완공검사 증명서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O38" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\체크리스트\소방시설공사 완공검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O38" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\37_소방시설공사 완공검사\체크리스트\소방시설공사 완공검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P38" s="30" t="n"/>
@@ -39142,8 +39145,8 @@
 2) 승강기 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\표준서\승강기 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\표준서\승강기 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L39" s="31" t="inlineStr">
@@ -39152,8 +39155,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\수행지침\승강기 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\수행지침\승강기 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N39" s="31" t="inlineStr">
@@ -39162,8 +39165,8 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치 신고서 제출 (WBS 9000-4-38) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O39" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\체크리스트\승강기 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O39" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\38_승강기 설치 신고서 제출\체크리스트\승강기 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P39" s="30" t="n"/>
@@ -39232,8 +39235,8 @@
 2) 저수조 설치현황 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\표준서\저수조 설치현황 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\표준서\저수조 설치현황 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L40" s="31" t="inlineStr">
@@ -39242,8 +39245,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\수행지침\저수조 설치현황 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\수행지침\저수조 설치현황 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N40" s="31" t="inlineStr">
@@ -39252,8 +39255,8 @@
 2) 미검측 및 정량 시방 미달에 따른 저수조 설치현황 신고서 제출 (WBS 9000-4-39) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 저수조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O40" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\체크리스트\저수조 설치현황 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O40" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\39_저수조 설치현황 신고서 제출\체크리스트\저수조 설치현황 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P40" s="30" t="n"/>
@@ -39323,8 +39326,8 @@
 2) 오수처리시설 / 정화조 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\표준서\오수처리시설 _ 정화조 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\표준서\오수처리시설 _ 정화조 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L41" s="31" t="inlineStr">
@@ -39333,8 +39336,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\수행지침\오수처리시설 _ 정화조 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\수행지침\오수처리시설 _ 정화조 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="inlineStr">
@@ -39343,8 +39346,8 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 설치 신고서 제출 (WBS 9000-4-40) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설/정화조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O41" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\체크리스트\오수처리시설 _ 정화조 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O41" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\40_오수처리시설 _ 정화조 설치 신고서 제출\체크리스트\오수처리시설 _ 정화조 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P41" s="30" t="n"/>
@@ -39413,8 +39416,8 @@
 2) 전기사용전 검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\표준서\전기사용전 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\표준서\전기사용전 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L42" s="31" t="inlineStr">
@@ -39423,8 +39426,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\수행지침\전기사용전 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\수행지침\전기사용전 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N42" s="31" t="inlineStr">
@@ -39433,8 +39436,8 @@
 2) 미검측 및 정량 시방 미달에 따른 전기사용전 검사 (WBS 9000-4-41) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 전기사용전 검사 필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O42" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\체크리스트\전기사용전 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O42" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\41_전기사용전 검사\체크리스트\전기사용전 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P42" s="30" t="n"/>
@@ -39504,8 +39507,8 @@
 2) 승강기 설치검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 서식 제출후 처...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\표준서\승강기 설치검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\표준서\승강기 설치검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L43" s="31" t="inlineStr">
@@ -39514,8 +39517,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\수행지침\승강기 설치검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\수행지침\승강기 설치검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N43" s="31" t="inlineStr">
@@ -39524,8 +39527,8 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치검사 (WBS 9000-4-42) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 사용필증, 합격증보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O43" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\체크리스트\승강기 설치검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O43" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\42_승강기 설치검사\체크리스트\승강기 설치검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P43" s="30" t="n"/>
@@ -39593,8 +39596,8 @@
 2) 배수설비 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\표준서\배수설비 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\표준서\배수설비 설치 신고서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L44" s="31" t="inlineStr">
@@ -39603,8 +39606,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\수행지침\배수설비 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\수행지침\배수설비 설치 신고서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N44" s="31" t="inlineStr">
@@ -39613,8 +39616,8 @@
 2) 미검측 및 정량 시방 미달에 따른 배수설비 설치 신고서 제출 (WBS 9000-4-43) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 배수설비 사용필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O44" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\체크리스트\배수설비 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O44" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\43_배수설비 설치 신고서 제출\체크리스트\배수설비 설치 신고서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P44" s="30" t="n"/>
@@ -39684,8 +39687,8 @@
 2) 정보통신공사 사용전검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후 처리기간 14...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\표준서\정보통신공사 사용전검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\표준서\정보통신공사 사용전검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L45" s="31" t="inlineStr">
@@ -39694,8 +39697,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\수행지침\정보통신공사 사용전검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\수행지침\정보통신공사 사용전검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N45" s="31" t="inlineStr">
@@ -39704,8 +39707,8 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 사용전검사 (WBS 9000-4-44) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신사용전 검사필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O45" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\체크리스트\정보통신공사 사용전검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O45" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\44_정보통신공사 사용전검사\체크리스트\정보통신공사 사용전검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P45" s="30" t="n"/>
@@ -39775,8 +39778,8 @@
 2) 오수처리시설 / 정화조 준공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\표준서\오수처리시설 _ 정화조 준공검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\표준서\오수처리시설 _ 정화조 준공검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L46" s="31" t="inlineStr">
@@ -39785,8 +39788,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\수행지침\오수처리시설 _ 정화조 준공검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\수행지침\오수처리시설 _ 정화조 준공검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N46" s="31" t="inlineStr">
@@ -39795,8 +39798,8 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 준공검사 (WBS 9000-4-45) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설 / 정화조 준공필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O46" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\체크리스트\오수처리시설 _ 정화조 준공검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O46" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\45_오수처리시설 _ 정화조 준공검사\체크리스트\오수처리시설 _ 정화조 준공검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P46" s="30" t="n"/>
@@ -39865,8 +39868,8 @@
 2) 급수공사 신청서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\표준서\급수공사 신청서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\표준서\급수공사 신청서 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L47" s="31" t="inlineStr">
@@ -39875,8 +39878,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\수행지침\급수공사 신청서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\수행지침\급수공사 신청서 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N47" s="31" t="inlineStr">
@@ -39885,8 +39888,8 @@
 2) 미검측 및 정량 시방 미달에 따른 급수공사 신청서 제출 (WBS 9000-4-46) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 급수 사용허가 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O47" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\체크리스트\급수공사 신청서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O47" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\46_급수공사 신청서 제출\체크리스트\급수공사 신청서 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P47" s="30" t="n"/>
@@ -39955,8 +39958,8 @@
 2) 업무대행 건축사 사용승인 검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 별지 제17호 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\표준서\업무대행 건축사 사용승인 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\표준서\업무대행 건축사 사용승인 검사_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L48" s="31" t="inlineStr">
@@ -39965,8 +39968,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\수행지침\업무대행 건축사 사용승인 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\수행지침\업무대행 건축사 사용승인 검사_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N48" s="31" t="inlineStr">
@@ -39975,8 +39978,8 @@
 2) 미검측 및 정량 시방 미달에 따른 업무대행 건축사 사용승인 검사 (WBS 9000-4-47) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O48" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\체크리스트\업무대행 건축사 사용승인 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O48" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\47_업무대행 건축사 사용승인 검사\체크리스트\업무대행 건축사 사용승인 검사_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P48" s="30" t="n"/>
@@ -40046,8 +40049,8 @@
 2) 건축물 사용승인 신청 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식 제출후 처리기...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\표준서\건축물 사용승인 신청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\표준서\건축물 사용승인 신청_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L49" s="31" t="inlineStr">
@@ -40056,8 +40059,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\수행지침\건축물 사용승인 신청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\수행지침\건축물 사용승인 신청_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N49" s="31" t="inlineStr">
@@ -40066,8 +40069,8 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물 사용승인 신청 (WBS 9000-4-48) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O49" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\체크리스트\건축물 사용승인 신청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O49" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\48_건축물 사용승인 신청\체크리스트\건축물 사용승인 신청_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P49" s="30" t="n"/>
@@ -40135,8 +40138,8 @@
 2) 건축물대장 등재 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\표준서\건축물대장 등재_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\표준서\건축물대장 등재_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L50" s="31" t="inlineStr">
@@ -40145,8 +40148,8 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\수행지침\건축물대장 등재_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\수행지침\건축물대장 등재_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N50" s="31" t="inlineStr">
@@ -40155,8 +40158,8 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물대장 등재 (WBS 9000-4-49) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 대장 등재 확인 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O50" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\체크리스트\건축물대장 등재_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O50" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\49_건축물대장 등재\체크리스트\건축물대장 등재_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P50" s="30" t="n"/>
@@ -40227,8 +40230,8 @@
 2) 후속 구조물 인계 달성을 위한 필수 시공 방법(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명서, 전기사용전...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\표준서\후속 구조물 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+      <c r="K51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\표준서\후속 구조물 인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
         <v/>
       </c>
       <c r="L51" s="31" t="inlineStr">
@@ -40237,8 +40240,8 @@
 2) 실무 작업방법 수칙(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\수행지침\후속 구조물 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+      <c r="M51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\수행지침\후속 구조물 인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
         <v/>
       </c>
       <c r="N51" s="31" t="inlineStr">
@@ -40247,8 +40250,8 @@
 2) 미검측 및 정량 시방 미달에 따른 후속 구조물 인계 (WBS 9000-4-50) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 유지관리기관 인수인계서, 건축 인허가 서류, 준공도서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O51" s="155">
-        <f>HYPERLINK("매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\체크리스트\후속 구조물 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+      <c r="O51" s="156">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\6.건축\50_후속 구조물 인계\체크리스트\후속 구조물 인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
         <v/>
       </c>
       <c r="P51" s="30" t="n"/>

--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -10592,8 +10592,8 @@
     <col width="28" customWidth="1" style="147" min="7" max="7"/>
     <col width="12" customWidth="1" style="147" min="8" max="8"/>
     <col width="12" customWidth="1" style="147" min="9" max="9"/>
-    <col width="36" customWidth="1" style="147" min="10" max="10"/>
-    <col width="32" customWidth="1" style="147" min="11" max="11"/>
+    <col width="38" customWidth="1" style="147" min="10" max="10"/>
+    <col width="52" customWidth="1" style="147" min="11" max="11"/>
     <col width="28" customWidth="1" style="147" min="12" max="12"/>
     <col width="36" customWidth="1" style="147" min="13" max="13"/>
     <col width="24" customWidth="1" style="147" min="14" max="14"/>
@@ -10719,7 +10719,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" s="147">
+    <row r="2" ht="48" customHeight="1" s="147">
       <c r="A2" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -10767,12 +10767,14 @@
       </c>
       <c r="J2" s="156" t="inlineStr">
         <is>
-          <t>동탄도시철도(트램) 기계설비(HVAC, 급배수, 위생, 오폐수, 승강기) 및 소방설비(소화, 제연, 경보)의 착공 전 설계도서(도면·시방서·수량산출서·내역서)의 적격성을 검토하고, 지하 및 지상 정거장, 변전소, 차량기지 내 법적 기준 충족 및 시공성을 사전 확보한다.</t>
+          <t>기계·소방설비 설계도서(도면/시방/계산서)의 KDS 47 및 NFTC 기준 적합성과 시공성·경제성 사전 검증</t>
         </is>
       </c>
       <c r="K2" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 설계도서 및 계산서 총괄 수집, STEP 2: 삼각 교차 대조 및 물량 정합성 검증 절차서 준수 시공</t>
+          <t>1) STEP 1 (설계도서 삼각 대조): KDS 47/NFTC 기준에 따라 공조/환기 부하계산서, 설계도면, 수량산출서 1:1 정합성 검증
+2) STEP 2 (주요 장비 용량 검토): 변전소 PAC(3대), 고내열 제연팬(250℃/1h), 인버터 펌프 정격 양정/유량 시방 일치성 확인
+3) STEP 3 (인터페이스 및 개선안 도출): 건축 슬리브, 전기 NFR-8 내화배선, 신호 배수공동구 연계성 검토 및 설계변경안 감리 승인</t>
         </is>
       </c>
       <c r="L2" s="156" t="inlineStr">
@@ -10831,7 +10833,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="147">
+    <row r="3" ht="48" customHeight="1" s="147">
       <c r="A3" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -10879,12 +10881,14 @@
       </c>
       <c r="J3" s="163" t="inlineStr">
         <is>
-          <t>기계 및 소방공사의 성공적인 수행을 위해 발주처, 책임감리단, 원도급사, 전문협력업체가 참여하는 Kick-Off Meeting을 개최하여 중점 품질관리 항목, 법적 인허가 일정, 장비 제작납기 및 자재 승인 프로세스를 일괄 확정한다.</t>
+          <t>기계·소방 공종 3자(발주처-감리-시공) 킥오프를 통한 주요 자재 조달 라인 및 4대 공정 마일스톤 확정</t>
         </is>
       </c>
       <c r="K3" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: KOM 킥오프 회의 소집 및 R&amp;R 확정, STEP 2: 주요 장비 제작 및 조달 계획 수립 절차서 준수 시공</t>
+          <t>1) STEP 1 (3자 협의체 구성): 발주처, 책임감리단, 기계/소방 협력사 간 공정·품질·안전 관리체계 및 업무 R&amp;R 확정
+2) STEP 2 (주요 자재 수급선 검토): STS 강관, 덕트, 펌프, 승강기 등 장납기 자재의 공장 승인 및 납품 스케줄 동기화
+3) STEP 3 (핵심 마일스톤 수립): 3D BIM 간섭해소, FAT 공장검수, 수압시험, 소방 완공검사 등 공정 임계경로(CP) 관리</t>
         </is>
       </c>
       <c r="L3" s="163" t="inlineStr">
@@ -10943,7 +10947,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="147">
+    <row r="4" ht="48" customHeight="1" s="147">
       <c r="A4" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -10991,12 +10995,14 @@
       </c>
       <c r="J4" s="156" t="inlineStr">
         <is>
-          <t>지하 정거장 천장 및 기계실, 차량기지 검수고 등 배관·덕트 밀집 구역에 대해 3D BIM(LOD 350) 통합 모델링을 수행하여 타 공종(건축, 전기, 신호, 궤도)과의 물리적 간섭을 착공 전 100% 제거하고 최적의 시공 동선을 도출한다.</t>
+          <t>LOD 350 기반 3D BIM을 활용하여 기계덕트·소화배관·전기트레이 간 Hard Clash 0건 달성 및 CSD 승인</t>
         </is>
       </c>
       <c r="K4" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 3D BIM 기계/소방 상세 모델링 (LOD 350), STEP 2: 다공종 통합 모델 합성 및 간섭 체크 절차서 준수 시공</t>
+          <t>1) STEP 1 (LOD 350 3D 모델링): 기계 공조덕트, 소화배관, 위생배관 및 전기 트레이의 3D 통합 모델 구축
+2) STEP 2 (복합 간섭체크 실행): Navisworks 간섭 체크 엔진을 가동하여 배관 교차 및 건축 골조 간섭(Clash) 전수 색출
+3) STEP 3 (시공상세도 CSD 확정): 정거장 유효 천장고(CH ≥ 2.7m) 확보를 위한 배관 입체 재배치 및 감리단 CSD 최종 승인</t>
         </is>
       </c>
       <c r="L4" s="156" t="inlineStr">
@@ -11055,7 +11061,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="147">
+    <row r="5" ht="48" customHeight="1" s="147">
       <c r="A5" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11103,12 +11109,14 @@
       </c>
       <c r="J5" s="163" t="inlineStr">
         <is>
-          <t>소방시설공사업법 및 물환경보전법에 따라 공사 착공 전 관할 소방서로부터 소방시설 시공 동의 및 착공신고를 득하고, 차량기지 위험물 저장소, 비상발전기 유류탱크, 오수처리시설 인허가를 적기에 완료하여 법적 리스크를 제거한다.</t>
+          <t>소방시설공사업법 제13조에 따른 착공신고 및 위험물·오폐수 환경 인허가 적기 득</t>
         </is>
       </c>
       <c r="K5" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방시설 착공신고서 작성 및 도서 구비, STEP 2: 소방시설 건축동의 및 기술 검토 보완 절차서 준수 시공</t>
+          <t>1) STEP 1 (소방 착공신고): 소방기술자/감리원 배치신고서 및 소방 설계도서를 관할 화성소방서에 제출하여 착공필증 수령
+2) STEP 2 (위험물 저장 승인): 비상발전기 유류탱크(경유) 저장소 설치허가 및 방유제(용량 110%) 안전기준 검증
+3) STEP 3 (환경 인허가 완료): 차량기지 오폐수배출시설 설치신고 및 수질 TMS 연동 계획 관할 지자체 승인</t>
         </is>
       </c>
       <c r="L5" s="163" t="inlineStr">
@@ -11167,7 +11175,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="147">
+    <row r="6" ht="48" customHeight="1" s="147">
       <c r="A6" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11215,12 +11223,14 @@
       </c>
       <c r="J6" s="156" t="inlineStr">
         <is>
-          <t>지하 정거장 기계실 및 차량기지 종합검수동에 설치되는 대형 중량물(공기조화기, 냉동기, 소방펌프, 열교환기)의 반입 개구부, 수직 인양 동선, 양중 크레인 작업 반경 및 현장 자재 야적장 보관 관리 계획을 수립한다.</t>
+          <t>지하 기계실 대형 장비(AHU, 펌프 등)의 DA 개구부 양중 및 안전 반입 동선 확보</t>
         </is>
       </c>
       <c r="K6" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 중량 장비 제원 및 반입 경로 실측, STEP 2: 양중 크레인 작업 계획 및 안전성 검토 절차서 준수 시공</t>
+          <t>1) STEP 1 (양중 크레인 계획): 50ton 하이드로 크레인 작업반경 설정, 복공판 하부 지지력(K30 ≥ 150) 및 아웃트리거 보강
+2) STEP 2 (개구부 통과 검토): 장비 분할 치수와 DA 개구부(W2.5m x L4.0m) 유효 통과폭 대조 및 호이스트/체인블록 가설
+3) STEP 3 (수평 인입 및 안착): 운반 롤러 및 레일 시스템을 이용하여 기계실 기초 패드 위로 유도 후 레벨링 및 앵커링</t>
         </is>
       </c>
       <c r="L6" s="156" t="inlineStr">
@@ -11279,7 +11289,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="147">
+    <row r="7" ht="48" customHeight="1" s="147">
       <c r="A7" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11327,12 +11337,14 @@
       </c>
       <c r="J7" s="163" t="inlineStr">
         <is>
-          <t>동탄트램 복합 공정의 성공을 위해 기계·소방 분야와 6대 연관 공종(토목 노반, 궤도 콘크리트도상, 건축 구조/마감, 전기 수변전, 신호 연동, 통신 LTE-R) 간의 주간 Big Room 합동 회의를 운영하여 시공 오차 및 인터페이스 누락을 원천 차단한다.</t>
+          <t>건축, 전기, 통신, 신호, 궤도 등 타 공종과의 시공 간섭 배제 및 시공 우선순위 룰 확립</t>
         </is>
       </c>
       <c r="K7" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: Big Room 합동 회의 안건 도출 및 3D 모델 준비, STEP 2: 7대 공종 합동 기술 조율 및 대안 확정 절차서 준수 시공</t>
+          <t>1) STEP 1 (Big Room 정례협의): 7대 공종 합동 주간 인터페이스 회의를 운영하여 주배관과 타 공종 지장물 간섭 해소
+2) STEP 2 (시공 우선순위 확정): 슬리브 선매립(건축) ⟶ 대형 풍도/주배관(기계) ⟶ 케이블트레이(전기) 순차 시공 룰 적용
+3) STEP 3 (인터페이스 체크시트 발행): 상호 인계인수 전 슬리브 위치, 방화구획, 배수구 트렌치 시공 상태 합동 서명 검측</t>
         </is>
       </c>
       <c r="L7" s="163" t="inlineStr">
@@ -11391,7 +11403,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="147">
+    <row r="8" ht="48" customHeight="1" s="147">
       <c r="A8" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11439,12 +11451,14 @@
       </c>
       <c r="J8" s="156" t="inlineStr">
         <is>
-          <t>트램 본선 도로 하부 및 정거장 외부 인입 구역에 매설되는 기계배관(상수도 급수관, 지열 집열관, 오배수 연결관)에 대해 지자체(화성시), 도로관리청 및 한국전력·가스·통신 유관기관과 지장물 이설 및 도로굴착 점용 협의를 수행한다.</t>
+          <t>트램 본선 도로 하부 지중매설 배관(상수도, 지열, 우오수)과 지하 지장물 간 안전 이격거리 확보</t>
         </is>
       </c>
       <c r="K8" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 지하 지장물 매설도 수집 및 3D GPR 탐사, STEP 2: 유관기관 협의 및 도로굴착점용 허가 획득 절차서 준수 시공</t>
+          <t>1) STEP 1 (3D 지하매설물 탐사): GPR 탐사 및 줄파기를 통해 기존 가스관, 한전관로, 통신관로 심도와 좌표 정밀 확인
+2) STEP 2 (안전 이격거리 유지): 타 지장물과 최소 300mm 이상 이격 배치하고 고저차 간섭 시 강관 보호공(Casing) 적용
+3) STEP 3 (모래부설 및 다짐): 배관 주위 양질의 모래(두께 100mm) 부설 후 되메우기 층별 다짐(다짐도 ≥ 95%) 및 경고테이프 매설</t>
         </is>
       </c>
       <c r="L8" s="156" t="inlineStr">
@@ -11503,7 +11517,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="147">
+    <row r="9" ht="48" customHeight="1" s="147">
       <c r="A9" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11551,12 +11565,14 @@
       </c>
       <c r="J9" s="163" t="inlineStr">
         <is>
-          <t>KCS 41(건축기계설비공사 표준시방서) 및 KDS 47(철도설계기준)에 의거하여 기계·소방설비의 단계별 세부 시공 방법, 동원 인원 및 장비 계획, 용접 절차서(WPS), 비파괴검사(NDT), 수압시험 및 품질·안전관리 종합 시공계획서를 작성하여 감리단 승인을 득한다.</t>
+          <t>KCS 41 시방 기준 준수, 유자격 용접사 WPS 승인 및 밀폐공간 안전보건 체계 확립</t>
         </is>
       </c>
       <c r="K9" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 공종별 세부 시공 방법 및 절차서 작성, STEP 2: 자재 시험 및 품질관리 계획서 수립 절차서 준수 시공</t>
+          <t>1) STEP 1 (공종별 절차서 수립): 배관, 덕트, 장비설치 등 세부 작업별 인원·장비·공정 계획 및 위험성평가서 작성
+2) STEP 2 (WPS 용접절차 승인): 배관 재질별(STS, 탄소강) 용접절차시방서(WPS) 수립 및 유자격 용접사 시험편 PQR 검증
+3) STEP 3 (밀폐공간 안전관리): 지하 집수조/탱크 작업 시 복합가스(산소, 황화수소) 측정, 송기마스크 착용 및 감시원 상주</t>
         </is>
       </c>
       <c r="L9" s="163" t="inlineStr">
@@ -11615,7 +11631,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" s="147">
+    <row r="10" ht="48" customHeight="1" s="147">
       <c r="A10" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11663,12 +11679,14 @@
       </c>
       <c r="J10" s="156" t="inlineStr">
         <is>
-          <t>현장에 반입되는 배관용 스테인리스 강관, 인버터 가압 부스터펌프, 옥내소화전함, 밸브류, 공조기 등 주요 기자재에 대해 KS 인증서, 공인기관 시험성적서(밀시트), 공장검수(FAT) 성적을 1:1 대조하여 불량 자재의 현장 반입을 원천 차단한다.</t>
+          <t>배관, 밸브, 펌프 등 주요 기계·소방 기자재의 KS/KFI 규격 검증 및 공장 시험(FAT) 수행</t>
         </is>
       </c>
       <c r="K10" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 자재 공급원 승인 요청서(MAR) 접수 및 검토, STEP 2: 주요 대형 장비 공장검수(FAT) 수행 절차서 준수 시공</t>
+          <t>1) STEP 1 (공장검수 FAT 실시): 인버터 부스터펌프, 공조기 공장을 방문하여 모터 효율, 정격 양정·유량, 소음·진동 시험 입회
+2) STEP 2 (자재 현장 반입 검수): 밀시트(Mill Sheet), KS/KFI 인증서 확인 및 STS 강관 두께·진원도 마이크로미터 정밀 검측
+3) STEP 3 (자재 보관 및 불합격 통제): 배관 단부 보호캡 체결, 옥내 전용 적치장 보관 및 불합격 자재 24시간 이내 반출 조치</t>
         </is>
       </c>
       <c r="L10" s="156" t="inlineStr">
@@ -11727,7 +11745,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="147">
+    <row r="11" ht="48" customHeight="1" s="147">
       <c r="A11" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11775,12 +11793,14 @@
       </c>
       <c r="J11" s="163" t="inlineStr">
         <is>
-          <t>건축물의 피난·방화구조 등의 기준에 관한 규칙에 따라 방화벽, 바닥 슬래브를 관통하는 기계 배관, 냉매관, 공조 덕트 주변의 관통 틈새에 대해 화재안전연구원 공인 인증을 득한 내화채움재(내화패드, 방화실란트, 차염/차열재)를 100% 밀폐 시공하여 화염 및 유독가스 층간 전파를 원천 차단한다.</t>
+          <t>콘크리트 골조 타설 전 관통 슬리브 선매립 및 2시간 차열·차염 내화채움구조 시공</t>
         </is>
       </c>
       <c r="K11" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 관통부 틈새 청소 및 공인 내화구조 매핑, STEP 2: 내부 불연재(미네랄울) 고밀도 충진 절차서 준수 시공</t>
+          <t>1) STEP 1 (골조 슬리브 선매립): 구조체 철근 배근 시 배관경 대비 1~2규격 큰 강관/PVC 슬리브 설치 및 단단히 고정
+2) STEP 2 (관통 틈새 내화충진): 배관 설치 후 슬리브 틈새에 고밀도 미네랄울(밀도 ≥ 100kg/㎥) 충진 및 방화실란트 15mm 도포
+3) STEP 3 (내화성능 확인): 공인기관 2시간 차열·차염 성적서 확인 및 우레탄폼 등 가연성 자재 사용 전면 금지 검측</t>
         </is>
       </c>
       <c r="L11" s="163" t="inlineStr">
@@ -11839,7 +11859,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="147">
+    <row r="12" ht="48" customHeight="1" s="147">
       <c r="A12" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11887,12 +11907,14 @@
       </c>
       <c r="J12" s="156" t="inlineStr">
         <is>
-          <t>트램 본선 궤도 분기부 및 차량기지 내 총 143개소의 핵심 선로전환기(Point Machine)와 열차 위치 검지용 차축검지기(Axle Counter) 구역의 침수 불량 및 동절기 결빙 사고를 원천 방지하기 위하여 궤도 콘크리트 타설 전 하부 횡단 배수용 파이프 및 전선관로 공동구를 정밀 선시공한다.</t>
+          <t>본선 및 차량기지 143개소 선로전환기 하부 배수관로 선시공으로 동절기 결빙 및 침수 방지</t>
         </is>
       </c>
       <c r="K12" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 신호·궤도팀 합동 분기기 143개소 좌표 실측, STEP 2: 횡단 배수관로 매설 및 지지틀 고정 절차서 준수 시공</t>
+          <t>1) STEP 1 (드레인 피트 가설): 선로전환기 구동부 하부에 침전 드레인 피트 및 STS 타공 스트레이너 설치
+2) STEP 2 (횡단 배수관로 연결): 도상 횡단 배수관(D100/150)을 자연유하 구배(i ≥ 1.0%)로 선로변 주 집수정까지 직결
+3) STEP 3 (궤도 타설 전 통수시험): 궤도 콘크리트 타설 전 통수 및 수압시험을 실시하여 관로 막힘 및 누수 0건 최종 확인</t>
         </is>
       </c>
       <c r="L12" s="156" t="inlineStr">
@@ -11951,7 +11973,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="147">
+    <row r="13" ht="48" customHeight="1" s="147">
       <c r="A13" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -11999,12 +12021,14 @@
       </c>
       <c r="J13" s="163" t="inlineStr">
         <is>
-          <t>화재안전기술기준(NFTC) 및 전기설비기술기준에 따라 소방펌프실 주펌프, 충압펌프, 지하차도 및 역사 제연팬에 공급되는 비상 전원 간선에 대해 최고 수준의 고내열 내화성능을 갖춘 NFR-8(또는 F-FR-8) 내화케이블을 전용 배관으로 포설하고, 전기분야 비상발전기·MCC반과 무결점 인터페이스를 완료한다.</t>
+          <t>소방펌프, 제연팬 등 소방설비의 10초 이내 비상전원 절환 및 NFR-8 내화배선 무중단 공급</t>
         </is>
       </c>
       <c r="K13" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방 기계 부하 용량(kW) 산정 및 전기팀 통보, STEP 2: NFR-8 고내열 내화케이블 전용 관로 시공 절차서 준수 시공</t>
+          <t>1) STEP 1 (비상전원 ATS 연계): 상용전원 정전 시 10초 이내 비상발전기 전원으로 자동 절환되는 ATS 인터록 구축
+2) STEP 2 (NFR-8 내화케이블 포설): 소방용 동력 간선에 고내열 NFR-8 케이블을 전용 금속관에 단독 배선하여 850℃ 내열 확보
+3) STEP 3 (MCC 제어반 세팅): 소방펌프 전용 MCC 제어반의 과부하 트립 기능을 배제(경보만 발생)하여 화재 시 연속 가동 보장</t>
         </is>
       </c>
       <c r="L13" s="163" t="inlineStr">
@@ -12063,7 +12087,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" s="147">
+    <row r="14" ht="48" customHeight="1" s="147">
       <c r="A14" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12111,12 +12135,14 @@
       </c>
       <c r="J14" s="156" t="inlineStr">
         <is>
-          <t>정거장 및 차량기지 지하 저수조 내에서 생활위생용수와 소화용수가 장기간 정체되어 발생하는 사수(死水, 물고임 부패) 현상을 방지하기 위하여, 급수펌프 흡입배관의 최저점을 소화용수 유효수위 상향으로 확보하고, 저수조 내부에 유지관리용 칸막이 1개소를 설치하는 고도화 수배관 시스템을 시공한다.</t>
+          <t>위생적인 STS304 패널형 저수조 설치, 생활용수 사수 방지 배관 및 소화수 유효용량 상시 확보</t>
         </is>
       </c>
       <c r="K14" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 저수조 용량 및 소화수 유효수위 계산, STEP 2: STS 패널형 저수조 조립 및 칸막이 가설 절차서 준수 시공</t>
+          <t>1) STEP 1 (STS 패널 조립 용접): STS304 패널 아르곤(TIG) 용접 조립 후 액체침투탐상(PT)으로 용접부 결함 100% 색출
+2) STEP 2 (사수방지 흡입배관 분리): 급수펌프 흡입관은 소화수위 상단에, 소방펌프 흡입관은 바닥 최하단에 분리 배치
+3) STEP 3 (만수 수밀시험): 저수조 만수 후 24시간 동안 수위 강하 및 외부 누수 유무를 정밀 측정하여 감리단 합격 승인</t>
         </is>
       </c>
       <c r="L14" s="156" t="inlineStr">
@@ -12175,7 +12201,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" s="147">
+    <row r="15" ht="48" customHeight="1" s="147">
       <c r="A15" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12223,12 +12249,14 @@
       </c>
       <c r="J15" s="163" t="inlineStr">
         <is>
-          <t>신에너지 및 재생에너지 개발·이용·보급 촉진법 및 친환경 녹색건축물 인증 기준에 따라 차량기지 및 정거장에 지중 열교환용 고밀도 폴리에틸렌관(HDPE, KSM 3408)을 지하 150~200m 깊이로 천공 매설하고, 전기융착(EF) 접합 및 1.0MPa 수압시험, 친환경 벤토나이트 그라우팅을 완벽 시공한다.</t>
+          <t>수직 밀폐형 지열 U-Tube(심도 150m) 시공 및 친환경 지열 히트펌프 연계 열교환 극대화</t>
         </is>
       </c>
       <c r="K15" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 지열 천공 지점 측량 및 천공기 가설, STEP 2: U-Tube PE 열교환관 조립 및 1차 수압시험 절차서 준수 시공</t>
+          <t>1) STEP 1 (천공 및 U-Tube 삽입): 직경 150mm x 심도 150m 천공 후 고밀도 PE 파이프(KSM 3408, SDR11) U-Tube 삽입
+2) STEP 2 (열전도 그라우팅): 천공 하부부터 지표면까지 벤토나이트 혼합 그라우트재(열전도도 ≥ 1.8 W/m·K)를 가압 연속 주입
+3) STEP 3 (수압시험 및 헤더 연결): 1.0 MPa 수압으로 2시간 동안 압력 유지 확인 후 기계실 지열 헤더 매니폴드 연결</t>
         </is>
       </c>
       <c r="L15" s="163" t="inlineStr">
@@ -12287,7 +12315,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" s="147">
+    <row r="16" ht="48" customHeight="1" s="147">
       <c r="A16" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12335,12 +12363,14 @@
       </c>
       <c r="J16" s="156" t="inlineStr">
         <is>
-          <t>지하 정거장 대합실/승강장 및 변전실·전기실의 쾌적한 실내 환경 유지와 전기기기 발열 배출을 위해 KCS 41 시방서에 맞춰 아연도금강판(GI) 공조덕트를 시공하며, 변전실 시간당 10회 환기, 화장실 15~20회 음압 배기 및 동절기 외기 역류 방지용 B.D.D(기류역류방지댐퍼)를 완벽 가설한다.</t>
+          <t>변전실 1종 급기가압(10회/h, 실온 ≤40℃) 및 화장실 3종 음압 환기, 역류방지(B.D.D) 구축</t>
         </is>
       </c>
       <c r="K16" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 덕트 제작 치수 검수 및 아연도금강판 가공, STEP 2: 풍도 댐퍼 및 B.D.D 기류역류방지댐퍼 조립 절차서 준수 시공</t>
+          <t>1) STEP 1 (아연도강판 덕트 제작): KCS 41 시방 기준에 따라 아연도강판(GI) 피츠버그 록 성형 및 기밀 실링 시공
+2) STEP 2 (방진행거 및 댐퍼 취부): 덕트 하중 지지를 위한 방진스프링 행거(간격 ≤ 2.0m) 및 역류방지 댐퍼(B.D.D) 체결
+3) STEP 3 (덕트 누기시험): 연기발생기 및 차압계를 이용하여 허용 누기량(클래스 3 이하) 만족 여부 정밀 측정</t>
         </is>
       </c>
       <c r="L16" s="156" t="inlineStr">
@@ -12399,7 +12429,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" s="147">
+    <row r="17" ht="48" customHeight="1" s="147">
       <c r="A17" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12447,12 +12477,14 @@
       </c>
       <c r="J17" s="163" t="inlineStr">
         <is>
-          <t>도시철도건설규칙 및 화재안전기준(NFTC 501)에 따라 화재 시 발생하는 고온의 유독가스를 신속히 배출하기 위해, 250℃ 고온에서 1시간 이상 연속 운전이 가능한 공인 시험기관 인증 제연팬(Axial Fan), 내화 풍도, 1.5mm 아연도 강판 덕트 및 불연 내열 캔버스를 완벽 시공한다.</t>
+          <t>KFI 공인 250℃ 1시간 연속운전 고내열 제연팬 및 1.5mm 내화풍도 시공으로 화재 유독가스 배출</t>
         </is>
       </c>
       <c r="K17" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 250℃ 고내열 제연팬 사양 검토 및 반입 검수, STEP 2: 1.5mm 이상 고강도 제연 풍도 및 내진 지지대 시공 절차서 준수 시공</t>
+          <t>1) STEP 1 (고내열 제연팬 거치): KFI 250℃/1h 내열인증 H종 절연 제연팬을 방진 스프링 베이스 위에 수평 거치
+2) STEP 2 (내화 제연덕트 체결): 1.5mm 이상 두꺼운 강판 덕트에 1,000℃ 세라믹 불연 가스켓을 삽입하여 고장력 볼트 체결
+3) STEP 3 (내진 브레이싱 및 기동 시험): 종·횡방향 내진 버팀대(간격 9m/4.5m) 시공 후 화재 신호 수신 시 30초 내 기동 검증</t>
         </is>
       </c>
       <c r="L17" s="163" t="inlineStr">
@@ -12511,7 +12543,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1" s="147">
+    <row r="18" ht="48" customHeight="1" s="147">
       <c r="A18" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12559,12 +12591,14 @@
       </c>
       <c r="J18" s="156" t="inlineStr">
         <is>
-          <t>차량기지 종합검수고동 등 층고가 높고 체적이 거대한 대공간을 전면 냉난방하는 에너지 비효율성을 방지하기 위하여, 정비원이 실제 작업하는 핏트(Pit) 및 차체 검수 구역에 이동식 에어컨과 원적외선 전기히터를 국부 배치하고, 변전소 전기실에는 패키지 에어컨(PAC)을 정밀 가설한다.</t>
+          <t>대공간 검수고 작업자 중심 국부 냉난방(이동식 에어컨/원적외선) 및 변전소 전용 PAC 3대 배치</t>
         </is>
       </c>
       <c r="K18" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 대공간 국부 작업 구역 부하 분석 및 장비 선정, STEP 2: 변전실 패키지 에어컨(PAC) 3대 정합성 가설 절차서 준수 시공</t>
+          <t>1) STEP 1 (변전소 PAC 3대 설치): 변전소별 패키지 에어컨(PAC) 3대를 등간격 배치하고 R-410A 냉매배관 기밀시험(3.8MPa)
+2) STEP 2 (검수고 국부 냉난방 가설): 정비 피트 및 작업대 위치에 이동식 플렉시블 토출 에어컨과 고효율 원적외선 난방기 설치
+3) STEP 3 (시운전 및 온습도 측정): 실별 자동온도조절기(TC) 세팅 및 24시간 연속 운전을 통해 실온 ≤ 28℃ 유지 성능 검증</t>
         </is>
       </c>
       <c r="L18" s="156" t="inlineStr">
@@ -12623,7 +12657,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1" s="147">
+    <row r="19" ht="48" customHeight="1" s="147">
       <c r="A19" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12671,12 +12705,14 @@
       </c>
       <c r="J19" s="163" t="inlineStr">
         <is>
-          <t>중앙 기계실 냉동기, 열교환기, 펌프와 공조기를 연결하는 냉온수 및 냉각수 주배관에 대해 KCS 41 시방 기준에 따라 숙련된 유자격 용접사가 맞대기 아크용접 및 TIG 용접을 수행하고, 용접부 비파괴검사(RT ≥ 10%), 설계압력 1.5배 수압시험, 방청 도장 및 보온 단열재를 완벽 시공한다.</t>
+          <t>KSD 3562 탄소강관 맞대기 용접, 비파괴검사(RT ≥ 10%) 및 1.5MPa 수압시험을 통한 누수 Zero</t>
         </is>
       </c>
       <c r="K19" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 배관 절단 및 개선(Beveling) 가공, STEP 2: 가접 및 다층 맞대기 용접(WPS 준수) 절차서 준수 시공</t>
+          <t>1) STEP 1 (그루브 가공 및 맞대기 용접): 배관 단부 30~35° 베벨 가공 후 TIG 루트패스 및 아크 다층 맞대기 용접
+2) STEP 2 (방사선 비파괴검사 RT): 용접부의 10% 이상을 무작위 추출하여 방사선 투과 촬영(RT) 및 결함(기공, 슬래그) 100% 판독
+3) STEP 3 (1.5배 수압시험 및 보온): 설계압력 1.5배(1.5MPa) 60분 무누수 확인 후 난연 고무발포 단열재(40mm) 밀착 시공</t>
         </is>
       </c>
       <c r="L19" s="163" t="inlineStr">
@@ -12735,7 +12771,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1" s="147">
+    <row r="20" ht="48" customHeight="1" s="147">
       <c r="A20" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12783,12 +12819,14 @@
       </c>
       <c r="J20" s="156" t="inlineStr">
         <is>
-          <t>도시철도건설규칙 제67조에 따라 능동지하차도 트램 전용터널 통과 구간에 화재 발생 시 승객의 안전 피난 방향으로 연기 유동을 제어(임계풍속 ≥ 2.5m/s 확보)하는 제연설비, 건식 연결송수관 및 CFD 컴퓨터 화재 수치해석 시뮬레이션을 완벽 시공·검증한다.</t>
+          <t>지하차도 트램 전용터널 제연(Jet Fan 임계풍속 ≥ 2.5m/s) 및 50m 간격 건식 연결송수관 구축</t>
         </is>
       </c>
       <c r="K20" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 3D CFD 화재 및 피난 시뮬레이션 모델링, STEP 2: 터널 천장 제연팬(Jet Fan) 앵커링 및 내진 시공 절차서 준수 시공</t>
+          <t>1) STEP 1 (Jet Fan 천장 앵커링): 터널 천장부에 진동 감쇠 방진행거 및 고장력 케미컬 앵커로 Jet Fan 안전 체결
+2) STEP 2 (3D CFD 풍속 검증): 터널 화재 시뮬레이션 기반 임계풍속(2.5m/s) 도출 및 연기 역류(Backlayering) 차단 검증
+3) STEP 3 (건식 연결송수관 시공): 50m 간격 방수구함(D100 Sch40) 설치 및 2.0MPa 고압 수압시험을 통한 배관 내력 확인</t>
         </is>
       </c>
       <c r="L20" s="156" t="inlineStr">
@@ -12847,7 +12885,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1" s="147">
+    <row r="21" ht="48" customHeight="1" s="147">
       <c r="A21" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -12895,12 +12933,14 @@
       </c>
       <c r="J21" s="163" t="inlineStr">
         <is>
-          <t>지하 정거장 공조기계실 및 전기실에 대형 공기조화기(AHU)와 항온항습기(PAC)를 반입하여 기초 콘크리트 패드 위에 거치하고, 기계 가동 진동이 건축 구조물로 전파되는 것을 차단하는 방진스프링 마운트(정적변위 25~50mm), 드레인 트랩 및 수평도(±1mm)를 완벽 시공한다.</t>
+          <t>공조기 케이싱 수평 거치, 방진마운트(정적변위 ≥ 25mm) 진동 차단 및 딥 U-Trap 배수</t>
         </is>
       </c>
       <c r="K21" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 기초 콘크리트 패드 검측 및 기준선 마킹, STEP 2: AHU 분할 반입 및 블록 조립 결속 절차서 준수 시공</t>
+          <t>1) STEP 1 (기초 패드 및 방진마운트): 콘크리트 패드 위에 정적 변위 25mm 밀폐형 스프링 방진기 설치 및 수평 레벨링
+2) STEP 2 (불연 캔버스 연결): 송풍기 토출구와 덕트 사이에 실리콘 코팅 불연 캔버스를 주름 없이 견고히 체결
+3) STEP 3 (딥 U-Trap 드레인 시공): 흡입 부압에 견디도록 유효 봉수 100mm 이상의 드레인 트랩 시공 후 배수 통수시험</t>
         </is>
       </c>
       <c r="L21" s="163" t="inlineStr">
@@ -12959,7 +12999,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="147">
+    <row r="22" ht="48" customHeight="1" s="147">
       <c r="A22" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13007,12 +13047,14 @@
       </c>
       <c r="J22" s="156" t="inlineStr">
         <is>
-          <t>정거장 및 차량기지 관리동의 위생적인 음용수 및 급탕 공급을 위하여 KSD 3595(일반배관용 스테인리스 강관) 및 KSD 3576(배관용 스테인리스 강관)을 적용하고, 전용 전동 압착공구를 사용한 무용접 프레스 조인트 시공, 1.0MPa 수압시험, 배관 내부 염소 소독 세척을 완벽 수행한다.</t>
+          <t>STS304 강관 무용접 프레스 피팅 전동 압착, 1.0MPa 수압시험 및 위생 염소소독 완료</t>
         </is>
       </c>
       <c r="K22" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: STS 파이프 정밀 절단 및 단부 버(Burr) 제거, STEP 2: 피팅 삽입 깊이 마킹 및 전동 압착 체결 절차서 준수 시공</t>
+          <t>1) STEP 1 (관 절단 및 프레스 압착): 롤러 커터로 관 직각 절단, 리머 버 제거, EPDM 오링 삽입 후 전동 압착공구 체결
+2) STEP 2 (육각 게이지 전수 검측): 전용 판정 게이지(Go/No-Go)를 결합부에 밀착하여 압착 치수 정밀도 100% 전수 검사
+3) STEP 3 (수압시험 및 차아염소산 소독): 1.0MPa 60분 수압 무누수 확인 후 50ppm 염소수로 24시간 통수 살균 및 수질검사</t>
         </is>
       </c>
       <c r="L22" s="156" t="inlineStr">
@@ -13071,7 +13113,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1" s="147">
+    <row r="23" ht="48" customHeight="1" s="147">
       <c r="A23" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13119,12 +13161,14 @@
       </c>
       <c r="J23" s="163" t="inlineStr">
         <is>
-          <t>정거장 화장실 오수, 바닥 잡배수 및 지하 침출수를 신속하고 안전하게 배출하기 위해, 오배수 배관의 자연유하 구배(1/50~1/100)를 확보하고, 지하 최하층 집수조에 고효율 수중 카터/오수 배수펌프 2대(1대 상용, 1대 예비)와 수위센서 연동 자동 교번 운전 제어반을 완벽 시공한다.</t>
+          <t>오배수관 자연유하 구배(i ≥ 1/100) 유지 및 집수조 수중배수펌프 자동교번 4단 수위제어</t>
         </is>
       </c>
       <c r="K23" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 오배수 배관 라인 먹매김 및 구배 계획, STEP 2: 주철관/PVC관 포설 및 배관 행거 고정 절차서 준수 시공</t>
+          <t>1) STEP 1 (자연유하 구배 시공): 레이저 레벨기를 이용하여 오수관 1/100, 배수관 1/50 구배를 철저히 유지하며 배관 포설
+2) STEP 2 (수중펌프 자동교번 안착): 집수조 바닥에 상용 및 예비 수중펌프 2대를 자동탈착 가이드레일 방식으로 거치
+3) STEP 3 (4단 전극봉 수위 인터록): 정지(LWL), 교번기동(HWL), 동시기동(E-HWL), 고수위경보(Alarm) 4단 센서 작동 검증</t>
         </is>
       </c>
       <c r="L23" s="163" t="inlineStr">
@@ -13183,7 +13227,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1" s="147">
+    <row r="24" ht="48" customHeight="1" s="147">
       <c r="A24" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13231,12 +13275,14 @@
       </c>
       <c r="J24" s="156" t="inlineStr">
         <is>
-          <t>차량기지 중정비 공장(대차도장, 대차세척, 부품세척 등 23.314 ㎥/일), 경정비 공장(4.054 ㎥/일) 및 청소선에서 발생하는 고농도 유기계·유류 폐수를 법정 환경 기준 이하로 정화 배출하기 위해 기지 외곽에 연면적 90㎡ 규모의 전용 가설 폐수처리장, 유수분리기, 화학응집침전조 및 활성탄 흡착탑을 완벽 시공한다.</t>
+          <t>중정비·경정비 발생 오폐수(35㎥/일)의 유수분리, 화학응집, 활성탄 흡착 및 수질 TMS 원격 방류</t>
         </is>
       </c>
       <c r="K24" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 폐수처리장(90㎡) 토목 구조물 및 방수 검측, STEP 2: 유수분리기 및 원수 수집조 설비 설치 절차서 준수 시공</t>
+          <t>1) STEP 1 (유수분리기 설치): 차량 정비 폐수의 비중차 유분 분리조 및 오일 스키머 설치로 유분 농도 90% 이상 제거
+2) STEP 2 (응집 침전 및 가압부상): PAC 응집제 및 폴리머 자동 주입기를 통해 플록(Floc) 침전 및 슬러지 탈수기 케이크 처리
+3) STEP 3 (활성탄 흡착 및 TMS 연동): 2단 활성탄 흡착탑 정화 후 BOD/COD ≤ 20mg/L 수질 TMS 데이터 환경청 자동 전송</t>
         </is>
       </c>
       <c r="L24" s="156" t="inlineStr">
@@ -13295,7 +13341,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1" s="147">
+    <row r="25" ht="48" customHeight="1" s="147">
       <c r="A25" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13343,12 +13389,14 @@
       </c>
       <c r="J25" s="163" t="inlineStr">
         <is>
-          <t>동탄트램 차량의 청결 상태를 유지하기 위해 차량기지 청소선에 트램 전용 갠트리식 자동세척설비(차체 전·측·후면 브러시, 세제 분사 펌프, 린스 노즐, 윈드 블로워 송풍 건조기, 폐수 회수 집수 트렌치)를 시공하고, 열차 진입 감지 센서 연동 100% 자동 세척 시퀀스를 완성한다.</t>
+          <t>트램 전동차 청소선 세차 갠트리, EVA 무스크래치 브러시 및 세척수 85% 회수 재활용</t>
         </is>
       </c>
       <c r="K25" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 청소선 궤도 건축한계 대조 및 기초 앵커 시공, STEP 2: 세차기 메인 갠트리 프레임 및 브러시 조립 절차서 준수 시공</t>
+          <t>1) STEP 1 (세차 갠트리 프레임 가설): 청소선 궤도 상부에 고압 노즐 파이프 및 갠트리 구조물 용접 앵커링
+2) STEP 2 (EVA 브러시 및 약품 분사): 전동차 차체 도장 손상을 방지하는 초미세 발포 EVA 브러시 및 중성 세제 분사 노즐 세팅
+3) STEP 3 (세척수 회수 트렌치 통수): 하부 STS 그레이팅 트렌치를 통해 세척수 85% 이상 회수 및 순환 정화조 인입 검측</t>
         </is>
       </c>
       <c r="L25" s="163" t="inlineStr">
@@ -13407,7 +13455,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1" s="147">
+    <row r="26" ht="48" customHeight="1" s="147">
       <c r="A26" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13455,12 +13503,14 @@
       </c>
       <c r="J26" s="156" t="inlineStr">
         <is>
-          <t>차량기지 종합관리동 및 정거장 정화조 수조에서 발생하는 황화수소(H2S), 암모니아(NH3), 메탄(CH4) 등 유해·악취 가스가 지상 역사 및 근무 공간으로 확산되는 것을 원천 차단하기 위해, 정화조실 내부를 3종 음압으로 유지하는 내식성 FRP 탈취 덕트, 약액세정식 2단 탈취탑 및 복합가스 감지 센서를 시공한다.</t>
+          <t>정화조실 3종 음압(-20Pa) 유지 및 2단 약액세정탑(산/알칼리)+첨착활성탄 복합 탈취</t>
         </is>
       </c>
       <c r="K26" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 정화조실 음압 환기량 및 유해가스 농도 계산, STEP 2: 내식성 FRP 탈취 덕트 및 배기팬 가설 절차서 준수 시공</t>
+          <t>1) STEP 1 (음압 덕트 및 후드 설치): 정화조 발생원 상부에 내식성 FRP 배기 후드 및 전용 음압 배기팬(15~20회/h) 가설
+2) STEP 2 (2단 스크러버 약액 세정): 산(H2SO4) 및 알칼리(NaOH) 세정탑 순환 펌프와 노즐을 통해 황화수소(H2S) 99% 중화
+3) STEP 3 (첨착 활성탄 흡착 배출): 최종 첨착 활성탄 흡착탑을 거쳐 복합악취 희석배수 ≤ 500 이하 기준 충족 확인</t>
         </is>
       </c>
       <c r="L26" s="156" t="inlineStr">
@@ -13519,7 +13569,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1" s="147">
+    <row r="27" ht="48" customHeight="1" s="147">
       <c r="A27" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13567,12 +13617,14 @@
       </c>
       <c r="J27" s="163" t="inlineStr">
         <is>
-          <t>화재안전기술기준(NFTC 102) 및 시방서 개선 사항에 따라 일반인이 혼자서도 손쉽게 당겨서 방수할 수 있는 고성능 '호스릴 옥내소화전(STS304 외함, 25mm 고무호스 릴, 분말소화기 3.3kg 2대 내장형)'을 정거장 및 차량기지 전 구역에 보행거리 25m 이내로 배치하고, 방수압력(0.17~0.7MPa) 및 방수량(130L/min)을 완벽 시공한다.</t>
+          <t>STS304 호스릴 옥내소화전(보행거리 25m 이내, 방수압 0.17~0.7MPa) 1인 조작 화재 진압</t>
         </is>
       </c>
       <c r="K27" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소화전함 설치 위치 먹매김 및 배관 인입선 실측, STEP 2: 배관 가설 및 그루브 조인트(Grooved Joint) 체결 절차서 준수 시공</t>
+          <t>1) STEP 1 (STS304 소화전함 매립): 정거장 및 역사 벽체에 STS304 방청 소화전함을 수직·수평 정밀 매립
+2) STEP 2 (25m 호스릴 및 밸브 체결): 1인 전개 인장력 5kgf 이하의 원형 회전 드럼식 25m 경량 호스릴 및 감압 앵글밸브 설치
+3) STEP 3 (방수압력 및 방수량 실측): 피토게이지를 이용하여 노즐 방수압 0.17~0.7MPa 및 방수량 ≥ 130L/min 20분간 방수 실측</t>
         </is>
       </c>
       <c r="L27" s="163" t="inlineStr">
@@ -13631,7 +13683,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1" s="147">
+    <row r="28" ht="48" customHeight="1" s="147">
       <c r="A28" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13679,12 +13731,14 @@
       </c>
       <c r="J28" s="156" t="inlineStr">
         <is>
-          <t>화재안전기술기준(NFTC 103, 502) 개정 법령에 따라 과거 겸용으로 시공되던 '연결송수관설비'와 '스프링클러설비'의 수직 주배관 및 옥외 소방차 연결 송수구를 물리적으로 각각 100% 완전 분리 시공하여, 화재 시 소방차 고압 가압에 따른 스프링클러 배관 파손을 막고 소화 수압 안정성을 극대화한다.</t>
+          <t>개정 화재안전기준에 따른 연결송수관과 스프링클러설비의 주배관 및 옥외 송수구 완전 물리적 분리</t>
         </is>
       </c>
       <c r="K28" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 개정 화재안전기술기준 설계도서 대조 및 입상 경로 분리, STEP 2: 연결송수관 전용 고압 배관 시공 절차서 준수 시공</t>
+          <t>1) STEP 1 (독립 배관 라인 포설): 연결송수관(고압 Sch40)과 스프링클러 알람밸브 2차측 배관을 완전 독립 경로로 가설
+2) STEP 2 (쌍구형 송수구 분리 설치): 옥외 소방차 진입로에 연결송수관용 및 스프링클러용 쌍구형 송수구를 명판과 함께 분리 취부
+3) STEP 3 (2.0MPa 고압 내압시험): 소방차 직결 가압을 상정하여 2.0MPa 압력으로 30분간 내압시험을 실시해 관로 안전성 입증</t>
         </is>
       </c>
       <c r="L28" s="156" t="inlineStr">
@@ -13743,7 +13797,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1" s="147">
+    <row r="29" ht="48" customHeight="1" s="147">
       <c r="A29" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13791,12 +13845,14 @@
       </c>
       <c r="J29" s="163" t="inlineStr">
         <is>
-          <t>전기 스파크 및 과부하로 인한 전기화재 위험이 높은 차량기지 변전소, 트램 배터리 충전 전기실, 종합관리동 및 본선 31개소 정거장의 특고압/저압 수배전반 큐비클(Cubicle) 내부에 KFI 형식승인을 득한 소공간용 고체에어로졸 자동소화장치를 1:1 취부하여 판넬 내부 화재를 3초 이내에 국부 진압한다.</t>
+          <t>특고압/저압 수배전반 판넬 내부 KFI 인증 소공간 고체에어로졸 설치 및 3초 내 초기 진압</t>
         </is>
       </c>
       <c r="K29" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 수배전반 큐비클 체적(㎥) 및 소화약제량 산정, STEP 2: 고체에어로졸 소화장치 브라켓 고정 절차서 준수 시공</t>
+          <t>1) STEP 1 (큐비클 내부 브래킷 고정): 수배전반 상단 발화 예상 지점에 내진 브래킷을 이용하여 에어로졸 소화장치 취부
+2) STEP 2 (열감지선 및 기폭선 결선): 105℃ 정온식 열감지선을 판넬 내부 주요 부스바 주변에 포설하고 제어부 결선
+3) STEP 3 (ACB 차단기 인터록 연동): 화재 감지 및 소화기 기폭 신호 출력 즉시 주차단기(ACB)가 자동 트립되는 인터록 검증</t>
         </is>
       </c>
       <c r="L29" s="163" t="inlineStr">
@@ -13855,7 +13911,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1" s="147">
+    <row r="30" ht="48" customHeight="1" s="147">
       <c r="A30" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -13903,12 +13959,14 @@
       </c>
       <c r="J30" s="156" t="inlineStr">
         <is>
-          <t>차량기지 주변전소, 정거장 변전실 등 가스계 소화설비(HFC-125, Novec 1230 등)가 적용된 밀폐 방호구역에 소화가스 방출 시 순간적인 압력 상승으로 인한 방화벽체, 출입문 및 유리창의 파손을 방지하기 위하여, 설정 압력(150~300Pa) 이상에서 자동으로 개방되는 과압배출구(P.R.D, Pressure Relief Damper)를 벽체에 완벽 가설한다.</t>
+          <t>가스소화약제 방출 시 실내 과압(200Pa) 자동 해소 및 자중 폐쇄를 통한 10분 설계농도 유지</t>
         </is>
       </c>
       <c r="K30" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 가스 방출 압력 상승치 및 P.R.D 배출 면적 계산, STEP 2: 방화벽체 개구부 타공 및 STS 프레임 가설 절차서 준수 시공</t>
+          <t>1) STEP 1 (방화벽체 개구부 프레임 취부): 변전실 외벽 또는 복도측 방화벽체에 P.R.D 댐퍼 프레임 수평 매립 고정
+2) STEP 2 (카운터웨이트 개방압 세팅): 실내 압력이 200Pa에 도달할 때 블레이드가 정확히 열리도록 카운터웨이트 추 정밀 교정
+3) STEP 3 (자중 폐쇄 및 기밀도 검측): 압력 해소 후 중력으로 완벽히 닫혀 소화가스 누출(약제 설계농도 10분 유지) 방지 검증</t>
         </is>
       </c>
       <c r="L30" s="156" t="inlineStr">
@@ -13967,7 +14025,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1" s="147">
+    <row r="31" ht="48" customHeight="1" s="147">
       <c r="A31" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14015,12 +14073,14 @@
       </c>
       <c r="J31" s="163" t="inlineStr">
         <is>
-          <t>화재안전기술기준(NFTC 102, 103)에 따라 정거장 및 차량기지 지하 소방펌프실에 주펌프(전기모터 구동), 보조 충압펌프, 성능시험배관, 압력챔버(또는 전자식 압력스위치), 순환배관 및 릴리프밸브를 가설하고, 3대 필수 성능시험(체절운전 시험, 정격부하 시험, 150% 최대부하 시험)을 완벽 수행한다.</t>
+          <t>소방펌프실 주/충압펌프 거치 및 체절압력(≤140%), 정격(100%), 150% 부하(≥65%) 법정 성능시험</t>
         </is>
       </c>
       <c r="K31" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방펌프 콘크리트 기초 패드 및 방진가대 시공, STEP 2: 흡입·토출 배관, 플렉시블 조인트 및 밸브류 체결 절차서 준수 시공</t>
+          <t>1) STEP 1 (펌프 기초 및 방진가설): 콘크리트 패드 위에 다단원심 소방 주펌프 및 충압펌프 방진마운트 거치 및 축정렬
+2) STEP 2 (성능시험 배관 및 유량계): 주배관에서 분기된 오리피스 차압식 유량계 배관 및 순환배관 릴리프밸브 설치
+3) STEP 3 (3대 법정 성능시험 입회): 감리원 입회 하에 체절운전(정격 140% 이하), 100% 정격부하, 150% 피크부하 곡선 검증</t>
         </is>
       </c>
       <c r="L31" s="163" t="inlineStr">
@@ -14079,7 +14139,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1" s="147">
+    <row r="32" ht="48" customHeight="1" s="147">
       <c r="A32" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14127,12 +14187,14 @@
       </c>
       <c r="J32" s="156" t="inlineStr">
         <is>
-          <t>교통약자의 수직 이동권 및 환승 편의를 보장하기 위해 정거장 외부 환승 동선에 17인승/24인승 MRL(기계실 없는) 인승용 엘리베이터를 설치하고, 승강로 수직도(±5mm), 가이드레일 브라켓, 도어 다점 적외선 안전센서, 비상통화장치 및 한국승강기안전공단 완성검사를 100% 합격 완료한다.</t>
+          <t>정거장 MRL(기계실 없는) 인승용 승강기 설치 및 KoELSA 완성검사 필증 획득</t>
         </is>
       </c>
       <c r="K32" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 승강로 골조 치수, 피트 깊이 및 수직도 실측, STEP 2: 가이드레일 브라켓 및 T형 레일 조립 절차서 준수 시공</t>
+          <t>1) STEP 1 (승강로 수직도 및 레일 조립): 승강로 수직도(오차 ≤ ±5mm) 실측 후 13K 가이드레일 브래킷 앵커링 및 조립
+2) STEP 2 (PMSM 권상기 및 카 조립): PMSM 영구자석 기어리스 권상기 안착, 메인로프(안전율 ≥ 12) 텐션 조정 및 카 조립
+3) STEP 3 (KoELSA 법정 완성검사): 128채널 3D 도어센서, 정전 시 ARD 구출장치, 조속기 비상정지장치 실부하 시험 100% 합격</t>
         </is>
       </c>
       <c r="L32" s="156" t="inlineStr">
@@ -14191,7 +14253,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1" s="147">
+    <row r="33" ht="48" customHeight="1" s="147">
       <c r="A33" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14239,12 +14301,14 @@
       </c>
       <c r="J33" s="163" t="inlineStr">
         <is>
-          <t>차량기지 종합검수고동 내 무거운 트램 부품, 대차 예비품 및 정비 공구의 층간 수직 이동을 전담하기 위해 3~5ton급 대용량 '관통형(양방향 도어 개폐형) 화물용 엘리베이터'를 설치하고, 지게차 진입 충격에 견디는 바닥 하중 보강, 도어 씰(Sill) 보강 및 화물 전용 안전장치를 완벽 시공한다.</t>
+          <t>차량기지 종합검수고 관통형(양방향 도어) 3~5ton 화물용 승강기 가설 및 지게차 진입 바닥 보강</t>
         </is>
       </c>
       <c r="K33" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 대형 화물용 승강로 구조 및 지게차 동선 검토, STEP 2: 대형 H형강 카 프레임 및 중량 레일 가설 절차서 준수 시공</t>
+          <t>1) STEP 1 (중하중 승강로 구조 보강): 지게차(자중 4.5ton) 진입 하중을 견디도록 카 바닥 H형강 및 4.5T 체크플레이트 보강
+2) STEP 2 (관통형 양방향 도어 인터록): 1층 전면 도어와 2층 후면 도어가 동시 개방되지 않도록 안전 인터록 릴레이 구축
+3) STEP 3 (125% 과부하 하중시험): 정격 적재하중의 125%(6.25ton) 추를 탑재하여 권상 제동력 및 슬립 유무 정밀 안전검사</t>
         </is>
       </c>
       <c r="L33" s="163" t="inlineStr">
@@ -14303,7 +14367,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1" s="147">
+    <row r="34" ht="48" customHeight="1" s="147">
       <c r="A34" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14351,12 +14415,14 @@
       </c>
       <c r="J34" s="156" t="inlineStr">
         <is>
-          <t>정거장 및 차량기지 내 모든 기계설비(공조기, 환기팬, 펌프, 댐퍼, 밸브, 저수조, 전력계)의 실시간 원격 감시 및 에너지 최적 제어를 위해 직접디지털제어(DDC/IP DDC) 패널을 가설하고, 개방형 BACnet/Modbus 프로토콜 적용 및 메인 서버 장애 시 0초 무중단 자동 절환되는 Backup Server 이중화 시스템을 완벽 구축한다.</t>
+          <t>기계설비 직접디지털제어(IP DDC) 판넬 설치, BACnet 국제표준 통신 및 관제서버 무중단 이중화</t>
         </is>
       </c>
       <c r="K34" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 자동제어 I/O 포인트 일람표 및 통신 선로 설계 대조, STEP 2: 기계실 IP DDC 패널 가설 및 필드 센서/밸브 배선 절차서 준수 시공</t>
+          <t>1) STEP 1 (IP DDC 필드 제어반 결선): 기계실 및 공조실 DDC 판넬에 아날로그(AI/AO), 디지털(DI/DO) 센서·밸브 케이블 결선
+2) STEP 2 (BACnet 통신 루프 구축): 개방형 BACnet/IP 프로토콜을 적용하여 중앙 방재실 관제 컴퓨터와 실시간 데이터 통신 연동
+3) STEP 3 (서버 0초 이중화 절환 시험): 메인 관제 서버 강제 다운 시 대기 중인 백업 서버로 데이터 손실 없이 0초 절환 검증</t>
         </is>
       </c>
       <c r="L34" s="156" t="inlineStr">
@@ -14415,7 +14481,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1" s="147">
+    <row r="35" ht="48" customHeight="1" s="147">
       <c r="A35" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14463,12 +14529,14 @@
       </c>
       <c r="J35" s="163" t="inlineStr">
         <is>
-          <t>화재안전기술기준 및 철도 방재 매뉴얼에 따라 화재 발생 시 연기가 공조 덕트를 타고 다른 구역으로 확산되는 대형 참사를 막기 위해, 화재수신반 경보 발생 즉시 공조기·냉난방기 마그네틱 전원을 100% 강제 차단하고, 해당 제연구역의 제연팬을 비상 배연 모드로 가동하는 방재 인터록 실부하 시험을 수행한다.</t>
+          <t>화재 수신반 신호 수신 즉시 공조기 100% 강제 정지 및 제연팬 배연 모드 자동 인터록</t>
         </is>
       </c>
       <c r="K35" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 화재 연동 방재 매트릭스(Cause &amp; Effect) 수립, STEP 2: 공조기 MCC 정지 접점 및 제연팬 기동 결선 점검 절차서 준수 시공</t>
+          <t>1) STEP 1 (하드와이어드 인터록 회로 구성): 화재수신반 경보 접점을 공조기 MCC 조작전원 차단 계전기(B접점)와 직결
+2) STEP 2 (제연댐퍼 및 팬 시퀀스 연동): 화재 구역 제연 풍도 댐퍼가 완전 개방된 후 리미트 스위치 신호로 제연팬 자동 가동
+3) STEP 3 (실부하 화재 모의시험): 연기감지기 실발화 시험을 실시하여 3초 이내 공조기 정지 및 제연팬 정상 기동 확인</t>
         </is>
       </c>
       <c r="L35" s="163" t="inlineStr">
@@ -14527,7 +14595,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1" s="147">
+    <row r="36" ht="48" customHeight="1" s="147">
       <c r="A36" s="153" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14575,12 +14643,14 @@
       </c>
       <c r="J36" s="156" t="inlineStr">
         <is>
-          <t>공조 및 배관 시스템의 완성도를 입증하고 실내 쾌적 환경과 에너지를 최적화하기 위해, 국가공인 TAB(Testing, Adjusting, Balancing) 전문기관에 의뢰하여 정거장 및 차량기지 전 구역의 공조 덕트 풍량, 디퓨저 취출 기류, 냉온수 배관 유량 및 실내 소음·차압을 정밀 측정하고 설계치 대비 오차 ±10% 이내로 균일 밸런싱한다.</t>
+          <t>공조 덕트 풍량(오차 ±10% 이내) 및 수배관 유량 정밀 측정·조정(TAB)으로 쾌적성 확보</t>
         </is>
       </c>
       <c r="K36" s="156" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: TAB 사전 검토 및 측정 계획서 수립, STEP 2: 공조 덕트 주풍량 및 디퓨저 풍량 측정·조정 절차서 준수 시공</t>
+          <t>1) STEP 1 (공조 덕트 풍량 TAB): 피토관 및 플로우 후드를 이용하여 주덕트와 각 디퓨저 취출 풍량을 설계치 ±10%로 교정
+2) STEP 2 (수배관 유량 TAB): 초음파 비파괴 유량계로 냉온수 배관 순환 유량을 측정하고 밸런싱 밸브 차압(ΔP) 정밀 조정
+3) STEP 3 (소음 및 온습도 검증): 정거장 실내 소음(NC 35~40) 및 실별 온·습도 분포도를 24시간 연속 측정하여 TAB 성적서 발급</t>
         </is>
       </c>
       <c r="L36" s="156" t="inlineStr">
@@ -14639,7 +14709,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1" s="147">
+    <row r="37" ht="48" customHeight="1" s="147">
       <c r="A37" s="160" t="inlineStr">
         <is>
           <t>9000</t>
@@ -14687,12 +14757,14 @@
       </c>
       <c r="J37" s="163" t="inlineStr">
         <is>
-          <t>동탄트램 기계설비 및 소방공사의 최종 마무리를 위해 관할 소방서(화성소방서 등)의 엄격한 현장 실사를 통해 '소방시설 완공검사증명서(소방필증)'를 획득하고, 준공도면(As-Built), 장비 매뉴얼, 예비품 목록, 종합시운전 성적서를 완비하여 화성도시공사 기계·소방 운영유지관리팀에 무결점 종합 인수인계를 완료한다.</t>
+          <t>관할 소방서 완공검사필증 획득, As-Built 준공도서 편찬 및 운영사(화성도시공사) 무결점 인수인계</t>
         </is>
       </c>
       <c r="K37" s="163" t="inlineStr">
         <is>
-          <t>KCS 41 시방 기준 및 STEP 1: 소방시설 완공검사 신청서 제출 및 사전 자체 점검, STEP 2: 관할 소방서 합동 현장 실사 및 성능 시연 절차서 준수 시공</t>
+          <t>1) STEP 1 (관할 소방서 완공 실사): 소방감리원 및 소방관 합동 현장 실사를 통해 소화·경보·피난설비 전수 작동 검사
+2) STEP 2 (소방완공검사필증 수령): 지적사항 0건으로 소방시설 완공검사증명서(필증)를 정식 교부받아 법적 준공 완료
+3) STEP 3 (준공도서 및 운영자 교육): 3D As-Built 준공도면, 시운전 성적서, 2년분 예비품을 인계하고 운영팀 40시간 기술교육 이수</t>
         </is>
       </c>
       <c r="L37" s="163" t="inlineStr">

--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v8.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전기" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIDE" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기계" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="철도종합시운전" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'공정매뉴얼'!$A$3:$P$88</definedName>
@@ -818,7 +819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1290,6 +1291,39 @@
     <xf numFmtId="0" fontId="40" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -14828,6 +14862,3348 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="147" min="1" max="1"/>
+    <col width="10" customWidth="1" style="147" min="2" max="2"/>
+    <col width="18" customWidth="1" style="147" min="3" max="3"/>
+    <col width="12" customWidth="1" style="147" min="4" max="4"/>
+    <col width="10" customWidth="1" style="147" min="5" max="5"/>
+    <col width="10" customWidth="1" style="147" min="6" max="6"/>
+    <col width="30" customWidth="1" style="147" min="7" max="7"/>
+    <col width="12" customWidth="1" style="147" min="8" max="8"/>
+    <col width="14" customWidth="1" style="147" min="9" max="9"/>
+    <col width="38" customWidth="1" style="147" min="10" max="10"/>
+    <col width="54" customWidth="1" style="147" min="11" max="11"/>
+    <col width="30" customWidth="1" style="147" min="12" max="12"/>
+    <col width="36" customWidth="1" style="147" min="13" max="13"/>
+    <col width="24" customWidth="1" style="147" min="14" max="14"/>
+    <col width="36" customWidth="1" style="147" min="15" max="15"/>
+    <col width="24" customWidth="1" style="147" min="16" max="16"/>
+    <col width="36" customWidth="1" style="147" min="17" max="17"/>
+    <col width="24" customWidth="1" style="147" min="18" max="18"/>
+    <col width="16" customWidth="1" style="147" min="19" max="19"/>
+    <col width="32" customWidth="1" style="147" min="20" max="20"/>
+    <col width="24" customWidth="1" style="147" min="21" max="21"/>
+    <col width="30" customWidth="1" style="147" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="147">
+      <c r="A1" s="167" t="inlineStr">
+        <is>
+          <t>L2 코드</t>
+        </is>
+      </c>
+      <c r="B1" s="167" t="inlineStr">
+        <is>
+          <t>L3 코드</t>
+        </is>
+      </c>
+      <c r="C1" s="167" t="inlineStr">
+        <is>
+          <t>L3 대공종명</t>
+        </is>
+      </c>
+      <c r="D1" s="167" t="inlineStr">
+        <is>
+          <t>L4 코드</t>
+        </is>
+      </c>
+      <c r="E1" s="167" t="inlineStr">
+        <is>
+          <t>선행</t>
+        </is>
+      </c>
+      <c r="F1" s="167" t="inlineStr">
+        <is>
+          <t>후행</t>
+        </is>
+      </c>
+      <c r="G1" s="167" t="inlineStr">
+        <is>
+          <t>작업단위 (Level 4 Task/Activity)</t>
+        </is>
+      </c>
+      <c r="H1" s="167" t="inlineStr">
+        <is>
+          <t>일정 (D-Day)</t>
+        </is>
+      </c>
+      <c r="I1" s="167" t="inlineStr">
+        <is>
+          <t>주관</t>
+        </is>
+      </c>
+      <c r="J1" s="167" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="K1" s="167" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="L1" s="167" t="inlineStr">
+        <is>
+          <t>산출물(결과)</t>
+        </is>
+      </c>
+      <c r="M1" s="167" t="inlineStr">
+        <is>
+          <t>표준서 (Standard) 요약</t>
+        </is>
+      </c>
+      <c r="N1" s="167" t="inlineStr">
+        <is>
+          <t>표준서 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="O1" s="167" t="inlineStr">
+        <is>
+          <t>수행지침 (Guideline) 요약</t>
+        </is>
+      </c>
+      <c r="P1" s="167" t="inlineStr">
+        <is>
+          <t>수행지침 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="Q1" s="167" t="inlineStr">
+        <is>
+          <t>체크리스트 (Checklist) 요약</t>
+        </is>
+      </c>
+      <c r="R1" s="167" t="inlineStr">
+        <is>
+          <t>체크리스트 파일 (HTML)</t>
+        </is>
+      </c>
+      <c r="S1" s="167" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="T1" s="167" t="inlineStr">
+        <is>
+          <t>첨부서류 연계 상세 설계기준</t>
+        </is>
+      </c>
+      <c r="U1" s="167" t="inlineStr">
+        <is>
+          <t>집행단계 리스크 체크리스트</t>
+        </is>
+      </c>
+      <c r="V1" s="167" t="inlineStr">
+        <is>
+          <t>협력사 시공/공사관리 자문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" s="147">
+      <c r="A2" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C2" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D2" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-1</t>
+        </is>
+      </c>
+      <c r="E2" s="169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="G2" s="155" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토</t>
+        </is>
+      </c>
+      <c r="H2" s="169" t="inlineStr">
+        <is>
+          <t>D-60</t>
+        </is>
+      </c>
+      <c r="I2" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J2" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 분석 및 3단계 종합시험운행 추진체계 사전 검토</t>
+        </is>
+      </c>
+      <c r="K2" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 법정 기준 및 절차 분석 (철도안전법 제38조(종합시험운행) 및 국토교통부 고시 철도종합시험운행 시행지침의 단계별 필수 검증 항목을 분석합니다.)
+2) STEP 2: 시험운행 단계별(사전점검·시설물검증·영업시운전) 마일스톤 도출 (사전점검(60일), 시설물검증시험(30일), 영업시운전(30일)에 필요한 최소 시험기간 및 법정 선행조건을 수립합니다.)
+3) STEP 3: 철도종합시험운행 사전검토서 편찬 및 승인 (사업단 개통운영팀 주관으로 전 공종(토목, 궤도, 건축, 기계, 전기, 신호, 통신, 차량) 검토의견을 취합하여 사전검토서를 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L2" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M2" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전검토 (9000-9-1) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 철도종합시험운행 시행지침 분석 및 3단계 종합시험운행 추진체계 사전 검토을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N2" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\1_철도종합시험운행 사전검토\표준서\1_철도종합시험운행 사전검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O2" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 법정 기준 및 절차 분석
+2) STEP 2: 시험운행 단계별(사전점검·시설물검증·영업시운전) 마일스톤 도출</t>
+        </is>
+      </c>
+      <c r="P2" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\1_철도종합시험운행 사전검토\수행지침\1_철도종합시험운행 사전검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q2" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 시행지침 검토 시방 및 국토교통부 고시 기준 전 조항 분석 기준을 100% 충족하였는가?
+2) 개통 목표일 역산정 공정 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R2" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\1_철도종합시험운행 사전검토\체크리스트\1_철도종합시험운행 사전검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S2" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T2" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U2" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V2" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" s="147">
+      <c r="A3" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B3" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C3" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D3" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="E3" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-1</t>
+        </is>
+      </c>
+      <c r="F3" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="G3" s="162" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 회의</t>
+        </is>
+      </c>
+      <c r="H3" s="174" t="inlineStr">
+        <is>
+          <t>D-50</t>
+        </is>
+      </c>
+      <c r="I3" s="174" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J3" s="163" t="inlineStr">
+        <is>
+          <t>사업단·감리단·협력사 합동 사전검토 회의 및 SOP 일정계획 상호 검토</t>
+        </is>
+      </c>
+      <c r="K3" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 공종 책임자 합동 사전검토 회의 소집 (사업단 개통운영팀 주관으로 토목, 궤도, 시스템, 차량 등 전 공종 감리원 및 현장소장 합동회의를 개최합니다.)
+2) STEP 2: 분야별 잔여 공종 및 시운전 간섭 요소 검토 (전기 가압, 통신망 개통, 신호 연동시험 등 시운전 선행 필수 공종의 완료 시점을 1:1 대조합니다.)
+3) STEP 3: 사전검토 회의록 작성 및 이행 확약 (도출된 120개 필수 점검항목과 일정 조정안을 회의록에 명시하고 참석자 전원 서명 날인하여 배포합니다.)</t>
+        </is>
+      </c>
+      <c r="L3" s="163" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전검토 회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M3" s="163" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전검토 회의 (9000-9-2) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사업단·감리단·협력사 합동 사전검토 회의 및 SOP 일정계획 상호 검토을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N3" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\2_철도종합시험운행 사전검토 회의\표준서\2_철도종합시험운행 사전검토 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O3" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 공종 책임자 합동 사전검토 회의 소집
+2) STEP 2: 분야별 잔여 공종 및 시운전 간섭 요소 검토</t>
+        </is>
+      </c>
+      <c r="P3" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\2_철도종합시험운행 사전검토 회의\수행지침\2_철도종합시험운행 사전검토 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="163" t="inlineStr">
+        <is>
+          <t>1) SOP 일정표 상호 검토 시방 및 공종별 준공 일정과 시운전 착수일 대조 기준을 100% 충족하였는가?
+2) 분야별 책임분계점 확정 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R3" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\2_철도종합시험운행 사전검토 회의\체크리스트\2_철도종합시험운행 사전검토 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S3" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T3" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U3" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V3" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" s="147">
+      <c r="A4" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B4" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C4" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D4" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="E4" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-2</t>
+        </is>
+      </c>
+      <c r="F4" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="G4" s="155" t="inlineStr">
+        <is>
+          <t>토목·궤도 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H4" s="169" t="inlineStr">
+        <is>
+          <t>D-40</t>
+        </is>
+      </c>
+      <c r="I4" s="169" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J4" s="156" t="inlineStr">
+        <is>
+          <t>노반·궤도·분기기 시공 상태 검증 및 신호설비 설치 사전 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="K4" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 매립형 궤도 기하구조 정밀 실측 데이터 검토 (트램 본선 34.4km 전 구간의 궤간(1,435mm), 수평, 고저, 평면성 및 유간 측정 데이터를 정밀 검증합니다.)
+2) STEP 2: 선로전환기(143개소) 및 신호 검지선 인터페이스 확인 (궤도 도상 타설부와 신호 선로전환기 모터/로드 결합부의 기계적 인터페이스를 검토합니다.)
+3) STEP 3: 토목·궤도 인터페이스 관리대장 확정 (승강장 연단과 트램 차량 발판 간격(50mm 이내) 및 건축한계 침범 여부를 최종 확인 후 관리대장을 작성합니다.)</t>
+        </is>
+      </c>
+      <c r="L4" s="156" t="inlineStr">
+        <is>
+          <t>토목·궤도 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M4" s="156" t="inlineStr">
+        <is>
+          <t>1) 토목·궤도 인터페이스 협의 (9000-9-3) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 노반·궤도·분기기 시공 상태 검증 및 신호설비 설치 사전 인터페이스 협의을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N4" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\3_토목·궤도 인터페이스 협의\표준서\3_토목·궤도 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O4" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 매립형 궤도 기하구조 정밀 실측 데이터 검토
+2) STEP 2: 선로전환기(143개소) 및 신호 검지선 인터페이스 확인</t>
+        </is>
+      </c>
+      <c r="P4" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\3_토목·궤도 인터페이스 협의\수행지침\3_토목·궤도 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="156" t="inlineStr">
+        <is>
+          <t>1) 궤도 단면 및 궤간 검측 시방 및 궤간 1,435mm ±2mm 이내 확인 기준을 100% 충족하였는가?
+2) 선로전환기 취부부 검토 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R4" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\3_토목·궤도 인터페이스 협의\체크리스트\3_토목·궤도 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S4" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T4" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U4" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V4" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" s="147">
+      <c r="A5" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B5" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C5" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D5" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="E5" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-3</t>
+        </is>
+      </c>
+      <c r="F5" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="G5" s="162" t="inlineStr">
+        <is>
+          <t>전기·통신·신호·차량 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H5" s="174" t="inlineStr">
+        <is>
+          <t>D-35</t>
+        </is>
+      </c>
+      <c r="I5" s="174" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J5" s="163" t="inlineStr">
+        <is>
+          <t>급전·LTE-R·T-ATP/ATO·차량 간 E&amp;M 복합 시스템 연동 인터페이스 조율</t>
+        </is>
+      </c>
+      <c r="K5" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전기 급전 및 배터리 급속충전 인터페이스 검토 (정거장 상부 강체 급속충전 아암(Arm)과 트램 차량 집전장치(Pantograph) 간의 접촉 압력 및 위치 정합성을 확인합니다.)
+2) STEP 2: LTE-R 통신망 및 신호 T-ATP/ATO 데이터 인터페이스 검증 (차상 단말장치(OBCU)와 지상 무선 기지국(DU/RU) 간의 무선 패킷 손실률(≤ 1%) 및 지연시간을 검증합니다.)
+3) STEP 3: PSD(스크린도어) ↔ 차량 도어 연동 시스템 확정 (트램 정위치 정차(오차 ±300mm 이내) 시 차량 도어와 승강장 PSD가 100% 동기화되어 개폐되는 인터페이스를 승인합니다.)</t>
+        </is>
+      </c>
+      <c r="L5" s="163" t="inlineStr">
+        <is>
+          <t>전기·통신·신호·차량 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M5" s="163" t="inlineStr">
+        <is>
+          <t>1) 전기·통신·신호·차량 인터페이스 협의 (9000-9-4) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 급전·LTE-R·T-ATP/ATO·차량 간 E&amp;M 복합 시스템 연동 인터페이스 조율을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N5" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\표준서\4_전기·통신·신호·차량 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O5" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전기 급전 및 배터리 급속충전 인터페이스 검토
+2) STEP 2: LTE-R 통신망 및 신호 T-ATP/ATO 데이터 인터페이스 검증</t>
+        </is>
+      </c>
+      <c r="P5" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\수행지침\4_전기·통신·신호·차량 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="163" t="inlineStr">
+        <is>
+          <t>1) 급속충전 시스템 연동 시방 및 정거장 강체 가선 및 집전장치 대조 기준을 100% 충족하였는가?
+2) LTE-R 무선 데이터 연동 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R5" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\4_전기·통신·신호·차량 인터페이스 협의\체크리스트\4_전기·통신·신호·차량 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S5" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T5" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U5" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V5" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="147">
+      <c r="A6" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B6" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C6" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D6" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="E6" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-4</t>
+        </is>
+      </c>
+      <c r="F6" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="G6" s="155" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의</t>
+        </is>
+      </c>
+      <c r="H6" s="169" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="I6" s="169" t="inlineStr">
+        <is>
+          <t>시스템팀</t>
+        </is>
+      </c>
+      <c r="J6" s="156" t="inlineStr">
+        <is>
+          <t>종합관제센터(OCC)·화성도시공사 운영사 요구사항 사전 반영 및 과업범위 최적화</t>
+        </is>
+      </c>
+      <c r="K6" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 종합관제센터 관제 설비 및 원격 감시 체계 검토 (종합관제센터 중앙 컴퓨터에 표출되는 트램 열차 위치, 변전소 전력 상태, 정거장 환기/승강기 상태 모니터링 화면을 검증합니다.)
+2) STEP 2: 화성도시공사 운영사 요구사항 수렴 및 기능 최적화 (운영 및 유지보수자 편의 향상을 위한 관제 화면 기능 추가/삭제 사항을 협의하고 불필요한 과업을 조정합니다.)
+3) STEP 3: 관제 및 운영 인터페이스 관리대장 승인 (사업단, 관제 소프트웨어 공급사, 화성도시공사 3자 서명 날인을 완료하고 시운전 연동 프로토콜을 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L6" s="156" t="inlineStr">
+        <is>
+          <t>관제 및 운영사 인터페이스 협의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M6" s="156" t="inlineStr">
+        <is>
+          <t>1) 관제 및 운영사 인터페이스 협의 (9000-9-5) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 종합관제센터(OCC)·화성도시공사 운영사 요구사항 사전 반영 및 과업범위 최적화을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N6" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\표준서\5_관제 및 운영사 인터페이스 협의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O6" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 종합관제센터 관제 설비 및 원격 감시 체계 검토
+2) STEP 2: 화성도시공사 운영사 요구사항 수렴 및 기능 최적화</t>
+        </is>
+      </c>
+      <c r="P6" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\수행지침\5_관제 및 운영사 인터페이스 협의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="156" t="inlineStr">
+        <is>
+          <t>1) 종합관제 SCADA 화면 검토 시방 및 전력/신호/설비 관제 화면 검증 기준을 100% 충족하였는가?
+2) 사령-현장 비상통신 라인 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R6" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\5_관제 및 운영사 인터페이스 협의\체크리스트\5_관제 및 운영사 인터페이스 협의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S6" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T6" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U6" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V6" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="147">
+      <c r="A7" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B7" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C7" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D7" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="E7" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-5</t>
+        </is>
+      </c>
+      <c r="F7" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="G7" s="162" t="inlineStr">
+        <is>
+          <t>인력·시험장비 투입계획 수립</t>
+        </is>
+      </c>
+      <c r="H7" s="174" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="I7" s="174" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J7" s="163" t="inlineStr">
+        <is>
+          <t>시험운전반, 유관기관 합동 점검단 인력 배치 및 공인 시험 계측기 확보</t>
+        </is>
+      </c>
+      <c r="K7" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 5대 전문 시험운전반 조직 체계 수립 (총괄관리반, 시설검증반(토목/궤도/건축), 시스템검증반(전기/신호/통신), 차량검증반, 안전비상대응반을 편성합니다.)
+2) STEP 2: 공인 교정 시험 계측기 및 검측 장비 확보 (트램 궤도 기하구조 검측기, 레이저 트랙게이지, 전력 분석계, LTE-R 무선 전계강도 측정기의 공인 교정 유효기간을 확인합니다.)
+3) STEP 3: 인력·시험장비 종합 투입계획서 감리 승인 (시운전 기간 동안의 일일 투입 공수, 장비 가동 계획 및 비상주기 장소를 명시한 계획서를 최종 확정합니다.)</t>
+        </is>
+      </c>
+      <c r="L7" s="163" t="inlineStr">
+        <is>
+          <t>인력·시험장비 투입계획 수립 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M7" s="163" t="inlineStr">
+        <is>
+          <t>1) 인력·시험장비 투입계획 수립 (9000-9-6) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시험운전반, 유관기관 합동 점검단 인력 배치 및 공인 시험 계측기 확보을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N7" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\6_인력·시험장비 투입계획 수립\표준서\6_인력·시험장비 투입계획 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O7" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 5대 전문 시험운전반 조직 체계 수립
+2) STEP 2: 공인 교정 시험 계측기 및 검측 장비 확보</t>
+        </is>
+      </c>
+      <c r="P7" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\6_인력·시험장비 투입계획 수립\수행지침\6_인력·시험장비 투입계획 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="163" t="inlineStr">
+        <is>
+          <t>1) 시험운전반 조직 구성표 시방 및 5개 분야 45명 전담 인력 편성 기준을 100% 충족하였는가?
+2) 시험 계측장비 목록 확정 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R7" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\6_인력·시험장비 투입계획 수립\체크리스트\6_인력·시험장비 투입계획 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S7" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T7" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U7" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V7" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="147">
+      <c r="A8" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B8" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C8" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D8" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="E8" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-6</t>
+        </is>
+      </c>
+      <c r="F8" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="G8" s="155" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전 협의사항(TS) 도출</t>
+        </is>
+      </c>
+      <c r="H8" s="169" t="inlineStr">
+        <is>
+          <t>D-25</t>
+        </is>
+      </c>
+      <c r="I8" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J8" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS) 사전 점검 항목 및 기술기준 적합성 쟁점 선제적 도출</t>
+        </is>
+      </c>
+      <c r="K8" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 도시철도건설규칙 및 철도시설 기술기준 전 조항 대조 (도시철도건설규칙 제67조(방재), 제32조(궤도), 제40조(전차선로) 등 동탄트램 해당 조항의 기술적 만족 여부를 전수 점검합니다.)
+2) STEP 2: 한국교통안전공단(TS) 주요 심사 지적사항 사전 스크리닝 (트램 승강장 연단 간격, 배터리 충전구 안전 인터록, 교차로 우선신호 연동 오류 등 예상 지적 45개 항목을 추출합니다.)
+3) STEP 3: TS 사전협의 대상 목록 보고서 완성 (사전컨설팅 회의에서 질의할 항목 및 기술 승인 요청 리스트를 정리하여 개통운영팀장 승인을 득합니다.)</t>
+        </is>
+      </c>
+      <c r="L8" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 사전 협의사항(TS) 도출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M8" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 사전 협의사항(TS) 도출 (9000-9-7) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 한국교통안전공단(TS) 사전 점검 항목 및 기술기준 적합성 쟁점 선제적 도출을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N8" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\표준서\7_철도종합시험운행 사전 협의사항(TS) 도출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O8" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 도시철도건설규칙 및 철도시설 기술기준 전 조항 대조
+2) STEP 2: 한국교통안전공단(TS) 주요 심사 지적사항 사전 스크리닝</t>
+        </is>
+      </c>
+      <c r="P8" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\수행지침\7_철도종합시험운행 사전 협의사항(TS) 도출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도시설 기술기준 매핑 시방 및 도시철도건설규칙 80개 조항 분석 기준을 100% 충족하였는가?
+2) TS 지적 예상 항목 검토 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R8" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\7_철도종합시험운행 사전 협의사항(TS) 도출\체크리스트\7_철도종합시험운행 사전 협의사항(TS) 도출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S8" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T8" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U8" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V8" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="147">
+      <c r="A9" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B9" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C9" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D9" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="E9" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-7</t>
+        </is>
+      </c>
+      <c r="F9" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="G9" s="162" t="inlineStr">
+        <is>
+          <t>착수 전 전공종 합동회의</t>
+        </is>
+      </c>
+      <c r="H9" s="174" t="inlineStr">
+        <is>
+          <t>D-20</t>
+        </is>
+      </c>
+      <c r="I9" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J9" s="163" t="inlineStr">
+        <is>
+          <t>8대 전 공종 단독·연동시험 결과보고서 검증 및 시운전 전제조건 100% 충족 확인</t>
+        </is>
+      </c>
+      <c r="K9" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 8대 공종별 단독·공종시험 결과보고서 전수 취합 (토목(평판재하), 궤도(기하구조), 기계(환기/소화수압), 전기(절연저항/가압), 신호(연동표검사), 통신(LTE-R 통화품질) 성적서를 심사합니다.)
+2) STEP 2: 법정 검사 필증 및 사전 승인 서류 확인 (전기안전공사 사용전검사 필증, 소방완공검사 필증, 승강기 완성검사 필증의 정식 수령 상태를 대조합니다.)
+3) STEP 3: 착수 전 합동회의 개최 및 시운전 개시 선언 (발주처, 사업단, 감리단, 운영사 전원 합의 하에 '철도종합시험운행 착수 전제조건 100% 충족'을 선언하고 회의록을 체결합니다.)</t>
+        </is>
+      </c>
+      <c r="L9" s="163" t="inlineStr">
+        <is>
+          <t>착수 전 전공종 합동회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M9" s="163" t="inlineStr">
+        <is>
+          <t>1) 착수 전 전공종 합동회의 (9000-9-8) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 8대 전 공종 단독·연동시험 결과보고서 검증 및 시운전 전제조건 100% 충족 확인을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N9" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\표준서\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O9" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 8대 공종별 단독·공종시험 결과보고서 전수 취합
+2) STEP 2: 법정 검사 필증 및 사전 승인 서류 확인</t>
+        </is>
+      </c>
+      <c r="P9" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\수행지침\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="163" t="inlineStr">
+        <is>
+          <t>1) 8대 공종 시험성적서 검토 시방 및 노반 다짐, 궤도 기하, 변전소 가압 기준을 100% 충족하였는가?
+2) 신호/통신 연동시험 검증 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R9" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증\체크리스트\8_착수 전 전공종 합동회의 및 공종별시험 완료 검증_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S9" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T9" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U9" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V9" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="147">
+      <c r="A10" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B10" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C10" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D10" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="E10" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-8</t>
+        </is>
+      </c>
+      <c r="F10" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="G10" s="155" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합계획서 수립</t>
+        </is>
+      </c>
+      <c r="H10" s="169" t="inlineStr">
+        <is>
+          <t>D+0</t>
+        </is>
+      </c>
+      <c r="I10" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J10" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 표준운영절차(SOP) 및 사전점검·시설물검증·영업시운전 종합계획서 편찬</t>
+        </is>
+      </c>
+      <c r="K10" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 종합계획서(SOP) 기본 골격 수립 (동탄트램 사업 개요, 시험운행 목적, 추진 기간, 분야별 시험 조직도 및 R&amp;R을 명확히 규정합니다.)
+2) STEP 2: 단계별 세부 시험계획서(사전점검/시설물검증/영업시운전) 작성 (사전점검 12개 분야 체크리스트 및 현장 확인 항목을 편찬합니다.)
+3) STEP 3: 책임감리원 검토의견서 첨부 및 종합계획서 승인 (각 분야 책임감리원의 기술 검토 서명을 완료하고 총괄사업단장의 최종 승인을 득합니다.)</t>
+        </is>
+      </c>
+      <c r="L10" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합계획서 수립 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M10" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 종합계획서 수립 (9000-9-9) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 철도종합시험운행 표준운영절차(SOP) 및 사전점검·시설물검증·영업시운전 종합계획서 편찬을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N10" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\표준서\9_철도종합시험운행 종합계획서(SOP) 수립_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O10" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 종합계획서(SOP) 기본 골격 수립
+2) STEP 2: 단계별 세부 시험계획서(사전점검/시설물검증/영업시운전) 작성</t>
+        </is>
+      </c>
+      <c r="P10" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\수행지침\9_철도종합시험운행 종합계획서(SOP) 수립_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="156" t="inlineStr">
+        <is>
+          <t>1) 종합계획서(SOP) 본안 작성 시방 및 개요, 조직, 안전관리, 세부일정 기준을 100% 충족하였는가?
+2) 사전점검 계획서 수립 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R10" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\9_철도종합시험운행 종합계획서(SOP) 수립\체크리스트\9_철도종합시험운행 종합계획서(SOP) 수립_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S10" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T10" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U10" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V10" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="147">
+      <c r="A11" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B11" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C11" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D11" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="E11" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-9</t>
+        </is>
+      </c>
+      <c r="F11" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="G11" s="162" t="inlineStr">
+        <is>
+          <t>TS 사전컨설팅 회의</t>
+        </is>
+      </c>
+      <c r="H11" s="174" t="inlineStr">
+        <is>
+          <t>D+30</t>
+        </is>
+      </c>
+      <c r="I11" s="174" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J11" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS) 합동 사전컨설팅 회의를 통한 계획서 보완 및 적합성 검증</t>
+        </is>
+      </c>
+      <c r="K11" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 한국교통안전공단(TS) 사전컨설팅 안건 상정 (종합시험운행 계획서 초안, 현장 공정 실적, 안전관리계획서 및 공종별 시험결과 요약본을 TS에 제출합니다.)
+2) STEP 2: TS 전문위원단 합동 대면 심의 회의 진행 (동탄트램 무가선 배터리 충전 안전성, 교차로 신호 우선권, 역사 승하차 안전 발판 등 특수 검증 항목을 집중 협의합니다.)
+3) STEP 3: 컨설팅 지적사항 보완 조치 및 최종본 확정 (TS 검토의견서에 명시된 권고 및 보완 사항을 계획서에 100% 반영하여 정식 제출용 최종안을 완성합니다.)</t>
+        </is>
+      </c>
+      <c r="L11" s="163" t="inlineStr">
+        <is>
+          <t>TS 사전컨설팅 회의 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M11" s="163" t="inlineStr">
+        <is>
+          <t>1) TS 사전컨설팅 회의 (9000-9-10) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 한국교통안전공단(TS) 합동 사전컨설팅 회의를 통한 계획서 보완 및 적합성 검증을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N11" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\표준서\10_계획서 제출 전 TS 사전컨설팅 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O11" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 한국교통안전공단(TS) 사전컨설팅 안건 상정
+2) STEP 2: TS 전문위원단 합동 대면 심의 회의 진행</t>
+        </is>
+      </c>
+      <c r="P11" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\수행지침\10_계획서 제출 전 TS 사전컨설팅 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="163" t="inlineStr">
+        <is>
+          <t>1) 사전컨설팅 신청서 제출 시방 및 종합계획서 초안 및 첨부자료 기준을 100% 충족하였는가?
+2) TS 합동 컨설팅 회의 개최 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R11" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\10_계획서 제출 전 TS 사전컨설팅 회의\체크리스트\10_계획서 제출 전 TS 사전컨설팅 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S11" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T11" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U11" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V11" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="147">
+      <c r="A12" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B12" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C12" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D12" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="E12" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-10</t>
+        </is>
+      </c>
+      <c r="F12" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="G12" s="155" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 연간계획 수립/제출</t>
+        </is>
+      </c>
+      <c r="H12" s="169" t="inlineStr">
+        <is>
+          <t>D+60</t>
+        </is>
+      </c>
+      <c r="I12" s="169" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J12" s="156" t="inlineStr">
+        <is>
+          <t>국토교통부 및 한국교통안전공단(TS)에 철도종합시험운행 계획서 정식 접수 및 승인 득</t>
+        </is>
+      </c>
+      <c r="K12" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 법정 제출 서류 편철 및 사업단장 결재 (철도종합시험운행 계획서 본안 3부, 사전점검 점검표, 안전관리계획서, 공종별 시험결과보고서를 편철합니다.)
+2) STEP 2: 국토교통부 및 TS 정식 공문 접수 (전자문서유통시스템을 통해 국토교통부(철도운행안전과) 및 한국교통안전공단(철도안전처)에 정식 접수합니다.)
+3) STEP 3: 심사 대응 및 국토부 승인 공문 접수 (TS 서류 심사관의 질의에 대한 기술적 근거를 제출하고, 국토교통부 장관의 '철도종합시험운행 계획 승인' 공문을 접수합니다.)</t>
+        </is>
+      </c>
+      <c r="L12" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 연간계획 수립/제출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M12" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 연간계획 수립/제출 (9000-9-11) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 국토교통부 및 한국교통안전공단(TS)에 철도종합시험운행 계획서 정식 접수 및 승인 득을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N12" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\표준서\11_철도종합시험운행 연간계획 수립 및 TS 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O12" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 법정 제출 서류 편철 및 사업단장 결재
+2) STEP 2: 국토교통부 및 TS 정식 공문 접수</t>
+        </is>
+      </c>
+      <c r="P12" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\수행지침\11_철도종합시험운행 연간계획 수립 및 TS 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 계획서 공문 발송 시방 및 국토교통부 철도안전정책과 기준을 100% 충족하였는가?
+2) 한국교통안전공단 서류 심사 대응 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R12" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\11_철도종합시험운행 연간계획 수립 및 TS 제출\체크리스트\11_철도종합시험운행 연간계획 수립 및 TS 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S12" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T12" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U12" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V12" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="147">
+      <c r="A13" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C13" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="E13" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-11</t>
+        </is>
+      </c>
+      <c r="F13" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="G13" s="162" t="inlineStr">
+        <is>
+          <t>안전관리계획서 수립 및 비상대응체계</t>
+        </is>
+      </c>
+      <c r="H13" s="174" t="inlineStr">
+        <is>
+          <t>D+80</t>
+        </is>
+      </c>
+      <c r="I13" s="174" t="inlineStr">
+        <is>
+          <t>안전품질팀</t>
+        </is>
+      </c>
+      <c r="J13" s="163" t="inlineStr">
+        <is>
+          <t>시운전 전 구간 선로 출입통제, 시험열차 안전통제관 탑승 및 관할 소방·경찰 비상연락망</t>
+        </is>
+      </c>
+      <c r="K13" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 안전관리계획서 수립 및 위험성평가 (시운전 구간 내 작업자 안전, 감전 방지, 열차 접촉 방지, 도로 교차로 보행자 통제 대책을 수립합니다.)
+2) STEP 2: 선로 출입 통제 시스템 및 안전통제관 지정 (선로 출입문 시건장치 및 출입대장을 운영하고, 시험열차 운행 시 안전통제관(2인 1조) 필수 탑승을 의무화합니다.)
+3) STEP 3: 비상연락망 구축 및 소방·경찰 합동 모의도상훈련 (화성소방서, 동탄경찰서, 응급의료센터와 24시간 비상 핫라인을 개통하고 가상 사고 대응 도상훈련을 실시합니다.)</t>
+        </is>
+      </c>
+      <c r="L13" s="163" t="inlineStr">
+        <is>
+          <t>안전관리계획서 수립 및 비상대응체계 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M13" s="163" t="inlineStr">
+        <is>
+          <t>1) 안전관리계획서 수립 및 비상대응체계 (9000-9-12) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시운전 전 구간 선로 출입통제, 시험열차 안전통제관 탑승 및 관할 소방·경찰 비상연락망을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N13" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\표준서\12_시험운행 안전관리계획서 수립 및 비상대응체계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O13" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도종합시험운행 안전관리계획서 수립 및 위험성평가
+2) STEP 2: 선로 출입 통제 시스템 및 안전통제관 지정</t>
+        </is>
+      </c>
+      <c r="P13" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\수행지침\12_시험운행 안전관리계획서 수립 및 비상대응체계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="163" t="inlineStr">
+        <is>
+          <t>1) 시운전 안전관리계획서 작성 시방 및 위험성평가 및 비상대응 매뉴얼 기준을 100% 충족하였는가?
+2) 선로 무단침입 방지 시설 점검 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R13" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\12_시험운행 안전관리계획서 수립 및 비상대응체계\체크리스트\12_시험운행 안전관리계획서 수립 및 비상대응체계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S13" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T13" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U13" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V13" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="147">
+      <c r="A14" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B14" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C14" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D14" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="E14" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-12</t>
+        </is>
+      </c>
+      <c r="F14" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="G14" s="155" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고</t>
+        </is>
+      </c>
+      <c r="H14" s="169" t="inlineStr">
+        <is>
+          <t>D+120</t>
+        </is>
+      </c>
+      <c r="I14" s="169" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J14" s="156" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고회(TS) 개최, 12개 분야별 정부 합동점검단 현장 정밀점검 개시</t>
+        </is>
+      </c>
+      <c r="K14" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 착수보고회(TS) 개최 및 현장 브리핑 (사업단 개통운영팀장이 TS 합동점검단에 동탄트램 시설 현황, 공종별 시험 결과 및 점검 지원 계획을 브리핑합니다.)
+2) STEP 2: 12개 분야별 합동점검단 현장 정밀 실사 수행 (토목/궤도(선로 침하, 유간), 건축(피난계단, 마감), 전기(가압, 접지), 신호(연동장치), 통신(LTE-R)을 도면과 1:1 대조합니다.)
+3) STEP 3: 일일 점검회의 및 지적사항 실시간 공유 (매일 점검 종료 후 현장 합동회의를 열어 도출된 지적사항을 즉시 공유하고 긴급 보완 지시서를 발행합니다.)</t>
+        </is>
+      </c>
+      <c r="L14" s="156" t="inlineStr">
+        <is>
+          <t>사전점검 착수보고 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M14" s="156" t="inlineStr">
+        <is>
+          <t>1) 사전점검 착수보고 (9000-9-13) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검 착수보고회(TS) 개최, 12개 분야별 정부 합동점검단 현장 정밀점검 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N14" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\표준서\13_사전점검 착수보고 및 분야별 점검단 가동_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O14" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 착수보고회(TS) 개최 및 현장 브리핑
+2) STEP 2: 12개 분야별 합동점검단 현장 정밀 실사 수행</t>
+        </is>
+      </c>
+      <c r="P14" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\수행지침\13_사전점검 착수보고 및 분야별 점검단 가동_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="156" t="inlineStr">
+        <is>
+          <t>1) 사전점검 착수회의 개최 시방 및 TS 주관 착수보고 및 점검일정 확정 기준을 100% 충족하였는가?
+2) 12개 분야 합동 현장 점검 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R14" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\13_사전점검 착수보고 및 분야별 점검단 가동\체크리스트\13_사전점검 착수보고 및 분야별 점검단 가동_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S14" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T14" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U14" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V14" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="147">
+      <c r="A15" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B15" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C15" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D15" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="E15" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-13</t>
+        </is>
+      </c>
+      <c r="F15" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="G15" s="162" t="inlineStr">
+        <is>
+          <t>철도시설 기술기준 검토 및 조치계획</t>
+        </is>
+      </c>
+      <c r="H15" s="174" t="inlineStr">
+        <is>
+          <t>D+130</t>
+        </is>
+      </c>
+      <c r="I15" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J15" s="163" t="inlineStr">
+        <is>
+          <t>도시철도건설규칙 전 조항 대조, 사전점검 지적사항 1:1 조치계획서 수립</t>
+        </is>
+      </c>
+      <c r="K15" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 지적사항 전수 등록 및 위험도 분류 (TS로부터 통보받은 지적사항을 '중대 결함', '일반 보완', '권고'로 분류하고 관리번호를 부여합니다.)
+2) STEP 2: 공학적 원인 분석 및 재시공/보강 기술 대책 수립 (해당 공종 협력사 및 설계사와 합동으로 문제 원인을 정밀 분석하고, 기술기준을 충족하는 상세 도면 및 시방을 작성합니다.)
+3) STEP 3: 사전점검 지적사항 조치계획서 편찬 및 감리 승인 (조치 기한(D+175 이전 완료)을 명시한 조치계획서를 작성하여 책임감리단 서명을 득하고 TS에 제출합니다.)</t>
+        </is>
+      </c>
+      <c r="L15" s="163" t="inlineStr">
+        <is>
+          <t>철도시설 기술기준 검토 및 조치계획 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M15" s="163" t="inlineStr">
+        <is>
+          <t>1) 철도시설 기술기준 검토 및 조치계획 (9000-9-14) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 도시철도건설규칙 전 조항 대조, 사전점검 지적사항 1:1 조치계획서 수립을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N15" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\표준서\14_철도시설의 기술기준 검토 및 지적사항 조치계획_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O15" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 지적사항 전수 등록 및 위험도 분류
+2) STEP 2: 공학적 원인 분석 및 재시공/보강 기술 대책 수립</t>
+        </is>
+      </c>
+      <c r="P15" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\수행지침\14_철도시설의 기술기준 검토 및 지적사항 조치계획_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="163" t="inlineStr">
+        <is>
+          <t>1) 지적사항 목록 전수 분류 시방 및 구조안전, 전기절연, 신호인터록 등 기준을 100% 충족하였는가?
+2) 분야별 원인분석 및 보강안 설계 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R15" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\14_철도시설의 기술기준 검토 및 지적사항 조치계획\체크리스트\14_철도시설의 기술기준 검토 및 지적사항 조치계획_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S15" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T15" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U15" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V15" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="147">
+      <c r="A16" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B16" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C16" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D16" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="E16" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-14</t>
+        </is>
+      </c>
+      <c r="F16" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="G16" s="155" t="inlineStr">
+        <is>
+          <t>사전점검 보완조치 및 국토부 승인</t>
+        </is>
+      </c>
+      <c r="H16" s="169" t="inlineStr">
+        <is>
+          <t>D+175</t>
+        </is>
+      </c>
+      <c r="I16" s="169" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J16" s="156" t="inlineStr">
+        <is>
+          <t>지적사항 100% 현장 보강 조치 완료, 조치결과보고서 제출 및 국토교통부 적합 승인</t>
+        </is>
+      </c>
+      <c r="K16" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 분야별 사전점검 지적사항 현장 보강 공사 완료 (궤도 선형 교정, 정거장 마감 보완, 전기 절연 보강, 신호 연동 시퀀스 튜닝을 전수 완료합니다.)
+2) STEP 2: 책임감리원 전수 입회 검측 및 결과보고서 편찬 (지적 전·중·후 사진, 공인 시험성적서, 감리원 확인서를 편철한 조치결과보고서를 편찬합니다.)
+3) STEP 3: 국토교통부 및 TS 최종 심사 대응 및 승인 공문 접수 (국토부 철도운행안전과로부터 '철도시설의 기술기준 적합 및 시설물검증시험 착수 승인' 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L16" s="156" t="inlineStr">
+        <is>
+          <t>사전점검 보완조치 및 국토부 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M16" s="156" t="inlineStr">
+        <is>
+          <t>1) 사전점검 보완조치 및 국토부 승인 (9000-9-15) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 지적사항 100% 현장 보강 조치 완료, 조치결과보고서 제출 및 국토교통부 적합 승인을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N16" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\표준서\15_사전점검 보완조치 및 조치결과 국토부 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O16" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 분야별 사전점검 지적사항 현장 보강 공사 완료
+2) STEP 2: 책임감리원 전수 입회 검측 및 결과보고서 편찬</t>
+        </is>
+      </c>
+      <c r="P16" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\수행지침\15_사전점검 보완조치 및 조치결과 국토부 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="156" t="inlineStr">
+        <is>
+          <t>1) 현장 재시공 및 보강 공사 시방 및 설계 변경 및 현장 보강 완료 기준을 100% 충족하였는가?
+2) 감리단 합동 검측 및 사진대지 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R16" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\15_사전점검 보완조치 및 조치결과 국토부 승인\체크리스트\15_사전점검 보완조치 및 조치결과 국토부 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S16" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T16" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U16" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V16" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="147">
+      <c r="A17" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B17" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C17" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D17" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="E17" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-15</t>
+        </is>
+      </c>
+      <c r="F17" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="G17" s="162" t="inlineStr">
+        <is>
+          <t>사전점검 종결회의 및 결과보고서 승인</t>
+        </is>
+      </c>
+      <c r="H17" s="174" t="inlineStr">
+        <is>
+          <t>D+180</t>
+        </is>
+      </c>
+      <c r="I17" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J17" s="163" t="inlineStr">
+        <is>
+          <t>사전점검 종결보고회(TS) 개최 및 1단계 사전점검 공식 종결 선언</t>
+        </is>
+      </c>
+      <c r="K17" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 종결회의 안건 브리핑 및 조치 실적 보고 (지적사항 조치 결과 및 국토부 적합 승인 공문 내용을 TS 합동점검단에 종합 보고합니다.)
+2) STEP 2: 점검단 최종 의견 수렴 및 사전점검 합격 판정 (점검단 전원 일치로 '동탄트램 사전점검 합격 및 시설물검증시험 진입 적합'을 최종 판정합니다.)
+3) STEP 3: 사전점검 종결 서명 날인 및 다음 단계 선언 (사전점검 종합결과보고서에 서명하고, 2단계 시설물검증시험 공식 개시를 선포합니다.)</t>
+        </is>
+      </c>
+      <c r="L17" s="163" t="inlineStr">
+        <is>
+          <t>사전점검 종결회의 및 결과보고서 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M17" s="163" t="inlineStr">
+        <is>
+          <t>1) 사전점검 종결회의 및 결과보고서 승인 (9000-9-16) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검 종결보고회(TS) 개최 및 1단계 사전점검 공식 종결 선언을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N17" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\표준서\16_사전점검 종결회의 및 결과보고서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O17" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검 종결회의 안건 브리핑 및 조치 실적 보고
+2) STEP 2: 점검단 최종 의견 수렴 및 사전점검 합격 판정</t>
+        </is>
+      </c>
+      <c r="P17" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\수행지침\16_사전점검 종결회의 및 결과보고서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="163" t="inlineStr">
+        <is>
+          <t>1) 사전점검 종결회의 개최 시방 및 TS 주관 종합 결과 브리핑 기준을 100% 충족하였는가?
+2) 사전점검 종합보고서 서명 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R17" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\16_사전점검 종결회의 및 결과보고서 승인\체크리스트\16_사전점검 종결회의 및 결과보고서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S17" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T17" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U17" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V17" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="147">
+      <c r="A18" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B18" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C18" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D18" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="E18" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-16</t>
+        </is>
+      </c>
+      <c r="F18" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="G18" s="155" t="inlineStr">
+        <is>
+          <t>시설물검증시험 착수보고 및 안전교육</t>
+        </is>
+      </c>
+      <c r="H18" s="169" t="inlineStr">
+        <is>
+          <t>D+185</t>
+        </is>
+      </c>
+      <c r="I18" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J18" s="156" t="inlineStr">
+        <is>
+          <t>2단계 시설물검증시험 착수보고회(TS) 및 시험참여자 전원 특별안전교육</t>
+        </is>
+      </c>
+      <c r="K18" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 착수보고회(TS) 개최 (시설물검증시험 28개 검증 항목(궤도/전기/신호/통신/승강장) 및 30일간의 시험 스케줄을 브리핑합니다.)
+2) STEP 2: 시험 참여 기관사 및 기술요원 특별 안전교육 (선로 내 작업자 통제, 제한속도 엄수, 무선통신 규격, 비상 제동 체결 절차를 집중 교육합니다.)
+3) STEP 3: 시설물검증시험 종합상황실 운영 개시 (차량기지 종합관제실 내에 시운전 종합상황실을 설치하고 실시간 모니터링을 개시합니다.)</t>
+        </is>
+      </c>
+      <c r="L18" s="156" t="inlineStr">
+        <is>
+          <t>시설물검증시험 착수보고 및 안전교육 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M18" s="156" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 착수보고 및 안전교육 (9000-9-17) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 2단계 시설물검증시험 착수보고회(TS) 및 시험참여자 전원 특별안전교육을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N18" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\표준서\17_시설물검증시험 착수보고 및 시험참여자 안전교육_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O18" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 착수보고회(TS) 개최
+2) STEP 2: 시험 참여 기관사 및 기술요원 특별 안전교육</t>
+        </is>
+      </c>
+      <c r="P18" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\수행지침\17_시설물검증시험 착수보고 및 시험참여자 안전교육_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="156" t="inlineStr">
+        <is>
+          <t>1) 시설물검증 착수보고회 시방 및 시험 항목, 일정, 조직 보고 기준을 100% 충족하였는가?
+2) 시험 참여자 안전교육 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R18" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\17_시설물검증시험 착수보고 및 시험참여자 안전교육\체크리스트\17_시설물검증시험 착수보고 및 시험참여자 안전교육_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S18" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T18" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U18" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V18" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="147">
+      <c r="A19" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B19" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C19" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D19" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="E19" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-17</t>
+        </is>
+      </c>
+      <c r="F19" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="G19" s="162" t="inlineStr">
+        <is>
+          <t>시험열차 투입 및 속도별 연동시험</t>
+        </is>
+      </c>
+      <c r="H19" s="174" t="inlineStr">
+        <is>
+          <t>D+190</t>
+        </is>
+      </c>
+      <c r="I19" s="174" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J19" s="163" t="inlineStr">
+        <is>
+          <t>본선 34.4km 시험열차 투입, 속도별(10~70km/h) 28개 항목 시설물 연동 성능 검증</t>
+        </is>
+      </c>
+      <c r="K19" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 속도 단계별 주행시험 계획 및 열차 편성 (10km/h 저속 주행부터 시작하여 30km/h, 50km/h, 설계 최고속도 70km/h까지 단계적으로 증속 주행합니다.)
+2) STEP 2: 28개 핵심 검증 항목 실시간 계측 데이터 취득 (궤도검측(동적 윤중/횡압), 전기(급속충전 아크/전압강하), 신호(ATP 차상 차단), 승차감(가속도계측) 데이터를 수집합니다.)
+3) STEP 3: 비상제동 거리 및 정위치 정차 정밀도 검증 (최고속도 주행 중 비상제동 체결 시 법정 안전거리(160m 이내) 및 정거장 정위치 정차(±300mm)를 100% 입증합니다.)</t>
+        </is>
+      </c>
+      <c r="L19" s="163" t="inlineStr">
+        <is>
+          <t>시험열차 투입 및 속도별 연동시험 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M19" s="163" t="inlineStr">
+        <is>
+          <t>1) 시험열차 투입 및 속도별 연동시험 (9000-9-18) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 본선 34.4km 시험열차 투입, 속도별(10~70km/h) 28개 항목 시설물 연동 성능 검증을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N19" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\표준서\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O19" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 속도 단계별 주행시험 계획 및 열차 편성
+2) STEP 2: 28개 핵심 검증 항목 실시간 계측 데이터 취득</t>
+        </is>
+      </c>
+      <c r="P19" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\수행지침\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="163" t="inlineStr">
+        <is>
+          <t>1) 저속 주행시험(10~30km/h) 시방 및 건축한계, 레일 조인트 통과 기준을 100% 충족하였는가?
+2) 중속 주행시험(30~50km/h) 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R19" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\18_시험열차 투입계획 및 본선 속도별 연동 주행시험\체크리스트\18_시험열차 투입계획 및 본선 속도별 연동 주행시험_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S19" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T19" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U19" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V19" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="147">
+      <c r="A20" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B20" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C20" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D20" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="E20" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-18</t>
+        </is>
+      </c>
+      <c r="F20" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="G20" s="155" t="inlineStr">
+        <is>
+          <t>시설물검증시험 중간점검 및 장애조치</t>
+        </is>
+      </c>
+      <c r="H20" s="169" t="inlineStr">
+        <is>
+          <t>D+195</t>
+        </is>
+      </c>
+      <c r="I20" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J20" s="156" t="inlineStr">
+        <is>
+          <t>시설물검증시험 50% 시점 중간점검, 주행 중 발생 결함 및 데이터 오차 완벽 조치</t>
+        </is>
+      </c>
+      <c r="K20" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 전반부 계측 데이터 종합 평가 (10~50km/h 주행 중 획득된 수십만 건의 계측 센서 데이터를 분석하여 허용 기준치 초과 여부를 검토합니다.)
+2) STEP 2: 도출된 미비점 및 장애 원인 공학적 분석 (곡선부 미세 레일 연마, LTE-R 기지국 지향각 조정, 차상 컴퓨터 소프트웨어 파라미터 튜닝을 실행합니다.)
+3) STEP 3: 보완 항목 재시험 실시 및 중간보고서 승인 (튜닝된 시스템에 대해 70km/h 재주행 시험을 실시하여 완전 무결함을 재확인하고 중간보고서를 작성합니다.)</t>
+        </is>
+      </c>
+      <c r="L20" s="156" t="inlineStr">
+        <is>
+          <t>시설물검증시험 중간점검 및 장애조치 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M20" s="156" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 중간점검 및 장애조치 (9000-9-19) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시설물검증시험 50% 시점 중간점검, 주행 중 발생 결함 및 데이터 오차 완벽 조치을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N20" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\표준서\19_시설물검증시험 중간점검 및 장애조치 회의_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O20" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 전반부 계측 데이터 종합 평가
+2) STEP 2: 도출된 미비점 및 장애 원인 공학적 분석</t>
+        </is>
+      </c>
+      <c r="P20" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\수행지침\19_시설물검증시험 중간점검 및 장애조치 회의_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="156" t="inlineStr">
+        <is>
+          <t>1) 중간 계측 데이터 종합 분석 시방 및 속도별 28개 항목 데이터 검증 기준을 100% 충족하였는가?
+2) 결함 및 이상 징후 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R20" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\19_시설물검증시험 중간점검 및 장애조치 회의\체크리스트\19_시설물검증시험 중간점검 및 장애조치 회의_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S20" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T20" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U20" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V20" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="147">
+      <c r="A21" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B21" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C21" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D21" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="E21" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-19</t>
+        </is>
+      </c>
+      <c r="F21" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="G21" s="162" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결회의 및 결과 승인</t>
+        </is>
+      </c>
+      <c r="H21" s="174" t="inlineStr">
+        <is>
+          <t>D+205</t>
+        </is>
+      </c>
+      <c r="I21" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J21" s="163" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결보고회(TS), 28개 항목 전수 합격 판정 및 결과보고서 승인 획득</t>
+        </is>
+      </c>
+      <c r="K21" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 28개 항목 최종 성적서 집대성 (궤도, 전력, 신호, 통신, 차량, 승강장 인터페이스 전 항목의 공인 시험성적서를 종합 편철합니다.)
+2) STEP 2: TS 주관 시설물검증시험 종결 심의 회의 대응 (TS 심사위원단에 종합 결과를 발표하고 질의응답을 거쳐 '전 항목 적합 판정'을 도출합니다.)
+3) STEP 3: 시설물검증시험 결과보고서 정식 획득 및 다음 단계 진입 (TS 및 국토부로부터 공인 결과보고서 및 영업시운전 착수 승인 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L21" s="163" t="inlineStr">
+        <is>
+          <t>시설물검증시험 종결회의 및 결과 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M21" s="163" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 종결회의 및 결과 승인 (9000-9-20) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 시설물검증시험 종결보고회(TS), 28개 항목 전수 합격 판정 및 결과보고서 승인 획득을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N21" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\표준서\20_시설물검증시험 종결회의 및 결과보고서 획득_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O21" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 시설물검증시험 28개 항목 최종 성적서 집대성
+2) STEP 2: TS 주관 시설물검증시험 종결 심의 회의 대응</t>
+        </is>
+      </c>
+      <c r="P21" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\수행지침\20_시설물검증시험 종결회의 및 결과보고서 획득_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="163" t="inlineStr">
+        <is>
+          <t>1) 시설물검증시험 종결회의 시방 및 TS 주관 최종 결과 심의 기준을 100% 충족하였는가?
+2) 공인 결과보고서 편찬 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R21" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\20_시설물검증시험 종결회의 및 결과보고서 획득\체크리스트\20_시설물검증시험 종결회의 및 결과보고서 획득_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S21" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T21" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U21" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V21" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="147">
+      <c r="A22" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B22" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C22" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D22" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="E22" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-20</t>
+        </is>
+      </c>
+      <c r="F22" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="G22" s="155" t="inlineStr">
+        <is>
+          <t>영업시운전 계획 수립 및 착수보고</t>
+        </is>
+      </c>
+      <c r="H22" s="169" t="inlineStr">
+        <is>
+          <t>D+210</t>
+        </is>
+      </c>
+      <c r="I22" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J22" s="156" t="inlineStr">
+        <is>
+          <t>3단계 영업시운전 계획서 수립, TS 착수보고회 개최 및 실제 영업 다이아 운행 체계 개시</t>
+        </is>
+      </c>
+      <c r="K22" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 실제 영업 다이아(시각표) 및 배차간격 편성 (출퇴근 첨두시간(RH 4분) 및 평시(NH 8분) 배차간격에 맞춘 일일 120회 이상 영업 운행 다이아를 수립합니다.)
+2) STEP 2: 운영사(화성도시공사) 종사자 실전 투입 및 숙달 계획 (트램 기관사, 관제사, 역무원, 유지보수 요원이 실제 개통과 동일한 근무 교대조로 전면 투입됩니다.)
+3) STEP 3: 영업시운전 착수보고회(TS) 개최 및 시험 개시 (TS 및 관할 지자체 관계자가 참석한 착수보고회를 열고 30일간의 영업시운전을 본격 개시합니다.)</t>
+        </is>
+      </c>
+      <c r="L22" s="156" t="inlineStr">
+        <is>
+          <t>영업시운전 계획 수립 및 착수보고 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M22" s="156" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 계획 수립 및 착수보고 (9000-9-21) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 3단계 영업시운전 계획서 수립, TS 착수보고회 개최 및 실제 영업 다이아 운행 체계 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N22" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\표준서\21_영업시운전 계획 수립 및 착수보고(TS)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O22" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 실제 영업 다이아(시각표) 및 배차간격 편성
+2) STEP 2: 운영사(화성도시공사) 종사자 실전 투입 및 숙달 계획</t>
+        </is>
+      </c>
+      <c r="P22" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\수행지침\21_영업시운전 계획 수립 및 착수보고(TS)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="156" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종합계획서 편찬 시방 및 열차다이아, 인력배치, 비상훈련 기준을 100% 충족하였는가?
+2) 영업시운전 착수보고회 개최 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R22" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\21_영업시운전 계획 수립 및 착수보고(TS)\체크리스트\21_영업시운전 계획 수립 및 착수보고(TS)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S22" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T22" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U22" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V22" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="147">
+      <c r="A23" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B23" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C23" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D23" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="E23" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-21</t>
+        </is>
+      </c>
+      <c r="F23" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="G23" s="162" t="inlineStr">
+        <is>
+          <t>영업 다이아 운행 및 비상대응훈련</t>
+        </is>
+      </c>
+      <c r="H23" s="174" t="inlineStr">
+        <is>
+          <t>D+215</t>
+        </is>
+      </c>
+      <c r="I23" s="174" t="inlineStr">
+        <is>
+          <t>화성도시공사</t>
+        </is>
+      </c>
+      <c r="J23" s="163" t="inlineStr">
+        <is>
+          <t>30일간 무사고 영업 다이아 주행(정시율 ≥ 99%), 화재·탈선·단전 8대 비상대응훈련</t>
+        </is>
+      </c>
+      <c r="K23" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 30일간 실전 영업 다이아 연속 무사고 운행 (매일 아침 05:30 첫차부터 익일 00:30 막차까지 실제 운행 시각표에 따라 정속 주행 및 승강장 정차를 수행합니다.)
+2) STEP 2: 열차 운행 정시율(≥ 99%) 및 고장률(Zero) 관리 (출발, 통과, 도착 시각을 1초 단위로 기록하여 정시율 99.0% 이상을 유지하고 장애 발생 시 즉시 원인을 제거합니다.)
+3) STEP 3: 소방·경찰·지자체 합동 8대 비상대응 실전 훈련 (트램 화재 발생 시 승객 비상탈출, 터널 제연팬 가동, 도로 교통사고 연쇄 충돌 등 실전 모의훈련을 완수합니다.)</t>
+        </is>
+      </c>
+      <c r="L23" s="163" t="inlineStr">
+        <is>
+          <t>영업 다이아 운행 및 비상대응훈련 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M23" s="163" t="inlineStr">
+        <is>
+          <t>1) 영업 다이아 운행 및 비상대응훈련 (9000-9-22) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 30일간 무사고 영업 다이아 주행(정시율 ≥ 99%), 화재·탈선·단전 8대 비상대응훈련을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N23" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\표준서\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O23" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 30일간 실전 영업 다이아 연속 무사고 운행
+2) STEP 2: 열차 운행 정시율(≥ 99%) 및 고장률(Zero) 관리</t>
+        </is>
+      </c>
+      <c r="P23" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\수행지침\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="163" t="inlineStr">
+        <is>
+          <t>1) 영업 다이아 연속 운행 시방 및 1일 120회, 30일간 3,600회 주행 기준을 100% 충족하였는가?
+2) 열차 정시율 및 지연 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R23" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련\체크리스트\22_실제 열차운행 다이아 기반 영업시운전 및 비상훈련_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S23" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T23" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U23" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V23" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="147">
+      <c r="A24" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B24" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C24" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D24" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="E24" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-22</t>
+        </is>
+      </c>
+      <c r="F24" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="G24" s="155" t="inlineStr">
+        <is>
+          <t>영업시운전 중간점검 및 조치</t>
+        </is>
+      </c>
+      <c r="H24" s="169" t="inlineStr">
+        <is>
+          <t>D+220</t>
+        </is>
+      </c>
+      <c r="I24" s="169" t="inlineStr">
+        <is>
+          <t>개통운영팀</t>
+        </is>
+      </c>
+      <c r="J24" s="156" t="inlineStr">
+        <is>
+          <t>영업시운전 15일 차 중간점검 회의, 운행 중 발생 이례상황 및 설비 오작동 100% 조치</t>
+        </is>
+      </c>
+      <c r="K24" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 15일간 누적 영업시운전 데이터 종합 분석 (총 1,800회 주행 데이터, 전력 소비 패턴, 정차 시간 준수율, 차내 소음도를 전수 분석합니다.)
+2) STEP 2: 운전 취급 및 승강장 설비 미세 이상 징후 조치 (승하차 도어 센서 민감도 조정, 안내방송 음압 레벨 보정, 교차로 신호 연동 지연시간을 0.1초 단위로 최적화합니다.)
+3) STEP 3: 영업시운전 중간점검 보고서 편찬 및 승인 (조치 결과를 포함한 중간보고서를 TS에 제출하여 후반부 영업시운전의 연속성을 확보합니다.)</t>
+        </is>
+      </c>
+      <c r="L24" s="156" t="inlineStr">
+        <is>
+          <t>영업시운전 중간점검 및 조치 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M24" s="156" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 중간점검 및 조치 (9000-9-23) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 영업시운전 15일 차 중간점검 회의, 운행 중 발생 이례상황 및 설비 오작동 100% 조치을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N24" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\표준서\23_영업시운전 중간점검 및 이례상황 조치결과 검토_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O24" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 15일간 누적 영업시운전 데이터 종합 분석
+2) STEP 2: 운전 취급 및 승강장 설비 미세 이상 징후 조치</t>
+        </is>
+      </c>
+      <c r="P24" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\수행지침\23_영업시운전 중간점검 및 이례상황 조치결과 검토_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="156" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 15일 누적 데이터 분석 시방 및 운행 횟수, 정시율, 전력소비량 기준을 100% 충족하였는가?
+2) 이례상황 및 미세 오류 분석 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R24" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\23_영업시운전 중간점검 및 이례상황 조치결과 검토\체크리스트\23_영업시운전 중간점검 및 이례상황 조치결과 검토_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S24" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T24" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U24" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V24" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="147">
+      <c r="A25" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B25" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C25" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D25" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="E25" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-23</t>
+        </is>
+      </c>
+      <c r="F25" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="G25" s="162" t="inlineStr">
+        <is>
+          <t>영업시운전 종결회의 및 결과보고서 승인</t>
+        </is>
+      </c>
+      <c r="H25" s="174" t="inlineStr">
+        <is>
+          <t>D+225</t>
+        </is>
+      </c>
+      <c r="I25" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J25" s="163" t="inlineStr">
+        <is>
+          <t>영업시운전 최종 종결보고회(TS), 3단계 종합시험운행 전 과정 완벽 합격 판정</t>
+        </is>
+      </c>
+      <c r="K25" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 영업시운전 30일간 전 운행 실적 종합 집계 (총 주행거리, 정시 운행률, 비상훈련 성과, 종사자 직무 평가표를 집대성한 결과보고서를 편찬합니다.)
+2) STEP 2: TS 합동 영업시운전 종결 심의 회의 대응 (TS 및 전문가 심사위원단의 최종 심의를 거쳐 '동탄트램 영업시운전 무결점 합격'을 공식 의결합니다.)
+3) STEP 3: 영업시운전 결과보고서 승인 및 종결 선언 (국토부 및 TS로부터 공인 영업시운전 결과보고서를 수령하고 3단계 종합시험운행의 공식 종결을 선포합니다.)</t>
+        </is>
+      </c>
+      <c r="L25" s="163" t="inlineStr">
+        <is>
+          <t>영업시운전 종결회의 및 결과보고서 승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M25" s="163" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종결회의 및 결과보고서 승인 (9000-9-24) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 영업시운전 최종 종결보고회(TS), 3단계 종합시험운행 전 과정 완벽 합격 판정을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N25" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\표준서\24_영업시운전 종결회의 및 결과보고서 승인_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O25" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 영업시운전 30일간 전 운행 실적 종합 집계
+2) STEP 2: TS 합동 영업시운전 종결 심의 회의 대응</t>
+        </is>
+      </c>
+      <c r="P25" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\수행지침\24_영업시운전 종결회의 및 결과보고서 승인_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="163" t="inlineStr">
+        <is>
+          <t>1) 영업시운전 종결회의 개최 시방 및 TS 주관 종합 평가 보고 기준을 100% 충족하였는가?
+2) 영업시운전 결과보고서 편찬 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R25" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\24_영업시운전 종결회의 및 결과보고서 승인\체크리스트\24_영업시운전 종결회의 및 결과보고서 승인_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S25" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T25" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U25" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V25" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="147">
+      <c r="A26" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B26" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C26" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D26" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="E26" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-24</t>
+        </is>
+      </c>
+      <c r="F26" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="G26" s="155" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합결과보고서 제출</t>
+        </is>
+      </c>
+      <c r="H26" s="169" t="inlineStr">
+        <is>
+          <t>D+230</t>
+        </is>
+      </c>
+      <c r="I26" s="169" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J26" s="156" t="inlineStr">
+        <is>
+          <t>사전점검·시설물검증·영업시운전 3단계 총괄 종합결과보고서 국토교통부 제출</t>
+        </is>
+      </c>
+      <c r="K26" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검·시설물검증·영업시운전 성과 종합 편철 (3단계 전 시험 과정의 측정 데이터, 사진대지, 필증, TS 합격증명서를 마스터 종합보고서로 바인딩합니다.)
+2) STEP 2: 총괄사업단장 및 책임감리원 최종 서명 날인 (발주처, 감리단, 시공사 3자 대표자가 서명 날인하여 기술적 무결성을 최종 보증합니다.)
+3) STEP 3: 국토교통부 정식 제출 및 정부 적합 승인 통보 수령 (국토교통부에 정식 공문으로 접수하고 최종 '철도종합시험운행 적합 승인' 공문을 수령합니다.)</t>
+        </is>
+      </c>
+      <c r="L26" s="156" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 종합결과보고서 제출 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M26" s="156" t="inlineStr">
+        <is>
+          <t>1) 철도종합시험운행 종합결과보고서 제출 (9000-9-25) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 사전점검·시설물검증·영업시운전 3단계 총괄 종합결과보고서 국토교통부 제출을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N26" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\표준서\25_철도종합시험운행 종합결과보고서 작성 및 제출_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O26" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 사전점검·시설물검증·영업시운전 성과 종합 편철
+2) STEP 2: 총괄사업단장 및 책임감리원 최종 서명 날인</t>
+        </is>
+      </c>
+      <c r="P26" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\수행지침\25_철도종합시험운행 종합결과보고서 작성 및 제출_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="156" t="inlineStr">
+        <is>
+          <t>1) 3단계 종합결과보고서 편찬 시방 및 사전점검+시설물검증+영업시운전 기준을 100% 충족하였는가?
+2) 사업단장 및 책임감리원 서명 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R26" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\25_철도종합시험운행 종합결과보고서 작성 및 제출\체크리스트\25_철도종합시험운행 종합결과보고서 작성 및 제출_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S26" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T26" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U26" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V26" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="147">
+      <c r="A27" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B27" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C27" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D27" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="E27" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-25</t>
+        </is>
+      </c>
+      <c r="F27" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="G27" s="162" t="inlineStr">
+        <is>
+          <t>철도운영자 안전관리체계 변경승인</t>
+        </is>
+      </c>
+      <c r="H27" s="174" t="inlineStr">
+        <is>
+          <t>D+235</t>
+        </is>
+      </c>
+      <c r="I27" s="174" t="inlineStr">
+        <is>
+          <t>화성도시공사</t>
+        </is>
+      </c>
+      <c r="J27" s="163" t="inlineStr">
+        <is>
+          <t>화성도시공사(철도운영자) 철도안전관리체계 변경승인 신청 및 TS 현장 검사 합격</t>
+        </is>
+      </c>
+      <c r="K27" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도안전관리체계 변경승인 신청 서류 작성 (안전경영 목표, 철도비상대응계획, 철도종사자 자격관리, 시설 및 차량 유지관리 규정 42종을 편찬합니다.)
+2) STEP 2: 한국교통안전공단(TS) 현장 실사 수검 (TS 심사위원단의 현장 실사 시 화성도시공사의 관제, 운전, 유지보수 조직의 실질적 이행 능력을 입증합니다.)
+3) STEP 3: 국토교통부 철도안전관리체계 변경승인증명서 획득 (국토교통부 장관 명의의 정식 승인증명서를 획득하여 영업 개통을 위한 법적 자격을 100% 완비합니다.)</t>
+        </is>
+      </c>
+      <c r="L27" s="163" t="inlineStr">
+        <is>
+          <t>철도운영자 안전관리체계 변경승인 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M27" s="163" t="inlineStr">
+        <is>
+          <t>1) 철도운영자 안전관리체계 변경승인 (9000-9-26) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 화성도시공사(철도운영자) 철도안전관리체계 변경승인 신청 및 TS 현장 검사 합격을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N27" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\표준서\26_철도운영자 안전관리체계 변경승인(TS)_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O27" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 철도안전관리체계 변경승인 신청 서류 작성
+2) STEP 2: 한국교통안전공단(TS) 현장 실사 수검</t>
+        </is>
+      </c>
+      <c r="P27" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\수행지침\26_철도운영자 안전관리체계 변경승인(TS)_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="163" t="inlineStr">
+        <is>
+          <t>1) 안전관리체계 변경승인 신청서 제출 시방 및 국토교통부 및 TS 기준을 100% 충족하였는가?
+2) TS 안전관리체계 현장 실사 대응 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R27" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\26_철도운영자 안전관리체계 변경승인(TS)\체크리스트\26_철도운영자 안전관리체계 변경승인(TS)_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S27" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T27" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U27" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V27" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="147">
+      <c r="A28" s="168" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B28" s="168" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C28" s="168" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D28" s="168" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="E28" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-26</t>
+        </is>
+      </c>
+      <c r="F28" s="169" t="inlineStr">
+        <is>
+          <t>9000-9-28</t>
+        </is>
+      </c>
+      <c r="G28" s="155" t="inlineStr">
+        <is>
+          <t>공사목적물 및 시설물 최종 인수인계</t>
+        </is>
+      </c>
+      <c r="H28" s="169" t="inlineStr">
+        <is>
+          <t>D+238</t>
+        </is>
+      </c>
+      <c r="I28" s="169" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J28" s="156" t="inlineStr">
+        <is>
+          <t>36개 정거장, 본선, 차량기지 시설물 및 2D/3D 준공도서·예비품 화성도시공사 합동 인수인계</t>
+        </is>
+      </c>
+      <c r="K28" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 역사 및 시설물 합동 정밀 인수인계 실사 (건축 마감, 기계 배관, 전기 수전반, 신호 기계실, 궤도 레일의 상태를 합동 점검하고 인수인계 목록을 작성합니다.)
+2) STEP 2: 준공도서, 운용 매뉴얼 및 유지보수 예비품 인계 (3D BIM 기반 As-Built 최종 준공도면, 장비별 정비 지침서 및 2년분 유지보수 예비품을 운영사에 공식 전달합니다.)
+3) STEP 3: 공사목적물 인수인계서 최종 체결 (화성시, 화성도시공사, 시공사업단 3자 대표자가 서명 날인하여 시설물 관리권을 공식 이관합니다.)</t>
+        </is>
+      </c>
+      <c r="L28" s="156" t="inlineStr">
+        <is>
+          <t>공사목적물 및 시설물 최종 인수인계 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M28" s="156" t="inlineStr">
+        <is>
+          <t>1) 공사목적물 및 시설물 최종 인수인계 (9000-9-27) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 36개 정거장, 본선, 차량기지 시설물 및 2D/3D 준공도서·예비품 화성도시공사 합동 인수인계을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N28" s="170">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\표준서\27_공사목적물 및 시설물 운영사 최종 인수인계_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O28" s="156" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 전 역사 및 시설물 합동 정밀 인수인계 실사
+2) STEP 2: 준공도서, 운용 매뉴얼 및 유지보수 예비품 인계</t>
+        </is>
+      </c>
+      <c r="P28" s="171">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\수행지침\27_공사목적물 및 시설물 운영사 최종 인수인계_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="156" t="inlineStr">
+        <is>
+          <t>1) 시설물 합동 실사 및 검측 시방 및 전 역사/차량기지/변전소 실사 기준을 100% 충족하였는가?
+2) 준공도서 및 매뉴얼 인계 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R28" s="172">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\27_공사목적물 및 시설물 운영사 최종 인수인계\체크리스트\27_공사목적물 및 시설물 운영사 최종 인수인계_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S28" s="169" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T28" s="156" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U28" s="168" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V28" s="156" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="147">
+      <c r="A29" s="173" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B29" s="173" t="inlineStr">
+        <is>
+          <t>9000-9</t>
+        </is>
+      </c>
+      <c r="C29" s="173" t="inlineStr">
+        <is>
+          <t>철도종합시험운행</t>
+        </is>
+      </c>
+      <c r="D29" s="173" t="inlineStr">
+        <is>
+          <t>9000-9-28</t>
+        </is>
+      </c>
+      <c r="E29" s="174" t="inlineStr">
+        <is>
+          <t>9000-9-27</t>
+        </is>
+      </c>
+      <c r="F29" s="174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="162" t="inlineStr">
+        <is>
+          <t>종합시험운행 종결 및 영업 개통</t>
+        </is>
+      </c>
+      <c r="H29" s="174" t="inlineStr">
+        <is>
+          <t>D+240</t>
+        </is>
+      </c>
+      <c r="I29" s="174" t="inlineStr">
+        <is>
+          <t>시공사업단</t>
+        </is>
+      </c>
+      <c r="J29" s="163" t="inlineStr">
+        <is>
+          <t>국토교통부 영업개통 승인 획득, 동탄트램 공식 개통식 거행 및 대시민 상업운전 개시</t>
+        </is>
+      </c>
+      <c r="K29" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 국토교통부 영업개통 최종 승인 공문 접수 (철도종합시험운행 및 안전관리체계 승인 성과를 바탕으로 국토교통부 장관의 정식 '영업개통 승인'을 수령합니다.)
+2) STEP 2: 동탄도시철도 개통 기념식 및 테이프 커팅 (화성시장, 국회의원, 시민대표, 사업단 관계자가 참석한 가운데 개통식을 개최하고 1호 열차 시승을 진행합니다.)
+3) STEP 3: 동탄트램 1·2호선 전 구간 대시민 상업운전 개시 (34.4km 36개 정거장 전 노선에서 시민 탑승 상업운전을 시작하여 동탄 트램 프로젝트를 성공적으로 완수합니다.)</t>
+        </is>
+      </c>
+      <c r="L29" s="163" t="inlineStr">
+        <is>
+          <t>종합시험운행 종결 및 영업 개통 결과보고서, 회의록 및 TS 공인 필증</t>
+        </is>
+      </c>
+      <c r="M29" s="163" t="inlineStr">
+        <is>
+          <t>1) 종합시험운행 종결 및 영업 개통 (9000-9-28) 업무 달성을 위해 철도안전법 제38조 및 국토부 시행지침을 100% 충족한다.
+2) 국토교통부 영업개통 승인 획득, 동탄트램 공식 개통식 거행 및 대시민 상업운전 개시을 엄격히 완수하여 국토교통부/TS 승인을 획득한다.</t>
+        </is>
+      </c>
+      <c r="N29" s="175">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\표준서\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_표준서.html", "👉 [클릭] 표준서 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="O29" s="163" t="inlineStr">
+        <is>
+          <t>1) STEP 1: 국토교통부 영업개통 최종 승인 공문 접수
+2) STEP 2: 동탄도시철도 개통 기념식 및 테이프 커팅</t>
+        </is>
+      </c>
+      <c r="P29" s="176">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\수행지침\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_수행지침.html", "👉 [클릭] 수행지침 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="163" t="inlineStr">
+        <is>
+          <t>1) 국토교통부 영업개통 승인 신청 시방 및 종합결과보고서 및 안전관리체계 기준을 100% 충족하였는가?
+2) 국토교통부 영업개통 정식 승인 검측 및 불합격 요소를 전면 차단하였는가?</t>
+        </is>
+      </c>
+      <c r="R29" s="177">
+        <f>HYPERLINK(LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)&amp;"매뉴얼BODY(집행단계-첨부폴더)v8\11.철도종합시운전\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통\체크리스트\28_동탄도시철도(트램) 종합시험운행 종결 및 영업 개통_체크리스트.html", "👉 [클릭] 체크리스트 열기 📄")</f>
+        <v/>
+      </c>
+      <c r="S29" s="174" t="inlineStr">
+        <is>
+          <t>철도종합시험운행 시행지침 준수</t>
+        </is>
+      </c>
+      <c r="T29" s="163" t="inlineStr">
+        <is>
+          <t>● 철도안전법 제38조, 동법 시행규칙 제75조 및 국토부 철도종합시험운행 시행지침 100% 준수</t>
+        </is>
+      </c>
+      <c r="U29" s="173" t="inlineStr">
+        <is>
+          <t>1) 👉 [더블클릭] 체크리스트 열기 📄</t>
+        </is>
+      </c>
+      <c r="V29" s="163" t="inlineStr">
+        <is>
+          <t>한국교통안전공단(TS), 국가철도공단 및 철도종합시운전 기술자문단 상시 운영</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
